--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22177AA9-6348-7E4B-B265-97D0B41CFCC0}"/>
+  <xr:revisionPtr revIDLastSave="340" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F4DF43-E9A5-0B46-9A53-DCFB40E9D98C}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="1720" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2780" yWindow="1020" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Public Health Emergencies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="55" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="903">
   <si>
     <t>start</t>
   </si>
@@ -2413,6 +2413,339 @@
   </si>
   <si>
     <t>VHT</t>
+  </si>
+  <si>
+    <t>Tool 8: Preparedness Assessment Tool</t>
+  </si>
+  <si>
+    <t>Mbuya1</t>
+  </si>
+  <si>
+    <t>The misinformation is that the outbreaks are brought in the during election times.</t>
+  </si>
+  <si>
+    <t>There just a few hand washing equipment in the school .</t>
+  </si>
+  <si>
+    <t>There is need for sensitization and also more hand washing equipment is needed</t>
+  </si>
+  <si>
+    <t>Mbuya C/U primary school</t>
+  </si>
+  <si>
+    <t>2daabf8b-42b3-426c-894a-9e647486cef9</t>
+  </si>
+  <si>
+    <t>uuid:2daabf8b-42b3-426c-894a-9e647486cef9</t>
+  </si>
+  <si>
+    <t>Sekiboobo Primary School</t>
+  </si>
+  <si>
+    <t>Misinformation - Some pupils were thinking that the normal diarrhea is also Ebola. Seeing someone frequenting the toilet would make them think that that person is an Ebola suspect. 2. They thought that mpox is chicken or small pox. Question. They wanted to know when we are going to go back because the information that we shared with them was very educative.</t>
+  </si>
+  <si>
+    <t>They have no IEC material and very few hand washing facilities.</t>
+  </si>
+  <si>
+    <t>Immagination because most of them have not got the chance to have this sensitization programs</t>
+  </si>
+  <si>
+    <t>The health club that we formed will be able to share information with the rest of the school.</t>
+  </si>
+  <si>
+    <t>580fed86-d4b9-4010-8fc4-1435c7f55ea2</t>
+  </si>
+  <si>
+    <t>uuid:580fed86-d4b9-4010-8fc4-1435c7f55ea2</t>
+  </si>
+  <si>
+    <t>Can the ministry of health avail us with Ebola posters?</t>
+  </si>
+  <si>
+    <t>The fear of high-water bills makes them reduce on the water supply in the hand washing facilities</t>
+  </si>
+  <si>
+    <t>Having a sensitization onduct sensitization for teachers and students on hygiene / having an isolation protocol.</t>
+  </si>
+  <si>
+    <t>The vector breeding sites are not found near food points</t>
+  </si>
+  <si>
+    <t>It is observed that the school is spacious enough but they dont have hand washing facilities. And the sanitation of the school is okay, however, when it comes to the condition of the toilet stances, its worrying</t>
+  </si>
+  <si>
+    <t>The school has no school nurse.</t>
+  </si>
+  <si>
+    <t>a2dc90d5-3fb4-4545-ab28-224820f82bac</t>
+  </si>
+  <si>
+    <t>uuid:a2dc90d5-3fb4-4545-ab28-224820f82bac</t>
+  </si>
+  <si>
+    <t>Community Gatekeeper Dialogue</t>
+  </si>
+  <si>
+    <t>seeta</t>
+  </si>
+  <si>
+    <t>LYNN</t>
+  </si>
+  <si>
+    <t>He promised to always remind the learners to was hands with water and soap. He also romised to make sure that the facilities have water and soap for the learners to wash their hand</t>
+  </si>
+  <si>
+    <t>Mpox is from witchcraft or a curse. Herbs, or steaming can cure Mpox</t>
+  </si>
+  <si>
+    <t>Belief that disease is caused by witchcraft or curse, and belief that herbs and steaming can cure it. Low knowledge on cause and treatment of mpox and fear of going to health facility.</t>
+  </si>
+  <si>
+    <t>community members, friends and family members</t>
+  </si>
+  <si>
+    <t>Conduct community sensitization sessions in schools to clarify that mpox is caused by a virus not witchcraft or a curse. Explain that it spreads through close contact, bedding and clothing</t>
+  </si>
+  <si>
+    <t>14bf9de0-4f89-4006-bd32-4540fe47774c</t>
+  </si>
+  <si>
+    <t>uuid:14bf9de0-4f89-4006-bd32-4540fe47774c</t>
+  </si>
+  <si>
+    <t>mukono central</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Vhts and Ureporters</t>
+  </si>
+  <si>
+    <t>They promised to sensitize the community and share required information about the public health emergencies.</t>
+  </si>
+  <si>
+    <t>Ebola is a government business to get money.Rumor, misinformation or question flagged: Ebola spreads through air and through school children</t>
+  </si>
+  <si>
+    <t>Deep mistrust in government and health system, low knowledge on Ebola cause, fear and anxiety due to past outbreaks. Limited knowledge on how Ebola spreads, fear and stigma leading to children being isolated.</t>
+  </si>
+  <si>
+    <t>Community members and boda riders during community dialogue at trading center. Parents and pupils during school listening session at primary school.</t>
+  </si>
+  <si>
+    <t>Conduct community dialogue meetings to build trust, explain that Ebola is a real virus that kills, clarify that government and partners provide free care to save lives not to make money. Encourage early reporting to VHT or health facility</t>
+  </si>
+  <si>
+    <t>bdb8ffaf-dd23-4463-8375-16a15afeecf2</t>
+  </si>
+  <si>
+    <t>uuid:bdb8ffaf-dd23-4463-8375-16a15afeecf2</t>
+  </si>
+  <si>
+    <t>Some Boda boda riders</t>
+  </si>
+  <si>
+    <t>Improvement of wash in the market</t>
+  </si>
+  <si>
+    <t>The place is not so clean</t>
+  </si>
+  <si>
+    <t>Market vendors are so close to each other</t>
+  </si>
+  <si>
+    <t>The market head only received orientation on mpox</t>
+  </si>
+  <si>
+    <t>12096547-0f8e-45ab-acdc-2e0c8bc56326</t>
+  </si>
+  <si>
+    <t>uuid:12096547-0f8e-45ab-acdc-2e0c8bc56326</t>
+  </si>
+  <si>
+    <t>Is mpox still a threat</t>
+  </si>
+  <si>
+    <t>Improvement of sanitation in the market</t>
+  </si>
+  <si>
+    <t>It's clean and ok</t>
+  </si>
+  <si>
+    <t>Since it's a market, congestion is always high.</t>
+  </si>
+  <si>
+    <t>,6</t>
+  </si>
+  <si>
+    <t>c80d483c-3e1a-4286-bf39-31e921aa1d53</t>
+  </si>
+  <si>
+    <t>uuid:c80d483c-3e1a-4286-bf39-31e921aa1d53</t>
+  </si>
+  <si>
+    <t>Ebola was used to get money from the donors</t>
+  </si>
+  <si>
+    <t>Market is highly populated and there is no hand washing equipment</t>
+  </si>
+  <si>
+    <t>From the community especially Nansana</t>
+  </si>
+  <si>
+    <t>Should put in place hand washing equipment</t>
+  </si>
+  <si>
+    <t>Some water trenches near food point</t>
+  </si>
+  <si>
+    <t>Busy market, but no hand washing</t>
+  </si>
+  <si>
+    <t>4 stances for 230 people</t>
+  </si>
+  <si>
+    <t>Yes by VHT</t>
+  </si>
+  <si>
+    <t>54b52051-7e70-4b9a-86ae-a9f4b877a41e</t>
+  </si>
+  <si>
+    <t>uuid:54b52051-7e70-4b9a-86ae-a9f4b877a41e</t>
+  </si>
+  <si>
+    <t>Nakasero Primary School</t>
+  </si>
+  <si>
+    <t>That wearing a mask helps prevent  Ebola  ,</t>
+  </si>
+  <si>
+    <t>Have heard it everywhere</t>
+  </si>
+  <si>
+    <t>The school sick bay only has deworming tablets, we have.asked them to get a first aid kit, there was no soap at the hand washing points we have asked them to provide it</t>
+  </si>
+  <si>
+    <t>476bbf53-08d0-4701-9145-f412f901f45c</t>
+  </si>
+  <si>
+    <t>uuid:476bbf53-08d0-4701-9145-f412f901f45c</t>
+  </si>
+  <si>
+    <t>Nsambya centra</t>
+  </si>
+  <si>
+    <t>Is MPox still there,  how come we have never  seen someone  die from ebola</t>
+  </si>
+  <si>
+    <t>Misinformation  present amongst</t>
+  </si>
+  <si>
+    <t>No vector breeding  sites at the different  points</t>
+  </si>
+  <si>
+    <t>Congestion is only in classes and canteens</t>
+  </si>
+  <si>
+    <t>20:800</t>
+  </si>
+  <si>
+    <t>Sanitation officer was trained</t>
+  </si>
+  <si>
+    <t>5a2d80eb-14e9-43d1-9257-a08dc61f1c34</t>
+  </si>
+  <si>
+    <t>uuid:5a2d80eb-14e9-43d1-9257-a08dc61f1c34</t>
+  </si>
+  <si>
+    <t>Wearing a mask prevents Ebola</t>
+  </si>
+  <si>
+    <t>General conversations</t>
+  </si>
+  <si>
+    <t>Have corrected the misinformation</t>
+  </si>
+  <si>
+    <t>3900ff0f-c118-47b3-9c59-4d778b2dcb68</t>
+  </si>
+  <si>
+    <t>uuid:3900ff0f-c118-47b3-9c59-4d778b2dcb68</t>
+  </si>
+  <si>
+    <t>Re address the misinformation</t>
+  </si>
+  <si>
+    <t>No dedicated waste bins</t>
+  </si>
+  <si>
+    <t>Torn Outdated posters</t>
+  </si>
+  <si>
+    <t>68604db0-f70b-420a-9287-6d7031e8d231</t>
+  </si>
+  <si>
+    <t>uuid:68604db0-f70b-420a-9287-6d7031e8d231</t>
+  </si>
+  <si>
+    <t>The food point was not properly cleaned</t>
+  </si>
+  <si>
+    <t>It is a very big number of pupils with limited resources ie the school has no water because of the accumulated water bills that government has not paid NWSC disconnected them</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>609afc30-11cc-49b6-9417-b94dc8620ae8</t>
+  </si>
+  <si>
+    <t>uuid:609afc30-11cc-49b6-9417-b94dc8620ae8</t>
+  </si>
+  <si>
+    <t>Nakasero 3</t>
+  </si>
+  <si>
+    <t>Buganda Rd Primary</t>
+  </si>
+  <si>
+    <t>To activate the clubs and use the members as ambassadors to their classmates and in the community</t>
+  </si>
+  <si>
+    <t>79575f33-0c52-4974-be0a-1fb9fd4eec54</t>
+  </si>
+  <si>
+    <t>uuid:79575f33-0c52-4974-be0a-1fb9fd4eec54</t>
+  </si>
+  <si>
+    <t>Cause of cholera</t>
+  </si>
+  <si>
+    <t>Cleared</t>
+  </si>
+  <si>
+    <t>The classes are full social distancing is not possible</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>a53b26e6-426b-47d4-9a36-290c5ab1f649</t>
+  </si>
+  <si>
+    <t>uuid:a53b26e6-426b-47d4-9a36-290c5ab1f649</t>
+  </si>
+  <si>
+    <t>Sensitization</t>
+  </si>
+  <si>
+    <t>5014bcf7-1e4f-4ba7-b488-19f9cf008735</t>
+  </si>
+  <si>
+    <t>uuid:5014bcf7-1e4f-4ba7-b488-19f9cf008735</t>
   </si>
 </sst>
 </file>
@@ -16461,7 +16794,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -16811,8 +17144,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:HF72" totalsRowShown="0">
-  <autoFilter ref="A1:HF72" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:HF88" totalsRowShown="0">
+  <autoFilter ref="A1:HF88" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="214">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="8"/>
@@ -17320,7 +17653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:HF72"/>
+  <dimension ref="A1:HF88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -26235,6 +26568,1860 @@
         <v>71</v>
       </c>
     </row>
+    <row r="73" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>46290.410415590282</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46290.431642719908</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D73" t="s">
+        <v>792</v>
+      </c>
+      <c r="E73" t="s">
+        <v>196</v>
+      </c>
+      <c r="F73" t="s">
+        <v>793</v>
+      </c>
+      <c r="G73" t="s">
+        <v>198</v>
+      </c>
+      <c r="H73" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ73" t="s">
+        <v>794</v>
+      </c>
+      <c r="AK73" t="s">
+        <v>795</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM73" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>796</v>
+      </c>
+      <c r="EY73" s="1"/>
+      <c r="EZ73" s="1">
+        <v>46290</v>
+      </c>
+      <c r="FA73" t="s">
+        <v>797</v>
+      </c>
+      <c r="FB73" t="s">
+        <v>416</v>
+      </c>
+      <c r="FD73">
+        <v>420</v>
+      </c>
+      <c r="FE73">
+        <v>450</v>
+      </c>
+      <c r="FF73">
+        <v>4</v>
+      </c>
+      <c r="FG73">
+        <v>17</v>
+      </c>
+      <c r="FH73" t="s">
+        <v>395</v>
+      </c>
+      <c r="FI73" t="s">
+        <v>426</v>
+      </c>
+      <c r="FJ73" t="s">
+        <v>427</v>
+      </c>
+      <c r="FK73" t="s">
+        <v>508</v>
+      </c>
+      <c r="FL73" t="s">
+        <v>428</v>
+      </c>
+      <c r="FN73" t="s">
+        <v>429</v>
+      </c>
+      <c r="FO73">
+        <v>4</v>
+      </c>
+      <c r="FP73" t="s">
+        <v>515</v>
+      </c>
+      <c r="FQ73" t="s">
+        <v>418</v>
+      </c>
+      <c r="FR73">
+        <v>15</v>
+      </c>
+      <c r="FS73">
+        <v>13</v>
+      </c>
+      <c r="FT73" t="s">
+        <v>383</v>
+      </c>
+      <c r="FU73" t="s">
+        <v>384</v>
+      </c>
+      <c r="FV73" t="s">
+        <v>420</v>
+      </c>
+      <c r="FW73">
+        <v>1</v>
+      </c>
+      <c r="FX73">
+        <v>1</v>
+      </c>
+      <c r="FY73">
+        <v>0</v>
+      </c>
+      <c r="FZ73">
+        <v>0</v>
+      </c>
+      <c r="GA73" t="s">
+        <v>395</v>
+      </c>
+      <c r="GC73">
+        <v>4</v>
+      </c>
+      <c r="GD73">
+        <v>3</v>
+      </c>
+      <c r="GE73">
+        <v>7</v>
+      </c>
+      <c r="GF73">
+        <v>10</v>
+      </c>
+      <c r="GG73">
+        <v>8</v>
+      </c>
+      <c r="GH73">
+        <v>7</v>
+      </c>
+      <c r="GQ73" s="1"/>
+      <c r="GR73" s="1"/>
+      <c r="GX73">
+        <v>877981855</v>
+      </c>
+      <c r="GY73" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="GZ73" s="1">
+        <v>46290.306643518517</v>
+      </c>
+      <c r="HA73" s="1"/>
+      <c r="HB73" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD73" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE73" t="s">
+        <v>799</v>
+      </c>
+      <c r="HF73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>46254.660598761577</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46290.505174305552</v>
+      </c>
+      <c r="C74" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D74" t="s">
+        <v>691</v>
+      </c>
+      <c r="E74" t="s">
+        <v>309</v>
+      </c>
+      <c r="F74" t="s">
+        <v>609</v>
+      </c>
+      <c r="G74" t="s">
+        <v>198</v>
+      </c>
+      <c r="H74" t="s">
+        <v>311</v>
+      </c>
+      <c r="J74" t="s">
+        <v>800</v>
+      </c>
+      <c r="K74" t="s">
+        <v>201</v>
+      </c>
+      <c r="L74">
+        <v>640</v>
+      </c>
+      <c r="M74">
+        <v>25</v>
+      </c>
+      <c r="N74">
+        <v>60</v>
+      </c>
+      <c r="O74">
+        <v>2</v>
+      </c>
+      <c r="P74">
+        <v>2</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74" t="s">
+        <v>340</v>
+      </c>
+      <c r="T74" t="s">
+        <v>341</v>
+      </c>
+      <c r="U74" t="s">
+        <v>203</v>
+      </c>
+      <c r="V74" t="s">
+        <v>216</v>
+      </c>
+      <c r="W74" t="s">
+        <v>203</v>
+      </c>
+      <c r="X74" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ74" t="s">
+        <v>801</v>
+      </c>
+      <c r="AK74" t="s">
+        <v>802</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>803</v>
+      </c>
+      <c r="AM74" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>804</v>
+      </c>
+      <c r="EY74" s="1"/>
+      <c r="GQ74" s="1"/>
+      <c r="GR74" s="1"/>
+      <c r="GX74">
+        <v>878077912</v>
+      </c>
+      <c r="GY74" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="GZ74" s="1">
+        <v>46290.380185185182</v>
+      </c>
+      <c r="HA74" s="1"/>
+      <c r="HB74" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD74" t="s">
+        <v>537</v>
+      </c>
+      <c r="HE74" t="s">
+        <v>806</v>
+      </c>
+      <c r="HF74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>46290.505176122693</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46290.517313263888</v>
+      </c>
+      <c r="C75" s="1">
+        <v>46289</v>
+      </c>
+      <c r="D75" t="s">
+        <v>354</v>
+      </c>
+      <c r="E75" t="s">
+        <v>309</v>
+      </c>
+      <c r="F75" t="s">
+        <v>609</v>
+      </c>
+      <c r="G75" t="s">
+        <v>198</v>
+      </c>
+      <c r="H75" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ75" t="s">
+        <v>807</v>
+      </c>
+      <c r="AK75" t="s">
+        <v>808</v>
+      </c>
+      <c r="AM75" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>809</v>
+      </c>
+      <c r="AO75" t="s">
+        <v>359</v>
+      </c>
+      <c r="AR75" t="s">
+        <v>404</v>
+      </c>
+      <c r="AS75">
+        <v>2</v>
+      </c>
+      <c r="AT75">
+        <v>6</v>
+      </c>
+      <c r="AU75" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>810</v>
+      </c>
+      <c r="AW75" t="s">
+        <v>392</v>
+      </c>
+      <c r="AX75" t="s">
+        <v>811</v>
+      </c>
+      <c r="AY75" t="s">
+        <v>465</v>
+      </c>
+      <c r="BA75" t="s">
+        <v>737</v>
+      </c>
+      <c r="BB75" t="s">
+        <v>655</v>
+      </c>
+      <c r="BC75" t="s">
+        <v>467</v>
+      </c>
+      <c r="EY75" s="1"/>
+      <c r="GO75" t="s">
+        <v>812</v>
+      </c>
+      <c r="GQ75" s="1"/>
+      <c r="GR75" s="1"/>
+      <c r="GX75">
+        <v>878093353</v>
+      </c>
+      <c r="GY75" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="GZ75" s="1">
+        <v>46290.392337962963</v>
+      </c>
+      <c r="HA75" s="1"/>
+      <c r="HB75" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD75" t="s">
+        <v>537</v>
+      </c>
+      <c r="HE75" t="s">
+        <v>814</v>
+      </c>
+      <c r="HF75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>46290.51731476852</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46290.545699201393</v>
+      </c>
+      <c r="C76" s="1">
+        <v>46289</v>
+      </c>
+      <c r="D76" t="s">
+        <v>815</v>
+      </c>
+      <c r="E76" t="s">
+        <v>309</v>
+      </c>
+      <c r="F76" t="s">
+        <v>816</v>
+      </c>
+      <c r="G76" t="s">
+        <v>198</v>
+      </c>
+      <c r="H76" t="s">
+        <v>817</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB76">
+        <v>1</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>395</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>818</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>326</v>
+      </c>
+      <c r="AG76" t="s">
+        <v>327</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>395</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>819</v>
+      </c>
+      <c r="AK76" t="s">
+        <v>820</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>821</v>
+      </c>
+      <c r="AM76" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>822</v>
+      </c>
+      <c r="EY76" s="1"/>
+      <c r="GQ76" s="1"/>
+      <c r="GR76" s="1"/>
+      <c r="GX76">
+        <v>878131979</v>
+      </c>
+      <c r="GY76" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="GZ76" s="1">
+        <v>46290.420740740738</v>
+      </c>
+      <c r="HA76" s="1"/>
+      <c r="HB76" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD76" t="s">
+        <v>537</v>
+      </c>
+      <c r="HE76" t="s">
+        <v>824</v>
+      </c>
+      <c r="HF76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>46290.545700763891</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46290.584407488423</v>
+      </c>
+      <c r="C77" s="1">
+        <v>46289</v>
+      </c>
+      <c r="D77" t="s">
+        <v>815</v>
+      </c>
+      <c r="E77" t="s">
+        <v>309</v>
+      </c>
+      <c r="F77" t="s">
+        <v>825</v>
+      </c>
+      <c r="G77" t="s">
+        <v>198</v>
+      </c>
+      <c r="H77" t="s">
+        <v>311</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>826</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>827</v>
+      </c>
+      <c r="AB77">
+        <v>1</v>
+      </c>
+      <c r="AC77">
+        <v>4</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>395</v>
+      </c>
+      <c r="AE77" t="s">
+        <v>828</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>687</v>
+      </c>
+      <c r="AG77" t="s">
+        <v>326</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>395</v>
+      </c>
+      <c r="AJ77" t="s">
+        <v>829</v>
+      </c>
+      <c r="AK77" t="s">
+        <v>830</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>831</v>
+      </c>
+      <c r="AM77" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>832</v>
+      </c>
+      <c r="EY77" s="1"/>
+      <c r="GQ77" s="1"/>
+      <c r="GR77" s="1"/>
+      <c r="GX77">
+        <v>878181645</v>
+      </c>
+      <c r="GY77" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="GZ77" s="1">
+        <v>46290.459421296298</v>
+      </c>
+      <c r="HA77" s="1"/>
+      <c r="HB77" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD77" t="s">
+        <v>537</v>
+      </c>
+      <c r="HE77" t="s">
+        <v>834</v>
+      </c>
+      <c r="HF77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>46290.580511817127</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46290.597616805557</v>
+      </c>
+      <c r="C78" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D78" t="s">
+        <v>354</v>
+      </c>
+      <c r="E78" t="s">
+        <v>210</v>
+      </c>
+      <c r="F78" t="s">
+        <v>401</v>
+      </c>
+      <c r="G78" t="s">
+        <v>198</v>
+      </c>
+      <c r="H78" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ78" t="s">
+        <v>423</v>
+      </c>
+      <c r="AL78" t="s">
+        <v>835</v>
+      </c>
+      <c r="AM78" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>836</v>
+      </c>
+      <c r="AO78" t="s">
+        <v>463</v>
+      </c>
+      <c r="AR78" t="s">
+        <v>520</v>
+      </c>
+      <c r="AS78">
+        <v>0</v>
+      </c>
+      <c r="AT78">
+        <v>500</v>
+      </c>
+      <c r="AU78" t="s">
+        <v>571</v>
+      </c>
+      <c r="AV78" t="s">
+        <v>837</v>
+      </c>
+      <c r="AW78" t="s">
+        <v>522</v>
+      </c>
+      <c r="AX78" t="s">
+        <v>838</v>
+      </c>
+      <c r="AY78" t="s">
+        <v>465</v>
+      </c>
+      <c r="BA78" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB78" t="s">
+        <v>719</v>
+      </c>
+      <c r="BC78" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD78" t="s">
+        <v>839</v>
+      </c>
+      <c r="EY78" s="1"/>
+      <c r="GQ78" s="1"/>
+      <c r="GR78" s="1"/>
+      <c r="GX78">
+        <v>878199543</v>
+      </c>
+      <c r="GY78" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="GZ78" s="1">
+        <v>46290.472974537042</v>
+      </c>
+      <c r="HA78" s="1"/>
+      <c r="HB78" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD78" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE78" t="s">
+        <v>841</v>
+      </c>
+      <c r="HF78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>46290.598360659722</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46290.603588379628</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D79" t="s">
+        <v>354</v>
+      </c>
+      <c r="E79" t="s">
+        <v>210</v>
+      </c>
+      <c r="F79" t="s">
+        <v>658</v>
+      </c>
+      <c r="G79" t="s">
+        <v>198</v>
+      </c>
+      <c r="H79" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ79" t="s">
+        <v>842</v>
+      </c>
+      <c r="AM79" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>843</v>
+      </c>
+      <c r="AO79" t="s">
+        <v>463</v>
+      </c>
+      <c r="AR79" t="s">
+        <v>404</v>
+      </c>
+      <c r="AS79">
+        <v>3</v>
+      </c>
+      <c r="AT79">
+        <v>200</v>
+      </c>
+      <c r="AU79" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV79" t="s">
+        <v>844</v>
+      </c>
+      <c r="AW79" t="s">
+        <v>522</v>
+      </c>
+      <c r="AX79" t="s">
+        <v>845</v>
+      </c>
+      <c r="AY79" t="s">
+        <v>475</v>
+      </c>
+      <c r="AZ79" t="s">
+        <v>324</v>
+      </c>
+      <c r="BA79" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB79" t="s">
+        <v>846</v>
+      </c>
+      <c r="BC79" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD79" t="s">
+        <v>324</v>
+      </c>
+      <c r="EY79" s="1"/>
+      <c r="GQ79" s="1"/>
+      <c r="GR79" s="1"/>
+      <c r="GX79">
+        <v>878207573</v>
+      </c>
+      <c r="GY79" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="GZ79" s="1">
+        <v>46290.478680555563</v>
+      </c>
+      <c r="HA79" s="1"/>
+      <c r="HB79" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD79" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE79" t="s">
+        <v>848</v>
+      </c>
+      <c r="HF79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>46290.579465543982</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46290.605737048609</v>
+      </c>
+      <c r="C80" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D80" t="s">
+        <v>354</v>
+      </c>
+      <c r="E80" t="s">
+        <v>196</v>
+      </c>
+      <c r="F80" t="s">
+        <v>793</v>
+      </c>
+      <c r="G80" t="s">
+        <v>198</v>
+      </c>
+      <c r="H80" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ80" t="s">
+        <v>849</v>
+      </c>
+      <c r="AK80" t="s">
+        <v>850</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>851</v>
+      </c>
+      <c r="AM80" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>852</v>
+      </c>
+      <c r="AO80" t="s">
+        <v>463</v>
+      </c>
+      <c r="AR80" t="s">
+        <v>520</v>
+      </c>
+      <c r="AS80">
+        <v>0</v>
+      </c>
+      <c r="AT80">
+        <v>230</v>
+      </c>
+      <c r="AU80" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV80" t="s">
+        <v>853</v>
+      </c>
+      <c r="AW80" t="s">
+        <v>392</v>
+      </c>
+      <c r="AX80" t="s">
+        <v>854</v>
+      </c>
+      <c r="AY80" t="s">
+        <v>475</v>
+      </c>
+      <c r="AZ80" t="s">
+        <v>395</v>
+      </c>
+      <c r="BA80" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB80" t="s">
+        <v>855</v>
+      </c>
+      <c r="BC80" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD80" t="s">
+        <v>856</v>
+      </c>
+      <c r="EY80" s="1"/>
+      <c r="GQ80" s="1"/>
+      <c r="GR80" s="1"/>
+      <c r="GX80">
+        <v>878210568</v>
+      </c>
+      <c r="GY80" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="GZ80" s="1">
+        <v>46290.480740740742</v>
+      </c>
+      <c r="HA80" s="1"/>
+      <c r="HB80" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD80" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE80" t="s">
+        <v>858</v>
+      </c>
+      <c r="HF80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>46290.758861805552</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46290.791165023147</v>
+      </c>
+      <c r="C81" s="1">
+        <v>46291</v>
+      </c>
+      <c r="D81" t="s">
+        <v>707</v>
+      </c>
+      <c r="E81" t="s">
+        <v>280</v>
+      </c>
+      <c r="F81" t="s">
+        <v>281</v>
+      </c>
+      <c r="G81" t="s">
+        <v>198</v>
+      </c>
+      <c r="H81" t="s">
+        <v>282</v>
+      </c>
+      <c r="J81" t="s">
+        <v>859</v>
+      </c>
+      <c r="K81" t="s">
+        <v>201</v>
+      </c>
+      <c r="L81">
+        <v>1622</v>
+      </c>
+      <c r="M81">
+        <v>341</v>
+      </c>
+      <c r="N81">
+        <v>366</v>
+      </c>
+      <c r="O81">
+        <v>48</v>
+      </c>
+      <c r="P81">
+        <v>2</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>395</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81" t="s">
+        <v>340</v>
+      </c>
+      <c r="T81" t="s">
+        <v>341</v>
+      </c>
+      <c r="U81" t="s">
+        <v>203</v>
+      </c>
+      <c r="V81" t="s">
+        <v>203</v>
+      </c>
+      <c r="W81" t="s">
+        <v>203</v>
+      </c>
+      <c r="X81" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>205</v>
+      </c>
+      <c r="AJ81" t="s">
+        <v>860</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>861</v>
+      </c>
+      <c r="AM81" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>862</v>
+      </c>
+      <c r="EY81" s="1"/>
+      <c r="GQ81" s="1"/>
+      <c r="GR81" s="1"/>
+      <c r="GX81">
+        <v>878431516</v>
+      </c>
+      <c r="GY81" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="GZ81" s="1">
+        <v>46290.653032407397</v>
+      </c>
+      <c r="HA81" s="1"/>
+      <c r="HB81" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD81" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE81" t="s">
+        <v>864</v>
+      </c>
+      <c r="HF81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>46290.782907303241</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46290.791121284718</v>
+      </c>
+      <c r="C82" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D82" t="s">
+        <v>354</v>
+      </c>
+      <c r="E82" t="s">
+        <v>237</v>
+      </c>
+      <c r="F82" t="s">
+        <v>865</v>
+      </c>
+      <c r="G82" t="s">
+        <v>198</v>
+      </c>
+      <c r="H82" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ82" t="s">
+        <v>866</v>
+      </c>
+      <c r="AK82" t="s">
+        <v>867</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>359</v>
+      </c>
+      <c r="AM82" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>628</v>
+      </c>
+      <c r="AO82" t="s">
+        <v>359</v>
+      </c>
+      <c r="AR82" t="s">
+        <v>360</v>
+      </c>
+      <c r="AS82">
+        <v>10</v>
+      </c>
+      <c r="AT82">
+        <v>800</v>
+      </c>
+      <c r="AU82" t="s">
+        <v>361</v>
+      </c>
+      <c r="AV82" t="s">
+        <v>868</v>
+      </c>
+      <c r="AW82" t="s">
+        <v>392</v>
+      </c>
+      <c r="AX82" t="s">
+        <v>869</v>
+      </c>
+      <c r="AY82" t="s">
+        <v>475</v>
+      </c>
+      <c r="AZ82" t="s">
+        <v>395</v>
+      </c>
+      <c r="BA82" t="s">
+        <v>366</v>
+      </c>
+      <c r="BB82" t="s">
+        <v>870</v>
+      </c>
+      <c r="BC82" t="s">
+        <v>397</v>
+      </c>
+      <c r="BD82" t="s">
+        <v>871</v>
+      </c>
+      <c r="EY82" s="1"/>
+      <c r="GQ82" s="1"/>
+      <c r="GR82" s="1"/>
+      <c r="GX82">
+        <v>878447924</v>
+      </c>
+      <c r="GY82" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="GZ82" s="1">
+        <v>46290.666261574072</v>
+      </c>
+      <c r="HA82" s="1"/>
+      <c r="HB82" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD82" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE82" t="s">
+        <v>873</v>
+      </c>
+      <c r="HF82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>46290.808730833327</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46290.814756793981</v>
+      </c>
+      <c r="C83" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D83" t="s">
+        <v>792</v>
+      </c>
+      <c r="E83" t="s">
+        <v>280</v>
+      </c>
+      <c r="F83" t="s">
+        <v>281</v>
+      </c>
+      <c r="G83" t="s">
+        <v>198</v>
+      </c>
+      <c r="H83" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ83" t="s">
+        <v>874</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>875</v>
+      </c>
+      <c r="AM83" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>876</v>
+      </c>
+      <c r="EY83" s="1"/>
+      <c r="EZ83" s="1">
+        <v>46290</v>
+      </c>
+      <c r="FA83" t="s">
+        <v>859</v>
+      </c>
+      <c r="FB83" t="s">
+        <v>416</v>
+      </c>
+      <c r="FD83">
+        <v>607</v>
+      </c>
+      <c r="FE83">
+        <v>812</v>
+      </c>
+      <c r="FF83">
+        <v>21</v>
+      </c>
+      <c r="FG83">
+        <v>27</v>
+      </c>
+      <c r="FH83" t="s">
+        <v>395</v>
+      </c>
+      <c r="FI83" t="s">
+        <v>417</v>
+      </c>
+      <c r="FJ83" t="s">
+        <v>377</v>
+      </c>
+      <c r="FK83" t="s">
+        <v>378</v>
+      </c>
+      <c r="FL83" t="s">
+        <v>379</v>
+      </c>
+      <c r="FN83" t="s">
+        <v>429</v>
+      </c>
+      <c r="FO83">
+        <v>5</v>
+      </c>
+      <c r="FP83" t="s">
+        <v>515</v>
+      </c>
+      <c r="FQ83" t="s">
+        <v>604</v>
+      </c>
+      <c r="FR83">
+        <v>4</v>
+      </c>
+      <c r="FS83">
+        <v>4</v>
+      </c>
+      <c r="FT83" t="s">
+        <v>383</v>
+      </c>
+      <c r="FU83" t="s">
+        <v>605</v>
+      </c>
+      <c r="FV83" t="s">
+        <v>385</v>
+      </c>
+      <c r="FW83">
+        <v>0</v>
+      </c>
+      <c r="FX83">
+        <v>0</v>
+      </c>
+      <c r="FY83">
+        <v>1</v>
+      </c>
+      <c r="FZ83">
+        <v>0</v>
+      </c>
+      <c r="GA83" t="s">
+        <v>395</v>
+      </c>
+      <c r="GC83">
+        <v>7</v>
+      </c>
+      <c r="GD83">
+        <v>4</v>
+      </c>
+      <c r="GE83">
+        <v>2</v>
+      </c>
+      <c r="GF83">
+        <v>7</v>
+      </c>
+      <c r="GG83">
+        <v>6</v>
+      </c>
+      <c r="GH83">
+        <v>3</v>
+      </c>
+      <c r="GQ83" s="1"/>
+      <c r="GR83" s="1"/>
+      <c r="GX83">
+        <v>878461161</v>
+      </c>
+      <c r="GY83" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="GZ83" s="1">
+        <v>46290.676631944443</v>
+      </c>
+      <c r="HA83" s="1"/>
+      <c r="HB83" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD83" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE83" t="s">
+        <v>878</v>
+      </c>
+      <c r="HF83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>46290.814761828697</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46290.818933425922</v>
+      </c>
+      <c r="C84" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D84" t="s">
+        <v>792</v>
+      </c>
+      <c r="E84" t="s">
+        <v>280</v>
+      </c>
+      <c r="F84" t="s">
+        <v>281</v>
+      </c>
+      <c r="G84" t="s">
+        <v>198</v>
+      </c>
+      <c r="H84" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ84" t="s">
+        <v>874</v>
+      </c>
+      <c r="AM84" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>879</v>
+      </c>
+      <c r="EY84" s="1"/>
+      <c r="EZ84" s="1">
+        <v>46290</v>
+      </c>
+      <c r="FA84" t="s">
+        <v>859</v>
+      </c>
+      <c r="FB84" t="s">
+        <v>416</v>
+      </c>
+      <c r="FD84">
+        <v>609</v>
+      </c>
+      <c r="FE84">
+        <v>819</v>
+      </c>
+      <c r="FF84">
+        <v>19</v>
+      </c>
+      <c r="FG84">
+        <v>24</v>
+      </c>
+      <c r="FH84" t="s">
+        <v>395</v>
+      </c>
+      <c r="FI84" t="s">
+        <v>417</v>
+      </c>
+      <c r="FJ84" t="s">
+        <v>377</v>
+      </c>
+      <c r="FK84" t="s">
+        <v>378</v>
+      </c>
+      <c r="FL84" t="s">
+        <v>379</v>
+      </c>
+      <c r="FN84" t="s">
+        <v>429</v>
+      </c>
+      <c r="FO84">
+        <v>4</v>
+      </c>
+      <c r="FP84" t="s">
+        <v>515</v>
+      </c>
+      <c r="FQ84" t="s">
+        <v>604</v>
+      </c>
+      <c r="FR84">
+        <v>4</v>
+      </c>
+      <c r="FS84">
+        <v>4</v>
+      </c>
+      <c r="FT84" t="s">
+        <v>880</v>
+      </c>
+      <c r="FU84" t="s">
+        <v>457</v>
+      </c>
+      <c r="FV84" t="s">
+        <v>881</v>
+      </c>
+      <c r="FW84">
+        <v>0</v>
+      </c>
+      <c r="FX84">
+        <v>1</v>
+      </c>
+      <c r="FY84">
+        <v>1</v>
+      </c>
+      <c r="FZ84">
+        <v>0</v>
+      </c>
+      <c r="GA84" t="s">
+        <v>395</v>
+      </c>
+      <c r="GC84">
+        <v>6</v>
+      </c>
+      <c r="GD84">
+        <v>5</v>
+      </c>
+      <c r="GE84">
+        <v>3</v>
+      </c>
+      <c r="GF84">
+        <v>7</v>
+      </c>
+      <c r="GG84">
+        <v>4</v>
+      </c>
+      <c r="GH84">
+        <v>4</v>
+      </c>
+      <c r="GQ84" s="1"/>
+      <c r="GR84" s="1"/>
+      <c r="GX84">
+        <v>878465700</v>
+      </c>
+      <c r="GY84" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="GZ84" s="1">
+        <v>46290.680810185193</v>
+      </c>
+      <c r="HA84" s="1"/>
+      <c r="HB84" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD84" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE84" t="s">
+        <v>883</v>
+      </c>
+      <c r="HF84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>46290.824045995367</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46290.832062951391</v>
+      </c>
+      <c r="C85" s="1">
+        <v>46291</v>
+      </c>
+      <c r="D85" t="s">
+        <v>354</v>
+      </c>
+      <c r="E85" t="s">
+        <v>280</v>
+      </c>
+      <c r="F85" t="s">
+        <v>281</v>
+      </c>
+      <c r="G85" t="s">
+        <v>198</v>
+      </c>
+      <c r="H85" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM85" t="s">
+        <v>357</v>
+      </c>
+      <c r="AO85" t="s">
+        <v>359</v>
+      </c>
+      <c r="AR85" t="s">
+        <v>360</v>
+      </c>
+      <c r="AS85">
+        <v>4</v>
+      </c>
+      <c r="AT85">
+        <v>1620</v>
+      </c>
+      <c r="AU85" t="s">
+        <v>571</v>
+      </c>
+      <c r="AV85" t="s">
+        <v>884</v>
+      </c>
+      <c r="AW85" t="s">
+        <v>363</v>
+      </c>
+      <c r="AX85" t="s">
+        <v>885</v>
+      </c>
+      <c r="AY85" t="s">
+        <v>465</v>
+      </c>
+      <c r="BA85" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB85" t="s">
+        <v>886</v>
+      </c>
+      <c r="BC85" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD85" t="s">
+        <v>324</v>
+      </c>
+      <c r="EY85" s="1"/>
+      <c r="GQ85" s="1"/>
+      <c r="GR85" s="1"/>
+      <c r="GX85">
+        <v>878480435</v>
+      </c>
+      <c r="GY85" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="GZ85" s="1">
+        <v>46290.693935185183</v>
+      </c>
+      <c r="HA85" s="1"/>
+      <c r="HB85" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD85" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE85" t="s">
+        <v>888</v>
+      </c>
+      <c r="HF85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>46290.843395416668</v>
+      </c>
+      <c r="B86" s="1">
+        <v>46290.847390798612</v>
+      </c>
+      <c r="C86" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D86" t="s">
+        <v>707</v>
+      </c>
+      <c r="E86" t="s">
+        <v>280</v>
+      </c>
+      <c r="F86" t="s">
+        <v>889</v>
+      </c>
+      <c r="G86" t="s">
+        <v>198</v>
+      </c>
+      <c r="H86" t="s">
+        <v>282</v>
+      </c>
+      <c r="J86" t="s">
+        <v>890</v>
+      </c>
+      <c r="K86" t="s">
+        <v>201</v>
+      </c>
+      <c r="L86">
+        <v>1995</v>
+      </c>
+      <c r="M86">
+        <v>407</v>
+      </c>
+      <c r="N86">
+        <v>423</v>
+      </c>
+      <c r="O86">
+        <v>44</v>
+      </c>
+      <c r="P86">
+        <v>2</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>395</v>
+      </c>
+      <c r="R86">
+        <v>20</v>
+      </c>
+      <c r="S86" t="s">
+        <v>340</v>
+      </c>
+      <c r="T86" t="s">
+        <v>341</v>
+      </c>
+      <c r="U86" t="s">
+        <v>202</v>
+      </c>
+      <c r="V86" t="s">
+        <v>203</v>
+      </c>
+      <c r="W86" t="s">
+        <v>202</v>
+      </c>
+      <c r="X86" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM86" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>891</v>
+      </c>
+      <c r="EY86" s="1"/>
+      <c r="GQ86" s="1"/>
+      <c r="GR86" s="1"/>
+      <c r="GX86">
+        <v>878496209</v>
+      </c>
+      <c r="GY86" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="GZ86" s="1">
+        <v>46290.70925925926</v>
+      </c>
+      <c r="HA86" s="1"/>
+      <c r="HB86" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD86" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE86" t="s">
+        <v>893</v>
+      </c>
+      <c r="HF86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>46290.847394305558</v>
+      </c>
+      <c r="B87" s="1">
+        <v>46290.854523680558</v>
+      </c>
+      <c r="C87" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D87" t="s">
+        <v>354</v>
+      </c>
+      <c r="E87" t="s">
+        <v>280</v>
+      </c>
+      <c r="F87" t="s">
+        <v>281</v>
+      </c>
+      <c r="G87" t="s">
+        <v>198</v>
+      </c>
+      <c r="H87" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ87" t="s">
+        <v>894</v>
+      </c>
+      <c r="AM87" t="s">
+        <v>357</v>
+      </c>
+      <c r="AO87" t="s">
+        <v>359</v>
+      </c>
+      <c r="AR87" t="s">
+        <v>360</v>
+      </c>
+      <c r="AS87">
+        <v>6</v>
+      </c>
+      <c r="AT87">
+        <v>10</v>
+      </c>
+      <c r="AU87" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV87" t="s">
+        <v>895</v>
+      </c>
+      <c r="AW87" t="s">
+        <v>522</v>
+      </c>
+      <c r="AX87" t="s">
+        <v>896</v>
+      </c>
+      <c r="AY87" t="s">
+        <v>365</v>
+      </c>
+      <c r="AZ87" t="s">
+        <v>395</v>
+      </c>
+      <c r="BA87" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB87" t="s">
+        <v>897</v>
+      </c>
+      <c r="BC87" t="s">
+        <v>397</v>
+      </c>
+      <c r="BD87" t="s">
+        <v>324</v>
+      </c>
+      <c r="EY87" s="1"/>
+      <c r="GQ87" s="1"/>
+      <c r="GR87" s="1"/>
+      <c r="GX87">
+        <v>878503679</v>
+      </c>
+      <c r="GY87" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="GZ87" s="1">
+        <v>46290.71638888889</v>
+      </c>
+      <c r="HA87" s="1"/>
+      <c r="HB87" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD87" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE87" t="s">
+        <v>899</v>
+      </c>
+      <c r="HF87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>46290.854527256954</v>
+      </c>
+      <c r="B88" s="1">
+        <v>46290.857335057874</v>
+      </c>
+      <c r="C88" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D88" t="s">
+        <v>792</v>
+      </c>
+      <c r="E88" t="s">
+        <v>280</v>
+      </c>
+      <c r="F88" t="s">
+        <v>281</v>
+      </c>
+      <c r="G88" t="s">
+        <v>198</v>
+      </c>
+      <c r="H88" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM88" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>900</v>
+      </c>
+      <c r="EY88" s="1"/>
+      <c r="EZ88" s="1">
+        <v>46290</v>
+      </c>
+      <c r="FA88" t="s">
+        <v>890</v>
+      </c>
+      <c r="FB88" t="s">
+        <v>416</v>
+      </c>
+      <c r="FD88">
+        <v>970</v>
+      </c>
+      <c r="FE88">
+        <v>1205</v>
+      </c>
+      <c r="FF88">
+        <v>8</v>
+      </c>
+      <c r="FG88">
+        <v>15</v>
+      </c>
+      <c r="FH88" t="s">
+        <v>395</v>
+      </c>
+      <c r="FI88" t="s">
+        <v>426</v>
+      </c>
+      <c r="FJ88" t="s">
+        <v>377</v>
+      </c>
+      <c r="FK88" t="s">
+        <v>378</v>
+      </c>
+      <c r="FL88" t="s">
+        <v>379</v>
+      </c>
+      <c r="FN88" t="s">
+        <v>380</v>
+      </c>
+      <c r="FO88">
+        <v>8</v>
+      </c>
+      <c r="FP88" t="s">
+        <v>381</v>
+      </c>
+      <c r="FQ88" t="s">
+        <v>418</v>
+      </c>
+      <c r="FR88">
+        <v>6</v>
+      </c>
+      <c r="FS88">
+        <v>5</v>
+      </c>
+      <c r="FT88" t="s">
+        <v>880</v>
+      </c>
+      <c r="FU88" t="s">
+        <v>457</v>
+      </c>
+      <c r="FV88" t="s">
+        <v>385</v>
+      </c>
+      <c r="FW88">
+        <v>0</v>
+      </c>
+      <c r="FX88">
+        <v>0</v>
+      </c>
+      <c r="FY88">
+        <v>1</v>
+      </c>
+      <c r="FZ88">
+        <v>0</v>
+      </c>
+      <c r="GA88" t="s">
+        <v>395</v>
+      </c>
+      <c r="GC88">
+        <v>6</v>
+      </c>
+      <c r="GD88">
+        <v>5</v>
+      </c>
+      <c r="GE88">
+        <v>5</v>
+      </c>
+      <c r="GF88">
+        <v>5</v>
+      </c>
+      <c r="GG88">
+        <v>4</v>
+      </c>
+      <c r="GH88">
+        <v>3</v>
+      </c>
+      <c r="GQ88" s="1"/>
+      <c r="GR88" s="1"/>
+      <c r="GX88">
+        <v>878506554</v>
+      </c>
+      <c r="GY88" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="GZ88" s="1">
+        <v>46290.719201388893</v>
+      </c>
+      <c r="HA88" s="1"/>
+      <c r="HB88" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD88" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE88" t="s">
+        <v>902</v>
+      </c>
+      <c r="HF88">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F4DF43-E9A5-0B46-9A53-DCFB40E9D98C}"/>
+  <xr:revisionPtr revIDLastSave="341" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E6B1929-5EA1-4C43-998E-3EBD3C475140}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="1020" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3869" uniqueCount="1436">
   <si>
     <t>start</t>
   </si>
@@ -2746,6 +2746,1605 @@
   </si>
   <si>
     <t>uuid:5014bcf7-1e4f-4ba7-b488-19f9cf008735</t>
+  </si>
+  <si>
+    <t>Tool 2: rapid audience assessment intercept survey</t>
+  </si>
+  <si>
+    <t>Ebola reduced and now the news about Ebola has declined</t>
+  </si>
+  <si>
+    <t>Other diseases that might be related with similar signs and symptoms. The other at times is attitude of health workers</t>
+  </si>
+  <si>
+    <t>More sensitization should be carried out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No, haven't seen or heard anything </t>
+  </si>
+  <si>
+    <t>I call a Health worker immediately since we have been seeing advise on tv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ministry of Health / KCCA        </t>
+  </si>
+  <si>
+    <t>f690c3de-6512-4dcb-9dc5-fc8da5d9c3fc</t>
+  </si>
+  <si>
+    <t>uuid:f690c3de-6512-4dcb-9dc5-fc8da5d9c3fc</t>
+  </si>
+  <si>
+    <t>Uganda was declared Uganda free by WHO I heard on radio.</t>
+  </si>
+  <si>
+    <t>Lack of information to treatment areas.</t>
+  </si>
+  <si>
+    <t>Friends</t>
+  </si>
+  <si>
+    <t>Posters should be used and pinned in the community.</t>
+  </si>
+  <si>
+    <t>School van driver</t>
+  </si>
+  <si>
+    <t>Heard radio broadcast / audio drive only</t>
+  </si>
+  <si>
+    <t>Bleeding and fever. I can use sanitizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named 1 symptom  </t>
+  </si>
+  <si>
+    <t>Moderate risk</t>
+  </si>
+  <si>
+    <t>LC1 Chairperson immediately</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local LC1 / Stage Chairman      </t>
+  </si>
+  <si>
+    <t>a377fbe1-ffe4-4d2d-aa62-0534f33276d6</t>
+  </si>
+  <si>
+    <t>uuid:a377fbe1-ffe4-4d2d-aa62-0534f33276d6</t>
+  </si>
+  <si>
+    <t>Is there an Ebola vaccine? People fear Ebola though take it at times as the outbreak being political</t>
+  </si>
+  <si>
+    <t>Political affiliation ,and low risk perception</t>
+  </si>
+  <si>
+    <t>Individuals people</t>
+  </si>
+  <si>
+    <t>More sensitization should be carried out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notify local VHT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VHT / Community Health Worker   </t>
+  </si>
+  <si>
+    <t>d29299fc-2430-417e-a8c3-1b7adb77acc4</t>
+  </si>
+  <si>
+    <t>uuid:d29299fc-2430-417e-a8c3-1b7adb77acc4</t>
+  </si>
+  <si>
+    <t>Is the outbreak still on?</t>
+  </si>
+  <si>
+    <t>Miscommunication from peers or different localities</t>
+  </si>
+  <si>
+    <t>Carry out community sensitization before VHTs</t>
+  </si>
+  <si>
+    <t>Call national/district toll-free hotline (0800-100-066 / 8500) Other</t>
+  </si>
+  <si>
+    <t>I can any medical personnel to do the needful</t>
+  </si>
+  <si>
+    <t>050df79b-bb77-434f-bc92-ab97f06eb28b</t>
+  </si>
+  <si>
+    <t>uuid:050df79b-bb77-434f-bc92-ab97f06eb28b</t>
+  </si>
+  <si>
+    <t>Currently people know there is no Ebola. People think Ebola is a resultbof poor hygiene</t>
+  </si>
+  <si>
+    <t>Carry out radio and television advertisement</t>
+  </si>
+  <si>
+    <t>937c725b-3783-44d7-b4b3-4cfe907b46fd</t>
+  </si>
+  <si>
+    <t>uuid:937c725b-3783-44d7-b4b3-4cfe907b46fd</t>
+  </si>
+  <si>
+    <t>We just hear on Radio that</t>
+  </si>
+  <si>
+    <t>No money</t>
+  </si>
+  <si>
+    <t>Fellow riders</t>
+  </si>
+  <si>
+    <t>Boda stage</t>
+  </si>
+  <si>
+    <t>Escort them quietly to a private clinic or pharmacy</t>
+  </si>
+  <si>
+    <t>83b39208-12aa-46ec-88bf-4b56c9b186f1</t>
+  </si>
+  <si>
+    <t>uuid:83b39208-12aa-46ec-88bf-4b56c9b186f1</t>
+  </si>
+  <si>
+    <t>The community has not seen anyone die from Ebola</t>
+  </si>
+  <si>
+    <t>Mistrust, people don't believe that Ebola is real and so they don't have hand wash equipment</t>
+  </si>
+  <si>
+    <t>Youth</t>
+  </si>
+  <si>
+    <t>More sensitization is needed on preparedness</t>
+  </si>
+  <si>
+    <t>Yes, actively engaged (e.g., Knowledge Wheel, megaphones, VHT talk)</t>
+  </si>
+  <si>
+    <t>High temperature. I can protect my self by washing my hands with soap and clean water</t>
+  </si>
+  <si>
+    <t>Don't know</t>
+  </si>
+  <si>
+    <t>Notify local VHT  LC1 Chairperson immediately Seek prayers / traditional healer</t>
+  </si>
+  <si>
+    <t>6799f5de-6d8a-499f-85f3-19ecae16c83c</t>
+  </si>
+  <si>
+    <t>uuid:6799f5de-6d8a-499f-85f3-19ecae16c83c</t>
+  </si>
+  <si>
+    <t>People are worried of Ebola when they come to a clinic due to stigma. The misinformation is most people know when you catch Ebola you die there and then. Low risk perception to follow guidelines like washing hands</t>
+  </si>
+  <si>
+    <t>Limited sensitization about the outbreaks as some do not pay attention to posters</t>
+  </si>
+  <si>
+    <t>The sick clients, and the community</t>
+  </si>
+  <si>
+    <t>Health talks should be carried out, even VHTs use megaphone while sensitizing</t>
+  </si>
+  <si>
+    <t>Private clinic</t>
+  </si>
+  <si>
+    <t>I get possible means to refer to a better facility other than my clinic as I think of a person better than me or a mean of transport means as I wait for MOH to respond.</t>
+  </si>
+  <si>
+    <t>4a6289de-4b9a-47b1-89ab-088a613f7892</t>
+  </si>
+  <si>
+    <t>uuid:4a6289de-4b9a-47b1-89ab-088a613f7892</t>
+  </si>
+  <si>
+    <t>Tool 3: 'ask 5' behavioral verification diagnostic tool</t>
+  </si>
+  <si>
+    <t>Ebola is no longer a threat since we are now ebola free.</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Peer</t>
+  </si>
+  <si>
+    <t>More sensitization still needed</t>
+  </si>
+  <si>
+    <t>Pupil leader</t>
+  </si>
+  <si>
+    <t>I can easily spot the signs of Ebola and Mpox If someone gets sick with outbreak signs, I will call the toll-free line or report immediately I have shared the emergency preparedness messages with my household and colleagues</t>
+  </si>
+  <si>
+    <t>For malaria you can get a high temperature while for mpox you get body spots on your body.</t>
+  </si>
+  <si>
+    <t>I inform the nearest teacher around or school nurse.</t>
+  </si>
+  <si>
+    <t>Severe Misinformation</t>
+  </si>
+  <si>
+    <t>Correct</t>
+  </si>
+  <si>
+    <t>Many questions maybe asked to me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knows Contact &amp; Willing  </t>
+  </si>
+  <si>
+    <t>We agreed that we shall encourage every student to wash their hands with soap and water</t>
+  </si>
+  <si>
+    <t>Is Ebola still a threat? Yes it is still a threat because our neighboring country still has it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentioned Casually  </t>
+  </si>
+  <si>
+    <t>9e8dd4f3-1da9-4507-aaf6-693fdf0f728b</t>
+  </si>
+  <si>
+    <t>uuid:9e8dd4f3-1da9-4507-aaf6-693fdf0f728b</t>
+  </si>
+  <si>
+    <t>Nansana East</t>
+  </si>
+  <si>
+    <t>Ebola is taken as witchcraft</t>
+  </si>
+  <si>
+    <t>Traditional healers</t>
+  </si>
+  <si>
+    <t>Neighbor</t>
+  </si>
+  <si>
+    <t>More sensitization being carried out in the school</t>
+  </si>
+  <si>
+    <t>Teacher/patron</t>
+  </si>
+  <si>
+    <t>We always wash our hands with soap throughout the day. I have shared the emergency preparedness messages with my household and colleagues</t>
+  </si>
+  <si>
+    <t>Today after visiting the washroom</t>
+  </si>
+  <si>
+    <t>Near the washroom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is the water vessel filled, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed Practicing  </t>
+  </si>
+  <si>
+    <t>We agreed to always encourage pupils to wash their hands with soap and water</t>
+  </si>
+  <si>
+    <t>Does having sex cause ebola? My answer was no because if my partner is not sick then I can not get it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Multiplier (Evidence of Dialogue)  </t>
+  </si>
+  <si>
+    <t>48876c80-8a43-47bb-9a99-ee4e23d4edeb</t>
+  </si>
+  <si>
+    <t>uuid:48876c80-8a43-47bb-9a99-ee4e23d4edeb</t>
+  </si>
+  <si>
+    <t>Nsuube - Nabuuti</t>
+  </si>
+  <si>
+    <t>Talents College SS</t>
+  </si>
+  <si>
+    <t>How different is marburg from ebola. Is it a must that one has to show all the signs and symptoms to be suspected with the virus? If someone is identified with ebola, do they close the whole school of they just isolate that one person.</t>
+  </si>
+  <si>
+    <t>Lack of soap at the points were hand washing is done</t>
+  </si>
+  <si>
+    <t>Didn't mention any</t>
+  </si>
+  <si>
+    <t>Encouraging the school administration to always avail soap at the hand washing facilities.  Continued sensitisation and utilising the Ureport health club to spread the message to the rest</t>
+  </si>
+  <si>
+    <t>e4712bca-8b7a-482a-a01f-fe536c07bb0e</t>
+  </si>
+  <si>
+    <t>uuid:e4712bca-8b7a-482a-a01f-fe536c07bb0e</t>
+  </si>
+  <si>
+    <t>Nsuube- Nabuti</t>
+  </si>
+  <si>
+    <t>What happens if an ebola suspect is identified at school. Do they close the whole school or just isolate the infected one</t>
+  </si>
+  <si>
+    <t>Lack of soap at the point where hands are washed.</t>
+  </si>
+  <si>
+    <t>No rumor mentioned</t>
+  </si>
+  <si>
+    <t>Use of the health club and continuous se senstization. Providing soap at the points where hands are washed.</t>
+  </si>
+  <si>
+    <t>Talents College Secondary school</t>
+  </si>
+  <si>
+    <t>e0b11b67-92f5-4978-9def-bfed817351de</t>
+  </si>
+  <si>
+    <t>uuid:e0b11b67-92f5-4978-9def-bfed817351de</t>
+  </si>
+  <si>
+    <t>Why do we get these diseases</t>
+  </si>
+  <si>
+    <t>Over crowdness because of the high population</t>
+  </si>
+  <si>
+    <t>Pupils</t>
+  </si>
+  <si>
+    <t>Ask help from the Division on how to help with some infrastructure to reduce on the number of pupils per class</t>
+  </si>
+  <si>
+    <t>0dac72b2-c1ee-431d-a9cc-a351e7554842</t>
+  </si>
+  <si>
+    <t>uuid:0dac72b2-c1ee-431d-a9cc-a351e7554842</t>
+  </si>
+  <si>
+    <t>These diseases are not true, it’s just a political stunt</t>
+  </si>
+  <si>
+    <t>No hand washing facility, poor waste disposal and over crowdness in the market</t>
+  </si>
+  <si>
+    <t>Vendors</t>
+  </si>
+  <si>
+    <t>The government to buy neighbours for market expansion</t>
+  </si>
+  <si>
+    <t>The markers is congested and dirty</t>
+  </si>
+  <si>
+    <t>The market has very many vendors and this is risky incase of an outbreak</t>
+  </si>
+  <si>
+    <t>100:1</t>
+  </si>
+  <si>
+    <t>c83d0f1d-491e-4a6e-a790-0d0be48ddfd9</t>
+  </si>
+  <si>
+    <t>uuid:c83d0f1d-491e-4a6e-a790-0d0be48ddfd9</t>
+  </si>
+  <si>
+    <t>Ebola has no cure</t>
+  </si>
+  <si>
+    <t>Flooding during rainy season, people are not reminded of outbreaks</t>
+  </si>
+  <si>
+    <t>The taxi drivers</t>
+  </si>
+  <si>
+    <t>Government to keep reminding communities disease prevention and control and not wait for outbreaks, provide stickers to reach a wider community Incase of an outbreak</t>
+  </si>
+  <si>
+    <t>The food points are not clean and are congested.</t>
+  </si>
+  <si>
+    <t>They only use the hand washing facilities during an outbreak and they also claim to get information on outbreaks or any health issues only during the outbreaks</t>
+  </si>
+  <si>
+    <t>80:1</t>
+  </si>
+  <si>
+    <t>436bc500-f073-405a-bbf2-307b23b3c721</t>
+  </si>
+  <si>
+    <t>uuid:436bc500-f073-405a-bbf2-307b23b3c721</t>
+  </si>
+  <si>
+    <t>Are there still cases of Ebola in Congo?</t>
+  </si>
+  <si>
+    <t>Enforcement of SOPs wasn't all that strict as compared during Covid 19</t>
+  </si>
+  <si>
+    <t>Use of village health teams to use megaphones to carryout awareness</t>
+  </si>
+  <si>
+    <t>If someone gets sick with outbreak signs, I will call the toll-free line or report immediately We do not discriminate against anyone who recovers from an infectious disease or their family</t>
+  </si>
+  <si>
+    <t>No sign</t>
+  </si>
+  <si>
+    <t>We shall comfort and console the person as it's evident was discharged after treatment</t>
+  </si>
+  <si>
+    <t>Yes, because there is proof of treatment and discharge form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supportive  </t>
+  </si>
+  <si>
+    <t>8e8bbf56-c5e4-41a0-a601-183ba775afa8</t>
+  </si>
+  <si>
+    <t>uuid:8e8bbf56-c5e4-41a0-a601-183ba775afa8</t>
+  </si>
+  <si>
+    <t>Expectations from government, many are waiting for government to intervene</t>
+  </si>
+  <si>
+    <t>Need to encourage communities to take responsibility for their own lives</t>
+  </si>
+  <si>
+    <t>Owino market is very populated with thousands coming in and going out,but nothing is in place for Emergency Preparedness</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>f016f84e-a0cc-4676-a3f5-ac3b86d980b9</t>
+  </si>
+  <si>
+    <t>uuid:f016f84e-a0cc-4676-a3f5-ac3b86d980b9</t>
+  </si>
+  <si>
+    <t>Economic constraints in the  community, many youth are using substances, sexual immorality in the area</t>
+  </si>
+  <si>
+    <t>If possible to address the issue of substance abuse by the youth</t>
+  </si>
+  <si>
+    <t>It is a slum setting with many drainage channels going it</t>
+  </si>
+  <si>
+    <t>Kakajjo zone is a slum in Kisenyi where the youth are using drugs,young girls are sexually active with multiple partners, teenage pregnancy is high</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2cdf50b5-65e2-4ac0-b591-66796fbcf1f4</t>
+  </si>
+  <si>
+    <t>uuid:2cdf50b5-65e2-4ac0-b591-66796fbcf1f4</t>
+  </si>
+  <si>
+    <t>Uganda is Ebola free, we are asked to wash our hands regularly with soap</t>
+  </si>
+  <si>
+    <t>Congestion of some areas that make it difficult to obey some SOPs</t>
+  </si>
+  <si>
+    <t>More sensitization campaigns should be carried out</t>
+  </si>
+  <si>
+    <t>We always wash our hands with soap throughout the day. I can easily spot the signs of Ebola and Mpox If someone gets sick with outbreak signs, I will call the toll-free line or report immediately We do not discriminate against anyone who recovers from an infectious disease or their family I have shared the emergency preparedness messages with my household and colleagues</t>
+  </si>
+  <si>
+    <t>Today morning before leaving home</t>
+  </si>
+  <si>
+    <t>At the nearby clinic</t>
+  </si>
+  <si>
+    <t>is the water vessel filled,  are soap residues</t>
+  </si>
+  <si>
+    <t>Malaria it's temperature is likely to be less than 37 degrees other than that of haemorrghic fever which is 38 degrees</t>
+  </si>
+  <si>
+    <t>I call the toll-free free line or send an alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accurate Clinical Understanding  </t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>I will comfort them and encourage them to take precautionary measures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fully Receptive </t>
+  </si>
+  <si>
+    <t>They were positive as they believe in me given the services  I extend to the community</t>
+  </si>
+  <si>
+    <t>Why do all outbreaks emerge from Congo? My reply was because Congo has various animals infected with the diseases which they eat some making infection very easy</t>
+  </si>
+  <si>
+    <t>ae3025b6-34a1-4590-855a-1dd294f7261f</t>
+  </si>
+  <si>
+    <t>uuid:ae3025b6-34a1-4590-855a-1dd294f7261f</t>
+  </si>
+  <si>
+    <t>Ebola is spread through air</t>
+  </si>
+  <si>
+    <t>Existence of diseases that have similar signs and symptoms</t>
+  </si>
+  <si>
+    <t>More sensitization on television with visuals should be done</t>
+  </si>
+  <si>
+    <t>Boda rider</t>
+  </si>
+  <si>
+    <t>I can easily spot the signs of Ebola and Mpox We do not discriminate against anyone who recovers from an infectious disease or their family</t>
+  </si>
+  <si>
+    <t>Only tells difference of Mpox a person having skin rash</t>
+  </si>
+  <si>
+    <t>I can inform a VHT so as to assist further</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confused with other illnesses  </t>
+  </si>
+  <si>
+    <t>At first we fear due to fear for our lives</t>
+  </si>
+  <si>
+    <t>619411f1-9a67-43f0-b08d-aa00c8175661</t>
+  </si>
+  <si>
+    <t>uuid:619411f1-9a67-43f0-b08d-aa00c8175661</t>
+  </si>
+  <si>
+    <t>Ebola outbreak was a political move by government to get donor momey</t>
+  </si>
+  <si>
+    <t>Village health teams should be empowered so as they inform the community the prevailing disease outbreaks</t>
+  </si>
+  <si>
+    <t>We always wash our hands with soap throughout the day. If someone gets sick with outbreak signs, I will call the toll-free line or report immediately</t>
+  </si>
+  <si>
+    <t>In the morning before having breakfast</t>
+  </si>
+  <si>
+    <t>At the restaurant</t>
+  </si>
+  <si>
+    <t>is the water vessel filled,  footprints visible?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial </t>
+  </si>
+  <si>
+    <t>Wrong</t>
+  </si>
+  <si>
+    <t>Sudden bleeding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsure of Contact  </t>
+  </si>
+  <si>
+    <t>c301377f-5a84-44b6-9919-6b32bb057ea2</t>
+  </si>
+  <si>
+    <t>uuid:c301377f-5a84-44b6-9919-6b32bb057ea2</t>
+  </si>
+  <si>
+    <t>Encouraging both teachers and pupils to always wash their hands.</t>
+  </si>
+  <si>
+    <t>We always wash our hands with soap throughout the day.</t>
+  </si>
+  <si>
+    <t>At the gate while entering the school</t>
+  </si>
+  <si>
+    <t>At the handwashing facility</t>
+  </si>
+  <si>
+    <t>ac8d5648-f563-4be3-94a2-c1b2d2e01043</t>
+  </si>
+  <si>
+    <t>uuid:ac8d5648-f563-4be3-94a2-c1b2d2e01043</t>
+  </si>
+  <si>
+    <t>Eating pork can lead to ebola</t>
+  </si>
+  <si>
+    <t>More sensitization needed</t>
+  </si>
+  <si>
+    <t>After using the washroom</t>
+  </si>
+  <si>
+    <t>At the washroom</t>
+  </si>
+  <si>
+    <t>Reporting to my parent or teacher Incase am not feeling well</t>
+  </si>
+  <si>
+    <t>0b5437fa-a116-4a7a-84f3-fb13cbfb9e6d</t>
+  </si>
+  <si>
+    <t>uuid:0b5437fa-a116-4a7a-84f3-fb13cbfb9e6d</t>
+  </si>
+  <si>
+    <t>Namirembe Bakuli</t>
+  </si>
+  <si>
+    <t>Infrastructural standard is very poor</t>
+  </si>
+  <si>
+    <t>Peopl</t>
+  </si>
+  <si>
+    <t>The market is very muddy but somehow clean</t>
+  </si>
+  <si>
+    <t>However much the market is muddy, they maintain it clean</t>
+  </si>
+  <si>
+    <t>70:1</t>
+  </si>
+  <si>
+    <t>ed43b8ef-9989-4221-b720-cb59ca4eacbf</t>
+  </si>
+  <si>
+    <t>uuid:ed43b8ef-9989-4221-b720-cb59ca4eacbf</t>
+  </si>
+  <si>
+    <t>These emergencies are not true</t>
+  </si>
+  <si>
+    <t>No help comes from KCCA</t>
+  </si>
+  <si>
+    <t>Talk to KCCA to provide incentives to the market because they pay taxes</t>
+  </si>
+  <si>
+    <t>Notify local VHT  LC1 Chairperson immediately</t>
+  </si>
+  <si>
+    <t>f7d3181f-1852-4df0-8254-aea24ee89680</t>
+  </si>
+  <si>
+    <t>uuid:f7d3181f-1852-4df0-8254-aea24ee89680</t>
+  </si>
+  <si>
+    <t>Ebola is a government way to make money</t>
+  </si>
+  <si>
+    <t>No hand washing equipment seen around</t>
+  </si>
+  <si>
+    <t>Youth in opposition</t>
+  </si>
+  <si>
+    <t>More sensitization is needed</t>
+  </si>
+  <si>
+    <t>52f854a2-325f-41d5-a057-18d7b742294e</t>
+  </si>
+  <si>
+    <t>uuid:52f854a2-325f-41d5-a057-18d7b742294e</t>
+  </si>
+  <si>
+    <t>Ebola is not real</t>
+  </si>
+  <si>
+    <t>Lack of sensitization</t>
+  </si>
+  <si>
+    <t>From neighbors</t>
+  </si>
+  <si>
+    <t>Notify local VHT  Escort them quietly to a private clinic or pharmacy</t>
+  </si>
+  <si>
+    <t>51e9ab03-ac1b-47aa-b94b-75740b9b728f</t>
+  </si>
+  <si>
+    <t>uuid:51e9ab03-ac1b-47aa-b94b-75740b9b728f</t>
+  </si>
+  <si>
+    <t>People have believed the rumor</t>
+  </si>
+  <si>
+    <t>More sensitization is needed.</t>
+  </si>
+  <si>
+    <t>Red eyes for ebola and high temperature, I can protect my self by washing my hands with clean water and soap</t>
+  </si>
+  <si>
+    <t>Notify local VHT  Escort them quietly to a private clinic or pharmacy Isolate them at home and treat with herbs/home care</t>
+  </si>
+  <si>
+    <t>c66296b7-1db5-4fb7-9795-1ca027daeb0d</t>
+  </si>
+  <si>
+    <t>uuid:c66296b7-1db5-4fb7-9795-1ca027daeb0d</t>
+  </si>
+  <si>
+    <t>Ebola and mpox are disease for the Congolese</t>
+  </si>
+  <si>
+    <t>More sensitization</t>
+  </si>
+  <si>
+    <t>e5af40f5-a4ea-4d64-82fd-7d2dced283e5</t>
+  </si>
+  <si>
+    <t>uuid:e5af40f5-a4ea-4d64-82fd-7d2dced283e5</t>
+  </si>
+  <si>
+    <t>From taxi drivers</t>
+  </si>
+  <si>
+    <t>Need for sensitization</t>
+  </si>
+  <si>
+    <t>Taxi driver</t>
+  </si>
+  <si>
+    <t>We always wash our hands with soap throughout the day. We do not discriminate against anyone who recovers from an infectious disease or their family</t>
+  </si>
+  <si>
+    <t>In the morning</t>
+  </si>
+  <si>
+    <t>We don't have soap but there is water</t>
+  </si>
+  <si>
+    <t>Socially Desirable Claim Only</t>
+  </si>
+  <si>
+    <t>we shall talk to them and welcome them</t>
+  </si>
+  <si>
+    <t>I would not buy food from them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive Avoidance  </t>
+  </si>
+  <si>
+    <t>0b572e49-596b-4935-9296-b4a70cff61ad</t>
+  </si>
+  <si>
+    <t>uuid:0b572e49-596b-4935-9296-b4a70cff61ad</t>
+  </si>
+  <si>
+    <t>Mbuya C/U primary</t>
+  </si>
+  <si>
+    <t>Visit 2</t>
+  </si>
+  <si>
+    <t>Few washing equipment</t>
+  </si>
+  <si>
+    <t>From the community</t>
+  </si>
+  <si>
+    <t>More hand washing equipment needed at school</t>
+  </si>
+  <si>
+    <t>407732bf-eb5f-4af2-9953-fcc550e9c108</t>
+  </si>
+  <si>
+    <t>uuid:407732bf-eb5f-4af2-9953-fcc550e9c108</t>
+  </si>
+  <si>
+    <t>Encouraging handwashing in the market</t>
+  </si>
+  <si>
+    <t>2aa9d022-6e4e-4b0e-8f38-6c891222251e</t>
+  </si>
+  <si>
+    <t>uuid:2aa9d022-6e4e-4b0e-8f38-6c891222251e</t>
+  </si>
+  <si>
+    <t>Nansana East ward</t>
+  </si>
+  <si>
+    <t>Ebola is a political move</t>
+  </si>
+  <si>
+    <t>Some market people</t>
+  </si>
+  <si>
+    <t>Improvement of wash</t>
+  </si>
+  <si>
+    <t>Blood from body openings,fever. Avoiding body contact with a suspected person of Ebola</t>
+  </si>
+  <si>
+    <t>aa34b61f-bf1d-4677-b1fb-e66784ea72ca</t>
+  </si>
+  <si>
+    <t>uuid:aa34b61f-bf1d-4677-b1fb-e66784ea72ca</t>
+  </si>
+  <si>
+    <t>Increased sensitization</t>
+  </si>
+  <si>
+    <t>Body weakness, blood from the ears, always wash your hands with soap and water</t>
+  </si>
+  <si>
+    <t>Low risk</t>
+  </si>
+  <si>
+    <t>Call national/district toll-free hotline (0800-100-066 / 8500)</t>
+  </si>
+  <si>
+    <t>a64647b6-1399-4cf7-84ba-ad61a122bca3</t>
+  </si>
+  <si>
+    <t>uuid:a64647b6-1399-4cf7-84ba-ad61a122bca3</t>
+  </si>
+  <si>
+    <t>Isolate them at home and treat with herbs/home care</t>
+  </si>
+  <si>
+    <t>Religious Leader / Pastor / Imam</t>
+  </si>
+  <si>
+    <t>5a5aaedc-1c4c-4637-9ba2-d98917d94c62</t>
+  </si>
+  <si>
+    <t>uuid:5a5aaedc-1c4c-4637-9ba2-d98917d94c62</t>
+  </si>
+  <si>
+    <t>Is Ebola still a threat</t>
+  </si>
+  <si>
+    <t>Headache</t>
+  </si>
+  <si>
+    <t>Threat is completely gone / nothing more needed</t>
+  </si>
+  <si>
+    <t>75af8f7c-1289-4024-aa30-50b547f15e63</t>
+  </si>
+  <si>
+    <t>uuid:75af8f7c-1289-4024-aa30-50b547f15e63</t>
+  </si>
+  <si>
+    <t>Encouraging people to visit the health facility Incase they see any signs.</t>
+  </si>
+  <si>
+    <t>Blood from the body openings, fever, control by avoiding sharing of clothes with an infected person</t>
+  </si>
+  <si>
+    <t>High risk remains (dense movement/regional threats)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call national/district toll-free hotline (0800-100-066 / 8500) Notify local VHT </t>
+  </si>
+  <si>
+    <t>3199c69b-1654-4f02-8386-1015ce6966d9</t>
+  </si>
+  <si>
+    <t>uuid:3199c69b-1654-4f02-8386-1015ce6966d9</t>
+  </si>
+  <si>
+    <t>Can ebola be go by a baby in the womb</t>
+  </si>
+  <si>
+    <t>Blood from the ears, fever</t>
+  </si>
+  <si>
+    <t>Call national/district toll-free hotline (0800-100-066 / 8500) Notify local VHT  LC1 Chairperson immediately Escort them quietly to a private clinic or pharmacy</t>
+  </si>
+  <si>
+    <t>2ab55439-1702-46b6-822d-2b0fc5c0d6e2</t>
+  </si>
+  <si>
+    <t>uuid:2ab55439-1702-46b6-822d-2b0fc5c0d6e2</t>
+  </si>
+  <si>
+    <t>Goma</t>
+  </si>
+  <si>
+    <t>"There is no Ebola, it's government / muzungu project to get money. They want to bring lockdown again like COVID." / "Ebola is just malaria. They call it Ebola to scare us." 2. If I carry a sick person on my boda and he dies, they will burn my boda / quarantine me for 21 days. I will lose my daily income." / "Boda riders who carry Ebola patients will be chased from stage."</t>
+  </si>
+  <si>
+    <t>Refusal to go for early screening, boda riders hide sick passengers, fear to call 0800 hotline. Late reporting Riders refuse to transport sick mothers / children to Mukono hospital. Patients walk or delay, bleeding at home.....      Some people dont know where to report incase of any suspect coming up</t>
+  </si>
+  <si>
+    <t>Source of rumor: Boda chairman at stage, older riders, TikTok / WhatsApp audio.</t>
+  </si>
+  <si>
+    <t>Holding a dialogue with Boda Chairman. Give clear assurance: No boda will be burnt, no boda impounded. Share real referral protocol Put 2 handwashing jerricans + soap at stage. .</t>
+  </si>
+  <si>
+    <t>I would consider it to be normal for one to be sick. I wouldn't really mind. The best i can do is to tell them to go for  medical attention. If not mature, i would inform the person responsible.</t>
+  </si>
+  <si>
+    <t>90be8397-4c4e-4de3-ba2f-252c7d8750c9</t>
+  </si>
+  <si>
+    <t>uuid:90be8397-4c4e-4de3-ba2f-252c7d8750c9</t>
+  </si>
+  <si>
+    <t>It’s the government trying to get money from it</t>
+  </si>
+  <si>
+    <t>Continuous sensitization</t>
+  </si>
+  <si>
+    <t>Bleeding from body openings. Fever.       Through washing hands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect </t>
+  </si>
+  <si>
+    <t>Call national/district toll-free hotline (0800-100-066 / 8500) Notify local VHT  Escort them quietly to a private clinic or pharmacy</t>
+  </si>
+  <si>
+    <t>41a9c435-51ce-4111-b76e-f6a391b4d78d</t>
+  </si>
+  <si>
+    <t>uuid:41a9c435-51ce-4111-b76e-f6a391b4d78d</t>
+  </si>
+  <si>
+    <t>Here many believe it's government's responsibility to provide the needed equipment ie.hand washing equipments,sanitizers</t>
+  </si>
+  <si>
+    <t>Mistrust in government, many still believe government had its motives  on the last Ebola outbreak</t>
+  </si>
+  <si>
+    <t>Open conversations, general</t>
+  </si>
+  <si>
+    <t>To not politize diseases</t>
+  </si>
+  <si>
+    <t>In a bad state making it easy for an outbreak like cholera</t>
+  </si>
+  <si>
+    <t>The market has many people coming in and out on a daily basis yet no preventive measures are in place. The vendors admitted that most of them sleep in the market  with no adquate services</t>
+  </si>
+  <si>
+    <t>56dba007-9c3c-4c8c-8300-afe0a5b20c26</t>
+  </si>
+  <si>
+    <t>uuid:56dba007-9c3c-4c8c-8300-afe0a5b20c26</t>
+  </si>
+  <si>
+    <t>People think they were bewitched</t>
+  </si>
+  <si>
+    <t>Consult health workers</t>
+  </si>
+  <si>
+    <t>Yes, saw posters / flyers only</t>
+  </si>
+  <si>
+    <t>Vomiting and headache.</t>
+  </si>
+  <si>
+    <t>Call national/district toll-free hotline (0800-100-066 / 8500) Notify local VHT  LC1 Chairperson immediately</t>
+  </si>
+  <si>
+    <t>dda48fb7-2c6d-4f15-860c-1163dabbd31d</t>
+  </si>
+  <si>
+    <t>uuid:dda48fb7-2c6d-4f15-860c-1163dabbd31d</t>
+  </si>
+  <si>
+    <t>Did we really have Ebola in Uganda in this last outbreak or government was looking for donors money?</t>
+  </si>
+  <si>
+    <t>Mistrust in government meaning the community is skeptical of the Emergency Preparedness campaign</t>
+  </si>
+  <si>
+    <t>Politicians,social media</t>
+  </si>
+  <si>
+    <t>Need to aggressively address the mistrust by government involving leaders right from.the grassroots</t>
+  </si>
+  <si>
+    <t>Cleared away</t>
+  </si>
+  <si>
+    <t>The park is covering few routes around Kampala so it's not so busy or congested as the other parks but equally busy</t>
+  </si>
+  <si>
+    <t>7f52b757-6fd6-4218-9ea0-00085d7f8223</t>
+  </si>
+  <si>
+    <t>uuid:7f52b757-6fd6-4218-9ea0-00085d7f8223</t>
+  </si>
+  <si>
+    <t>It is not real</t>
+  </si>
+  <si>
+    <t>Encourage hand washing</t>
+  </si>
+  <si>
+    <t>Diarrhea and severe headache.  Avoid close contact with the victim</t>
+  </si>
+  <si>
+    <t>ac82f71b-21c2-4db4-a820-81a4b6c64a8a</t>
+  </si>
+  <si>
+    <t>uuid:ac82f71b-21c2-4db4-a820-81a4b6c64a8a</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Continued sensitization</t>
+  </si>
+  <si>
+    <t>Clean and well maintained</t>
+  </si>
+  <si>
+    <t>This particular bus terminal has received sensitization and the leadership has been  engaged, they have been very cooperative in outbreaks campaigns. The SOPs and alertness have been maintained</t>
+  </si>
+  <si>
+    <t>Yes the leadership has received orientation</t>
+  </si>
+  <si>
+    <t>98a104ea-c1fa-418b-884d-4784e8ecdbac</t>
+  </si>
+  <si>
+    <t>uuid:98a104ea-c1fa-418b-884d-4784e8ecdbac</t>
+  </si>
+  <si>
+    <t>Some people be seeking attention yet they are not that very sick</t>
+  </si>
+  <si>
+    <t>Rashes and fever.   Avoid sharing clothes</t>
+  </si>
+  <si>
+    <t>3d4165ee-a506-40db-b7ea-63786a99a1fc</t>
+  </si>
+  <si>
+    <t>uuid:3d4165ee-a506-40db-b7ea-63786a99a1fc</t>
+  </si>
+  <si>
+    <t>All people who get sick of Ebola die</t>
+  </si>
+  <si>
+    <t>Always wash hands</t>
+  </si>
+  <si>
+    <t>Body weakness and stomach pains. Seek medical attention</t>
+  </si>
+  <si>
+    <t>Call national/district toll-free hotline (0800-100-066 / 8500) LC1 Chairperson immediately Escort them quietly to a private clinic or pharmacy</t>
+  </si>
+  <si>
+    <t>7f7b42ae-bb75-42ca-806b-8053aa9d8008</t>
+  </si>
+  <si>
+    <t>uuid:7f7b42ae-bb75-42ca-806b-8053aa9d8008</t>
+  </si>
+  <si>
+    <t>It is spread by animals</t>
+  </si>
+  <si>
+    <t>Vomiting and diarrhea.   Wash hands with soap</t>
+  </si>
+  <si>
+    <t>b79438eb-4c61-48d3-ad9a-8482da88c68d</t>
+  </si>
+  <si>
+    <t>uuid:b79438eb-4c61-48d3-ad9a-8482da88c68d</t>
+  </si>
+  <si>
+    <t>It is a political rumor</t>
+  </si>
+  <si>
+    <t>Fever and bleeding from body openings. Avoid contact with infected people</t>
+  </si>
+  <si>
+    <t>71b9ceb6-3a64-4fb9-a121-6800ba87267b</t>
+  </si>
+  <si>
+    <t>uuid:71b9ceb6-3a64-4fb9-a121-6800ba87267b</t>
+  </si>
+  <si>
+    <t>It is witchcraft</t>
+  </si>
+  <si>
+    <t>Fever and severe headache. Seek medical attention</t>
+  </si>
+  <si>
+    <t>Notify local VHT  LC1 Chairperson immediately Escort them quietly to a private clinic or pharmacy</t>
+  </si>
+  <si>
+    <t>adb84bfe-2efa-4c1e-811e-e4f66cd4ac06</t>
+  </si>
+  <si>
+    <t>uuid:adb84bfe-2efa-4c1e-811e-e4f66cd4ac06</t>
+  </si>
+  <si>
+    <t>It doesn’t exist</t>
+  </si>
+  <si>
+    <t>Stomach pain and vomiting. Seek medical attention</t>
+  </si>
+  <si>
+    <t>18960eae-3e84-40cc-bdd1-65f14b56e6b5</t>
+  </si>
+  <si>
+    <t>uuid:18960eae-3e84-40cc-bdd1-65f14b56e6b5</t>
+  </si>
+  <si>
+    <t>Vomiting and diarrhea. Wash hands regularly</t>
+  </si>
+  <si>
+    <t>084616f8-eec6-417e-bcde-6421566adcd3</t>
+  </si>
+  <si>
+    <t>uuid:084616f8-eec6-417e-bcde-6421566adcd3</t>
+  </si>
+  <si>
+    <t>Do we have Ugandans that have died of the recent Ebola outbreak</t>
+  </si>
+  <si>
+    <t>Low risk perception as some people believe after seeing</t>
+  </si>
+  <si>
+    <t>Use of posters to reach more people with information</t>
+  </si>
+  <si>
+    <t>After using the latrine</t>
+  </si>
+  <si>
+    <t>No soap at her stall</t>
+  </si>
+  <si>
+    <t>I for one I will comfort and accept them</t>
+  </si>
+  <si>
+    <t>c87adfd3-d199-4be9-a3d4-b0a7e63d7ef3</t>
+  </si>
+  <si>
+    <t>uuid:c87adfd3-d199-4be9-a3d4-b0a7e63d7ef3</t>
+  </si>
+  <si>
+    <t>There is more Ebola in DRC congo</t>
+  </si>
+  <si>
+    <t>Porus boarders</t>
+  </si>
+  <si>
+    <t>Boarder points should be have restricted ebtry</t>
+  </si>
+  <si>
+    <t>I would fear them at first since the disease is strange, but when I am counseled I can accept them</t>
+  </si>
+  <si>
+    <t>fc01eea5-db32-4029-9fac-905235f2cbca</t>
+  </si>
+  <si>
+    <t>uuid:fc01eea5-db32-4029-9fac-905235f2cbca</t>
+  </si>
+  <si>
+    <t>Ebola outbreak was political the government was after getting money</t>
+  </si>
+  <si>
+    <t>Low risk perception associated with few Ebola cases</t>
+  </si>
+  <si>
+    <t>Market vendor</t>
+  </si>
+  <si>
+    <t>Can't not differentiate them</t>
+  </si>
+  <si>
+    <t>I inform the market leader or reffer them to a government facility</t>
+  </si>
+  <si>
+    <t>We would encourage them to follow guidelines and complete treatment if any</t>
+  </si>
+  <si>
+    <t>93b27be6-b943-4a87-8653-a96ddf0789e5</t>
+  </si>
+  <si>
+    <t>uuid:93b27be6-b943-4a87-8653-a96ddf0789e5</t>
+  </si>
+  <si>
+    <t>Uganda is Ebola free</t>
+  </si>
+  <si>
+    <t>Advised Vhts to carryout sensitization using megaphones as it's done with current MR</t>
+  </si>
+  <si>
+    <t>Fever, diarrhea, bleeding</t>
+  </si>
+  <si>
+    <t>c2a6484c-4f0b-430a-b54f-33ecfd7c6b03</t>
+  </si>
+  <si>
+    <t>uuid:c2a6484c-4f0b-430a-b54f-33ecfd7c6b03</t>
+  </si>
+  <si>
+    <t>Is Mpox chicken pox?</t>
+  </si>
+  <si>
+    <t>Illiteracy of some community members</t>
+  </si>
+  <si>
+    <t>More sensitization should be done by local leaders</t>
+  </si>
+  <si>
+    <t>Bleeding, Skin rash</t>
+  </si>
+  <si>
+    <t>b4afe3cb-1dad-4ccb-b8bf-914a88532ebd</t>
+  </si>
+  <si>
+    <t>uuid:b4afe3cb-1dad-4ccb-b8bf-914a88532ebd</t>
+  </si>
+  <si>
+    <t>What causes Ebola?</t>
+  </si>
+  <si>
+    <t>Low risk perception as the country is Ebola free</t>
+  </si>
+  <si>
+    <t>More sensitization should be carries out</t>
+  </si>
+  <si>
+    <t>Bleeding, fever, we can protect ourselves by not getting near an Ebola patient or by reporting the suspect</t>
+  </si>
+  <si>
+    <t>3026b8f0-1a80-40a2-a0bf-14263edc1912</t>
+  </si>
+  <si>
+    <t>uuid:3026b8f0-1a80-40a2-a0bf-14263edc1912</t>
+  </si>
+  <si>
+    <t>N.A</t>
+  </si>
+  <si>
+    <t>Government should Carry out more sensitization in the community</t>
+  </si>
+  <si>
+    <t>Bleeding , joint pain</t>
+  </si>
+  <si>
+    <t>98560e11-4490-47af-93e5-fb56b5cde654</t>
+  </si>
+  <si>
+    <t>uuid:98560e11-4490-47af-93e5-fb56b5cde654</t>
+  </si>
+  <si>
+    <t>Ebola is a program organised by the government to get money</t>
+  </si>
+  <si>
+    <t>They don't have good and enough information about ebola</t>
+  </si>
+  <si>
+    <t>From friends</t>
+  </si>
+  <si>
+    <t>Continued sensitisation is required</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>93f2876c-2b83-4e0b-bdc5-6947b6832b6e</t>
+  </si>
+  <si>
+    <t>uuid:93f2876c-2b83-4e0b-bdc5-6947b6832b6e</t>
+  </si>
+  <si>
+    <t>Reminding people to always wash their hands with soap and water</t>
+  </si>
+  <si>
+    <t>Throat pain, muscle pain.   I can protect myself by following SOPs.</t>
+  </si>
+  <si>
+    <t>ab446cac-34fa-48a3-a873-94a99a9313b7</t>
+  </si>
+  <si>
+    <t>uuid:ab446cac-34fa-48a3-a873-94a99a9313b7</t>
+  </si>
+  <si>
+    <t>If a person has received a vaccine of Ebola, can they die</t>
+  </si>
+  <si>
+    <t>P6 pupil</t>
+  </si>
+  <si>
+    <t>Encouraging learns to get involved in the health club activities.</t>
+  </si>
+  <si>
+    <t>Vomiting, headache</t>
+  </si>
+  <si>
+    <t>Call national/district toll-free hotline (0800-100-066 / 8500) Notify local VHT  Isolate them at home and treat with herbs/home care</t>
+  </si>
+  <si>
+    <t>Radio / Megaphone announcer</t>
+  </si>
+  <si>
+    <t>dce6fd67-ff70-4961-bccd-a2665ba7e611</t>
+  </si>
+  <si>
+    <t>uuid:dce6fd67-ff70-4961-bccd-a2665ba7e611</t>
+  </si>
+  <si>
+    <t>More sensitization still needed for parents</t>
+  </si>
+  <si>
+    <t>Vomiting,red eyes</t>
+  </si>
+  <si>
+    <t>Seek prayers / traditional healer</t>
+  </si>
+  <si>
+    <t>52b37879-ad3d-4cf0-affb-060650a4a054</t>
+  </si>
+  <si>
+    <t>uuid:52b37879-ad3d-4cf0-affb-060650a4a054</t>
+  </si>
+  <si>
+    <t>Does Mpox kill</t>
+  </si>
+  <si>
+    <t>Encouraging everyone to always wash their hands</t>
+  </si>
+  <si>
+    <t>Vomiting, body weakness</t>
+  </si>
+  <si>
+    <t>Notify local VHT  LC1 Chairperson immediately Isolate them at home and treat with herbs/home care</t>
+  </si>
+  <si>
+    <t>e243577e-d301-4e23-93c1-7008dc94a5a6</t>
+  </si>
+  <si>
+    <t>uuid:e243577e-d301-4e23-93c1-7008dc94a5a6</t>
+  </si>
+  <si>
+    <t>Ebola is caused by change in climate</t>
+  </si>
+  <si>
+    <t>Body weakness, blood from body openings</t>
+  </si>
+  <si>
+    <t>Call national/district toll-free hotline (0800-100-066 / 8500) LC1 Chairperson immediately</t>
+  </si>
+  <si>
+    <t>a7452c77-e8c5-4404-942d-d7e9c21bd901</t>
+  </si>
+  <si>
+    <t>uuid:a7452c77-e8c5-4404-942d-d7e9c21bd901</t>
+  </si>
+  <si>
+    <t>Uganda Youth Aid primary school</t>
+  </si>
+  <si>
+    <t>The rumor that Ebola is not real</t>
+  </si>
+  <si>
+    <t>Lack of sensitization and adqate hand washinh wquipment</t>
+  </si>
+  <si>
+    <t>More hand washing equipment are needed</t>
+  </si>
+  <si>
+    <t>72a364b8-4a85-4206-a0fd-aee19c050578</t>
+  </si>
+  <si>
+    <t>uuid:72a364b8-4a85-4206-a0fd-aee19c050578</t>
+  </si>
+  <si>
+    <t>Why are these outbreaks in urban areas mostly</t>
+  </si>
+  <si>
+    <t>Area is overpopulated</t>
+  </si>
+  <si>
+    <t>The question is common in the community</t>
+  </si>
+  <si>
+    <t>People in the area need awnsiti7</t>
+  </si>
+  <si>
+    <t>When I was going to have lunch at 2pm</t>
+  </si>
+  <si>
+    <t>At the restaurant, there is some distance</t>
+  </si>
+  <si>
+    <t>b33e3c05-472d-4ac7-9df2-41ffb639c30a</t>
+  </si>
+  <si>
+    <t>uuid:b33e3c05-472d-4ac7-9df2-41ffb639c30a</t>
+  </si>
+  <si>
+    <t>Market leader</t>
+  </si>
+  <si>
+    <t>They are going to put more hand washing equipment in the market and also</t>
+  </si>
+  <si>
+    <t>Ebola is used by government to get donor money</t>
+  </si>
+  <si>
+    <t>Few hand washing equipment with no saop</t>
+  </si>
+  <si>
+    <t>From the youth</t>
+  </si>
+  <si>
+    <t>More hand washing equipment is needed</t>
+  </si>
+  <si>
+    <t>aa8a714b-e7b8-484f-a7ed-ff10213d4774</t>
+  </si>
+  <si>
+    <t>uuid:aa8a714b-e7b8-484f-a7ed-ff10213d4774</t>
+  </si>
+  <si>
+    <t>They committed to support the newly formed Ureport health club, to always put liquid soap and water at the hand washing station.</t>
+  </si>
+  <si>
+    <t>That Ebola is not real</t>
+  </si>
+  <si>
+    <t>Few functional hand Wash equipment</t>
+  </si>
+  <si>
+    <t>There is need for more hand washing with</t>
+  </si>
+  <si>
+    <t>Need for more hand washing equipment</t>
+  </si>
+  <si>
+    <t>90d05f76-faf2-4e37-b88d-3ebffeba3f57</t>
+  </si>
+  <si>
+    <t>uuid:90d05f76-faf2-4e37-b88d-3ebffeba3f57</t>
+  </si>
+  <si>
+    <t>Mpox and Ebola are mainly for the rich</t>
+  </si>
+  <si>
+    <t>Neighbors are me</t>
+  </si>
+  <si>
+    <t>After visiting the washroom</t>
+  </si>
+  <si>
+    <t>At the school gate</t>
+  </si>
+  <si>
+    <t>202b1258-a0a8-408e-bc8e-f52159896d2e</t>
+  </si>
+  <si>
+    <t>uuid:202b1258-a0a8-408e-bc8e-f52159896d2e</t>
+  </si>
+  <si>
+    <t>Do domestic animals have ebola virus</t>
+  </si>
+  <si>
+    <t>P4 pupil</t>
+  </si>
+  <si>
+    <t>Continuous engagements with the parents</t>
+  </si>
+  <si>
+    <t>As I was entering the school gate</t>
+  </si>
+  <si>
+    <t>Dont know</t>
+  </si>
+  <si>
+    <t>I don't have a phone to use.</t>
+  </si>
+  <si>
+    <t>2e9ac8bc-7091-415b-95d2-433c286bc797</t>
+  </si>
+  <si>
+    <t>uuid:2e9ac8bc-7091-415b-95d2-433c286bc797</t>
+  </si>
+  <si>
+    <t>Engagement with different gatekeepers</t>
+  </si>
+  <si>
+    <t>We always wash our hands with soap throughout the day. I can easily spot the signs of Ebola and Mpox</t>
+  </si>
+  <si>
+    <t>After visiting the toilet</t>
+  </si>
+  <si>
+    <t>No soap available</t>
+  </si>
+  <si>
+    <t>Mpox can be observed by seeing skin rushs on the body while malaria can be seen when one has high body temperature</t>
+  </si>
+  <si>
+    <t>I call the school nurse to come and support him.</t>
+  </si>
+  <si>
+    <t>c633ee67-6c86-4fd8-9be8-dc986a161e7c</t>
+  </si>
+  <si>
+    <t>uuid:c633ee67-6c86-4fd8-9be8-dc986a161e7c</t>
+  </si>
+  <si>
+    <t>Is Ebola or Mpox now among the 6 killer diseases</t>
+  </si>
+  <si>
+    <t>If someone gets sick with outbreak signs, I will call the toll-free line or report immediately</t>
+  </si>
+  <si>
+    <t>The only fear would be over asking questions</t>
+  </si>
+  <si>
+    <t>1214d55f-8083-41a1-b988-ede1131a97ff</t>
+  </si>
+  <si>
+    <t>uuid:1214d55f-8083-41a1-b988-ede1131a97ff</t>
+  </si>
+  <si>
+    <t>Encouraging handwashing</t>
+  </si>
+  <si>
+    <t>After eating food</t>
+  </si>
+  <si>
+    <t>At the tap near the kitchen</t>
+  </si>
+  <si>
+    <t>A person with malaria may have high temperature while a person with Mpox has skin rushs</t>
+  </si>
+  <si>
+    <t>I escort that pupil to the isolation room if any.</t>
+  </si>
+  <si>
+    <t>7e961f99-4c83-42cb-93d6-cad85a9a26e6</t>
+  </si>
+  <si>
+    <t>uuid:7e961f99-4c83-42cb-93d6-cad85a9a26e6</t>
+  </si>
+  <si>
+    <t>Progressive SS Kitintale</t>
+  </si>
+  <si>
+    <t>More sensitization and more hand washing equipment needed at school</t>
+  </si>
+  <si>
+    <t>3cb1aa33-17b0-4894-a99f-e81d20fb6c82</t>
+  </si>
+  <si>
+    <t>uuid:3cb1aa33-17b0-4894-a99f-e81d20fb6c82</t>
   </si>
 </sst>
 </file>
@@ -16794,7 +18393,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -17144,8 +18743,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:HF88" totalsRowShown="0">
-  <autoFilter ref="A1:HF88" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:HF163" totalsRowShown="0">
+  <autoFilter ref="A1:HF163" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="214">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="8"/>
@@ -17653,7 +19252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:HF88"/>
+  <dimension ref="A1:HF163"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -28422,6 +30021,8175 @@
         <v>87</v>
       </c>
     </row>
+    <row r="89" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>46293.365824699067</v>
+      </c>
+      <c r="B89" s="1">
+        <v>46293.483164930563</v>
+      </c>
+      <c r="C89" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D89" t="s">
+        <v>903</v>
+      </c>
+      <c r="E89" t="s">
+        <v>254</v>
+      </c>
+      <c r="F89" t="s">
+        <v>355</v>
+      </c>
+      <c r="G89" t="s">
+        <v>198</v>
+      </c>
+      <c r="H89" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ89" t="s">
+        <v>904</v>
+      </c>
+      <c r="AK89" t="s">
+        <v>905</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM89" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>906</v>
+      </c>
+      <c r="AO89" t="s">
+        <v>570</v>
+      </c>
+      <c r="BF89" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ89" t="s">
+        <v>826</v>
+      </c>
+      <c r="BK89">
+        <v>0</v>
+      </c>
+      <c r="BL89">
+        <v>0</v>
+      </c>
+      <c r="BM89">
+        <v>0</v>
+      </c>
+      <c r="BN89">
+        <v>0</v>
+      </c>
+      <c r="BO89">
+        <v>0</v>
+      </c>
+      <c r="BP89">
+        <v>0</v>
+      </c>
+      <c r="BQ89">
+        <v>1</v>
+      </c>
+      <c r="BR89" t="s">
+        <v>908</v>
+      </c>
+      <c r="BS89" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY89" s="1"/>
+      <c r="GQ89" s="1"/>
+      <c r="GR89" s="1"/>
+      <c r="GX89">
+        <v>880072702</v>
+      </c>
+      <c r="GY89" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="GZ89" s="1">
+        <v>46293.358182870368</v>
+      </c>
+      <c r="HA89" s="1"/>
+      <c r="HB89" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD89" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE89" t="s">
+        <v>911</v>
+      </c>
+      <c r="HF89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>46293.48316689815</v>
+      </c>
+      <c r="B90" s="1">
+        <v>46293.491836921297</v>
+      </c>
+      <c r="C90" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D90" t="s">
+        <v>903</v>
+      </c>
+      <c r="E90" t="s">
+        <v>254</v>
+      </c>
+      <c r="F90" t="s">
+        <v>355</v>
+      </c>
+      <c r="G90" t="s">
+        <v>198</v>
+      </c>
+      <c r="H90" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ90" t="s">
+        <v>912</v>
+      </c>
+      <c r="AK90" t="s">
+        <v>913</v>
+      </c>
+      <c r="AL90" t="s">
+        <v>914</v>
+      </c>
+      <c r="AM90" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN90" t="s">
+        <v>915</v>
+      </c>
+      <c r="AO90" t="s">
+        <v>826</v>
+      </c>
+      <c r="AP90" t="s">
+        <v>916</v>
+      </c>
+      <c r="BF90" t="s">
+        <v>917</v>
+      </c>
+      <c r="BG90" t="s">
+        <v>918</v>
+      </c>
+      <c r="BH90" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI90" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ90" t="s">
+        <v>921</v>
+      </c>
+      <c r="BK90">
+        <v>0</v>
+      </c>
+      <c r="BL90">
+        <v>0</v>
+      </c>
+      <c r="BM90">
+        <v>1</v>
+      </c>
+      <c r="BN90">
+        <v>0</v>
+      </c>
+      <c r="BO90">
+        <v>0</v>
+      </c>
+      <c r="BP90">
+        <v>0</v>
+      </c>
+      <c r="BQ90">
+        <v>0</v>
+      </c>
+      <c r="BS90" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY90" s="1"/>
+      <c r="GQ90" s="1"/>
+      <c r="GR90" s="1"/>
+      <c r="GX90">
+        <v>880085623</v>
+      </c>
+      <c r="GY90" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="GZ90" s="1">
+        <v>46293.366851851853</v>
+      </c>
+      <c r="HA90" s="1"/>
+      <c r="HB90" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD90" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE90" t="s">
+        <v>924</v>
+      </c>
+      <c r="HF90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>46293.491838668982</v>
+      </c>
+      <c r="B91" s="1">
+        <v>46293.501660532413</v>
+      </c>
+      <c r="C91" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D91" t="s">
+        <v>903</v>
+      </c>
+      <c r="E91" t="s">
+        <v>254</v>
+      </c>
+      <c r="F91" t="s">
+        <v>355</v>
+      </c>
+      <c r="G91" t="s">
+        <v>198</v>
+      </c>
+      <c r="H91" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ91" t="s">
+        <v>925</v>
+      </c>
+      <c r="AK91" t="s">
+        <v>926</v>
+      </c>
+      <c r="AL91" t="s">
+        <v>927</v>
+      </c>
+      <c r="AM91" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN91" t="s">
+        <v>928</v>
+      </c>
+      <c r="AO91" t="s">
+        <v>570</v>
+      </c>
+      <c r="BF91" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ91" t="s">
+        <v>929</v>
+      </c>
+      <c r="BK91">
+        <v>0</v>
+      </c>
+      <c r="BL91">
+        <v>1</v>
+      </c>
+      <c r="BM91">
+        <v>0</v>
+      </c>
+      <c r="BN91">
+        <v>0</v>
+      </c>
+      <c r="BO91">
+        <v>0</v>
+      </c>
+      <c r="BP91">
+        <v>0</v>
+      </c>
+      <c r="BQ91">
+        <v>0</v>
+      </c>
+      <c r="BS91" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY91" s="1"/>
+      <c r="GQ91" s="1"/>
+      <c r="GR91" s="1"/>
+      <c r="GX91">
+        <v>880099942</v>
+      </c>
+      <c r="GY91" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="GZ91" s="1">
+        <v>46293.376666666663</v>
+      </c>
+      <c r="HA91" s="1"/>
+      <c r="HB91" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD91" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE91" t="s">
+        <v>932</v>
+      </c>
+      <c r="HF91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>46293.50166144676</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46293.511539097221</v>
+      </c>
+      <c r="C92" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D92" t="s">
+        <v>903</v>
+      </c>
+      <c r="E92" t="s">
+        <v>254</v>
+      </c>
+      <c r="F92" t="s">
+        <v>355</v>
+      </c>
+      <c r="G92" t="s">
+        <v>198</v>
+      </c>
+      <c r="H92" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ92" t="s">
+        <v>933</v>
+      </c>
+      <c r="AK92" t="s">
+        <v>934</v>
+      </c>
+      <c r="AL92" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM92" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN92" t="s">
+        <v>935</v>
+      </c>
+      <c r="AO92" t="s">
+        <v>359</v>
+      </c>
+      <c r="BF92" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ92" t="s">
+        <v>936</v>
+      </c>
+      <c r="BK92">
+        <v>1</v>
+      </c>
+      <c r="BL92">
+        <v>0</v>
+      </c>
+      <c r="BM92">
+        <v>0</v>
+      </c>
+      <c r="BN92">
+        <v>0</v>
+      </c>
+      <c r="BO92">
+        <v>0</v>
+      </c>
+      <c r="BP92">
+        <v>0</v>
+      </c>
+      <c r="BQ92">
+        <v>1</v>
+      </c>
+      <c r="BR92" t="s">
+        <v>937</v>
+      </c>
+      <c r="BS92" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY92" s="1"/>
+      <c r="GQ92" s="1"/>
+      <c r="GR92" s="1"/>
+      <c r="GX92">
+        <v>880113235</v>
+      </c>
+      <c r="GY92" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="GZ92" s="1">
+        <v>46293.386550925927</v>
+      </c>
+      <c r="HA92" s="1"/>
+      <c r="HB92" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD92" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE92" t="s">
+        <v>939</v>
+      </c>
+      <c r="HF92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>46293.511540266198</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46293.51593021991</v>
+      </c>
+      <c r="C93" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D93" t="s">
+        <v>903</v>
+      </c>
+      <c r="E93" t="s">
+        <v>254</v>
+      </c>
+      <c r="F93" t="s">
+        <v>355</v>
+      </c>
+      <c r="G93" t="s">
+        <v>198</v>
+      </c>
+      <c r="H93" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ93" t="s">
+        <v>940</v>
+      </c>
+      <c r="AK93" t="s">
+        <v>743</v>
+      </c>
+      <c r="AL93" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM93" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN93" t="s">
+        <v>941</v>
+      </c>
+      <c r="AO93" t="s">
+        <v>570</v>
+      </c>
+      <c r="BF93" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ93" t="s">
+        <v>929</v>
+      </c>
+      <c r="BK93">
+        <v>0</v>
+      </c>
+      <c r="BL93">
+        <v>1</v>
+      </c>
+      <c r="BM93">
+        <v>0</v>
+      </c>
+      <c r="BN93">
+        <v>0</v>
+      </c>
+      <c r="BO93">
+        <v>0</v>
+      </c>
+      <c r="BP93">
+        <v>0</v>
+      </c>
+      <c r="BQ93">
+        <v>0</v>
+      </c>
+      <c r="BS93" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY93" s="1"/>
+      <c r="GQ93" s="1"/>
+      <c r="GR93" s="1"/>
+      <c r="GX93">
+        <v>880119047</v>
+      </c>
+      <c r="GY93" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="GZ93" s="1">
+        <v>46293.3909375</v>
+      </c>
+      <c r="HA93" s="1"/>
+      <c r="HB93" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD93" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE93" t="s">
+        <v>943</v>
+      </c>
+      <c r="HF93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>46293.515931678237</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46293.525055405087</v>
+      </c>
+      <c r="C94" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D94" t="s">
+        <v>903</v>
+      </c>
+      <c r="E94" t="s">
+        <v>254</v>
+      </c>
+      <c r="F94" t="s">
+        <v>355</v>
+      </c>
+      <c r="G94" t="s">
+        <v>198</v>
+      </c>
+      <c r="H94" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ94" t="s">
+        <v>944</v>
+      </c>
+      <c r="AK94" t="s">
+        <v>945</v>
+      </c>
+      <c r="AL94" t="s">
+        <v>946</v>
+      </c>
+      <c r="AM94" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN94" t="s">
+        <v>906</v>
+      </c>
+      <c r="AO94" t="s">
+        <v>947</v>
+      </c>
+      <c r="BF94" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ94" t="s">
+        <v>948</v>
+      </c>
+      <c r="BK94">
+        <v>0</v>
+      </c>
+      <c r="BL94">
+        <v>0</v>
+      </c>
+      <c r="BM94">
+        <v>0</v>
+      </c>
+      <c r="BN94">
+        <v>1</v>
+      </c>
+      <c r="BO94">
+        <v>0</v>
+      </c>
+      <c r="BP94">
+        <v>0</v>
+      </c>
+      <c r="BQ94">
+        <v>0</v>
+      </c>
+      <c r="BS94" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY94" s="1"/>
+      <c r="GQ94" s="1"/>
+      <c r="GR94" s="1"/>
+      <c r="GX94">
+        <v>880132044</v>
+      </c>
+      <c r="GY94" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="GZ94" s="1">
+        <v>46293.400057870371</v>
+      </c>
+      <c r="HA94" s="1"/>
+      <c r="HB94" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD94" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE94" t="s">
+        <v>950</v>
+      </c>
+      <c r="HF94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>46292.875610428237</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46293.535827777778</v>
+      </c>
+      <c r="C95" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D95" t="s">
+        <v>903</v>
+      </c>
+      <c r="E95" t="s">
+        <v>196</v>
+      </c>
+      <c r="F95" t="s">
+        <v>196</v>
+      </c>
+      <c r="G95" t="s">
+        <v>198</v>
+      </c>
+      <c r="H95" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ95" t="s">
+        <v>951</v>
+      </c>
+      <c r="AK95" t="s">
+        <v>952</v>
+      </c>
+      <c r="AL95" t="s">
+        <v>953</v>
+      </c>
+      <c r="AM95" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN95" t="s">
+        <v>954</v>
+      </c>
+      <c r="AO95" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF95" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG95" t="s">
+        <v>956</v>
+      </c>
+      <c r="BH95" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI95" t="s">
+        <v>957</v>
+      </c>
+      <c r="BJ95" t="s">
+        <v>958</v>
+      </c>
+      <c r="BK95">
+        <v>0</v>
+      </c>
+      <c r="BL95">
+        <v>1</v>
+      </c>
+      <c r="BM95">
+        <v>1</v>
+      </c>
+      <c r="BN95">
+        <v>0</v>
+      </c>
+      <c r="BO95">
+        <v>0</v>
+      </c>
+      <c r="BP95">
+        <v>1</v>
+      </c>
+      <c r="BQ95">
+        <v>0</v>
+      </c>
+      <c r="BS95" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY95" s="1"/>
+      <c r="GQ95" s="1"/>
+      <c r="GR95" s="1"/>
+      <c r="GX95">
+        <v>880146776</v>
+      </c>
+      <c r="GY95" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="GZ95" s="1">
+        <v>46293.410856481481</v>
+      </c>
+      <c r="HA95" s="1"/>
+      <c r="HB95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD95" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE95" t="s">
+        <v>960</v>
+      </c>
+      <c r="HF95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>46293.525056585648</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46293.536306099537</v>
+      </c>
+      <c r="C96" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D96" t="s">
+        <v>903</v>
+      </c>
+      <c r="E96" t="s">
+        <v>254</v>
+      </c>
+      <c r="F96" t="s">
+        <v>256</v>
+      </c>
+      <c r="G96" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ96" t="s">
+        <v>961</v>
+      </c>
+      <c r="AK96" t="s">
+        <v>962</v>
+      </c>
+      <c r="AL96" t="s">
+        <v>963</v>
+      </c>
+      <c r="AM96" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN96" t="s">
+        <v>964</v>
+      </c>
+      <c r="AO96" t="s">
+        <v>826</v>
+      </c>
+      <c r="AP96" t="s">
+        <v>965</v>
+      </c>
+      <c r="BF96" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ96" t="s">
+        <v>936</v>
+      </c>
+      <c r="BK96">
+        <v>1</v>
+      </c>
+      <c r="BL96">
+        <v>0</v>
+      </c>
+      <c r="BM96">
+        <v>0</v>
+      </c>
+      <c r="BN96">
+        <v>0</v>
+      </c>
+      <c r="BO96">
+        <v>0</v>
+      </c>
+      <c r="BP96">
+        <v>0</v>
+      </c>
+      <c r="BQ96">
+        <v>1</v>
+      </c>
+      <c r="BR96" t="s">
+        <v>966</v>
+      </c>
+      <c r="BS96" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY96" s="1"/>
+      <c r="GQ96" s="1"/>
+      <c r="GR96" s="1"/>
+      <c r="GX96">
+        <v>880147393</v>
+      </c>
+      <c r="GY96" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="GZ96" s="1">
+        <v>46293.411307870367</v>
+      </c>
+      <c r="HA96" s="1"/>
+      <c r="HB96" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD96" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE96" t="s">
+        <v>968</v>
+      </c>
+      <c r="HF96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>46293.462860451393</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46293.539335636568</v>
+      </c>
+      <c r="C97" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D97" t="s">
+        <v>969</v>
+      </c>
+      <c r="E97" t="s">
+        <v>210</v>
+      </c>
+      <c r="F97" t="s">
+        <v>401</v>
+      </c>
+      <c r="G97" t="s">
+        <v>198</v>
+      </c>
+      <c r="H97" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ97" t="s">
+        <v>970</v>
+      </c>
+      <c r="AK97" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL97" t="s">
+        <v>972</v>
+      </c>
+      <c r="AM97" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN97" t="s">
+        <v>973</v>
+      </c>
+      <c r="AO97" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU97" t="s">
+        <v>974</v>
+      </c>
+      <c r="BV97" t="s">
+        <v>975</v>
+      </c>
+      <c r="BW97">
+        <v>0</v>
+      </c>
+      <c r="BX97">
+        <v>1</v>
+      </c>
+      <c r="BY97">
+        <v>1</v>
+      </c>
+      <c r="BZ97">
+        <v>0</v>
+      </c>
+      <c r="CA97">
+        <v>1</v>
+      </c>
+      <c r="CK97" t="s">
+        <v>976</v>
+      </c>
+      <c r="CL97" t="s">
+        <v>977</v>
+      </c>
+      <c r="CM97" t="s">
+        <v>978</v>
+      </c>
+      <c r="CO97" t="s">
+        <v>979</v>
+      </c>
+      <c r="CP97" t="s">
+        <v>980</v>
+      </c>
+      <c r="CQ97" t="s">
+        <v>981</v>
+      </c>
+      <c r="CW97" t="s">
+        <v>982</v>
+      </c>
+      <c r="CX97" t="s">
+        <v>983</v>
+      </c>
+      <c r="CY97" t="s">
+        <v>984</v>
+      </c>
+      <c r="EY97" s="1"/>
+      <c r="GQ97" s="1"/>
+      <c r="GR97" s="1"/>
+      <c r="GX97">
+        <v>880151351</v>
+      </c>
+      <c r="GY97" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="GZ97" s="1">
+        <v>46293.414375</v>
+      </c>
+      <c r="HA97" s="1"/>
+      <c r="HB97" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD97" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE97" t="s">
+        <v>986</v>
+      </c>
+      <c r="HF97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>46293.542157442127</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46293.625741805547</v>
+      </c>
+      <c r="C98" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D98" t="s">
+        <v>969</v>
+      </c>
+      <c r="E98" t="s">
+        <v>210</v>
+      </c>
+      <c r="F98" t="s">
+        <v>987</v>
+      </c>
+      <c r="G98" t="s">
+        <v>198</v>
+      </c>
+      <c r="H98" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ98" t="s">
+        <v>988</v>
+      </c>
+      <c r="AK98" t="s">
+        <v>989</v>
+      </c>
+      <c r="AL98" t="s">
+        <v>990</v>
+      </c>
+      <c r="AM98" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN98" t="s">
+        <v>991</v>
+      </c>
+      <c r="AO98" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU98" t="s">
+        <v>992</v>
+      </c>
+      <c r="BV98" t="s">
+        <v>993</v>
+      </c>
+      <c r="BW98">
+        <v>1</v>
+      </c>
+      <c r="BX98">
+        <v>0</v>
+      </c>
+      <c r="BY98">
+        <v>0</v>
+      </c>
+      <c r="BZ98">
+        <v>0</v>
+      </c>
+      <c r="CA98">
+        <v>1</v>
+      </c>
+      <c r="CC98" t="s">
+        <v>994</v>
+      </c>
+      <c r="CD98" t="s">
+        <v>995</v>
+      </c>
+      <c r="CE98" t="s">
+        <v>996</v>
+      </c>
+      <c r="CF98">
+        <v>1</v>
+      </c>
+      <c r="CG98">
+        <v>0</v>
+      </c>
+      <c r="CH98">
+        <v>0</v>
+      </c>
+      <c r="CI98" t="s">
+        <v>997</v>
+      </c>
+      <c r="CW98" t="s">
+        <v>998</v>
+      </c>
+      <c r="CX98" t="s">
+        <v>999</v>
+      </c>
+      <c r="CY98" t="s">
+        <v>1000</v>
+      </c>
+      <c r="EY98" s="1"/>
+      <c r="GQ98" s="1"/>
+      <c r="GR98" s="1"/>
+      <c r="GX98">
+        <v>880263337</v>
+      </c>
+      <c r="GY98" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="GZ98" s="1">
+        <v>46293.500798611109</v>
+      </c>
+      <c r="HA98" s="1"/>
+      <c r="HB98" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD98" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE98" t="s">
+        <v>1002</v>
+      </c>
+      <c r="HF98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>46289.549434942128</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46293.718195949077</v>
+      </c>
+      <c r="C99" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D99" t="s">
+        <v>707</v>
+      </c>
+      <c r="E99" t="s">
+        <v>309</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G99" t="s">
+        <v>198</v>
+      </c>
+      <c r="H99" t="s">
+        <v>311</v>
+      </c>
+      <c r="J99" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K99" t="s">
+        <v>201</v>
+      </c>
+      <c r="L99">
+        <v>780</v>
+      </c>
+      <c r="M99">
+        <v>8</v>
+      </c>
+      <c r="N99">
+        <v>12</v>
+      </c>
+      <c r="O99">
+        <v>2</v>
+      </c>
+      <c r="P99">
+        <v>2</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>324</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99" t="s">
+        <v>340</v>
+      </c>
+      <c r="T99" t="s">
+        <v>341</v>
+      </c>
+      <c r="U99" t="s">
+        <v>203</v>
+      </c>
+      <c r="V99" t="s">
+        <v>202</v>
+      </c>
+      <c r="W99" t="s">
+        <v>217</v>
+      </c>
+      <c r="X99" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>205</v>
+      </c>
+      <c r="AJ99" t="s">
+        <v>1005</v>
+      </c>
+      <c r="AK99" t="s">
+        <v>1006</v>
+      </c>
+      <c r="AL99" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AM99" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN99" t="s">
+        <v>1008</v>
+      </c>
+      <c r="EY99" s="1"/>
+      <c r="GQ99" s="1"/>
+      <c r="GR99" s="1"/>
+      <c r="GX99">
+        <v>880408370</v>
+      </c>
+      <c r="GY99" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="GZ99" s="1">
+        <v>46293.593206018522</v>
+      </c>
+      <c r="HA99" s="1"/>
+      <c r="HB99" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD99" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE99" t="s">
+        <v>1010</v>
+      </c>
+      <c r="HF99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>46288.648351516204</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46293.732373553241</v>
+      </c>
+      <c r="C100" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D100" t="s">
+        <v>792</v>
+      </c>
+      <c r="E100" t="s">
+        <v>309</v>
+      </c>
+      <c r="F100" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G100" t="s">
+        <v>198</v>
+      </c>
+      <c r="H100" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ100" t="s">
+        <v>1012</v>
+      </c>
+      <c r="AK100" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AL100" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AM100" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN100" t="s">
+        <v>1015</v>
+      </c>
+      <c r="EY100" s="1"/>
+      <c r="EZ100" s="1">
+        <v>46290</v>
+      </c>
+      <c r="FA100" t="s">
+        <v>1016</v>
+      </c>
+      <c r="FB100" t="s">
+        <v>376</v>
+      </c>
+      <c r="FD100">
+        <v>380</v>
+      </c>
+      <c r="FE100">
+        <v>400</v>
+      </c>
+      <c r="FF100">
+        <v>9</v>
+      </c>
+      <c r="FG100">
+        <v>6</v>
+      </c>
+      <c r="FH100" t="s">
+        <v>324</v>
+      </c>
+      <c r="FJ100" t="s">
+        <v>377</v>
+      </c>
+      <c r="FK100" t="s">
+        <v>378</v>
+      </c>
+      <c r="FL100" t="s">
+        <v>428</v>
+      </c>
+      <c r="FN100" t="s">
+        <v>429</v>
+      </c>
+      <c r="FO100">
+        <v>3</v>
+      </c>
+      <c r="FP100" t="s">
+        <v>430</v>
+      </c>
+      <c r="FQ100" t="s">
+        <v>382</v>
+      </c>
+      <c r="FR100">
+        <v>3</v>
+      </c>
+      <c r="FS100">
+        <v>4</v>
+      </c>
+      <c r="FT100" t="s">
+        <v>383</v>
+      </c>
+      <c r="FU100" t="s">
+        <v>384</v>
+      </c>
+      <c r="FV100" t="s">
+        <v>385</v>
+      </c>
+      <c r="FW100">
+        <v>0</v>
+      </c>
+      <c r="FX100">
+        <v>0</v>
+      </c>
+      <c r="FY100">
+        <v>1</v>
+      </c>
+      <c r="FZ100">
+        <v>0</v>
+      </c>
+      <c r="GA100" t="s">
+        <v>324</v>
+      </c>
+      <c r="GC100">
+        <v>10</v>
+      </c>
+      <c r="GD100">
+        <v>9</v>
+      </c>
+      <c r="GE100">
+        <v>6</v>
+      </c>
+      <c r="GF100">
+        <v>7</v>
+      </c>
+      <c r="GG100">
+        <v>3</v>
+      </c>
+      <c r="GH100">
+        <v>6</v>
+      </c>
+      <c r="GQ100" s="1"/>
+      <c r="GR100" s="1"/>
+      <c r="GX100">
+        <v>880430380</v>
+      </c>
+      <c r="GY100" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="GZ100" s="1">
+        <v>46293.60738425926</v>
+      </c>
+      <c r="HA100" s="1"/>
+      <c r="HB100" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD100" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE100" t="s">
+        <v>1018</v>
+      </c>
+      <c r="HF100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>46293.729340034719</v>
+      </c>
+      <c r="B101" s="1">
+        <v>46293.732859814823</v>
+      </c>
+      <c r="C101" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D101" t="s">
+        <v>707</v>
+      </c>
+      <c r="E101" t="s">
+        <v>295</v>
+      </c>
+      <c r="F101" t="s">
+        <v>305</v>
+      </c>
+      <c r="G101" t="s">
+        <v>198</v>
+      </c>
+      <c r="H101" t="s">
+        <v>297</v>
+      </c>
+      <c r="J101" t="s">
+        <v>455</v>
+      </c>
+      <c r="K101" t="s">
+        <v>201</v>
+      </c>
+      <c r="L101">
+        <v>714</v>
+      </c>
+      <c r="M101">
+        <v>321</v>
+      </c>
+      <c r="N101">
+        <v>393</v>
+      </c>
+      <c r="O101">
+        <v>16</v>
+      </c>
+      <c r="P101">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>395</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+      <c r="S101" t="s">
+        <v>214</v>
+      </c>
+      <c r="T101" t="s">
+        <v>313</v>
+      </c>
+      <c r="U101" t="s">
+        <v>217</v>
+      </c>
+      <c r="V101" t="s">
+        <v>202</v>
+      </c>
+      <c r="W101" t="s">
+        <v>217</v>
+      </c>
+      <c r="X101" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ101" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AK101" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AL101" t="s">
+        <v>1021</v>
+      </c>
+      <c r="AM101" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN101" t="s">
+        <v>1022</v>
+      </c>
+      <c r="EY101" s="1"/>
+      <c r="GQ101" s="1"/>
+      <c r="GR101" s="1"/>
+      <c r="GX101">
+        <v>880431405</v>
+      </c>
+      <c r="GY101" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="GZ101" s="1">
+        <v>46293.607870370368</v>
+      </c>
+      <c r="HA101" s="1"/>
+      <c r="HB101" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD101" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE101" t="s">
+        <v>1024</v>
+      </c>
+      <c r="HF101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>46293.732859988428</v>
+      </c>
+      <c r="B102" s="1">
+        <v>46293.736794259261</v>
+      </c>
+      <c r="C102" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D102" t="s">
+        <v>354</v>
+      </c>
+      <c r="E102" t="s">
+        <v>295</v>
+      </c>
+      <c r="F102" t="s">
+        <v>338</v>
+      </c>
+      <c r="G102" t="s">
+        <v>198</v>
+      </c>
+      <c r="H102" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ102" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AK102" t="s">
+        <v>1026</v>
+      </c>
+      <c r="AL102" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AM102" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN102" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AO102" t="s">
+        <v>463</v>
+      </c>
+      <c r="AR102" t="s">
+        <v>520</v>
+      </c>
+      <c r="AS102">
+        <v>0</v>
+      </c>
+      <c r="AT102">
+        <v>1600</v>
+      </c>
+      <c r="AU102" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV102" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AW102" t="s">
+        <v>522</v>
+      </c>
+      <c r="AX102" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AY102" t="s">
+        <v>465</v>
+      </c>
+      <c r="BA102" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB102" t="s">
+        <v>1031</v>
+      </c>
+      <c r="BC102" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD102" t="s">
+        <v>395</v>
+      </c>
+      <c r="EY102" s="1"/>
+      <c r="GQ102" s="1"/>
+      <c r="GR102" s="1"/>
+      <c r="GX102">
+        <v>880436810</v>
+      </c>
+      <c r="GY102" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="GZ102" s="1">
+        <v>46293.611805555563</v>
+      </c>
+      <c r="HA102" s="1"/>
+      <c r="HB102" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD102" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE102" t="s">
+        <v>1033</v>
+      </c>
+      <c r="HF102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>46293.73679451389</v>
+      </c>
+      <c r="B103" s="1">
+        <v>46293.740749988428</v>
+      </c>
+      <c r="C103" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D103" t="s">
+        <v>354</v>
+      </c>
+      <c r="E103" t="s">
+        <v>295</v>
+      </c>
+      <c r="F103" t="s">
+        <v>338</v>
+      </c>
+      <c r="G103" t="s">
+        <v>198</v>
+      </c>
+      <c r="H103" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ103" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AK103" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AL103" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AM103" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN103" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AO103" t="s">
+        <v>561</v>
+      </c>
+      <c r="AR103" t="s">
+        <v>404</v>
+      </c>
+      <c r="AS103">
+        <v>0</v>
+      </c>
+      <c r="AT103">
+        <v>300</v>
+      </c>
+      <c r="AU103" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV103" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AW103" t="s">
+        <v>522</v>
+      </c>
+      <c r="AX103" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AY103" t="s">
+        <v>465</v>
+      </c>
+      <c r="BA103" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB103" t="s">
+        <v>1040</v>
+      </c>
+      <c r="BC103" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD103" t="s">
+        <v>395</v>
+      </c>
+      <c r="EY103" s="1"/>
+      <c r="GQ103" s="1"/>
+      <c r="GR103" s="1"/>
+      <c r="GX103">
+        <v>880442475</v>
+      </c>
+      <c r="GY103" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="GZ103" s="1">
+        <v>46293.615763888891</v>
+      </c>
+      <c r="HA103" s="1"/>
+      <c r="HB103" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD103" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE103" t="s">
+        <v>1042</v>
+      </c>
+      <c r="HF103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>46293.731438472219</v>
+      </c>
+      <c r="B104" s="1">
+        <v>46293.803376898148</v>
+      </c>
+      <c r="C104" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D104" t="s">
+        <v>969</v>
+      </c>
+      <c r="E104" t="s">
+        <v>254</v>
+      </c>
+      <c r="F104" t="s">
+        <v>355</v>
+      </c>
+      <c r="G104" t="s">
+        <v>198</v>
+      </c>
+      <c r="H104" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ104" t="s">
+        <v>1043</v>
+      </c>
+      <c r="AK104" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AL104" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM104" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN104" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AO104" t="s">
+        <v>570</v>
+      </c>
+      <c r="BU104" t="s">
+        <v>992</v>
+      </c>
+      <c r="BV104" t="s">
+        <v>1046</v>
+      </c>
+      <c r="BW104">
+        <v>0</v>
+      </c>
+      <c r="BX104">
+        <v>0</v>
+      </c>
+      <c r="BY104">
+        <v>1</v>
+      </c>
+      <c r="BZ104">
+        <v>1</v>
+      </c>
+      <c r="CA104">
+        <v>0</v>
+      </c>
+      <c r="CO104" t="s">
+        <v>979</v>
+      </c>
+      <c r="CP104" t="s">
+        <v>1047</v>
+      </c>
+      <c r="CQ104" t="s">
+        <v>981</v>
+      </c>
+      <c r="CS104" t="s">
+        <v>1048</v>
+      </c>
+      <c r="CT104" t="s">
+        <v>1049</v>
+      </c>
+      <c r="CU104" t="s">
+        <v>1050</v>
+      </c>
+      <c r="EY104" s="1"/>
+      <c r="GQ104" s="1"/>
+      <c r="GR104" s="1"/>
+      <c r="GX104">
+        <v>880538561</v>
+      </c>
+      <c r="GY104" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="GZ104" s="1">
+        <v>46293.678379629629</v>
+      </c>
+      <c r="HA104" s="1"/>
+      <c r="HB104" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD104" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE104" t="s">
+        <v>1052</v>
+      </c>
+      <c r="HF104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>46293.815275972222</v>
+      </c>
+      <c r="B105" s="1">
+        <v>46293.821052870371</v>
+      </c>
+      <c r="C105" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D105" t="s">
+        <v>354</v>
+      </c>
+      <c r="E105" t="s">
+        <v>280</v>
+      </c>
+      <c r="F105" t="s">
+        <v>672</v>
+      </c>
+      <c r="G105" t="s">
+        <v>198</v>
+      </c>
+      <c r="H105" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ105" t="s">
+        <v>628</v>
+      </c>
+      <c r="AK105" t="s">
+        <v>1053</v>
+      </c>
+      <c r="AL105" t="s">
+        <v>628</v>
+      </c>
+      <c r="AM105" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN105" t="s">
+        <v>1054</v>
+      </c>
+      <c r="AO105" t="s">
+        <v>463</v>
+      </c>
+      <c r="AR105" t="s">
+        <v>520</v>
+      </c>
+      <c r="AS105">
+        <v>0</v>
+      </c>
+      <c r="AT105">
+        <v>500</v>
+      </c>
+      <c r="AU105" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV105" t="s">
+        <v>628</v>
+      </c>
+      <c r="AW105" t="s">
+        <v>392</v>
+      </c>
+      <c r="AX105" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AY105" t="s">
+        <v>475</v>
+      </c>
+      <c r="AZ105" t="s">
+        <v>395</v>
+      </c>
+      <c r="BA105" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB105" t="s">
+        <v>1056</v>
+      </c>
+      <c r="BC105" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD105" t="s">
+        <v>628</v>
+      </c>
+      <c r="EY105" s="1"/>
+      <c r="GQ105" s="1"/>
+      <c r="GR105" s="1"/>
+      <c r="GX105">
+        <v>880544752</v>
+      </c>
+      <c r="GY105" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="GZ105" s="1">
+        <v>46293.682858796303</v>
+      </c>
+      <c r="HA105" s="1"/>
+      <c r="HB105" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD105" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE105" t="s">
+        <v>1058</v>
+      </c>
+      <c r="HF105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>46293.823807754627</v>
+      </c>
+      <c r="B106" s="1">
+        <v>46293.830123020831</v>
+      </c>
+      <c r="C106" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D106" t="s">
+        <v>354</v>
+      </c>
+      <c r="E106" t="s">
+        <v>280</v>
+      </c>
+      <c r="F106" t="s">
+        <v>672</v>
+      </c>
+      <c r="G106" t="s">
+        <v>198</v>
+      </c>
+      <c r="H106" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ106" t="s">
+        <v>628</v>
+      </c>
+      <c r="AK106" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AL106" t="s">
+        <v>628</v>
+      </c>
+      <c r="AM106" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN106" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AO106" t="s">
+        <v>570</v>
+      </c>
+      <c r="AR106" t="s">
+        <v>520</v>
+      </c>
+      <c r="AS106">
+        <v>1</v>
+      </c>
+      <c r="AT106">
+        <v>375</v>
+      </c>
+      <c r="AU106" t="s">
+        <v>571</v>
+      </c>
+      <c r="AV106" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AW106" t="s">
+        <v>522</v>
+      </c>
+      <c r="AX106" t="s">
+        <v>1062</v>
+      </c>
+      <c r="AY106" t="s">
+        <v>365</v>
+      </c>
+      <c r="AZ106" t="s">
+        <v>324</v>
+      </c>
+      <c r="BA106" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB106" t="s">
+        <v>1063</v>
+      </c>
+      <c r="BC106" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD106" t="s">
+        <v>628</v>
+      </c>
+      <c r="EY106" s="1"/>
+      <c r="GQ106" s="1"/>
+      <c r="GR106" s="1"/>
+      <c r="GX106">
+        <v>880555781</v>
+      </c>
+      <c r="GY106" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="GZ106" s="1">
+        <v>46293.691932870373</v>
+      </c>
+      <c r="HA106" s="1"/>
+      <c r="HB106" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD106" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE106" t="s">
+        <v>1065</v>
+      </c>
+      <c r="HF106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>46293.803378958342</v>
+      </c>
+      <c r="B107" s="1">
+        <v>46293.85530383102</v>
+      </c>
+      <c r="C107" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D107" t="s">
+        <v>969</v>
+      </c>
+      <c r="E107" t="s">
+        <v>254</v>
+      </c>
+      <c r="F107" t="s">
+        <v>355</v>
+      </c>
+      <c r="G107" t="s">
+        <v>198</v>
+      </c>
+      <c r="H107" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ107" t="s">
+        <v>1066</v>
+      </c>
+      <c r="AK107" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AL107" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM107" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN107" t="s">
+        <v>1068</v>
+      </c>
+      <c r="AO107" t="s">
+        <v>570</v>
+      </c>
+      <c r="BU107" t="s">
+        <v>791</v>
+      </c>
+      <c r="BV107" t="s">
+        <v>1069</v>
+      </c>
+      <c r="BW107">
+        <v>1</v>
+      </c>
+      <c r="BX107">
+        <v>1</v>
+      </c>
+      <c r="BY107">
+        <v>1</v>
+      </c>
+      <c r="BZ107">
+        <v>1</v>
+      </c>
+      <c r="CA107">
+        <v>1</v>
+      </c>
+      <c r="CC107" t="s">
+        <v>1070</v>
+      </c>
+      <c r="CD107" t="s">
+        <v>1071</v>
+      </c>
+      <c r="CE107" t="s">
+        <v>1072</v>
+      </c>
+      <c r="CF107">
+        <v>1</v>
+      </c>
+      <c r="CG107">
+        <v>1</v>
+      </c>
+      <c r="CH107">
+        <v>0</v>
+      </c>
+      <c r="CI107" t="s">
+        <v>997</v>
+      </c>
+      <c r="CK107" t="s">
+        <v>1073</v>
+      </c>
+      <c r="CL107" t="s">
+        <v>1074</v>
+      </c>
+      <c r="CM107" t="s">
+        <v>1075</v>
+      </c>
+      <c r="CO107" t="s">
+        <v>979</v>
+      </c>
+      <c r="CP107" t="s">
+        <v>1076</v>
+      </c>
+      <c r="CQ107" t="s">
+        <v>981</v>
+      </c>
+      <c r="CS107" t="s">
+        <v>1077</v>
+      </c>
+      <c r="CT107" t="s">
+        <v>395</v>
+      </c>
+      <c r="CU107" t="s">
+        <v>1078</v>
+      </c>
+      <c r="CW107" t="s">
+        <v>1079</v>
+      </c>
+      <c r="CX107" t="s">
+        <v>1080</v>
+      </c>
+      <c r="CY107" t="s">
+        <v>984</v>
+      </c>
+      <c r="EY107" s="1"/>
+      <c r="GQ107" s="1"/>
+      <c r="GR107" s="1"/>
+      <c r="GX107">
+        <v>880607706</v>
+      </c>
+      <c r="GY107" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="GZ107" s="1">
+        <v>46293.730312500003</v>
+      </c>
+      <c r="HA107" s="1"/>
+      <c r="HB107" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD107" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE107" t="s">
+        <v>1082</v>
+      </c>
+      <c r="HF107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>46293.813637777777</v>
+      </c>
+      <c r="B108" s="1">
+        <v>46293.855407986113</v>
+      </c>
+      <c r="C108" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D108" t="s">
+        <v>969</v>
+      </c>
+      <c r="E108" t="s">
+        <v>254</v>
+      </c>
+      <c r="F108" t="s">
+        <v>355</v>
+      </c>
+      <c r="G108" t="s">
+        <v>198</v>
+      </c>
+      <c r="H108" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ108" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AK108" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AL108" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM108" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AO108" t="s">
+        <v>570</v>
+      </c>
+      <c r="BU108" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BV108" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BW108">
+        <v>0</v>
+      </c>
+      <c r="BX108">
+        <v>1</v>
+      </c>
+      <c r="BY108">
+        <v>0</v>
+      </c>
+      <c r="BZ108">
+        <v>1</v>
+      </c>
+      <c r="CA108">
+        <v>0</v>
+      </c>
+      <c r="CK108" t="s">
+        <v>1088</v>
+      </c>
+      <c r="CL108" t="s">
+        <v>1089</v>
+      </c>
+      <c r="CM108" t="s">
+        <v>1090</v>
+      </c>
+      <c r="CS108" t="s">
+        <v>1091</v>
+      </c>
+      <c r="CT108" t="s">
+        <v>395</v>
+      </c>
+      <c r="CU108" t="s">
+        <v>1050</v>
+      </c>
+      <c r="EY108" s="1"/>
+      <c r="GQ108" s="1"/>
+      <c r="GR108" s="1"/>
+      <c r="GX108">
+        <v>880607824</v>
+      </c>
+      <c r="GY108" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="GZ108" s="1">
+        <v>46293.730416666673</v>
+      </c>
+      <c r="HA108" s="1"/>
+      <c r="HB108" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD108" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE108" t="s">
+        <v>1093</v>
+      </c>
+      <c r="HF108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>46293.816578796293</v>
+      </c>
+      <c r="B109" s="1">
+        <v>46293.855511747694</v>
+      </c>
+      <c r="C109" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D109" t="s">
+        <v>969</v>
+      </c>
+      <c r="E109" t="s">
+        <v>254</v>
+      </c>
+      <c r="F109" t="s">
+        <v>355</v>
+      </c>
+      <c r="G109" t="s">
+        <v>198</v>
+      </c>
+      <c r="H109" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ109" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AK109" t="s">
+        <v>743</v>
+      </c>
+      <c r="AL109" t="s">
+        <v>914</v>
+      </c>
+      <c r="AM109" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN109" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AO109" t="s">
+        <v>570</v>
+      </c>
+      <c r="BU109" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BV109" t="s">
+        <v>1096</v>
+      </c>
+      <c r="BW109">
+        <v>1</v>
+      </c>
+      <c r="BX109">
+        <v>0</v>
+      </c>
+      <c r="BY109">
+        <v>1</v>
+      </c>
+      <c r="BZ109">
+        <v>0</v>
+      </c>
+      <c r="CA109">
+        <v>0</v>
+      </c>
+      <c r="CC109" t="s">
+        <v>1097</v>
+      </c>
+      <c r="CD109" t="s">
+        <v>1098</v>
+      </c>
+      <c r="CE109" t="s">
+        <v>1099</v>
+      </c>
+      <c r="CF109">
+        <v>1</v>
+      </c>
+      <c r="CG109">
+        <v>0</v>
+      </c>
+      <c r="CH109">
+        <v>1</v>
+      </c>
+      <c r="CI109" t="s">
+        <v>1100</v>
+      </c>
+      <c r="CO109" t="s">
+        <v>1101</v>
+      </c>
+      <c r="CP109" t="s">
+        <v>1102</v>
+      </c>
+      <c r="CQ109" t="s">
+        <v>1103</v>
+      </c>
+      <c r="EY109" s="1"/>
+      <c r="GQ109" s="1"/>
+      <c r="GR109" s="1"/>
+      <c r="GX109">
+        <v>880607945</v>
+      </c>
+      <c r="GY109" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="GZ109" s="1">
+        <v>46293.730509259258</v>
+      </c>
+      <c r="HA109" s="1"/>
+      <c r="HB109" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD109" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE109" t="s">
+        <v>1105</v>
+      </c>
+      <c r="HF109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>46293.625744837962</v>
+      </c>
+      <c r="B110" s="1">
+        <v>46294.48826327546</v>
+      </c>
+      <c r="C110" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D110" t="s">
+        <v>969</v>
+      </c>
+      <c r="E110" t="s">
+        <v>210</v>
+      </c>
+      <c r="F110" t="s">
+        <v>401</v>
+      </c>
+      <c r="G110" t="s">
+        <v>198</v>
+      </c>
+      <c r="H110" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ110" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK110" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL110" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM110" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN110" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AO110" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU110" t="s">
+        <v>992</v>
+      </c>
+      <c r="BV110" t="s">
+        <v>1107</v>
+      </c>
+      <c r="BW110">
+        <v>1</v>
+      </c>
+      <c r="BX110">
+        <v>0</v>
+      </c>
+      <c r="BY110">
+        <v>0</v>
+      </c>
+      <c r="BZ110">
+        <v>0</v>
+      </c>
+      <c r="CA110">
+        <v>0</v>
+      </c>
+      <c r="CC110" t="s">
+        <v>1108</v>
+      </c>
+      <c r="CD110" t="s">
+        <v>1109</v>
+      </c>
+      <c r="CE110" t="s">
+        <v>1072</v>
+      </c>
+      <c r="CF110">
+        <v>1</v>
+      </c>
+      <c r="CG110">
+        <v>1</v>
+      </c>
+      <c r="CH110">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="s">
+        <v>997</v>
+      </c>
+      <c r="EY110" s="1"/>
+      <c r="GQ110" s="1"/>
+      <c r="GR110" s="1"/>
+      <c r="GX110">
+        <v>881103441</v>
+      </c>
+      <c r="GY110" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="GZ110" s="1">
+        <v>46294.363298611112</v>
+      </c>
+      <c r="HA110" s="1"/>
+      <c r="HB110" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD110" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE110" t="s">
+        <v>1111</v>
+      </c>
+      <c r="HF110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>46294.488265138891</v>
+      </c>
+      <c r="B111" s="1">
+        <v>46294.491391134259</v>
+      </c>
+      <c r="C111" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D111" t="s">
+        <v>969</v>
+      </c>
+      <c r="E111" t="s">
+        <v>210</v>
+      </c>
+      <c r="F111" t="s">
+        <v>401</v>
+      </c>
+      <c r="G111" t="s">
+        <v>198</v>
+      </c>
+      <c r="H111" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ111" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AK111" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL111" t="s">
+        <v>972</v>
+      </c>
+      <c r="AM111" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN111" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AO111" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU111" t="s">
+        <v>974</v>
+      </c>
+      <c r="BV111" t="s">
+        <v>993</v>
+      </c>
+      <c r="BW111">
+        <v>1</v>
+      </c>
+      <c r="BX111">
+        <v>0</v>
+      </c>
+      <c r="BY111">
+        <v>0</v>
+      </c>
+      <c r="BZ111">
+        <v>0</v>
+      </c>
+      <c r="CA111">
+        <v>1</v>
+      </c>
+      <c r="CC111" t="s">
+        <v>1114</v>
+      </c>
+      <c r="CD111" t="s">
+        <v>1115</v>
+      </c>
+      <c r="CE111" t="s">
+        <v>1072</v>
+      </c>
+      <c r="CF111">
+        <v>1</v>
+      </c>
+      <c r="CG111">
+        <v>1</v>
+      </c>
+      <c r="CH111">
+        <v>0</v>
+      </c>
+      <c r="CI111" t="s">
+        <v>997</v>
+      </c>
+      <c r="CW111" t="s">
+        <v>1116</v>
+      </c>
+      <c r="CX111" t="s">
+        <v>971</v>
+      </c>
+      <c r="CY111" t="s">
+        <v>1000</v>
+      </c>
+      <c r="EY111" s="1"/>
+      <c r="GQ111" s="1"/>
+      <c r="GR111" s="1"/>
+      <c r="GX111">
+        <v>881108214</v>
+      </c>
+      <c r="GY111" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="GZ111" s="1">
+        <v>46294.366423611107</v>
+      </c>
+      <c r="HA111" s="1"/>
+      <c r="HB111" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD111" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE111" t="s">
+        <v>1118</v>
+      </c>
+      <c r="HF111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>46294.552163206019</v>
+      </c>
+      <c r="B112" s="1">
+        <v>46294.555845578703</v>
+      </c>
+      <c r="C112" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D112" t="s">
+        <v>354</v>
+      </c>
+      <c r="E112" t="s">
+        <v>295</v>
+      </c>
+      <c r="F112" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G112" t="s">
+        <v>198</v>
+      </c>
+      <c r="H112" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ112" t="s">
+        <v>628</v>
+      </c>
+      <c r="AK112" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AL112" t="s">
+        <v>628</v>
+      </c>
+      <c r="AM112" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN112" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AO112" t="s">
+        <v>463</v>
+      </c>
+      <c r="AR112" t="s">
+        <v>520</v>
+      </c>
+      <c r="AS112">
+        <v>0</v>
+      </c>
+      <c r="AT112">
+        <v>300</v>
+      </c>
+      <c r="AU112" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV112" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW112" t="s">
+        <v>392</v>
+      </c>
+      <c r="AX112" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AY112" t="s">
+        <v>465</v>
+      </c>
+      <c r="BA112" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB112" t="s">
+        <v>1124</v>
+      </c>
+      <c r="BC112" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD112" t="s">
+        <v>395</v>
+      </c>
+      <c r="EY112" s="1"/>
+      <c r="GQ112" s="1"/>
+      <c r="GR112" s="1"/>
+      <c r="GX112">
+        <v>881200379</v>
+      </c>
+      <c r="GY112" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="GZ112" s="1">
+        <v>46294.430856481478</v>
+      </c>
+      <c r="HA112" s="1"/>
+      <c r="HB112" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD112" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE112" t="s">
+        <v>1126</v>
+      </c>
+      <c r="HF112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>46294.55584572917</v>
+      </c>
+      <c r="B113" s="1">
+        <v>46294.558842430553</v>
+      </c>
+      <c r="C113" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D113" t="s">
+        <v>903</v>
+      </c>
+      <c r="E113" t="s">
+        <v>295</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G113" t="s">
+        <v>198</v>
+      </c>
+      <c r="H113" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ113" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AK113" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AL113" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AM113" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN113" t="s">
+        <v>1129</v>
+      </c>
+      <c r="AO113" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF113" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ113" t="s">
+        <v>1130</v>
+      </c>
+      <c r="BK113">
+        <v>0</v>
+      </c>
+      <c r="BL113">
+        <v>1</v>
+      </c>
+      <c r="BM113">
+        <v>1</v>
+      </c>
+      <c r="BN113">
+        <v>0</v>
+      </c>
+      <c r="BO113">
+        <v>0</v>
+      </c>
+      <c r="BP113">
+        <v>0</v>
+      </c>
+      <c r="BQ113">
+        <v>0</v>
+      </c>
+      <c r="BS113" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY113" s="1"/>
+      <c r="GQ113" s="1"/>
+      <c r="GR113" s="1"/>
+      <c r="GX113">
+        <v>881205166</v>
+      </c>
+      <c r="GY113" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="GZ113" s="1">
+        <v>46294.433854166673</v>
+      </c>
+      <c r="HA113" s="1"/>
+      <c r="HB113" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD113" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE113" t="s">
+        <v>1132</v>
+      </c>
+      <c r="HF113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>46293.535828969907</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46293.556272337963</v>
+      </c>
+      <c r="C114" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D114" t="s">
+        <v>903</v>
+      </c>
+      <c r="E114" t="s">
+        <v>196</v>
+      </c>
+      <c r="F114" t="s">
+        <v>196</v>
+      </c>
+      <c r="G114" t="s">
+        <v>198</v>
+      </c>
+      <c r="H114" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ114" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AK114" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AL114" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AM114" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN114" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AO114" t="s">
+        <v>561</v>
+      </c>
+      <c r="BF114" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ114" t="s">
+        <v>948</v>
+      </c>
+      <c r="BK114">
+        <v>0</v>
+      </c>
+      <c r="BL114">
+        <v>0</v>
+      </c>
+      <c r="BM114">
+        <v>0</v>
+      </c>
+      <c r="BN114">
+        <v>1</v>
+      </c>
+      <c r="BO114">
+        <v>0</v>
+      </c>
+      <c r="BP114">
+        <v>0</v>
+      </c>
+      <c r="BQ114">
+        <v>0</v>
+      </c>
+      <c r="BS114" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY114" s="1"/>
+      <c r="GQ114" s="1"/>
+      <c r="GR114" s="1"/>
+      <c r="GX114">
+        <v>881281904</v>
+      </c>
+      <c r="GY114" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="GZ114" s="1">
+        <v>46294.48777777778</v>
+      </c>
+      <c r="HA114" s="1"/>
+      <c r="HB114" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD114" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE114" t="s">
+        <v>1138</v>
+      </c>
+      <c r="HF114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>46293.556273576389</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46293.568581886568</v>
+      </c>
+      <c r="C115" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D115" t="s">
+        <v>903</v>
+      </c>
+      <c r="E115" t="s">
+        <v>196</v>
+      </c>
+      <c r="F115" t="s">
+        <v>196</v>
+      </c>
+      <c r="G115" t="s">
+        <v>198</v>
+      </c>
+      <c r="H115" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ115" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AK115" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AL115" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AM115" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN115" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AO115" t="s">
+        <v>947</v>
+      </c>
+      <c r="BF115" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ115" t="s">
+        <v>1142</v>
+      </c>
+      <c r="BK115">
+        <v>0</v>
+      </c>
+      <c r="BL115">
+        <v>1</v>
+      </c>
+      <c r="BM115">
+        <v>0</v>
+      </c>
+      <c r="BN115">
+        <v>1</v>
+      </c>
+      <c r="BO115">
+        <v>0</v>
+      </c>
+      <c r="BP115">
+        <v>0</v>
+      </c>
+      <c r="BQ115">
+        <v>0</v>
+      </c>
+      <c r="BS115" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY115" s="1"/>
+      <c r="GQ115" s="1"/>
+      <c r="GR115" s="1"/>
+      <c r="GX115">
+        <v>881281915</v>
+      </c>
+      <c r="GY115" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="GZ115" s="1">
+        <v>46294.48778935185</v>
+      </c>
+      <c r="HA115" s="1"/>
+      <c r="HB115" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD115" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE115" t="s">
+        <v>1144</v>
+      </c>
+      <c r="HF115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>46293.571447662027</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46293.574183599543</v>
+      </c>
+      <c r="C116" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D116" t="s">
+        <v>903</v>
+      </c>
+      <c r="E116" t="s">
+        <v>196</v>
+      </c>
+      <c r="F116" t="s">
+        <v>196</v>
+      </c>
+      <c r="G116" t="s">
+        <v>198</v>
+      </c>
+      <c r="H116" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ116" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AK116" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AL116" t="s">
+        <v>953</v>
+      </c>
+      <c r="AM116" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN116" t="s">
+        <v>1146</v>
+      </c>
+      <c r="AO116" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF116" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG116" t="s">
+        <v>1147</v>
+      </c>
+      <c r="BH116" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI116" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ116" t="s">
+        <v>1148</v>
+      </c>
+      <c r="BK116">
+        <v>0</v>
+      </c>
+      <c r="BL116">
+        <v>1</v>
+      </c>
+      <c r="BM116">
+        <v>0</v>
+      </c>
+      <c r="BN116">
+        <v>1</v>
+      </c>
+      <c r="BO116">
+        <v>1</v>
+      </c>
+      <c r="BP116">
+        <v>0</v>
+      </c>
+      <c r="BQ116">
+        <v>0</v>
+      </c>
+      <c r="BS116" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY116" s="1"/>
+      <c r="GQ116" s="1"/>
+      <c r="GR116" s="1"/>
+      <c r="GX116">
+        <v>881281928</v>
+      </c>
+      <c r="GY116" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="GZ116" s="1">
+        <v>46294.48778935185</v>
+      </c>
+      <c r="HA116" s="1"/>
+      <c r="HB116" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD116" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE116" t="s">
+        <v>1150</v>
+      </c>
+      <c r="HF116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>46293.583647256943</v>
+      </c>
+      <c r="B117" s="1">
+        <v>46293.585227627307</v>
+      </c>
+      <c r="C117" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D117" t="s">
+        <v>903</v>
+      </c>
+      <c r="E117" t="s">
+        <v>196</v>
+      </c>
+      <c r="F117" t="s">
+        <v>196</v>
+      </c>
+      <c r="G117" t="s">
+        <v>198</v>
+      </c>
+      <c r="H117" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ117" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AK117" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AL117" t="s">
+        <v>651</v>
+      </c>
+      <c r="AM117" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN117" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AO117" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF117" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ117" t="s">
+        <v>1142</v>
+      </c>
+      <c r="BK117">
+        <v>0</v>
+      </c>
+      <c r="BL117">
+        <v>1</v>
+      </c>
+      <c r="BM117">
+        <v>0</v>
+      </c>
+      <c r="BN117">
+        <v>1</v>
+      </c>
+      <c r="BO117">
+        <v>0</v>
+      </c>
+      <c r="BP117">
+        <v>0</v>
+      </c>
+      <c r="BQ117">
+        <v>0</v>
+      </c>
+      <c r="BS117" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY117" s="1"/>
+      <c r="GQ117" s="1"/>
+      <c r="GR117" s="1"/>
+      <c r="GX117">
+        <v>881281944</v>
+      </c>
+      <c r="GY117" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="GZ117" s="1">
+        <v>46294.487800925926</v>
+      </c>
+      <c r="HA117" s="1"/>
+      <c r="HB117" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD117" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE117" t="s">
+        <v>1154</v>
+      </c>
+      <c r="HF117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>46293.585437430564</v>
+      </c>
+      <c r="B118" s="1">
+        <v>46293.596937164351</v>
+      </c>
+      <c r="C118" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D118" t="s">
+        <v>969</v>
+      </c>
+      <c r="E118" t="s">
+        <v>196</v>
+      </c>
+      <c r="F118" t="s">
+        <v>196</v>
+      </c>
+      <c r="G118" t="s">
+        <v>198</v>
+      </c>
+      <c r="H118" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ118" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AK118" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AL118" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AM118" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN118" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AO118" t="s">
+        <v>561</v>
+      </c>
+      <c r="BU118" t="s">
+        <v>1157</v>
+      </c>
+      <c r="BV118" t="s">
+        <v>1158</v>
+      </c>
+      <c r="BW118">
+        <v>1</v>
+      </c>
+      <c r="BX118">
+        <v>0</v>
+      </c>
+      <c r="BY118">
+        <v>0</v>
+      </c>
+      <c r="BZ118">
+        <v>1</v>
+      </c>
+      <c r="CA118">
+        <v>0</v>
+      </c>
+      <c r="CC118" t="s">
+        <v>1159</v>
+      </c>
+      <c r="CD118" t="s">
+        <v>1160</v>
+      </c>
+      <c r="CE118" t="s">
+        <v>996</v>
+      </c>
+      <c r="CF118">
+        <v>1</v>
+      </c>
+      <c r="CG118">
+        <v>0</v>
+      </c>
+      <c r="CH118">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="s">
+        <v>1161</v>
+      </c>
+      <c r="CS118" t="s">
+        <v>1162</v>
+      </c>
+      <c r="CT118" t="s">
+        <v>1163</v>
+      </c>
+      <c r="CU118" t="s">
+        <v>1164</v>
+      </c>
+      <c r="EY118" s="1"/>
+      <c r="GQ118" s="1"/>
+      <c r="GR118" s="1"/>
+      <c r="GX118">
+        <v>881281959</v>
+      </c>
+      <c r="GY118" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="GZ118" s="1">
+        <v>46294.487800925926</v>
+      </c>
+      <c r="HA118" s="1"/>
+      <c r="HB118" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD118" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE118" t="s">
+        <v>1166</v>
+      </c>
+      <c r="HF118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>46293.596938391202</v>
+      </c>
+      <c r="B119" s="1">
+        <v>46294.620387152783</v>
+      </c>
+      <c r="C119" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D119" t="s">
+        <v>707</v>
+      </c>
+      <c r="E119" t="s">
+        <v>196</v>
+      </c>
+      <c r="F119" t="s">
+        <v>793</v>
+      </c>
+      <c r="G119" t="s">
+        <v>198</v>
+      </c>
+      <c r="H119" t="s">
+        <v>199</v>
+      </c>
+      <c r="J119" t="s">
+        <v>1167</v>
+      </c>
+      <c r="K119" t="s">
+        <v>1168</v>
+      </c>
+      <c r="L119">
+        <v>870</v>
+      </c>
+      <c r="M119">
+        <v>420</v>
+      </c>
+      <c r="N119">
+        <v>450</v>
+      </c>
+      <c r="O119">
+        <v>25</v>
+      </c>
+      <c r="P119">
+        <v>2</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>395</v>
+      </c>
+      <c r="R119">
+        <v>30</v>
+      </c>
+      <c r="S119" t="s">
+        <v>214</v>
+      </c>
+      <c r="T119" t="s">
+        <v>320</v>
+      </c>
+      <c r="U119" t="s">
+        <v>202</v>
+      </c>
+      <c r="V119" t="s">
+        <v>216</v>
+      </c>
+      <c r="W119" t="s">
+        <v>203</v>
+      </c>
+      <c r="X119" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ119" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AK119" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AL119" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AM119" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN119" t="s">
+        <v>1171</v>
+      </c>
+      <c r="EY119" s="1"/>
+      <c r="GQ119" s="1"/>
+      <c r="GR119" s="1"/>
+      <c r="GX119">
+        <v>881292547</v>
+      </c>
+      <c r="GY119" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="GZ119" s="1">
+        <v>46294.495416666658</v>
+      </c>
+      <c r="HA119" s="1"/>
+      <c r="HB119" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD119" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE119" t="s">
+        <v>1173</v>
+      </c>
+      <c r="HF119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>46294.49139398148</v>
+      </c>
+      <c r="B120" s="1">
+        <v>46294.586002060183</v>
+      </c>
+      <c r="C120" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D120" t="s">
+        <v>903</v>
+      </c>
+      <c r="E120" t="s">
+        <v>210</v>
+      </c>
+      <c r="F120" t="s">
+        <v>518</v>
+      </c>
+      <c r="G120" t="s">
+        <v>198</v>
+      </c>
+      <c r="H120" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ120" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK120" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL120" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM120" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN120" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AO120" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF120" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ120" t="s">
+        <v>948</v>
+      </c>
+      <c r="BK120">
+        <v>0</v>
+      </c>
+      <c r="BL120">
+        <v>0</v>
+      </c>
+      <c r="BM120">
+        <v>0</v>
+      </c>
+      <c r="BN120">
+        <v>1</v>
+      </c>
+      <c r="BO120">
+        <v>0</v>
+      </c>
+      <c r="BP120">
+        <v>0</v>
+      </c>
+      <c r="BQ120">
+        <v>0</v>
+      </c>
+      <c r="BS120" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY120" s="1"/>
+      <c r="GQ120" s="1"/>
+      <c r="GR120" s="1"/>
+      <c r="GX120">
+        <v>881293083</v>
+      </c>
+      <c r="GY120" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="GZ120" s="1">
+        <v>46294.495752314811</v>
+      </c>
+      <c r="HA120" s="1"/>
+      <c r="HB120" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD120" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE120" t="s">
+        <v>1176</v>
+      </c>
+      <c r="HF120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>46294.586004293982</v>
+      </c>
+      <c r="B121" s="1">
+        <v>46294.634886215281</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D121" t="s">
+        <v>903</v>
+      </c>
+      <c r="E121" t="s">
+        <v>210</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G121" t="s">
+        <v>198</v>
+      </c>
+      <c r="H121" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ121" t="s">
+        <v>1178</v>
+      </c>
+      <c r="AK121" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL121" t="s">
+        <v>1179</v>
+      </c>
+      <c r="AM121" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN121" t="s">
+        <v>1180</v>
+      </c>
+      <c r="AO121" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF121" t="s">
+        <v>917</v>
+      </c>
+      <c r="BG121" t="s">
+        <v>1181</v>
+      </c>
+      <c r="BH121" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI121" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ121" t="s">
+        <v>1130</v>
+      </c>
+      <c r="BK121">
+        <v>0</v>
+      </c>
+      <c r="BL121">
+        <v>1</v>
+      </c>
+      <c r="BM121">
+        <v>1</v>
+      </c>
+      <c r="BN121">
+        <v>0</v>
+      </c>
+      <c r="BO121">
+        <v>0</v>
+      </c>
+      <c r="BP121">
+        <v>0</v>
+      </c>
+      <c r="BQ121">
+        <v>0</v>
+      </c>
+      <c r="BS121" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY121" s="1"/>
+      <c r="GQ121" s="1"/>
+      <c r="GR121" s="1"/>
+      <c r="GX121">
+        <v>881333329</v>
+      </c>
+      <c r="GY121" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="GZ121" s="1">
+        <v>46294.521932870368</v>
+      </c>
+      <c r="HA121" s="1"/>
+      <c r="HB121" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD121" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE121" t="s">
+        <v>1183</v>
+      </c>
+      <c r="HF121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>46294.634888472217</v>
+      </c>
+      <c r="B122" s="1">
+        <v>46294.638464780102</v>
+      </c>
+      <c r="C122" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D122" t="s">
+        <v>903</v>
+      </c>
+      <c r="E122" t="s">
+        <v>210</v>
+      </c>
+      <c r="F122" t="s">
+        <v>401</v>
+      </c>
+      <c r="G122" t="s">
+        <v>198</v>
+      </c>
+      <c r="H122" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ122" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK122" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL122" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM122" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN122" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AO122" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF122" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG122" t="s">
+        <v>1185</v>
+      </c>
+      <c r="BH122" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI122" t="s">
+        <v>1186</v>
+      </c>
+      <c r="BJ122" t="s">
+        <v>1187</v>
+      </c>
+      <c r="BK122">
+        <v>1</v>
+      </c>
+      <c r="BL122">
+        <v>0</v>
+      </c>
+      <c r="BM122">
+        <v>0</v>
+      </c>
+      <c r="BN122">
+        <v>0</v>
+      </c>
+      <c r="BO122">
+        <v>0</v>
+      </c>
+      <c r="BP122">
+        <v>0</v>
+      </c>
+      <c r="BQ122">
+        <v>0</v>
+      </c>
+      <c r="BS122" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY122" s="1"/>
+      <c r="GQ122" s="1"/>
+      <c r="GR122" s="1"/>
+      <c r="GX122">
+        <v>881333348</v>
+      </c>
+      <c r="GY122" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="GZ122" s="1">
+        <v>46294.521944444437</v>
+      </c>
+      <c r="HA122" s="1"/>
+      <c r="HB122" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD122" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE122" t="s">
+        <v>1189</v>
+      </c>
+      <c r="HF122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>46294.638466377313</v>
+      </c>
+      <c r="B123" s="1">
+        <v>46294.640931134258</v>
+      </c>
+      <c r="C123" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D123" t="s">
+        <v>903</v>
+      </c>
+      <c r="E123" t="s">
+        <v>210</v>
+      </c>
+      <c r="F123" t="s">
+        <v>401</v>
+      </c>
+      <c r="G123" t="s">
+        <v>198</v>
+      </c>
+      <c r="H123" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ123" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK123" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL123" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM123" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN123" t="s">
+        <v>900</v>
+      </c>
+      <c r="AO123" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF123" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ123" t="s">
+        <v>1190</v>
+      </c>
+      <c r="BK123">
+        <v>0</v>
+      </c>
+      <c r="BL123">
+        <v>0</v>
+      </c>
+      <c r="BM123">
+        <v>0</v>
+      </c>
+      <c r="BN123">
+        <v>0</v>
+      </c>
+      <c r="BO123">
+        <v>1</v>
+      </c>
+      <c r="BP123">
+        <v>0</v>
+      </c>
+      <c r="BQ123">
+        <v>0</v>
+      </c>
+      <c r="BS123" t="s">
+        <v>1191</v>
+      </c>
+      <c r="EY123" s="1"/>
+      <c r="GQ123" s="1"/>
+      <c r="GR123" s="1"/>
+      <c r="GX123">
+        <v>881333579</v>
+      </c>
+      <c r="GY123" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="GZ123" s="1">
+        <v>46294.52207175926</v>
+      </c>
+      <c r="HA123" s="1"/>
+      <c r="HB123" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD123" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE123" t="s">
+        <v>1193</v>
+      </c>
+      <c r="HF123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>46294.640932835653</v>
+      </c>
+      <c r="B124" s="1">
+        <v>46294.642852233803</v>
+      </c>
+      <c r="C124" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D124" t="s">
+        <v>903</v>
+      </c>
+      <c r="E124" t="s">
+        <v>210</v>
+      </c>
+      <c r="F124" t="s">
+        <v>401</v>
+      </c>
+      <c r="G124" t="s">
+        <v>198</v>
+      </c>
+      <c r="H124" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ124" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AK124" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL124" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM124" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN124" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AO124" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF124" t="s">
+        <v>917</v>
+      </c>
+      <c r="BG124" t="s">
+        <v>1195</v>
+      </c>
+      <c r="BH124" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI124" t="s">
+        <v>1196</v>
+      </c>
+      <c r="BJ124" t="s">
+        <v>948</v>
+      </c>
+      <c r="BK124">
+        <v>0</v>
+      </c>
+      <c r="BL124">
+        <v>0</v>
+      </c>
+      <c r="BM124">
+        <v>0</v>
+      </c>
+      <c r="BN124">
+        <v>1</v>
+      </c>
+      <c r="BO124">
+        <v>0</v>
+      </c>
+      <c r="BP124">
+        <v>0</v>
+      </c>
+      <c r="BQ124">
+        <v>0</v>
+      </c>
+      <c r="BS124" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY124" s="1"/>
+      <c r="GQ124" s="1"/>
+      <c r="GR124" s="1"/>
+      <c r="GX124">
+        <v>881333850</v>
+      </c>
+      <c r="GY124" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="GZ124" s="1">
+        <v>46294.522245370368</v>
+      </c>
+      <c r="HA124" s="1"/>
+      <c r="HB124" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD124" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE124" t="s">
+        <v>1198</v>
+      </c>
+      <c r="HF124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>46294.642854039354</v>
+      </c>
+      <c r="B125" s="1">
+        <v>46294.645222627318</v>
+      </c>
+      <c r="C125" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D125" t="s">
+        <v>903</v>
+      </c>
+      <c r="E125" t="s">
+        <v>210</v>
+      </c>
+      <c r="F125" t="s">
+        <v>401</v>
+      </c>
+      <c r="G125" t="s">
+        <v>198</v>
+      </c>
+      <c r="H125" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ125" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK125" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL125" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM125" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN125" t="s">
+        <v>1199</v>
+      </c>
+      <c r="AO125" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF125" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG125" t="s">
+        <v>1200</v>
+      </c>
+      <c r="BH125" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI125" t="s">
+        <v>1201</v>
+      </c>
+      <c r="BJ125" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BK125">
+        <v>1</v>
+      </c>
+      <c r="BL125">
+        <v>1</v>
+      </c>
+      <c r="BM125">
+        <v>0</v>
+      </c>
+      <c r="BN125">
+        <v>0</v>
+      </c>
+      <c r="BO125">
+        <v>0</v>
+      </c>
+      <c r="BP125">
+        <v>0</v>
+      </c>
+      <c r="BQ125">
+        <v>0</v>
+      </c>
+      <c r="BS125" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY125" s="1"/>
+      <c r="GQ125" s="1"/>
+      <c r="GR125" s="1"/>
+      <c r="GX125">
+        <v>881333858</v>
+      </c>
+      <c r="GY125" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="GZ125" s="1">
+        <v>46294.522256944438</v>
+      </c>
+      <c r="HA125" s="1"/>
+      <c r="HB125" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD125" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE125" t="s">
+        <v>1204</v>
+      </c>
+      <c r="HF125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>46294.64522431713</v>
+      </c>
+      <c r="B126" s="1">
+        <v>46294.646622442131</v>
+      </c>
+      <c r="C126" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D126" t="s">
+        <v>903</v>
+      </c>
+      <c r="E126" t="s">
+        <v>210</v>
+      </c>
+      <c r="F126" t="s">
+        <v>401</v>
+      </c>
+      <c r="G126" t="s">
+        <v>198</v>
+      </c>
+      <c r="H126" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ126" t="s">
+        <v>1205</v>
+      </c>
+      <c r="AK126" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL126" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM126" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN126" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AO126" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF126" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG126" t="s">
+        <v>1206</v>
+      </c>
+      <c r="BH126" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI126" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ126" t="s">
+        <v>1207</v>
+      </c>
+      <c r="BK126">
+        <v>1</v>
+      </c>
+      <c r="BL126">
+        <v>1</v>
+      </c>
+      <c r="BM126">
+        <v>1</v>
+      </c>
+      <c r="BN126">
+        <v>1</v>
+      </c>
+      <c r="BO126">
+        <v>0</v>
+      </c>
+      <c r="BP126">
+        <v>0</v>
+      </c>
+      <c r="BQ126">
+        <v>0</v>
+      </c>
+      <c r="BS126" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY126" s="1"/>
+      <c r="GQ126" s="1"/>
+      <c r="GR126" s="1"/>
+      <c r="GX126">
+        <v>881333868</v>
+      </c>
+      <c r="GY126" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="GZ126" s="1">
+        <v>46294.522256944438</v>
+      </c>
+      <c r="HA126" s="1"/>
+      <c r="HB126" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD126" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE126" t="s">
+        <v>1209</v>
+      </c>
+      <c r="HF126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>46294.684677696758</v>
+      </c>
+      <c r="B127" s="1">
+        <v>46294.71088712963</v>
+      </c>
+      <c r="C127" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D127" t="s">
+        <v>903</v>
+      </c>
+      <c r="E127" t="s">
+        <v>309</v>
+      </c>
+      <c r="F127" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G127" t="s">
+        <v>198</v>
+      </c>
+      <c r="H127" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ127" t="s">
+        <v>1211</v>
+      </c>
+      <c r="AK127" t="s">
+        <v>1212</v>
+      </c>
+      <c r="AL127" t="s">
+        <v>1213</v>
+      </c>
+      <c r="AM127" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN127" t="s">
+        <v>1214</v>
+      </c>
+      <c r="AO127" t="s">
+        <v>947</v>
+      </c>
+      <c r="BF127" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ127" t="s">
+        <v>826</v>
+      </c>
+      <c r="BK127">
+        <v>0</v>
+      </c>
+      <c r="BL127">
+        <v>0</v>
+      </c>
+      <c r="BM127">
+        <v>0</v>
+      </c>
+      <c r="BN127">
+        <v>0</v>
+      </c>
+      <c r="BO127">
+        <v>0</v>
+      </c>
+      <c r="BP127">
+        <v>0</v>
+      </c>
+      <c r="BQ127">
+        <v>1</v>
+      </c>
+      <c r="BR127" t="s">
+        <v>1215</v>
+      </c>
+      <c r="BS127" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY127" s="1"/>
+      <c r="GQ127" s="1"/>
+      <c r="GR127" s="1"/>
+      <c r="GX127">
+        <v>881430170</v>
+      </c>
+      <c r="GY127" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="GZ127" s="1">
+        <v>46294.585914351846</v>
+      </c>
+      <c r="HA127" s="1"/>
+      <c r="HB127" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD127" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE127" t="s">
+        <v>1217</v>
+      </c>
+      <c r="HF127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>46294.7240499537</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46294.731223761577</v>
+      </c>
+      <c r="C128" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D128" t="s">
+        <v>903</v>
+      </c>
+      <c r="E128" t="s">
+        <v>210</v>
+      </c>
+      <c r="F128" t="s">
+        <v>987</v>
+      </c>
+      <c r="G128" t="s">
+        <v>198</v>
+      </c>
+      <c r="H128" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ128" t="s">
+        <v>1218</v>
+      </c>
+      <c r="AK128" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL128" t="s">
+        <v>972</v>
+      </c>
+      <c r="AM128" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN128" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO128" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF128" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG128" t="s">
+        <v>1220</v>
+      </c>
+      <c r="BH128" t="s">
+        <v>1221</v>
+      </c>
+      <c r="BI128" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ128" t="s">
+        <v>1222</v>
+      </c>
+      <c r="BK128">
+        <v>1</v>
+      </c>
+      <c r="BL128">
+        <v>1</v>
+      </c>
+      <c r="BM128">
+        <v>0</v>
+      </c>
+      <c r="BN128">
+        <v>1</v>
+      </c>
+      <c r="BO128">
+        <v>0</v>
+      </c>
+      <c r="BP128">
+        <v>0</v>
+      </c>
+      <c r="BQ128">
+        <v>0</v>
+      </c>
+      <c r="BS128" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY128" s="1"/>
+      <c r="GQ128" s="1"/>
+      <c r="GR128" s="1"/>
+      <c r="GX128">
+        <v>881464319</v>
+      </c>
+      <c r="GY128" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="GZ128" s="1">
+        <v>46294.606238425928</v>
+      </c>
+      <c r="HA128" s="1"/>
+      <c r="HB128" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD128" t="s">
+        <v>371</v>
+      </c>
+      <c r="HE128" t="s">
+        <v>1224</v>
+      </c>
+      <c r="HF128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>46294.740338090283</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46294.755190208343</v>
+      </c>
+      <c r="C129" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D129" t="s">
+        <v>354</v>
+      </c>
+      <c r="E129" t="s">
+        <v>280</v>
+      </c>
+      <c r="F129" t="s">
+        <v>672</v>
+      </c>
+      <c r="G129" t="s">
+        <v>198</v>
+      </c>
+      <c r="H129" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ129" t="s">
+        <v>1225</v>
+      </c>
+      <c r="AK129" t="s">
+        <v>1226</v>
+      </c>
+      <c r="AL129" t="s">
+        <v>1227</v>
+      </c>
+      <c r="AM129" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN129" t="s">
+        <v>1228</v>
+      </c>
+      <c r="AO129" t="s">
+        <v>463</v>
+      </c>
+      <c r="AR129" t="s">
+        <v>520</v>
+      </c>
+      <c r="AS129">
+        <v>0</v>
+      </c>
+      <c r="AT129">
+        <v>1000</v>
+      </c>
+      <c r="AU129" t="s">
+        <v>571</v>
+      </c>
+      <c r="AV129" t="s">
+        <v>1229</v>
+      </c>
+      <c r="AW129" t="s">
+        <v>392</v>
+      </c>
+      <c r="AX129" t="s">
+        <v>1230</v>
+      </c>
+      <c r="AY129" t="s">
+        <v>465</v>
+      </c>
+      <c r="BA129" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB129" t="s">
+        <v>1063</v>
+      </c>
+      <c r="BC129" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD129" t="s">
+        <v>628</v>
+      </c>
+      <c r="EY129" s="1"/>
+      <c r="GQ129" s="1"/>
+      <c r="GR129" s="1"/>
+      <c r="GX129">
+        <v>881490088</v>
+      </c>
+      <c r="GY129" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="GZ129" s="1">
+        <v>46294.622060185182</v>
+      </c>
+      <c r="HA129" s="1"/>
+      <c r="HB129" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD129" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE129" t="s">
+        <v>1232</v>
+      </c>
+      <c r="HF129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>46294.739667569447</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46294.751934907406</v>
+      </c>
+      <c r="C130" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D130" t="s">
+        <v>903</v>
+      </c>
+      <c r="E130" t="s">
+        <v>210</v>
+      </c>
+      <c r="F130" t="s">
+        <v>987</v>
+      </c>
+      <c r="G130" t="s">
+        <v>198</v>
+      </c>
+      <c r="H130" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ130" t="s">
+        <v>1233</v>
+      </c>
+      <c r="AK130" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL130" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM130" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN130" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AO130" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF130" t="s">
+        <v>1235</v>
+      </c>
+      <c r="BG130" t="s">
+        <v>1236</v>
+      </c>
+      <c r="BH130" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI130" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ130" t="s">
+        <v>1237</v>
+      </c>
+      <c r="BK130">
+        <v>1</v>
+      </c>
+      <c r="BL130">
+        <v>1</v>
+      </c>
+      <c r="BM130">
+        <v>1</v>
+      </c>
+      <c r="BN130">
+        <v>0</v>
+      </c>
+      <c r="BO130">
+        <v>0</v>
+      </c>
+      <c r="BP130">
+        <v>0</v>
+      </c>
+      <c r="BQ130">
+        <v>0</v>
+      </c>
+      <c r="BS130" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY130" s="1"/>
+      <c r="GQ130" s="1"/>
+      <c r="GR130" s="1"/>
+      <c r="GX130">
+        <v>881498141</v>
+      </c>
+      <c r="GY130" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="GZ130" s="1">
+        <v>46294.626944444448</v>
+      </c>
+      <c r="HA130" s="1"/>
+      <c r="HB130" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD130" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE130" t="s">
+        <v>1239</v>
+      </c>
+      <c r="HF130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>46294.755193831021</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46294.761262164349</v>
+      </c>
+      <c r="C131" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D131" t="s">
+        <v>354</v>
+      </c>
+      <c r="E131" t="s">
+        <v>280</v>
+      </c>
+      <c r="F131" t="s">
+        <v>672</v>
+      </c>
+      <c r="G131" t="s">
+        <v>198</v>
+      </c>
+      <c r="H131" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ131" t="s">
+        <v>1240</v>
+      </c>
+      <c r="AK131" t="s">
+        <v>1241</v>
+      </c>
+      <c r="AL131" t="s">
+        <v>1242</v>
+      </c>
+      <c r="AM131" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN131" t="s">
+        <v>1243</v>
+      </c>
+      <c r="AO131" t="s">
+        <v>561</v>
+      </c>
+      <c r="AR131" t="s">
+        <v>520</v>
+      </c>
+      <c r="AS131">
+        <v>0</v>
+      </c>
+      <c r="AT131">
+        <v>800</v>
+      </c>
+      <c r="AU131" t="s">
+        <v>405</v>
+      </c>
+      <c r="AV131" t="s">
+        <v>1244</v>
+      </c>
+      <c r="AW131" t="s">
+        <v>363</v>
+      </c>
+      <c r="AX131" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AY131" t="s">
+        <v>465</v>
+      </c>
+      <c r="BA131" t="s">
+        <v>524</v>
+      </c>
+      <c r="BB131" t="s">
+        <v>1063</v>
+      </c>
+      <c r="BC131" t="s">
+        <v>467</v>
+      </c>
+      <c r="BD131" t="s">
+        <v>628</v>
+      </c>
+      <c r="EY131" s="1"/>
+      <c r="GQ131" s="1"/>
+      <c r="GR131" s="1"/>
+      <c r="GX131">
+        <v>881500259</v>
+      </c>
+      <c r="GY131" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="GZ131" s="1">
+        <v>46294.628136574072</v>
+      </c>
+      <c r="HA131" s="1"/>
+      <c r="HB131" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD131" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE131" t="s">
+        <v>1247</v>
+      </c>
+      <c r="HF131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>46294.75193539352</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46294.754593414349</v>
+      </c>
+      <c r="C132" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D132" t="s">
+        <v>903</v>
+      </c>
+      <c r="E132" t="s">
+        <v>210</v>
+      </c>
+      <c r="F132" t="s">
+        <v>987</v>
+      </c>
+      <c r="G132" t="s">
+        <v>198</v>
+      </c>
+      <c r="H132" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ132" t="s">
+        <v>1248</v>
+      </c>
+      <c r="AK132" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL132" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM132" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN132" t="s">
+        <v>1249</v>
+      </c>
+      <c r="AO132" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF132" t="s">
+        <v>917</v>
+      </c>
+      <c r="BG132" t="s">
+        <v>1250</v>
+      </c>
+      <c r="BH132" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI132" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ132" t="s">
+        <v>1237</v>
+      </c>
+      <c r="BK132">
+        <v>1</v>
+      </c>
+      <c r="BL132">
+        <v>1</v>
+      </c>
+      <c r="BM132">
+        <v>1</v>
+      </c>
+      <c r="BN132">
+        <v>0</v>
+      </c>
+      <c r="BO132">
+        <v>0</v>
+      </c>
+      <c r="BP132">
+        <v>0</v>
+      </c>
+      <c r="BQ132">
+        <v>0</v>
+      </c>
+      <c r="BS132" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY132" s="1"/>
+      <c r="GQ132" s="1"/>
+      <c r="GR132" s="1"/>
+      <c r="GX132">
+        <v>881502699</v>
+      </c>
+      <c r="GY132" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="GZ132" s="1">
+        <v>46294.629618055558</v>
+      </c>
+      <c r="HA132" s="1"/>
+      <c r="HB132" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD132" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE132" t="s">
+        <v>1252</v>
+      </c>
+      <c r="HF132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>46294.761264895831</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46294.765374097216</v>
+      </c>
+      <c r="C133" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D133" t="s">
+        <v>354</v>
+      </c>
+      <c r="E133" t="s">
+        <v>280</v>
+      </c>
+      <c r="F133" t="s">
+        <v>672</v>
+      </c>
+      <c r="G133" t="s">
+        <v>198</v>
+      </c>
+      <c r="H133" t="s">
+        <v>282</v>
+      </c>
+      <c r="AJ133" t="s">
+        <v>628</v>
+      </c>
+      <c r="AK133" t="s">
+        <v>628</v>
+      </c>
+      <c r="AL133" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AM133" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN133" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AO133" t="s">
+        <v>561</v>
+      </c>
+      <c r="AR133" t="s">
+        <v>360</v>
+      </c>
+      <c r="AS133">
+        <v>6</v>
+      </c>
+      <c r="AT133">
+        <v>1000</v>
+      </c>
+      <c r="AU133" t="s">
+        <v>361</v>
+      </c>
+      <c r="AV133" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AW133" t="s">
+        <v>392</v>
+      </c>
+      <c r="AX133" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AY133" t="s">
+        <v>394</v>
+      </c>
+      <c r="AZ133" t="s">
+        <v>395</v>
+      </c>
+      <c r="BA133" t="s">
+        <v>366</v>
+      </c>
+      <c r="BB133" t="s">
+        <v>1063</v>
+      </c>
+      <c r="BC133" t="s">
+        <v>397</v>
+      </c>
+      <c r="BD133" t="s">
+        <v>1257</v>
+      </c>
+      <c r="EY133" s="1"/>
+      <c r="GQ133" s="1"/>
+      <c r="GR133" s="1"/>
+      <c r="GX133">
+        <v>881506936</v>
+      </c>
+      <c r="GY133" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="GZ133" s="1">
+        <v>46294.632245370369</v>
+      </c>
+      <c r="HA133" s="1"/>
+      <c r="HB133" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD133" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE133" t="s">
+        <v>1259</v>
+      </c>
+      <c r="HF133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>46294.754593750004</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46294.75748699074</v>
+      </c>
+      <c r="C134" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D134" t="s">
+        <v>903</v>
+      </c>
+      <c r="E134" t="s">
+        <v>210</v>
+      </c>
+      <c r="F134" t="s">
+        <v>987</v>
+      </c>
+      <c r="G134" t="s">
+        <v>198</v>
+      </c>
+      <c r="H134" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ134" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AK134" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL134" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM134" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN134" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO134" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF134" t="s">
+        <v>917</v>
+      </c>
+      <c r="BG134" t="s">
+        <v>1261</v>
+      </c>
+      <c r="BH134" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI134" t="s">
+        <v>1186</v>
+      </c>
+      <c r="BJ134" t="s">
+        <v>1222</v>
+      </c>
+      <c r="BK134">
+        <v>1</v>
+      </c>
+      <c r="BL134">
+        <v>1</v>
+      </c>
+      <c r="BM134">
+        <v>0</v>
+      </c>
+      <c r="BN134">
+        <v>1</v>
+      </c>
+      <c r="BO134">
+        <v>0</v>
+      </c>
+      <c r="BP134">
+        <v>0</v>
+      </c>
+      <c r="BQ134">
+        <v>0</v>
+      </c>
+      <c r="BS134" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY134" s="1"/>
+      <c r="GQ134" s="1"/>
+      <c r="GR134" s="1"/>
+      <c r="GX134">
+        <v>881507402</v>
+      </c>
+      <c r="GY134" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="GZ134" s="1">
+        <v>46294.6325</v>
+      </c>
+      <c r="HA134" s="1"/>
+      <c r="HB134" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD134" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE134" t="s">
+        <v>1263</v>
+      </c>
+      <c r="HF134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>46294.757487442133</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46294.760891296297</v>
+      </c>
+      <c r="C135" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D135" t="s">
+        <v>903</v>
+      </c>
+      <c r="E135" t="s">
+        <v>210</v>
+      </c>
+      <c r="F135" t="s">
+        <v>987</v>
+      </c>
+      <c r="G135" t="s">
+        <v>198</v>
+      </c>
+      <c r="H135" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ135" t="s">
+        <v>1264</v>
+      </c>
+      <c r="AK135" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL135" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM135" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN135" t="s">
+        <v>1265</v>
+      </c>
+      <c r="AO135" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF135" t="s">
+        <v>1235</v>
+      </c>
+      <c r="BG135" t="s">
+        <v>1266</v>
+      </c>
+      <c r="BH135" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI135" t="s">
+        <v>1186</v>
+      </c>
+      <c r="BJ135" t="s">
+        <v>1267</v>
+      </c>
+      <c r="BK135">
+        <v>1</v>
+      </c>
+      <c r="BL135">
+        <v>0</v>
+      </c>
+      <c r="BM135">
+        <v>1</v>
+      </c>
+      <c r="BN135">
+        <v>1</v>
+      </c>
+      <c r="BO135">
+        <v>0</v>
+      </c>
+      <c r="BP135">
+        <v>0</v>
+      </c>
+      <c r="BQ135">
+        <v>0</v>
+      </c>
+      <c r="BS135" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY135" s="1"/>
+      <c r="GQ135" s="1"/>
+      <c r="GR135" s="1"/>
+      <c r="GX135">
+        <v>881512990</v>
+      </c>
+      <c r="GY135" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="GZ135" s="1">
+        <v>46294.63590277778</v>
+      </c>
+      <c r="HA135" s="1"/>
+      <c r="HB135" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD135" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE135" t="s">
+        <v>1269</v>
+      </c>
+      <c r="HF135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>46294.760891759259</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46294.776597291668</v>
+      </c>
+      <c r="C136" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D136" t="s">
+        <v>903</v>
+      </c>
+      <c r="E136" t="s">
+        <v>210</v>
+      </c>
+      <c r="F136" t="s">
+        <v>987</v>
+      </c>
+      <c r="G136" t="s">
+        <v>198</v>
+      </c>
+      <c r="H136" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ136" t="s">
+        <v>1270</v>
+      </c>
+      <c r="AK136" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL136" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM136" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN136" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO136" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF136" t="s">
+        <v>1235</v>
+      </c>
+      <c r="BG136" t="s">
+        <v>1271</v>
+      </c>
+      <c r="BH136" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI136" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ136" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BK136">
+        <v>1</v>
+      </c>
+      <c r="BL136">
+        <v>1</v>
+      </c>
+      <c r="BM136">
+        <v>0</v>
+      </c>
+      <c r="BN136">
+        <v>0</v>
+      </c>
+      <c r="BO136">
+        <v>0</v>
+      </c>
+      <c r="BP136">
+        <v>0</v>
+      </c>
+      <c r="BQ136">
+        <v>0</v>
+      </c>
+      <c r="BS136" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY136" s="1"/>
+      <c r="GQ136" s="1"/>
+      <c r="GR136" s="1"/>
+      <c r="GX136">
+        <v>881537457</v>
+      </c>
+      <c r="GY136" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="GZ136" s="1">
+        <v>46294.651608796303</v>
+      </c>
+      <c r="HA136" s="1"/>
+      <c r="HB136" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD136" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE136" t="s">
+        <v>1273</v>
+      </c>
+      <c r="HF136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>46294.776597719909</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46294.795517326391</v>
+      </c>
+      <c r="C137" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D137" t="s">
+        <v>903</v>
+      </c>
+      <c r="E137" t="s">
+        <v>210</v>
+      </c>
+      <c r="F137" t="s">
+        <v>987</v>
+      </c>
+      <c r="G137" t="s">
+        <v>198</v>
+      </c>
+      <c r="H137" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ137" t="s">
+        <v>1274</v>
+      </c>
+      <c r="AK137" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL137" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM137" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN137" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO137" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF137" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG137" t="s">
+        <v>1275</v>
+      </c>
+      <c r="BH137" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI137" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ137" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BK137">
+        <v>1</v>
+      </c>
+      <c r="BL137">
+        <v>1</v>
+      </c>
+      <c r="BM137">
+        <v>0</v>
+      </c>
+      <c r="BN137">
+        <v>0</v>
+      </c>
+      <c r="BO137">
+        <v>0</v>
+      </c>
+      <c r="BP137">
+        <v>0</v>
+      </c>
+      <c r="BQ137">
+        <v>0</v>
+      </c>
+      <c r="BS137" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY137" s="1"/>
+      <c r="GQ137" s="1"/>
+      <c r="GR137" s="1"/>
+      <c r="GX137">
+        <v>881567912</v>
+      </c>
+      <c r="GY137" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="GZ137" s="1">
+        <v>46294.670532407406</v>
+      </c>
+      <c r="HA137" s="1"/>
+      <c r="HB137" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD137" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE137" t="s">
+        <v>1277</v>
+      </c>
+      <c r="HF137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>46294.795517766201</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46294.799215231476</v>
+      </c>
+      <c r="C138" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D138" t="s">
+        <v>903</v>
+      </c>
+      <c r="E138" t="s">
+        <v>210</v>
+      </c>
+      <c r="F138" t="s">
+        <v>987</v>
+      </c>
+      <c r="G138" t="s">
+        <v>198</v>
+      </c>
+      <c r="H138" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ138" t="s">
+        <v>1278</v>
+      </c>
+      <c r="AK138" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL138" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM138" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN138" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO138" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF138" t="s">
+        <v>917</v>
+      </c>
+      <c r="BG138" t="s">
+        <v>1279</v>
+      </c>
+      <c r="BH138" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI138" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ138" t="s">
+        <v>1280</v>
+      </c>
+      <c r="BK138">
+        <v>0</v>
+      </c>
+      <c r="BL138">
+        <v>1</v>
+      </c>
+      <c r="BM138">
+        <v>1</v>
+      </c>
+      <c r="BN138">
+        <v>1</v>
+      </c>
+      <c r="BO138">
+        <v>0</v>
+      </c>
+      <c r="BP138">
+        <v>0</v>
+      </c>
+      <c r="BQ138">
+        <v>0</v>
+      </c>
+      <c r="BS138" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY138" s="1"/>
+      <c r="GQ138" s="1"/>
+      <c r="GR138" s="1"/>
+      <c r="GX138">
+        <v>881573473</v>
+      </c>
+      <c r="GY138" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="GZ138" s="1">
+        <v>46294.674224537041</v>
+      </c>
+      <c r="HA138" s="1"/>
+      <c r="HB138" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD138" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE138" t="s">
+        <v>1282</v>
+      </c>
+      <c r="HF138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>46294.799215694453</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46294.802037164351</v>
+      </c>
+      <c r="C139" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D139" t="s">
+        <v>903</v>
+      </c>
+      <c r="E139" t="s">
+        <v>210</v>
+      </c>
+      <c r="F139" t="s">
+        <v>987</v>
+      </c>
+      <c r="G139" t="s">
+        <v>198</v>
+      </c>
+      <c r="H139" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ139" t="s">
+        <v>1283</v>
+      </c>
+      <c r="AK139" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL139" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM139" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN139" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO139" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF139" t="s">
+        <v>1235</v>
+      </c>
+      <c r="BG139" t="s">
+        <v>1284</v>
+      </c>
+      <c r="BH139" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI139" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ139" t="s">
+        <v>1237</v>
+      </c>
+      <c r="BK139">
+        <v>1</v>
+      </c>
+      <c r="BL139">
+        <v>1</v>
+      </c>
+      <c r="BM139">
+        <v>1</v>
+      </c>
+      <c r="BN139">
+        <v>0</v>
+      </c>
+      <c r="BO139">
+        <v>0</v>
+      </c>
+      <c r="BP139">
+        <v>0</v>
+      </c>
+      <c r="BQ139">
+        <v>0</v>
+      </c>
+      <c r="BS139" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY139" s="1"/>
+      <c r="GQ139" s="1"/>
+      <c r="GR139" s="1"/>
+      <c r="GX139">
+        <v>881577726</v>
+      </c>
+      <c r="GY139" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="GZ139" s="1">
+        <v>46294.677048611113</v>
+      </c>
+      <c r="HA139" s="1"/>
+      <c r="HB139" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD139" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE139" t="s">
+        <v>1286</v>
+      </c>
+      <c r="HF139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>46294.802037627313</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46294.803749027778</v>
+      </c>
+      <c r="C140" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D140" t="s">
+        <v>903</v>
+      </c>
+      <c r="E140" t="s">
+        <v>210</v>
+      </c>
+      <c r="F140" t="s">
+        <v>987</v>
+      </c>
+      <c r="G140" t="s">
+        <v>198</v>
+      </c>
+      <c r="H140" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ140" t="s">
+        <v>1278</v>
+      </c>
+      <c r="AK140" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL140" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM140" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN140" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO140" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF140" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG140" t="s">
+        <v>1287</v>
+      </c>
+      <c r="BH140" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI140" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ140" t="s">
+        <v>1280</v>
+      </c>
+      <c r="BK140">
+        <v>0</v>
+      </c>
+      <c r="BL140">
+        <v>1</v>
+      </c>
+      <c r="BM140">
+        <v>1</v>
+      </c>
+      <c r="BN140">
+        <v>1</v>
+      </c>
+      <c r="BO140">
+        <v>0</v>
+      </c>
+      <c r="BP140">
+        <v>0</v>
+      </c>
+      <c r="BQ140">
+        <v>0</v>
+      </c>
+      <c r="BS140" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY140" s="1"/>
+      <c r="GQ140" s="1"/>
+      <c r="GR140" s="1"/>
+      <c r="GX140">
+        <v>881580224</v>
+      </c>
+      <c r="GY140" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="GZ140" s="1">
+        <v>46294.678749999999</v>
+      </c>
+      <c r="HA140" s="1"/>
+      <c r="HB140" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD140" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE140" t="s">
+        <v>1289</v>
+      </c>
+      <c r="HF140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>46294.620284849538</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46294.9428796875</v>
+      </c>
+      <c r="C141" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D141" t="s">
+        <v>969</v>
+      </c>
+      <c r="E141" t="s">
+        <v>254</v>
+      </c>
+      <c r="F141" t="s">
+        <v>332</v>
+      </c>
+      <c r="G141" t="s">
+        <v>198</v>
+      </c>
+      <c r="H141" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ141" t="s">
+        <v>1290</v>
+      </c>
+      <c r="AK141" t="s">
+        <v>1291</v>
+      </c>
+      <c r="AL141" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM141" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN141" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AO141" t="s">
+        <v>463</v>
+      </c>
+      <c r="BU141" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BV141" t="s">
+        <v>1158</v>
+      </c>
+      <c r="BW141">
+        <v>1</v>
+      </c>
+      <c r="BX141">
+        <v>0</v>
+      </c>
+      <c r="BY141">
+        <v>0</v>
+      </c>
+      <c r="BZ141">
+        <v>1</v>
+      </c>
+      <c r="CA141">
+        <v>0</v>
+      </c>
+      <c r="CC141" t="s">
+        <v>1293</v>
+      </c>
+      <c r="CD141" t="s">
+        <v>1294</v>
+      </c>
+      <c r="CE141" t="s">
+        <v>996</v>
+      </c>
+      <c r="CF141">
+        <v>1</v>
+      </c>
+      <c r="CG141">
+        <v>0</v>
+      </c>
+      <c r="CH141">
+        <v>0</v>
+      </c>
+      <c r="CI141" t="s">
+        <v>1100</v>
+      </c>
+      <c r="CS141" t="s">
+        <v>1295</v>
+      </c>
+      <c r="CT141" t="s">
+        <v>395</v>
+      </c>
+      <c r="CU141" t="s">
+        <v>1050</v>
+      </c>
+      <c r="EY141" s="1"/>
+      <c r="GQ141" s="1"/>
+      <c r="GR141" s="1"/>
+      <c r="GX141">
+        <v>881740632</v>
+      </c>
+      <c r="GY141" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="GZ141" s="1">
+        <v>46294.817928240736</v>
+      </c>
+      <c r="HA141" s="1"/>
+      <c r="HB141" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD141" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE141" t="s">
+        <v>1297</v>
+      </c>
+      <c r="HF141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>46294.750292604163</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46294.943034189811</v>
+      </c>
+      <c r="C142" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D142" t="s">
+        <v>969</v>
+      </c>
+      <c r="E142" t="s">
+        <v>254</v>
+      </c>
+      <c r="F142" t="s">
+        <v>332</v>
+      </c>
+      <c r="G142" t="s">
+        <v>198</v>
+      </c>
+      <c r="H142" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ142" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AK142" t="s">
+        <v>1299</v>
+      </c>
+      <c r="AL142" t="s">
+        <v>914</v>
+      </c>
+      <c r="AM142" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN142" t="s">
+        <v>1300</v>
+      </c>
+      <c r="AO142" t="s">
+        <v>947</v>
+      </c>
+      <c r="BU142" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BV142" t="s">
+        <v>1046</v>
+      </c>
+      <c r="BW142">
+        <v>0</v>
+      </c>
+      <c r="BX142">
+        <v>0</v>
+      </c>
+      <c r="BY142">
+        <v>1</v>
+      </c>
+      <c r="BZ142">
+        <v>1</v>
+      </c>
+      <c r="CA142">
+        <v>0</v>
+      </c>
+      <c r="CO142" t="s">
+        <v>1101</v>
+      </c>
+      <c r="CP142" t="s">
+        <v>628</v>
+      </c>
+      <c r="CQ142" t="s">
+        <v>1103</v>
+      </c>
+      <c r="CS142" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CT142" t="s">
+        <v>395</v>
+      </c>
+      <c r="CU142" t="s">
+        <v>1164</v>
+      </c>
+      <c r="EY142" s="1"/>
+      <c r="GQ142" s="1"/>
+      <c r="GR142" s="1"/>
+      <c r="GX142">
+        <v>881740830</v>
+      </c>
+      <c r="GY142" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="GZ142" s="1">
+        <v>46294.818055555559</v>
+      </c>
+      <c r="HA142" s="1"/>
+      <c r="HB142" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD142" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE142" t="s">
+        <v>1303</v>
+      </c>
+      <c r="HF142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>46294.75457420139</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46294.943127997692</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D143" t="s">
+        <v>969</v>
+      </c>
+      <c r="E143" t="s">
+        <v>254</v>
+      </c>
+      <c r="F143" t="s">
+        <v>332</v>
+      </c>
+      <c r="G143" t="s">
+        <v>198</v>
+      </c>
+      <c r="H143" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ143" t="s">
+        <v>1304</v>
+      </c>
+      <c r="AK143" t="s">
+        <v>1305</v>
+      </c>
+      <c r="AL143" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM143" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN143" t="s">
+        <v>906</v>
+      </c>
+      <c r="AO143" t="s">
+        <v>463</v>
+      </c>
+      <c r="BU143" t="s">
+        <v>1306</v>
+      </c>
+      <c r="BV143" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BW143">
+        <v>0</v>
+      </c>
+      <c r="BX143">
+        <v>1</v>
+      </c>
+      <c r="BY143">
+        <v>0</v>
+      </c>
+      <c r="BZ143">
+        <v>1</v>
+      </c>
+      <c r="CA143">
+        <v>0</v>
+      </c>
+      <c r="CK143" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CL143" t="s">
+        <v>1308</v>
+      </c>
+      <c r="CM143" t="s">
+        <v>978</v>
+      </c>
+      <c r="CS143" t="s">
+        <v>1309</v>
+      </c>
+      <c r="CT143" t="s">
+        <v>395</v>
+      </c>
+      <c r="CU143" t="s">
+        <v>1050</v>
+      </c>
+      <c r="EY143" s="1"/>
+      <c r="GQ143" s="1"/>
+      <c r="GR143" s="1"/>
+      <c r="GX143">
+        <v>881740935</v>
+      </c>
+      <c r="GY143" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="GZ143" s="1">
+        <v>46294.818148148152</v>
+      </c>
+      <c r="HA143" s="1"/>
+      <c r="HB143" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD143" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE143" t="s">
+        <v>1311</v>
+      </c>
+      <c r="HF143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>46294.76850484954</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46294.943231481477</v>
+      </c>
+      <c r="C144" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D144" t="s">
+        <v>903</v>
+      </c>
+      <c r="E144" t="s">
+        <v>254</v>
+      </c>
+      <c r="F144" t="s">
+        <v>332</v>
+      </c>
+      <c r="G144" t="s">
+        <v>198</v>
+      </c>
+      <c r="H144" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ144" t="s">
+        <v>1312</v>
+      </c>
+      <c r="AK144" t="s">
+        <v>628</v>
+      </c>
+      <c r="AL144" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM144" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN144" t="s">
+        <v>1313</v>
+      </c>
+      <c r="AO144" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF144" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG144" t="s">
+        <v>1314</v>
+      </c>
+      <c r="BH144" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI144" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ144" t="s">
+        <v>1237</v>
+      </c>
+      <c r="BK144">
+        <v>1</v>
+      </c>
+      <c r="BL144">
+        <v>1</v>
+      </c>
+      <c r="BM144">
+        <v>1</v>
+      </c>
+      <c r="BN144">
+        <v>0</v>
+      </c>
+      <c r="BO144">
+        <v>0</v>
+      </c>
+      <c r="BP144">
+        <v>0</v>
+      </c>
+      <c r="BQ144">
+        <v>0</v>
+      </c>
+      <c r="BS144" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY144" s="1"/>
+      <c r="GQ144" s="1"/>
+      <c r="GR144" s="1"/>
+      <c r="GX144">
+        <v>881741005</v>
+      </c>
+      <c r="GY144" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="GZ144" s="1">
+        <v>46294.818252314813</v>
+      </c>
+      <c r="HA144" s="1"/>
+      <c r="HB144" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD144" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE144" t="s">
+        <v>1316</v>
+      </c>
+      <c r="HF144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>46294.770551990739</v>
+      </c>
+      <c r="B145" s="1">
+        <v>46294.943342384257</v>
+      </c>
+      <c r="C145" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D145" t="s">
+        <v>903</v>
+      </c>
+      <c r="E145" t="s">
+        <v>254</v>
+      </c>
+      <c r="F145" t="s">
+        <v>332</v>
+      </c>
+      <c r="G145" t="s">
+        <v>198</v>
+      </c>
+      <c r="H145" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ145" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AK145" t="s">
+        <v>1318</v>
+      </c>
+      <c r="AL145" t="s">
+        <v>914</v>
+      </c>
+      <c r="AM145" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN145" t="s">
+        <v>1319</v>
+      </c>
+      <c r="AO145" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF145" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG145" t="s">
+        <v>1320</v>
+      </c>
+      <c r="BH145" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI145" t="s">
+        <v>1196</v>
+      </c>
+      <c r="BJ145" t="s">
+        <v>1187</v>
+      </c>
+      <c r="BK145">
+        <v>1</v>
+      </c>
+      <c r="BL145">
+        <v>0</v>
+      </c>
+      <c r="BM145">
+        <v>0</v>
+      </c>
+      <c r="BN145">
+        <v>0</v>
+      </c>
+      <c r="BO145">
+        <v>0</v>
+      </c>
+      <c r="BP145">
+        <v>0</v>
+      </c>
+      <c r="BQ145">
+        <v>0</v>
+      </c>
+      <c r="BS145" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY145" s="1"/>
+      <c r="GQ145" s="1"/>
+      <c r="GR145" s="1"/>
+      <c r="GX145">
+        <v>881741087</v>
+      </c>
+      <c r="GY145" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="GZ145" s="1">
+        <v>46294.818368055552</v>
+      </c>
+      <c r="HA145" s="1"/>
+      <c r="HB145" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD145" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE145" t="s">
+        <v>1322</v>
+      </c>
+      <c r="HF145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>46294.77235269676</v>
+      </c>
+      <c r="B146" s="1">
+        <v>46294.943435092588</v>
+      </c>
+      <c r="C146" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D146" t="s">
+        <v>903</v>
+      </c>
+      <c r="E146" t="s">
+        <v>254</v>
+      </c>
+      <c r="F146" t="s">
+        <v>332</v>
+      </c>
+      <c r="G146" t="s">
+        <v>198</v>
+      </c>
+      <c r="H146" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ146" t="s">
+        <v>1323</v>
+      </c>
+      <c r="AK146" t="s">
+        <v>1324</v>
+      </c>
+      <c r="AL146" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM146" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN146" t="s">
+        <v>1325</v>
+      </c>
+      <c r="AO146" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF146" t="s">
+        <v>1235</v>
+      </c>
+      <c r="BG146" t="s">
+        <v>1326</v>
+      </c>
+      <c r="BH146" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI146" t="s">
+        <v>1201</v>
+      </c>
+      <c r="BJ146" t="s">
+        <v>1237</v>
+      </c>
+      <c r="BK146">
+        <v>1</v>
+      </c>
+      <c r="BL146">
+        <v>1</v>
+      </c>
+      <c r="BM146">
+        <v>1</v>
+      </c>
+      <c r="BN146">
+        <v>0</v>
+      </c>
+      <c r="BO146">
+        <v>0</v>
+      </c>
+      <c r="BP146">
+        <v>0</v>
+      </c>
+      <c r="BQ146">
+        <v>0</v>
+      </c>
+      <c r="BS146" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY146" s="1"/>
+      <c r="GQ146" s="1"/>
+      <c r="GR146" s="1"/>
+      <c r="GX146">
+        <v>881741150</v>
+      </c>
+      <c r="GY146" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="GZ146" s="1">
+        <v>46294.818460648137</v>
+      </c>
+      <c r="HA146" s="1"/>
+      <c r="HB146" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD146" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE146" t="s">
+        <v>1328</v>
+      </c>
+      <c r="HF146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>46294.774383877317</v>
+      </c>
+      <c r="B147" s="1">
+        <v>46294.943521250003</v>
+      </c>
+      <c r="C147" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D147" t="s">
+        <v>903</v>
+      </c>
+      <c r="E147" t="s">
+        <v>254</v>
+      </c>
+      <c r="F147" t="s">
+        <v>332</v>
+      </c>
+      <c r="G147" t="s">
+        <v>198</v>
+      </c>
+      <c r="H147" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ147" t="s">
+        <v>628</v>
+      </c>
+      <c r="AK147" t="s">
+        <v>628</v>
+      </c>
+      <c r="AL147" t="s">
+        <v>1329</v>
+      </c>
+      <c r="AM147" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN147" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AO147" t="s">
+        <v>463</v>
+      </c>
+      <c r="BF147" t="s">
+        <v>917</v>
+      </c>
+      <c r="BG147" t="s">
+        <v>1331</v>
+      </c>
+      <c r="BH147" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI147" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ147" t="s">
+        <v>921</v>
+      </c>
+      <c r="BK147">
+        <v>0</v>
+      </c>
+      <c r="BL147">
+        <v>0</v>
+      </c>
+      <c r="BM147">
+        <v>1</v>
+      </c>
+      <c r="BN147">
+        <v>0</v>
+      </c>
+      <c r="BO147">
+        <v>0</v>
+      </c>
+      <c r="BP147">
+        <v>0</v>
+      </c>
+      <c r="BQ147">
+        <v>0</v>
+      </c>
+      <c r="BS147" t="s">
+        <v>922</v>
+      </c>
+      <c r="EY147" s="1"/>
+      <c r="GQ147" s="1"/>
+      <c r="GR147" s="1"/>
+      <c r="GX147">
+        <v>881741218</v>
+      </c>
+      <c r="GY147" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="GZ147" s="1">
+        <v>46294.818541666667</v>
+      </c>
+      <c r="HA147" s="1"/>
+      <c r="HB147" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD147" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE147" t="s">
+        <v>1333</v>
+      </c>
+      <c r="HF147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>46295.431909814812</v>
+      </c>
+      <c r="B148" s="1">
+        <v>46295.435575416668</v>
+      </c>
+      <c r="C148" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D148" t="s">
+        <v>903</v>
+      </c>
+      <c r="E148" t="s">
+        <v>309</v>
+      </c>
+      <c r="F148" t="s">
+        <v>609</v>
+      </c>
+      <c r="G148" t="s">
+        <v>198</v>
+      </c>
+      <c r="H148" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ148" t="s">
+        <v>1334</v>
+      </c>
+      <c r="AK148" t="s">
+        <v>1335</v>
+      </c>
+      <c r="AL148" t="s">
+        <v>1336</v>
+      </c>
+      <c r="AM148" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN148" t="s">
+        <v>1337</v>
+      </c>
+      <c r="AO148" t="s">
+        <v>826</v>
+      </c>
+      <c r="AP148" t="s">
+        <v>1338</v>
+      </c>
+      <c r="BF148" t="s">
+        <v>907</v>
+      </c>
+      <c r="BJ148" t="s">
+        <v>1190</v>
+      </c>
+      <c r="BK148">
+        <v>0</v>
+      </c>
+      <c r="BL148">
+        <v>0</v>
+      </c>
+      <c r="BM148">
+        <v>0</v>
+      </c>
+      <c r="BN148">
+        <v>0</v>
+      </c>
+      <c r="BO148">
+        <v>1</v>
+      </c>
+      <c r="BP148">
+        <v>0</v>
+      </c>
+      <c r="BQ148">
+        <v>0</v>
+      </c>
+      <c r="BS148" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY148" s="1"/>
+      <c r="GQ148" s="1"/>
+      <c r="GR148" s="1"/>
+      <c r="GX148">
+        <v>882078081</v>
+      </c>
+      <c r="GY148" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="GZ148" s="1">
+        <v>46295.310601851852</v>
+      </c>
+      <c r="HA148" s="1"/>
+      <c r="HB148" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD148" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE148" t="s">
+        <v>1340</v>
+      </c>
+      <c r="HF148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>46294.713914699067</v>
+      </c>
+      <c r="B149" s="1">
+        <v>46295.534694606482</v>
+      </c>
+      <c r="C149" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D149" t="s">
+        <v>903</v>
+      </c>
+      <c r="E149" t="s">
+        <v>210</v>
+      </c>
+      <c r="F149" t="s">
+        <v>275</v>
+      </c>
+      <c r="G149" t="s">
+        <v>198</v>
+      </c>
+      <c r="H149" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ149" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK149" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL149" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM149" t="s">
+        <v>357</v>
+      </c>
+      <c r="AN149" t="s">
+        <v>1341</v>
+      </c>
+      <c r="AO149" t="s">
+        <v>359</v>
+      </c>
+      <c r="BF149" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG149" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BH149" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI149" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ149" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BK149">
+        <v>1</v>
+      </c>
+      <c r="BL149">
+        <v>1</v>
+      </c>
+      <c r="BM149">
+        <v>0</v>
+      </c>
+      <c r="BN149">
+        <v>0</v>
+      </c>
+      <c r="BO149">
+        <v>0</v>
+      </c>
+      <c r="BP149">
+        <v>0</v>
+      </c>
+      <c r="BQ149">
+        <v>0</v>
+      </c>
+      <c r="BS149" t="s">
+        <v>930</v>
+      </c>
+      <c r="EY149" s="1"/>
+      <c r="GQ149" s="1"/>
+      <c r="GR149" s="1"/>
+      <c r="GX149">
+        <v>882291517</v>
+      </c>
+      <c r="GY149" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="GZ149" s="1">
+        <v>46295.437291666669</v>
+      </c>
+      <c r="HA149" s="1"/>
+      <c r="HB149" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD149" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE149" t="s">
+        <v>1344</v>
+      </c>
+      <c r="HF149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>46295.534696747687</v>
+      </c>
+      <c r="B150" s="1">
+        <v>46295.53698931713</v>
+      </c>
+      <c r="C150" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D150" t="s">
+        <v>903</v>
+      </c>
+      <c r="E150" t="s">
+        <v>210</v>
+      </c>
+      <c r="F150" t="s">
+        <v>275</v>
+      </c>
+      <c r="G150" t="s">
+        <v>198</v>
+      </c>
+      <c r="H150" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ150" t="s">
+        <v>1345</v>
+      </c>
+      <c r="AK150" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL150" t="s">
+        <v>1346</v>
+      </c>
+      <c r="AM150" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN150" t="s">
+        <v>1347</v>
+      </c>
+      <c r="AO150" t="s">
+        <v>359</v>
+      </c>
+      <c r="BF150" t="s">
+        <v>1235</v>
+      </c>
+      <c r="BG150" t="s">
+        <v>1348</v>
+      </c>
+      <c r="BH150" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI150" t="s">
+        <v>1201</v>
+      </c>
+      <c r="BJ150" t="s">
+        <v>1349</v>
+      </c>
+      <c r="BK150">
+        <v>1</v>
+      </c>
+      <c r="BL150">
+        <v>1</v>
+      </c>
+      <c r="BM150">
+        <v>0</v>
+      </c>
+      <c r="BN150">
+        <v>0</v>
+      </c>
+      <c r="BO150">
+        <v>1</v>
+      </c>
+      <c r="BP150">
+        <v>0</v>
+      </c>
+      <c r="BQ150">
+        <v>0</v>
+      </c>
+      <c r="BS150" t="s">
+        <v>1350</v>
+      </c>
+      <c r="EY150" s="1"/>
+      <c r="GQ150" s="1"/>
+      <c r="GR150" s="1"/>
+      <c r="GX150">
+        <v>882291526</v>
+      </c>
+      <c r="GY150" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="GZ150" s="1">
+        <v>46295.437291666669</v>
+      </c>
+      <c r="HA150" s="1"/>
+      <c r="HB150" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD150" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE150" t="s">
+        <v>1352</v>
+      </c>
+      <c r="HF150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>46295.537180023151</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46295.538937650461</v>
+      </c>
+      <c r="C151" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D151" t="s">
+        <v>903</v>
+      </c>
+      <c r="E151" t="s">
+        <v>210</v>
+      </c>
+      <c r="F151" t="s">
+        <v>275</v>
+      </c>
+      <c r="G151" t="s">
+        <v>198</v>
+      </c>
+      <c r="H151" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ151" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK151" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL151" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM151" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN151" t="s">
+        <v>1353</v>
+      </c>
+      <c r="AO151" t="s">
+        <v>359</v>
+      </c>
+      <c r="BF151" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG151" t="s">
+        <v>1354</v>
+      </c>
+      <c r="BH151" t="s">
+        <v>1221</v>
+      </c>
+      <c r="BI151" t="s">
+        <v>957</v>
+      </c>
+      <c r="BJ151" t="s">
+        <v>1355</v>
+      </c>
+      <c r="BK151">
+        <v>0</v>
+      </c>
+      <c r="BL151">
+        <v>0</v>
+      </c>
+      <c r="BM151">
+        <v>0</v>
+      </c>
+      <c r="BN151">
+        <v>0</v>
+      </c>
+      <c r="BO151">
+        <v>0</v>
+      </c>
+      <c r="BP151">
+        <v>1</v>
+      </c>
+      <c r="BQ151">
+        <v>0</v>
+      </c>
+      <c r="BS151" t="s">
+        <v>1191</v>
+      </c>
+      <c r="EY151" s="1"/>
+      <c r="GQ151" s="1"/>
+      <c r="GR151" s="1"/>
+      <c r="GX151">
+        <v>882291539</v>
+      </c>
+      <c r="GY151" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="GZ151" s="1">
+        <v>46295.437303240738</v>
+      </c>
+      <c r="HA151" s="1"/>
+      <c r="HB151" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD151" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE151" t="s">
+        <v>1357</v>
+      </c>
+      <c r="HF151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>46295.538939444443</v>
+      </c>
+      <c r="B152" s="1">
+        <v>46295.541102152783</v>
+      </c>
+      <c r="C152" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D152" t="s">
+        <v>903</v>
+      </c>
+      <c r="E152" t="s">
+        <v>210</v>
+      </c>
+      <c r="F152" t="s">
+        <v>275</v>
+      </c>
+      <c r="G152" t="s">
+        <v>198</v>
+      </c>
+      <c r="H152" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ152" t="s">
+        <v>1358</v>
+      </c>
+      <c r="AK152" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL152" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM152" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN152" t="s">
+        <v>1359</v>
+      </c>
+      <c r="AO152" t="s">
+        <v>359</v>
+      </c>
+      <c r="BF152" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG152" t="s">
+        <v>1360</v>
+      </c>
+      <c r="BH152" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI152" t="s">
+        <v>920</v>
+      </c>
+      <c r="BJ152" t="s">
+        <v>1361</v>
+      </c>
+      <c r="BK152">
+        <v>0</v>
+      </c>
+      <c r="BL152">
+        <v>1</v>
+      </c>
+      <c r="BM152">
+        <v>1</v>
+      </c>
+      <c r="BN152">
+        <v>0</v>
+      </c>
+      <c r="BO152">
+        <v>1</v>
+      </c>
+      <c r="BP152">
+        <v>0</v>
+      </c>
+      <c r="BQ152">
+        <v>0</v>
+      </c>
+      <c r="BS152" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY152" s="1"/>
+      <c r="GQ152" s="1"/>
+      <c r="GR152" s="1"/>
+      <c r="GX152">
+        <v>882291550</v>
+      </c>
+      <c r="GY152" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="GZ152" s="1">
+        <v>46295.437303240738</v>
+      </c>
+      <c r="HA152" s="1"/>
+      <c r="HB152" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD152" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE152" t="s">
+        <v>1363</v>
+      </c>
+      <c r="HF152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>46295.541104618052</v>
+      </c>
+      <c r="B153" s="1">
+        <v>46295.561193657413</v>
+      </c>
+      <c r="C153" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D153" t="s">
+        <v>903</v>
+      </c>
+      <c r="E153" t="s">
+        <v>210</v>
+      </c>
+      <c r="F153" t="s">
+        <v>275</v>
+      </c>
+      <c r="G153" t="s">
+        <v>198</v>
+      </c>
+      <c r="H153" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ153" t="s">
+        <v>1364</v>
+      </c>
+      <c r="AK153" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL153" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM153" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN153" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO153" t="s">
+        <v>359</v>
+      </c>
+      <c r="BF153" t="s">
+        <v>955</v>
+      </c>
+      <c r="BG153" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BH153" t="s">
+        <v>919</v>
+      </c>
+      <c r="BI153" t="s">
+        <v>1186</v>
+      </c>
+      <c r="BJ153" t="s">
+        <v>1366</v>
+      </c>
+      <c r="BK153">
+        <v>1</v>
+      </c>
+      <c r="BL153">
+        <v>0</v>
+      </c>
+      <c r="BM153">
+        <v>1</v>
+      </c>
+      <c r="BN153">
+        <v>0</v>
+      </c>
+      <c r="BO153">
+        <v>0</v>
+      </c>
+      <c r="BP153">
+        <v>0</v>
+      </c>
+      <c r="BQ153">
+        <v>0</v>
+      </c>
+      <c r="BS153" t="s">
+        <v>909</v>
+      </c>
+      <c r="EY153" s="1"/>
+      <c r="GQ153" s="1"/>
+      <c r="GR153" s="1"/>
+      <c r="GX153">
+        <v>882291559</v>
+      </c>
+      <c r="GY153" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="GZ153" s="1">
+        <v>46295.437314814822</v>
+      </c>
+      <c r="HA153" s="1"/>
+      <c r="HB153" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD153" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE153" t="s">
+        <v>1368</v>
+      </c>
+      <c r="HF153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>46294.620388888892</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46295.648787395832</v>
+      </c>
+      <c r="C154" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D154" t="s">
+        <v>707</v>
+      </c>
+      <c r="E154" t="s">
+        <v>196</v>
+      </c>
+      <c r="F154" t="s">
+        <v>793</v>
+      </c>
+      <c r="G154" t="s">
+        <v>198</v>
+      </c>
+      <c r="H154" t="s">
+        <v>199</v>
+      </c>
+      <c r="J154" t="s">
+        <v>1369</v>
+      </c>
+      <c r="K154" t="s">
+        <v>1168</v>
+      </c>
+      <c r="L154">
+        <v>800</v>
+      </c>
+      <c r="M154">
+        <v>378</v>
+      </c>
+      <c r="N154">
+        <v>422</v>
+      </c>
+      <c r="O154">
+        <v>10</v>
+      </c>
+      <c r="P154">
+        <v>2</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>395</v>
+      </c>
+      <c r="R154">
+        <v>30</v>
+      </c>
+      <c r="S154" t="s">
+        <v>214</v>
+      </c>
+      <c r="T154" t="s">
+        <v>215</v>
+      </c>
+      <c r="U154" t="s">
+        <v>217</v>
+      </c>
+      <c r="V154" t="s">
+        <v>216</v>
+      </c>
+      <c r="W154" t="s">
+        <v>217</v>
+      </c>
+      <c r="X154" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ154" t="s">
+        <v>1370</v>
+      </c>
+      <c r="AK154" t="s">
+        <v>1371</v>
+      </c>
+      <c r="AL154" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AM154" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN154" t="s">
+        <v>1372</v>
+      </c>
+      <c r="EY154" s="1"/>
+      <c r="GQ154" s="1"/>
+      <c r="GR154" s="1"/>
+      <c r="GX154">
+        <v>882434680</v>
+      </c>
+      <c r="GY154" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="GZ154" s="1">
+        <v>46295.523819444446</v>
+      </c>
+      <c r="HA154" s="1"/>
+      <c r="HB154" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD154" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE154" t="s">
+        <v>1374</v>
+      </c>
+      <c r="HF154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>46295.648789212973</v>
+      </c>
+      <c r="B155" s="1">
+        <v>46295.654622361108</v>
+      </c>
+      <c r="C155" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D155" t="s">
+        <v>969</v>
+      </c>
+      <c r="E155" t="s">
+        <v>196</v>
+      </c>
+      <c r="F155" t="s">
+        <v>228</v>
+      </c>
+      <c r="G155" t="s">
+        <v>198</v>
+      </c>
+      <c r="H155" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ155" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AK155" t="s">
+        <v>1376</v>
+      </c>
+      <c r="AL155" t="s">
+        <v>1377</v>
+      </c>
+      <c r="AM155" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN155" t="s">
+        <v>1378</v>
+      </c>
+      <c r="AO155" t="s">
+        <v>570</v>
+      </c>
+      <c r="BU155" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BV155" t="s">
+        <v>1107</v>
+      </c>
+      <c r="BW155">
+        <v>1</v>
+      </c>
+      <c r="BX155">
+        <v>0</v>
+      </c>
+      <c r="BY155">
+        <v>0</v>
+      </c>
+      <c r="BZ155">
+        <v>0</v>
+      </c>
+      <c r="CA155">
+        <v>0</v>
+      </c>
+      <c r="CC155" t="s">
+        <v>1379</v>
+      </c>
+      <c r="CD155" t="s">
+        <v>1380</v>
+      </c>
+      <c r="CE155" t="s">
+        <v>996</v>
+      </c>
+      <c r="CF155">
+        <v>1</v>
+      </c>
+      <c r="CG155">
+        <v>0</v>
+      </c>
+      <c r="CH155">
+        <v>0</v>
+      </c>
+      <c r="CI155" t="s">
+        <v>1100</v>
+      </c>
+      <c r="EY155" s="1"/>
+      <c r="GQ155" s="1"/>
+      <c r="GR155" s="1"/>
+      <c r="GX155">
+        <v>882444804</v>
+      </c>
+      <c r="GY155" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="GZ155" s="1">
+        <v>46295.529652777783</v>
+      </c>
+      <c r="HA155" s="1"/>
+      <c r="HB155" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD155" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE155" t="s">
+        <v>1382</v>
+      </c>
+      <c r="HF155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>46295.654624247683</v>
+      </c>
+      <c r="B156" s="1">
+        <v>46295.662365636577</v>
+      </c>
+      <c r="C156" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D156" t="s">
+        <v>706</v>
+      </c>
+      <c r="E156" t="s">
+        <v>196</v>
+      </c>
+      <c r="F156" t="s">
+        <v>196</v>
+      </c>
+      <c r="G156" t="s">
+        <v>198</v>
+      </c>
+      <c r="H156" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z156" t="s">
+        <v>826</v>
+      </c>
+      <c r="AA156" t="s">
+        <v>1383</v>
+      </c>
+      <c r="AB156">
+        <v>2</v>
+      </c>
+      <c r="AC156">
+        <v>2</v>
+      </c>
+      <c r="AD156" t="s">
+        <v>395</v>
+      </c>
+      <c r="AE156" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AF156" t="s">
+        <v>687</v>
+      </c>
+      <c r="AG156" t="s">
+        <v>327</v>
+      </c>
+      <c r="AH156" t="s">
+        <v>324</v>
+      </c>
+      <c r="AJ156" t="s">
+        <v>1385</v>
+      </c>
+      <c r="AK156" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AL156" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AM156" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN156" t="s">
+        <v>1388</v>
+      </c>
+      <c r="EY156" s="1"/>
+      <c r="GQ156" s="1"/>
+      <c r="GR156" s="1"/>
+      <c r="GX156">
+        <v>882457796</v>
+      </c>
+      <c r="GY156" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="GZ156" s="1">
+        <v>46295.537395833337</v>
+      </c>
+      <c r="HA156" s="1"/>
+      <c r="HB156" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD156" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE156" t="s">
+        <v>1390</v>
+      </c>
+      <c r="HF156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>46295.662366921293</v>
+      </c>
+      <c r="B157" s="1">
+        <v>46295.66547644676</v>
+      </c>
+      <c r="C157" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D157" t="s">
+        <v>706</v>
+      </c>
+      <c r="E157" t="s">
+        <v>196</v>
+      </c>
+      <c r="F157" t="s">
+        <v>793</v>
+      </c>
+      <c r="G157" t="s">
+        <v>198</v>
+      </c>
+      <c r="H157" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z157" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB157">
+        <v>4</v>
+      </c>
+      <c r="AC157">
+        <v>16</v>
+      </c>
+      <c r="AD157" t="s">
+        <v>395</v>
+      </c>
+      <c r="AE157" t="s">
+        <v>1391</v>
+      </c>
+      <c r="AF157" t="s">
+        <v>326</v>
+      </c>
+      <c r="AG157" t="s">
+        <v>327</v>
+      </c>
+      <c r="AH157" t="s">
+        <v>395</v>
+      </c>
+      <c r="AJ157" t="s">
+        <v>1392</v>
+      </c>
+      <c r="AK157" t="s">
+        <v>1393</v>
+      </c>
+      <c r="AL157" t="s">
+        <v>1394</v>
+      </c>
+      <c r="AM157" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN157" t="s">
+        <v>1395</v>
+      </c>
+      <c r="EY157" s="1"/>
+      <c r="GQ157" s="1"/>
+      <c r="GR157" s="1"/>
+      <c r="GX157">
+        <v>882463311</v>
+      </c>
+      <c r="GY157" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="GZ157" s="1">
+        <v>46295.540509259263</v>
+      </c>
+      <c r="HA157" s="1"/>
+      <c r="HB157" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD157" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE157" t="s">
+        <v>1397</v>
+      </c>
+      <c r="HF157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>46295.701731238427</v>
+      </c>
+      <c r="B158" s="1">
+        <v>46295.704091446758</v>
+      </c>
+      <c r="C158" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D158" t="s">
+        <v>969</v>
+      </c>
+      <c r="E158" t="s">
+        <v>210</v>
+      </c>
+      <c r="F158" t="s">
+        <v>275</v>
+      </c>
+      <c r="G158" t="s">
+        <v>198</v>
+      </c>
+      <c r="H158" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ158" t="s">
+        <v>1398</v>
+      </c>
+      <c r="AK158" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL158" t="s">
+        <v>1399</v>
+      </c>
+      <c r="AM158" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN158" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO158" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU158" t="s">
+        <v>992</v>
+      </c>
+      <c r="BV158" t="s">
+        <v>1107</v>
+      </c>
+      <c r="BW158">
+        <v>1</v>
+      </c>
+      <c r="BX158">
+        <v>0</v>
+      </c>
+      <c r="BY158">
+        <v>0</v>
+      </c>
+      <c r="BZ158">
+        <v>0</v>
+      </c>
+      <c r="CA158">
+        <v>0</v>
+      </c>
+      <c r="CC158" t="s">
+        <v>1400</v>
+      </c>
+      <c r="CD158" t="s">
+        <v>1401</v>
+      </c>
+      <c r="CE158" t="s">
+        <v>996</v>
+      </c>
+      <c r="CF158">
+        <v>1</v>
+      </c>
+      <c r="CG158">
+        <v>0</v>
+      </c>
+      <c r="CH158">
+        <v>0</v>
+      </c>
+      <c r="CI158" t="s">
+        <v>1100</v>
+      </c>
+      <c r="EY158" s="1"/>
+      <c r="GQ158" s="1"/>
+      <c r="GR158" s="1"/>
+      <c r="GX158">
+        <v>882566347</v>
+      </c>
+      <c r="GY158" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="GZ158" s="1">
+        <v>46295.597604166673</v>
+      </c>
+      <c r="HA158" s="1"/>
+      <c r="HB158" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD158" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE158" t="s">
+        <v>1403</v>
+      </c>
+      <c r="HF158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>46295.704093333326</v>
+      </c>
+      <c r="B159" s="1">
+        <v>46295.709933587961</v>
+      </c>
+      <c r="C159" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D159" t="s">
+        <v>969</v>
+      </c>
+      <c r="E159" t="s">
+        <v>210</v>
+      </c>
+      <c r="F159" t="s">
+        <v>275</v>
+      </c>
+      <c r="G159" t="s">
+        <v>198</v>
+      </c>
+      <c r="H159" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ159" t="s">
+        <v>1404</v>
+      </c>
+      <c r="AK159" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL159" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AM159" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN159" t="s">
+        <v>1406</v>
+      </c>
+      <c r="AO159" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU159" t="s">
+        <v>974</v>
+      </c>
+      <c r="BV159" t="s">
+        <v>1096</v>
+      </c>
+      <c r="BW159">
+        <v>1</v>
+      </c>
+      <c r="BX159">
+        <v>0</v>
+      </c>
+      <c r="BY159">
+        <v>1</v>
+      </c>
+      <c r="BZ159">
+        <v>0</v>
+      </c>
+      <c r="CA159">
+        <v>0</v>
+      </c>
+      <c r="CC159" t="s">
+        <v>1407</v>
+      </c>
+      <c r="CD159" t="s">
+        <v>1401</v>
+      </c>
+      <c r="CE159" t="s">
+        <v>996</v>
+      </c>
+      <c r="CF159">
+        <v>1</v>
+      </c>
+      <c r="CG159">
+        <v>0</v>
+      </c>
+      <c r="CH159">
+        <v>0</v>
+      </c>
+      <c r="CI159" t="s">
+        <v>1100</v>
+      </c>
+      <c r="CO159" t="s">
+        <v>1408</v>
+      </c>
+      <c r="CP159" t="s">
+        <v>1409</v>
+      </c>
+      <c r="CQ159" t="s">
+        <v>1103</v>
+      </c>
+      <c r="EY159" s="1"/>
+      <c r="GQ159" s="1"/>
+      <c r="GR159" s="1"/>
+      <c r="GX159">
+        <v>882566372</v>
+      </c>
+      <c r="GY159" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="GZ159" s="1">
+        <v>46295.597615740742</v>
+      </c>
+      <c r="HA159" s="1"/>
+      <c r="HB159" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD159" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE159" t="s">
+        <v>1411</v>
+      </c>
+      <c r="HF159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>46295.709935613428</v>
+      </c>
+      <c r="B160" s="1">
+        <v>46295.713655601852</v>
+      </c>
+      <c r="C160" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D160" t="s">
+        <v>969</v>
+      </c>
+      <c r="E160" t="s">
+        <v>210</v>
+      </c>
+      <c r="F160" t="s">
+        <v>275</v>
+      </c>
+      <c r="G160" t="s">
+        <v>198</v>
+      </c>
+      <c r="H160" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ160" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK160" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL160" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM160" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN160" t="s">
+        <v>1412</v>
+      </c>
+      <c r="AO160" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU160" t="s">
+        <v>974</v>
+      </c>
+      <c r="BV160" t="s">
+        <v>1413</v>
+      </c>
+      <c r="BW160">
+        <v>1</v>
+      </c>
+      <c r="BX160">
+        <v>1</v>
+      </c>
+      <c r="BY160">
+        <v>0</v>
+      </c>
+      <c r="BZ160">
+        <v>0</v>
+      </c>
+      <c r="CA160">
+        <v>0</v>
+      </c>
+      <c r="CC160" t="s">
+        <v>1414</v>
+      </c>
+      <c r="CD160" t="s">
+        <v>1415</v>
+      </c>
+      <c r="CE160" t="s">
+        <v>996</v>
+      </c>
+      <c r="CF160">
+        <v>1</v>
+      </c>
+      <c r="CG160">
+        <v>0</v>
+      </c>
+      <c r="CH160">
+        <v>0</v>
+      </c>
+      <c r="CI160" t="s">
+        <v>1100</v>
+      </c>
+      <c r="CK160" t="s">
+        <v>1416</v>
+      </c>
+      <c r="CL160" t="s">
+        <v>1417</v>
+      </c>
+      <c r="CM160" t="s">
+        <v>1075</v>
+      </c>
+      <c r="EY160" s="1"/>
+      <c r="GQ160" s="1"/>
+      <c r="GR160" s="1"/>
+      <c r="GX160">
+        <v>882566385</v>
+      </c>
+      <c r="GY160" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="GZ160" s="1">
+        <v>46295.597627314812</v>
+      </c>
+      <c r="HA160" s="1"/>
+      <c r="HB160" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD160" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE160" t="s">
+        <v>1419</v>
+      </c>
+      <c r="HF160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>46295.71365740741</v>
+      </c>
+      <c r="B161" s="1">
+        <v>46295.716883854169</v>
+      </c>
+      <c r="C161" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D161" t="s">
+        <v>969</v>
+      </c>
+      <c r="E161" t="s">
+        <v>210</v>
+      </c>
+      <c r="F161" t="s">
+        <v>275</v>
+      </c>
+      <c r="G161" t="s">
+        <v>198</v>
+      </c>
+      <c r="H161" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ161" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AK161" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL161" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM161" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN161" t="s">
+        <v>1219</v>
+      </c>
+      <c r="AO161" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU161" t="s">
+        <v>974</v>
+      </c>
+      <c r="BV161" t="s">
+        <v>1421</v>
+      </c>
+      <c r="BW161">
+        <v>0</v>
+      </c>
+      <c r="BX161">
+        <v>0</v>
+      </c>
+      <c r="BY161">
+        <v>1</v>
+      </c>
+      <c r="BZ161">
+        <v>0</v>
+      </c>
+      <c r="CA161">
+        <v>0</v>
+      </c>
+      <c r="CO161" t="s">
+        <v>979</v>
+      </c>
+      <c r="CP161" t="s">
+        <v>1422</v>
+      </c>
+      <c r="CQ161" t="s">
+        <v>981</v>
+      </c>
+      <c r="EY161" s="1"/>
+      <c r="GQ161" s="1"/>
+      <c r="GR161" s="1"/>
+      <c r="GX161">
+        <v>882566394</v>
+      </c>
+      <c r="GY161" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="GZ161" s="1">
+        <v>46295.597627314812</v>
+      </c>
+      <c r="HA161" s="1"/>
+      <c r="HB161" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD161" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE161" t="s">
+        <v>1424</v>
+      </c>
+      <c r="HF161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>46295.716885624999</v>
+      </c>
+      <c r="B162" s="1">
+        <v>46295.722203263889</v>
+      </c>
+      <c r="C162" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D162" t="s">
+        <v>969</v>
+      </c>
+      <c r="E162" t="s">
+        <v>210</v>
+      </c>
+      <c r="F162" t="s">
+        <v>275</v>
+      </c>
+      <c r="G162" t="s">
+        <v>198</v>
+      </c>
+      <c r="H162" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ162" t="s">
+        <v>971</v>
+      </c>
+      <c r="AK162" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL162" t="s">
+        <v>971</v>
+      </c>
+      <c r="AM162" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN162" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AO162" t="s">
+        <v>359</v>
+      </c>
+      <c r="BU162" t="s">
+        <v>992</v>
+      </c>
+      <c r="BV162" t="s">
+        <v>1413</v>
+      </c>
+      <c r="BW162">
+        <v>1</v>
+      </c>
+      <c r="BX162">
+        <v>1</v>
+      </c>
+      <c r="BY162">
+        <v>0</v>
+      </c>
+      <c r="BZ162">
+        <v>0</v>
+      </c>
+      <c r="CA162">
+        <v>0</v>
+      </c>
+      <c r="CC162" t="s">
+        <v>1426</v>
+      </c>
+      <c r="CD162" t="s">
+        <v>1427</v>
+      </c>
+      <c r="CE162" t="s">
+        <v>1072</v>
+      </c>
+      <c r="CF162">
+        <v>1</v>
+      </c>
+      <c r="CG162">
+        <v>1</v>
+      </c>
+      <c r="CH162">
+        <v>0</v>
+      </c>
+      <c r="CI162" t="s">
+        <v>997</v>
+      </c>
+      <c r="CK162" t="s">
+        <v>1428</v>
+      </c>
+      <c r="CL162" t="s">
+        <v>1429</v>
+      </c>
+      <c r="CM162" t="s">
+        <v>1075</v>
+      </c>
+      <c r="EY162" s="1"/>
+      <c r="GQ162" s="1"/>
+      <c r="GR162" s="1"/>
+      <c r="GX162">
+        <v>882566412</v>
+      </c>
+      <c r="GY162" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="GZ162" s="1">
+        <v>46295.597638888888</v>
+      </c>
+      <c r="HA162" s="1"/>
+      <c r="HB162" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD162" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE162" t="s">
+        <v>1431</v>
+      </c>
+      <c r="HF162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:214" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
+        <v>46295.665477905102</v>
+      </c>
+      <c r="B163" s="1">
+        <v>46295.750759849543</v>
+      </c>
+      <c r="C163" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D163" t="s">
+        <v>707</v>
+      </c>
+      <c r="E163" t="s">
+        <v>196</v>
+      </c>
+      <c r="F163" t="s">
+        <v>634</v>
+      </c>
+      <c r="G163" t="s">
+        <v>198</v>
+      </c>
+      <c r="H163" t="s">
+        <v>199</v>
+      </c>
+      <c r="J163" t="s">
+        <v>1432</v>
+      </c>
+      <c r="K163" t="s">
+        <v>1168</v>
+      </c>
+      <c r="L163">
+        <v>830</v>
+      </c>
+      <c r="M163">
+        <v>357</v>
+      </c>
+      <c r="N163">
+        <v>473</v>
+      </c>
+      <c r="O163">
+        <v>22</v>
+      </c>
+      <c r="P163">
+        <v>2</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>395</v>
+      </c>
+      <c r="R163">
+        <v>25</v>
+      </c>
+      <c r="S163" t="s">
+        <v>214</v>
+      </c>
+      <c r="T163" t="s">
+        <v>215</v>
+      </c>
+      <c r="U163" t="s">
+        <v>203</v>
+      </c>
+      <c r="V163" t="s">
+        <v>202</v>
+      </c>
+      <c r="W163" t="s">
+        <v>203</v>
+      </c>
+      <c r="X163" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y163" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ163" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AK163" t="s">
+        <v>637</v>
+      </c>
+      <c r="AL163" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AM163" t="s">
+        <v>453</v>
+      </c>
+      <c r="AN163" t="s">
+        <v>1433</v>
+      </c>
+      <c r="EY163" s="1"/>
+      <c r="GQ163" s="1"/>
+      <c r="GR163" s="1"/>
+      <c r="GX163">
+        <v>882619721</v>
+      </c>
+      <c r="GY163" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="GZ163" s="1">
+        <v>46295.625798611109</v>
+      </c>
+      <c r="HA163" s="1"/>
+      <c r="HB163" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="HD163" t="s">
+        <v>722</v>
+      </c>
+      <c r="HE163" t="s">
+        <v>1435</v>
+      </c>
+      <c r="HF163">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="369" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3277152B-F0BF-3344-819C-8C0827C055DA}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2CDC854-83CA-4E4B-8813-206183A71E2C}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2060" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1820" yWindow="900" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Public Health Emergencies" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4962" uniqueCount="1784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5095" uniqueCount="1816">
   <si>
     <t>start</t>
   </si>
@@ -5389,6 +5389,102 @@
   </si>
   <si>
     <t>uuid:edb547f0-2b31-425c-9ceb-1aa336f4becb</t>
+  </si>
+  <si>
+    <t>In the morning while entering school</t>
+  </si>
+  <si>
+    <t>At the kitchen</t>
+  </si>
+  <si>
+    <t>Mpox can be seen by body rushs while malaria is by high temperature</t>
+  </si>
+  <si>
+    <t>I talk to the school nurse to help him</t>
+  </si>
+  <si>
+    <t>37097fdb-ddbd-4571-9b4d-b5a9883bdc0d</t>
+  </si>
+  <si>
+    <t>uuid:37097fdb-ddbd-4571-9b4d-b5a9883bdc0d</t>
+  </si>
+  <si>
+    <t>Busega</t>
+  </si>
+  <si>
+    <t>KCCA Busega Community School</t>
+  </si>
+  <si>
+    <t>Ebola kills instantly</t>
+  </si>
+  <si>
+    <t>Little knowledge on public health emergencies</t>
+  </si>
+  <si>
+    <t>Encourage the school health club to continue sensitization of pupils on public health emergencies</t>
+  </si>
+  <si>
+    <t>4a6e3196-52a9-4086-9c32-b8ef4858d984</t>
+  </si>
+  <si>
+    <t>v7P6Cr66geEtrTnJmvbR3K</t>
+  </si>
+  <si>
+    <t>uuid:4a6e3196-52a9-4086-9c32-b8ef4858d984</t>
+  </si>
+  <si>
+    <t>Ebola is a political stunt. This has been said several times</t>
+  </si>
+  <si>
+    <t>Over population and congestion</t>
+  </si>
+  <si>
+    <t>Reduce on the prices for rent inside the  market such that the people can leave the drainage area and settle inside the markets</t>
+  </si>
+  <si>
+    <t>121755e1-9242-497b-8bb4-a65613e2db92</t>
+  </si>
+  <si>
+    <t>uuid:121755e1-9242-497b-8bb4-a65613e2db92</t>
+  </si>
+  <si>
+    <t>Ignorance on public health emergency</t>
+  </si>
+  <si>
+    <t>Work with KCCA to ensure that the sewage is removed before it overflows</t>
+  </si>
+  <si>
+    <t>aa4af4ec-028a-4ee4-8c97-76886b04d681</t>
+  </si>
+  <si>
+    <t>uuid:aa4af4ec-028a-4ee4-8c97-76886b04d681</t>
+  </si>
+  <si>
+    <t>Yes, already active</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>School assembly</t>
+  </si>
+  <si>
+    <t>What is UNICEF in full? Do we still have Ebola cases in Uganda?</t>
+  </si>
+  <si>
+    <t>Limited knowledge at times that leads to people not doing the right thing</t>
+  </si>
+  <si>
+    <t>More engagements should be carried. A U report talking point was requested to be placed in the school compound.</t>
+  </si>
+  <si>
+    <t>6dcc52e1-0b13-4cf0-9e4d-a6d77fb4c2cd</t>
+  </si>
+  <si>
+    <t>uuid:6dcc52e1-0b13-4cf0-9e4d-a6d77fb4c2cd</t>
   </si>
 </sst>
 </file>
@@ -19793,8 +19889,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY206" totalsRowShown="0">
-  <autoFilter ref="A1:IY206" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY211" totalsRowShown="0">
+  <autoFilter ref="A1:IY211" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -20347,7 +20443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY206"/>
+  <dimension ref="A1:IY211"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -20530,6 +20626,8 @@
     <col min="202" max="202" width="15" customWidth="1"/>
     <col min="203" max="203" width="12.5" customWidth="1"/>
     <col min="204" max="204" width="15.33203125" customWidth="1"/>
+    <col min="251" max="251" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="253" max="253" width="17.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:259" x14ac:dyDescent="0.2">
@@ -43848,6 +43946,720 @@
       </c>
       <c r="IY206">
         <v>207</v>
+      </c>
+    </row>
+    <row r="207" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A207" s="1">
+        <v>46296.826218819442</v>
+      </c>
+      <c r="B207" s="1">
+        <v>46296.838381712972</v>
+      </c>
+      <c r="C207" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D207" t="s">
+        <v>945</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+      <c r="F207" t="s">
+        <v>398</v>
+      </c>
+      <c r="G207" t="s">
+        <v>198</v>
+      </c>
+      <c r="H207" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS207" t="s">
+        <v>947</v>
+      </c>
+      <c r="BT207" t="s">
+        <v>947</v>
+      </c>
+      <c r="BU207" t="s">
+        <v>1670</v>
+      </c>
+      <c r="BW207" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX207" t="s">
+        <v>1195</v>
+      </c>
+      <c r="BY207" t="s">
+        <v>356</v>
+      </c>
+      <c r="DE207" t="s">
+        <v>950</v>
+      </c>
+      <c r="DF207" t="s">
+        <v>1389</v>
+      </c>
+      <c r="DG207">
+        <v>1</v>
+      </c>
+      <c r="DH207">
+        <v>1</v>
+      </c>
+      <c r="DI207">
+        <v>0</v>
+      </c>
+      <c r="DJ207">
+        <v>0</v>
+      </c>
+      <c r="DK207">
+        <v>0</v>
+      </c>
+      <c r="DM207" t="s">
+        <v>1784</v>
+      </c>
+      <c r="DN207" t="s">
+        <v>1785</v>
+      </c>
+      <c r="DO207" t="s">
+        <v>972</v>
+      </c>
+      <c r="DP207">
+        <v>1</v>
+      </c>
+      <c r="DQ207">
+        <v>0</v>
+      </c>
+      <c r="DR207">
+        <v>0</v>
+      </c>
+      <c r="DS207" t="s">
+        <v>1076</v>
+      </c>
+      <c r="DU207" t="s">
+        <v>1786</v>
+      </c>
+      <c r="DV207" t="s">
+        <v>1787</v>
+      </c>
+      <c r="DW207" t="s">
+        <v>1051</v>
+      </c>
+      <c r="EY207" s="1"/>
+      <c r="GQ207" s="1"/>
+      <c r="GR207" s="1"/>
+      <c r="GY207" s="1"/>
+      <c r="GZ207" s="1"/>
+      <c r="HA207" s="1"/>
+      <c r="HB207" s="1"/>
+      <c r="IQ207" s="1">
+        <v>883775489</v>
+      </c>
+      <c r="IR207" t="s">
+        <v>1788</v>
+      </c>
+      <c r="IS207" s="1">
+        <v>46296.713414351849</v>
+      </c>
+      <c r="IU207" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW207" t="s">
+        <v>1593</v>
+      </c>
+      <c r="IX207" t="s">
+        <v>1789</v>
+      </c>
+      <c r="IY207">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="208" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A208" s="1">
+        <v>46296.903357361109</v>
+      </c>
+      <c r="B208" s="1">
+        <v>46296.906310636572</v>
+      </c>
+      <c r="C208" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D208" t="s">
+        <v>684</v>
+      </c>
+      <c r="E208" t="s">
+        <v>292</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G208" t="s">
+        <v>198</v>
+      </c>
+      <c r="H208" t="s">
+        <v>294</v>
+      </c>
+      <c r="J208" t="s">
+        <v>1791</v>
+      </c>
+      <c r="K208" t="s">
+        <v>201</v>
+      </c>
+      <c r="L208" t="s">
+        <v>321</v>
+      </c>
+      <c r="M208" t="s">
+        <v>605</v>
+      </c>
+      <c r="N208" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O208" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AH208">
+        <v>558</v>
+      </c>
+      <c r="AI208">
+        <v>284</v>
+      </c>
+      <c r="AJ208">
+        <v>274</v>
+      </c>
+      <c r="AK208">
+        <v>14</v>
+      </c>
+      <c r="AL208">
+        <v>2</v>
+      </c>
+      <c r="AM208">
+        <v>0</v>
+      </c>
+      <c r="AN208">
+        <v>0</v>
+      </c>
+      <c r="AO208" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AP208">
+        <v>0</v>
+      </c>
+      <c r="AQ208" t="s">
+        <v>337</v>
+      </c>
+      <c r="AR208" t="s">
+        <v>338</v>
+      </c>
+      <c r="AS208" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT208" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU208" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV208" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW208" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS208" t="s">
+        <v>1792</v>
+      </c>
+      <c r="BT208" t="s">
+        <v>1793</v>
+      </c>
+      <c r="BU208" t="s">
+        <v>1670</v>
+      </c>
+      <c r="BW208" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX208" t="s">
+        <v>1794</v>
+      </c>
+      <c r="EY208" s="1"/>
+      <c r="GQ208" s="1"/>
+      <c r="GR208" s="1"/>
+      <c r="GY208" s="1"/>
+      <c r="GZ208" s="1"/>
+      <c r="HA208" s="1"/>
+      <c r="HB208" s="1"/>
+      <c r="IQ208" s="1">
+        <v>883861420</v>
+      </c>
+      <c r="IR208" t="s">
+        <v>1795</v>
+      </c>
+      <c r="IS208" s="1">
+        <v>46296.781342592592</v>
+      </c>
+      <c r="IU208" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW208" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX208" t="s">
+        <v>1797</v>
+      </c>
+      <c r="IY208">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="209" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A209" s="1">
+        <v>46296.906311192128</v>
+      </c>
+      <c r="B209" s="1">
+        <v>46296.908533993053</v>
+      </c>
+      <c r="C209" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D209" t="s">
+        <v>879</v>
+      </c>
+      <c r="E209" t="s">
+        <v>292</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G209" t="s">
+        <v>198</v>
+      </c>
+      <c r="H209" t="s">
+        <v>294</v>
+      </c>
+      <c r="BS209" t="s">
+        <v>1798</v>
+      </c>
+      <c r="BT209" t="s">
+        <v>1799</v>
+      </c>
+      <c r="BU209" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV209" t="s">
+        <v>1003</v>
+      </c>
+      <c r="BW209" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX209" t="s">
+        <v>1800</v>
+      </c>
+      <c r="BY209" t="s">
+        <v>453</v>
+      </c>
+      <c r="CP209" t="s">
+        <v>1211</v>
+      </c>
+      <c r="CQ209" t="s">
+        <v>392</v>
+      </c>
+      <c r="CR209" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS209" t="s">
+        <v>933</v>
+      </c>
+      <c r="CT209" t="s">
+        <v>1337</v>
+      </c>
+      <c r="CU209">
+        <v>0</v>
+      </c>
+      <c r="CV209">
+        <v>1</v>
+      </c>
+      <c r="CW209">
+        <v>1</v>
+      </c>
+      <c r="CX209">
+        <v>0</v>
+      </c>
+      <c r="CY209">
+        <v>1</v>
+      </c>
+      <c r="CZ209">
+        <v>0</v>
+      </c>
+      <c r="DA209">
+        <v>0</v>
+      </c>
+      <c r="DC209" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY209" s="1"/>
+      <c r="GQ209" s="1"/>
+      <c r="GR209" s="1"/>
+      <c r="GY209" s="1"/>
+      <c r="GZ209" s="1"/>
+      <c r="HA209" s="1"/>
+      <c r="HB209" s="1"/>
+      <c r="IQ209" s="1">
+        <v>883864451</v>
+      </c>
+      <c r="IR209" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IS209" s="1">
+        <v>46296.783553240741</v>
+      </c>
+      <c r="IU209" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW209" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX209" t="s">
+        <v>1802</v>
+      </c>
+      <c r="IY209">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="210" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A210" s="1">
+        <v>46296.908534444447</v>
+      </c>
+      <c r="B210" s="1">
+        <v>46296.912112175924</v>
+      </c>
+      <c r="C210" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D210" t="s">
+        <v>769</v>
+      </c>
+      <c r="E210" t="s">
+        <v>292</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G210" t="s">
+        <v>198</v>
+      </c>
+      <c r="H210" t="s">
+        <v>294</v>
+      </c>
+      <c r="BS210" t="s">
+        <v>1610</v>
+      </c>
+      <c r="BT210" t="s">
+        <v>1803</v>
+      </c>
+      <c r="BU210" t="s">
+        <v>1670</v>
+      </c>
+      <c r="BW210" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX210" t="s">
+        <v>1804</v>
+      </c>
+      <c r="EY210" s="1"/>
+      <c r="GJ210" s="1">
+        <v>46296</v>
+      </c>
+      <c r="GK210" t="s">
+        <v>1791</v>
+      </c>
+      <c r="GL210" t="s">
+        <v>413</v>
+      </c>
+      <c r="GN210">
+        <v>284</v>
+      </c>
+      <c r="GO210">
+        <v>274</v>
+      </c>
+      <c r="GP210">
+        <v>6</v>
+      </c>
+      <c r="GQ210" s="1">
+        <v>8</v>
+      </c>
+      <c r="GR210" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="GS210" t="s">
+        <v>423</v>
+      </c>
+      <c r="GT210" t="s">
+        <v>374</v>
+      </c>
+      <c r="GU210" t="s">
+        <v>375</v>
+      </c>
+      <c r="GV210" t="s">
+        <v>425</v>
+      </c>
+      <c r="GX210" t="s">
+        <v>426</v>
+      </c>
+      <c r="GY210" s="1">
+        <v>4</v>
+      </c>
+      <c r="GZ210" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="HA210" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="HB210" s="1">
+        <v>9</v>
+      </c>
+      <c r="HC210">
+        <v>9</v>
+      </c>
+      <c r="HD210" t="s">
+        <v>416</v>
+      </c>
+      <c r="HE210" t="s">
+        <v>447</v>
+      </c>
+      <c r="HF210" t="s">
+        <v>474</v>
+      </c>
+      <c r="HG210">
+        <v>0</v>
+      </c>
+      <c r="HH210">
+        <v>1</v>
+      </c>
+      <c r="HI210">
+        <v>0</v>
+      </c>
+      <c r="HJ210">
+        <v>0</v>
+      </c>
+      <c r="HK210" t="s">
+        <v>392</v>
+      </c>
+      <c r="HM210">
+        <v>5</v>
+      </c>
+      <c r="HN210">
+        <v>5</v>
+      </c>
+      <c r="HO210">
+        <v>2</v>
+      </c>
+      <c r="HP210">
+        <v>8</v>
+      </c>
+      <c r="HQ210">
+        <v>3</v>
+      </c>
+      <c r="HR210">
+        <v>4</v>
+      </c>
+      <c r="IQ210" s="1">
+        <v>883868242</v>
+      </c>
+      <c r="IR210" t="s">
+        <v>1805</v>
+      </c>
+      <c r="IS210" s="1">
+        <v>46296.787129629629</v>
+      </c>
+      <c r="IU210" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW210" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX210" t="s">
+        <v>1806</v>
+      </c>
+      <c r="IY210">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="211" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A211" s="1">
+        <v>46297.307513391213</v>
+      </c>
+      <c r="B211" s="1">
+        <v>46297.323723969908</v>
+      </c>
+      <c r="C211" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D211" t="s">
+        <v>684</v>
+      </c>
+      <c r="E211" t="s">
+        <v>251</v>
+      </c>
+      <c r="F211" t="s">
+        <v>268</v>
+      </c>
+      <c r="G211" t="s">
+        <v>198</v>
+      </c>
+      <c r="H211" t="s">
+        <v>253</v>
+      </c>
+      <c r="J211" t="s">
+        <v>412</v>
+      </c>
+      <c r="K211" t="s">
+        <v>201</v>
+      </c>
+      <c r="L211" t="s">
+        <v>321</v>
+      </c>
+      <c r="M211" t="s">
+        <v>1694</v>
+      </c>
+      <c r="N211" t="s">
+        <v>1665</v>
+      </c>
+      <c r="O211" t="s">
+        <v>1807</v>
+      </c>
+      <c r="R211">
+        <v>5</v>
+      </c>
+      <c r="S211">
+        <v>5</v>
+      </c>
+      <c r="T211" t="s">
+        <v>1808</v>
+      </c>
+      <c r="U211" t="s">
+        <v>1809</v>
+      </c>
+      <c r="V211">
+        <v>0</v>
+      </c>
+      <c r="W211">
+        <v>0</v>
+      </c>
+      <c r="X211">
+        <v>0</v>
+      </c>
+      <c r="Y211">
+        <v>1</v>
+      </c>
+      <c r="Z211">
+        <v>0</v>
+      </c>
+      <c r="AA211">
+        <v>0</v>
+      </c>
+      <c r="AB211" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AC211">
+        <v>1</v>
+      </c>
+      <c r="AD211">
+        <v>0</v>
+      </c>
+      <c r="AE211">
+        <v>0</v>
+      </c>
+      <c r="AF211">
+        <v>0</v>
+      </c>
+      <c r="AG211">
+        <v>0</v>
+      </c>
+      <c r="AH211">
+        <v>430</v>
+      </c>
+      <c r="AI211">
+        <v>186</v>
+      </c>
+      <c r="AJ211">
+        <v>129</v>
+      </c>
+      <c r="AK211">
+        <v>5</v>
+      </c>
+      <c r="AL211">
+        <v>2</v>
+      </c>
+      <c r="AM211">
+        <v>0</v>
+      </c>
+      <c r="AN211">
+        <v>0</v>
+      </c>
+      <c r="AO211" t="s">
+        <v>1697</v>
+      </c>
+      <c r="AP211">
+        <v>0</v>
+      </c>
+      <c r="AQ211" t="s">
+        <v>337</v>
+      </c>
+      <c r="AR211" t="s">
+        <v>338</v>
+      </c>
+      <c r="AS211" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT211" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU211" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV211" t="s">
+        <v>231</v>
+      </c>
+      <c r="AW211" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS211" t="s">
+        <v>1811</v>
+      </c>
+      <c r="BT211" t="s">
+        <v>1812</v>
+      </c>
+      <c r="BU211" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW211" t="s">
+        <v>354</v>
+      </c>
+      <c r="BX211" t="s">
+        <v>1813</v>
+      </c>
+      <c r="EY211" s="1"/>
+      <c r="GQ211" s="1"/>
+      <c r="GR211" s="1"/>
+      <c r="GY211" s="1"/>
+      <c r="GZ211" s="1"/>
+      <c r="HA211" s="1"/>
+      <c r="HB211" s="1"/>
+      <c r="IQ211" s="1">
+        <v>884066747</v>
+      </c>
+      <c r="IR211" t="s">
+        <v>1814</v>
+      </c>
+      <c r="IS211" s="1">
+        <v>46297.198738425926</v>
+      </c>
+      <c r="IU211" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW211" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX211" t="s">
+        <v>1815</v>
+      </c>
+      <c r="IY211">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2CDC854-83CA-4E4B-8813-206183A71E2C}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06CD88B6-0E2B-F54F-8399-8959E82628C4}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="900" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5095" uniqueCount="1816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6052" uniqueCount="2089">
   <si>
     <t>start</t>
   </si>
@@ -5485,6 +5485,825 @@
   </si>
   <si>
     <t>uuid:6dcc52e1-0b13-4cf0-9e4d-a6d77fb4c2cd</t>
+  </si>
+  <si>
+    <t>Lc chairperson</t>
+  </si>
+  <si>
+    <t>To support  the public health emergency  preparedness  in the community</t>
+  </si>
+  <si>
+    <t>Why are we still talking about ebola yet we don't have any threat of disease, is ebola still there,  can you get support from the government  healthfacility or we can go to any facility  and we get all the required help</t>
+  </si>
+  <si>
+    <t>Bodaboda  riders and mechanics</t>
+  </si>
+  <si>
+    <t>Engage their leaders to increase risk perception</t>
+  </si>
+  <si>
+    <t>92be9d77-2537-405d-8e84-a5f0210a5d27</t>
+  </si>
+  <si>
+    <t>uuid:92be9d77-2537-405d-8e84-a5f0210a5d27</t>
+  </si>
+  <si>
+    <t>Market / Trading Center</t>
+  </si>
+  <si>
+    <t>Market / Vendor Head</t>
+  </si>
+  <si>
+    <t>Market chairperson</t>
+  </si>
+  <si>
+    <t>Encouraging people to wash hands</t>
+  </si>
+  <si>
+    <t>Ebola can't be got by people who are healthy</t>
+  </si>
+  <si>
+    <t>Boda boda rider</t>
+  </si>
+  <si>
+    <t>987ce1b8-4c51-44d8-b4ce-b2cfeda4deff</t>
+  </si>
+  <si>
+    <t>uuid:987ce1b8-4c51-44d8-b4ce-b2cfeda4deff</t>
+  </si>
+  <si>
+    <t>Mengo</t>
+  </si>
+  <si>
+    <t>The last Ebola was not real but staged by government</t>
+  </si>
+  <si>
+    <t>Something he has heard in conversations</t>
+  </si>
+  <si>
+    <t>Have asked him not to assume on rumors but seek information from established sources</t>
+  </si>
+  <si>
+    <t>60753643-caa5-4687-afa1-63d6f7dc07ce</t>
+  </si>
+  <si>
+    <t>uuid:60753643-caa5-4687-afa1-63d6f7dc07ce</t>
+  </si>
+  <si>
+    <t>The last outbreak was a lie government told us</t>
+  </si>
+  <si>
+    <t>Mistrust in government</t>
+  </si>
+  <si>
+    <t>Verification of information source</t>
+  </si>
+  <si>
+    <t>Not yet roday</t>
+  </si>
+  <si>
+    <t>About 100 meters from here outside a restaurant</t>
+  </si>
+  <si>
+    <t>c84d709a-bdb2-45d2-ad2f-148d2cf301ae</t>
+  </si>
+  <si>
+    <t>uuid:c84d709a-bdb2-45d2-ad2f-148d2cf301ae</t>
+  </si>
+  <si>
+    <t>Have the disease  come back ,ebola affects only congolesw</t>
+  </si>
+  <si>
+    <t>Bodaboda</t>
+  </si>
+  <si>
+    <t>I can easily spot the signs of Ebola and Mpox If someone gets sick with outbreak signs, I will call the toll-free line or report immediately We do not discriminate against anyone who recovers from an infectious disease or their family I have shared the emergency preparedness messages with my household and colleagues</t>
+  </si>
+  <si>
+    <t>Someone vomiting, red eyes, vomiting  with diarrhea,</t>
+  </si>
+  <si>
+    <t>Send an alert to 6767, send to a health facility</t>
+  </si>
+  <si>
+    <t>They delay to respond</t>
+  </si>
+  <si>
+    <t>Ask them about how they were cared for, what were you given to make sure you are safe</t>
+  </si>
+  <si>
+    <t>Yed</t>
+  </si>
+  <si>
+    <t>Protect themselves by knowing the signs and symptoms  incase someone has signs and symptoms  and alert the VHY and LC chairpersons</t>
+  </si>
+  <si>
+    <t>If someone  goes to isolation, what happens to the family,? Government  has medicine  and treatment  is free and everything  is catered for and community will support the family but you will remain, you will  spread to the family</t>
+  </si>
+  <si>
+    <t>e38b9729-126b-4f31-9d07-b3391acb8cd5</t>
+  </si>
+  <si>
+    <t>uuid:e38b9729-126b-4f31-9d07-b3391acb8cd5</t>
+  </si>
+  <si>
+    <t>That government staged the last Ebola suspects ,how come none where known locals?</t>
+  </si>
+  <si>
+    <t>Work space</t>
+  </si>
+  <si>
+    <t>Did a small session on Ebola with her and her colleagues</t>
+  </si>
+  <si>
+    <t>What if the person is not actually sick with that particular disease?</t>
+  </si>
+  <si>
+    <t>High Reluctance</t>
+  </si>
+  <si>
+    <t>70756fd3-86e5-46d0-bba1-ab745b3addab</t>
+  </si>
+  <si>
+    <t>uuid:70756fd3-86e5-46d0-bba1-ab745b3addab</t>
+  </si>
+  <si>
+    <t>Nsambya</t>
+  </si>
+  <si>
+    <t>They are people who say that  ebola has never existed because they have never seen any one sick</t>
+  </si>
+  <si>
+    <t>Educating them that the disease  is there and  they should  protect themselves</t>
+  </si>
+  <si>
+    <t>Red eyes,vomiting of blood,  high body temperature,  body weakness</t>
+  </si>
+  <si>
+    <t>Call the toll free  number</t>
+  </si>
+  <si>
+    <t>Fear of isolation</t>
+  </si>
+  <si>
+    <t>Calling tools free number, informing the VHT and chairman</t>
+  </si>
+  <si>
+    <t>Have you ever reached where they take the ebola and mpox patients for treatment,  what happens there:i have never reached there but  I think people are cared for</t>
+  </si>
+  <si>
+    <t>1fc12766-e57f-48ce-a711-8b1a797ebec5</t>
+  </si>
+  <si>
+    <t>uuid:1fc12766-e57f-48ce-a711-8b1a797ebec5</t>
+  </si>
+  <si>
+    <t>Is ebola curable</t>
+  </si>
+  <si>
+    <t>People  don't wash hands  because there are washing points</t>
+  </si>
+  <si>
+    <t>Bodaboda  rider</t>
+  </si>
+  <si>
+    <t>Improve hygienic conditions</t>
+  </si>
+  <si>
+    <t>7fcf63aa-ff4e-49d2-ba8f-590576f7035d</t>
+  </si>
+  <si>
+    <t>uuid:7fcf63aa-ff4e-49d2-ba8f-590576f7035d</t>
+  </si>
+  <si>
+    <t>Did ebola reach kampala  or uganda,  i did see any sick of ebola</t>
+  </si>
+  <si>
+    <t>Disbelief  that ebola exists</t>
+  </si>
+  <si>
+    <t>Personally</t>
+  </si>
+  <si>
+    <t>Increase  risk perception</t>
+  </si>
+  <si>
+    <t>The skin rashes   for mpox</t>
+  </si>
+  <si>
+    <t>Advise them to go to hospital, we don't have health worker contacts</t>
+  </si>
+  <si>
+    <t>We interact as usual</t>
+  </si>
+  <si>
+    <t>35a51299-dac1-49df-ab13-aa75cf89e657</t>
+  </si>
+  <si>
+    <t>uuid:35a51299-dac1-49df-ab13-aa75cf89e657</t>
+  </si>
+  <si>
+    <t>NSAMBYA CENTRAL</t>
+  </si>
+  <si>
+    <t>COGRA</t>
+  </si>
+  <si>
+    <t>Ebola is brought by people from Congo</t>
+  </si>
+  <si>
+    <t>Communities is mixed</t>
+  </si>
+  <si>
+    <t>Improve on the hygiene</t>
+  </si>
+  <si>
+    <t>Fever ,vomiting with blood</t>
+  </si>
+  <si>
+    <t>4d25c4aa-dd3a-4510-b3bb-342e87112036</t>
+  </si>
+  <si>
+    <t>uuid:4d25c4aa-dd3a-4510-b3bb-342e87112036</t>
+  </si>
+  <si>
+    <t>People doubt ,I believe  that ebola  is not there, because  I have never seen anybody sick of ebola because we belive government  wants to pass  its own agendas</t>
+  </si>
+  <si>
+    <t>Bodaboda  stages</t>
+  </si>
+  <si>
+    <t>We do not discriminate against anyone who recovers from an infectious disease or their family</t>
+  </si>
+  <si>
+    <t>There is no isolation at all</t>
+  </si>
+  <si>
+    <t>5e8746c7-816e-44d5-ad9e-9a386009db44</t>
+  </si>
+  <si>
+    <t>uuid:5e8746c7-816e-44d5-ad9e-9a386009db44</t>
+  </si>
+  <si>
+    <t>Nsamby Central</t>
+  </si>
+  <si>
+    <t>Ebola is not there</t>
+  </si>
+  <si>
+    <t>Different groups of people</t>
+  </si>
+  <si>
+    <t>People  should have the opportunity to see the sick one</t>
+  </si>
+  <si>
+    <t>fa7cec20-d28a-4ecf-8596-1e659d5c964b</t>
+  </si>
+  <si>
+    <t>uuid:fa7cec20-d28a-4ecf-8596-1e659d5c964b</t>
+  </si>
+  <si>
+    <t>Is ebola  still there or it got done</t>
+  </si>
+  <si>
+    <t>Congested area</t>
+  </si>
+  <si>
+    <t>Call the healthworker from  the clinic  nearby to come to check on the person</t>
+  </si>
+  <si>
+    <t>27e5e1a8-b745-429b-99be-6f2b48e1480a</t>
+  </si>
+  <si>
+    <t>uuid:27e5e1a8-b745-429b-99be-6f2b48e1480a</t>
+  </si>
+  <si>
+    <t>Nsamby central</t>
+  </si>
+  <si>
+    <t>Mpox is real</t>
+  </si>
+  <si>
+    <t>Lack of information</t>
+  </si>
+  <si>
+    <t>Washing hands</t>
+  </si>
+  <si>
+    <t>Rash on the body and High temperature</t>
+  </si>
+  <si>
+    <t>21a71359-cbb6-41b6-adf0-155019414a2b</t>
+  </si>
+  <si>
+    <t>uuid:21a71359-cbb6-41b6-adf0-155019414a2b</t>
+  </si>
+  <si>
+    <t>Congra</t>
+  </si>
+  <si>
+    <t>We donot have Ebola now</t>
+  </si>
+  <si>
+    <t>No ebola</t>
+  </si>
+  <si>
+    <t>Skin rsh</t>
+  </si>
+  <si>
+    <t>259e8e74-cda6-48d1-8974-55b78014f7a0</t>
+  </si>
+  <si>
+    <t>uuid:259e8e74-cda6-48d1-8974-55b78014f7a0</t>
+  </si>
+  <si>
+    <t>Nsambya Central</t>
+  </si>
+  <si>
+    <t>Government brings up diseases to get money</t>
+  </si>
+  <si>
+    <t>Have never had of people  dying of Ebola in the community</t>
+  </si>
+  <si>
+    <t>Empower vhts</t>
+  </si>
+  <si>
+    <t>b6d8ec60-482e-4cf8-9261-bc42ce8901b9</t>
+  </si>
+  <si>
+    <t>uuid:b6d8ec60-482e-4cf8-9261-bc42ce8901b9</t>
+  </si>
+  <si>
+    <t>Nsambya Centrl</t>
+  </si>
+  <si>
+    <t>We do not have any  threatening diseases</t>
+  </si>
+  <si>
+    <t>Dening of any diseases may lead to risk of children and families of getting diseases</t>
+  </si>
+  <si>
+    <t>Reinforce  health message so that people understand the riskss</t>
+  </si>
+  <si>
+    <t>Vomiting , high fever</t>
+  </si>
+  <si>
+    <t>b9a6e26c-b3d7-49be-8830-89a8c46f5fd4</t>
+  </si>
+  <si>
+    <t>uuid:b9a6e26c-b3d7-49be-8830-89a8c46f5fd4</t>
+  </si>
+  <si>
+    <t>We haven't received any case last month</t>
+  </si>
+  <si>
+    <t>Many people believe there have been no cases, so they see no need for protective behaviours or early reporting.</t>
+  </si>
+  <si>
+    <t>Strengthen community feedback messaging that confirms cases are occurring or have occurred and reinforce early symptom recognition &amp;  care-seeking</t>
+  </si>
+  <si>
+    <t>a8e90e9e-ca67-467b-8341-babd99a25bf0</t>
+  </si>
+  <si>
+    <t>uuid:a8e90e9e-ca67-467b-8341-babd99a25bf0</t>
+  </si>
+  <si>
+    <t>We haven’t received any case last month people are saying there is no disease ,no cases in the community.</t>
+  </si>
+  <si>
+    <t>Low risk perception and denial , community members believe there are no cases, so they see little reason to follow prevention messages or report early symptoms.</t>
+  </si>
+  <si>
+    <t>Reinforce early symptom recognition and the importance of reporting even when people think the situation is calm.</t>
+  </si>
+  <si>
+    <t>3258fdc2-9c86-4da0-9da9-45d60a486bee</t>
+  </si>
+  <si>
+    <t>uuid:3258fdc2-9c86-4da0-9da9-45d60a486bee</t>
+  </si>
+  <si>
+    <t>Do we have any out break</t>
+  </si>
+  <si>
+    <t>Uncertainty community members are unsure whether an outbreak is happening, which reduces urgency to follow prevention advice .</t>
+  </si>
+  <si>
+    <t>Provide clear, simple updates confirming the current outbreak status .</t>
+  </si>
+  <si>
+    <t>Vomiting blood,body weakness</t>
+  </si>
+  <si>
+    <t>7d36af2e-ee5c-41e6-ba7c-b4b795eea47d</t>
+  </si>
+  <si>
+    <t>uuid:7d36af2e-ee5c-41e6-ba7c-b4b795eea47d</t>
+  </si>
+  <si>
+    <t>People are saying Uganda is free from any threat of diseases</t>
+  </si>
+  <si>
+    <t>Communities believe no ebola diseases in the country and can stop washing hands often</t>
+  </si>
+  <si>
+    <t>Always  motivate vhts to keep us sensitive people about the diseases</t>
+  </si>
+  <si>
+    <t>Committing , fever</t>
+  </si>
+  <si>
+    <t>015cece1-ab50-4f8c-a935-28405d8ccc8d</t>
+  </si>
+  <si>
+    <t>uuid:015cece1-ab50-4f8c-a935-28405d8ccc8d</t>
+  </si>
+  <si>
+    <t>Gayaza Road secondary school</t>
+  </si>
+  <si>
+    <t>Ebola affects Congolese alone. Uganda is Ebola free</t>
+  </si>
+  <si>
+    <t>Politicking of the outbreaks</t>
+  </si>
+  <si>
+    <t>Institutions of learning should be engaged more</t>
+  </si>
+  <si>
+    <t>cec65995-37be-4727-a20f-4a92fcede934</t>
+  </si>
+  <si>
+    <t>uuid:cec65995-37be-4727-a20f-4a92fcede934</t>
+  </si>
+  <si>
+    <t>Do home rats cause Ebola?</t>
+  </si>
+  <si>
+    <t>Low risk perception  which at times is triggeref by limted information</t>
+  </si>
+  <si>
+    <t>More sensitization on radio and television shoukd be done</t>
+  </si>
+  <si>
+    <t>0ca241f0-d08c-44e1-a771-0983d94e797e</t>
+  </si>
+  <si>
+    <t>uuid:0ca241f0-d08c-44e1-a771-0983d94e797e</t>
+  </si>
+  <si>
+    <t>Taxi / Bus Park</t>
+  </si>
+  <si>
+    <t>Taxi park committe Supervisor</t>
+  </si>
+  <si>
+    <t>Suprvise continued use of handwsshing facilities at different stages</t>
+  </si>
+  <si>
+    <t>Low / Stigmatizing</t>
+  </si>
+  <si>
+    <t>Ebola can spread through air like covid 19</t>
+  </si>
+  <si>
+    <t>Myths and misconceptions in the community lead to low response</t>
+  </si>
+  <si>
+    <t>More engagements at village level through one on one sessions should be done more</t>
+  </si>
+  <si>
+    <t>28e600f8-847b-476b-a8a3-44de769bb740</t>
+  </si>
+  <si>
+    <t>uuid:28e600f8-847b-476b-a8a3-44de769bb740</t>
+  </si>
+  <si>
+    <t>Leader of market vendors</t>
+  </si>
+  <si>
+    <t>Lobby for hand washing facility for the market</t>
+  </si>
+  <si>
+    <t>There is no more Ebola in the country</t>
+  </si>
+  <si>
+    <t>Socia media platforms that mislead with fake information</t>
+  </si>
+  <si>
+    <t>More sensitizaton using mobilisation van should be carried out</t>
+  </si>
+  <si>
+    <t>a9f21b63-3f75-47f3-8d39-39572aefc789</t>
+  </si>
+  <si>
+    <t>uuid:a9f21b63-3f75-47f3-8d39-39572aefc789</t>
+  </si>
+  <si>
+    <t>Boda stage leader</t>
+  </si>
+  <si>
+    <t>Continued awareness creation to fellow riders and customers</t>
+  </si>
+  <si>
+    <t>Government was after making money there was no Ebola</t>
+  </si>
+  <si>
+    <t>Politiking of the outbreak</t>
+  </si>
+  <si>
+    <t>Passengers/customers</t>
+  </si>
+  <si>
+    <t>More comnunity engagements should be carried out</t>
+  </si>
+  <si>
+    <t>e1ab6348-2aa8-49d2-8d14-3f7dd8eda016</t>
+  </si>
+  <si>
+    <t>uuid:e1ab6348-2aa8-49d2-8d14-3f7dd8eda016</t>
+  </si>
+  <si>
+    <t>Boda boda riders and their leader</t>
+  </si>
+  <si>
+    <t>Sharing of right information from right sources</t>
+  </si>
+  <si>
+    <t>Is there an Ebola vaccine ?</t>
+  </si>
+  <si>
+    <t>Congestion of some areas that easens spread</t>
+  </si>
+  <si>
+    <t>Empower local leaders by government so as to equip people with information</t>
+  </si>
+  <si>
+    <t>7066e223-13fe-466e-a67d-6ccd20ea6b13</t>
+  </si>
+  <si>
+    <t>uuid:7066e223-13fe-466e-a67d-6ccd20ea6b13</t>
+  </si>
+  <si>
+    <t>Boda boda</t>
+  </si>
+  <si>
+    <t>He said they were going to put hand washing equipment at the stage,</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>Ebola outbreak is political</t>
+  </si>
+  <si>
+    <t>The youth have convinced the bodaboda community that Ebola is not real</t>
+  </si>
+  <si>
+    <t>The youth</t>
+  </si>
+  <si>
+    <t>e1fcd3bd-7974-4a89-9a85-13324372f609</t>
+  </si>
+  <si>
+    <t>uuid:e1fcd3bd-7974-4a89-9a85-13324372f609</t>
+  </si>
+  <si>
+    <t>Where did ebola come from, I really  want to know where ebola came from</t>
+  </si>
+  <si>
+    <t>10 minutes back</t>
+  </si>
+  <si>
+    <t>Near the vegetables</t>
+  </si>
+  <si>
+    <t>High body temperature,  headache  that does not heal and red eyes</t>
+  </si>
+  <si>
+    <t>I would call the health worker  in the nearby  clinic so that they verify if its ebola or not</t>
+  </si>
+  <si>
+    <t>84f72ae7-72af-4be5-a1de-fa58a835e50f</t>
+  </si>
+  <si>
+    <t>uuid:84f72ae7-72af-4be5-a1de-fa58a835e50f</t>
+  </si>
+  <si>
+    <t>Bar / Malwa Joint / Hospitality</t>
+  </si>
+  <si>
+    <t>Bar attendant manager</t>
+  </si>
+  <si>
+    <t>We found the bar (vibes suits) having no hand-washing facilities. The bar attendant committed to solicit for a handwashing facility and put one at the entrance. She also requested for some posters to put in the bar as a way to remind people that we have to keep caution.</t>
+  </si>
+  <si>
+    <t>Ebola moves through air. Is the hotline number free of charge or i need airtime to communicate.</t>
+  </si>
+  <si>
+    <t>No hand-washing facilities. They don't have knowledge about ebola and they believe that they are very safe so they dont take precaution.</t>
+  </si>
+  <si>
+    <t>Intesify targeted RCCE on social media and in the community and conduction of community senstization especially through the community leaders</t>
+  </si>
+  <si>
+    <t>f2f18fa1-36d7-4093-b530-5e93d09a66ed</t>
+  </si>
+  <si>
+    <t>uuid:f2f18fa1-36d7-4093-b530-5e93d09a66ed</t>
+  </si>
+  <si>
+    <t>Misindye COU Primary and Nursery school</t>
+  </si>
+  <si>
+    <t>Completely dry/absent</t>
+  </si>
+  <si>
+    <t>The HM mentioned and said that we just have to learn how to live with Ebola because it is part of us now. Comes and goes. Unlike other outbreaks that have been coming and going, Ebola is diffent that it has frequently suffaced.</t>
+  </si>
+  <si>
+    <t>As a school, they have a challenge of water. The community from out keeps intruding and end up staeling and destroying school property. They also have a challenge of soap that is always wasted and taken by the pupils whenever it is availed.</t>
+  </si>
+  <si>
+    <t>School senstization on ebola facts and hand hygiene, using of peer leaders and forming a u-report club to counter rumors in the school.</t>
+  </si>
+  <si>
+    <t>b5144cea-687d-4cc7-a486-bbf8c6ab6095</t>
+  </si>
+  <si>
+    <t>uuid:b5144cea-687d-4cc7-a486-bbf8c6ab6095</t>
+  </si>
+  <si>
+    <t>Misindye</t>
+  </si>
+  <si>
+    <t>No specific one.</t>
+  </si>
+  <si>
+    <t>Using the student leaders in school to address ehat these public health emergencies are.</t>
+  </si>
+  <si>
+    <t>There is a distance of 10 m from the toilet ro the kitchen</t>
+  </si>
+  <si>
+    <t>The school is spacious enough, this creates more space for isolation reducing on the risk of body to body contact. However, when it comes to the basics of hand washing, they have challenges with water. The school also has limited toilets compared to the number of children available</t>
+  </si>
+  <si>
+    <t>They have a total of 8 toilets.  This makes the student to stance ratio unproportionally big</t>
+  </si>
+  <si>
+    <t>Yes the teacher in charge of health has ever received orientation on epidemics</t>
+  </si>
+  <si>
+    <t>3d6b8e7f-922b-45e2-a0ab-6fefc8a96456</t>
+  </si>
+  <si>
+    <t>uuid:3d6b8e7f-922b-45e2-a0ab-6fefc8a96456</t>
+  </si>
+  <si>
+    <t>Seeta COU Primary and Nursery School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Science teacher </t>
+  </si>
+  <si>
+    <t>Yes / Easily</t>
+  </si>
+  <si>
+    <t>Its only the people that eat monkeys that get infected with ebola. Other people are safe because ebola comes from eating monkeys, dogs, cats and bats</t>
+  </si>
+  <si>
+    <t>High level of ignorance in the school</t>
+  </si>
+  <si>
+    <t>Emphasized school senstization especially on the ways how ebola spreads.</t>
+  </si>
+  <si>
+    <t>af83c7ce-4699-4e7a-9622-c0898e81f6d2</t>
+  </si>
+  <si>
+    <t>uuid:af83c7ce-4699-4e7a-9622-c0898e81f6d2</t>
+  </si>
+  <si>
+    <t>Gulu ward</t>
+  </si>
+  <si>
+    <t>Parish heads / leaders</t>
+  </si>
+  <si>
+    <t>The parish leaders were having a meeting at a community place so they didnt have any protocol. strengthening community based surveillance, enhancing early reporting, and clarifying roles of community leaders in risk communication.</t>
+  </si>
+  <si>
+    <t>If someone has even just two signs of those from ebola like severe headache and restlessness, loss of appetite, should i conclude that the person could be a suspect.</t>
+  </si>
+  <si>
+    <t>Nothing really. They were willing to lear</t>
+  </si>
+  <si>
+    <t>Social media and the communities where we serve</t>
+  </si>
+  <si>
+    <t>Engage parish leaders to cascade correct Ebola prevention messages to their congregations, support installation of handwashing facilities with soap at churches/mosques, and use religious gatherings for community sensitization and rumor tracking.</t>
+  </si>
+  <si>
+    <t>b11a7596-5b40-41b2-8d3b-d09a5e9bc82f</t>
+  </si>
+  <si>
+    <t>uuid:b11a7596-5b40-41b2-8d3b-d09a5e9bc82f</t>
+  </si>
+  <si>
+    <t>Nabuti</t>
+  </si>
+  <si>
+    <t>None shared</t>
+  </si>
+  <si>
+    <t>I was given lim ited time bacause they were having a meetin g in the next 1 hour and they had to prepare.</t>
+  </si>
+  <si>
+    <t>No rumor</t>
+  </si>
+  <si>
+    <t>Will share later in the next visit</t>
+  </si>
+  <si>
+    <t>No breeding sites</t>
+  </si>
+  <si>
+    <t>The school is located on a hilly place with a lot of trees. They are organised generally the only challenge comes from the absence of</t>
+  </si>
+  <si>
+    <t>40&gt;5</t>
+  </si>
+  <si>
+    <t>the school has no school nurse.</t>
+  </si>
+  <si>
+    <t>e93a6459-565b-47cc-a1f3-3ec0511b551a</t>
+  </si>
+  <si>
+    <t>uuid:e93a6459-565b-47cc-a1f3-3ec0511b551a</t>
+  </si>
+  <si>
+    <t>No in-depth discussion. The discussion was somehow quick but i was requested to go back</t>
+  </si>
+  <si>
+    <t>will share soon</t>
+  </si>
+  <si>
+    <t>c9fb9dd4-3b9b-471f-9c6c-ff3fdb21dae0</t>
+  </si>
+  <si>
+    <t>uuid:c9fb9dd4-3b9b-471f-9c6c-ff3fdb21dae0</t>
+  </si>
+  <si>
+    <t>Nabuuti</t>
+  </si>
+  <si>
+    <t>Yet to identify one</t>
+  </si>
+  <si>
+    <t>Ebola is not real and that handwashing cannot prevent it. 2 Pupils believe Ebola only affects adults, children cannot get it.   3Question from students: If there are no handwashing facilities, how can we prevent Ebola at school? Requested to get them some hand washing facilities</t>
+  </si>
+  <si>
+    <t>Absence of handwashing facilities leading to low hand hygiene practice.    2No dedicated budget for soap and water for handwashing.  3Teachers not trained to deliver Ebola prevention messages</t>
+  </si>
+  <si>
+    <t>Conduct school-based RCCE orientation on Ebola facts and demonstrate proper handwashing with soap.    2Distribute and paste IEC materials on Ebola prevention (having the hotline)in classrooms and latrines.       3Train health clubs / prefects as peer influencers to promote hand hygiene and rumor reporting.</t>
+  </si>
+  <si>
+    <t>3da34766-85ff-4920-9cfa-06ce3d54d541</t>
+  </si>
+  <si>
+    <t>uuid:3da34766-85ff-4920-9cfa-06ce3d54d541</t>
+  </si>
+  <si>
+    <t>It’s is witchcraft</t>
+  </si>
+  <si>
+    <t>Vomiting and diarrhea. Seek medical attention</t>
+  </si>
+  <si>
+    <t>4b5c95af-32ad-40d2-a6ac-b8139380216b</t>
+  </si>
+  <si>
+    <t>uuid:4b5c95af-32ad-40d2-a6ac-b8139380216b</t>
+  </si>
+  <si>
+    <t>The government is trying to steal money</t>
+  </si>
+  <si>
+    <t>Sore throat and bleeding from body openings. Always wash hands</t>
+  </si>
+  <si>
+    <t>3bb96029-cd2d-4916-badc-1c6a84e22ecd</t>
+  </si>
+  <si>
+    <t>uuid:3bb96029-cd2d-4916-badc-1c6a84e22ecd</t>
   </si>
 </sst>
 </file>
@@ -19539,7 +20358,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -19889,8 +20708,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY211" totalsRowShown="0">
-  <autoFilter ref="A1:IY211" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY250" totalsRowShown="0">
+  <autoFilter ref="A1:IY250" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -20443,7 +21262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY211"/>
+  <dimension ref="A1:IY250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -44662,6 +45481,4683 @@
         <v>212</v>
       </c>
     </row>
+    <row r="212" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A212" s="1">
+        <v>46296.695491331018</v>
+      </c>
+      <c r="B212" s="1">
+        <v>46297.523458993062</v>
+      </c>
+      <c r="C212" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D212" t="s">
+        <v>683</v>
+      </c>
+      <c r="E212" t="s">
+        <v>234</v>
+      </c>
+      <c r="F212" t="s">
+        <v>245</v>
+      </c>
+      <c r="G212" t="s">
+        <v>198</v>
+      </c>
+      <c r="H212" t="s">
+        <v>237</v>
+      </c>
+      <c r="AX212" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AY212" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ212" t="s">
+        <v>1710</v>
+      </c>
+      <c r="BA212" t="s">
+        <v>1816</v>
+      </c>
+      <c r="BB212">
+        <v>1</v>
+      </c>
+      <c r="BC212">
+        <v>0</v>
+      </c>
+      <c r="BD212" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE212" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF212" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG212" t="s">
+        <v>1817</v>
+      </c>
+      <c r="BH212" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI212" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ212" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK212">
+        <v>5</v>
+      </c>
+      <c r="BL212" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM212">
+        <v>45</v>
+      </c>
+      <c r="BN212">
+        <v>50</v>
+      </c>
+      <c r="BO212" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BP212" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ212" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS212" t="s">
+        <v>1818</v>
+      </c>
+      <c r="BT212" t="s">
+        <v>720</v>
+      </c>
+      <c r="BU212" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV212" t="s">
+        <v>1819</v>
+      </c>
+      <c r="BW212" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX212" t="s">
+        <v>1820</v>
+      </c>
+      <c r="EY212" s="1"/>
+      <c r="GQ212" s="1"/>
+      <c r="GR212" s="1"/>
+      <c r="GY212" s="1"/>
+      <c r="GZ212" s="1"/>
+      <c r="HA212" s="1"/>
+      <c r="HB212" s="1"/>
+      <c r="IQ212" s="1">
+        <v>884222422</v>
+      </c>
+      <c r="IR212" t="s">
+        <v>1821</v>
+      </c>
+      <c r="IS212" s="1">
+        <v>46297.3984837963</v>
+      </c>
+      <c r="IU212" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW212" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX212" t="s">
+        <v>1822</v>
+      </c>
+      <c r="IY212">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="213" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A213" s="1">
+        <v>46296.838384155089</v>
+      </c>
+      <c r="B213" s="1">
+        <v>46297.57576313657</v>
+      </c>
+      <c r="C213" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D213" t="s">
+        <v>683</v>
+      </c>
+      <c r="E213" t="s">
+        <v>210</v>
+      </c>
+      <c r="F213" t="s">
+        <v>963</v>
+      </c>
+      <c r="G213" t="s">
+        <v>198</v>
+      </c>
+      <c r="H213" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX213" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AY213" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ213" t="s">
+        <v>1824</v>
+      </c>
+      <c r="BA213" t="s">
+        <v>1825</v>
+      </c>
+      <c r="BB213">
+        <v>12</v>
+      </c>
+      <c r="BC213">
+        <v>6</v>
+      </c>
+      <c r="BD213" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE213" t="s">
+        <v>392</v>
+      </c>
+      <c r="BF213" t="s">
+        <v>1620</v>
+      </c>
+      <c r="BG213" t="s">
+        <v>1826</v>
+      </c>
+      <c r="BH213" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI213" t="s">
+        <v>323</v>
+      </c>
+      <c r="BJ213" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK213">
+        <v>4</v>
+      </c>
+      <c r="BL213" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM213">
+        <v>200</v>
+      </c>
+      <c r="BN213">
+        <v>165</v>
+      </c>
+      <c r="BO213" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BP213" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BQ213" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS213" t="s">
+        <v>1827</v>
+      </c>
+      <c r="BT213" t="s">
+        <v>947</v>
+      </c>
+      <c r="BU213" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV213" t="s">
+        <v>1828</v>
+      </c>
+      <c r="BW213" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX213" t="s">
+        <v>1401</v>
+      </c>
+      <c r="EY213" s="1"/>
+      <c r="GQ213" s="1"/>
+      <c r="GR213" s="1"/>
+      <c r="GY213" s="1"/>
+      <c r="GZ213" s="1"/>
+      <c r="HA213" s="1"/>
+      <c r="HB213" s="1"/>
+      <c r="IQ213" s="1">
+        <v>884275941</v>
+      </c>
+      <c r="IR213" t="s">
+        <v>1829</v>
+      </c>
+      <c r="IS213" s="1">
+        <v>46297.450833333343</v>
+      </c>
+      <c r="IU213" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW213" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX213" t="s">
+        <v>1830</v>
+      </c>
+      <c r="IY213">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="214" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A214" s="1">
+        <v>46297.595784861107</v>
+      </c>
+      <c r="B214" s="1">
+        <v>46297.59977896991</v>
+      </c>
+      <c r="C214" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D214" t="s">
+        <v>879</v>
+      </c>
+      <c r="E214" t="s">
+        <v>277</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1831</v>
+      </c>
+      <c r="G214" t="s">
+        <v>198</v>
+      </c>
+      <c r="H214" t="s">
+        <v>279</v>
+      </c>
+      <c r="BS214" t="s">
+        <v>1832</v>
+      </c>
+      <c r="BT214" t="s">
+        <v>605</v>
+      </c>
+      <c r="BU214" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV214" t="s">
+        <v>1833</v>
+      </c>
+      <c r="BW214" t="s">
+        <v>354</v>
+      </c>
+      <c r="BX214" t="s">
+        <v>1834</v>
+      </c>
+      <c r="BY214" t="s">
+        <v>923</v>
+      </c>
+      <c r="CP214" t="s">
+        <v>883</v>
+      </c>
+      <c r="CT214" t="s">
+        <v>897</v>
+      </c>
+      <c r="CU214">
+        <v>0</v>
+      </c>
+      <c r="CV214">
+        <v>0</v>
+      </c>
+      <c r="CW214">
+        <v>1</v>
+      </c>
+      <c r="CX214">
+        <v>0</v>
+      </c>
+      <c r="CY214">
+        <v>0</v>
+      </c>
+      <c r="CZ214">
+        <v>0</v>
+      </c>
+      <c r="DA214">
+        <v>0</v>
+      </c>
+      <c r="DC214" t="s">
+        <v>898</v>
+      </c>
+      <c r="EY214" s="1"/>
+      <c r="GQ214" s="1"/>
+      <c r="GR214" s="1"/>
+      <c r="GY214" s="1"/>
+      <c r="GZ214" s="1"/>
+      <c r="HA214" s="1"/>
+      <c r="HB214" s="1"/>
+      <c r="IQ214" s="1">
+        <v>884293982</v>
+      </c>
+      <c r="IR214" t="s">
+        <v>1835</v>
+      </c>
+      <c r="IS214" s="1">
+        <v>46297.466597222221</v>
+      </c>
+      <c r="IU214" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW214" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX214" t="s">
+        <v>1836</v>
+      </c>
+      <c r="IY214">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="215" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A215" s="1">
+        <v>46297.603049039353</v>
+      </c>
+      <c r="B215" s="1">
+        <v>46297.609141956018</v>
+      </c>
+      <c r="C215" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D215" t="s">
+        <v>945</v>
+      </c>
+      <c r="E215" t="s">
+        <v>277</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1831</v>
+      </c>
+      <c r="G215" t="s">
+        <v>198</v>
+      </c>
+      <c r="H215" t="s">
+        <v>279</v>
+      </c>
+      <c r="BS215" t="s">
+        <v>1837</v>
+      </c>
+      <c r="BT215" t="s">
+        <v>1838</v>
+      </c>
+      <c r="BU215" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW215" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX215" t="s">
+        <v>1839</v>
+      </c>
+      <c r="BY215" t="s">
+        <v>923</v>
+      </c>
+      <c r="DE215" t="s">
+        <v>1062</v>
+      </c>
+      <c r="DF215" t="s">
+        <v>1083</v>
+      </c>
+      <c r="DG215">
+        <v>1</v>
+      </c>
+      <c r="DH215">
+        <v>0</v>
+      </c>
+      <c r="DI215">
+        <v>0</v>
+      </c>
+      <c r="DJ215">
+        <v>0</v>
+      </c>
+      <c r="DK215">
+        <v>0</v>
+      </c>
+      <c r="DM215" t="s">
+        <v>1840</v>
+      </c>
+      <c r="DN215" t="s">
+        <v>1841</v>
+      </c>
+      <c r="DO215" t="s">
+        <v>972</v>
+      </c>
+      <c r="DP215">
+        <v>1</v>
+      </c>
+      <c r="DQ215">
+        <v>0</v>
+      </c>
+      <c r="DR215">
+        <v>0</v>
+      </c>
+      <c r="DS215" t="s">
+        <v>973</v>
+      </c>
+      <c r="EY215" s="1"/>
+      <c r="GQ215" s="1"/>
+      <c r="GR215" s="1"/>
+      <c r="GY215" s="1"/>
+      <c r="GZ215" s="1"/>
+      <c r="HA215" s="1"/>
+      <c r="HB215" s="1"/>
+      <c r="IQ215" s="1">
+        <v>884305401</v>
+      </c>
+      <c r="IR215" t="s">
+        <v>1842</v>
+      </c>
+      <c r="IS215" s="1">
+        <v>46297.475960648153</v>
+      </c>
+      <c r="IU215" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW215" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX215" t="s">
+        <v>1843</v>
+      </c>
+      <c r="IY215">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="216" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A216" s="1">
+        <v>46297.523460810182</v>
+      </c>
+      <c r="B216" s="1">
+        <v>46297.611049826388</v>
+      </c>
+      <c r="C216" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D216" t="s">
+        <v>945</v>
+      </c>
+      <c r="E216" t="s">
+        <v>234</v>
+      </c>
+      <c r="F216" t="s">
+        <v>735</v>
+      </c>
+      <c r="G216" t="s">
+        <v>198</v>
+      </c>
+      <c r="H216" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS216" t="s">
+        <v>1844</v>
+      </c>
+      <c r="BT216" t="s">
+        <v>1705</v>
+      </c>
+      <c r="BU216" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV216" t="s">
+        <v>1845</v>
+      </c>
+      <c r="BW216" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX216" t="s">
+        <v>876</v>
+      </c>
+      <c r="BY216" t="s">
+        <v>558</v>
+      </c>
+      <c r="DE216" t="s">
+        <v>768</v>
+      </c>
+      <c r="DF216" t="s">
+        <v>1846</v>
+      </c>
+      <c r="DG216">
+        <v>0</v>
+      </c>
+      <c r="DH216">
+        <v>1</v>
+      </c>
+      <c r="DI216">
+        <v>1</v>
+      </c>
+      <c r="DJ216">
+        <v>1</v>
+      </c>
+      <c r="DK216">
+        <v>1</v>
+      </c>
+      <c r="DU216" t="s">
+        <v>1847</v>
+      </c>
+      <c r="DV216" t="s">
+        <v>1848</v>
+      </c>
+      <c r="DW216" t="s">
+        <v>1066</v>
+      </c>
+      <c r="DY216" t="s">
+        <v>955</v>
+      </c>
+      <c r="DZ216" t="s">
+        <v>1849</v>
+      </c>
+      <c r="EA216" t="s">
+        <v>957</v>
+      </c>
+      <c r="EC216" t="s">
+        <v>1850</v>
+      </c>
+      <c r="ED216" t="s">
+        <v>1851</v>
+      </c>
+      <c r="EE216" t="s">
+        <v>1054</v>
+      </c>
+      <c r="EG216" t="s">
+        <v>1852</v>
+      </c>
+      <c r="EH216" t="s">
+        <v>1853</v>
+      </c>
+      <c r="EI216" t="s">
+        <v>976</v>
+      </c>
+      <c r="EY216" s="1"/>
+      <c r="GQ216" s="1"/>
+      <c r="GR216" s="1"/>
+      <c r="GY216" s="1"/>
+      <c r="GZ216" s="1"/>
+      <c r="HA216" s="1"/>
+      <c r="HB216" s="1"/>
+      <c r="IQ216" s="1">
+        <v>884317779</v>
+      </c>
+      <c r="IR216" t="s">
+        <v>1854</v>
+      </c>
+      <c r="IS216" s="1">
+        <v>46297.486076388886</v>
+      </c>
+      <c r="IU216" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW216" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX216" t="s">
+        <v>1855</v>
+      </c>
+      <c r="IY216">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="217" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A217" s="1">
+        <v>46297.616067442133</v>
+      </c>
+      <c r="B217" s="1">
+        <v>46297.621636481483</v>
+      </c>
+      <c r="C217" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D217" t="s">
+        <v>945</v>
+      </c>
+      <c r="E217" t="s">
+        <v>277</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1831</v>
+      </c>
+      <c r="G217" t="s">
+        <v>198</v>
+      </c>
+      <c r="H217" t="s">
+        <v>279</v>
+      </c>
+      <c r="BS217" t="s">
+        <v>1856</v>
+      </c>
+      <c r="BT217" t="s">
+        <v>605</v>
+      </c>
+      <c r="BU217" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV217" t="s">
+        <v>1857</v>
+      </c>
+      <c r="BW217" t="s">
+        <v>354</v>
+      </c>
+      <c r="BX217" t="s">
+        <v>1858</v>
+      </c>
+      <c r="BY217" t="s">
+        <v>453</v>
+      </c>
+      <c r="DE217" t="s">
+        <v>1282</v>
+      </c>
+      <c r="DF217" t="s">
+        <v>1397</v>
+      </c>
+      <c r="DG217">
+        <v>0</v>
+      </c>
+      <c r="DH217">
+        <v>0</v>
+      </c>
+      <c r="DI217">
+        <v>1</v>
+      </c>
+      <c r="DJ217">
+        <v>0</v>
+      </c>
+      <c r="DK217">
+        <v>0</v>
+      </c>
+      <c r="DY217" t="s">
+        <v>1384</v>
+      </c>
+      <c r="DZ217" t="s">
+        <v>1859</v>
+      </c>
+      <c r="EA217" t="s">
+        <v>1860</v>
+      </c>
+      <c r="EY217" s="1"/>
+      <c r="GQ217" s="1"/>
+      <c r="GR217" s="1"/>
+      <c r="GY217" s="1"/>
+      <c r="GZ217" s="1"/>
+      <c r="HA217" s="1"/>
+      <c r="HB217" s="1"/>
+      <c r="IQ217" s="1">
+        <v>884320488</v>
+      </c>
+      <c r="IR217" t="s">
+        <v>1861</v>
+      </c>
+      <c r="IS217" s="1">
+        <v>46297.488449074073</v>
+      </c>
+      <c r="IU217" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW217" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX217" t="s">
+        <v>1862</v>
+      </c>
+      <c r="IY217">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="218" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A218" s="1">
+        <v>46297.611051006941</v>
+      </c>
+      <c r="B218" s="1">
+        <v>46297.62155783565</v>
+      </c>
+      <c r="C218" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D218" t="s">
+        <v>945</v>
+      </c>
+      <c r="E218" t="s">
+        <v>234</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1863</v>
+      </c>
+      <c r="G218" t="s">
+        <v>198</v>
+      </c>
+      <c r="H218" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS218" t="s">
+        <v>1864</v>
+      </c>
+      <c r="BT218" t="s">
+        <v>720</v>
+      </c>
+      <c r="BU218" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV218" t="s">
+        <v>890</v>
+      </c>
+      <c r="BW218" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX218" t="s">
+        <v>1865</v>
+      </c>
+      <c r="BY218" t="s">
+        <v>453</v>
+      </c>
+      <c r="DE218" t="s">
+        <v>1282</v>
+      </c>
+      <c r="DF218" t="s">
+        <v>951</v>
+      </c>
+      <c r="DG218">
+        <v>0</v>
+      </c>
+      <c r="DH218">
+        <v>1</v>
+      </c>
+      <c r="DI218">
+        <v>1</v>
+      </c>
+      <c r="DJ218">
+        <v>0</v>
+      </c>
+      <c r="DK218">
+        <v>1</v>
+      </c>
+      <c r="DU218" t="s">
+        <v>1866</v>
+      </c>
+      <c r="DV218" t="s">
+        <v>1867</v>
+      </c>
+      <c r="DW218" t="s">
+        <v>1051</v>
+      </c>
+      <c r="DY218" t="s">
+        <v>1384</v>
+      </c>
+      <c r="DZ218" t="s">
+        <v>1868</v>
+      </c>
+      <c r="EA218" t="s">
+        <v>1079</v>
+      </c>
+      <c r="EG218" t="s">
+        <v>1869</v>
+      </c>
+      <c r="EH218" t="s">
+        <v>1870</v>
+      </c>
+      <c r="EI218" t="s">
+        <v>976</v>
+      </c>
+      <c r="EY218" s="1"/>
+      <c r="GQ218" s="1"/>
+      <c r="GR218" s="1"/>
+      <c r="GY218" s="1"/>
+      <c r="GZ218" s="1"/>
+      <c r="HA218" s="1"/>
+      <c r="HB218" s="1"/>
+      <c r="IQ218" s="1">
+        <v>884329703</v>
+      </c>
+      <c r="IR218" t="s">
+        <v>1871</v>
+      </c>
+      <c r="IS218" s="1">
+        <v>46297.49659722222</v>
+      </c>
+      <c r="IU218" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW218" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX218" t="s">
+        <v>1872</v>
+      </c>
+      <c r="IY218">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="219" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A219" s="1">
+        <v>46297.623010995369</v>
+      </c>
+      <c r="B219" s="1">
+        <v>46297.629228090278</v>
+      </c>
+      <c r="C219" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D219" t="s">
+        <v>879</v>
+      </c>
+      <c r="E219" t="s">
+        <v>234</v>
+      </c>
+      <c r="F219" t="s">
+        <v>245</v>
+      </c>
+      <c r="G219" t="s">
+        <v>198</v>
+      </c>
+      <c r="H219" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS219" t="s">
+        <v>1873</v>
+      </c>
+      <c r="BT219" t="s">
+        <v>1874</v>
+      </c>
+      <c r="BU219" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV219" t="s">
+        <v>1875</v>
+      </c>
+      <c r="BW219" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX219" t="s">
+        <v>1876</v>
+      </c>
+      <c r="BY219" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP219" t="s">
+        <v>883</v>
+      </c>
+      <c r="CT219" t="s">
+        <v>905</v>
+      </c>
+      <c r="CU219">
+        <v>0</v>
+      </c>
+      <c r="CV219">
+        <v>1</v>
+      </c>
+      <c r="CW219">
+        <v>0</v>
+      </c>
+      <c r="CX219">
+        <v>0</v>
+      </c>
+      <c r="CY219">
+        <v>0</v>
+      </c>
+      <c r="CZ219">
+        <v>0</v>
+      </c>
+      <c r="DA219">
+        <v>0</v>
+      </c>
+      <c r="DC219" t="s">
+        <v>1732</v>
+      </c>
+      <c r="EY219" s="1"/>
+      <c r="GQ219" s="1"/>
+      <c r="GR219" s="1"/>
+      <c r="GY219" s="1"/>
+      <c r="GZ219" s="1"/>
+      <c r="HA219" s="1"/>
+      <c r="HB219" s="1"/>
+      <c r="IQ219" s="1">
+        <v>884338842</v>
+      </c>
+      <c r="IR219" t="s">
+        <v>1877</v>
+      </c>
+      <c r="IS219" s="1">
+        <v>46297.504259259258</v>
+      </c>
+      <c r="IU219" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW219" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX219" t="s">
+        <v>1878</v>
+      </c>
+      <c r="IY219">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="220" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A220" s="1">
+        <v>46297.629230914346</v>
+      </c>
+      <c r="B220" s="1">
+        <v>46297.636683217592</v>
+      </c>
+      <c r="C220" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D220" t="s">
+        <v>945</v>
+      </c>
+      <c r="E220" t="s">
+        <v>234</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1863</v>
+      </c>
+      <c r="G220" t="s">
+        <v>198</v>
+      </c>
+      <c r="H220" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS220" t="s">
+        <v>1879</v>
+      </c>
+      <c r="BT220" t="s">
+        <v>1880</v>
+      </c>
+      <c r="BU220" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV220" t="s">
+        <v>1881</v>
+      </c>
+      <c r="BW220" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX220" t="s">
+        <v>1882</v>
+      </c>
+      <c r="BY220" t="s">
+        <v>453</v>
+      </c>
+      <c r="DE220" t="s">
+        <v>1062</v>
+      </c>
+      <c r="DF220" t="s">
+        <v>1063</v>
+      </c>
+      <c r="DG220">
+        <v>0</v>
+      </c>
+      <c r="DH220">
+        <v>1</v>
+      </c>
+      <c r="DI220">
+        <v>0</v>
+      </c>
+      <c r="DJ220">
+        <v>1</v>
+      </c>
+      <c r="DK220">
+        <v>0</v>
+      </c>
+      <c r="DU220" t="s">
+        <v>1883</v>
+      </c>
+      <c r="DV220" t="s">
+        <v>1884</v>
+      </c>
+      <c r="DW220" t="s">
+        <v>1066</v>
+      </c>
+      <c r="EC220" t="s">
+        <v>1885</v>
+      </c>
+      <c r="ED220" t="s">
+        <v>392</v>
+      </c>
+      <c r="EE220" t="s">
+        <v>1054</v>
+      </c>
+      <c r="EY220" s="1"/>
+      <c r="GQ220" s="1"/>
+      <c r="GR220" s="1"/>
+      <c r="GY220" s="1"/>
+      <c r="GZ220" s="1"/>
+      <c r="HA220" s="1"/>
+      <c r="HB220" s="1"/>
+      <c r="IQ220" s="1">
+        <v>884348130</v>
+      </c>
+      <c r="IR220" t="s">
+        <v>1886</v>
+      </c>
+      <c r="IS220" s="1">
+        <v>46297.511712962973</v>
+      </c>
+      <c r="IU220" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW220" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX220" t="s">
+        <v>1887</v>
+      </c>
+      <c r="IY220">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="221" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A221" s="1">
+        <v>46297.625507025463</v>
+      </c>
+      <c r="B221" s="1">
+        <v>46297.642066782413</v>
+      </c>
+      <c r="C221" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D221" t="s">
+        <v>879</v>
+      </c>
+      <c r="E221" t="s">
+        <v>234</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1888</v>
+      </c>
+      <c r="G221" t="s">
+        <v>198</v>
+      </c>
+      <c r="H221" t="s">
+        <v>1889</v>
+      </c>
+      <c r="BS221" t="s">
+        <v>1890</v>
+      </c>
+      <c r="BT221" t="s">
+        <v>1891</v>
+      </c>
+      <c r="BU221" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW221" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX221" t="s">
+        <v>1892</v>
+      </c>
+      <c r="BY221" t="s">
+        <v>923</v>
+      </c>
+      <c r="CP221" t="s">
+        <v>931</v>
+      </c>
+      <c r="CQ221" t="s">
+        <v>1893</v>
+      </c>
+      <c r="CR221" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS221" t="s">
+        <v>896</v>
+      </c>
+      <c r="CT221" t="s">
+        <v>905</v>
+      </c>
+      <c r="CU221">
+        <v>0</v>
+      </c>
+      <c r="CV221">
+        <v>1</v>
+      </c>
+      <c r="CW221">
+        <v>0</v>
+      </c>
+      <c r="CX221">
+        <v>0</v>
+      </c>
+      <c r="CY221">
+        <v>0</v>
+      </c>
+      <c r="CZ221">
+        <v>0</v>
+      </c>
+      <c r="DA221">
+        <v>0</v>
+      </c>
+      <c r="DC221" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY221" s="1"/>
+      <c r="GQ221" s="1"/>
+      <c r="GR221" s="1"/>
+      <c r="GY221" s="1"/>
+      <c r="GZ221" s="1"/>
+      <c r="HA221" s="1"/>
+      <c r="HB221" s="1"/>
+      <c r="IQ221" s="1">
+        <v>884354487</v>
+      </c>
+      <c r="IR221" t="s">
+        <v>1894</v>
+      </c>
+      <c r="IS221" s="1">
+        <v>46297.517094907409</v>
+      </c>
+      <c r="IU221" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW221" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX221" t="s">
+        <v>1895</v>
+      </c>
+      <c r="IY221">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="222" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A222" s="1">
+        <v>46297.636685254627</v>
+      </c>
+      <c r="B222" s="1">
+        <v>46297.642085659732</v>
+      </c>
+      <c r="C222" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D222" t="s">
+        <v>945</v>
+      </c>
+      <c r="E222" t="s">
+        <v>234</v>
+      </c>
+      <c r="F222" t="s">
+        <v>245</v>
+      </c>
+      <c r="G222" t="s">
+        <v>198</v>
+      </c>
+      <c r="H222" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS222" t="s">
+        <v>1896</v>
+      </c>
+      <c r="BT222" t="s">
+        <v>1705</v>
+      </c>
+      <c r="BU222" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV222" t="s">
+        <v>1897</v>
+      </c>
+      <c r="BW222" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX222" t="s">
+        <v>876</v>
+      </c>
+      <c r="BY222" t="s">
+        <v>923</v>
+      </c>
+      <c r="DE222" t="s">
+        <v>1062</v>
+      </c>
+      <c r="DF222" t="s">
+        <v>1898</v>
+      </c>
+      <c r="DG222">
+        <v>0</v>
+      </c>
+      <c r="DH222">
+        <v>0</v>
+      </c>
+      <c r="DI222">
+        <v>0</v>
+      </c>
+      <c r="DJ222">
+        <v>1</v>
+      </c>
+      <c r="DK222">
+        <v>0</v>
+      </c>
+      <c r="EC222" t="s">
+        <v>1899</v>
+      </c>
+      <c r="ED222" t="s">
+        <v>392</v>
+      </c>
+      <c r="EE222" t="s">
+        <v>1054</v>
+      </c>
+      <c r="EY222" s="1"/>
+      <c r="GQ222" s="1"/>
+      <c r="GR222" s="1"/>
+      <c r="GY222" s="1"/>
+      <c r="GZ222" s="1"/>
+      <c r="HA222" s="1"/>
+      <c r="HB222" s="1"/>
+      <c r="IQ222" s="1">
+        <v>884354508</v>
+      </c>
+      <c r="IR222" t="s">
+        <v>1900</v>
+      </c>
+      <c r="IS222" s="1">
+        <v>46297.517118055563</v>
+      </c>
+      <c r="IU222" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW222" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX222" t="s">
+        <v>1901</v>
+      </c>
+      <c r="IY222">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="223" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A223" s="1">
+        <v>46297.642068576388</v>
+      </c>
+      <c r="B223" s="1">
+        <v>46297.645295543982</v>
+      </c>
+      <c r="C223" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D223" t="s">
+        <v>879</v>
+      </c>
+      <c r="E223" t="s">
+        <v>234</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G223" t="s">
+        <v>198</v>
+      </c>
+      <c r="H223" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS223" t="s">
+        <v>1903</v>
+      </c>
+      <c r="BT223" t="s">
+        <v>1904</v>
+      </c>
+      <c r="BU223" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW223" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX223" t="s">
+        <v>1905</v>
+      </c>
+      <c r="BY223" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP223" t="s">
+        <v>883</v>
+      </c>
+      <c r="CT223" t="s">
+        <v>897</v>
+      </c>
+      <c r="CU223">
+        <v>0</v>
+      </c>
+      <c r="CV223">
+        <v>0</v>
+      </c>
+      <c r="CW223">
+        <v>1</v>
+      </c>
+      <c r="CX223">
+        <v>0</v>
+      </c>
+      <c r="CY223">
+        <v>0</v>
+      </c>
+      <c r="CZ223">
+        <v>0</v>
+      </c>
+      <c r="DA223">
+        <v>0</v>
+      </c>
+      <c r="DC223" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY223" s="1"/>
+      <c r="GQ223" s="1"/>
+      <c r="GR223" s="1"/>
+      <c r="GY223" s="1"/>
+      <c r="GZ223" s="1"/>
+      <c r="HA223" s="1"/>
+      <c r="HB223" s="1"/>
+      <c r="IQ223" s="1">
+        <v>884358611</v>
+      </c>
+      <c r="IR223" t="s">
+        <v>1906</v>
+      </c>
+      <c r="IS223" s="1">
+        <v>46297.520312499997</v>
+      </c>
+      <c r="IU223" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW223" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX223" t="s">
+        <v>1907</v>
+      </c>
+      <c r="IY223">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="224" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A224" s="1">
+        <v>46297.642087673608</v>
+      </c>
+      <c r="B224" s="1">
+        <v>46297.645586828701</v>
+      </c>
+      <c r="C224" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D224" t="s">
+        <v>879</v>
+      </c>
+      <c r="E224" t="s">
+        <v>234</v>
+      </c>
+      <c r="F224" t="s">
+        <v>245</v>
+      </c>
+      <c r="G224" t="s">
+        <v>198</v>
+      </c>
+      <c r="H224" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS224" t="s">
+        <v>1908</v>
+      </c>
+      <c r="BT224" t="s">
+        <v>1909</v>
+      </c>
+      <c r="BU224" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW224" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX224" t="s">
+        <v>876</v>
+      </c>
+      <c r="BY224" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP224" t="s">
+        <v>883</v>
+      </c>
+      <c r="CT224" t="s">
+        <v>802</v>
+      </c>
+      <c r="CU224">
+        <v>0</v>
+      </c>
+      <c r="CV224">
+        <v>0</v>
+      </c>
+      <c r="CW224">
+        <v>0</v>
+      </c>
+      <c r="CX224">
+        <v>0</v>
+      </c>
+      <c r="CY224">
+        <v>0</v>
+      </c>
+      <c r="CZ224">
+        <v>0</v>
+      </c>
+      <c r="DA224">
+        <v>1</v>
+      </c>
+      <c r="DB224" t="s">
+        <v>1910</v>
+      </c>
+      <c r="DC224" t="s">
+        <v>898</v>
+      </c>
+      <c r="EY224" s="1"/>
+      <c r="GQ224" s="1"/>
+      <c r="GR224" s="1"/>
+      <c r="GY224" s="1"/>
+      <c r="GZ224" s="1"/>
+      <c r="HA224" s="1"/>
+      <c r="HB224" s="1"/>
+      <c r="IQ224" s="1">
+        <v>884359010</v>
+      </c>
+      <c r="IR224" t="s">
+        <v>1911</v>
+      </c>
+      <c r="IS224" s="1">
+        <v>46297.520613425928</v>
+      </c>
+      <c r="IU224" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW224" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX224" t="s">
+        <v>1912</v>
+      </c>
+      <c r="IY224">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="225" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A225" s="1">
+        <v>46297.645297141207</v>
+      </c>
+      <c r="B225" s="1">
+        <v>46297.647904282407</v>
+      </c>
+      <c r="C225" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D225" t="s">
+        <v>879</v>
+      </c>
+      <c r="E225" t="s">
+        <v>234</v>
+      </c>
+      <c r="F225" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G225" t="s">
+        <v>198</v>
+      </c>
+      <c r="H225" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS225" t="s">
+        <v>1914</v>
+      </c>
+      <c r="BT225" t="s">
+        <v>1915</v>
+      </c>
+      <c r="BU225" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW225" t="s">
+        <v>354</v>
+      </c>
+      <c r="BX225" t="s">
+        <v>1916</v>
+      </c>
+      <c r="BY225" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP225" t="s">
+        <v>931</v>
+      </c>
+      <c r="CQ225" t="s">
+        <v>1917</v>
+      </c>
+      <c r="CR225" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS225" t="s">
+        <v>896</v>
+      </c>
+      <c r="CT225" t="s">
+        <v>1118</v>
+      </c>
+      <c r="CU225">
+        <v>0</v>
+      </c>
+      <c r="CV225">
+        <v>1</v>
+      </c>
+      <c r="CW225">
+        <v>0</v>
+      </c>
+      <c r="CX225">
+        <v>1</v>
+      </c>
+      <c r="CY225">
+        <v>0</v>
+      </c>
+      <c r="CZ225">
+        <v>0</v>
+      </c>
+      <c r="DA225">
+        <v>0</v>
+      </c>
+      <c r="DC225" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY225" s="1"/>
+      <c r="GQ225" s="1"/>
+      <c r="GR225" s="1"/>
+      <c r="GY225" s="1"/>
+      <c r="GZ225" s="1"/>
+      <c r="HA225" s="1"/>
+      <c r="HB225" s="1"/>
+      <c r="IQ225" s="1">
+        <v>884361775</v>
+      </c>
+      <c r="IR225" t="s">
+        <v>1918</v>
+      </c>
+      <c r="IS225" s="1">
+        <v>46297.523055555554</v>
+      </c>
+      <c r="IU225" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW225" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX225" t="s">
+        <v>1919</v>
+      </c>
+      <c r="IY225">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="226" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A226" s="1">
+        <v>46297.647905798607</v>
+      </c>
+      <c r="B226" s="1">
+        <v>46297.65831741898</v>
+      </c>
+      <c r="C226" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D226" t="s">
+        <v>879</v>
+      </c>
+      <c r="E226" t="s">
+        <v>234</v>
+      </c>
+      <c r="F226" t="s">
+        <v>735</v>
+      </c>
+      <c r="G226" t="s">
+        <v>198</v>
+      </c>
+      <c r="H226" t="s">
+        <v>1920</v>
+      </c>
+      <c r="BS226" t="s">
+        <v>1921</v>
+      </c>
+      <c r="BT226" t="s">
+        <v>1922</v>
+      </c>
+      <c r="BU226" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW226" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX226" t="s">
+        <v>876</v>
+      </c>
+      <c r="BY226" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP226" t="s">
+        <v>1211</v>
+      </c>
+      <c r="CQ226" t="s">
+        <v>1923</v>
+      </c>
+      <c r="CR226" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS226" t="s">
+        <v>896</v>
+      </c>
+      <c r="CT226" t="s">
+        <v>905</v>
+      </c>
+      <c r="CU226">
+        <v>0</v>
+      </c>
+      <c r="CV226">
+        <v>1</v>
+      </c>
+      <c r="CW226">
+        <v>0</v>
+      </c>
+      <c r="CX226">
+        <v>0</v>
+      </c>
+      <c r="CY226">
+        <v>0</v>
+      </c>
+      <c r="CZ226">
+        <v>0</v>
+      </c>
+      <c r="DA226">
+        <v>0</v>
+      </c>
+      <c r="DC226" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY226" s="1"/>
+      <c r="GQ226" s="1"/>
+      <c r="GR226" s="1"/>
+      <c r="GY226" s="1"/>
+      <c r="GZ226" s="1"/>
+      <c r="HA226" s="1"/>
+      <c r="HB226" s="1"/>
+      <c r="IQ226" s="1">
+        <v>884439661</v>
+      </c>
+      <c r="IR226" t="s">
+        <v>1924</v>
+      </c>
+      <c r="IS226" s="1">
+        <v>46297.586840277778</v>
+      </c>
+      <c r="IU226" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW226" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX226" t="s">
+        <v>1925</v>
+      </c>
+      <c r="IY226">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="227" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A227" s="1">
+        <v>46297.658319340277</v>
+      </c>
+      <c r="B227" s="1">
+        <v>46297.664369479156</v>
+      </c>
+      <c r="C227" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D227" t="s">
+        <v>879</v>
+      </c>
+      <c r="E227" t="s">
+        <v>234</v>
+      </c>
+      <c r="F227" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G227" t="s">
+        <v>198</v>
+      </c>
+      <c r="H227" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS227" t="s">
+        <v>1927</v>
+      </c>
+      <c r="BT227" t="s">
+        <v>1928</v>
+      </c>
+      <c r="BU227" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW227" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX227" t="s">
+        <v>1929</v>
+      </c>
+      <c r="BY227" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP227" t="s">
+        <v>883</v>
+      </c>
+      <c r="CT227" t="s">
+        <v>1106</v>
+      </c>
+      <c r="CU227">
+        <v>0</v>
+      </c>
+      <c r="CV227">
+        <v>1</v>
+      </c>
+      <c r="CW227">
+        <v>1</v>
+      </c>
+      <c r="CX227">
+        <v>0</v>
+      </c>
+      <c r="CY227">
+        <v>0</v>
+      </c>
+      <c r="CZ227">
+        <v>0</v>
+      </c>
+      <c r="DA227">
+        <v>0</v>
+      </c>
+      <c r="DC227" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY227" s="1"/>
+      <c r="GQ227" s="1"/>
+      <c r="GR227" s="1"/>
+      <c r="GY227" s="1"/>
+      <c r="GZ227" s="1"/>
+      <c r="HA227" s="1"/>
+      <c r="HB227" s="1"/>
+      <c r="IQ227" s="1">
+        <v>884439671</v>
+      </c>
+      <c r="IR227" t="s">
+        <v>1930</v>
+      </c>
+      <c r="IS227" s="1">
+        <v>46297.586840277778</v>
+      </c>
+      <c r="IU227" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW227" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX227" t="s">
+        <v>1931</v>
+      </c>
+      <c r="IY227">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="228" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A228" s="1">
+        <v>46297.664371840277</v>
+      </c>
+      <c r="B228" s="1">
+        <v>46297.697084953703</v>
+      </c>
+      <c r="C228" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D228" t="s">
+        <v>879</v>
+      </c>
+      <c r="E228" t="s">
+        <v>234</v>
+      </c>
+      <c r="F228" t="s">
+        <v>1932</v>
+      </c>
+      <c r="G228" t="s">
+        <v>198</v>
+      </c>
+      <c r="H228" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS228" t="s">
+        <v>1933</v>
+      </c>
+      <c r="BT228" t="s">
+        <v>1934</v>
+      </c>
+      <c r="BU228" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW228" t="s">
+        <v>354</v>
+      </c>
+      <c r="BX228" t="s">
+        <v>1935</v>
+      </c>
+      <c r="BY228" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP228" t="s">
+        <v>931</v>
+      </c>
+      <c r="CQ228" t="s">
+        <v>1936</v>
+      </c>
+      <c r="CR228" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS228" t="s">
+        <v>1172</v>
+      </c>
+      <c r="CT228" t="s">
+        <v>1106</v>
+      </c>
+      <c r="CU228">
+        <v>0</v>
+      </c>
+      <c r="CV228">
+        <v>1</v>
+      </c>
+      <c r="CW228">
+        <v>1</v>
+      </c>
+      <c r="CX228">
+        <v>0</v>
+      </c>
+      <c r="CY228">
+        <v>0</v>
+      </c>
+      <c r="CZ228">
+        <v>0</v>
+      </c>
+      <c r="DA228">
+        <v>0</v>
+      </c>
+      <c r="DC228" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY228" s="1"/>
+      <c r="GQ228" s="1"/>
+      <c r="GR228" s="1"/>
+      <c r="GY228" s="1"/>
+      <c r="GZ228" s="1"/>
+      <c r="HA228" s="1"/>
+      <c r="HB228" s="1"/>
+      <c r="IQ228" s="1">
+        <v>884439687</v>
+      </c>
+      <c r="IR228" t="s">
+        <v>1937</v>
+      </c>
+      <c r="IS228" s="1">
+        <v>46297.586851851847</v>
+      </c>
+      <c r="IU228" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW228" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX228" t="s">
+        <v>1938</v>
+      </c>
+      <c r="IY228">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="229" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A229" s="1">
+        <v>46297.697087002307</v>
+      </c>
+      <c r="B229" s="1">
+        <v>46297.717213634263</v>
+      </c>
+      <c r="C229" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D229" t="s">
+        <v>879</v>
+      </c>
+      <c r="E229" t="s">
+        <v>234</v>
+      </c>
+      <c r="F229" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G229" t="s">
+        <v>198</v>
+      </c>
+      <c r="H229" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS229" t="s">
+        <v>1939</v>
+      </c>
+      <c r="BT229" t="s">
+        <v>1940</v>
+      </c>
+      <c r="BU229" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW229" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX229" t="s">
+        <v>1941</v>
+      </c>
+      <c r="BY229" t="s">
+        <v>356</v>
+      </c>
+      <c r="CP229" t="s">
+        <v>883</v>
+      </c>
+      <c r="CT229" t="s">
+        <v>1106</v>
+      </c>
+      <c r="CU229">
+        <v>0</v>
+      </c>
+      <c r="CV229">
+        <v>1</v>
+      </c>
+      <c r="CW229">
+        <v>1</v>
+      </c>
+      <c r="CX229">
+        <v>0</v>
+      </c>
+      <c r="CY229">
+        <v>0</v>
+      </c>
+      <c r="CZ229">
+        <v>0</v>
+      </c>
+      <c r="DA229">
+        <v>0</v>
+      </c>
+      <c r="DC229" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY229" s="1"/>
+      <c r="GQ229" s="1"/>
+      <c r="GR229" s="1"/>
+      <c r="GY229" s="1"/>
+      <c r="GZ229" s="1"/>
+      <c r="HA229" s="1"/>
+      <c r="HB229" s="1"/>
+      <c r="IQ229" s="1">
+        <v>884446980</v>
+      </c>
+      <c r="IR229" t="s">
+        <v>1942</v>
+      </c>
+      <c r="IS229" s="1">
+        <v>46297.592233796298</v>
+      </c>
+      <c r="IU229" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW229" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX229" t="s">
+        <v>1943</v>
+      </c>
+      <c r="IY229">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="230" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A230" s="1">
+        <v>46297.717215694443</v>
+      </c>
+      <c r="B230" s="1">
+        <v>46297.720687835637</v>
+      </c>
+      <c r="C230" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D230" t="s">
+        <v>879</v>
+      </c>
+      <c r="E230" t="s">
+        <v>234</v>
+      </c>
+      <c r="F230" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G230" t="s">
+        <v>198</v>
+      </c>
+      <c r="H230" t="s">
+        <v>1920</v>
+      </c>
+      <c r="BS230" t="s">
+        <v>1944</v>
+      </c>
+      <c r="BT230" t="s">
+        <v>1945</v>
+      </c>
+      <c r="BU230" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW230" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX230" t="s">
+        <v>1946</v>
+      </c>
+      <c r="BY230" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP230" t="s">
+        <v>883</v>
+      </c>
+      <c r="CT230" t="s">
+        <v>1514</v>
+      </c>
+      <c r="CU230">
+        <v>0</v>
+      </c>
+      <c r="CV230">
+        <v>0</v>
+      </c>
+      <c r="CW230">
+        <v>1</v>
+      </c>
+      <c r="CX230">
+        <v>1</v>
+      </c>
+      <c r="CY230">
+        <v>0</v>
+      </c>
+      <c r="CZ230">
+        <v>0</v>
+      </c>
+      <c r="DA230">
+        <v>0</v>
+      </c>
+      <c r="DC230" t="s">
+        <v>885</v>
+      </c>
+      <c r="EY230" s="1"/>
+      <c r="GQ230" s="1"/>
+      <c r="GR230" s="1"/>
+      <c r="GY230" s="1"/>
+      <c r="GZ230" s="1"/>
+      <c r="HA230" s="1"/>
+      <c r="HB230" s="1"/>
+      <c r="IQ230" s="1">
+        <v>884451766</v>
+      </c>
+      <c r="IR230" t="s">
+        <v>1947</v>
+      </c>
+      <c r="IS230" s="1">
+        <v>46297.595706018517</v>
+      </c>
+      <c r="IU230" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW230" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX230" t="s">
+        <v>1948</v>
+      </c>
+      <c r="IY230">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="231" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A231" s="1">
+        <v>46297.720690405091</v>
+      </c>
+      <c r="B231" s="1">
+        <v>46297.72633459491</v>
+      </c>
+      <c r="C231" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D231" t="s">
+        <v>879</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+      <c r="F231" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G231" t="s">
+        <v>198</v>
+      </c>
+      <c r="H231" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS231" t="s">
+        <v>1949</v>
+      </c>
+      <c r="BT231" t="s">
+        <v>1950</v>
+      </c>
+      <c r="BU231" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW231" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX231" t="s">
+        <v>1951</v>
+      </c>
+      <c r="BY231" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP231" t="s">
+        <v>931</v>
+      </c>
+      <c r="CQ231" t="s">
+        <v>1952</v>
+      </c>
+      <c r="CR231" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS231" t="s">
+        <v>933</v>
+      </c>
+      <c r="CT231" t="s">
+        <v>897</v>
+      </c>
+      <c r="CU231">
+        <v>0</v>
+      </c>
+      <c r="CV231">
+        <v>0</v>
+      </c>
+      <c r="CW231">
+        <v>1</v>
+      </c>
+      <c r="CX231">
+        <v>0</v>
+      </c>
+      <c r="CY231">
+        <v>0</v>
+      </c>
+      <c r="CZ231">
+        <v>0</v>
+      </c>
+      <c r="DA231">
+        <v>0</v>
+      </c>
+      <c r="DC231" t="s">
+        <v>885</v>
+      </c>
+      <c r="EY231" s="1"/>
+      <c r="GQ231" s="1"/>
+      <c r="GR231" s="1"/>
+      <c r="GY231" s="1"/>
+      <c r="GZ231" s="1"/>
+      <c r="HA231" s="1"/>
+      <c r="HB231" s="1"/>
+      <c r="IQ231" s="1">
+        <v>884459300</v>
+      </c>
+      <c r="IR231" t="s">
+        <v>1953</v>
+      </c>
+      <c r="IS231" s="1">
+        <v>46297.601354166669</v>
+      </c>
+      <c r="IU231" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW231" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX231" t="s">
+        <v>1954</v>
+      </c>
+      <c r="IY231">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="232" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A232" s="1">
+        <v>46297.726336203697</v>
+      </c>
+      <c r="B232" s="1">
+        <v>46297.731607372683</v>
+      </c>
+      <c r="C232" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D232" t="s">
+        <v>879</v>
+      </c>
+      <c r="E232" t="s">
+        <v>234</v>
+      </c>
+      <c r="F232" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G232" t="s">
+        <v>198</v>
+      </c>
+      <c r="H232" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS232" t="s">
+        <v>1955</v>
+      </c>
+      <c r="BT232" t="s">
+        <v>1956</v>
+      </c>
+      <c r="BU232" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW232" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX232" t="s">
+        <v>1957</v>
+      </c>
+      <c r="BY232" t="s">
+        <v>558</v>
+      </c>
+      <c r="CP232" t="s">
+        <v>931</v>
+      </c>
+      <c r="CQ232" t="s">
+        <v>1958</v>
+      </c>
+      <c r="CR232" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS232" t="s">
+        <v>1162</v>
+      </c>
+      <c r="CT232" t="s">
+        <v>905</v>
+      </c>
+      <c r="CU232">
+        <v>0</v>
+      </c>
+      <c r="CV232">
+        <v>1</v>
+      </c>
+      <c r="CW232">
+        <v>0</v>
+      </c>
+      <c r="CX232">
+        <v>0</v>
+      </c>
+      <c r="CY232">
+        <v>0</v>
+      </c>
+      <c r="CZ232">
+        <v>0</v>
+      </c>
+      <c r="DA232">
+        <v>0</v>
+      </c>
+      <c r="DC232" t="s">
+        <v>906</v>
+      </c>
+      <c r="EY232" s="1"/>
+      <c r="GQ232" s="1"/>
+      <c r="GR232" s="1"/>
+      <c r="GY232" s="1"/>
+      <c r="GZ232" s="1"/>
+      <c r="HA232" s="1"/>
+      <c r="HB232" s="1"/>
+      <c r="IQ232" s="1">
+        <v>884466442</v>
+      </c>
+      <c r="IR232" t="s">
+        <v>1959</v>
+      </c>
+      <c r="IS232" s="1">
+        <v>46297.606620370367</v>
+      </c>
+      <c r="IU232" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW232" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX232" t="s">
+        <v>1960</v>
+      </c>
+      <c r="IY232">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="233" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A233" s="1">
+        <v>46297.727836921287</v>
+      </c>
+      <c r="B233" s="1">
+        <v>46297.733301273147</v>
+      </c>
+      <c r="C233" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D233" t="s">
+        <v>684</v>
+      </c>
+      <c r="E233" t="s">
+        <v>251</v>
+      </c>
+      <c r="F233" t="s">
+        <v>258</v>
+      </c>
+      <c r="G233" t="s">
+        <v>198</v>
+      </c>
+      <c r="H233" t="s">
+        <v>253</v>
+      </c>
+      <c r="J233" t="s">
+        <v>1961</v>
+      </c>
+      <c r="K233" t="s">
+        <v>201</v>
+      </c>
+      <c r="L233" t="s">
+        <v>321</v>
+      </c>
+      <c r="M233" t="s">
+        <v>1694</v>
+      </c>
+      <c r="N233" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O233" t="s">
+        <v>1666</v>
+      </c>
+      <c r="P233" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AH233">
+        <v>210</v>
+      </c>
+      <c r="AI233">
+        <v>65</v>
+      </c>
+      <c r="AJ233">
+        <v>105</v>
+      </c>
+      <c r="AK233">
+        <v>2</v>
+      </c>
+      <c r="AL233">
+        <v>2</v>
+      </c>
+      <c r="AM233">
+        <v>0</v>
+      </c>
+      <c r="AN233">
+        <v>0</v>
+      </c>
+      <c r="AO233" t="s">
+        <v>1697</v>
+      </c>
+      <c r="AP233">
+        <v>0</v>
+      </c>
+      <c r="AQ233" t="s">
+        <v>337</v>
+      </c>
+      <c r="AR233" t="s">
+        <v>338</v>
+      </c>
+      <c r="AS233" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT233" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU233" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV233" t="s">
+        <v>231</v>
+      </c>
+      <c r="AW233" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS233" t="s">
+        <v>1962</v>
+      </c>
+      <c r="BT233" t="s">
+        <v>1963</v>
+      </c>
+      <c r="BU233" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW233" t="s">
+        <v>354</v>
+      </c>
+      <c r="BX233" t="s">
+        <v>1964</v>
+      </c>
+      <c r="EY233" s="1"/>
+      <c r="GQ233" s="1"/>
+      <c r="GR233" s="1"/>
+      <c r="GY233" s="1"/>
+      <c r="GZ233" s="1"/>
+      <c r="HA233" s="1"/>
+      <c r="HB233" s="1"/>
+      <c r="IQ233" s="1">
+        <v>884468553</v>
+      </c>
+      <c r="IR233" t="s">
+        <v>1965</v>
+      </c>
+      <c r="IS233" s="1">
+        <v>46297.60833333333</v>
+      </c>
+      <c r="IU233" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW233" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX233" t="s">
+        <v>1966</v>
+      </c>
+      <c r="IY233">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="234" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A234" s="1">
+        <v>46297.733303923611</v>
+      </c>
+      <c r="B234" s="1">
+        <v>46297.741435150463</v>
+      </c>
+      <c r="C234" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D234" t="s">
+        <v>684</v>
+      </c>
+      <c r="E234" t="s">
+        <v>251</v>
+      </c>
+      <c r="F234" t="s">
+        <v>264</v>
+      </c>
+      <c r="G234" t="s">
+        <v>198</v>
+      </c>
+      <c r="H234" t="s">
+        <v>253</v>
+      </c>
+      <c r="J234" t="s">
+        <v>265</v>
+      </c>
+      <c r="K234" t="s">
+        <v>201</v>
+      </c>
+      <c r="L234" t="s">
+        <v>321</v>
+      </c>
+      <c r="M234" t="s">
+        <v>1694</v>
+      </c>
+      <c r="N234" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O234" t="s">
+        <v>1666</v>
+      </c>
+      <c r="P234" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AH234">
+        <v>44</v>
+      </c>
+      <c r="AI234">
+        <v>13</v>
+      </c>
+      <c r="AJ234">
+        <v>21</v>
+      </c>
+      <c r="AK234">
+        <v>1</v>
+      </c>
+      <c r="AL234">
+        <v>2</v>
+      </c>
+      <c r="AM234">
+        <v>0</v>
+      </c>
+      <c r="AN234">
+        <v>0</v>
+      </c>
+      <c r="AO234" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AP234">
+        <v>2</v>
+      </c>
+      <c r="AQ234" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR234" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS234" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT234" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU234" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV234" t="s">
+        <v>231</v>
+      </c>
+      <c r="AW234" t="s">
+        <v>227</v>
+      </c>
+      <c r="BS234" t="s">
+        <v>1967</v>
+      </c>
+      <c r="BT234" t="s">
+        <v>1968</v>
+      </c>
+      <c r="BU234" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW234" t="s">
+        <v>354</v>
+      </c>
+      <c r="BX234" t="s">
+        <v>1969</v>
+      </c>
+      <c r="EY234" s="1"/>
+      <c r="GQ234" s="1"/>
+      <c r="GR234" s="1"/>
+      <c r="GY234" s="1"/>
+      <c r="GZ234" s="1"/>
+      <c r="HA234" s="1"/>
+      <c r="HB234" s="1"/>
+      <c r="IQ234" s="1">
+        <v>884478652</v>
+      </c>
+      <c r="IR234" t="s">
+        <v>1970</v>
+      </c>
+      <c r="IS234" s="1">
+        <v>46297.61645833333</v>
+      </c>
+      <c r="IU234" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW234" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX234" t="s">
+        <v>1971</v>
+      </c>
+      <c r="IY234">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="235" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A235" s="1">
+        <v>46297.741437164354</v>
+      </c>
+      <c r="B235" s="1">
+        <v>46297.747532696761</v>
+      </c>
+      <c r="C235" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D235" t="s">
+        <v>683</v>
+      </c>
+      <c r="E235" t="s">
+        <v>251</v>
+      </c>
+      <c r="F235" t="s">
+        <v>758</v>
+      </c>
+      <c r="G235" t="s">
+        <v>198</v>
+      </c>
+      <c r="H235" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX235" t="s">
+        <v>1972</v>
+      </c>
+      <c r="AY235" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ235" t="s">
+        <v>1618</v>
+      </c>
+      <c r="BA235" t="s">
+        <v>1973</v>
+      </c>
+      <c r="BB235">
+        <v>72</v>
+      </c>
+      <c r="BC235">
+        <v>135</v>
+      </c>
+      <c r="BD235" t="s">
+        <v>392</v>
+      </c>
+      <c r="BE235" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF235" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG235" t="s">
+        <v>1974</v>
+      </c>
+      <c r="BH235" t="s">
+        <v>324</v>
+      </c>
+      <c r="BI235" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ235" t="s">
+        <v>392</v>
+      </c>
+      <c r="BK235">
+        <v>6</v>
+      </c>
+      <c r="BL235" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM235">
+        <v>312</v>
+      </c>
+      <c r="BN235">
+        <v>256</v>
+      </c>
+      <c r="BO235" t="s">
+        <v>324</v>
+      </c>
+      <c r="BP235" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ235" t="s">
+        <v>1975</v>
+      </c>
+      <c r="BS235" t="s">
+        <v>1976</v>
+      </c>
+      <c r="BT235" t="s">
+        <v>1977</v>
+      </c>
+      <c r="BU235" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW235" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX235" t="s">
+        <v>1978</v>
+      </c>
+      <c r="EY235" s="1"/>
+      <c r="GQ235" s="1"/>
+      <c r="GR235" s="1"/>
+      <c r="GY235" s="1"/>
+      <c r="GZ235" s="1"/>
+      <c r="HA235" s="1"/>
+      <c r="HB235" s="1"/>
+      <c r="IQ235" s="1">
+        <v>884487033</v>
+      </c>
+      <c r="IR235" t="s">
+        <v>1979</v>
+      </c>
+      <c r="IS235" s="1">
+        <v>46297.622557870367</v>
+      </c>
+      <c r="IU235" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW235" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX235" t="s">
+        <v>1980</v>
+      </c>
+      <c r="IY235">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="236" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A236" s="1">
+        <v>46297.74753537037</v>
+      </c>
+      <c r="B236" s="1">
+        <v>46297.753938796297</v>
+      </c>
+      <c r="C236" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D236" t="s">
+        <v>683</v>
+      </c>
+      <c r="E236" t="s">
+        <v>251</v>
+      </c>
+      <c r="F236" t="s">
+        <v>329</v>
+      </c>
+      <c r="G236" t="s">
+        <v>198</v>
+      </c>
+      <c r="H236" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX236" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AY236" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ236" t="s">
+        <v>1824</v>
+      </c>
+      <c r="BA236" t="s">
+        <v>1981</v>
+      </c>
+      <c r="BB236">
+        <v>4</v>
+      </c>
+      <c r="BC236">
+        <v>3</v>
+      </c>
+      <c r="BD236" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE236" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF236" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG236" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BH236" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI236" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ236" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK236">
+        <v>4</v>
+      </c>
+      <c r="BL236" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM236">
+        <v>146</v>
+      </c>
+      <c r="BN236">
+        <v>120</v>
+      </c>
+      <c r="BO236" t="s">
+        <v>324</v>
+      </c>
+      <c r="BP236" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ236" t="s">
+        <v>1623</v>
+      </c>
+      <c r="BS236" t="s">
+        <v>1983</v>
+      </c>
+      <c r="BT236" t="s">
+        <v>1984</v>
+      </c>
+      <c r="BU236" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW236" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX236" t="s">
+        <v>1985</v>
+      </c>
+      <c r="EY236" s="1"/>
+      <c r="GQ236" s="1"/>
+      <c r="GR236" s="1"/>
+      <c r="GY236" s="1"/>
+      <c r="GZ236" s="1"/>
+      <c r="HA236" s="1"/>
+      <c r="HB236" s="1"/>
+      <c r="IQ236" s="1">
+        <v>884493999</v>
+      </c>
+      <c r="IR236" t="s">
+        <v>1986</v>
+      </c>
+      <c r="IS236" s="1">
+        <v>46297.628969907397</v>
+      </c>
+      <c r="IU236" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW236" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX236" t="s">
+        <v>1987</v>
+      </c>
+      <c r="IY236">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="237" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A237" s="1">
+        <v>46297.753942407413</v>
+      </c>
+      <c r="B237" s="1">
+        <v>46297.757288715278</v>
+      </c>
+      <c r="C237" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D237" t="s">
+        <v>683</v>
+      </c>
+      <c r="E237" t="s">
+        <v>251</v>
+      </c>
+      <c r="F237" t="s">
+        <v>329</v>
+      </c>
+      <c r="G237" t="s">
+        <v>198</v>
+      </c>
+      <c r="H237" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX237" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AY237" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ237" t="s">
+        <v>1618</v>
+      </c>
+      <c r="BA237" t="s">
+        <v>1988</v>
+      </c>
+      <c r="BB237">
+        <v>5</v>
+      </c>
+      <c r="BC237">
+        <v>0</v>
+      </c>
+      <c r="BD237" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE237" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF237" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG237" t="s">
+        <v>1989</v>
+      </c>
+      <c r="BH237" t="s">
+        <v>324</v>
+      </c>
+      <c r="BI237" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ237" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK237">
+        <v>3</v>
+      </c>
+      <c r="BL237" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM237">
+        <v>210</v>
+      </c>
+      <c r="BN237">
+        <v>342</v>
+      </c>
+      <c r="BO237" t="s">
+        <v>324</v>
+      </c>
+      <c r="BP237" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ237" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS237" t="s">
+        <v>1990</v>
+      </c>
+      <c r="BT237" t="s">
+        <v>1991</v>
+      </c>
+      <c r="BU237" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV237" t="s">
+        <v>1992</v>
+      </c>
+      <c r="BW237" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX237" t="s">
+        <v>1993</v>
+      </c>
+      <c r="EY237" s="1"/>
+      <c r="GQ237" s="1"/>
+      <c r="GR237" s="1"/>
+      <c r="GY237" s="1"/>
+      <c r="GZ237" s="1"/>
+      <c r="HA237" s="1"/>
+      <c r="HB237" s="1"/>
+      <c r="IQ237" s="1">
+        <v>884497672</v>
+      </c>
+      <c r="IR237" t="s">
+        <v>1994</v>
+      </c>
+      <c r="IS237" s="1">
+        <v>46297.632303240738</v>
+      </c>
+      <c r="IU237" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW237" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX237" t="s">
+        <v>1995</v>
+      </c>
+      <c r="IY237">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="238" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A238" s="1">
+        <v>46297.757290694448</v>
+      </c>
+      <c r="B238" s="1">
+        <v>46297.760939953703</v>
+      </c>
+      <c r="C238" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D238" t="s">
+        <v>683</v>
+      </c>
+      <c r="E238" t="s">
+        <v>251</v>
+      </c>
+      <c r="F238" t="s">
+        <v>758</v>
+      </c>
+      <c r="G238" t="s">
+        <v>198</v>
+      </c>
+      <c r="H238" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX238" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AY238" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ238" t="s">
+        <v>1618</v>
+      </c>
+      <c r="BA238" t="s">
+        <v>1996</v>
+      </c>
+      <c r="BB238">
+        <v>3</v>
+      </c>
+      <c r="BC238">
+        <v>0</v>
+      </c>
+      <c r="BD238" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE238" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF238" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG238" t="s">
+        <v>1997</v>
+      </c>
+      <c r="BH238" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI238" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ238" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK238">
+        <v>3</v>
+      </c>
+      <c r="BL238" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM238">
+        <v>311</v>
+      </c>
+      <c r="BN238">
+        <v>244</v>
+      </c>
+      <c r="BO238" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BP238" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ238" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS238" t="s">
+        <v>1998</v>
+      </c>
+      <c r="BT238" t="s">
+        <v>1999</v>
+      </c>
+      <c r="BU238" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV238" t="s">
+        <v>890</v>
+      </c>
+      <c r="BW238" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX238" t="s">
+        <v>2000</v>
+      </c>
+      <c r="EY238" s="1"/>
+      <c r="GQ238" s="1"/>
+      <c r="GR238" s="1"/>
+      <c r="GY238" s="1"/>
+      <c r="GZ238" s="1"/>
+      <c r="HA238" s="1"/>
+      <c r="HB238" s="1"/>
+      <c r="IQ238" s="1">
+        <v>884502228</v>
+      </c>
+      <c r="IR238" t="s">
+        <v>2001</v>
+      </c>
+      <c r="IS238" s="1">
+        <v>46297.635960648149</v>
+      </c>
+      <c r="IU238" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW238" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX238" t="s">
+        <v>2002</v>
+      </c>
+      <c r="IY238">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="239" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A239" s="1">
+        <v>46297.848862210652</v>
+      </c>
+      <c r="B239" s="1">
+        <v>46297.87210753472</v>
+      </c>
+      <c r="C239" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D239" t="s">
+        <v>683</v>
+      </c>
+      <c r="E239" t="s">
+        <v>196</v>
+      </c>
+      <c r="F239" t="s">
+        <v>611</v>
+      </c>
+      <c r="G239" t="s">
+        <v>198</v>
+      </c>
+      <c r="H239" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX239" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AY239" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ239" t="s">
+        <v>1618</v>
+      </c>
+      <c r="BA239" t="s">
+        <v>2003</v>
+      </c>
+      <c r="BB239">
+        <v>25</v>
+      </c>
+      <c r="BC239">
+        <v>5</v>
+      </c>
+      <c r="BD239" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE239" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF239" t="s">
+        <v>1620</v>
+      </c>
+      <c r="BG239" t="s">
+        <v>2004</v>
+      </c>
+      <c r="BH239" t="s">
+        <v>324</v>
+      </c>
+      <c r="BI239" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ239" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK239">
+        <v>3</v>
+      </c>
+      <c r="BL239" t="s">
+        <v>2005</v>
+      </c>
+      <c r="BM239">
+        <v>20</v>
+      </c>
+      <c r="BN239">
+        <v>30</v>
+      </c>
+      <c r="BO239" t="s">
+        <v>324</v>
+      </c>
+      <c r="BP239" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ239" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS239" t="s">
+        <v>2006</v>
+      </c>
+      <c r="BT239" t="s">
+        <v>2007</v>
+      </c>
+      <c r="BU239" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV239" t="s">
+        <v>2008</v>
+      </c>
+      <c r="BW239" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX239" t="s">
+        <v>1112</v>
+      </c>
+      <c r="EY239" s="1"/>
+      <c r="GQ239" s="1"/>
+      <c r="GR239" s="1"/>
+      <c r="GY239" s="1"/>
+      <c r="GZ239" s="1"/>
+      <c r="HA239" s="1"/>
+      <c r="HB239" s="1"/>
+      <c r="IQ239" s="1">
+        <v>884616009</v>
+      </c>
+      <c r="IR239" t="s">
+        <v>2009</v>
+      </c>
+      <c r="IS239" s="1">
+        <v>46297.747118055559</v>
+      </c>
+      <c r="IU239" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW239" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX239" t="s">
+        <v>2010</v>
+      </c>
+      <c r="IY239">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="240" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A240" s="1">
+        <v>46297.645588900457</v>
+      </c>
+      <c r="B240" s="1">
+        <v>46297.908402372683</v>
+      </c>
+      <c r="C240" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D240" t="s">
+        <v>945</v>
+      </c>
+      <c r="E240" t="s">
+        <v>234</v>
+      </c>
+      <c r="F240" t="s">
+        <v>735</v>
+      </c>
+      <c r="G240" t="s">
+        <v>198</v>
+      </c>
+      <c r="H240" t="s">
+        <v>237</v>
+      </c>
+      <c r="BS240" t="s">
+        <v>2011</v>
+      </c>
+      <c r="BT240" t="s">
+        <v>1705</v>
+      </c>
+      <c r="BU240" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW240" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX240" t="s">
+        <v>876</v>
+      </c>
+      <c r="BY240" t="s">
+        <v>558</v>
+      </c>
+      <c r="DE240" t="s">
+        <v>1282</v>
+      </c>
+      <c r="DF240" t="s">
+        <v>1389</v>
+      </c>
+      <c r="DG240">
+        <v>1</v>
+      </c>
+      <c r="DH240">
+        <v>1</v>
+      </c>
+      <c r="DI240">
+        <v>0</v>
+      </c>
+      <c r="DJ240">
+        <v>0</v>
+      </c>
+      <c r="DK240">
+        <v>0</v>
+      </c>
+      <c r="DM240" t="s">
+        <v>2012</v>
+      </c>
+      <c r="DN240" t="s">
+        <v>2013</v>
+      </c>
+      <c r="DO240" t="s">
+        <v>972</v>
+      </c>
+      <c r="DP240">
+        <v>1</v>
+      </c>
+      <c r="DQ240">
+        <v>0</v>
+      </c>
+      <c r="DR240">
+        <v>0</v>
+      </c>
+      <c r="DS240" t="s">
+        <v>1076</v>
+      </c>
+      <c r="DU240" t="s">
+        <v>2014</v>
+      </c>
+      <c r="DV240" t="s">
+        <v>2015</v>
+      </c>
+      <c r="DW240" t="s">
+        <v>1066</v>
+      </c>
+      <c r="EY240" s="1"/>
+      <c r="GQ240" s="1"/>
+      <c r="GR240" s="1"/>
+      <c r="GY240" s="1"/>
+      <c r="GZ240" s="1"/>
+      <c r="HA240" s="1"/>
+      <c r="HB240" s="1"/>
+      <c r="IQ240" s="1">
+        <v>884649140</v>
+      </c>
+      <c r="IR240" t="s">
+        <v>2016</v>
+      </c>
+      <c r="IS240" s="1">
+        <v>46297.783425925933</v>
+      </c>
+      <c r="IU240" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW240" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX240" t="s">
+        <v>2017</v>
+      </c>
+      <c r="IY240">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="241" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A241" s="1">
+        <v>46296.555081018523</v>
+      </c>
+      <c r="B241" s="1">
+        <v>46298.436994710653</v>
+      </c>
+      <c r="C241" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D241" t="s">
+        <v>683</v>
+      </c>
+      <c r="E241" t="s">
+        <v>306</v>
+      </c>
+      <c r="F241" t="s">
+        <v>586</v>
+      </c>
+      <c r="G241" t="s">
+        <v>198</v>
+      </c>
+      <c r="H241" t="s">
+        <v>308</v>
+      </c>
+      <c r="AX241" t="s">
+        <v>2018</v>
+      </c>
+      <c r="AY241" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ241" t="s">
+        <v>1824</v>
+      </c>
+      <c r="BA241" t="s">
+        <v>2019</v>
+      </c>
+      <c r="BB241">
+        <v>2</v>
+      </c>
+      <c r="BC241">
+        <v>5</v>
+      </c>
+      <c r="BD241" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE241" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF241" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG241" t="s">
+        <v>2020</v>
+      </c>
+      <c r="BH241" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI241" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ241" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK241">
+        <v>4</v>
+      </c>
+      <c r="BL241" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM241">
+        <v>4</v>
+      </c>
+      <c r="BN241">
+        <v>6</v>
+      </c>
+      <c r="BO241" t="s">
+        <v>324</v>
+      </c>
+      <c r="BP241" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ241" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS241" t="s">
+        <v>2021</v>
+      </c>
+      <c r="BT241" t="s">
+        <v>2022</v>
+      </c>
+      <c r="BU241" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW241" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX241" t="s">
+        <v>2023</v>
+      </c>
+      <c r="EY241" s="1"/>
+      <c r="GQ241" s="1"/>
+      <c r="GR241" s="1"/>
+      <c r="GY241" s="1"/>
+      <c r="GZ241" s="1"/>
+      <c r="HA241" s="1"/>
+      <c r="HB241" s="1"/>
+      <c r="IQ241" s="1">
+        <v>884864655</v>
+      </c>
+      <c r="IR241" t="s">
+        <v>2024</v>
+      </c>
+      <c r="IS241" s="1">
+        <v>46298.312025462961</v>
+      </c>
+      <c r="IU241" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW241" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX241" t="s">
+        <v>2025</v>
+      </c>
+      <c r="IY241">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="242" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A242" s="1">
+        <v>46298.436995810189</v>
+      </c>
+      <c r="B242" s="1">
+        <v>46298.477971215281</v>
+      </c>
+      <c r="C242" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D242" t="s">
+        <v>684</v>
+      </c>
+      <c r="E242" t="s">
+        <v>306</v>
+      </c>
+      <c r="F242" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G242" t="s">
+        <v>198</v>
+      </c>
+      <c r="H242" t="s">
+        <v>308</v>
+      </c>
+      <c r="J242" t="s">
+        <v>2026</v>
+      </c>
+      <c r="K242" t="s">
+        <v>201</v>
+      </c>
+      <c r="L242" t="s">
+        <v>321</v>
+      </c>
+      <c r="M242" t="s">
+        <v>605</v>
+      </c>
+      <c r="N242" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O242" t="s">
+        <v>321</v>
+      </c>
+      <c r="AH242">
+        <v>780</v>
+      </c>
+      <c r="AI242">
+        <v>388</v>
+      </c>
+      <c r="AJ242">
+        <v>398</v>
+      </c>
+      <c r="AK242">
+        <v>10</v>
+      </c>
+      <c r="AL242">
+        <v>2</v>
+      </c>
+      <c r="AM242">
+        <v>70</v>
+      </c>
+      <c r="AN242">
+        <v>0</v>
+      </c>
+      <c r="AO242" t="s">
+        <v>2027</v>
+      </c>
+      <c r="AP242">
+        <v>5</v>
+      </c>
+      <c r="AQ242" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR242" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS242" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT242" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU242" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV242" t="s">
+        <v>231</v>
+      </c>
+      <c r="AW242" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS242" t="s">
+        <v>2028</v>
+      </c>
+      <c r="BT242" t="s">
+        <v>2029</v>
+      </c>
+      <c r="BU242" t="s">
+        <v>1670</v>
+      </c>
+      <c r="BW242" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX242" t="s">
+        <v>2030</v>
+      </c>
+      <c r="EY242" s="1"/>
+      <c r="GQ242" s="1"/>
+      <c r="GR242" s="1"/>
+      <c r="GY242" s="1"/>
+      <c r="GZ242" s="1"/>
+      <c r="HA242" s="1"/>
+      <c r="HB242" s="1"/>
+      <c r="IQ242" s="1">
+        <v>884891716</v>
+      </c>
+      <c r="IR242" t="s">
+        <v>2031</v>
+      </c>
+      <c r="IS242" s="1">
+        <v>46298.352986111109</v>
+      </c>
+      <c r="IU242" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW242" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX242" t="s">
+        <v>2032</v>
+      </c>
+      <c r="IY242">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="243" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A243" s="1">
+        <v>46294.744592546303</v>
+      </c>
+      <c r="B243" s="1">
+        <v>46298.49458979167</v>
+      </c>
+      <c r="C243" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D243" t="s">
+        <v>351</v>
+      </c>
+      <c r="E243" t="s">
+        <v>210</v>
+      </c>
+      <c r="F243" t="s">
+        <v>2033</v>
+      </c>
+      <c r="G243" t="s">
+        <v>198</v>
+      </c>
+      <c r="H243" t="s">
+        <v>308</v>
+      </c>
+      <c r="BS243" t="s">
+        <v>605</v>
+      </c>
+      <c r="BT243" t="s">
+        <v>507</v>
+      </c>
+      <c r="BU243" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV243" t="s">
+        <v>2034</v>
+      </c>
+      <c r="BW243" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX243" t="s">
+        <v>2035</v>
+      </c>
+      <c r="BY243" t="s">
+        <v>356</v>
+      </c>
+      <c r="CB243" t="s">
+        <v>401</v>
+      </c>
+      <c r="CC243">
+        <v>2</v>
+      </c>
+      <c r="CD243">
+        <v>780</v>
+      </c>
+      <c r="CE243" t="s">
+        <v>358</v>
+      </c>
+      <c r="CF243" t="s">
+        <v>2036</v>
+      </c>
+      <c r="CG243" t="s">
+        <v>360</v>
+      </c>
+      <c r="CH243" t="s">
+        <v>2037</v>
+      </c>
+      <c r="CI243" t="s">
+        <v>455</v>
+      </c>
+      <c r="CK243" t="s">
+        <v>363</v>
+      </c>
+      <c r="CL243" t="s">
+        <v>2038</v>
+      </c>
+      <c r="CM243" t="s">
+        <v>457</v>
+      </c>
+      <c r="CN243" t="s">
+        <v>2039</v>
+      </c>
+      <c r="EY243" s="1"/>
+      <c r="GQ243" s="1"/>
+      <c r="GR243" s="1"/>
+      <c r="GY243" s="1"/>
+      <c r="GZ243" s="1"/>
+      <c r="HA243" s="1"/>
+      <c r="HB243" s="1"/>
+      <c r="IQ243" s="1">
+        <v>884902960</v>
+      </c>
+      <c r="IR243" t="s">
+        <v>2040</v>
+      </c>
+      <c r="IS243" s="1">
+        <v>46298.369606481479</v>
+      </c>
+      <c r="IU243" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW243" t="s">
+        <v>1593</v>
+      </c>
+      <c r="IX243" t="s">
+        <v>2041</v>
+      </c>
+      <c r="IY243">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="244" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A244" s="1">
+        <v>46298.477973055553</v>
+      </c>
+      <c r="B244" s="1">
+        <v>46298.51031474537</v>
+      </c>
+      <c r="C244" s="1">
+        <v>46268</v>
+      </c>
+      <c r="D244" t="s">
+        <v>684</v>
+      </c>
+      <c r="E244" t="s">
+        <v>306</v>
+      </c>
+      <c r="F244" t="s">
+        <v>586</v>
+      </c>
+      <c r="G244" t="s">
+        <v>198</v>
+      </c>
+      <c r="H244" t="s">
+        <v>308</v>
+      </c>
+      <c r="J244" t="s">
+        <v>2042</v>
+      </c>
+      <c r="K244" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L244" t="s">
+        <v>321</v>
+      </c>
+      <c r="M244" t="s">
+        <v>605</v>
+      </c>
+      <c r="N244" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O244" t="s">
+        <v>1666</v>
+      </c>
+      <c r="P244" t="s">
+        <v>2043</v>
+      </c>
+      <c r="AH244">
+        <v>1028</v>
+      </c>
+      <c r="AI244">
+        <v>246</v>
+      </c>
+      <c r="AJ244">
+        <v>268</v>
+      </c>
+      <c r="AK244">
+        <v>10</v>
+      </c>
+      <c r="AL244">
+        <v>2</v>
+      </c>
+      <c r="AM244">
+        <v>70</v>
+      </c>
+      <c r="AN244">
+        <v>0</v>
+      </c>
+      <c r="AO244" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AP244">
+        <v>2</v>
+      </c>
+      <c r="AQ244" t="s">
+        <v>2044</v>
+      </c>
+      <c r="AR244" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS244" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT244" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU244" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV244" t="s">
+        <v>204</v>
+      </c>
+      <c r="AW244" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS244" t="s">
+        <v>2045</v>
+      </c>
+      <c r="BT244" t="s">
+        <v>2046</v>
+      </c>
+      <c r="BU244" t="s">
+        <v>1670</v>
+      </c>
+      <c r="BW244" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX244" t="s">
+        <v>2047</v>
+      </c>
+      <c r="EY244" s="1"/>
+      <c r="GQ244" s="1"/>
+      <c r="GR244" s="1"/>
+      <c r="GY244" s="1"/>
+      <c r="GZ244" s="1"/>
+      <c r="HA244" s="1"/>
+      <c r="HB244" s="1"/>
+      <c r="IQ244" s="1">
+        <v>884912356</v>
+      </c>
+      <c r="IR244" t="s">
+        <v>2048</v>
+      </c>
+      <c r="IS244" s="1">
+        <v>46298.385358796288</v>
+      </c>
+      <c r="IU244" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW244" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX244" t="s">
+        <v>2049</v>
+      </c>
+      <c r="IY244">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="245" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A245" s="1">
+        <v>46298.510316689812</v>
+      </c>
+      <c r="B245" s="1">
+        <v>46298.534484548611</v>
+      </c>
+      <c r="C245" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D245" t="s">
+        <v>683</v>
+      </c>
+      <c r="E245" t="s">
+        <v>306</v>
+      </c>
+      <c r="F245" t="s">
+        <v>2050</v>
+      </c>
+      <c r="G245" t="s">
+        <v>198</v>
+      </c>
+      <c r="H245" t="s">
+        <v>308</v>
+      </c>
+      <c r="AX245" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AY245" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ245" t="s">
+        <v>1710</v>
+      </c>
+      <c r="BA245" t="s">
+        <v>2051</v>
+      </c>
+      <c r="BB245">
+        <v>10</v>
+      </c>
+      <c r="BC245">
+        <v>25</v>
+      </c>
+      <c r="BD245" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE245" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF245" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG245" t="s">
+        <v>2052</v>
+      </c>
+      <c r="BH245" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI245" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ245" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK245">
+        <v>2</v>
+      </c>
+      <c r="BL245" t="s">
+        <v>1622</v>
+      </c>
+      <c r="BM245">
+        <v>0</v>
+      </c>
+      <c r="BN245">
+        <v>0</v>
+      </c>
+      <c r="BO245" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BP245" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BQ245" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS245" t="s">
+        <v>2053</v>
+      </c>
+      <c r="BT245" t="s">
+        <v>2054</v>
+      </c>
+      <c r="BU245" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV245" t="s">
+        <v>2055</v>
+      </c>
+      <c r="BW245" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX245" t="s">
+        <v>2056</v>
+      </c>
+      <c r="EY245" s="1"/>
+      <c r="GQ245" s="1"/>
+      <c r="GR245" s="1"/>
+      <c r="GY245" s="1"/>
+      <c r="GZ245" s="1"/>
+      <c r="HA245" s="1"/>
+      <c r="HB245" s="1"/>
+      <c r="IQ245" s="1">
+        <v>884927780</v>
+      </c>
+      <c r="IR245" t="s">
+        <v>2057</v>
+      </c>
+      <c r="IS245" s="1">
+        <v>46298.409502314818</v>
+      </c>
+      <c r="IU245" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW245" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX245" t="s">
+        <v>2058</v>
+      </c>
+      <c r="IY245">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="246" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A246" s="1">
+        <v>46298.534485775461</v>
+      </c>
+      <c r="B246" s="1">
+        <v>46298.551648287037</v>
+      </c>
+      <c r="C246" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D246" t="s">
+        <v>351</v>
+      </c>
+      <c r="E246" t="s">
+        <v>306</v>
+      </c>
+      <c r="F246" t="s">
+        <v>2059</v>
+      </c>
+      <c r="G246" t="s">
+        <v>198</v>
+      </c>
+      <c r="H246" t="s">
+        <v>308</v>
+      </c>
+      <c r="BS246" t="s">
+        <v>2060</v>
+      </c>
+      <c r="BT246" t="s">
+        <v>2061</v>
+      </c>
+      <c r="BU246" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV246" t="s">
+        <v>2062</v>
+      </c>
+      <c r="BW246" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX246" t="s">
+        <v>2063</v>
+      </c>
+      <c r="BY246" t="s">
+        <v>356</v>
+      </c>
+      <c r="CB246" t="s">
+        <v>508</v>
+      </c>
+      <c r="CC246">
+        <v>0</v>
+      </c>
+      <c r="CD246">
+        <v>400</v>
+      </c>
+      <c r="CE246" t="s">
+        <v>358</v>
+      </c>
+      <c r="CF246" t="s">
+        <v>2064</v>
+      </c>
+      <c r="CG246" t="s">
+        <v>389</v>
+      </c>
+      <c r="CH246" t="s">
+        <v>2065</v>
+      </c>
+      <c r="CI246" t="s">
+        <v>455</v>
+      </c>
+      <c r="CK246" t="s">
+        <v>512</v>
+      </c>
+      <c r="CL246" t="s">
+        <v>2066</v>
+      </c>
+      <c r="CM246" t="s">
+        <v>574</v>
+      </c>
+      <c r="CN246" t="s">
+        <v>2067</v>
+      </c>
+      <c r="EY246" s="1"/>
+      <c r="GQ246" s="1"/>
+      <c r="GR246" s="1"/>
+      <c r="GY246" s="1"/>
+      <c r="GZ246" s="1"/>
+      <c r="HA246" s="1"/>
+      <c r="HB246" s="1"/>
+      <c r="IQ246" s="1">
+        <v>884940073</v>
+      </c>
+      <c r="IR246" t="s">
+        <v>2068</v>
+      </c>
+      <c r="IS246" s="1">
+        <v>46298.426678240743</v>
+      </c>
+      <c r="IU246" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW246" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX246" t="s">
+        <v>2069</v>
+      </c>
+      <c r="IY246">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="247" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A247" s="1">
+        <v>46298.551648703702</v>
+      </c>
+      <c r="B247" s="1">
+        <v>46298.564663217592</v>
+      </c>
+      <c r="C247" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D247" t="s">
+        <v>769</v>
+      </c>
+      <c r="E247" t="s">
+        <v>306</v>
+      </c>
+      <c r="F247" t="s">
+        <v>2059</v>
+      </c>
+      <c r="G247" t="s">
+        <v>198</v>
+      </c>
+      <c r="H247" t="s">
+        <v>308</v>
+      </c>
+      <c r="BS247" t="s">
+        <v>2060</v>
+      </c>
+      <c r="BT247" t="s">
+        <v>2070</v>
+      </c>
+      <c r="BU247" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV247" t="s">
+        <v>2062</v>
+      </c>
+      <c r="BW247" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX247" t="s">
+        <v>2071</v>
+      </c>
+      <c r="EY247" s="1"/>
+      <c r="GJ247" s="1">
+        <v>46296</v>
+      </c>
+      <c r="GK247" t="s">
+        <v>980</v>
+      </c>
+      <c r="GL247" t="s">
+        <v>373</v>
+      </c>
+      <c r="GN247">
+        <v>270</v>
+      </c>
+      <c r="GO247">
+        <v>230</v>
+      </c>
+      <c r="GP247">
+        <v>6</v>
+      </c>
+      <c r="GQ247" s="1">
+        <v>4</v>
+      </c>
+      <c r="GR247" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="GT247" t="s">
+        <v>374</v>
+      </c>
+      <c r="GU247" t="s">
+        <v>375</v>
+      </c>
+      <c r="GV247" t="s">
+        <v>376</v>
+      </c>
+      <c r="GX247" t="s">
+        <v>580</v>
+      </c>
+      <c r="GY247" s="1">
+        <v>0</v>
+      </c>
+      <c r="GZ247" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="HA247" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="HB247" s="1">
+        <v>6</v>
+      </c>
+      <c r="HC247">
+        <v>6</v>
+      </c>
+      <c r="HD247" t="s">
+        <v>380</v>
+      </c>
+      <c r="HE247" t="s">
+        <v>381</v>
+      </c>
+      <c r="HF247" t="s">
+        <v>448</v>
+      </c>
+      <c r="HG247">
+        <v>0</v>
+      </c>
+      <c r="HH247">
+        <v>0</v>
+      </c>
+      <c r="HI247">
+        <v>0</v>
+      </c>
+      <c r="HJ247">
+        <v>1</v>
+      </c>
+      <c r="HK247" t="s">
+        <v>321</v>
+      </c>
+      <c r="HM247">
+        <v>6</v>
+      </c>
+      <c r="HN247">
+        <v>4</v>
+      </c>
+      <c r="HO247">
+        <v>5</v>
+      </c>
+      <c r="HP247">
+        <v>5</v>
+      </c>
+      <c r="HQ247">
+        <v>5</v>
+      </c>
+      <c r="HR247">
+        <v>0</v>
+      </c>
+      <c r="IQ247" s="1">
+        <v>884949698</v>
+      </c>
+      <c r="IR247" t="s">
+        <v>2072</v>
+      </c>
+      <c r="IS247" s="1">
+        <v>46298.439675925933</v>
+      </c>
+      <c r="IU247" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW247" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX247" t="s">
+        <v>2073</v>
+      </c>
+      <c r="IY247">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="248" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A248" s="1">
+        <v>46298.56466358796</v>
+      </c>
+      <c r="B248" s="1">
+        <v>46298.582582962961</v>
+      </c>
+      <c r="C248" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D248" t="s">
+        <v>684</v>
+      </c>
+      <c r="E248" t="s">
+        <v>306</v>
+      </c>
+      <c r="F248" t="s">
+        <v>2074</v>
+      </c>
+      <c r="G248" t="s">
+        <v>198</v>
+      </c>
+      <c r="H248" t="s">
+        <v>308</v>
+      </c>
+      <c r="J248" t="s">
+        <v>980</v>
+      </c>
+      <c r="K248" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L248" t="s">
+        <v>321</v>
+      </c>
+      <c r="M248" t="s">
+        <v>605</v>
+      </c>
+      <c r="N248" t="s">
+        <v>1702</v>
+      </c>
+      <c r="O248" t="s">
+        <v>1666</v>
+      </c>
+      <c r="P248" t="s">
+        <v>1695</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>2075</v>
+      </c>
+      <c r="AH248">
+        <v>400</v>
+      </c>
+      <c r="AI248">
+        <v>199</v>
+      </c>
+      <c r="AJ248">
+        <v>201</v>
+      </c>
+      <c r="AK248">
+        <v>1</v>
+      </c>
+      <c r="AL248">
+        <v>2</v>
+      </c>
+      <c r="AM248">
+        <v>70</v>
+      </c>
+      <c r="AN248">
+        <v>0</v>
+      </c>
+      <c r="AO248" t="s">
+        <v>2027</v>
+      </c>
+      <c r="AP248">
+        <v>6</v>
+      </c>
+      <c r="AQ248" t="s">
+        <v>2044</v>
+      </c>
+      <c r="AR248" t="s">
+        <v>310</v>
+      </c>
+      <c r="AS248" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT248" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU248" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV248" t="s">
+        <v>204</v>
+      </c>
+      <c r="AW248" t="s">
+        <v>227</v>
+      </c>
+      <c r="BS248" t="s">
+        <v>2076</v>
+      </c>
+      <c r="BT248" t="s">
+        <v>2077</v>
+      </c>
+      <c r="BU248" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW248" t="s">
+        <v>354</v>
+      </c>
+      <c r="BX248" t="s">
+        <v>2078</v>
+      </c>
+      <c r="EY248" s="1"/>
+      <c r="GQ248" s="1"/>
+      <c r="GR248" s="1"/>
+      <c r="GY248" s="1"/>
+      <c r="GZ248" s="1"/>
+      <c r="HA248" s="1"/>
+      <c r="HB248" s="1"/>
+      <c r="IQ248" s="1">
+        <v>884963193</v>
+      </c>
+      <c r="IR248" t="s">
+        <v>2079</v>
+      </c>
+      <c r="IS248" s="1">
+        <v>46298.457604166673</v>
+      </c>
+      <c r="IU248" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW248" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX248" t="s">
+        <v>2080</v>
+      </c>
+      <c r="IY248">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="249" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A249" s="1">
+        <v>46298.60764490741</v>
+      </c>
+      <c r="B249" s="1">
+        <v>46298.613121620372</v>
+      </c>
+      <c r="C249" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D249" t="s">
+        <v>879</v>
+      </c>
+      <c r="E249" t="s">
+        <v>210</v>
+      </c>
+      <c r="F249" t="s">
+        <v>963</v>
+      </c>
+      <c r="G249" t="s">
+        <v>198</v>
+      </c>
+      <c r="H249" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS249" t="s">
+        <v>2081</v>
+      </c>
+      <c r="BT249" t="s">
+        <v>947</v>
+      </c>
+      <c r="BW249" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX249" t="s">
+        <v>1195</v>
+      </c>
+      <c r="BY249" t="s">
+        <v>923</v>
+      </c>
+      <c r="CP249" t="s">
+        <v>1211</v>
+      </c>
+      <c r="CQ249" t="s">
+        <v>2082</v>
+      </c>
+      <c r="CR249" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS249" t="s">
+        <v>896</v>
+      </c>
+      <c r="CT249" t="s">
+        <v>897</v>
+      </c>
+      <c r="CU249">
+        <v>0</v>
+      </c>
+      <c r="CV249">
+        <v>0</v>
+      </c>
+      <c r="CW249">
+        <v>1</v>
+      </c>
+      <c r="CX249">
+        <v>0</v>
+      </c>
+      <c r="CY249">
+        <v>0</v>
+      </c>
+      <c r="CZ249">
+        <v>0</v>
+      </c>
+      <c r="DA249">
+        <v>0</v>
+      </c>
+      <c r="DC249" t="s">
+        <v>898</v>
+      </c>
+      <c r="EY249" s="1"/>
+      <c r="GQ249" s="1"/>
+      <c r="GR249" s="1"/>
+      <c r="GY249" s="1"/>
+      <c r="GZ249" s="1"/>
+      <c r="HA249" s="1"/>
+      <c r="HB249" s="1"/>
+      <c r="IC249" t="s">
+        <v>223</v>
+      </c>
+      <c r="IQ249" s="1">
+        <v>884984347</v>
+      </c>
+      <c r="IR249" t="s">
+        <v>2083</v>
+      </c>
+      <c r="IS249" s="1">
+        <v>46298.48814814815</v>
+      </c>
+      <c r="IU249" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW249" t="s">
+        <v>699</v>
+      </c>
+      <c r="IX249" t="s">
+        <v>2084</v>
+      </c>
+      <c r="IY249">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="250" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A250" s="1">
+        <v>46298.613122175928</v>
+      </c>
+      <c r="B250" s="1">
+        <v>46298.61480505787</v>
+      </c>
+      <c r="C250" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D250" t="s">
+        <v>879</v>
+      </c>
+      <c r="E250" t="s">
+        <v>210</v>
+      </c>
+      <c r="F250" t="s">
+        <v>963</v>
+      </c>
+      <c r="G250" t="s">
+        <v>198</v>
+      </c>
+      <c r="H250" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS250" t="s">
+        <v>2085</v>
+      </c>
+      <c r="BT250" t="s">
+        <v>947</v>
+      </c>
+      <c r="BW250" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX250" t="s">
+        <v>1195</v>
+      </c>
+      <c r="BY250" t="s">
+        <v>923</v>
+      </c>
+      <c r="CP250" t="s">
+        <v>893</v>
+      </c>
+      <c r="CQ250" t="s">
+        <v>2086</v>
+      </c>
+      <c r="CR250" t="s">
+        <v>895</v>
+      </c>
+      <c r="CS250" t="s">
+        <v>896</v>
+      </c>
+      <c r="CT250" t="s">
+        <v>905</v>
+      </c>
+      <c r="CU250">
+        <v>0</v>
+      </c>
+      <c r="CV250">
+        <v>1</v>
+      </c>
+      <c r="CW250">
+        <v>0</v>
+      </c>
+      <c r="CX250">
+        <v>0</v>
+      </c>
+      <c r="CY250">
+        <v>0</v>
+      </c>
+      <c r="CZ250">
+        <v>0</v>
+      </c>
+      <c r="DA250">
+        <v>0</v>
+      </c>
+      <c r="DC250" t="s">
+        <v>885</v>
+      </c>
+      <c r="EY250" s="1"/>
+      <c r="GQ250" s="1"/>
+      <c r="GR250" s="1"/>
+      <c r="GY250" s="1"/>
+      <c r="GZ250" s="1"/>
+      <c r="HA250" s="1"/>
+      <c r="HB250" s="1"/>
+      <c r="IC250" t="s">
+        <v>223</v>
+      </c>
+      <c r="IQ250" s="1">
+        <v>884986316</v>
+      </c>
+      <c r="IR250" t="s">
+        <v>2087</v>
+      </c>
+      <c r="IS250" s="1">
+        <v>46298.489814814813</v>
+      </c>
+      <c r="IU250" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW250" t="s">
+        <v>699</v>
+      </c>
+      <c r="IX250" t="s">
+        <v>2088</v>
+      </c>
+      <c r="IY250">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06CD88B6-0E2B-F54F-8399-8959E82628C4}"/>
+  <xr:revisionPtr revIDLastSave="374" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7F44CA1-97BA-9A4C-8747-7CFFBCEF895E}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="900" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6052" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6209" uniqueCount="2130">
   <si>
     <t>start</t>
   </si>
@@ -6304,6 +6304,129 @@
   </si>
   <si>
     <t>uuid:3bb96029-cd2d-4916-badc-1c6a84e22ecd</t>
+  </si>
+  <si>
+    <t>Tool 4: most significant change story collection form</t>
+  </si>
+  <si>
+    <t>Kazo</t>
+  </si>
+  <si>
+    <t>Ebola can't come back.</t>
+  </si>
+  <si>
+    <t>Washing hands regularly</t>
+  </si>
+  <si>
+    <t>We had stopped washing our hands because we thought the was gone and no more in the country.</t>
+  </si>
+  <si>
+    <t>The U-reporters came to us as youths and sensitized the need to always wash our hands with soap and water.</t>
+  </si>
+  <si>
+    <t>Most of the community members currently know the signs and symptoms of outbreaks that have been with in us.</t>
+  </si>
+  <si>
+    <t>Because even after the government announced Uganda as an Ebola free country, The U-reporters and VHTs have always moved to our homes to encourage us to always wash our hand but also reminded us the signs and symptoms.</t>
+  </si>
+  <si>
+    <t>39e5e4d9-f5ba-4ad1-a2ef-873a527cc80f</t>
+  </si>
+  <si>
+    <t>uuid:39e5e4d9-f5ba-4ad1-a2ef-873a527cc80f</t>
+  </si>
+  <si>
+    <t>Resturant owner</t>
+  </si>
+  <si>
+    <t>Ensure functionality of handwashing facilities</t>
+  </si>
+  <si>
+    <t>How does Ebola spread from animals to Humans</t>
+  </si>
+  <si>
+    <t>Alot of miss information from the public</t>
+  </si>
+  <si>
+    <t>More village sensitization programs should be carried out</t>
+  </si>
+  <si>
+    <t>461dc488-4752-4b20-ad0a-54293b066eb0</t>
+  </si>
+  <si>
+    <t>uuid:461dc488-4752-4b20-ad0a-54293b066eb0</t>
+  </si>
+  <si>
+    <t>Already shared</t>
+  </si>
+  <si>
+    <t>Yes — all steps followed</t>
+  </si>
+  <si>
+    <t>Tuesday Thursday</t>
+  </si>
+  <si>
+    <t>Since ebola is not in the country right, that means we are not at risk</t>
+  </si>
+  <si>
+    <t>More sensitization in the school</t>
+  </si>
+  <si>
+    <t>b3f041d0-65b8-4385-85a9-4cf1f1a88cb5</t>
+  </si>
+  <si>
+    <t>uuid:b3f041d0-65b8-4385-85a9-4cf1f1a88cb5</t>
+  </si>
+  <si>
+    <t>Market commite</t>
+  </si>
+  <si>
+    <t>They committed to report to MOH any person suspected to have signs of Ebola</t>
+  </si>
+  <si>
+    <t>Some times the government gives wrong figures.</t>
+  </si>
+  <si>
+    <t>More sensitization needed in the area.</t>
+  </si>
+  <si>
+    <t>64b1850c-b8a5-4dd6-ae7c-1ea0369e1d19</t>
+  </si>
+  <si>
+    <t>uuid:64b1850c-b8a5-4dd6-ae7c-1ea0369e1d19</t>
+  </si>
+  <si>
+    <t>More sensitization needed in the lower section</t>
+  </si>
+  <si>
+    <t>Before the intervention in this school, the school had less functional hand washing facilities, and was not having soap. The school didn't have an activity school health club. It only had unless than 15 members. The pupils had very less knowledge on PHE .</t>
+  </si>
+  <si>
+    <t>With the introduction of the snakes and ladders game,the Knowledge wheel sessions, these have helped the learners to understand well the PHE sign and symptoms and where to report Incase of any suspect.</t>
+  </si>
+  <si>
+    <t>The school currently has enough hand washing facilities around the school.</t>
+  </si>
+  <si>
+    <t>This is because currently all the students are encouraged to was their hands, the health club report any pupil who is seen not washing their hands.</t>
+  </si>
+  <si>
+    <t>7a2d0cb9-ca50-4c82-b593-3b92cc3526c4</t>
+  </si>
+  <si>
+    <t>uuid:7a2d0cb9-ca50-4c82-b593-3b92cc3526c4</t>
+  </si>
+  <si>
+    <t>They are going to put hand washing equipment at the stage</t>
+  </si>
+  <si>
+    <t>Fellow boda boda riders</t>
+  </si>
+  <si>
+    <t>7142423b-9e74-4959-8dca-0b6c1c39bd35</t>
+  </si>
+  <si>
+    <t>uuid:7142423b-9e74-4959-8dca-0b6c1c39bd35</t>
   </si>
 </sst>
 </file>
@@ -20708,8 +20831,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY250" totalsRowShown="0">
-  <autoFilter ref="A1:IY250" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY256" totalsRowShown="0">
+  <autoFilter ref="A1:IY256" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -21262,7 +21385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY250"/>
+  <dimension ref="A1:IY256"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -50158,6 +50281,747 @@
         <v>251</v>
       </c>
     </row>
+    <row r="251" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A251" s="1">
+        <v>46300.650030763893</v>
+      </c>
+      <c r="B251" s="1">
+        <v>46300.65832422454</v>
+      </c>
+      <c r="C251" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D251" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E251" t="s">
+        <v>210</v>
+      </c>
+      <c r="F251" t="s">
+        <v>2090</v>
+      </c>
+      <c r="G251" t="s">
+        <v>198</v>
+      </c>
+      <c r="H251" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS251" t="s">
+        <v>2091</v>
+      </c>
+      <c r="BT251" t="s">
+        <v>947</v>
+      </c>
+      <c r="BU251" t="s">
+        <v>1598</v>
+      </c>
+      <c r="BW251" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX251" t="s">
+        <v>2092</v>
+      </c>
+      <c r="BY251" t="s">
+        <v>558</v>
+      </c>
+      <c r="EK251" t="s">
+        <v>2093</v>
+      </c>
+      <c r="EL251" t="s">
+        <v>2094</v>
+      </c>
+      <c r="EM251" t="s">
+        <v>2095</v>
+      </c>
+      <c r="EN251" t="s">
+        <v>2096</v>
+      </c>
+      <c r="EY251" s="1"/>
+      <c r="GQ251" s="1"/>
+      <c r="GR251" s="1"/>
+      <c r="GY251" s="1"/>
+      <c r="GZ251" s="1"/>
+      <c r="HA251" s="1"/>
+      <c r="HB251" s="1"/>
+      <c r="IQ251" s="1">
+        <v>886160807</v>
+      </c>
+      <c r="IR251" t="s">
+        <v>2097</v>
+      </c>
+      <c r="IS251" s="1">
+        <v>46300.53334490741</v>
+      </c>
+      <c r="IU251" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW251" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX251" t="s">
+        <v>2098</v>
+      </c>
+      <c r="IY251">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="252" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A252" s="1">
+        <v>46300.410002256947</v>
+      </c>
+      <c r="B252" s="1">
+        <v>46300.779925717587</v>
+      </c>
+      <c r="C252" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D252" t="s">
+        <v>683</v>
+      </c>
+      <c r="E252" t="s">
+        <v>251</v>
+      </c>
+      <c r="F252" t="s">
+        <v>758</v>
+      </c>
+      <c r="G252" t="s">
+        <v>198</v>
+      </c>
+      <c r="H252" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX252" t="s">
+        <v>1972</v>
+      </c>
+      <c r="AY252" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ252" t="s">
+        <v>1618</v>
+      </c>
+      <c r="BA252" t="s">
+        <v>2099</v>
+      </c>
+      <c r="BB252">
+        <v>10</v>
+      </c>
+      <c r="BC252">
+        <v>8</v>
+      </c>
+      <c r="BD252" t="s">
+        <v>321</v>
+      </c>
+      <c r="BE252" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF252" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG252" t="s">
+        <v>2100</v>
+      </c>
+      <c r="BH252" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI252" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ252" t="s">
+        <v>392</v>
+      </c>
+      <c r="BK252">
+        <v>5</v>
+      </c>
+      <c r="BL252" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM252">
+        <v>58</v>
+      </c>
+      <c r="BN252">
+        <v>89</v>
+      </c>
+      <c r="BO252" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BP252" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ252" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS252" t="s">
+        <v>2101</v>
+      </c>
+      <c r="BT252" t="s">
+        <v>2102</v>
+      </c>
+      <c r="BU252" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW252" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX252" t="s">
+        <v>2103</v>
+      </c>
+      <c r="EY252" s="1"/>
+      <c r="GQ252" s="1"/>
+      <c r="GR252" s="1"/>
+      <c r="GY252" s="1"/>
+      <c r="GZ252" s="1"/>
+      <c r="HA252" s="1"/>
+      <c r="HB252" s="1"/>
+      <c r="IQ252" s="1">
+        <v>886310872</v>
+      </c>
+      <c r="IR252" t="s">
+        <v>2104</v>
+      </c>
+      <c r="IS252" s="1">
+        <v>46300.654930555553</v>
+      </c>
+      <c r="IU252" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW252" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX252" t="s">
+        <v>2105</v>
+      </c>
+      <c r="IY252">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="253" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A253" s="1">
+        <v>46301.522519942133</v>
+      </c>
+      <c r="B253" s="1">
+        <v>46301.532062418977</v>
+      </c>
+      <c r="C253" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D253" t="s">
+        <v>684</v>
+      </c>
+      <c r="E253" t="s">
+        <v>210</v>
+      </c>
+      <c r="F253" t="s">
+        <v>272</v>
+      </c>
+      <c r="G253" t="s">
+        <v>198</v>
+      </c>
+      <c r="H253" t="s">
+        <v>212</v>
+      </c>
+      <c r="J253" t="s">
+        <v>495</v>
+      </c>
+      <c r="K253" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L253" t="s">
+        <v>2106</v>
+      </c>
+      <c r="M253" t="s">
+        <v>1694</v>
+      </c>
+      <c r="N253" t="s">
+        <v>1665</v>
+      </c>
+      <c r="O253" t="s">
+        <v>1807</v>
+      </c>
+      <c r="R253">
+        <v>16</v>
+      </c>
+      <c r="S253">
+        <v>14</v>
+      </c>
+      <c r="T253" t="s">
+        <v>2107</v>
+      </c>
+      <c r="U253" t="s">
+        <v>2108</v>
+      </c>
+      <c r="V253">
+        <v>0</v>
+      </c>
+      <c r="W253">
+        <v>1</v>
+      </c>
+      <c r="X253">
+        <v>0</v>
+      </c>
+      <c r="Y253">
+        <v>1</v>
+      </c>
+      <c r="Z253">
+        <v>0</v>
+      </c>
+      <c r="AA253">
+        <v>0</v>
+      </c>
+      <c r="AB253" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AC253">
+        <v>1</v>
+      </c>
+      <c r="AD253">
+        <v>0</v>
+      </c>
+      <c r="AE253">
+        <v>0</v>
+      </c>
+      <c r="AF253">
+        <v>0</v>
+      </c>
+      <c r="AG253">
+        <v>0</v>
+      </c>
+      <c r="AH253">
+        <v>520</v>
+      </c>
+      <c r="AI253">
+        <v>200</v>
+      </c>
+      <c r="AJ253">
+        <v>234</v>
+      </c>
+      <c r="AK253">
+        <v>3</v>
+      </c>
+      <c r="AL253">
+        <v>3</v>
+      </c>
+      <c r="AM253">
+        <v>60</v>
+      </c>
+      <c r="AN253">
+        <v>0</v>
+      </c>
+      <c r="AO253" t="s">
+        <v>1697</v>
+      </c>
+      <c r="AP253">
+        <v>6</v>
+      </c>
+      <c r="AQ253" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR253" t="s">
+        <v>310</v>
+      </c>
+      <c r="AS253" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT253" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU253" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV253" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW253" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS253" t="s">
+        <v>2109</v>
+      </c>
+      <c r="BT253" t="s">
+        <v>947</v>
+      </c>
+      <c r="BU253" t="s">
+        <v>1670</v>
+      </c>
+      <c r="BW253" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX253" t="s">
+        <v>2110</v>
+      </c>
+      <c r="EY253" s="1"/>
+      <c r="GQ253" s="1"/>
+      <c r="GR253" s="1"/>
+      <c r="GY253" s="1"/>
+      <c r="GZ253" s="1"/>
+      <c r="HA253" s="1"/>
+      <c r="HB253" s="1"/>
+      <c r="IQ253" s="1">
+        <v>886860356</v>
+      </c>
+      <c r="IR253" t="s">
+        <v>2111</v>
+      </c>
+      <c r="IS253" s="1">
+        <v>46301.408761574072</v>
+      </c>
+      <c r="IU253" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW253" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX253" t="s">
+        <v>2112</v>
+      </c>
+      <c r="IY253">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="254" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A254" s="1">
+        <v>46301.532065358799</v>
+      </c>
+      <c r="B254" s="1">
+        <v>46301.538736805553</v>
+      </c>
+      <c r="C254" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D254" t="s">
+        <v>683</v>
+      </c>
+      <c r="E254" t="s">
+        <v>210</v>
+      </c>
+      <c r="F254" t="s">
+        <v>272</v>
+      </c>
+      <c r="G254" t="s">
+        <v>198</v>
+      </c>
+      <c r="H254" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX254" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AY254" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ254" t="s">
+        <v>1824</v>
+      </c>
+      <c r="BA254" t="s">
+        <v>2113</v>
+      </c>
+      <c r="BB254">
+        <v>6</v>
+      </c>
+      <c r="BC254">
+        <v>4</v>
+      </c>
+      <c r="BD254" t="s">
+        <v>392</v>
+      </c>
+      <c r="BE254" t="s">
+        <v>321</v>
+      </c>
+      <c r="BF254" t="s">
+        <v>1620</v>
+      </c>
+      <c r="BG254" t="s">
+        <v>2114</v>
+      </c>
+      <c r="BH254" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI254" t="s">
+        <v>323</v>
+      </c>
+      <c r="BJ254" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK254">
+        <v>5</v>
+      </c>
+      <c r="BL254" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM254">
+        <v>300</v>
+      </c>
+      <c r="BN254">
+        <v>250</v>
+      </c>
+      <c r="BO254" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BP254" t="s">
+        <v>1714</v>
+      </c>
+      <c r="BQ254" t="s">
+        <v>1623</v>
+      </c>
+      <c r="BS254" t="s">
+        <v>2115</v>
+      </c>
+      <c r="BT254" t="s">
+        <v>947</v>
+      </c>
+      <c r="BU254" t="s">
+        <v>1631</v>
+      </c>
+      <c r="BW254" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX254" t="s">
+        <v>2116</v>
+      </c>
+      <c r="EY254" s="1"/>
+      <c r="GQ254" s="1"/>
+      <c r="GR254" s="1"/>
+      <c r="GY254" s="1"/>
+      <c r="GZ254" s="1"/>
+      <c r="HA254" s="1"/>
+      <c r="HB254" s="1"/>
+      <c r="IQ254" s="1">
+        <v>886876407</v>
+      </c>
+      <c r="IR254" t="s">
+        <v>2117</v>
+      </c>
+      <c r="IS254" s="1">
+        <v>46301.421956018523</v>
+      </c>
+      <c r="IU254" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW254" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX254" t="s">
+        <v>2118</v>
+      </c>
+      <c r="IY254">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="255" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A255" s="1">
+        <v>46301.538739317133</v>
+      </c>
+      <c r="B255" s="1">
+        <v>46301.546786574072</v>
+      </c>
+      <c r="C255" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D255" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E255" t="s">
+        <v>210</v>
+      </c>
+      <c r="F255" t="s">
+        <v>272</v>
+      </c>
+      <c r="G255" t="s">
+        <v>198</v>
+      </c>
+      <c r="H255" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS255" t="s">
+        <v>947</v>
+      </c>
+      <c r="BT255" t="s">
+        <v>947</v>
+      </c>
+      <c r="BU255" t="s">
+        <v>1670</v>
+      </c>
+      <c r="BW255" t="s">
+        <v>386</v>
+      </c>
+      <c r="BX255" t="s">
+        <v>2119</v>
+      </c>
+      <c r="BY255" t="s">
+        <v>356</v>
+      </c>
+      <c r="EK255" t="s">
+        <v>2120</v>
+      </c>
+      <c r="EL255" t="s">
+        <v>2121</v>
+      </c>
+      <c r="EM255" t="s">
+        <v>2122</v>
+      </c>
+      <c r="EN255" t="s">
+        <v>2123</v>
+      </c>
+      <c r="EY255" s="1"/>
+      <c r="GQ255" s="1"/>
+      <c r="GR255" s="1"/>
+      <c r="GY255" s="1"/>
+      <c r="GZ255" s="1"/>
+      <c r="HA255" s="1"/>
+      <c r="HB255" s="1"/>
+      <c r="IQ255" s="1">
+        <v>886876415</v>
+      </c>
+      <c r="IR255" t="s">
+        <v>2124</v>
+      </c>
+      <c r="IS255" s="1">
+        <v>46301.421967592592</v>
+      </c>
+      <c r="IU255" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW255" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX255" t="s">
+        <v>2125</v>
+      </c>
+      <c r="IY255">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="256" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A256" s="1">
+        <v>46301.478870706022</v>
+      </c>
+      <c r="B256" s="1">
+        <v>46301.674378379626</v>
+      </c>
+      <c r="C256" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D256" t="s">
+        <v>683</v>
+      </c>
+      <c r="E256" t="s">
+        <v>196</v>
+      </c>
+      <c r="F256" t="s">
+        <v>770</v>
+      </c>
+      <c r="G256" t="s">
+        <v>198</v>
+      </c>
+      <c r="H256" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX256" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AY256" t="s">
+        <v>802</v>
+      </c>
+      <c r="AZ256" t="s">
+        <v>1618</v>
+      </c>
+      <c r="BA256" t="s">
+        <v>2003</v>
+      </c>
+      <c r="BB256">
+        <v>40</v>
+      </c>
+      <c r="BC256">
+        <v>3</v>
+      </c>
+      <c r="BD256" t="s">
+        <v>392</v>
+      </c>
+      <c r="BE256" t="s">
+        <v>392</v>
+      </c>
+      <c r="BF256" t="s">
+        <v>1620</v>
+      </c>
+      <c r="BG256" t="s">
+        <v>2126</v>
+      </c>
+      <c r="BH256" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI256" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ256" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK256">
+        <v>4</v>
+      </c>
+      <c r="BL256" t="s">
+        <v>1713</v>
+      </c>
+      <c r="BM256">
+        <v>15</v>
+      </c>
+      <c r="BN256">
+        <v>30</v>
+      </c>
+      <c r="BO256" t="s">
+        <v>324</v>
+      </c>
+      <c r="BP256" t="s">
+        <v>324</v>
+      </c>
+      <c r="BQ256" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS256" t="s">
+        <v>1115</v>
+      </c>
+      <c r="BT256" t="s">
+        <v>1630</v>
+      </c>
+      <c r="BU256" t="s">
+        <v>802</v>
+      </c>
+      <c r="BV256" t="s">
+        <v>2127</v>
+      </c>
+      <c r="BW256" t="s">
+        <v>443</v>
+      </c>
+      <c r="BX256" t="s">
+        <v>1128</v>
+      </c>
+      <c r="EY256" s="1"/>
+      <c r="GQ256" s="1"/>
+      <c r="GR256" s="1"/>
+      <c r="GY256" s="1"/>
+      <c r="GZ256" s="1"/>
+      <c r="HA256" s="1"/>
+      <c r="HB256" s="1"/>
+      <c r="IQ256" s="1">
+        <v>887049943</v>
+      </c>
+      <c r="IR256" t="s">
+        <v>2128</v>
+      </c>
+      <c r="IS256" s="1">
+        <v>46301.549386574072</v>
+      </c>
+      <c r="IU256" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW256" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IX256" t="s">
+        <v>2129</v>
+      </c>
+      <c r="IY256">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBFBFA7B-B646-2D40-8876-E6275C4D9F6F}"/>
+  <xr:revisionPtr revIDLastSave="377" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{868EC490-CBCF-2C45-81EB-2BC9B17CD40F}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="1500" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="5" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4972" uniqueCount="1786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6444" uniqueCount="2188">
   <si>
     <t>start</t>
   </si>
@@ -5395,6 +5395,1212 @@
   </si>
   <si>
     <t>Demonstrate how to wash your hands properly using running water and soap.23</t>
+  </si>
+  <si>
+    <t>Greenland Islamic Secondary school</t>
+  </si>
+  <si>
+    <t>Dedicated &amp; ventilated room</t>
+  </si>
+  <si>
+    <t>How many Ebola viruses are in Uganda ?</t>
+  </si>
+  <si>
+    <t>edb547f0-2b31-425c-9ceb-1aa336f4becb</t>
+  </si>
+  <si>
+    <t>uuid:edb547f0-2b31-425c-9ceb-1aa336f4becb</t>
+  </si>
+  <si>
+    <t>In the morning while entering school</t>
+  </si>
+  <si>
+    <t>At the kitchen</t>
+  </si>
+  <si>
+    <t>Mpox can be seen by body rushs while malaria is by high temperature</t>
+  </si>
+  <si>
+    <t>I talk to the school nurse to help him</t>
+  </si>
+  <si>
+    <t>37097fdb-ddbd-4571-9b4d-b5a9883bdc0d</t>
+  </si>
+  <si>
+    <t>uuid:37097fdb-ddbd-4571-9b4d-b5a9883bdc0d</t>
+  </si>
+  <si>
+    <t>Busega</t>
+  </si>
+  <si>
+    <t>KCCA Busega Community School</t>
+  </si>
+  <si>
+    <t>Ebola kills instantly</t>
+  </si>
+  <si>
+    <t>Little knowledge on public health emergencies</t>
+  </si>
+  <si>
+    <t>Encourage the school health club to continue sensitization of pupils on public health emergencies</t>
+  </si>
+  <si>
+    <t>4a6e3196-52a9-4086-9c32-b8ef4858d984</t>
+  </si>
+  <si>
+    <t>v7P6Cr66geEtrTnJmvbR3K</t>
+  </si>
+  <si>
+    <t>uuid:4a6e3196-52a9-4086-9c32-b8ef4858d984</t>
+  </si>
+  <si>
+    <t>Ebola is a political stunt. This has been said several times</t>
+  </si>
+  <si>
+    <t>Over population and congestion</t>
+  </si>
+  <si>
+    <t>Reduce on the prices for rent inside the  market such that the people can leave the drainage area and settle inside the markets</t>
+  </si>
+  <si>
+    <t>121755e1-9242-497b-8bb4-a65613e2db92</t>
+  </si>
+  <si>
+    <t>uuid:121755e1-9242-497b-8bb4-a65613e2db92</t>
+  </si>
+  <si>
+    <t>Ignorance on public health emergency</t>
+  </si>
+  <si>
+    <t>Work with KCCA to ensure that the sewage is removed before it overflows</t>
+  </si>
+  <si>
+    <t>aa4af4ec-028a-4ee4-8c97-76886b04d681</t>
+  </si>
+  <si>
+    <t>uuid:aa4af4ec-028a-4ee4-8c97-76886b04d681</t>
+  </si>
+  <si>
+    <t>Yes, already active</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>School assembly</t>
+  </si>
+  <si>
+    <t>What is UNICEF in full? Do we still have Ebola cases in Uganda?</t>
+  </si>
+  <si>
+    <t>Limited knowledge at times that leads to people not doing the right thing</t>
+  </si>
+  <si>
+    <t>More engagements should be carried. A U report talking point was requested to be placed in the school compound.</t>
+  </si>
+  <si>
+    <t>6dcc52e1-0b13-4cf0-9e4d-a6d77fb4c2cd</t>
+  </si>
+  <si>
+    <t>uuid:6dcc52e1-0b13-4cf0-9e4d-a6d77fb4c2cd</t>
+  </si>
+  <si>
+    <t>Lc chairperson</t>
+  </si>
+  <si>
+    <t>To support  the public health emergency  preparedness  in the community</t>
+  </si>
+  <si>
+    <t>Why are we still talking about ebola yet we don't have any threat of disease, is ebola still there,  can you get support from the government  healthfacility or we can go to any facility  and we get all the required help</t>
+  </si>
+  <si>
+    <t>Bodaboda  riders and mechanics</t>
+  </si>
+  <si>
+    <t>Engage their leaders to increase risk perception</t>
+  </si>
+  <si>
+    <t>92be9d77-2537-405d-8e84-a5f0210a5d27</t>
+  </si>
+  <si>
+    <t>uuid:92be9d77-2537-405d-8e84-a5f0210a5d27</t>
+  </si>
+  <si>
+    <t>Market / Trading Center</t>
+  </si>
+  <si>
+    <t>Market / Vendor Head</t>
+  </si>
+  <si>
+    <t>Market chairperson</t>
+  </si>
+  <si>
+    <t>Encouraging people to wash hands</t>
+  </si>
+  <si>
+    <t>Ebola can't be got by people who are healthy</t>
+  </si>
+  <si>
+    <t>Boda boda rider</t>
+  </si>
+  <si>
+    <t>987ce1b8-4c51-44d8-b4ce-b2cfeda4deff</t>
+  </si>
+  <si>
+    <t>uuid:987ce1b8-4c51-44d8-b4ce-b2cfeda4deff</t>
+  </si>
+  <si>
+    <t>Mengo</t>
+  </si>
+  <si>
+    <t>The last Ebola was not real but staged by government</t>
+  </si>
+  <si>
+    <t>Something he has heard in conversations</t>
+  </si>
+  <si>
+    <t>Have asked him not to assume on rumors but seek information from established sources</t>
+  </si>
+  <si>
+    <t>60753643-caa5-4687-afa1-63d6f7dc07ce</t>
+  </si>
+  <si>
+    <t>uuid:60753643-caa5-4687-afa1-63d6f7dc07ce</t>
+  </si>
+  <si>
+    <t>The last outbreak was a lie government told us</t>
+  </si>
+  <si>
+    <t>Mistrust in government</t>
+  </si>
+  <si>
+    <t>Verification of information source</t>
+  </si>
+  <si>
+    <t>Not yet roday</t>
+  </si>
+  <si>
+    <t>About 100 meters from here outside a restaurant</t>
+  </si>
+  <si>
+    <t>c84d709a-bdb2-45d2-ad2f-148d2cf301ae</t>
+  </si>
+  <si>
+    <t>uuid:c84d709a-bdb2-45d2-ad2f-148d2cf301ae</t>
+  </si>
+  <si>
+    <t>Have the disease  come back ,ebola affects only congolesw</t>
+  </si>
+  <si>
+    <t>Bodaboda</t>
+  </si>
+  <si>
+    <t>I can easily spot the signs of Ebola and Mpox If someone gets sick with outbreak signs, I will call the toll-free line or report immediately We do not discriminate against anyone who recovers from an infectious disease or their family I have shared the emergency preparedness messages with my household and colleagues</t>
+  </si>
+  <si>
+    <t>Someone vomiting, red eyes, vomiting  with diarrhea,</t>
+  </si>
+  <si>
+    <t>Send an alert to 6767, send to a health facility</t>
+  </si>
+  <si>
+    <t>They delay to respond</t>
+  </si>
+  <si>
+    <t>Ask them about how they were cared for, what were you given to make sure you are safe</t>
+  </si>
+  <si>
+    <t>Yed</t>
+  </si>
+  <si>
+    <t>Protect themselves by knowing the signs and symptoms  incase someone has signs and symptoms  and alert the VHY and LC chairpersons</t>
+  </si>
+  <si>
+    <t>If someone  goes to isolation, what happens to the family,? Government  has medicine  and treatment  is free and everything  is catered for and community will support the family but you will remain, you will  spread to the family</t>
+  </si>
+  <si>
+    <t>e38b9729-126b-4f31-9d07-b3391acb8cd5</t>
+  </si>
+  <si>
+    <t>uuid:e38b9729-126b-4f31-9d07-b3391acb8cd5</t>
+  </si>
+  <si>
+    <t>That government staged the last Ebola suspects ,how come none where known locals?</t>
+  </si>
+  <si>
+    <t>Work space</t>
+  </si>
+  <si>
+    <t>Did a small session on Ebola with her and her colleagues</t>
+  </si>
+  <si>
+    <t>What if the person is not actually sick with that particular disease?</t>
+  </si>
+  <si>
+    <t>High Reluctance</t>
+  </si>
+  <si>
+    <t>70756fd3-86e5-46d0-bba1-ab745b3addab</t>
+  </si>
+  <si>
+    <t>uuid:70756fd3-86e5-46d0-bba1-ab745b3addab</t>
+  </si>
+  <si>
+    <t>Nsambya</t>
+  </si>
+  <si>
+    <t>They are people who say that  ebola has never existed because they have never seen any one sick</t>
+  </si>
+  <si>
+    <t>Educating them that the disease  is there and  they should  protect themselves</t>
+  </si>
+  <si>
+    <t>Red eyes,vomiting of blood,  high body temperature,  body weakness</t>
+  </si>
+  <si>
+    <t>Call the toll free  number</t>
+  </si>
+  <si>
+    <t>Fear of isolation</t>
+  </si>
+  <si>
+    <t>Calling tools free number, informing the VHT and chairman</t>
+  </si>
+  <si>
+    <t>Have you ever reached where they take the ebola and mpox patients for treatment,  what happens there:i have never reached there but  I think people are cared for</t>
+  </si>
+  <si>
+    <t>1fc12766-e57f-48ce-a711-8b1a797ebec5</t>
+  </si>
+  <si>
+    <t>uuid:1fc12766-e57f-48ce-a711-8b1a797ebec5</t>
+  </si>
+  <si>
+    <t>Is ebola curable</t>
+  </si>
+  <si>
+    <t>People  don't wash hands  because there are washing points</t>
+  </si>
+  <si>
+    <t>Bodaboda  rider</t>
+  </si>
+  <si>
+    <t>Improve hygienic conditions</t>
+  </si>
+  <si>
+    <t>7fcf63aa-ff4e-49d2-ba8f-590576f7035d</t>
+  </si>
+  <si>
+    <t>uuid:7fcf63aa-ff4e-49d2-ba8f-590576f7035d</t>
+  </si>
+  <si>
+    <t>Did ebola reach kampala  or uganda,  i did see any sick of ebola</t>
+  </si>
+  <si>
+    <t>Disbelief  that ebola exists</t>
+  </si>
+  <si>
+    <t>Personally</t>
+  </si>
+  <si>
+    <t>Increase  risk perception</t>
+  </si>
+  <si>
+    <t>The skin rashes   for mpox</t>
+  </si>
+  <si>
+    <t>Advise them to go to hospital, we don't have health worker contacts</t>
+  </si>
+  <si>
+    <t>We interact as usual</t>
+  </si>
+  <si>
+    <t>35a51299-dac1-49df-ab13-aa75cf89e657</t>
+  </si>
+  <si>
+    <t>uuid:35a51299-dac1-49df-ab13-aa75cf89e657</t>
+  </si>
+  <si>
+    <t>NSAMBYA CENTRAL</t>
+  </si>
+  <si>
+    <t>COGRA</t>
+  </si>
+  <si>
+    <t>Ebola is brought by people from Congo</t>
+  </si>
+  <si>
+    <t>Communities is mixed</t>
+  </si>
+  <si>
+    <t>Improve on the hygiene</t>
+  </si>
+  <si>
+    <t>Fever ,vomiting with blood</t>
+  </si>
+  <si>
+    <t>4d25c4aa-dd3a-4510-b3bb-342e87112036</t>
+  </si>
+  <si>
+    <t>uuid:4d25c4aa-dd3a-4510-b3bb-342e87112036</t>
+  </si>
+  <si>
+    <t>People doubt ,I believe  that ebola  is not there, because  I have never seen anybody sick of ebola because we belive government  wants to pass  its own agendas</t>
+  </si>
+  <si>
+    <t>Bodaboda  stages</t>
+  </si>
+  <si>
+    <t>We do not discriminate against anyone who recovers from an infectious disease or their family</t>
+  </si>
+  <si>
+    <t>There is no isolation at all</t>
+  </si>
+  <si>
+    <t>5e8746c7-816e-44d5-ad9e-9a386009db44</t>
+  </si>
+  <si>
+    <t>uuid:5e8746c7-816e-44d5-ad9e-9a386009db44</t>
+  </si>
+  <si>
+    <t>Nsamby Central</t>
+  </si>
+  <si>
+    <t>Ebola is not there</t>
+  </si>
+  <si>
+    <t>Different groups of people</t>
+  </si>
+  <si>
+    <t>People  should have the opportunity to see the sick one</t>
+  </si>
+  <si>
+    <t>fa7cec20-d28a-4ecf-8596-1e659d5c964b</t>
+  </si>
+  <si>
+    <t>uuid:fa7cec20-d28a-4ecf-8596-1e659d5c964b</t>
+  </si>
+  <si>
+    <t>Is ebola  still there or it got done</t>
+  </si>
+  <si>
+    <t>Congested area</t>
+  </si>
+  <si>
+    <t>Call the healthworker from  the clinic  nearby to come to check on the person</t>
+  </si>
+  <si>
+    <t>27e5e1a8-b745-429b-99be-6f2b48e1480a</t>
+  </si>
+  <si>
+    <t>uuid:27e5e1a8-b745-429b-99be-6f2b48e1480a</t>
+  </si>
+  <si>
+    <t>Nsamby central</t>
+  </si>
+  <si>
+    <t>Mpox is real</t>
+  </si>
+  <si>
+    <t>Lack of information</t>
+  </si>
+  <si>
+    <t>Washing hands</t>
+  </si>
+  <si>
+    <t>Rash on the body and High temperature</t>
+  </si>
+  <si>
+    <t>21a71359-cbb6-41b6-adf0-155019414a2b</t>
+  </si>
+  <si>
+    <t>uuid:21a71359-cbb6-41b6-adf0-155019414a2b</t>
+  </si>
+  <si>
+    <t>Congra</t>
+  </si>
+  <si>
+    <t>We donot have Ebola now</t>
+  </si>
+  <si>
+    <t>No ebola</t>
+  </si>
+  <si>
+    <t>Skin rsh</t>
+  </si>
+  <si>
+    <t>259e8e74-cda6-48d1-8974-55b78014f7a0</t>
+  </si>
+  <si>
+    <t>uuid:259e8e74-cda6-48d1-8974-55b78014f7a0</t>
+  </si>
+  <si>
+    <t>Nsambya Central</t>
+  </si>
+  <si>
+    <t>Government brings up diseases to get money</t>
+  </si>
+  <si>
+    <t>Have never had of people  dying of Ebola in the community</t>
+  </si>
+  <si>
+    <t>Empower vhts</t>
+  </si>
+  <si>
+    <t>b6d8ec60-482e-4cf8-9261-bc42ce8901b9</t>
+  </si>
+  <si>
+    <t>uuid:b6d8ec60-482e-4cf8-9261-bc42ce8901b9</t>
+  </si>
+  <si>
+    <t>Nsambya Centrl</t>
+  </si>
+  <si>
+    <t>We do not have any  threatening diseases</t>
+  </si>
+  <si>
+    <t>Dening of any diseases may lead to risk of children and families of getting diseases</t>
+  </si>
+  <si>
+    <t>Reinforce  health message so that people understand the riskss</t>
+  </si>
+  <si>
+    <t>Vomiting , high fever</t>
+  </si>
+  <si>
+    <t>b9a6e26c-b3d7-49be-8830-89a8c46f5fd4</t>
+  </si>
+  <si>
+    <t>uuid:b9a6e26c-b3d7-49be-8830-89a8c46f5fd4</t>
+  </si>
+  <si>
+    <t>We haven't received any case last month</t>
+  </si>
+  <si>
+    <t>Many people believe there have been no cases, so they see no need for protective behaviours or early reporting.</t>
+  </si>
+  <si>
+    <t>Strengthen community feedback messaging that confirms cases are occurring or have occurred and reinforce early symptom recognition &amp;  care-seeking</t>
+  </si>
+  <si>
+    <t>a8e90e9e-ca67-467b-8341-babd99a25bf0</t>
+  </si>
+  <si>
+    <t>uuid:a8e90e9e-ca67-467b-8341-babd99a25bf0</t>
+  </si>
+  <si>
+    <t>We haven’t received any case last month people are saying there is no disease ,no cases in the community.</t>
+  </si>
+  <si>
+    <t>Low risk perception and denial , community members believe there are no cases, so they see little reason to follow prevention messages or report early symptoms.</t>
+  </si>
+  <si>
+    <t>Reinforce early symptom recognition and the importance of reporting even when people think the situation is calm.</t>
+  </si>
+  <si>
+    <t>3258fdc2-9c86-4da0-9da9-45d60a486bee</t>
+  </si>
+  <si>
+    <t>uuid:3258fdc2-9c86-4da0-9da9-45d60a486bee</t>
+  </si>
+  <si>
+    <t>Do we have any out break</t>
+  </si>
+  <si>
+    <t>Uncertainty community members are unsure whether an outbreak is happening, which reduces urgency to follow prevention advice .</t>
+  </si>
+  <si>
+    <t>Provide clear, simple updates confirming the current outbreak status .</t>
+  </si>
+  <si>
+    <t>Vomiting blood,body weakness</t>
+  </si>
+  <si>
+    <t>7d36af2e-ee5c-41e6-ba7c-b4b795eea47d</t>
+  </si>
+  <si>
+    <t>uuid:7d36af2e-ee5c-41e6-ba7c-b4b795eea47d</t>
+  </si>
+  <si>
+    <t>People are saying Uganda is free from any threat of diseases</t>
+  </si>
+  <si>
+    <t>Communities believe no ebola diseases in the country and can stop washing hands often</t>
+  </si>
+  <si>
+    <t>Always  motivate vhts to keep us sensitive people about the diseases</t>
+  </si>
+  <si>
+    <t>Committing , fever</t>
+  </si>
+  <si>
+    <t>015cece1-ab50-4f8c-a935-28405d8ccc8d</t>
+  </si>
+  <si>
+    <t>uuid:015cece1-ab50-4f8c-a935-28405d8ccc8d</t>
+  </si>
+  <si>
+    <t>Gayaza Road secondary school</t>
+  </si>
+  <si>
+    <t>Ebola affects Congolese alone. Uganda is Ebola free</t>
+  </si>
+  <si>
+    <t>Politicking of the outbreaks</t>
+  </si>
+  <si>
+    <t>Institutions of learning should be engaged more</t>
+  </si>
+  <si>
+    <t>cec65995-37be-4727-a20f-4a92fcede934</t>
+  </si>
+  <si>
+    <t>uuid:cec65995-37be-4727-a20f-4a92fcede934</t>
+  </si>
+  <si>
+    <t>Do home rats cause Ebola?</t>
+  </si>
+  <si>
+    <t>Low risk perception  which at times is triggeref by limted information</t>
+  </si>
+  <si>
+    <t>More sensitization on radio and television shoukd be done</t>
+  </si>
+  <si>
+    <t>0ca241f0-d08c-44e1-a771-0983d94e797e</t>
+  </si>
+  <si>
+    <t>uuid:0ca241f0-d08c-44e1-a771-0983d94e797e</t>
+  </si>
+  <si>
+    <t>Taxi / Bus Park</t>
+  </si>
+  <si>
+    <t>Taxi park committe Supervisor</t>
+  </si>
+  <si>
+    <t>Suprvise continued use of handwsshing facilities at different stages</t>
+  </si>
+  <si>
+    <t>Low / Stigmatizing</t>
+  </si>
+  <si>
+    <t>Ebola can spread through air like covid 19</t>
+  </si>
+  <si>
+    <t>Myths and misconceptions in the community lead to low response</t>
+  </si>
+  <si>
+    <t>More engagements at village level through one on one sessions should be done more</t>
+  </si>
+  <si>
+    <t>28e600f8-847b-476b-a8a3-44de769bb740</t>
+  </si>
+  <si>
+    <t>uuid:28e600f8-847b-476b-a8a3-44de769bb740</t>
+  </si>
+  <si>
+    <t>Leader of market vendors</t>
+  </si>
+  <si>
+    <t>Lobby for hand washing facility for the market</t>
+  </si>
+  <si>
+    <t>There is no more Ebola in the country</t>
+  </si>
+  <si>
+    <t>Socia media platforms that mislead with fake information</t>
+  </si>
+  <si>
+    <t>More sensitizaton using mobilisation van should be carried out</t>
+  </si>
+  <si>
+    <t>a9f21b63-3f75-47f3-8d39-39572aefc789</t>
+  </si>
+  <si>
+    <t>uuid:a9f21b63-3f75-47f3-8d39-39572aefc789</t>
+  </si>
+  <si>
+    <t>Boda stage leader</t>
+  </si>
+  <si>
+    <t>Continued awareness creation to fellow riders and customers</t>
+  </si>
+  <si>
+    <t>Government was after making money there was no Ebola</t>
+  </si>
+  <si>
+    <t>Politiking of the outbreak</t>
+  </si>
+  <si>
+    <t>Passengers/customers</t>
+  </si>
+  <si>
+    <t>More comnunity engagements should be carried out</t>
+  </si>
+  <si>
+    <t>e1ab6348-2aa8-49d2-8d14-3f7dd8eda016</t>
+  </si>
+  <si>
+    <t>uuid:e1ab6348-2aa8-49d2-8d14-3f7dd8eda016</t>
+  </si>
+  <si>
+    <t>Boda boda riders and their leader</t>
+  </si>
+  <si>
+    <t>Sharing of right information from right sources</t>
+  </si>
+  <si>
+    <t>Is there an Ebola vaccine ?</t>
+  </si>
+  <si>
+    <t>Congestion of some areas that easens spread</t>
+  </si>
+  <si>
+    <t>Empower local leaders by government so as to equip people with information</t>
+  </si>
+  <si>
+    <t>7066e223-13fe-466e-a67d-6ccd20ea6b13</t>
+  </si>
+  <si>
+    <t>uuid:7066e223-13fe-466e-a67d-6ccd20ea6b13</t>
+  </si>
+  <si>
+    <t>Boda boda</t>
+  </si>
+  <si>
+    <t>He said they were going to put hand washing equipment at the stage,</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>Ebola outbreak is political</t>
+  </si>
+  <si>
+    <t>The youth have convinced the bodaboda community that Ebola is not real</t>
+  </si>
+  <si>
+    <t>The youth</t>
+  </si>
+  <si>
+    <t>e1fcd3bd-7974-4a89-9a85-13324372f609</t>
+  </si>
+  <si>
+    <t>uuid:e1fcd3bd-7974-4a89-9a85-13324372f609</t>
+  </si>
+  <si>
+    <t>Where did ebola come from, I really  want to know where ebola came from</t>
+  </si>
+  <si>
+    <t>10 minutes back</t>
+  </si>
+  <si>
+    <t>Near the vegetables</t>
+  </si>
+  <si>
+    <t>High body temperature,  headache  that does not heal and red eyes</t>
+  </si>
+  <si>
+    <t>I would call the health worker  in the nearby  clinic so that they verify if its ebola or not</t>
+  </si>
+  <si>
+    <t>84f72ae7-72af-4be5-a1de-fa58a835e50f</t>
+  </si>
+  <si>
+    <t>uuid:84f72ae7-72af-4be5-a1de-fa58a835e50f</t>
+  </si>
+  <si>
+    <t>Bar / Malwa Joint / Hospitality</t>
+  </si>
+  <si>
+    <t>Bar attendant manager</t>
+  </si>
+  <si>
+    <t>We found the bar (vibes suits) having no hand-washing facilities. The bar attendant committed to solicit for a handwashing facility and put one at the entrance. She also requested for some posters to put in the bar as a way to remind people that we have to keep caution.</t>
+  </si>
+  <si>
+    <t>Ebola moves through air. Is the hotline number free of charge or i need airtime to communicate.</t>
+  </si>
+  <si>
+    <t>No hand-washing facilities. They don't have knowledge about ebola and they believe that they are very safe so they dont take precaution.</t>
+  </si>
+  <si>
+    <t>Intesify targeted RCCE on social media and in the community and conduction of community senstization especially through the community leaders</t>
+  </si>
+  <si>
+    <t>f2f18fa1-36d7-4093-b530-5e93d09a66ed</t>
+  </si>
+  <si>
+    <t>uuid:f2f18fa1-36d7-4093-b530-5e93d09a66ed</t>
+  </si>
+  <si>
+    <t>Misindye COU Primary and Nursery school</t>
+  </si>
+  <si>
+    <t>Completely dry/absent</t>
+  </si>
+  <si>
+    <t>The HM mentioned and said that we just have to learn how to live with Ebola because it is part of us now. Comes and goes. Unlike other outbreaks that have been coming and going, Ebola is diffent that it has frequently suffaced.</t>
+  </si>
+  <si>
+    <t>As a school, they have a challenge of water. The community from out keeps intruding and end up staeling and destroying school property. They also have a challenge of soap that is always wasted and taken by the pupils whenever it is availed.</t>
+  </si>
+  <si>
+    <t>School senstization on ebola facts and hand hygiene, using of peer leaders and forming a u-report club to counter rumors in the school.</t>
+  </si>
+  <si>
+    <t>b5144cea-687d-4cc7-a486-bbf8c6ab6095</t>
+  </si>
+  <si>
+    <t>uuid:b5144cea-687d-4cc7-a486-bbf8c6ab6095</t>
+  </si>
+  <si>
+    <t>Misindye</t>
+  </si>
+  <si>
+    <t>No specific one.</t>
+  </si>
+  <si>
+    <t>Using the student leaders in school to address ehat these public health emergencies are.</t>
+  </si>
+  <si>
+    <t>There is a distance of 10 m from the toilet ro the kitchen</t>
+  </si>
+  <si>
+    <t>The school is spacious enough, this creates more space for isolation reducing on the risk of body to body contact. However, when it comes to the basics of hand washing, they have challenges with water. The school also has limited toilets compared to the number of children available</t>
+  </si>
+  <si>
+    <t>They have a total of 8 toilets.  This makes the student to stance ratio unproportionally big</t>
+  </si>
+  <si>
+    <t>Yes the teacher in charge of health has ever received orientation on epidemics</t>
+  </si>
+  <si>
+    <t>3d6b8e7f-922b-45e2-a0ab-6fefc8a96456</t>
+  </si>
+  <si>
+    <t>uuid:3d6b8e7f-922b-45e2-a0ab-6fefc8a96456</t>
+  </si>
+  <si>
+    <t>Seeta COU Primary and Nursery School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Science teacher </t>
+  </si>
+  <si>
+    <t>Yes / Easily</t>
+  </si>
+  <si>
+    <t>Its only the people that eat monkeys that get infected with ebola. Other people are safe because ebola comes from eating monkeys, dogs, cats and bats</t>
+  </si>
+  <si>
+    <t>High level of ignorance in the school</t>
+  </si>
+  <si>
+    <t>Emphasized school senstization especially on the ways how ebola spreads.</t>
+  </si>
+  <si>
+    <t>af83c7ce-4699-4e7a-9622-c0898e81f6d2</t>
+  </si>
+  <si>
+    <t>uuid:af83c7ce-4699-4e7a-9622-c0898e81f6d2</t>
+  </si>
+  <si>
+    <t>Gulu ward</t>
+  </si>
+  <si>
+    <t>Parish heads / leaders</t>
+  </si>
+  <si>
+    <t>The parish leaders were having a meeting at a community place so they didnt have any protocol. strengthening community based surveillance, enhancing early reporting, and clarifying roles of community leaders in risk communication.</t>
+  </si>
+  <si>
+    <t>If someone has even just two signs of those from ebola like severe headache and restlessness, loss of appetite, should i conclude that the person could be a suspect.</t>
+  </si>
+  <si>
+    <t>Nothing really. They were willing to lear</t>
+  </si>
+  <si>
+    <t>Social media and the communities where we serve</t>
+  </si>
+  <si>
+    <t>Engage parish leaders to cascade correct Ebola prevention messages to their congregations, support installation of handwashing facilities with soap at churches/mosques, and use religious gatherings for community sensitization and rumor tracking.</t>
+  </si>
+  <si>
+    <t>b11a7596-5b40-41b2-8d3b-d09a5e9bc82f</t>
+  </si>
+  <si>
+    <t>uuid:b11a7596-5b40-41b2-8d3b-d09a5e9bc82f</t>
+  </si>
+  <si>
+    <t>Nabuti</t>
+  </si>
+  <si>
+    <t>None shared</t>
+  </si>
+  <si>
+    <t>I was given lim ited time bacause they were having a meetin g in the next 1 hour and they had to prepare.</t>
+  </si>
+  <si>
+    <t>No rumor</t>
+  </si>
+  <si>
+    <t>Will share later in the next visit</t>
+  </si>
+  <si>
+    <t>No breeding sites</t>
+  </si>
+  <si>
+    <t>The school is located on a hilly place with a lot of trees. They are organised generally the only challenge comes from the absence of</t>
+  </si>
+  <si>
+    <t>40&gt;5</t>
+  </si>
+  <si>
+    <t>the school has no school nurse.</t>
+  </si>
+  <si>
+    <t>e93a6459-565b-47cc-a1f3-3ec0511b551a</t>
+  </si>
+  <si>
+    <t>uuid:e93a6459-565b-47cc-a1f3-3ec0511b551a</t>
+  </si>
+  <si>
+    <t>No in-depth discussion. The discussion was somehow quick but i was requested to go back</t>
+  </si>
+  <si>
+    <t>will share soon</t>
+  </si>
+  <si>
+    <t>c9fb9dd4-3b9b-471f-9c6c-ff3fdb21dae0</t>
+  </si>
+  <si>
+    <t>uuid:c9fb9dd4-3b9b-471f-9c6c-ff3fdb21dae0</t>
+  </si>
+  <si>
+    <t>Nabuuti</t>
+  </si>
+  <si>
+    <t>Yet to identify one</t>
+  </si>
+  <si>
+    <t>Ebola is not real and that handwashing cannot prevent it. 2 Pupils believe Ebola only affects adults, children cannot get it.   3Question from students: If there are no handwashing facilities, how can we prevent Ebola at school? Requested to get them some hand washing facilities</t>
+  </si>
+  <si>
+    <t>Absence of handwashing facilities leading to low hand hygiene practice.    2No dedicated budget for soap and water for handwashing.  3Teachers not trained to deliver Ebola prevention messages</t>
+  </si>
+  <si>
+    <t>Conduct school-based RCCE orientation on Ebola facts and demonstrate proper handwashing with soap.    2Distribute and paste IEC materials on Ebola prevention (having the hotline)in classrooms and latrines.       3Train health clubs / prefects as peer influencers to promote hand hygiene and rumor reporting.</t>
+  </si>
+  <si>
+    <t>3da34766-85ff-4920-9cfa-06ce3d54d541</t>
+  </si>
+  <si>
+    <t>uuid:3da34766-85ff-4920-9cfa-06ce3d54d541</t>
+  </si>
+  <si>
+    <t>It’s is witchcraft</t>
+  </si>
+  <si>
+    <t>Vomiting and diarrhea. Seek medical attention</t>
+  </si>
+  <si>
+    <t>4b5c95af-32ad-40d2-a6ac-b8139380216b</t>
+  </si>
+  <si>
+    <t>uuid:4b5c95af-32ad-40d2-a6ac-b8139380216b</t>
+  </si>
+  <si>
+    <t>The government is trying to steal money</t>
+  </si>
+  <si>
+    <t>Sore throat and bleeding from body openings. Always wash hands</t>
+  </si>
+  <si>
+    <t>3bb96029-cd2d-4916-badc-1c6a84e22ecd</t>
+  </si>
+  <si>
+    <t>uuid:3bb96029-cd2d-4916-badc-1c6a84e22ecd</t>
+  </si>
+  <si>
+    <t>Tool 4: most significant change story collection form</t>
+  </si>
+  <si>
+    <t>Kazo</t>
+  </si>
+  <si>
+    <t>Ebola can't come back.</t>
+  </si>
+  <si>
+    <t>Washing hands regularly</t>
+  </si>
+  <si>
+    <t>We had stopped washing our hands because we thought the was gone and no more in the country.</t>
+  </si>
+  <si>
+    <t>The U-reporters came to us as youths and sensitized the need to always wash our hands with soap and water.</t>
+  </si>
+  <si>
+    <t>Most of the community members currently know the signs and symptoms of outbreaks that have been with in us.</t>
+  </si>
+  <si>
+    <t>Because even after the government announced Uganda as an Ebola free country, The U-reporters and VHTs have always moved to our homes to encourage us to always wash our hand but also reminded us the signs and symptoms.</t>
+  </si>
+  <si>
+    <t>39e5e4d9-f5ba-4ad1-a2ef-873a527cc80f</t>
+  </si>
+  <si>
+    <t>uuid:39e5e4d9-f5ba-4ad1-a2ef-873a527cc80f</t>
+  </si>
+  <si>
+    <t>Resturant owner</t>
+  </si>
+  <si>
+    <t>Ensure functionality of handwashing facilities</t>
+  </si>
+  <si>
+    <t>How does Ebola spread from animals to Humans</t>
+  </si>
+  <si>
+    <t>Alot of miss information from the public</t>
+  </si>
+  <si>
+    <t>More village sensitization programs should be carried out</t>
+  </si>
+  <si>
+    <t>461dc488-4752-4b20-ad0a-54293b066eb0</t>
+  </si>
+  <si>
+    <t>uuid:461dc488-4752-4b20-ad0a-54293b066eb0</t>
+  </si>
+  <si>
+    <t>Already shared</t>
+  </si>
+  <si>
+    <t>Yes — all steps followed</t>
+  </si>
+  <si>
+    <t>Tuesday Thursday</t>
+  </si>
+  <si>
+    <t>Since ebola is not in the country right, that means we are not at risk</t>
+  </si>
+  <si>
+    <t>More sensitization in the school</t>
+  </si>
+  <si>
+    <t>b3f041d0-65b8-4385-85a9-4cf1f1a88cb5</t>
+  </si>
+  <si>
+    <t>uuid:b3f041d0-65b8-4385-85a9-4cf1f1a88cb5</t>
+  </si>
+  <si>
+    <t>Market commite</t>
+  </si>
+  <si>
+    <t>They committed to report to MOH any person suspected to have signs of Ebola</t>
+  </si>
+  <si>
+    <t>Some times the government gives wrong figures.</t>
+  </si>
+  <si>
+    <t>More sensitization needed in the area.</t>
+  </si>
+  <si>
+    <t>64b1850c-b8a5-4dd6-ae7c-1ea0369e1d19</t>
+  </si>
+  <si>
+    <t>uuid:64b1850c-b8a5-4dd6-ae7c-1ea0369e1d19</t>
+  </si>
+  <si>
+    <t>More sensitization needed in the lower section</t>
+  </si>
+  <si>
+    <t>Before the intervention in this school, the school had less functional hand washing facilities, and was not having soap. The school didn't have an activity school health club. It only had unless than 15 members. The pupils had very less knowledge on PHE .</t>
+  </si>
+  <si>
+    <t>With the introduction of the snakes and ladders game,the Knowledge wheel sessions, these have helped the learners to understand well the PHE sign and symptoms and where to report Incase of any suspect.</t>
+  </si>
+  <si>
+    <t>The school currently has enough hand washing facilities around the school.</t>
+  </si>
+  <si>
+    <t>This is because currently all the students are encouraged to was their hands, the health club report any pupil who is seen not washing their hands.</t>
+  </si>
+  <si>
+    <t>7a2d0cb9-ca50-4c82-b593-3b92cc3526c4</t>
+  </si>
+  <si>
+    <t>uuid:7a2d0cb9-ca50-4c82-b593-3b92cc3526c4</t>
+  </si>
+  <si>
+    <t>They are going to put hand washing equipment at the stage</t>
+  </si>
+  <si>
+    <t>Fellow boda boda riders</t>
+  </si>
+  <si>
+    <t>7142423b-9e74-4959-8dca-0b6c1c39bd35</t>
+  </si>
+  <si>
+    <t>uuid:7142423b-9e74-4959-8dca-0b6c1c39bd35</t>
+  </si>
+  <si>
+    <t>This week was measles immunization week,the pupils mentioned that some pupils had been kept at home by the parents not to be immunized yet others had come to be immunized it was  confusing them</t>
+  </si>
+  <si>
+    <t>The mistrust between government and the community/parents creates a challenge for children on who to believe</t>
+  </si>
+  <si>
+    <t>All parties need to find a middle ground on dealing with the mistrust,government needs to align clear channels that are not political</t>
+  </si>
+  <si>
+    <t>4810d950-05a1-4dda-9bda-b16686bd89d4</t>
+  </si>
+  <si>
+    <t>uuid:4810d950-05a1-4dda-9bda-b16686bd89d4</t>
+  </si>
+  <si>
+    <t>Kololo High</t>
+  </si>
+  <si>
+    <t>Head of clubs teacher</t>
+  </si>
+  <si>
+    <t>Ebola can not be cured,vaccines are trials and whites use us as specimen, that during Covid patients were intentionally poisoned and killed by government, that ARV's taken by HIV patients make a heap in their stomachs that eventually kills them</t>
+  </si>
+  <si>
+    <t>So many sources of information that are not being verified</t>
+  </si>
+  <si>
+    <t>Encourage them to verify the information through proper channels</t>
+  </si>
+  <si>
+    <t>9449a059-de6f-4d9c-8a69-413b02b84851</t>
+  </si>
+  <si>
+    <t>uuid:9449a059-de6f-4d9c-8a69-413b02b84851</t>
+  </si>
+  <si>
+    <t>Dirtness causes Ebola, it was a  government scheme but no Ebola, it's airborne, it's not curable</t>
+  </si>
+  <si>
+    <t>Confusion on who to believe, government or the community where they don’t agree</t>
+  </si>
+  <si>
+    <t>Address the misconceptions</t>
+  </si>
+  <si>
+    <t>Clean and well  cleared</t>
+  </si>
+  <si>
+    <t>Some of the SOPs are being followed</t>
+  </si>
+  <si>
+    <t>3 to 10</t>
+  </si>
+  <si>
+    <t>b5c8a6b0-4387-4b5f-924e-053c17c80dee</t>
+  </si>
+  <si>
+    <t>uuid:b5c8a6b0-4387-4b5f-924e-053c17c80dee</t>
+  </si>
+  <si>
+    <t>Namumira Anthony ward</t>
+  </si>
+  <si>
+    <t>St Stephen High School</t>
+  </si>
+  <si>
+    <t>Because of Ebola we shall not study, Because of Ebola, there is a suspension of school for 2 days</t>
+  </si>
+  <si>
+    <t>The need to have likes on social media makes people to keep spreading the rumors</t>
+  </si>
+  <si>
+    <t>Information should be got from the official websites of the government entities</t>
+  </si>
+  <si>
+    <t>281322bb-f2f3-42d6-83b8-efd8059feb0d</t>
+  </si>
+  <si>
+    <t>uuid:281322bb-f2f3-42d6-83b8-efd8059feb0d</t>
+  </si>
+  <si>
+    <t>Makerere I</t>
+  </si>
+  <si>
+    <t>Fish Market</t>
+  </si>
+  <si>
+    <t>Ensuring restoration of hand washing facilities at entry points</t>
+  </si>
+  <si>
+    <t>Is Ebola spread by bats? Is there an Ebola vaccine?</t>
+  </si>
+  <si>
+    <t>Limited information about the emergency signs and symptoms, causes and prevention measures</t>
+  </si>
+  <si>
+    <t>Friends, customers</t>
+  </si>
+  <si>
+    <t>More grassroot senstizations and health barazzas shoul be carried out.</t>
+  </si>
+  <si>
+    <t>dd83022d-2f9d-4d9b-bae0-ffbe122762bf</t>
+  </si>
+  <si>
+    <t>uuid:dd83022d-2f9d-4d9b-bae0-ffbe122762bf</t>
+  </si>
+  <si>
+    <t>Boda boda stage leader</t>
+  </si>
+  <si>
+    <t>Being vigilant for suspecious cases and report using MOH toll free line. Encouraging riders have pockect friendly sanitizer</t>
+  </si>
+  <si>
+    <t>Uganda is Ebola free. Ebola is in Congo. The recent Ebola wasnt all that deadly as few people died</t>
+  </si>
+  <si>
+    <t>Information gaps on the emergencies making practice of SOPs hard</t>
+  </si>
+  <si>
+    <t>Community generally like from fellow riders, politicians</t>
+  </si>
+  <si>
+    <t>The community should be equiped with information ad regards the disease outbreaks</t>
+  </si>
+  <si>
+    <t>e93de61b-b568-48d9-a01f-bf7bc0995bb9</t>
+  </si>
+  <si>
+    <t>uuid:e93de61b-b568-48d9-a01f-bf7bc0995bb9</t>
+  </si>
+  <si>
+    <t>Vaccines are trials, Ebola is not curable,Covid patients were killed by government</t>
+  </si>
+  <si>
+    <t>Many sources of information and mistrust for almost all of them</t>
+  </si>
+  <si>
+    <t>Need to emphasize the importance of verifying the source</t>
+  </si>
+  <si>
+    <t>The school is very clean and actively involved in public health activities</t>
+  </si>
+  <si>
+    <t>The student number is very high</t>
+  </si>
+  <si>
+    <t>5ee8b729-ee78-4727-bd2f-07765ca81721</t>
+  </si>
+  <si>
+    <t>uuid:5ee8b729-ee78-4727-bd2f-07765ca81721</t>
   </si>
 </sst>
 </file>
@@ -19449,7 +20655,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -19799,12 +21005,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY207" totalsRowShown="0">
-  <autoFilter ref="A1:IY207" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY265" totalsRowShown="0">
+  <autoFilter ref="A1:IY265" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
-    <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{88DF6524-6E04-DF49-88CE-CEC8D3CDF985}" name="Date" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{88DF6524-6E04-DF49-88CE-CEC8D3CDF985}" name="Date" dataDxfId="9"/>
     <tableColumn id="4" xr3:uid="{21B021AC-1A4F-9643-AD1E-92E8845CF4F5}" name="Public Health Emergencies "/>
     <tableColumn id="5" xr3:uid="{BCAFB874-40F2-E248-AC87-2F767B3AA935}" name="District"/>
     <tableColumn id="6" xr3:uid="{91864CF8-09C1-4F43-8730-5036D8A4FB1E}" name="Parish"/>
@@ -19956,7 +21162,7 @@
     <tableColumn id="152" xr3:uid="{CCC62284-8220-A74F-9667-4A6B0FC7197F}" name="##### Transport hubs"/>
     <tableColumn id="153" xr3:uid="{287C7C17-3E56-D546-A3AC-8B54B50420AF}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-Who is actually listened to&lt;/span&gt;"/>
     <tableColumn id="154" xr3:uid="{AB54E2D1-07BC-A542-A5F4-4A5643E21A8C}" name="&lt;span style=&quot;display:none&quot;&gt;row_1-What is be best engagement strategy&lt;/span&gt;"/>
-    <tableColumn id="155" xr3:uid="{F8536A7C-7408-5E41-B644-2E50476A335A}" name="##### Trade and markets" dataDxfId="11"/>
+    <tableColumn id="155" xr3:uid="{F8536A7C-7408-5E41-B644-2E50476A335A}" name="##### Trade and markets" dataDxfId="8"/>
     <tableColumn id="156" xr3:uid="{C011352D-AE70-8C46-A813-C1AD66C18450}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-Who is actually listened to&lt;/span&gt;"/>
     <tableColumn id="157" xr3:uid="{DD1A8AC6-3ADF-D44A-8492-E5FF11A138B5}" name="&lt;span style=&quot;display:none&quot;&gt;row_2-What is be best engagement strategy&lt;/span&gt;"/>
     <tableColumn id="158" xr3:uid="{E234F96F-1755-1748-9C94-456E62F048C0}" name="##### Faith institutions"/>
@@ -20000,18 +21206,18 @@
     <tableColumn id="196" xr3:uid="{B7D9977F-A71C-3A48-B484-8589CCCBDCDE}" name="total enrolment for boys"/>
     <tableColumn id="197" xr3:uid="{5C39133D-C0CA-444A-8DDA-6ABC398DA448}" name="Totla enrolement for girls"/>
     <tableColumn id="200" xr3:uid="{8E1CD290-68BC-9C47-BEEF-2C565F41FCB7}" name="Total male teaching staff"/>
-    <tableColumn id="201" xr3:uid="{34BCC6C6-281B-D440-AE51-DB01CFEB8103}" name="Total female teaching staff" dataDxfId="10"/>
-    <tableColumn id="202" xr3:uid="{CF8401CD-F11B-AE47-B55E-A60CC00A351E}" name="Presence of health club" dataDxfId="9"/>
+    <tableColumn id="201" xr3:uid="{34BCC6C6-281B-D440-AE51-DB01CFEB8103}" name="Total female teaching staff" dataDxfId="7"/>
+    <tableColumn id="202" xr3:uid="{CF8401CD-F11B-AE47-B55E-A60CC00A351E}" name="Presence of health club" dataDxfId="6"/>
     <tableColumn id="203" xr3:uid="{7C69AAD7-4189-D34F-B4E2-C13680BC2552}" name="School Health Club Status"/>
     <tableColumn id="204" xr3:uid="{F3A533AE-B20E-B245-96CA-E41E9BE1138C}" name="Does the school have a Epidemic Preparedness Plan"/>
     <tableColumn id="205" xr3:uid="{ADBFD779-AB4A-6141-8BFA-9A6306FFAEDE}" name="Can the school leadership state the official toll-free reporting lines (e.g., MoH/KCCA hotlines: 0800-100-066 / 8500) and the focal Division Health Officer/VHT contact without checking notes?"/>
     <tableColumn id="206" xr3:uid="{86D1EA6D-95C2-2645-B69C-E5E52EA9F6A2}" name="Does the school have a Designated Isolation place incase of an epidemic"/>
     <tableColumn id="207" xr3:uid="{CAB84FE7-A576-D345-9A4C-86E7BB8DE174}" name="Walk the compound; do not rely solely on verbal assertions."/>
     <tableColumn id="208" xr3:uid="{30D2B9FA-2C8A-124B-968B-2BADF142A1FA}" name="Q1 Stations present at gates, outside latrines, and near dining/canteen areas with both clean running water AND soap."/>
-    <tableColumn id="227" xr3:uid="{7D03EC66-017D-E146-8F0F-4DCAC1D6B120}" name="Record number of working water stations " dataDxfId="8"/>
-    <tableColumn id="228" xr3:uid="{76BE5A74-21A4-EF44-8C6A-1D9101DEF5BF}" name="Q2 Soap is consistently replenished for pupil use, not kept locked away for staff only." dataDxfId="7"/>
-    <tableColumn id="229" xr3:uid="{B71FFB51-4715-9F45-9BB4-F055E0B6579E}" name="Record toilet stances separated by gender, functional locks, clean floors, and handwash stations within 5 meters of exits." dataDxfId="6"/>
-    <tableColumn id="230" xr3:uid="{CFF4AA7F-A594-E644-BD64-9E6188518B37}" name="Record number of stances for boys " dataDxfId="5"/>
+    <tableColumn id="227" xr3:uid="{7D03EC66-017D-E146-8F0F-4DCAC1D6B120}" name="Record number of working water stations " dataDxfId="5"/>
+    <tableColumn id="228" xr3:uid="{76BE5A74-21A4-EF44-8C6A-1D9101DEF5BF}" name="Q2 Soap is consistently replenished for pupil use, not kept locked away for staff only." dataDxfId="4"/>
+    <tableColumn id="229" xr3:uid="{B71FFB51-4715-9F45-9BB4-F055E0B6579E}" name="Record toilet stances separated by gender, functional locks, clean floors, and handwash stations within 5 meters of exits." dataDxfId="3"/>
+    <tableColumn id="230" xr3:uid="{CFF4AA7F-A594-E644-BD64-9E6188518B37}" name="Record number of stances for boys " dataDxfId="2"/>
     <tableColumn id="209" xr3:uid="{E52E2A7C-6DA3-554D-AAF9-AFEAFE55AE6C}" name="record number of stances for girls"/>
     <tableColumn id="210" xr3:uid="{23C5A474-3E42-CF4D-B1CA-D625CD5BEB70}" name="Enclosed bins, absence of overflowing compost/litter pits or open medical/menstrual waste."/>
     <tableColumn id="211" xr3:uid="{AE3122DB-41A6-9643-8893-A6FD698F51BF}" name="Record drainage conditions around the waste collection area"/>
@@ -20052,7 +21258,7 @@
     <tableColumn id="248" xr3:uid="{5C1530A7-CA9A-4C4D-9F45-6693CADC9AE1}" name="If a classmate or family member collapses or has high fever and bleeding, who should be notified first?21"/>
     <tableColumn id="249" xr3:uid="{A2CC249A-1234-024F-A3D7-16B73F840535}" name="If a pupil returns to school after being discharged from an isolation treatment unit, how should they be treated?22"/>
     <tableColumn id="250" xr3:uid="{78ACA442-93DA-AB41-96CB-34502301F17C}" name="Demonstrate how to wash your hands properly using running water and soap.23"/>
-    <tableColumn id="251" xr3:uid="{D5D20011-7866-054C-8B43-D0949BB622FE}" name="_id" dataDxfId="4"/>
+    <tableColumn id="251" xr3:uid="{D5D20011-7866-054C-8B43-D0949BB622FE}" name="_id" dataDxfId="1"/>
     <tableColumn id="252" xr3:uid="{1F4CDE39-C604-5347-99FA-D6630307CFFA}" name="_uuid"/>
     <tableColumn id="253" xr3:uid="{D27DDB93-675C-3445-9BC8-EC9291560D20}" name="_submission_time" dataDxfId="0"/>
     <tableColumn id="254" xr3:uid="{38D71597-6EFA-C743-BB49-6EC26707B8D9}" name="_validation_status"/>
@@ -20353,7 +21559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY207"/>
+  <dimension ref="A1:IY265"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -43935,6 +45141,7167 @@
         <v>206</v>
       </c>
     </row>
+    <row r="208" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A208" s="1">
+        <v>46296.657187523153</v>
+      </c>
+      <c r="B208" s="1">
+        <v>46296.826213819448</v>
+      </c>
+      <c r="C208" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D208" t="s">
+        <v>691</v>
+      </c>
+      <c r="E208" t="s">
+        <v>210</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G208" t="s">
+        <v>198</v>
+      </c>
+      <c r="H208" t="s">
+        <v>212</v>
+      </c>
+      <c r="J208" t="s">
+        <v>1786</v>
+      </c>
+      <c r="K208" t="s">
+        <v>201</v>
+      </c>
+      <c r="L208" t="s">
+        <v>324</v>
+      </c>
+      <c r="M208" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N208" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O208" t="s">
+        <v>1710</v>
+      </c>
+      <c r="AH208">
+        <v>632</v>
+      </c>
+      <c r="AI208">
+        <v>264</v>
+      </c>
+      <c r="AJ208">
+        <v>311</v>
+      </c>
+      <c r="AK208">
+        <v>20</v>
+      </c>
+      <c r="AL208">
+        <v>3</v>
+      </c>
+      <c r="AM208">
+        <v>0</v>
+      </c>
+      <c r="AN208">
+        <v>0</v>
+      </c>
+      <c r="AO208" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AP208">
+        <v>3</v>
+      </c>
+      <c r="AQ208" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR208" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS208" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT208" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU208" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV208" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW208" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS208" t="s">
+        <v>1788</v>
+      </c>
+      <c r="BT208" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU208" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW208" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX208" t="s">
+        <v>1202</v>
+      </c>
+      <c r="EY208" s="1"/>
+      <c r="GQ208" s="1"/>
+      <c r="GR208" s="1"/>
+      <c r="GY208" s="1"/>
+      <c r="GZ208" s="1"/>
+      <c r="HA208" s="1"/>
+      <c r="HB208" s="1"/>
+      <c r="IQ208" s="1">
+        <v>883762999</v>
+      </c>
+      <c r="IR208" t="s">
+        <v>1789</v>
+      </c>
+      <c r="IS208" s="1">
+        <v>46296.701261574082</v>
+      </c>
+      <c r="IU208" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW208" t="s">
+        <v>1600</v>
+      </c>
+      <c r="IX208" t="s">
+        <v>1790</v>
+      </c>
+      <c r="IY208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A209" s="1">
+        <v>46296.826218819442</v>
+      </c>
+      <c r="B209" s="1">
+        <v>46296.838381712972</v>
+      </c>
+      <c r="C209" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D209" t="s">
+        <v>952</v>
+      </c>
+      <c r="E209" t="s">
+        <v>210</v>
+      </c>
+      <c r="F209" t="s">
+        <v>401</v>
+      </c>
+      <c r="G209" t="s">
+        <v>198</v>
+      </c>
+      <c r="H209" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS209" t="s">
+        <v>954</v>
+      </c>
+      <c r="BT209" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU209" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW209" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX209" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BY209" t="s">
+        <v>359</v>
+      </c>
+      <c r="DE209" t="s">
+        <v>957</v>
+      </c>
+      <c r="DF209" t="s">
+        <v>1396</v>
+      </c>
+      <c r="DG209">
+        <v>1</v>
+      </c>
+      <c r="DH209">
+        <v>1</v>
+      </c>
+      <c r="DI209">
+        <v>0</v>
+      </c>
+      <c r="DJ209">
+        <v>0</v>
+      </c>
+      <c r="DK209">
+        <v>0</v>
+      </c>
+      <c r="DM209" t="s">
+        <v>1791</v>
+      </c>
+      <c r="DN209" t="s">
+        <v>1792</v>
+      </c>
+      <c r="DO209" t="s">
+        <v>979</v>
+      </c>
+      <c r="DP209">
+        <v>1</v>
+      </c>
+      <c r="DQ209">
+        <v>0</v>
+      </c>
+      <c r="DR209">
+        <v>0</v>
+      </c>
+      <c r="DS209" t="s">
+        <v>1083</v>
+      </c>
+      <c r="DU209" t="s">
+        <v>1793</v>
+      </c>
+      <c r="DV209" t="s">
+        <v>1794</v>
+      </c>
+      <c r="DW209" t="s">
+        <v>1058</v>
+      </c>
+      <c r="EY209" s="1"/>
+      <c r="GQ209" s="1"/>
+      <c r="GR209" s="1"/>
+      <c r="GY209" s="1"/>
+      <c r="GZ209" s="1"/>
+      <c r="HA209" s="1"/>
+      <c r="HB209" s="1"/>
+      <c r="IQ209" s="1">
+        <v>883775489</v>
+      </c>
+      <c r="IR209" t="s">
+        <v>1795</v>
+      </c>
+      <c r="IS209" s="1">
+        <v>46296.713414351849</v>
+      </c>
+      <c r="IU209" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW209" t="s">
+        <v>1600</v>
+      </c>
+      <c r="IX209" t="s">
+        <v>1796</v>
+      </c>
+      <c r="IY209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A210" s="1">
+        <v>46296.903357361109</v>
+      </c>
+      <c r="B210" s="1">
+        <v>46296.906310636572</v>
+      </c>
+      <c r="C210" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D210" t="s">
+        <v>691</v>
+      </c>
+      <c r="E210" t="s">
+        <v>295</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G210" t="s">
+        <v>198</v>
+      </c>
+      <c r="H210" t="s">
+        <v>297</v>
+      </c>
+      <c r="J210" t="s">
+        <v>1798</v>
+      </c>
+      <c r="K210" t="s">
+        <v>201</v>
+      </c>
+      <c r="L210" t="s">
+        <v>324</v>
+      </c>
+      <c r="M210" t="s">
+        <v>612</v>
+      </c>
+      <c r="N210" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O210" t="s">
+        <v>1710</v>
+      </c>
+      <c r="AH210">
+        <v>558</v>
+      </c>
+      <c r="AI210">
+        <v>284</v>
+      </c>
+      <c r="AJ210">
+        <v>274</v>
+      </c>
+      <c r="AK210">
+        <v>14</v>
+      </c>
+      <c r="AL210">
+        <v>2</v>
+      </c>
+      <c r="AM210">
+        <v>0</v>
+      </c>
+      <c r="AN210">
+        <v>0</v>
+      </c>
+      <c r="AO210" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AP210">
+        <v>0</v>
+      </c>
+      <c r="AQ210" t="s">
+        <v>340</v>
+      </c>
+      <c r="AR210" t="s">
+        <v>341</v>
+      </c>
+      <c r="AS210" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT210" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU210" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV210" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW210" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS210" t="s">
+        <v>1799</v>
+      </c>
+      <c r="BT210" t="s">
+        <v>1800</v>
+      </c>
+      <c r="BU210" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW210" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX210" t="s">
+        <v>1801</v>
+      </c>
+      <c r="EY210" s="1"/>
+      <c r="GQ210" s="1"/>
+      <c r="GR210" s="1"/>
+      <c r="GY210" s="1"/>
+      <c r="GZ210" s="1"/>
+      <c r="HA210" s="1"/>
+      <c r="HB210" s="1"/>
+      <c r="IQ210" s="1">
+        <v>883861420</v>
+      </c>
+      <c r="IR210" t="s">
+        <v>1802</v>
+      </c>
+      <c r="IS210" s="1">
+        <v>46296.781342592592</v>
+      </c>
+      <c r="IU210" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW210" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX210" t="s">
+        <v>1804</v>
+      </c>
+      <c r="IY210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A211" s="1">
+        <v>46296.906311192128</v>
+      </c>
+      <c r="B211" s="1">
+        <v>46296.908533993053</v>
+      </c>
+      <c r="C211" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D211" t="s">
+        <v>886</v>
+      </c>
+      <c r="E211" t="s">
+        <v>295</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G211" t="s">
+        <v>198</v>
+      </c>
+      <c r="H211" t="s">
+        <v>297</v>
+      </c>
+      <c r="BS211" t="s">
+        <v>1805</v>
+      </c>
+      <c r="BT211" t="s">
+        <v>1806</v>
+      </c>
+      <c r="BU211" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV211" t="s">
+        <v>1010</v>
+      </c>
+      <c r="BW211" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX211" t="s">
+        <v>1807</v>
+      </c>
+      <c r="BY211" t="s">
+        <v>456</v>
+      </c>
+      <c r="CP211" t="s">
+        <v>1218</v>
+      </c>
+      <c r="CQ211" t="s">
+        <v>395</v>
+      </c>
+      <c r="CR211" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS211" t="s">
+        <v>940</v>
+      </c>
+      <c r="CT211" t="s">
+        <v>1344</v>
+      </c>
+      <c r="CU211">
+        <v>0</v>
+      </c>
+      <c r="CV211">
+        <v>1</v>
+      </c>
+      <c r="CW211">
+        <v>1</v>
+      </c>
+      <c r="CX211">
+        <v>0</v>
+      </c>
+      <c r="CY211">
+        <v>1</v>
+      </c>
+      <c r="CZ211">
+        <v>0</v>
+      </c>
+      <c r="DA211">
+        <v>0</v>
+      </c>
+      <c r="DC211" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY211" s="1"/>
+      <c r="GQ211" s="1"/>
+      <c r="GR211" s="1"/>
+      <c r="GY211" s="1"/>
+      <c r="GZ211" s="1"/>
+      <c r="HA211" s="1"/>
+      <c r="HB211" s="1"/>
+      <c r="IQ211" s="1">
+        <v>883864451</v>
+      </c>
+      <c r="IR211" t="s">
+        <v>1808</v>
+      </c>
+      <c r="IS211" s="1">
+        <v>46296.783553240741</v>
+      </c>
+      <c r="IU211" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW211" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX211" t="s">
+        <v>1809</v>
+      </c>
+      <c r="IY211">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A212" s="1">
+        <v>46296.908534444447</v>
+      </c>
+      <c r="B212" s="1">
+        <v>46296.912112175924</v>
+      </c>
+      <c r="C212" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D212" t="s">
+        <v>776</v>
+      </c>
+      <c r="E212" t="s">
+        <v>295</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G212" t="s">
+        <v>198</v>
+      </c>
+      <c r="H212" t="s">
+        <v>297</v>
+      </c>
+      <c r="BS212" t="s">
+        <v>1617</v>
+      </c>
+      <c r="BT212" t="s">
+        <v>1810</v>
+      </c>
+      <c r="BU212" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW212" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX212" t="s">
+        <v>1811</v>
+      </c>
+      <c r="EY212" s="1"/>
+      <c r="GJ212" s="1">
+        <v>46296</v>
+      </c>
+      <c r="GK212" t="s">
+        <v>1798</v>
+      </c>
+      <c r="GL212" t="s">
+        <v>416</v>
+      </c>
+      <c r="GN212">
+        <v>284</v>
+      </c>
+      <c r="GO212">
+        <v>274</v>
+      </c>
+      <c r="GP212">
+        <v>6</v>
+      </c>
+      <c r="GQ212" s="1">
+        <v>8</v>
+      </c>
+      <c r="GR212" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="GS212" t="s">
+        <v>426</v>
+      </c>
+      <c r="GT212" t="s">
+        <v>377</v>
+      </c>
+      <c r="GU212" t="s">
+        <v>378</v>
+      </c>
+      <c r="GV212" t="s">
+        <v>428</v>
+      </c>
+      <c r="GX212" t="s">
+        <v>429</v>
+      </c>
+      <c r="GY212" s="1">
+        <v>4</v>
+      </c>
+      <c r="GZ212" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="HA212" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="HB212" s="1">
+        <v>9</v>
+      </c>
+      <c r="HC212">
+        <v>9</v>
+      </c>
+      <c r="HD212" t="s">
+        <v>419</v>
+      </c>
+      <c r="HE212" t="s">
+        <v>450</v>
+      </c>
+      <c r="HF212" t="s">
+        <v>477</v>
+      </c>
+      <c r="HG212">
+        <v>0</v>
+      </c>
+      <c r="HH212">
+        <v>1</v>
+      </c>
+      <c r="HI212">
+        <v>0</v>
+      </c>
+      <c r="HJ212">
+        <v>0</v>
+      </c>
+      <c r="HK212" t="s">
+        <v>395</v>
+      </c>
+      <c r="HM212">
+        <v>5</v>
+      </c>
+      <c r="HN212">
+        <v>5</v>
+      </c>
+      <c r="HO212">
+        <v>2</v>
+      </c>
+      <c r="HP212">
+        <v>8</v>
+      </c>
+      <c r="HQ212">
+        <v>3</v>
+      </c>
+      <c r="HR212">
+        <v>4</v>
+      </c>
+      <c r="IQ212" s="1">
+        <v>883868242</v>
+      </c>
+      <c r="IR212" t="s">
+        <v>1812</v>
+      </c>
+      <c r="IS212" s="1">
+        <v>46296.787129629629</v>
+      </c>
+      <c r="IU212" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW212" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX212" t="s">
+        <v>1813</v>
+      </c>
+      <c r="IY212">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A213" s="1">
+        <v>46297.307513391213</v>
+      </c>
+      <c r="B213" s="1">
+        <v>46297.323723969908</v>
+      </c>
+      <c r="C213" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D213" t="s">
+        <v>691</v>
+      </c>
+      <c r="E213" t="s">
+        <v>254</v>
+      </c>
+      <c r="F213" t="s">
+        <v>271</v>
+      </c>
+      <c r="G213" t="s">
+        <v>198</v>
+      </c>
+      <c r="H213" t="s">
+        <v>256</v>
+      </c>
+      <c r="J213" t="s">
+        <v>415</v>
+      </c>
+      <c r="K213" t="s">
+        <v>201</v>
+      </c>
+      <c r="L213" t="s">
+        <v>324</v>
+      </c>
+      <c r="M213" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N213" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O213" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R213">
+        <v>5</v>
+      </c>
+      <c r="S213">
+        <v>5</v>
+      </c>
+      <c r="T213" t="s">
+        <v>1815</v>
+      </c>
+      <c r="U213" t="s">
+        <v>1816</v>
+      </c>
+      <c r="V213">
+        <v>0</v>
+      </c>
+      <c r="W213">
+        <v>0</v>
+      </c>
+      <c r="X213">
+        <v>0</v>
+      </c>
+      <c r="Y213">
+        <v>1</v>
+      </c>
+      <c r="Z213">
+        <v>0</v>
+      </c>
+      <c r="AA213">
+        <v>0</v>
+      </c>
+      <c r="AB213" t="s">
+        <v>1817</v>
+      </c>
+      <c r="AC213">
+        <v>1</v>
+      </c>
+      <c r="AD213">
+        <v>0</v>
+      </c>
+      <c r="AE213">
+        <v>0</v>
+      </c>
+      <c r="AF213">
+        <v>0</v>
+      </c>
+      <c r="AG213">
+        <v>0</v>
+      </c>
+      <c r="AH213">
+        <v>430</v>
+      </c>
+      <c r="AI213">
+        <v>186</v>
+      </c>
+      <c r="AJ213">
+        <v>129</v>
+      </c>
+      <c r="AK213">
+        <v>5</v>
+      </c>
+      <c r="AL213">
+        <v>2</v>
+      </c>
+      <c r="AM213">
+        <v>0</v>
+      </c>
+      <c r="AN213">
+        <v>0</v>
+      </c>
+      <c r="AO213" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP213">
+        <v>0</v>
+      </c>
+      <c r="AQ213" t="s">
+        <v>340</v>
+      </c>
+      <c r="AR213" t="s">
+        <v>341</v>
+      </c>
+      <c r="AS213" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT213" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU213" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV213" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW213" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS213" t="s">
+        <v>1818</v>
+      </c>
+      <c r="BT213" t="s">
+        <v>1819</v>
+      </c>
+      <c r="BU213" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW213" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX213" t="s">
+        <v>1820</v>
+      </c>
+      <c r="EY213" s="1"/>
+      <c r="GQ213" s="1"/>
+      <c r="GR213" s="1"/>
+      <c r="GY213" s="1"/>
+      <c r="GZ213" s="1"/>
+      <c r="HA213" s="1"/>
+      <c r="HB213" s="1"/>
+      <c r="IQ213" s="1">
+        <v>884066747</v>
+      </c>
+      <c r="IR213" t="s">
+        <v>1821</v>
+      </c>
+      <c r="IS213" s="1">
+        <v>46297.198738425926</v>
+      </c>
+      <c r="IU213" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW213" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX213" t="s">
+        <v>1822</v>
+      </c>
+      <c r="IY213">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A214" s="1">
+        <v>46296.695491331018</v>
+      </c>
+      <c r="B214" s="1">
+        <v>46297.523458993062</v>
+      </c>
+      <c r="C214" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D214" t="s">
+        <v>690</v>
+      </c>
+      <c r="E214" t="s">
+        <v>237</v>
+      </c>
+      <c r="F214" t="s">
+        <v>248</v>
+      </c>
+      <c r="G214" t="s">
+        <v>198</v>
+      </c>
+      <c r="H214" t="s">
+        <v>240</v>
+      </c>
+      <c r="AX214" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY214" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ214" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA214" t="s">
+        <v>1823</v>
+      </c>
+      <c r="BB214">
+        <v>1</v>
+      </c>
+      <c r="BC214">
+        <v>0</v>
+      </c>
+      <c r="BD214" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE214" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF214" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG214" t="s">
+        <v>1824</v>
+      </c>
+      <c r="BH214" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI214" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ214" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK214">
+        <v>5</v>
+      </c>
+      <c r="BL214" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM214">
+        <v>45</v>
+      </c>
+      <c r="BN214">
+        <v>50</v>
+      </c>
+      <c r="BO214" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP214" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ214" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS214" t="s">
+        <v>1825</v>
+      </c>
+      <c r="BT214" t="s">
+        <v>727</v>
+      </c>
+      <c r="BU214" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV214" t="s">
+        <v>1826</v>
+      </c>
+      <c r="BW214" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX214" t="s">
+        <v>1827</v>
+      </c>
+      <c r="EY214" s="1"/>
+      <c r="GQ214" s="1"/>
+      <c r="GR214" s="1"/>
+      <c r="GY214" s="1"/>
+      <c r="GZ214" s="1"/>
+      <c r="HA214" s="1"/>
+      <c r="HB214" s="1"/>
+      <c r="IQ214" s="1">
+        <v>884222422</v>
+      </c>
+      <c r="IR214" t="s">
+        <v>1828</v>
+      </c>
+      <c r="IS214" s="1">
+        <v>46297.3984837963</v>
+      </c>
+      <c r="IU214" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW214" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX214" t="s">
+        <v>1829</v>
+      </c>
+      <c r="IY214">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A215" s="1">
+        <v>46296.838384155089</v>
+      </c>
+      <c r="B215" s="1">
+        <v>46297.57576313657</v>
+      </c>
+      <c r="C215" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D215" t="s">
+        <v>690</v>
+      </c>
+      <c r="E215" t="s">
+        <v>210</v>
+      </c>
+      <c r="F215" t="s">
+        <v>970</v>
+      </c>
+      <c r="G215" t="s">
+        <v>198</v>
+      </c>
+      <c r="H215" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX215" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY215" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ215" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA215" t="s">
+        <v>1832</v>
+      </c>
+      <c r="BB215">
+        <v>12</v>
+      </c>
+      <c r="BC215">
+        <v>6</v>
+      </c>
+      <c r="BD215" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE215" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF215" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG215" t="s">
+        <v>1833</v>
+      </c>
+      <c r="BH215" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI215" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ215" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK215">
+        <v>4</v>
+      </c>
+      <c r="BL215" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM215">
+        <v>200</v>
+      </c>
+      <c r="BN215">
+        <v>165</v>
+      </c>
+      <c r="BO215" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP215" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ215" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS215" t="s">
+        <v>1834</v>
+      </c>
+      <c r="BT215" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU215" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV215" t="s">
+        <v>1835</v>
+      </c>
+      <c r="BW215" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX215" t="s">
+        <v>1408</v>
+      </c>
+      <c r="EY215" s="1"/>
+      <c r="GQ215" s="1"/>
+      <c r="GR215" s="1"/>
+      <c r="GY215" s="1"/>
+      <c r="GZ215" s="1"/>
+      <c r="HA215" s="1"/>
+      <c r="HB215" s="1"/>
+      <c r="IQ215" s="1">
+        <v>884275941</v>
+      </c>
+      <c r="IR215" t="s">
+        <v>1836</v>
+      </c>
+      <c r="IS215" s="1">
+        <v>46297.450833333343</v>
+      </c>
+      <c r="IU215" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW215" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX215" t="s">
+        <v>1837</v>
+      </c>
+      <c r="IY215">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A216" s="1">
+        <v>46297.595784861107</v>
+      </c>
+      <c r="B216" s="1">
+        <v>46297.59977896991</v>
+      </c>
+      <c r="C216" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D216" t="s">
+        <v>886</v>
+      </c>
+      <c r="E216" t="s">
+        <v>280</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1838</v>
+      </c>
+      <c r="G216" t="s">
+        <v>198</v>
+      </c>
+      <c r="H216" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS216" t="s">
+        <v>1839</v>
+      </c>
+      <c r="BT216" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU216" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV216" t="s">
+        <v>1840</v>
+      </c>
+      <c r="BW216" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX216" t="s">
+        <v>1841</v>
+      </c>
+      <c r="BY216" t="s">
+        <v>930</v>
+      </c>
+      <c r="CP216" t="s">
+        <v>890</v>
+      </c>
+      <c r="CT216" t="s">
+        <v>904</v>
+      </c>
+      <c r="CU216">
+        <v>0</v>
+      </c>
+      <c r="CV216">
+        <v>0</v>
+      </c>
+      <c r="CW216">
+        <v>1</v>
+      </c>
+      <c r="CX216">
+        <v>0</v>
+      </c>
+      <c r="CY216">
+        <v>0</v>
+      </c>
+      <c r="CZ216">
+        <v>0</v>
+      </c>
+      <c r="DA216">
+        <v>0</v>
+      </c>
+      <c r="DC216" t="s">
+        <v>905</v>
+      </c>
+      <c r="EY216" s="1"/>
+      <c r="GQ216" s="1"/>
+      <c r="GR216" s="1"/>
+      <c r="GY216" s="1"/>
+      <c r="GZ216" s="1"/>
+      <c r="HA216" s="1"/>
+      <c r="HB216" s="1"/>
+      <c r="IQ216" s="1">
+        <v>884293982</v>
+      </c>
+      <c r="IR216" t="s">
+        <v>1842</v>
+      </c>
+      <c r="IS216" s="1">
+        <v>46297.466597222221</v>
+      </c>
+      <c r="IU216" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW216" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX216" t="s">
+        <v>1843</v>
+      </c>
+      <c r="IY216">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A217" s="1">
+        <v>46297.603049039353</v>
+      </c>
+      <c r="B217" s="1">
+        <v>46297.609141956018</v>
+      </c>
+      <c r="C217" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D217" t="s">
+        <v>952</v>
+      </c>
+      <c r="E217" t="s">
+        <v>280</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1838</v>
+      </c>
+      <c r="G217" t="s">
+        <v>198</v>
+      </c>
+      <c r="H217" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS217" t="s">
+        <v>1844</v>
+      </c>
+      <c r="BT217" t="s">
+        <v>1845</v>
+      </c>
+      <c r="BU217" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW217" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX217" t="s">
+        <v>1846</v>
+      </c>
+      <c r="BY217" t="s">
+        <v>930</v>
+      </c>
+      <c r="DE217" t="s">
+        <v>1069</v>
+      </c>
+      <c r="DF217" t="s">
+        <v>1090</v>
+      </c>
+      <c r="DG217">
+        <v>1</v>
+      </c>
+      <c r="DH217">
+        <v>0</v>
+      </c>
+      <c r="DI217">
+        <v>0</v>
+      </c>
+      <c r="DJ217">
+        <v>0</v>
+      </c>
+      <c r="DK217">
+        <v>0</v>
+      </c>
+      <c r="DM217" t="s">
+        <v>1847</v>
+      </c>
+      <c r="DN217" t="s">
+        <v>1848</v>
+      </c>
+      <c r="DO217" t="s">
+        <v>979</v>
+      </c>
+      <c r="DP217">
+        <v>1</v>
+      </c>
+      <c r="DQ217">
+        <v>0</v>
+      </c>
+      <c r="DR217">
+        <v>0</v>
+      </c>
+      <c r="DS217" t="s">
+        <v>980</v>
+      </c>
+      <c r="EY217" s="1"/>
+      <c r="GQ217" s="1"/>
+      <c r="GR217" s="1"/>
+      <c r="GY217" s="1"/>
+      <c r="GZ217" s="1"/>
+      <c r="HA217" s="1"/>
+      <c r="HB217" s="1"/>
+      <c r="IQ217" s="1">
+        <v>884305401</v>
+      </c>
+      <c r="IR217" t="s">
+        <v>1849</v>
+      </c>
+      <c r="IS217" s="1">
+        <v>46297.475960648153</v>
+      </c>
+      <c r="IU217" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW217" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX217" t="s">
+        <v>1850</v>
+      </c>
+      <c r="IY217">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A218" s="1">
+        <v>46297.523460810182</v>
+      </c>
+      <c r="B218" s="1">
+        <v>46297.611049826388</v>
+      </c>
+      <c r="C218" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D218" t="s">
+        <v>952</v>
+      </c>
+      <c r="E218" t="s">
+        <v>237</v>
+      </c>
+      <c r="F218" t="s">
+        <v>742</v>
+      </c>
+      <c r="G218" t="s">
+        <v>198</v>
+      </c>
+      <c r="H218" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS218" t="s">
+        <v>1851</v>
+      </c>
+      <c r="BT218" t="s">
+        <v>1712</v>
+      </c>
+      <c r="BU218" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV218" t="s">
+        <v>1852</v>
+      </c>
+      <c r="BW218" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX218" t="s">
+        <v>883</v>
+      </c>
+      <c r="BY218" t="s">
+        <v>561</v>
+      </c>
+      <c r="DE218" t="s">
+        <v>775</v>
+      </c>
+      <c r="DF218" t="s">
+        <v>1853</v>
+      </c>
+      <c r="DG218">
+        <v>0</v>
+      </c>
+      <c r="DH218">
+        <v>1</v>
+      </c>
+      <c r="DI218">
+        <v>1</v>
+      </c>
+      <c r="DJ218">
+        <v>1</v>
+      </c>
+      <c r="DK218">
+        <v>1</v>
+      </c>
+      <c r="DU218" t="s">
+        <v>1854</v>
+      </c>
+      <c r="DV218" t="s">
+        <v>1855</v>
+      </c>
+      <c r="DW218" t="s">
+        <v>1073</v>
+      </c>
+      <c r="DY218" t="s">
+        <v>962</v>
+      </c>
+      <c r="DZ218" t="s">
+        <v>1856</v>
+      </c>
+      <c r="EA218" t="s">
+        <v>964</v>
+      </c>
+      <c r="EC218" t="s">
+        <v>1857</v>
+      </c>
+      <c r="ED218" t="s">
+        <v>1858</v>
+      </c>
+      <c r="EE218" t="s">
+        <v>1061</v>
+      </c>
+      <c r="EG218" t="s">
+        <v>1859</v>
+      </c>
+      <c r="EH218" t="s">
+        <v>1860</v>
+      </c>
+      <c r="EI218" t="s">
+        <v>983</v>
+      </c>
+      <c r="EY218" s="1"/>
+      <c r="GQ218" s="1"/>
+      <c r="GR218" s="1"/>
+      <c r="GY218" s="1"/>
+      <c r="GZ218" s="1"/>
+      <c r="HA218" s="1"/>
+      <c r="HB218" s="1"/>
+      <c r="IQ218" s="1">
+        <v>884317779</v>
+      </c>
+      <c r="IR218" t="s">
+        <v>1861</v>
+      </c>
+      <c r="IS218" s="1">
+        <v>46297.486076388886</v>
+      </c>
+      <c r="IU218" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW218" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX218" t="s">
+        <v>1862</v>
+      </c>
+      <c r="IY218">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A219" s="1">
+        <v>46297.616067442133</v>
+      </c>
+      <c r="B219" s="1">
+        <v>46297.621636481483</v>
+      </c>
+      <c r="C219" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D219" t="s">
+        <v>952</v>
+      </c>
+      <c r="E219" t="s">
+        <v>280</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1838</v>
+      </c>
+      <c r="G219" t="s">
+        <v>198</v>
+      </c>
+      <c r="H219" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS219" t="s">
+        <v>1863</v>
+      </c>
+      <c r="BT219" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU219" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV219" t="s">
+        <v>1864</v>
+      </c>
+      <c r="BW219" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX219" t="s">
+        <v>1865</v>
+      </c>
+      <c r="BY219" t="s">
+        <v>456</v>
+      </c>
+      <c r="DE219" t="s">
+        <v>1289</v>
+      </c>
+      <c r="DF219" t="s">
+        <v>1404</v>
+      </c>
+      <c r="DG219">
+        <v>0</v>
+      </c>
+      <c r="DH219">
+        <v>0</v>
+      </c>
+      <c r="DI219">
+        <v>1</v>
+      </c>
+      <c r="DJ219">
+        <v>0</v>
+      </c>
+      <c r="DK219">
+        <v>0</v>
+      </c>
+      <c r="DY219" t="s">
+        <v>1391</v>
+      </c>
+      <c r="DZ219" t="s">
+        <v>1866</v>
+      </c>
+      <c r="EA219" t="s">
+        <v>1867</v>
+      </c>
+      <c r="EY219" s="1"/>
+      <c r="GQ219" s="1"/>
+      <c r="GR219" s="1"/>
+      <c r="GY219" s="1"/>
+      <c r="GZ219" s="1"/>
+      <c r="HA219" s="1"/>
+      <c r="HB219" s="1"/>
+      <c r="IQ219" s="1">
+        <v>884320488</v>
+      </c>
+      <c r="IR219" t="s">
+        <v>1868</v>
+      </c>
+      <c r="IS219" s="1">
+        <v>46297.488449074073</v>
+      </c>
+      <c r="IU219" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW219" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX219" t="s">
+        <v>1869</v>
+      </c>
+      <c r="IY219">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A220" s="1">
+        <v>46297.611051006941</v>
+      </c>
+      <c r="B220" s="1">
+        <v>46297.62155783565</v>
+      </c>
+      <c r="C220" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D220" t="s">
+        <v>952</v>
+      </c>
+      <c r="E220" t="s">
+        <v>237</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G220" t="s">
+        <v>198</v>
+      </c>
+      <c r="H220" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS220" t="s">
+        <v>1871</v>
+      </c>
+      <c r="BT220" t="s">
+        <v>727</v>
+      </c>
+      <c r="BU220" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV220" t="s">
+        <v>897</v>
+      </c>
+      <c r="BW220" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX220" t="s">
+        <v>1872</v>
+      </c>
+      <c r="BY220" t="s">
+        <v>456</v>
+      </c>
+      <c r="DE220" t="s">
+        <v>1289</v>
+      </c>
+      <c r="DF220" t="s">
+        <v>958</v>
+      </c>
+      <c r="DG220">
+        <v>0</v>
+      </c>
+      <c r="DH220">
+        <v>1</v>
+      </c>
+      <c r="DI220">
+        <v>1</v>
+      </c>
+      <c r="DJ220">
+        <v>0</v>
+      </c>
+      <c r="DK220">
+        <v>1</v>
+      </c>
+      <c r="DU220" t="s">
+        <v>1873</v>
+      </c>
+      <c r="DV220" t="s">
+        <v>1874</v>
+      </c>
+      <c r="DW220" t="s">
+        <v>1058</v>
+      </c>
+      <c r="DY220" t="s">
+        <v>1391</v>
+      </c>
+      <c r="DZ220" t="s">
+        <v>1875</v>
+      </c>
+      <c r="EA220" t="s">
+        <v>1086</v>
+      </c>
+      <c r="EG220" t="s">
+        <v>1876</v>
+      </c>
+      <c r="EH220" t="s">
+        <v>1877</v>
+      </c>
+      <c r="EI220" t="s">
+        <v>983</v>
+      </c>
+      <c r="EY220" s="1"/>
+      <c r="GQ220" s="1"/>
+      <c r="GR220" s="1"/>
+      <c r="GY220" s="1"/>
+      <c r="GZ220" s="1"/>
+      <c r="HA220" s="1"/>
+      <c r="HB220" s="1"/>
+      <c r="IQ220" s="1">
+        <v>884329703</v>
+      </c>
+      <c r="IR220" t="s">
+        <v>1878</v>
+      </c>
+      <c r="IS220" s="1">
+        <v>46297.49659722222</v>
+      </c>
+      <c r="IU220" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW220" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX220" t="s">
+        <v>1879</v>
+      </c>
+      <c r="IY220">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A221" s="1">
+        <v>46297.623010995369</v>
+      </c>
+      <c r="B221" s="1">
+        <v>46297.629228090278</v>
+      </c>
+      <c r="C221" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D221" t="s">
+        <v>886</v>
+      </c>
+      <c r="E221" t="s">
+        <v>237</v>
+      </c>
+      <c r="F221" t="s">
+        <v>248</v>
+      </c>
+      <c r="G221" t="s">
+        <v>198</v>
+      </c>
+      <c r="H221" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS221" t="s">
+        <v>1880</v>
+      </c>
+      <c r="BT221" t="s">
+        <v>1881</v>
+      </c>
+      <c r="BU221" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV221" t="s">
+        <v>1882</v>
+      </c>
+      <c r="BW221" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX221" t="s">
+        <v>1883</v>
+      </c>
+      <c r="BY221" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP221" t="s">
+        <v>890</v>
+      </c>
+      <c r="CT221" t="s">
+        <v>912</v>
+      </c>
+      <c r="CU221">
+        <v>0</v>
+      </c>
+      <c r="CV221">
+        <v>1</v>
+      </c>
+      <c r="CW221">
+        <v>0</v>
+      </c>
+      <c r="CX221">
+        <v>0</v>
+      </c>
+      <c r="CY221">
+        <v>0</v>
+      </c>
+      <c r="CZ221">
+        <v>0</v>
+      </c>
+      <c r="DA221">
+        <v>0</v>
+      </c>
+      <c r="DC221" t="s">
+        <v>1739</v>
+      </c>
+      <c r="EY221" s="1"/>
+      <c r="GQ221" s="1"/>
+      <c r="GR221" s="1"/>
+      <c r="GY221" s="1"/>
+      <c r="GZ221" s="1"/>
+      <c r="HA221" s="1"/>
+      <c r="HB221" s="1"/>
+      <c r="IQ221" s="1">
+        <v>884338842</v>
+      </c>
+      <c r="IR221" t="s">
+        <v>1884</v>
+      </c>
+      <c r="IS221" s="1">
+        <v>46297.504259259258</v>
+      </c>
+      <c r="IU221" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW221" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX221" t="s">
+        <v>1885</v>
+      </c>
+      <c r="IY221">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A222" s="1">
+        <v>46297.629230914346</v>
+      </c>
+      <c r="B222" s="1">
+        <v>46297.636683217592</v>
+      </c>
+      <c r="C222" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D222" t="s">
+        <v>952</v>
+      </c>
+      <c r="E222" t="s">
+        <v>237</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G222" t="s">
+        <v>198</v>
+      </c>
+      <c r="H222" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS222" t="s">
+        <v>1886</v>
+      </c>
+      <c r="BT222" t="s">
+        <v>1887</v>
+      </c>
+      <c r="BU222" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV222" t="s">
+        <v>1888</v>
+      </c>
+      <c r="BW222" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX222" t="s">
+        <v>1889</v>
+      </c>
+      <c r="BY222" t="s">
+        <v>456</v>
+      </c>
+      <c r="DE222" t="s">
+        <v>1069</v>
+      </c>
+      <c r="DF222" t="s">
+        <v>1070</v>
+      </c>
+      <c r="DG222">
+        <v>0</v>
+      </c>
+      <c r="DH222">
+        <v>1</v>
+      </c>
+      <c r="DI222">
+        <v>0</v>
+      </c>
+      <c r="DJ222">
+        <v>1</v>
+      </c>
+      <c r="DK222">
+        <v>0</v>
+      </c>
+      <c r="DU222" t="s">
+        <v>1890</v>
+      </c>
+      <c r="DV222" t="s">
+        <v>1891</v>
+      </c>
+      <c r="DW222" t="s">
+        <v>1073</v>
+      </c>
+      <c r="EC222" t="s">
+        <v>1892</v>
+      </c>
+      <c r="ED222" t="s">
+        <v>395</v>
+      </c>
+      <c r="EE222" t="s">
+        <v>1061</v>
+      </c>
+      <c r="EY222" s="1"/>
+      <c r="GQ222" s="1"/>
+      <c r="GR222" s="1"/>
+      <c r="GY222" s="1"/>
+      <c r="GZ222" s="1"/>
+      <c r="HA222" s="1"/>
+      <c r="HB222" s="1"/>
+      <c r="IQ222" s="1">
+        <v>884348130</v>
+      </c>
+      <c r="IR222" t="s">
+        <v>1893</v>
+      </c>
+      <c r="IS222" s="1">
+        <v>46297.511712962973</v>
+      </c>
+      <c r="IU222" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW222" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX222" t="s">
+        <v>1894</v>
+      </c>
+      <c r="IY222">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A223" s="1">
+        <v>46297.625507025463</v>
+      </c>
+      <c r="B223" s="1">
+        <v>46297.642066782413</v>
+      </c>
+      <c r="C223" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D223" t="s">
+        <v>886</v>
+      </c>
+      <c r="E223" t="s">
+        <v>237</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1895</v>
+      </c>
+      <c r="G223" t="s">
+        <v>198</v>
+      </c>
+      <c r="H223" t="s">
+        <v>1896</v>
+      </c>
+      <c r="BS223" t="s">
+        <v>1897</v>
+      </c>
+      <c r="BT223" t="s">
+        <v>1898</v>
+      </c>
+      <c r="BU223" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW223" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX223" t="s">
+        <v>1899</v>
+      </c>
+      <c r="BY223" t="s">
+        <v>930</v>
+      </c>
+      <c r="CP223" t="s">
+        <v>938</v>
+      </c>
+      <c r="CQ223" t="s">
+        <v>1900</v>
+      </c>
+      <c r="CR223" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS223" t="s">
+        <v>903</v>
+      </c>
+      <c r="CT223" t="s">
+        <v>912</v>
+      </c>
+      <c r="CU223">
+        <v>0</v>
+      </c>
+      <c r="CV223">
+        <v>1</v>
+      </c>
+      <c r="CW223">
+        <v>0</v>
+      </c>
+      <c r="CX223">
+        <v>0</v>
+      </c>
+      <c r="CY223">
+        <v>0</v>
+      </c>
+      <c r="CZ223">
+        <v>0</v>
+      </c>
+      <c r="DA223">
+        <v>0</v>
+      </c>
+      <c r="DC223" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY223" s="1"/>
+      <c r="GQ223" s="1"/>
+      <c r="GR223" s="1"/>
+      <c r="GY223" s="1"/>
+      <c r="GZ223" s="1"/>
+      <c r="HA223" s="1"/>
+      <c r="HB223" s="1"/>
+      <c r="IQ223" s="1">
+        <v>884354487</v>
+      </c>
+      <c r="IR223" t="s">
+        <v>1901</v>
+      </c>
+      <c r="IS223" s="1">
+        <v>46297.517094907409</v>
+      </c>
+      <c r="IU223" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW223" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX223" t="s">
+        <v>1902</v>
+      </c>
+      <c r="IY223">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A224" s="1">
+        <v>46297.636685254627</v>
+      </c>
+      <c r="B224" s="1">
+        <v>46297.642085659732</v>
+      </c>
+      <c r="C224" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D224" t="s">
+        <v>952</v>
+      </c>
+      <c r="E224" t="s">
+        <v>237</v>
+      </c>
+      <c r="F224" t="s">
+        <v>248</v>
+      </c>
+      <c r="G224" t="s">
+        <v>198</v>
+      </c>
+      <c r="H224" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS224" t="s">
+        <v>1903</v>
+      </c>
+      <c r="BT224" t="s">
+        <v>1712</v>
+      </c>
+      <c r="BU224" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV224" t="s">
+        <v>1904</v>
+      </c>
+      <c r="BW224" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX224" t="s">
+        <v>883</v>
+      </c>
+      <c r="BY224" t="s">
+        <v>930</v>
+      </c>
+      <c r="DE224" t="s">
+        <v>1069</v>
+      </c>
+      <c r="DF224" t="s">
+        <v>1905</v>
+      </c>
+      <c r="DG224">
+        <v>0</v>
+      </c>
+      <c r="DH224">
+        <v>0</v>
+      </c>
+      <c r="DI224">
+        <v>0</v>
+      </c>
+      <c r="DJ224">
+        <v>1</v>
+      </c>
+      <c r="DK224">
+        <v>0</v>
+      </c>
+      <c r="EC224" t="s">
+        <v>1906</v>
+      </c>
+      <c r="ED224" t="s">
+        <v>395</v>
+      </c>
+      <c r="EE224" t="s">
+        <v>1061</v>
+      </c>
+      <c r="EY224" s="1"/>
+      <c r="GQ224" s="1"/>
+      <c r="GR224" s="1"/>
+      <c r="GY224" s="1"/>
+      <c r="GZ224" s="1"/>
+      <c r="HA224" s="1"/>
+      <c r="HB224" s="1"/>
+      <c r="IQ224" s="1">
+        <v>884354508</v>
+      </c>
+      <c r="IR224" t="s">
+        <v>1907</v>
+      </c>
+      <c r="IS224" s="1">
+        <v>46297.517118055563</v>
+      </c>
+      <c r="IU224" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW224" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX224" t="s">
+        <v>1908</v>
+      </c>
+      <c r="IY224">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A225" s="1">
+        <v>46297.642068576388</v>
+      </c>
+      <c r="B225" s="1">
+        <v>46297.645295543982</v>
+      </c>
+      <c r="C225" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D225" t="s">
+        <v>886</v>
+      </c>
+      <c r="E225" t="s">
+        <v>237</v>
+      </c>
+      <c r="F225" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G225" t="s">
+        <v>198</v>
+      </c>
+      <c r="H225" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS225" t="s">
+        <v>1910</v>
+      </c>
+      <c r="BT225" t="s">
+        <v>1911</v>
+      </c>
+      <c r="BU225" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW225" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX225" t="s">
+        <v>1912</v>
+      </c>
+      <c r="BY225" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP225" t="s">
+        <v>890</v>
+      </c>
+      <c r="CT225" t="s">
+        <v>904</v>
+      </c>
+      <c r="CU225">
+        <v>0</v>
+      </c>
+      <c r="CV225">
+        <v>0</v>
+      </c>
+      <c r="CW225">
+        <v>1</v>
+      </c>
+      <c r="CX225">
+        <v>0</v>
+      </c>
+      <c r="CY225">
+        <v>0</v>
+      </c>
+      <c r="CZ225">
+        <v>0</v>
+      </c>
+      <c r="DA225">
+        <v>0</v>
+      </c>
+      <c r="DC225" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY225" s="1"/>
+      <c r="GQ225" s="1"/>
+      <c r="GR225" s="1"/>
+      <c r="GY225" s="1"/>
+      <c r="GZ225" s="1"/>
+      <c r="HA225" s="1"/>
+      <c r="HB225" s="1"/>
+      <c r="IQ225" s="1">
+        <v>884358611</v>
+      </c>
+      <c r="IR225" t="s">
+        <v>1913</v>
+      </c>
+      <c r="IS225" s="1">
+        <v>46297.520312499997</v>
+      </c>
+      <c r="IU225" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW225" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX225" t="s">
+        <v>1914</v>
+      </c>
+      <c r="IY225">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A226" s="1">
+        <v>46297.642087673608</v>
+      </c>
+      <c r="B226" s="1">
+        <v>46297.645586828701</v>
+      </c>
+      <c r="C226" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D226" t="s">
+        <v>886</v>
+      </c>
+      <c r="E226" t="s">
+        <v>237</v>
+      </c>
+      <c r="F226" t="s">
+        <v>248</v>
+      </c>
+      <c r="G226" t="s">
+        <v>198</v>
+      </c>
+      <c r="H226" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS226" t="s">
+        <v>1915</v>
+      </c>
+      <c r="BT226" t="s">
+        <v>1916</v>
+      </c>
+      <c r="BU226" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW226" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX226" t="s">
+        <v>883</v>
+      </c>
+      <c r="BY226" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP226" t="s">
+        <v>890</v>
+      </c>
+      <c r="CT226" t="s">
+        <v>809</v>
+      </c>
+      <c r="CU226">
+        <v>0</v>
+      </c>
+      <c r="CV226">
+        <v>0</v>
+      </c>
+      <c r="CW226">
+        <v>0</v>
+      </c>
+      <c r="CX226">
+        <v>0</v>
+      </c>
+      <c r="CY226">
+        <v>0</v>
+      </c>
+      <c r="CZ226">
+        <v>0</v>
+      </c>
+      <c r="DA226">
+        <v>1</v>
+      </c>
+      <c r="DB226" t="s">
+        <v>1917</v>
+      </c>
+      <c r="DC226" t="s">
+        <v>905</v>
+      </c>
+      <c r="EY226" s="1"/>
+      <c r="GQ226" s="1"/>
+      <c r="GR226" s="1"/>
+      <c r="GY226" s="1"/>
+      <c r="GZ226" s="1"/>
+      <c r="HA226" s="1"/>
+      <c r="HB226" s="1"/>
+      <c r="IQ226" s="1">
+        <v>884359010</v>
+      </c>
+      <c r="IR226" t="s">
+        <v>1918</v>
+      </c>
+      <c r="IS226" s="1">
+        <v>46297.520613425928</v>
+      </c>
+      <c r="IU226" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW226" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX226" t="s">
+        <v>1919</v>
+      </c>
+      <c r="IY226">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A227" s="1">
+        <v>46297.645297141207</v>
+      </c>
+      <c r="B227" s="1">
+        <v>46297.647904282407</v>
+      </c>
+      <c r="C227" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D227" t="s">
+        <v>886</v>
+      </c>
+      <c r="E227" t="s">
+        <v>237</v>
+      </c>
+      <c r="F227" t="s">
+        <v>1920</v>
+      </c>
+      <c r="G227" t="s">
+        <v>198</v>
+      </c>
+      <c r="H227" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS227" t="s">
+        <v>1921</v>
+      </c>
+      <c r="BT227" t="s">
+        <v>1922</v>
+      </c>
+      <c r="BU227" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW227" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX227" t="s">
+        <v>1923</v>
+      </c>
+      <c r="BY227" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP227" t="s">
+        <v>938</v>
+      </c>
+      <c r="CQ227" t="s">
+        <v>1924</v>
+      </c>
+      <c r="CR227" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS227" t="s">
+        <v>903</v>
+      </c>
+      <c r="CT227" t="s">
+        <v>1125</v>
+      </c>
+      <c r="CU227">
+        <v>0</v>
+      </c>
+      <c r="CV227">
+        <v>1</v>
+      </c>
+      <c r="CW227">
+        <v>0</v>
+      </c>
+      <c r="CX227">
+        <v>1</v>
+      </c>
+      <c r="CY227">
+        <v>0</v>
+      </c>
+      <c r="CZ227">
+        <v>0</v>
+      </c>
+      <c r="DA227">
+        <v>0</v>
+      </c>
+      <c r="DC227" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY227" s="1"/>
+      <c r="GQ227" s="1"/>
+      <c r="GR227" s="1"/>
+      <c r="GY227" s="1"/>
+      <c r="GZ227" s="1"/>
+      <c r="HA227" s="1"/>
+      <c r="HB227" s="1"/>
+      <c r="IQ227" s="1">
+        <v>884361775</v>
+      </c>
+      <c r="IR227" t="s">
+        <v>1925</v>
+      </c>
+      <c r="IS227" s="1">
+        <v>46297.523055555554</v>
+      </c>
+      <c r="IU227" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW227" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX227" t="s">
+        <v>1926</v>
+      </c>
+      <c r="IY227">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A228" s="1">
+        <v>46297.647905798607</v>
+      </c>
+      <c r="B228" s="1">
+        <v>46297.65831741898</v>
+      </c>
+      <c r="C228" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D228" t="s">
+        <v>886</v>
+      </c>
+      <c r="E228" t="s">
+        <v>237</v>
+      </c>
+      <c r="F228" t="s">
+        <v>742</v>
+      </c>
+      <c r="G228" t="s">
+        <v>198</v>
+      </c>
+      <c r="H228" t="s">
+        <v>1927</v>
+      </c>
+      <c r="BS228" t="s">
+        <v>1928</v>
+      </c>
+      <c r="BT228" t="s">
+        <v>1929</v>
+      </c>
+      <c r="BU228" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW228" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX228" t="s">
+        <v>883</v>
+      </c>
+      <c r="BY228" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP228" t="s">
+        <v>1218</v>
+      </c>
+      <c r="CQ228" t="s">
+        <v>1930</v>
+      </c>
+      <c r="CR228" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS228" t="s">
+        <v>903</v>
+      </c>
+      <c r="CT228" t="s">
+        <v>912</v>
+      </c>
+      <c r="CU228">
+        <v>0</v>
+      </c>
+      <c r="CV228">
+        <v>1</v>
+      </c>
+      <c r="CW228">
+        <v>0</v>
+      </c>
+      <c r="CX228">
+        <v>0</v>
+      </c>
+      <c r="CY228">
+        <v>0</v>
+      </c>
+      <c r="CZ228">
+        <v>0</v>
+      </c>
+      <c r="DA228">
+        <v>0</v>
+      </c>
+      <c r="DC228" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY228" s="1"/>
+      <c r="GQ228" s="1"/>
+      <c r="GR228" s="1"/>
+      <c r="GY228" s="1"/>
+      <c r="GZ228" s="1"/>
+      <c r="HA228" s="1"/>
+      <c r="HB228" s="1"/>
+      <c r="IQ228" s="1">
+        <v>884439661</v>
+      </c>
+      <c r="IR228" t="s">
+        <v>1931</v>
+      </c>
+      <c r="IS228" s="1">
+        <v>46297.586840277778</v>
+      </c>
+      <c r="IU228" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW228" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX228" t="s">
+        <v>1932</v>
+      </c>
+      <c r="IY228">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A229" s="1">
+        <v>46297.658319340277</v>
+      </c>
+      <c r="B229" s="1">
+        <v>46297.664369479156</v>
+      </c>
+      <c r="C229" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D229" t="s">
+        <v>886</v>
+      </c>
+      <c r="E229" t="s">
+        <v>237</v>
+      </c>
+      <c r="F229" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G229" t="s">
+        <v>198</v>
+      </c>
+      <c r="H229" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS229" t="s">
+        <v>1934</v>
+      </c>
+      <c r="BT229" t="s">
+        <v>1935</v>
+      </c>
+      <c r="BU229" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW229" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX229" t="s">
+        <v>1936</v>
+      </c>
+      <c r="BY229" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP229" t="s">
+        <v>890</v>
+      </c>
+      <c r="CT229" t="s">
+        <v>1113</v>
+      </c>
+      <c r="CU229">
+        <v>0</v>
+      </c>
+      <c r="CV229">
+        <v>1</v>
+      </c>
+      <c r="CW229">
+        <v>1</v>
+      </c>
+      <c r="CX229">
+        <v>0</v>
+      </c>
+      <c r="CY229">
+        <v>0</v>
+      </c>
+      <c r="CZ229">
+        <v>0</v>
+      </c>
+      <c r="DA229">
+        <v>0</v>
+      </c>
+      <c r="DC229" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY229" s="1"/>
+      <c r="GQ229" s="1"/>
+      <c r="GR229" s="1"/>
+      <c r="GY229" s="1"/>
+      <c r="GZ229" s="1"/>
+      <c r="HA229" s="1"/>
+      <c r="HB229" s="1"/>
+      <c r="IQ229" s="1">
+        <v>884439671</v>
+      </c>
+      <c r="IR229" t="s">
+        <v>1937</v>
+      </c>
+      <c r="IS229" s="1">
+        <v>46297.586840277778</v>
+      </c>
+      <c r="IU229" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW229" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX229" t="s">
+        <v>1938</v>
+      </c>
+      <c r="IY229">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A230" s="1">
+        <v>46297.664371840277</v>
+      </c>
+      <c r="B230" s="1">
+        <v>46297.697084953703</v>
+      </c>
+      <c r="C230" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D230" t="s">
+        <v>886</v>
+      </c>
+      <c r="E230" t="s">
+        <v>237</v>
+      </c>
+      <c r="F230" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G230" t="s">
+        <v>198</v>
+      </c>
+      <c r="H230" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS230" t="s">
+        <v>1940</v>
+      </c>
+      <c r="BT230" t="s">
+        <v>1941</v>
+      </c>
+      <c r="BU230" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW230" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX230" t="s">
+        <v>1942</v>
+      </c>
+      <c r="BY230" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP230" t="s">
+        <v>938</v>
+      </c>
+      <c r="CQ230" t="s">
+        <v>1943</v>
+      </c>
+      <c r="CR230" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS230" t="s">
+        <v>1179</v>
+      </c>
+      <c r="CT230" t="s">
+        <v>1113</v>
+      </c>
+      <c r="CU230">
+        <v>0</v>
+      </c>
+      <c r="CV230">
+        <v>1</v>
+      </c>
+      <c r="CW230">
+        <v>1</v>
+      </c>
+      <c r="CX230">
+        <v>0</v>
+      </c>
+      <c r="CY230">
+        <v>0</v>
+      </c>
+      <c r="CZ230">
+        <v>0</v>
+      </c>
+      <c r="DA230">
+        <v>0</v>
+      </c>
+      <c r="DC230" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY230" s="1"/>
+      <c r="GQ230" s="1"/>
+      <c r="GR230" s="1"/>
+      <c r="GY230" s="1"/>
+      <c r="GZ230" s="1"/>
+      <c r="HA230" s="1"/>
+      <c r="HB230" s="1"/>
+      <c r="IQ230" s="1">
+        <v>884439687</v>
+      </c>
+      <c r="IR230" t="s">
+        <v>1944</v>
+      </c>
+      <c r="IS230" s="1">
+        <v>46297.586851851847</v>
+      </c>
+      <c r="IU230" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW230" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX230" t="s">
+        <v>1945</v>
+      </c>
+      <c r="IY230">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A231" s="1">
+        <v>46297.697087002307</v>
+      </c>
+      <c r="B231" s="1">
+        <v>46297.717213634263</v>
+      </c>
+      <c r="C231" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D231" t="s">
+        <v>886</v>
+      </c>
+      <c r="E231" t="s">
+        <v>237</v>
+      </c>
+      <c r="F231" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G231" t="s">
+        <v>198</v>
+      </c>
+      <c r="H231" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS231" t="s">
+        <v>1946</v>
+      </c>
+      <c r="BT231" t="s">
+        <v>1947</v>
+      </c>
+      <c r="BU231" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW231" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX231" t="s">
+        <v>1948</v>
+      </c>
+      <c r="BY231" t="s">
+        <v>359</v>
+      </c>
+      <c r="CP231" t="s">
+        <v>890</v>
+      </c>
+      <c r="CT231" t="s">
+        <v>1113</v>
+      </c>
+      <c r="CU231">
+        <v>0</v>
+      </c>
+      <c r="CV231">
+        <v>1</v>
+      </c>
+      <c r="CW231">
+        <v>1</v>
+      </c>
+      <c r="CX231">
+        <v>0</v>
+      </c>
+      <c r="CY231">
+        <v>0</v>
+      </c>
+      <c r="CZ231">
+        <v>0</v>
+      </c>
+      <c r="DA231">
+        <v>0</v>
+      </c>
+      <c r="DC231" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY231" s="1"/>
+      <c r="GQ231" s="1"/>
+      <c r="GR231" s="1"/>
+      <c r="GY231" s="1"/>
+      <c r="GZ231" s="1"/>
+      <c r="HA231" s="1"/>
+      <c r="HB231" s="1"/>
+      <c r="IQ231" s="1">
+        <v>884446980</v>
+      </c>
+      <c r="IR231" t="s">
+        <v>1949</v>
+      </c>
+      <c r="IS231" s="1">
+        <v>46297.592233796298</v>
+      </c>
+      <c r="IU231" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW231" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX231" t="s">
+        <v>1950</v>
+      </c>
+      <c r="IY231">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A232" s="1">
+        <v>46297.717215694443</v>
+      </c>
+      <c r="B232" s="1">
+        <v>46297.720687835637</v>
+      </c>
+      <c r="C232" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D232" t="s">
+        <v>886</v>
+      </c>
+      <c r="E232" t="s">
+        <v>237</v>
+      </c>
+      <c r="F232" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G232" t="s">
+        <v>198</v>
+      </c>
+      <c r="H232" t="s">
+        <v>1927</v>
+      </c>
+      <c r="BS232" t="s">
+        <v>1951</v>
+      </c>
+      <c r="BT232" t="s">
+        <v>1952</v>
+      </c>
+      <c r="BU232" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW232" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX232" t="s">
+        <v>1953</v>
+      </c>
+      <c r="BY232" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP232" t="s">
+        <v>890</v>
+      </c>
+      <c r="CT232" t="s">
+        <v>1521</v>
+      </c>
+      <c r="CU232">
+        <v>0</v>
+      </c>
+      <c r="CV232">
+        <v>0</v>
+      </c>
+      <c r="CW232">
+        <v>1</v>
+      </c>
+      <c r="CX232">
+        <v>1</v>
+      </c>
+      <c r="CY232">
+        <v>0</v>
+      </c>
+      <c r="CZ232">
+        <v>0</v>
+      </c>
+      <c r="DA232">
+        <v>0</v>
+      </c>
+      <c r="DC232" t="s">
+        <v>892</v>
+      </c>
+      <c r="EY232" s="1"/>
+      <c r="GQ232" s="1"/>
+      <c r="GR232" s="1"/>
+      <c r="GY232" s="1"/>
+      <c r="GZ232" s="1"/>
+      <c r="HA232" s="1"/>
+      <c r="HB232" s="1"/>
+      <c r="IQ232" s="1">
+        <v>884451766</v>
+      </c>
+      <c r="IR232" t="s">
+        <v>1954</v>
+      </c>
+      <c r="IS232" s="1">
+        <v>46297.595706018517</v>
+      </c>
+      <c r="IU232" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW232" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX232" t="s">
+        <v>1955</v>
+      </c>
+      <c r="IY232">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A233" s="1">
+        <v>46297.720690405091</v>
+      </c>
+      <c r="B233" s="1">
+        <v>46297.72633459491</v>
+      </c>
+      <c r="C233" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D233" t="s">
+        <v>886</v>
+      </c>
+      <c r="E233" t="s">
+        <v>237</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G233" t="s">
+        <v>198</v>
+      </c>
+      <c r="H233" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS233" t="s">
+        <v>1956</v>
+      </c>
+      <c r="BT233" t="s">
+        <v>1957</v>
+      </c>
+      <c r="BU233" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW233" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX233" t="s">
+        <v>1958</v>
+      </c>
+      <c r="BY233" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP233" t="s">
+        <v>938</v>
+      </c>
+      <c r="CQ233" t="s">
+        <v>1959</v>
+      </c>
+      <c r="CR233" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS233" t="s">
+        <v>940</v>
+      </c>
+      <c r="CT233" t="s">
+        <v>904</v>
+      </c>
+      <c r="CU233">
+        <v>0</v>
+      </c>
+      <c r="CV233">
+        <v>0</v>
+      </c>
+      <c r="CW233">
+        <v>1</v>
+      </c>
+      <c r="CX233">
+        <v>0</v>
+      </c>
+      <c r="CY233">
+        <v>0</v>
+      </c>
+      <c r="CZ233">
+        <v>0</v>
+      </c>
+      <c r="DA233">
+        <v>0</v>
+      </c>
+      <c r="DC233" t="s">
+        <v>892</v>
+      </c>
+      <c r="EY233" s="1"/>
+      <c r="GQ233" s="1"/>
+      <c r="GR233" s="1"/>
+      <c r="GY233" s="1"/>
+      <c r="GZ233" s="1"/>
+      <c r="HA233" s="1"/>
+      <c r="HB233" s="1"/>
+      <c r="IQ233" s="1">
+        <v>884459300</v>
+      </c>
+      <c r="IR233" t="s">
+        <v>1960</v>
+      </c>
+      <c r="IS233" s="1">
+        <v>46297.601354166669</v>
+      </c>
+      <c r="IU233" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW233" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX233" t="s">
+        <v>1961</v>
+      </c>
+      <c r="IY233">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A234" s="1">
+        <v>46297.726336203697</v>
+      </c>
+      <c r="B234" s="1">
+        <v>46297.731607372683</v>
+      </c>
+      <c r="C234" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D234" t="s">
+        <v>886</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+      <c r="F234" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G234" t="s">
+        <v>198</v>
+      </c>
+      <c r="H234" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS234" t="s">
+        <v>1962</v>
+      </c>
+      <c r="BT234" t="s">
+        <v>1963</v>
+      </c>
+      <c r="BU234" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW234" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX234" t="s">
+        <v>1964</v>
+      </c>
+      <c r="BY234" t="s">
+        <v>561</v>
+      </c>
+      <c r="CP234" t="s">
+        <v>938</v>
+      </c>
+      <c r="CQ234" t="s">
+        <v>1965</v>
+      </c>
+      <c r="CR234" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS234" t="s">
+        <v>1169</v>
+      </c>
+      <c r="CT234" t="s">
+        <v>912</v>
+      </c>
+      <c r="CU234">
+        <v>0</v>
+      </c>
+      <c r="CV234">
+        <v>1</v>
+      </c>
+      <c r="CW234">
+        <v>0</v>
+      </c>
+      <c r="CX234">
+        <v>0</v>
+      </c>
+      <c r="CY234">
+        <v>0</v>
+      </c>
+      <c r="CZ234">
+        <v>0</v>
+      </c>
+      <c r="DA234">
+        <v>0</v>
+      </c>
+      <c r="DC234" t="s">
+        <v>913</v>
+      </c>
+      <c r="EY234" s="1"/>
+      <c r="GQ234" s="1"/>
+      <c r="GR234" s="1"/>
+      <c r="GY234" s="1"/>
+      <c r="GZ234" s="1"/>
+      <c r="HA234" s="1"/>
+      <c r="HB234" s="1"/>
+      <c r="IQ234" s="1">
+        <v>884466442</v>
+      </c>
+      <c r="IR234" t="s">
+        <v>1966</v>
+      </c>
+      <c r="IS234" s="1">
+        <v>46297.606620370367</v>
+      </c>
+      <c r="IU234" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW234" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX234" t="s">
+        <v>1967</v>
+      </c>
+      <c r="IY234">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A235" s="1">
+        <v>46297.727836921287</v>
+      </c>
+      <c r="B235" s="1">
+        <v>46297.733301273147</v>
+      </c>
+      <c r="C235" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D235" t="s">
+        <v>691</v>
+      </c>
+      <c r="E235" t="s">
+        <v>254</v>
+      </c>
+      <c r="F235" t="s">
+        <v>261</v>
+      </c>
+      <c r="G235" t="s">
+        <v>198</v>
+      </c>
+      <c r="H235" t="s">
+        <v>256</v>
+      </c>
+      <c r="J235" t="s">
+        <v>1968</v>
+      </c>
+      <c r="K235" t="s">
+        <v>201</v>
+      </c>
+      <c r="L235" t="s">
+        <v>324</v>
+      </c>
+      <c r="M235" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N235" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O235" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P235" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AH235">
+        <v>210</v>
+      </c>
+      <c r="AI235">
+        <v>65</v>
+      </c>
+      <c r="AJ235">
+        <v>105</v>
+      </c>
+      <c r="AK235">
+        <v>2</v>
+      </c>
+      <c r="AL235">
+        <v>2</v>
+      </c>
+      <c r="AM235">
+        <v>0</v>
+      </c>
+      <c r="AN235">
+        <v>0</v>
+      </c>
+      <c r="AO235" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP235">
+        <v>0</v>
+      </c>
+      <c r="AQ235" t="s">
+        <v>340</v>
+      </c>
+      <c r="AR235" t="s">
+        <v>341</v>
+      </c>
+      <c r="AS235" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT235" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU235" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV235" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW235" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS235" t="s">
+        <v>1969</v>
+      </c>
+      <c r="BT235" t="s">
+        <v>1970</v>
+      </c>
+      <c r="BU235" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW235" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX235" t="s">
+        <v>1971</v>
+      </c>
+      <c r="EY235" s="1"/>
+      <c r="GQ235" s="1"/>
+      <c r="GR235" s="1"/>
+      <c r="GY235" s="1"/>
+      <c r="GZ235" s="1"/>
+      <c r="HA235" s="1"/>
+      <c r="HB235" s="1"/>
+      <c r="IQ235" s="1">
+        <v>884468553</v>
+      </c>
+      <c r="IR235" t="s">
+        <v>1972</v>
+      </c>
+      <c r="IS235" s="1">
+        <v>46297.60833333333</v>
+      </c>
+      <c r="IU235" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW235" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX235" t="s">
+        <v>1973</v>
+      </c>
+      <c r="IY235">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A236" s="1">
+        <v>46297.733303923611</v>
+      </c>
+      <c r="B236" s="1">
+        <v>46297.741435150463</v>
+      </c>
+      <c r="C236" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D236" t="s">
+        <v>691</v>
+      </c>
+      <c r="E236" t="s">
+        <v>254</v>
+      </c>
+      <c r="F236" t="s">
+        <v>267</v>
+      </c>
+      <c r="G236" t="s">
+        <v>198</v>
+      </c>
+      <c r="H236" t="s">
+        <v>256</v>
+      </c>
+      <c r="J236" t="s">
+        <v>268</v>
+      </c>
+      <c r="K236" t="s">
+        <v>201</v>
+      </c>
+      <c r="L236" t="s">
+        <v>324</v>
+      </c>
+      <c r="M236" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N236" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O236" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P236" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AH236">
+        <v>44</v>
+      </c>
+      <c r="AI236">
+        <v>13</v>
+      </c>
+      <c r="AJ236">
+        <v>21</v>
+      </c>
+      <c r="AK236">
+        <v>1</v>
+      </c>
+      <c r="AL236">
+        <v>2</v>
+      </c>
+      <c r="AM236">
+        <v>0</v>
+      </c>
+      <c r="AN236">
+        <v>0</v>
+      </c>
+      <c r="AO236" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AP236">
+        <v>2</v>
+      </c>
+      <c r="AQ236" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR236" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS236" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT236" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU236" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV236" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW236" t="s">
+        <v>230</v>
+      </c>
+      <c r="BS236" t="s">
+        <v>1974</v>
+      </c>
+      <c r="BT236" t="s">
+        <v>1975</v>
+      </c>
+      <c r="BU236" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW236" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX236" t="s">
+        <v>1976</v>
+      </c>
+      <c r="EY236" s="1"/>
+      <c r="GQ236" s="1"/>
+      <c r="GR236" s="1"/>
+      <c r="GY236" s="1"/>
+      <c r="GZ236" s="1"/>
+      <c r="HA236" s="1"/>
+      <c r="HB236" s="1"/>
+      <c r="IQ236" s="1">
+        <v>884478652</v>
+      </c>
+      <c r="IR236" t="s">
+        <v>1977</v>
+      </c>
+      <c r="IS236" s="1">
+        <v>46297.61645833333</v>
+      </c>
+      <c r="IU236" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW236" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX236" t="s">
+        <v>1978</v>
+      </c>
+      <c r="IY236">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A237" s="1">
+        <v>46297.741437164354</v>
+      </c>
+      <c r="B237" s="1">
+        <v>46297.747532696761</v>
+      </c>
+      <c r="C237" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D237" t="s">
+        <v>690</v>
+      </c>
+      <c r="E237" t="s">
+        <v>254</v>
+      </c>
+      <c r="F237" t="s">
+        <v>765</v>
+      </c>
+      <c r="G237" t="s">
+        <v>198</v>
+      </c>
+      <c r="H237" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX237" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AY237" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ237" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA237" t="s">
+        <v>1980</v>
+      </c>
+      <c r="BB237">
+        <v>72</v>
+      </c>
+      <c r="BC237">
+        <v>135</v>
+      </c>
+      <c r="BD237" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE237" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF237" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG237" t="s">
+        <v>1981</v>
+      </c>
+      <c r="BH237" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI237" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ237" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK237">
+        <v>6</v>
+      </c>
+      <c r="BL237" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM237">
+        <v>312</v>
+      </c>
+      <c r="BN237">
+        <v>256</v>
+      </c>
+      <c r="BO237" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP237" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ237" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BS237" t="s">
+        <v>1983</v>
+      </c>
+      <c r="BT237" t="s">
+        <v>1984</v>
+      </c>
+      <c r="BU237" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW237" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX237" t="s">
+        <v>1985</v>
+      </c>
+      <c r="EY237" s="1"/>
+      <c r="GQ237" s="1"/>
+      <c r="GR237" s="1"/>
+      <c r="GY237" s="1"/>
+      <c r="GZ237" s="1"/>
+      <c r="HA237" s="1"/>
+      <c r="HB237" s="1"/>
+      <c r="IQ237" s="1">
+        <v>884487033</v>
+      </c>
+      <c r="IR237" t="s">
+        <v>1986</v>
+      </c>
+      <c r="IS237" s="1">
+        <v>46297.622557870367</v>
+      </c>
+      <c r="IU237" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW237" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX237" t="s">
+        <v>1987</v>
+      </c>
+      <c r="IY237">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A238" s="1">
+        <v>46297.74753537037</v>
+      </c>
+      <c r="B238" s="1">
+        <v>46297.753938796297</v>
+      </c>
+      <c r="C238" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D238" t="s">
+        <v>690</v>
+      </c>
+      <c r="E238" t="s">
+        <v>254</v>
+      </c>
+      <c r="F238" t="s">
+        <v>332</v>
+      </c>
+      <c r="G238" t="s">
+        <v>198</v>
+      </c>
+      <c r="H238" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX238" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY238" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ238" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA238" t="s">
+        <v>1988</v>
+      </c>
+      <c r="BB238">
+        <v>4</v>
+      </c>
+      <c r="BC238">
+        <v>3</v>
+      </c>
+      <c r="BD238" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE238" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF238" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG238" t="s">
+        <v>1989</v>
+      </c>
+      <c r="BH238" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI238" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ238" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK238">
+        <v>4</v>
+      </c>
+      <c r="BL238" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM238">
+        <v>146</v>
+      </c>
+      <c r="BN238">
+        <v>120</v>
+      </c>
+      <c r="BO238" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP238" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ238" t="s">
+        <v>1630</v>
+      </c>
+      <c r="BS238" t="s">
+        <v>1990</v>
+      </c>
+      <c r="BT238" t="s">
+        <v>1991</v>
+      </c>
+      <c r="BU238" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW238" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX238" t="s">
+        <v>1992</v>
+      </c>
+      <c r="EY238" s="1"/>
+      <c r="GQ238" s="1"/>
+      <c r="GR238" s="1"/>
+      <c r="GY238" s="1"/>
+      <c r="GZ238" s="1"/>
+      <c r="HA238" s="1"/>
+      <c r="HB238" s="1"/>
+      <c r="IQ238" s="1">
+        <v>884493999</v>
+      </c>
+      <c r="IR238" t="s">
+        <v>1993</v>
+      </c>
+      <c r="IS238" s="1">
+        <v>46297.628969907397</v>
+      </c>
+      <c r="IU238" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW238" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX238" t="s">
+        <v>1994</v>
+      </c>
+      <c r="IY238">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A239" s="1">
+        <v>46297.753942407413</v>
+      </c>
+      <c r="B239" s="1">
+        <v>46297.757288715278</v>
+      </c>
+      <c r="C239" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D239" t="s">
+        <v>690</v>
+      </c>
+      <c r="E239" t="s">
+        <v>254</v>
+      </c>
+      <c r="F239" t="s">
+        <v>332</v>
+      </c>
+      <c r="G239" t="s">
+        <v>198</v>
+      </c>
+      <c r="H239" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX239" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY239" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ239" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA239" t="s">
+        <v>1995</v>
+      </c>
+      <c r="BB239">
+        <v>5</v>
+      </c>
+      <c r="BC239">
+        <v>0</v>
+      </c>
+      <c r="BD239" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE239" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF239" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG239" t="s">
+        <v>1996</v>
+      </c>
+      <c r="BH239" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI239" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ239" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK239">
+        <v>3</v>
+      </c>
+      <c r="BL239" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM239">
+        <v>210</v>
+      </c>
+      <c r="BN239">
+        <v>342</v>
+      </c>
+      <c r="BO239" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP239" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ239" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS239" t="s">
+        <v>1997</v>
+      </c>
+      <c r="BT239" t="s">
+        <v>1998</v>
+      </c>
+      <c r="BU239" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV239" t="s">
+        <v>1999</v>
+      </c>
+      <c r="BW239" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX239" t="s">
+        <v>2000</v>
+      </c>
+      <c r="EY239" s="1"/>
+      <c r="GQ239" s="1"/>
+      <c r="GR239" s="1"/>
+      <c r="GY239" s="1"/>
+      <c r="GZ239" s="1"/>
+      <c r="HA239" s="1"/>
+      <c r="HB239" s="1"/>
+      <c r="IQ239" s="1">
+        <v>884497672</v>
+      </c>
+      <c r="IR239" t="s">
+        <v>2001</v>
+      </c>
+      <c r="IS239" s="1">
+        <v>46297.632303240738</v>
+      </c>
+      <c r="IU239" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW239" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX239" t="s">
+        <v>2002</v>
+      </c>
+      <c r="IY239">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A240" s="1">
+        <v>46297.757290694448</v>
+      </c>
+      <c r="B240" s="1">
+        <v>46297.760939953703</v>
+      </c>
+      <c r="C240" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D240" t="s">
+        <v>690</v>
+      </c>
+      <c r="E240" t="s">
+        <v>254</v>
+      </c>
+      <c r="F240" t="s">
+        <v>765</v>
+      </c>
+      <c r="G240" t="s">
+        <v>198</v>
+      </c>
+      <c r="H240" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX240" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY240" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ240" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA240" t="s">
+        <v>2003</v>
+      </c>
+      <c r="BB240">
+        <v>3</v>
+      </c>
+      <c r="BC240">
+        <v>0</v>
+      </c>
+      <c r="BD240" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE240" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF240" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG240" t="s">
+        <v>2004</v>
+      </c>
+      <c r="BH240" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI240" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ240" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK240">
+        <v>3</v>
+      </c>
+      <c r="BL240" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM240">
+        <v>311</v>
+      </c>
+      <c r="BN240">
+        <v>244</v>
+      </c>
+      <c r="BO240" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP240" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ240" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS240" t="s">
+        <v>2005</v>
+      </c>
+      <c r="BT240" t="s">
+        <v>2006</v>
+      </c>
+      <c r="BU240" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV240" t="s">
+        <v>897</v>
+      </c>
+      <c r="BW240" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX240" t="s">
+        <v>2007</v>
+      </c>
+      <c r="EY240" s="1"/>
+      <c r="GQ240" s="1"/>
+      <c r="GR240" s="1"/>
+      <c r="GY240" s="1"/>
+      <c r="GZ240" s="1"/>
+      <c r="HA240" s="1"/>
+      <c r="HB240" s="1"/>
+      <c r="IQ240" s="1">
+        <v>884502228</v>
+      </c>
+      <c r="IR240" t="s">
+        <v>2008</v>
+      </c>
+      <c r="IS240" s="1">
+        <v>46297.635960648149</v>
+      </c>
+      <c r="IU240" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW240" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX240" t="s">
+        <v>2009</v>
+      </c>
+      <c r="IY240">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A241" s="1">
+        <v>46297.848862210652</v>
+      </c>
+      <c r="B241" s="1">
+        <v>46297.87210753472</v>
+      </c>
+      <c r="C241" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D241" t="s">
+        <v>690</v>
+      </c>
+      <c r="E241" t="s">
+        <v>196</v>
+      </c>
+      <c r="F241" t="s">
+        <v>618</v>
+      </c>
+      <c r="G241" t="s">
+        <v>198</v>
+      </c>
+      <c r="H241" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX241" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY241" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ241" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA241" t="s">
+        <v>2010</v>
+      </c>
+      <c r="BB241">
+        <v>25</v>
+      </c>
+      <c r="BC241">
+        <v>5</v>
+      </c>
+      <c r="BD241" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE241" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF241" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG241" t="s">
+        <v>2011</v>
+      </c>
+      <c r="BH241" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI241" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ241" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK241">
+        <v>3</v>
+      </c>
+      <c r="BL241" t="s">
+        <v>2012</v>
+      </c>
+      <c r="BM241">
+        <v>20</v>
+      </c>
+      <c r="BN241">
+        <v>30</v>
+      </c>
+      <c r="BO241" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP241" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ241" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS241" t="s">
+        <v>2013</v>
+      </c>
+      <c r="BT241" t="s">
+        <v>2014</v>
+      </c>
+      <c r="BU241" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV241" t="s">
+        <v>2015</v>
+      </c>
+      <c r="BW241" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX241" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY241" s="1"/>
+      <c r="GQ241" s="1"/>
+      <c r="GR241" s="1"/>
+      <c r="GY241" s="1"/>
+      <c r="GZ241" s="1"/>
+      <c r="HA241" s="1"/>
+      <c r="HB241" s="1"/>
+      <c r="IQ241" s="1">
+        <v>884616009</v>
+      </c>
+      <c r="IR241" t="s">
+        <v>2016</v>
+      </c>
+      <c r="IS241" s="1">
+        <v>46297.747118055559</v>
+      </c>
+      <c r="IU241" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW241" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX241" t="s">
+        <v>2017</v>
+      </c>
+      <c r="IY241">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A242" s="1">
+        <v>46297.645588900457</v>
+      </c>
+      <c r="B242" s="1">
+        <v>46297.908402372683</v>
+      </c>
+      <c r="C242" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D242" t="s">
+        <v>952</v>
+      </c>
+      <c r="E242" t="s">
+        <v>237</v>
+      </c>
+      <c r="F242" t="s">
+        <v>742</v>
+      </c>
+      <c r="G242" t="s">
+        <v>198</v>
+      </c>
+      <c r="H242" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS242" t="s">
+        <v>2018</v>
+      </c>
+      <c r="BT242" t="s">
+        <v>1712</v>
+      </c>
+      <c r="BU242" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW242" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX242" t="s">
+        <v>883</v>
+      </c>
+      <c r="BY242" t="s">
+        <v>561</v>
+      </c>
+      <c r="DE242" t="s">
+        <v>1289</v>
+      </c>
+      <c r="DF242" t="s">
+        <v>1396</v>
+      </c>
+      <c r="DG242">
+        <v>1</v>
+      </c>
+      <c r="DH242">
+        <v>1</v>
+      </c>
+      <c r="DI242">
+        <v>0</v>
+      </c>
+      <c r="DJ242">
+        <v>0</v>
+      </c>
+      <c r="DK242">
+        <v>0</v>
+      </c>
+      <c r="DM242" t="s">
+        <v>2019</v>
+      </c>
+      <c r="DN242" t="s">
+        <v>2020</v>
+      </c>
+      <c r="DO242" t="s">
+        <v>979</v>
+      </c>
+      <c r="DP242">
+        <v>1</v>
+      </c>
+      <c r="DQ242">
+        <v>0</v>
+      </c>
+      <c r="DR242">
+        <v>0</v>
+      </c>
+      <c r="DS242" t="s">
+        <v>1083</v>
+      </c>
+      <c r="DU242" t="s">
+        <v>2021</v>
+      </c>
+      <c r="DV242" t="s">
+        <v>2022</v>
+      </c>
+      <c r="DW242" t="s">
+        <v>1073</v>
+      </c>
+      <c r="EY242" s="1"/>
+      <c r="GQ242" s="1"/>
+      <c r="GR242" s="1"/>
+      <c r="GY242" s="1"/>
+      <c r="GZ242" s="1"/>
+      <c r="HA242" s="1"/>
+      <c r="HB242" s="1"/>
+      <c r="IQ242" s="1">
+        <v>884649140</v>
+      </c>
+      <c r="IR242" t="s">
+        <v>2023</v>
+      </c>
+      <c r="IS242" s="1">
+        <v>46297.783425925933</v>
+      </c>
+      <c r="IU242" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW242" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX242" t="s">
+        <v>2024</v>
+      </c>
+      <c r="IY242">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A243" s="1">
+        <v>46296.555081018523</v>
+      </c>
+      <c r="B243" s="1">
+        <v>46298.436994710653</v>
+      </c>
+      <c r="C243" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D243" t="s">
+        <v>690</v>
+      </c>
+      <c r="E243" t="s">
+        <v>309</v>
+      </c>
+      <c r="F243" t="s">
+        <v>593</v>
+      </c>
+      <c r="G243" t="s">
+        <v>198</v>
+      </c>
+      <c r="H243" t="s">
+        <v>311</v>
+      </c>
+      <c r="AX243" t="s">
+        <v>2025</v>
+      </c>
+      <c r="AY243" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ243" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA243" t="s">
+        <v>2026</v>
+      </c>
+      <c r="BB243">
+        <v>2</v>
+      </c>
+      <c r="BC243">
+        <v>5</v>
+      </c>
+      <c r="BD243" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE243" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF243" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG243" t="s">
+        <v>2027</v>
+      </c>
+      <c r="BH243" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI243" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ243" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK243">
+        <v>4</v>
+      </c>
+      <c r="BL243" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM243">
+        <v>4</v>
+      </c>
+      <c r="BN243">
+        <v>6</v>
+      </c>
+      <c r="BO243" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP243" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ243" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS243" t="s">
+        <v>2028</v>
+      </c>
+      <c r="BT243" t="s">
+        <v>2029</v>
+      </c>
+      <c r="BU243" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW243" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX243" t="s">
+        <v>2030</v>
+      </c>
+      <c r="EY243" s="1"/>
+      <c r="GQ243" s="1"/>
+      <c r="GR243" s="1"/>
+      <c r="GY243" s="1"/>
+      <c r="GZ243" s="1"/>
+      <c r="HA243" s="1"/>
+      <c r="HB243" s="1"/>
+      <c r="IQ243" s="1">
+        <v>884864655</v>
+      </c>
+      <c r="IR243" t="s">
+        <v>2031</v>
+      </c>
+      <c r="IS243" s="1">
+        <v>46298.312025462961</v>
+      </c>
+      <c r="IU243" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW243" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX243" t="s">
+        <v>2032</v>
+      </c>
+      <c r="IY243">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A244" s="1">
+        <v>46298.436995810189</v>
+      </c>
+      <c r="B244" s="1">
+        <v>46298.477971215281</v>
+      </c>
+      <c r="C244" s="1">
+        <v>46294</v>
+      </c>
+      <c r="D244" t="s">
+        <v>691</v>
+      </c>
+      <c r="E244" t="s">
+        <v>309</v>
+      </c>
+      <c r="F244" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G244" t="s">
+        <v>198</v>
+      </c>
+      <c r="H244" t="s">
+        <v>311</v>
+      </c>
+      <c r="J244" t="s">
+        <v>2033</v>
+      </c>
+      <c r="K244" t="s">
+        <v>201</v>
+      </c>
+      <c r="L244" t="s">
+        <v>324</v>
+      </c>
+      <c r="M244" t="s">
+        <v>612</v>
+      </c>
+      <c r="N244" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O244" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH244">
+        <v>780</v>
+      </c>
+      <c r="AI244">
+        <v>388</v>
+      </c>
+      <c r="AJ244">
+        <v>398</v>
+      </c>
+      <c r="AK244">
+        <v>10</v>
+      </c>
+      <c r="AL244">
+        <v>2</v>
+      </c>
+      <c r="AM244">
+        <v>70</v>
+      </c>
+      <c r="AN244">
+        <v>0</v>
+      </c>
+      <c r="AO244" t="s">
+        <v>2034</v>
+      </c>
+      <c r="AP244">
+        <v>5</v>
+      </c>
+      <c r="AQ244" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR244" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS244" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT244" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU244" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV244" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW244" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS244" t="s">
+        <v>2035</v>
+      </c>
+      <c r="BT244" t="s">
+        <v>2036</v>
+      </c>
+      <c r="BU244" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW244" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX244" t="s">
+        <v>2037</v>
+      </c>
+      <c r="EY244" s="1"/>
+      <c r="GQ244" s="1"/>
+      <c r="GR244" s="1"/>
+      <c r="GY244" s="1"/>
+      <c r="GZ244" s="1"/>
+      <c r="HA244" s="1"/>
+      <c r="HB244" s="1"/>
+      <c r="IQ244" s="1">
+        <v>884891716</v>
+      </c>
+      <c r="IR244" t="s">
+        <v>2038</v>
+      </c>
+      <c r="IS244" s="1">
+        <v>46298.352986111109</v>
+      </c>
+      <c r="IU244" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW244" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX244" t="s">
+        <v>2039</v>
+      </c>
+      <c r="IY244">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A245" s="1">
+        <v>46294.744592546303</v>
+      </c>
+      <c r="B245" s="1">
+        <v>46298.49458979167</v>
+      </c>
+      <c r="C245" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D245" t="s">
+        <v>354</v>
+      </c>
+      <c r="E245" t="s">
+        <v>210</v>
+      </c>
+      <c r="F245" t="s">
+        <v>2040</v>
+      </c>
+      <c r="G245" t="s">
+        <v>198</v>
+      </c>
+      <c r="H245" t="s">
+        <v>311</v>
+      </c>
+      <c r="BS245" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT245" t="s">
+        <v>510</v>
+      </c>
+      <c r="BU245" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV245" t="s">
+        <v>2041</v>
+      </c>
+      <c r="BW245" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX245" t="s">
+        <v>2042</v>
+      </c>
+      <c r="BY245" t="s">
+        <v>359</v>
+      </c>
+      <c r="CB245" t="s">
+        <v>404</v>
+      </c>
+      <c r="CC245">
+        <v>2</v>
+      </c>
+      <c r="CD245">
+        <v>780</v>
+      </c>
+      <c r="CE245" t="s">
+        <v>361</v>
+      </c>
+      <c r="CF245" t="s">
+        <v>2043</v>
+      </c>
+      <c r="CG245" t="s">
+        <v>363</v>
+      </c>
+      <c r="CH245" t="s">
+        <v>2044</v>
+      </c>
+      <c r="CI245" t="s">
+        <v>458</v>
+      </c>
+      <c r="CK245" t="s">
+        <v>366</v>
+      </c>
+      <c r="CL245" t="s">
+        <v>2045</v>
+      </c>
+      <c r="CM245" t="s">
+        <v>460</v>
+      </c>
+      <c r="CN245" t="s">
+        <v>2046</v>
+      </c>
+      <c r="EY245" s="1"/>
+      <c r="GQ245" s="1"/>
+      <c r="GR245" s="1"/>
+      <c r="GY245" s="1"/>
+      <c r="GZ245" s="1"/>
+      <c r="HA245" s="1"/>
+      <c r="HB245" s="1"/>
+      <c r="IQ245" s="1">
+        <v>884902960</v>
+      </c>
+      <c r="IR245" t="s">
+        <v>2047</v>
+      </c>
+      <c r="IS245" s="1">
+        <v>46298.369606481479</v>
+      </c>
+      <c r="IU245" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW245" t="s">
+        <v>1600</v>
+      </c>
+      <c r="IX245" t="s">
+        <v>2048</v>
+      </c>
+      <c r="IY245">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A246" s="1">
+        <v>46298.477973055553</v>
+      </c>
+      <c r="B246" s="1">
+        <v>46298.51031474537</v>
+      </c>
+      <c r="C246" s="1">
+        <v>46268</v>
+      </c>
+      <c r="D246" t="s">
+        <v>691</v>
+      </c>
+      <c r="E246" t="s">
+        <v>309</v>
+      </c>
+      <c r="F246" t="s">
+        <v>593</v>
+      </c>
+      <c r="G246" t="s">
+        <v>198</v>
+      </c>
+      <c r="H246" t="s">
+        <v>311</v>
+      </c>
+      <c r="J246" t="s">
+        <v>2049</v>
+      </c>
+      <c r="K246" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L246" t="s">
+        <v>324</v>
+      </c>
+      <c r="M246" t="s">
+        <v>612</v>
+      </c>
+      <c r="N246" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O246" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P246" t="s">
+        <v>2050</v>
+      </c>
+      <c r="AH246">
+        <v>1028</v>
+      </c>
+      <c r="AI246">
+        <v>246</v>
+      </c>
+      <c r="AJ246">
+        <v>268</v>
+      </c>
+      <c r="AK246">
+        <v>10</v>
+      </c>
+      <c r="AL246">
+        <v>2</v>
+      </c>
+      <c r="AM246">
+        <v>70</v>
+      </c>
+      <c r="AN246">
+        <v>0</v>
+      </c>
+      <c r="AO246" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AP246">
+        <v>2</v>
+      </c>
+      <c r="AQ246" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR246" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS246" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT246" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU246" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV246" t="s">
+        <v>204</v>
+      </c>
+      <c r="AW246" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS246" t="s">
+        <v>2052</v>
+      </c>
+      <c r="BT246" t="s">
+        <v>2053</v>
+      </c>
+      <c r="BU246" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW246" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX246" t="s">
+        <v>2054</v>
+      </c>
+      <c r="EY246" s="1"/>
+      <c r="GQ246" s="1"/>
+      <c r="GR246" s="1"/>
+      <c r="GY246" s="1"/>
+      <c r="GZ246" s="1"/>
+      <c r="HA246" s="1"/>
+      <c r="HB246" s="1"/>
+      <c r="IQ246" s="1">
+        <v>884912356</v>
+      </c>
+      <c r="IR246" t="s">
+        <v>2055</v>
+      </c>
+      <c r="IS246" s="1">
+        <v>46298.385358796288</v>
+      </c>
+      <c r="IU246" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW246" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX246" t="s">
+        <v>2056</v>
+      </c>
+      <c r="IY246">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A247" s="1">
+        <v>46298.510316689812</v>
+      </c>
+      <c r="B247" s="1">
+        <v>46298.534484548611</v>
+      </c>
+      <c r="C247" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D247" t="s">
+        <v>690</v>
+      </c>
+      <c r="E247" t="s">
+        <v>309</v>
+      </c>
+      <c r="F247" t="s">
+        <v>2057</v>
+      </c>
+      <c r="G247" t="s">
+        <v>198</v>
+      </c>
+      <c r="H247" t="s">
+        <v>311</v>
+      </c>
+      <c r="AX247" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY247" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ247" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA247" t="s">
+        <v>2058</v>
+      </c>
+      <c r="BB247">
+        <v>10</v>
+      </c>
+      <c r="BC247">
+        <v>25</v>
+      </c>
+      <c r="BD247" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE247" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF247" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG247" t="s">
+        <v>2059</v>
+      </c>
+      <c r="BH247" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI247" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ247" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK247">
+        <v>2</v>
+      </c>
+      <c r="BL247" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM247">
+        <v>0</v>
+      </c>
+      <c r="BN247">
+        <v>0</v>
+      </c>
+      <c r="BO247" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP247" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ247" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS247" t="s">
+        <v>2060</v>
+      </c>
+      <c r="BT247" t="s">
+        <v>2061</v>
+      </c>
+      <c r="BU247" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV247" t="s">
+        <v>2062</v>
+      </c>
+      <c r="BW247" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX247" t="s">
+        <v>2063</v>
+      </c>
+      <c r="EY247" s="1"/>
+      <c r="GQ247" s="1"/>
+      <c r="GR247" s="1"/>
+      <c r="GY247" s="1"/>
+      <c r="GZ247" s="1"/>
+      <c r="HA247" s="1"/>
+      <c r="HB247" s="1"/>
+      <c r="IQ247" s="1">
+        <v>884927780</v>
+      </c>
+      <c r="IR247" t="s">
+        <v>2064</v>
+      </c>
+      <c r="IS247" s="1">
+        <v>46298.409502314818</v>
+      </c>
+      <c r="IU247" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW247" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX247" t="s">
+        <v>2065</v>
+      </c>
+      <c r="IY247">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A248" s="1">
+        <v>46298.534485775461</v>
+      </c>
+      <c r="B248" s="1">
+        <v>46298.551648287037</v>
+      </c>
+      <c r="C248" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D248" t="s">
+        <v>354</v>
+      </c>
+      <c r="E248" t="s">
+        <v>309</v>
+      </c>
+      <c r="F248" t="s">
+        <v>2066</v>
+      </c>
+      <c r="G248" t="s">
+        <v>198</v>
+      </c>
+      <c r="H248" t="s">
+        <v>311</v>
+      </c>
+      <c r="BS248" t="s">
+        <v>2067</v>
+      </c>
+      <c r="BT248" t="s">
+        <v>2068</v>
+      </c>
+      <c r="BU248" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV248" t="s">
+        <v>2069</v>
+      </c>
+      <c r="BW248" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX248" t="s">
+        <v>2070</v>
+      </c>
+      <c r="BY248" t="s">
+        <v>359</v>
+      </c>
+      <c r="CB248" t="s">
+        <v>511</v>
+      </c>
+      <c r="CC248">
+        <v>0</v>
+      </c>
+      <c r="CD248">
+        <v>400</v>
+      </c>
+      <c r="CE248" t="s">
+        <v>361</v>
+      </c>
+      <c r="CF248" t="s">
+        <v>2071</v>
+      </c>
+      <c r="CG248" t="s">
+        <v>392</v>
+      </c>
+      <c r="CH248" t="s">
+        <v>2072</v>
+      </c>
+      <c r="CI248" t="s">
+        <v>458</v>
+      </c>
+      <c r="CK248" t="s">
+        <v>515</v>
+      </c>
+      <c r="CL248" t="s">
+        <v>2073</v>
+      </c>
+      <c r="CM248" t="s">
+        <v>581</v>
+      </c>
+      <c r="CN248" t="s">
+        <v>2074</v>
+      </c>
+      <c r="EY248" s="1"/>
+      <c r="GQ248" s="1"/>
+      <c r="GR248" s="1"/>
+      <c r="GY248" s="1"/>
+      <c r="GZ248" s="1"/>
+      <c r="HA248" s="1"/>
+      <c r="HB248" s="1"/>
+      <c r="IQ248" s="1">
+        <v>884940073</v>
+      </c>
+      <c r="IR248" t="s">
+        <v>2075</v>
+      </c>
+      <c r="IS248" s="1">
+        <v>46298.426678240743</v>
+      </c>
+      <c r="IU248" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW248" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX248" t="s">
+        <v>2076</v>
+      </c>
+      <c r="IY248">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A249" s="1">
+        <v>46298.551648703702</v>
+      </c>
+      <c r="B249" s="1">
+        <v>46298.564663217592</v>
+      </c>
+      <c r="C249" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D249" t="s">
+        <v>776</v>
+      </c>
+      <c r="E249" t="s">
+        <v>309</v>
+      </c>
+      <c r="F249" t="s">
+        <v>2066</v>
+      </c>
+      <c r="G249" t="s">
+        <v>198</v>
+      </c>
+      <c r="H249" t="s">
+        <v>311</v>
+      </c>
+      <c r="BS249" t="s">
+        <v>2067</v>
+      </c>
+      <c r="BT249" t="s">
+        <v>2077</v>
+      </c>
+      <c r="BU249" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV249" t="s">
+        <v>2069</v>
+      </c>
+      <c r="BW249" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX249" t="s">
+        <v>2078</v>
+      </c>
+      <c r="EY249" s="1"/>
+      <c r="GJ249" s="1">
+        <v>46296</v>
+      </c>
+      <c r="GK249" t="s">
+        <v>987</v>
+      </c>
+      <c r="GL249" t="s">
+        <v>376</v>
+      </c>
+      <c r="GN249">
+        <v>270</v>
+      </c>
+      <c r="GO249">
+        <v>230</v>
+      </c>
+      <c r="GP249">
+        <v>6</v>
+      </c>
+      <c r="GQ249" s="1">
+        <v>4</v>
+      </c>
+      <c r="GR249" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="GT249" t="s">
+        <v>377</v>
+      </c>
+      <c r="GU249" t="s">
+        <v>378</v>
+      </c>
+      <c r="GV249" t="s">
+        <v>379</v>
+      </c>
+      <c r="GX249" t="s">
+        <v>587</v>
+      </c>
+      <c r="GY249" s="1">
+        <v>0</v>
+      </c>
+      <c r="GZ249" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="HA249" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="HB249" s="1">
+        <v>6</v>
+      </c>
+      <c r="HC249">
+        <v>6</v>
+      </c>
+      <c r="HD249" t="s">
+        <v>383</v>
+      </c>
+      <c r="HE249" t="s">
+        <v>384</v>
+      </c>
+      <c r="HF249" t="s">
+        <v>451</v>
+      </c>
+      <c r="HG249">
+        <v>0</v>
+      </c>
+      <c r="HH249">
+        <v>0</v>
+      </c>
+      <c r="HI249">
+        <v>0</v>
+      </c>
+      <c r="HJ249">
+        <v>1</v>
+      </c>
+      <c r="HK249" t="s">
+        <v>324</v>
+      </c>
+      <c r="HM249">
+        <v>6</v>
+      </c>
+      <c r="HN249">
+        <v>4</v>
+      </c>
+      <c r="HO249">
+        <v>5</v>
+      </c>
+      <c r="HP249">
+        <v>5</v>
+      </c>
+      <c r="HQ249">
+        <v>5</v>
+      </c>
+      <c r="HR249">
+        <v>0</v>
+      </c>
+      <c r="IQ249" s="1">
+        <v>884949698</v>
+      </c>
+      <c r="IR249" t="s">
+        <v>2079</v>
+      </c>
+      <c r="IS249" s="1">
+        <v>46298.439675925933</v>
+      </c>
+      <c r="IU249" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW249" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX249" t="s">
+        <v>2080</v>
+      </c>
+      <c r="IY249">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A250" s="1">
+        <v>46298.56466358796</v>
+      </c>
+      <c r="B250" s="1">
+        <v>46298.582582962961</v>
+      </c>
+      <c r="C250" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D250" t="s">
+        <v>691</v>
+      </c>
+      <c r="E250" t="s">
+        <v>309</v>
+      </c>
+      <c r="F250" t="s">
+        <v>2081</v>
+      </c>
+      <c r="G250" t="s">
+        <v>198</v>
+      </c>
+      <c r="H250" t="s">
+        <v>311</v>
+      </c>
+      <c r="J250" t="s">
+        <v>987</v>
+      </c>
+      <c r="K250" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L250" t="s">
+        <v>324</v>
+      </c>
+      <c r="M250" t="s">
+        <v>612</v>
+      </c>
+      <c r="N250" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O250" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P250" t="s">
+        <v>1702</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>2082</v>
+      </c>
+      <c r="AH250">
+        <v>400</v>
+      </c>
+      <c r="AI250">
+        <v>199</v>
+      </c>
+      <c r="AJ250">
+        <v>201</v>
+      </c>
+      <c r="AK250">
+        <v>1</v>
+      </c>
+      <c r="AL250">
+        <v>2</v>
+      </c>
+      <c r="AM250">
+        <v>70</v>
+      </c>
+      <c r="AN250">
+        <v>0</v>
+      </c>
+      <c r="AO250" t="s">
+        <v>2034</v>
+      </c>
+      <c r="AP250">
+        <v>6</v>
+      </c>
+      <c r="AQ250" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR250" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS250" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT250" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU250" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV250" t="s">
+        <v>204</v>
+      </c>
+      <c r="AW250" t="s">
+        <v>230</v>
+      </c>
+      <c r="BS250" t="s">
+        <v>2083</v>
+      </c>
+      <c r="BT250" t="s">
+        <v>2084</v>
+      </c>
+      <c r="BU250" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW250" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX250" t="s">
+        <v>2085</v>
+      </c>
+      <c r="EY250" s="1"/>
+      <c r="GQ250" s="1"/>
+      <c r="GR250" s="1"/>
+      <c r="GY250" s="1"/>
+      <c r="GZ250" s="1"/>
+      <c r="HA250" s="1"/>
+      <c r="HB250" s="1"/>
+      <c r="IQ250" s="1">
+        <v>884963193</v>
+      </c>
+      <c r="IR250" t="s">
+        <v>2086</v>
+      </c>
+      <c r="IS250" s="1">
+        <v>46298.457604166673</v>
+      </c>
+      <c r="IU250" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW250" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX250" t="s">
+        <v>2087</v>
+      </c>
+      <c r="IY250">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A251" s="1">
+        <v>46298.60764490741</v>
+      </c>
+      <c r="B251" s="1">
+        <v>46298.613121620372</v>
+      </c>
+      <c r="C251" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D251" t="s">
+        <v>886</v>
+      </c>
+      <c r="E251" t="s">
+        <v>210</v>
+      </c>
+      <c r="F251" t="s">
+        <v>970</v>
+      </c>
+      <c r="G251" t="s">
+        <v>198</v>
+      </c>
+      <c r="H251" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS251" t="s">
+        <v>2088</v>
+      </c>
+      <c r="BT251" t="s">
+        <v>954</v>
+      </c>
+      <c r="BW251" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX251" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BY251" t="s">
+        <v>930</v>
+      </c>
+      <c r="CP251" t="s">
+        <v>1218</v>
+      </c>
+      <c r="CQ251" t="s">
+        <v>2089</v>
+      </c>
+      <c r="CR251" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS251" t="s">
+        <v>903</v>
+      </c>
+      <c r="CT251" t="s">
+        <v>904</v>
+      </c>
+      <c r="CU251">
+        <v>0</v>
+      </c>
+      <c r="CV251">
+        <v>0</v>
+      </c>
+      <c r="CW251">
+        <v>1</v>
+      </c>
+      <c r="CX251">
+        <v>0</v>
+      </c>
+      <c r="CY251">
+        <v>0</v>
+      </c>
+      <c r="CZ251">
+        <v>0</v>
+      </c>
+      <c r="DA251">
+        <v>0</v>
+      </c>
+      <c r="DC251" t="s">
+        <v>905</v>
+      </c>
+      <c r="EY251" s="1"/>
+      <c r="GQ251" s="1"/>
+      <c r="GR251" s="1"/>
+      <c r="GY251" s="1"/>
+      <c r="GZ251" s="1"/>
+      <c r="HA251" s="1"/>
+      <c r="HB251" s="1"/>
+      <c r="IC251" t="s">
+        <v>224</v>
+      </c>
+      <c r="IQ251" s="1">
+        <v>884984347</v>
+      </c>
+      <c r="IR251" t="s">
+        <v>2090</v>
+      </c>
+      <c r="IS251" s="1">
+        <v>46298.48814814815</v>
+      </c>
+      <c r="IU251" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW251" t="s">
+        <v>706</v>
+      </c>
+      <c r="IX251" t="s">
+        <v>2091</v>
+      </c>
+      <c r="IY251">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A252" s="1">
+        <v>46298.613122175928</v>
+      </c>
+      <c r="B252" s="1">
+        <v>46298.61480505787</v>
+      </c>
+      <c r="C252" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D252" t="s">
+        <v>886</v>
+      </c>
+      <c r="E252" t="s">
+        <v>210</v>
+      </c>
+      <c r="F252" t="s">
+        <v>970</v>
+      </c>
+      <c r="G252" t="s">
+        <v>198</v>
+      </c>
+      <c r="H252" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS252" t="s">
+        <v>2092</v>
+      </c>
+      <c r="BT252" t="s">
+        <v>954</v>
+      </c>
+      <c r="BW252" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX252" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BY252" t="s">
+        <v>930</v>
+      </c>
+      <c r="CP252" t="s">
+        <v>900</v>
+      </c>
+      <c r="CQ252" t="s">
+        <v>2093</v>
+      </c>
+      <c r="CR252" t="s">
+        <v>902</v>
+      </c>
+      <c r="CS252" t="s">
+        <v>903</v>
+      </c>
+      <c r="CT252" t="s">
+        <v>912</v>
+      </c>
+      <c r="CU252">
+        <v>0</v>
+      </c>
+      <c r="CV252">
+        <v>1</v>
+      </c>
+      <c r="CW252">
+        <v>0</v>
+      </c>
+      <c r="CX252">
+        <v>0</v>
+      </c>
+      <c r="CY252">
+        <v>0</v>
+      </c>
+      <c r="CZ252">
+        <v>0</v>
+      </c>
+      <c r="DA252">
+        <v>0</v>
+      </c>
+      <c r="DC252" t="s">
+        <v>892</v>
+      </c>
+      <c r="EY252" s="1"/>
+      <c r="GQ252" s="1"/>
+      <c r="GR252" s="1"/>
+      <c r="GY252" s="1"/>
+      <c r="GZ252" s="1"/>
+      <c r="HA252" s="1"/>
+      <c r="HB252" s="1"/>
+      <c r="IC252" t="s">
+        <v>224</v>
+      </c>
+      <c r="IQ252" s="1">
+        <v>884986316</v>
+      </c>
+      <c r="IR252" t="s">
+        <v>2094</v>
+      </c>
+      <c r="IS252" s="1">
+        <v>46298.489814814813</v>
+      </c>
+      <c r="IU252" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW252" t="s">
+        <v>706</v>
+      </c>
+      <c r="IX252" t="s">
+        <v>2095</v>
+      </c>
+      <c r="IY252">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A253" s="1">
+        <v>46300.650030763893</v>
+      </c>
+      <c r="B253" s="1">
+        <v>46300.65832422454</v>
+      </c>
+      <c r="C253" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D253" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E253" t="s">
+        <v>210</v>
+      </c>
+      <c r="F253" t="s">
+        <v>2097</v>
+      </c>
+      <c r="G253" t="s">
+        <v>198</v>
+      </c>
+      <c r="H253" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS253" t="s">
+        <v>2098</v>
+      </c>
+      <c r="BT253" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU253" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW253" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX253" t="s">
+        <v>2099</v>
+      </c>
+      <c r="BY253" t="s">
+        <v>561</v>
+      </c>
+      <c r="EK253" t="s">
+        <v>2100</v>
+      </c>
+      <c r="EL253" t="s">
+        <v>2101</v>
+      </c>
+      <c r="EM253" t="s">
+        <v>2102</v>
+      </c>
+      <c r="EN253" t="s">
+        <v>2103</v>
+      </c>
+      <c r="EY253" s="1"/>
+      <c r="GQ253" s="1"/>
+      <c r="GR253" s="1"/>
+      <c r="GY253" s="1"/>
+      <c r="GZ253" s="1"/>
+      <c r="HA253" s="1"/>
+      <c r="HB253" s="1"/>
+      <c r="IQ253" s="1">
+        <v>886160807</v>
+      </c>
+      <c r="IR253" t="s">
+        <v>2104</v>
+      </c>
+      <c r="IS253" s="1">
+        <v>46300.53334490741</v>
+      </c>
+      <c r="IU253" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW253" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX253" t="s">
+        <v>2105</v>
+      </c>
+      <c r="IY253">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A254" s="1">
+        <v>46300.410002256947</v>
+      </c>
+      <c r="B254" s="1">
+        <v>46300.779925717587</v>
+      </c>
+      <c r="C254" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D254" t="s">
+        <v>690</v>
+      </c>
+      <c r="E254" t="s">
+        <v>254</v>
+      </c>
+      <c r="F254" t="s">
+        <v>765</v>
+      </c>
+      <c r="G254" t="s">
+        <v>198</v>
+      </c>
+      <c r="H254" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX254" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AY254" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ254" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA254" t="s">
+        <v>2106</v>
+      </c>
+      <c r="BB254">
+        <v>10</v>
+      </c>
+      <c r="BC254">
+        <v>8</v>
+      </c>
+      <c r="BD254" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE254" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF254" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG254" t="s">
+        <v>2107</v>
+      </c>
+      <c r="BH254" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI254" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ254" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK254">
+        <v>5</v>
+      </c>
+      <c r="BL254" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM254">
+        <v>58</v>
+      </c>
+      <c r="BN254">
+        <v>89</v>
+      </c>
+      <c r="BO254" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP254" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ254" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS254" t="s">
+        <v>2108</v>
+      </c>
+      <c r="BT254" t="s">
+        <v>2109</v>
+      </c>
+      <c r="BU254" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW254" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX254" t="s">
+        <v>2110</v>
+      </c>
+      <c r="EY254" s="1"/>
+      <c r="GQ254" s="1"/>
+      <c r="GR254" s="1"/>
+      <c r="GY254" s="1"/>
+      <c r="GZ254" s="1"/>
+      <c r="HA254" s="1"/>
+      <c r="HB254" s="1"/>
+      <c r="IQ254" s="1">
+        <v>886310872</v>
+      </c>
+      <c r="IR254" t="s">
+        <v>2111</v>
+      </c>
+      <c r="IS254" s="1">
+        <v>46300.654930555553</v>
+      </c>
+      <c r="IU254" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW254" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX254" t="s">
+        <v>2112</v>
+      </c>
+      <c r="IY254">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A255" s="1">
+        <v>46301.522519942133</v>
+      </c>
+      <c r="B255" s="1">
+        <v>46301.532062418977</v>
+      </c>
+      <c r="C255" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D255" t="s">
+        <v>691</v>
+      </c>
+      <c r="E255" t="s">
+        <v>210</v>
+      </c>
+      <c r="F255" t="s">
+        <v>275</v>
+      </c>
+      <c r="G255" t="s">
+        <v>198</v>
+      </c>
+      <c r="H255" t="s">
+        <v>212</v>
+      </c>
+      <c r="J255" t="s">
+        <v>498</v>
+      </c>
+      <c r="K255" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L255" t="s">
+        <v>2113</v>
+      </c>
+      <c r="M255" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N255" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O255" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R255">
+        <v>16</v>
+      </c>
+      <c r="S255">
+        <v>14</v>
+      </c>
+      <c r="T255" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U255" t="s">
+        <v>2115</v>
+      </c>
+      <c r="V255">
+        <v>0</v>
+      </c>
+      <c r="W255">
+        <v>1</v>
+      </c>
+      <c r="X255">
+        <v>0</v>
+      </c>
+      <c r="Y255">
+        <v>1</v>
+      </c>
+      <c r="Z255">
+        <v>0</v>
+      </c>
+      <c r="AA255">
+        <v>0</v>
+      </c>
+      <c r="AB255" t="s">
+        <v>1817</v>
+      </c>
+      <c r="AC255">
+        <v>1</v>
+      </c>
+      <c r="AD255">
+        <v>0</v>
+      </c>
+      <c r="AE255">
+        <v>0</v>
+      </c>
+      <c r="AF255">
+        <v>0</v>
+      </c>
+      <c r="AG255">
+        <v>0</v>
+      </c>
+      <c r="AH255">
+        <v>520</v>
+      </c>
+      <c r="AI255">
+        <v>200</v>
+      </c>
+      <c r="AJ255">
+        <v>234</v>
+      </c>
+      <c r="AK255">
+        <v>3</v>
+      </c>
+      <c r="AL255">
+        <v>3</v>
+      </c>
+      <c r="AM255">
+        <v>60</v>
+      </c>
+      <c r="AN255">
+        <v>0</v>
+      </c>
+      <c r="AO255" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP255">
+        <v>6</v>
+      </c>
+      <c r="AQ255" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR255" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS255" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT255" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU255" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV255" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW255" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS255" t="s">
+        <v>2116</v>
+      </c>
+      <c r="BT255" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU255" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW255" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX255" t="s">
+        <v>2117</v>
+      </c>
+      <c r="EY255" s="1"/>
+      <c r="GQ255" s="1"/>
+      <c r="GR255" s="1"/>
+      <c r="GY255" s="1"/>
+      <c r="GZ255" s="1"/>
+      <c r="HA255" s="1"/>
+      <c r="HB255" s="1"/>
+      <c r="IQ255" s="1">
+        <v>886860356</v>
+      </c>
+      <c r="IR255" t="s">
+        <v>2118</v>
+      </c>
+      <c r="IS255" s="1">
+        <v>46301.408761574072</v>
+      </c>
+      <c r="IU255" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW255" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX255" t="s">
+        <v>2119</v>
+      </c>
+      <c r="IY255">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A256" s="1">
+        <v>46301.532065358799</v>
+      </c>
+      <c r="B256" s="1">
+        <v>46301.538736805553</v>
+      </c>
+      <c r="C256" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D256" t="s">
+        <v>690</v>
+      </c>
+      <c r="E256" t="s">
+        <v>210</v>
+      </c>
+      <c r="F256" t="s">
+        <v>275</v>
+      </c>
+      <c r="G256" t="s">
+        <v>198</v>
+      </c>
+      <c r="H256" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX256" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY256" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ256" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA256" t="s">
+        <v>2120</v>
+      </c>
+      <c r="BB256">
+        <v>6</v>
+      </c>
+      <c r="BC256">
+        <v>4</v>
+      </c>
+      <c r="BD256" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE256" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF256" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG256" t="s">
+        <v>2121</v>
+      </c>
+      <c r="BH256" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI256" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ256" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK256">
+        <v>5</v>
+      </c>
+      <c r="BL256" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM256">
+        <v>300</v>
+      </c>
+      <c r="BN256">
+        <v>250</v>
+      </c>
+      <c r="BO256" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP256" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ256" t="s">
+        <v>1630</v>
+      </c>
+      <c r="BS256" t="s">
+        <v>2122</v>
+      </c>
+      <c r="BT256" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU256" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW256" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX256" t="s">
+        <v>2123</v>
+      </c>
+      <c r="EY256" s="1"/>
+      <c r="GQ256" s="1"/>
+      <c r="GR256" s="1"/>
+      <c r="GY256" s="1"/>
+      <c r="GZ256" s="1"/>
+      <c r="HA256" s="1"/>
+      <c r="HB256" s="1"/>
+      <c r="IQ256" s="1">
+        <v>886876407</v>
+      </c>
+      <c r="IR256" t="s">
+        <v>2124</v>
+      </c>
+      <c r="IS256" s="1">
+        <v>46301.421956018523</v>
+      </c>
+      <c r="IU256" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW256" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX256" t="s">
+        <v>2125</v>
+      </c>
+      <c r="IY256">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A257" s="1">
+        <v>46301.538739317133</v>
+      </c>
+      <c r="B257" s="1">
+        <v>46301.546786574072</v>
+      </c>
+      <c r="C257" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D257" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E257" t="s">
+        <v>210</v>
+      </c>
+      <c r="F257" t="s">
+        <v>275</v>
+      </c>
+      <c r="G257" t="s">
+        <v>198</v>
+      </c>
+      <c r="H257" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS257" t="s">
+        <v>954</v>
+      </c>
+      <c r="BT257" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU257" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW257" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX257" t="s">
+        <v>2126</v>
+      </c>
+      <c r="BY257" t="s">
+        <v>359</v>
+      </c>
+      <c r="EK257" t="s">
+        <v>2127</v>
+      </c>
+      <c r="EL257" t="s">
+        <v>2128</v>
+      </c>
+      <c r="EM257" t="s">
+        <v>2129</v>
+      </c>
+      <c r="EN257" t="s">
+        <v>2130</v>
+      </c>
+      <c r="EY257" s="1"/>
+      <c r="GQ257" s="1"/>
+      <c r="GR257" s="1"/>
+      <c r="GY257" s="1"/>
+      <c r="GZ257" s="1"/>
+      <c r="HA257" s="1"/>
+      <c r="HB257" s="1"/>
+      <c r="IQ257" s="1">
+        <v>886876415</v>
+      </c>
+      <c r="IR257" t="s">
+        <v>2131</v>
+      </c>
+      <c r="IS257" s="1">
+        <v>46301.421967592592</v>
+      </c>
+      <c r="IU257" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW257" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX257" t="s">
+        <v>2132</v>
+      </c>
+      <c r="IY257">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A258" s="1">
+        <v>46301.478870706022</v>
+      </c>
+      <c r="B258" s="1">
+        <v>46301.674378379626</v>
+      </c>
+      <c r="C258" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D258" t="s">
+        <v>690</v>
+      </c>
+      <c r="E258" t="s">
+        <v>196</v>
+      </c>
+      <c r="F258" t="s">
+        <v>777</v>
+      </c>
+      <c r="G258" t="s">
+        <v>198</v>
+      </c>
+      <c r="H258" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX258" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY258" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ258" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA258" t="s">
+        <v>2010</v>
+      </c>
+      <c r="BB258">
+        <v>40</v>
+      </c>
+      <c r="BC258">
+        <v>3</v>
+      </c>
+      <c r="BD258" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE258" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF258" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG258" t="s">
+        <v>2133</v>
+      </c>
+      <c r="BH258" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI258" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ258" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK258">
+        <v>4</v>
+      </c>
+      <c r="BL258" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM258">
+        <v>15</v>
+      </c>
+      <c r="BN258">
+        <v>30</v>
+      </c>
+      <c r="BO258" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP258" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ258" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS258" t="s">
+        <v>1122</v>
+      </c>
+      <c r="BT258" t="s">
+        <v>1637</v>
+      </c>
+      <c r="BU258" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV258" t="s">
+        <v>2134</v>
+      </c>
+      <c r="BW258" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX258" t="s">
+        <v>1135</v>
+      </c>
+      <c r="EY258" s="1"/>
+      <c r="GQ258" s="1"/>
+      <c r="GR258" s="1"/>
+      <c r="GY258" s="1"/>
+      <c r="GZ258" s="1"/>
+      <c r="HA258" s="1"/>
+      <c r="HB258" s="1"/>
+      <c r="IQ258" s="1">
+        <v>887049943</v>
+      </c>
+      <c r="IR258" t="s">
+        <v>2135</v>
+      </c>
+      <c r="IS258" s="1">
+        <v>46301.549386574072</v>
+      </c>
+      <c r="IU258" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW258" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX258" t="s">
+        <v>2136</v>
+      </c>
+      <c r="IY258">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A259" s="1">
+        <v>46302.423721701387</v>
+      </c>
+      <c r="B259" s="1">
+        <v>46302.433867326392</v>
+      </c>
+      <c r="C259" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D259" t="s">
+        <v>691</v>
+      </c>
+      <c r="E259" t="s">
+        <v>280</v>
+      </c>
+      <c r="F259" t="s">
+        <v>281</v>
+      </c>
+      <c r="G259" t="s">
+        <v>198</v>
+      </c>
+      <c r="H259" t="s">
+        <v>282</v>
+      </c>
+      <c r="J259" t="s">
+        <v>283</v>
+      </c>
+      <c r="K259" t="s">
+        <v>201</v>
+      </c>
+      <c r="L259" t="s">
+        <v>395</v>
+      </c>
+      <c r="M259" t="s">
+        <v>612</v>
+      </c>
+      <c r="N259" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O259" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P259" t="s">
+        <v>2050</v>
+      </c>
+      <c r="AH259">
+        <v>503</v>
+      </c>
+      <c r="AI259">
+        <v>102</v>
+      </c>
+      <c r="AJ259">
+        <v>138</v>
+      </c>
+      <c r="AK259">
+        <v>3</v>
+      </c>
+      <c r="AL259">
+        <v>2</v>
+      </c>
+      <c r="AM259">
+        <v>45</v>
+      </c>
+      <c r="AN259">
+        <v>15</v>
+      </c>
+      <c r="AO259" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AP259">
+        <v>3</v>
+      </c>
+      <c r="AQ259" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR259" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS259" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT259" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU259" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV259" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW259" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS259" t="s">
+        <v>2137</v>
+      </c>
+      <c r="BT259" t="s">
+        <v>2138</v>
+      </c>
+      <c r="BU259" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW259" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX259" t="s">
+        <v>2139</v>
+      </c>
+      <c r="EY259" s="1"/>
+      <c r="GQ259" s="1"/>
+      <c r="GR259" s="1"/>
+      <c r="GY259" s="1"/>
+      <c r="GZ259" s="1"/>
+      <c r="HA259" s="1"/>
+      <c r="HB259" s="1"/>
+      <c r="IQ259" s="1">
+        <v>887702059</v>
+      </c>
+      <c r="IR259" t="s">
+        <v>2140</v>
+      </c>
+      <c r="IS259" s="1">
+        <v>46302.300578703696</v>
+      </c>
+      <c r="IU259" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW259" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX259" t="s">
+        <v>2141</v>
+      </c>
+      <c r="IY259">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A260" s="1">
+        <v>46302.43387108796</v>
+      </c>
+      <c r="B260" s="1">
+        <v>46302.44524734954</v>
+      </c>
+      <c r="C260" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D260" t="s">
+        <v>691</v>
+      </c>
+      <c r="E260" t="s">
+        <v>280</v>
+      </c>
+      <c r="F260" t="s">
+        <v>281</v>
+      </c>
+      <c r="G260" t="s">
+        <v>198</v>
+      </c>
+      <c r="H260" t="s">
+        <v>282</v>
+      </c>
+      <c r="J260" t="s">
+        <v>2142</v>
+      </c>
+      <c r="K260" t="s">
+        <v>201</v>
+      </c>
+      <c r="L260" t="s">
+        <v>395</v>
+      </c>
+      <c r="M260" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N260" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O260" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P260" t="s">
+        <v>1702</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>2143</v>
+      </c>
+      <c r="AH260">
+        <v>3269</v>
+      </c>
+      <c r="AI260">
+        <v>604</v>
+      </c>
+      <c r="AJ260">
+        <v>717</v>
+      </c>
+      <c r="AK260">
+        <v>5</v>
+      </c>
+      <c r="AL260">
+        <v>2</v>
+      </c>
+      <c r="AM260">
+        <v>50</v>
+      </c>
+      <c r="AN260">
+        <v>30</v>
+      </c>
+      <c r="AO260" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP260">
+        <v>12</v>
+      </c>
+      <c r="AQ260" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR260" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS260" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT260" t="s">
+        <v>216</v>
+      </c>
+      <c r="AU260" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV260" t="s">
+        <v>284</v>
+      </c>
+      <c r="AW260" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS260" t="s">
+        <v>2144</v>
+      </c>
+      <c r="BT260" t="s">
+        <v>2145</v>
+      </c>
+      <c r="BU260" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW260" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX260" t="s">
+        <v>2146</v>
+      </c>
+      <c r="EY260" s="1"/>
+      <c r="GQ260" s="1"/>
+      <c r="GR260" s="1"/>
+      <c r="GY260" s="1"/>
+      <c r="GZ260" s="1"/>
+      <c r="HA260" s="1"/>
+      <c r="HB260" s="1"/>
+      <c r="IQ260" s="1">
+        <v>887714978</v>
+      </c>
+      <c r="IR260" t="s">
+        <v>2147</v>
+      </c>
+      <c r="IS260" s="1">
+        <v>46302.311956018522</v>
+      </c>
+      <c r="IU260" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW260" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX260" t="s">
+        <v>2148</v>
+      </c>
+      <c r="IY260">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A261" s="1">
+        <v>46302.446020150463</v>
+      </c>
+      <c r="B261" s="1">
+        <v>46302.453492060187</v>
+      </c>
+      <c r="C261" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D261" t="s">
+        <v>354</v>
+      </c>
+      <c r="E261" t="s">
+        <v>280</v>
+      </c>
+      <c r="F261" t="s">
+        <v>281</v>
+      </c>
+      <c r="G261" t="s">
+        <v>198</v>
+      </c>
+      <c r="H261" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS261" t="s">
+        <v>2149</v>
+      </c>
+      <c r="BT261" t="s">
+        <v>2150</v>
+      </c>
+      <c r="BU261" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW261" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX261" t="s">
+        <v>2151</v>
+      </c>
+      <c r="BY261" t="s">
+        <v>359</v>
+      </c>
+      <c r="CB261" t="s">
+        <v>404</v>
+      </c>
+      <c r="CC261">
+        <v>3</v>
+      </c>
+      <c r="CD261">
+        <v>407</v>
+      </c>
+      <c r="CE261" t="s">
+        <v>361</v>
+      </c>
+      <c r="CF261" t="s">
+        <v>2152</v>
+      </c>
+      <c r="CG261" t="s">
+        <v>363</v>
+      </c>
+      <c r="CH261" t="s">
+        <v>2153</v>
+      </c>
+      <c r="CI261" t="s">
+        <v>458</v>
+      </c>
+      <c r="CK261" t="s">
+        <v>366</v>
+      </c>
+      <c r="CL261" t="s">
+        <v>2154</v>
+      </c>
+      <c r="CM261" t="s">
+        <v>460</v>
+      </c>
+      <c r="CN261" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY261" s="1"/>
+      <c r="GQ261" s="1"/>
+      <c r="GR261" s="1"/>
+      <c r="GY261" s="1"/>
+      <c r="GZ261" s="1"/>
+      <c r="HA261" s="1"/>
+      <c r="HB261" s="1"/>
+      <c r="IQ261" s="1">
+        <v>887725061</v>
+      </c>
+      <c r="IR261" t="s">
+        <v>2155</v>
+      </c>
+      <c r="IS261" s="1">
+        <v>46302.320196759261</v>
+      </c>
+      <c r="IU261" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW261" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX261" t="s">
+        <v>2156</v>
+      </c>
+      <c r="IY261">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A262" s="1">
+        <v>46302.438089305557</v>
+      </c>
+      <c r="B262" s="1">
+        <v>46302.448505243046</v>
+      </c>
+      <c r="C262" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D262" t="s">
+        <v>691</v>
+      </c>
+      <c r="E262" t="s">
+        <v>309</v>
+      </c>
+      <c r="F262" t="s">
+        <v>2157</v>
+      </c>
+      <c r="G262" t="s">
+        <v>198</v>
+      </c>
+      <c r="H262" t="s">
+        <v>311</v>
+      </c>
+      <c r="J262" t="s">
+        <v>2158</v>
+      </c>
+      <c r="K262" t="s">
+        <v>201</v>
+      </c>
+      <c r="L262" t="s">
+        <v>324</v>
+      </c>
+      <c r="M262" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N262" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O262" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH262">
+        <v>680</v>
+      </c>
+      <c r="AI262">
+        <v>0</v>
+      </c>
+      <c r="AJ262">
+        <v>0</v>
+      </c>
+      <c r="AK262">
+        <v>48</v>
+      </c>
+      <c r="AL262">
+        <v>2</v>
+      </c>
+      <c r="AM262">
+        <v>50</v>
+      </c>
+      <c r="AN262">
+        <v>0</v>
+      </c>
+      <c r="AO262" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AP262">
+        <v>0</v>
+      </c>
+      <c r="AQ262" t="s">
+        <v>340</v>
+      </c>
+      <c r="AR262" t="s">
+        <v>341</v>
+      </c>
+      <c r="AS262" t="s">
+        <v>216</v>
+      </c>
+      <c r="AT262" t="s">
+        <v>216</v>
+      </c>
+      <c r="AU262" t="s">
+        <v>216</v>
+      </c>
+      <c r="AV262" t="s">
+        <v>204</v>
+      </c>
+      <c r="AW262" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS262" t="s">
+        <v>2159</v>
+      </c>
+      <c r="BT262" t="s">
+        <v>2160</v>
+      </c>
+      <c r="BU262" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW262" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX262" t="s">
+        <v>2161</v>
+      </c>
+      <c r="EY262" s="1"/>
+      <c r="GQ262" s="1"/>
+      <c r="GR262" s="1"/>
+      <c r="GY262" s="1"/>
+      <c r="GZ262" s="1"/>
+      <c r="HA262" s="1"/>
+      <c r="HB262" s="1"/>
+      <c r="IQ262" s="1">
+        <v>887729173</v>
+      </c>
+      <c r="IR262" t="s">
+        <v>2162</v>
+      </c>
+      <c r="IS262" s="1">
+        <v>46302.323530092603</v>
+      </c>
+      <c r="IU262" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW262" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX262" t="s">
+        <v>2163</v>
+      </c>
+      <c r="IY262">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A263" s="1">
+        <v>46302.326570335637</v>
+      </c>
+      <c r="B263" s="1">
+        <v>46302.464538182867</v>
+      </c>
+      <c r="C263" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D263" t="s">
+        <v>690</v>
+      </c>
+      <c r="E263" t="s">
+        <v>254</v>
+      </c>
+      <c r="F263" t="s">
+        <v>2164</v>
+      </c>
+      <c r="G263" t="s">
+        <v>198</v>
+      </c>
+      <c r="H263" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX263" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY263" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ263" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA263" t="s">
+        <v>2165</v>
+      </c>
+      <c r="BB263">
+        <v>5</v>
+      </c>
+      <c r="BC263">
+        <v>3</v>
+      </c>
+      <c r="BD263" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE263" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF263" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG263" t="s">
+        <v>2166</v>
+      </c>
+      <c r="BH263" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI263" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ263" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK263">
+        <v>4</v>
+      </c>
+      <c r="BL263" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM263">
+        <v>56</v>
+      </c>
+      <c r="BN263">
+        <v>120</v>
+      </c>
+      <c r="BO263" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP263" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ263" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS263" t="s">
+        <v>2167</v>
+      </c>
+      <c r="BT263" t="s">
+        <v>2168</v>
+      </c>
+      <c r="BU263" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV263" t="s">
+        <v>2169</v>
+      </c>
+      <c r="BW263" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX263" t="s">
+        <v>2170</v>
+      </c>
+      <c r="EY263" s="1"/>
+      <c r="GQ263" s="1"/>
+      <c r="GR263" s="1"/>
+      <c r="GY263" s="1"/>
+      <c r="GZ263" s="1"/>
+      <c r="HA263" s="1"/>
+      <c r="HB263" s="1"/>
+      <c r="IQ263" s="1">
+        <v>887748221</v>
+      </c>
+      <c r="IR263" t="s">
+        <v>2171</v>
+      </c>
+      <c r="IS263" s="1">
+        <v>46302.339548611111</v>
+      </c>
+      <c r="IU263" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW263" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX263" t="s">
+        <v>2172</v>
+      </c>
+      <c r="IY263">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A264" s="1">
+        <v>46302.332111678239</v>
+      </c>
+      <c r="B264" s="1">
+        <v>46302.464770451392</v>
+      </c>
+      <c r="C264" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D264" t="s">
+        <v>690</v>
+      </c>
+      <c r="E264" t="s">
+        <v>254</v>
+      </c>
+      <c r="F264" t="s">
+        <v>2164</v>
+      </c>
+      <c r="G264" t="s">
+        <v>198</v>
+      </c>
+      <c r="H264" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX264" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY264" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ264" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA264" t="s">
+        <v>2173</v>
+      </c>
+      <c r="BB264">
+        <v>5</v>
+      </c>
+      <c r="BC264">
+        <v>0</v>
+      </c>
+      <c r="BD264" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE264" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF264" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG264" t="s">
+        <v>2174</v>
+      </c>
+      <c r="BH264" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI264" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ264" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK264">
+        <v>5</v>
+      </c>
+      <c r="BL264" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM264">
+        <v>200</v>
+      </c>
+      <c r="BN264">
+        <v>340</v>
+      </c>
+      <c r="BO264" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP264" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ264" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BS264" t="s">
+        <v>2175</v>
+      </c>
+      <c r="BT264" t="s">
+        <v>2176</v>
+      </c>
+      <c r="BU264" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV264" t="s">
+        <v>2177</v>
+      </c>
+      <c r="BW264" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX264" t="s">
+        <v>2178</v>
+      </c>
+      <c r="EY264" s="1"/>
+      <c r="GQ264" s="1"/>
+      <c r="GR264" s="1"/>
+      <c r="GY264" s="1"/>
+      <c r="GZ264" s="1"/>
+      <c r="HA264" s="1"/>
+      <c r="HB264" s="1"/>
+      <c r="IQ264" s="1">
+        <v>887748499</v>
+      </c>
+      <c r="IR264" t="s">
+        <v>2179</v>
+      </c>
+      <c r="IS264" s="1">
+        <v>46302.339780092603</v>
+      </c>
+      <c r="IU264" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW264" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX264" t="s">
+        <v>2180</v>
+      </c>
+      <c r="IY264">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A265" s="1">
+        <v>46302.480987708332</v>
+      </c>
+      <c r="B265" s="1">
+        <v>46302.48536146991</v>
+      </c>
+      <c r="C265" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D265" t="s">
+        <v>354</v>
+      </c>
+      <c r="E265" t="s">
+        <v>280</v>
+      </c>
+      <c r="F265" t="s">
+        <v>281</v>
+      </c>
+      <c r="G265" t="s">
+        <v>198</v>
+      </c>
+      <c r="H265" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS265" t="s">
+        <v>2181</v>
+      </c>
+      <c r="BT265" t="s">
+        <v>2182</v>
+      </c>
+      <c r="BU265" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW265" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX265" t="s">
+        <v>2183</v>
+      </c>
+      <c r="BY265" t="s">
+        <v>359</v>
+      </c>
+      <c r="CB265" t="s">
+        <v>360</v>
+      </c>
+      <c r="CC265">
+        <v>5</v>
+      </c>
+      <c r="CD265">
+        <v>3269</v>
+      </c>
+      <c r="CE265" t="s">
+        <v>361</v>
+      </c>
+      <c r="CF265" t="s">
+        <v>1648</v>
+      </c>
+      <c r="CG265" t="s">
+        <v>392</v>
+      </c>
+      <c r="CH265" t="s">
+        <v>2184</v>
+      </c>
+      <c r="CI265" t="s">
+        <v>458</v>
+      </c>
+      <c r="CK265" t="s">
+        <v>366</v>
+      </c>
+      <c r="CL265" t="s">
+        <v>2185</v>
+      </c>
+      <c r="CM265" t="s">
+        <v>368</v>
+      </c>
+      <c r="CN265" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY265" s="1"/>
+      <c r="GQ265" s="1"/>
+      <c r="GR265" s="1"/>
+      <c r="GY265" s="1"/>
+      <c r="GZ265" s="1"/>
+      <c r="HA265" s="1"/>
+      <c r="HB265" s="1"/>
+      <c r="IQ265" s="1">
+        <v>887764786</v>
+      </c>
+      <c r="IR265" t="s">
+        <v>2186</v>
+      </c>
+      <c r="IS265" s="1">
+        <v>46302.352071759262</v>
+      </c>
+      <c r="IU265" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW265" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX265" t="s">
+        <v>2187</v>
+      </c>
+      <c r="IY265">
+        <v>264</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="377" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{868EC490-CBCF-2C45-81EB-2BC9B17CD40F}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54EF4CB0-AFCE-914B-8063-4FF879F015EE}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="1500" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId3"/>
+    <pivotCache cacheId="6" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6444" uniqueCount="2188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6678" uniqueCount="2252">
   <si>
     <t>start</t>
   </si>
@@ -6601,6 +6601,198 @@
   </si>
   <si>
     <t>uuid:5ee8b729-ee78-4727-bd2f-07765ca81721</t>
+  </si>
+  <si>
+    <t>The last outbreak was a business transaction for government they wanted money after spending alot on elections,when i wear a mask idont get Ebola</t>
+  </si>
+  <si>
+    <t>Trust in individuals but not government</t>
+  </si>
+  <si>
+    <t>Need to engage communities to address the misinformation</t>
+  </si>
+  <si>
+    <t>If it's the wrong diagnosis</t>
+  </si>
+  <si>
+    <t>As long as the authorities assure us that the person is completely healed, no problem but i know that not everyone is going to accept them.back</t>
+  </si>
+  <si>
+    <t>Am not sure may be later but not immediately</t>
+  </si>
+  <si>
+    <t>e105b323-993d-454e-afe2-40e8a8f11d01</t>
+  </si>
+  <si>
+    <t>uuid:e105b323-993d-454e-afe2-40e8a8f11d01</t>
+  </si>
+  <si>
+    <t>Last Ebola outbreak was a government lie,Covid was made by the Chinese, Ebola and Mpox are caused the same way</t>
+  </si>
+  <si>
+    <t>Outbreaks have been politised, mistrust of government</t>
+  </si>
+  <si>
+    <t>Social engagements ,government intervention ,need to verify the source</t>
+  </si>
+  <si>
+    <t>Moderately clean</t>
+  </si>
+  <si>
+    <t>After declaring Uganda free the market vendors relaxed and items like the hand washing equipment were kept</t>
+  </si>
+  <si>
+    <t>The market is populated with about 600 people but with 3 units for each sez</t>
+  </si>
+  <si>
+    <t>5154acc5-7a10-4ca6-a2e8-ebd37b9a187b</t>
+  </si>
+  <si>
+    <t>uuid:5154acc5-7a10-4ca6-a2e8-ebd37b9a187b</t>
+  </si>
+  <si>
+    <t>Market leaders</t>
+  </si>
+  <si>
+    <t>To put back the hand washing stations,  and in the meetings have a segment on health</t>
+  </si>
+  <si>
+    <t>Why do these outbreaks come.in particular seasons?</t>
+  </si>
+  <si>
+    <t>Expecting government to take the whole burden of intervention ie provide sanitizers, bring the hand washing equipment, soap without community taking any responsibility</t>
+  </si>
+  <si>
+    <t>Need for individual and community responsibility for their own health</t>
+  </si>
+  <si>
+    <t>c9da5eb0-b506-4f14-8335-d39afe9c4527</t>
+  </si>
+  <si>
+    <t>uuid:c9da5eb0-b506-4f14-8335-d39afe9c4527</t>
+  </si>
+  <si>
+    <t>Special hire.team at Kamwokya market</t>
+  </si>
+  <si>
+    <t>To be on the lookout for signs and symptoms, use sanitizers in their daily dealings and talk to their customers about being prepared for emergencies</t>
+  </si>
+  <si>
+    <t>Last outbreak Ebola was in Congo but not here in Uganda government's was looking for money  ,it was staged.Why is it no one knows the suspects</t>
+  </si>
+  <si>
+    <t>Here they don't believe in the government at all,the level of mistrust is alarming</t>
+  </si>
+  <si>
+    <t>It seems Kamwokya as a parish is opposed to government and all it represents</t>
+  </si>
+  <si>
+    <t>Need to separate health issues from politics</t>
+  </si>
+  <si>
+    <t>4f85b311-39d2-4e9e-8446-adf7e0cf2313</t>
+  </si>
+  <si>
+    <t>uuid:4f85b311-39d2-4e9e-8446-adf7e0cf2313</t>
+  </si>
+  <si>
+    <t>Why does government fool us? We didn't  and do not have an outbreak</t>
+  </si>
+  <si>
+    <t>The slum settings have proven a challenge the youth are using drugs ,high crime rates</t>
+  </si>
+  <si>
+    <t>Need to address the challenges of the community ie engaging the youth in economic development, fight drug abuse and sexual immorality among the teen</t>
+  </si>
+  <si>
+    <t>I believe the signs and symptoms  of Ebola are more severe and rapid</t>
+  </si>
+  <si>
+    <t>By seeking help from a health facility, or calling Police</t>
+  </si>
+  <si>
+    <t>We will normally interact with them but will not let them do heavy work because i think they suffer permanent side effects,</t>
+  </si>
+  <si>
+    <t>I will social distance</t>
+  </si>
+  <si>
+    <t>Rejection</t>
+  </si>
+  <si>
+    <t>f6f87c0a-2378-46bf-b2dd-618cab7ef2ad</t>
+  </si>
+  <si>
+    <t>uuid:f6f87c0a-2378-46bf-b2dd-618cab7ef2ad</t>
+  </si>
+  <si>
+    <t>What are the side effects of Ebola, what do the survivors deal with?</t>
+  </si>
+  <si>
+    <t>Today i have not wasted yet</t>
+  </si>
+  <si>
+    <t>No where</t>
+  </si>
+  <si>
+    <t>are soap residues</t>
+  </si>
+  <si>
+    <t>f9db2eb8-1777-4a6d-89af-8741254b008a</t>
+  </si>
+  <si>
+    <t>uuid:f9db2eb8-1777-4a6d-89af-8741254b008a</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Class talks</t>
+  </si>
+  <si>
+    <t>Now that the person who died of ebola in Kenya passed in Uganda, does it mean we have cases in Uganda now</t>
+  </si>
+  <si>
+    <t>a2f1ad47-b088-4084-9a40-1c674afd354f</t>
+  </si>
+  <si>
+    <t>uuid:a2f1ad47-b088-4084-9a40-1c674afd354f</t>
+  </si>
+  <si>
+    <t>The school pupils and some teachers had less knowledge about PHE,the school has a high population of students but had few handwashing facilities.</t>
+  </si>
+  <si>
+    <t>The distribution of snakes and ladders game, wheel sessions and introduction of a U-report health club club to boost the knowledge of the students. Through the games that help them understand the PHE.</t>
+  </si>
+  <si>
+    <t>Currently the school health club presents health tips to the pupils during assembly time. This helps the learners understand well health issues.</t>
+  </si>
+  <si>
+    <t>The change is significant because it practiced.</t>
+  </si>
+  <si>
+    <t>34d00fbe-215d-47d3-aa69-c074c4702b39</t>
+  </si>
+  <si>
+    <t>uuid:34d00fbe-215d-47d3-aa69-c074c4702b39</t>
+  </si>
+  <si>
+    <t>Nabweru south</t>
+  </si>
+  <si>
+    <t>Motherland academy secondary school</t>
+  </si>
+  <si>
+    <t>School assembly Class talks</t>
+  </si>
+  <si>
+    <t>Ebola is no longer a threat</t>
+  </si>
+  <si>
+    <t>d3324116-878e-4189-a21b-e650dffea3e1</t>
+  </si>
+  <si>
+    <t>uuid:d3324116-878e-4189-a21b-e650dffea3e1</t>
   </si>
 </sst>
 </file>
@@ -20655,7 +20847,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -21005,8 +21197,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY265" totalsRowShown="0">
-  <autoFilter ref="A1:IY265" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY274" totalsRowShown="0">
+  <autoFilter ref="A1:IY274" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -21559,7 +21751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY265"/>
+  <dimension ref="A1:IY274"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -52302,6 +52494,1167 @@
         <v>264</v>
       </c>
     </row>
+    <row r="266" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A266" s="1">
+        <v>46302.507625208331</v>
+      </c>
+      <c r="B266" s="1">
+        <v>46302.513549675918</v>
+      </c>
+      <c r="C266" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D266" t="s">
+        <v>952</v>
+      </c>
+      <c r="E266" t="s">
+        <v>280</v>
+      </c>
+      <c r="F266" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G266" t="s">
+        <v>198</v>
+      </c>
+      <c r="H266" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS266" t="s">
+        <v>2188</v>
+      </c>
+      <c r="BT266" t="s">
+        <v>2189</v>
+      </c>
+      <c r="BU266" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW266" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX266" t="s">
+        <v>2190</v>
+      </c>
+      <c r="BY266" t="s">
+        <v>456</v>
+      </c>
+      <c r="DE266" t="s">
+        <v>1289</v>
+      </c>
+      <c r="DF266" t="s">
+        <v>1029</v>
+      </c>
+      <c r="DG266">
+        <v>0</v>
+      </c>
+      <c r="DH266">
+        <v>0</v>
+      </c>
+      <c r="DI266">
+        <v>1</v>
+      </c>
+      <c r="DJ266">
+        <v>1</v>
+      </c>
+      <c r="DK266">
+        <v>0</v>
+      </c>
+      <c r="DY266" t="s">
+        <v>962</v>
+      </c>
+      <c r="DZ266" t="s">
+        <v>2191</v>
+      </c>
+      <c r="EA266" t="s">
+        <v>964</v>
+      </c>
+      <c r="EC266" t="s">
+        <v>2192</v>
+      </c>
+      <c r="ED266" t="s">
+        <v>2193</v>
+      </c>
+      <c r="EE266" t="s">
+        <v>1147</v>
+      </c>
+      <c r="EY266" s="1"/>
+      <c r="GQ266" s="1"/>
+      <c r="GR266" s="1"/>
+      <c r="GY266" s="1"/>
+      <c r="GZ266" s="1"/>
+      <c r="HA266" s="1"/>
+      <c r="HB266" s="1"/>
+      <c r="IQ266" s="1">
+        <v>887801308</v>
+      </c>
+      <c r="IR266" t="s">
+        <v>2194</v>
+      </c>
+      <c r="IS266" s="1">
+        <v>46302.380254629628</v>
+      </c>
+      <c r="IU266" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW266" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX266" t="s">
+        <v>2195</v>
+      </c>
+      <c r="IY266">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A267" s="1">
+        <v>46302.632995671287</v>
+      </c>
+      <c r="B267" s="1">
+        <v>46302.641289837957</v>
+      </c>
+      <c r="C267" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D267" t="s">
+        <v>354</v>
+      </c>
+      <c r="E267" t="s">
+        <v>280</v>
+      </c>
+      <c r="F267" t="s">
+        <v>349</v>
+      </c>
+      <c r="G267" t="s">
+        <v>198</v>
+      </c>
+      <c r="H267" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS267" t="s">
+        <v>2196</v>
+      </c>
+      <c r="BT267" t="s">
+        <v>2197</v>
+      </c>
+      <c r="BU267" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW267" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX267" t="s">
+        <v>2198</v>
+      </c>
+      <c r="BY267" t="s">
+        <v>456</v>
+      </c>
+      <c r="CB267" t="s">
+        <v>511</v>
+      </c>
+      <c r="CC267">
+        <v>6</v>
+      </c>
+      <c r="CD267">
+        <v>400</v>
+      </c>
+      <c r="CE267" t="s">
+        <v>405</v>
+      </c>
+      <c r="CF267" t="s">
+        <v>2199</v>
+      </c>
+      <c r="CG267" t="s">
+        <v>392</v>
+      </c>
+      <c r="CH267" t="s">
+        <v>2200</v>
+      </c>
+      <c r="CI267" t="s">
+        <v>365</v>
+      </c>
+      <c r="CJ267" t="s">
+        <v>395</v>
+      </c>
+      <c r="CK267" t="s">
+        <v>515</v>
+      </c>
+      <c r="CL267" t="s">
+        <v>2201</v>
+      </c>
+      <c r="CM267" t="s">
+        <v>460</v>
+      </c>
+      <c r="CN267" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY267" s="1"/>
+      <c r="GQ267" s="1"/>
+      <c r="GR267" s="1"/>
+      <c r="GY267" s="1"/>
+      <c r="GZ267" s="1"/>
+      <c r="HA267" s="1"/>
+      <c r="HB267" s="1"/>
+      <c r="IQ267" s="1">
+        <v>887977037</v>
+      </c>
+      <c r="IR267" t="s">
+        <v>2202</v>
+      </c>
+      <c r="IS267" s="1">
+        <v>46302.507997685178</v>
+      </c>
+      <c r="IU267" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW267" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX267" t="s">
+        <v>2203</v>
+      </c>
+      <c r="IY267">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A268" s="1">
+        <v>46302.659143252313</v>
+      </c>
+      <c r="B268" s="1">
+        <v>46302.667036666673</v>
+      </c>
+      <c r="C268" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D268" t="s">
+        <v>690</v>
+      </c>
+      <c r="E268" t="s">
+        <v>280</v>
+      </c>
+      <c r="F268" t="s">
+        <v>349</v>
+      </c>
+      <c r="G268" t="s">
+        <v>198</v>
+      </c>
+      <c r="H268" t="s">
+        <v>282</v>
+      </c>
+      <c r="AX268" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY268" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ268" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA268" t="s">
+        <v>2204</v>
+      </c>
+      <c r="BB268">
+        <v>5</v>
+      </c>
+      <c r="BC268">
+        <v>4</v>
+      </c>
+      <c r="BD268" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE268" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF268" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG268" t="s">
+        <v>2205</v>
+      </c>
+      <c r="BH268" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI268" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ268" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK268">
+        <v>8</v>
+      </c>
+      <c r="BL268" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM268">
+        <v>200</v>
+      </c>
+      <c r="BN268">
+        <v>180</v>
+      </c>
+      <c r="BO268" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP268" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ268" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS268" t="s">
+        <v>2206</v>
+      </c>
+      <c r="BT268" t="s">
+        <v>2207</v>
+      </c>
+      <c r="BU268" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW268" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX268" t="s">
+        <v>2208</v>
+      </c>
+      <c r="EY268" s="1"/>
+      <c r="GQ268" s="1"/>
+      <c r="GR268" s="1"/>
+      <c r="GY268" s="1"/>
+      <c r="GZ268" s="1"/>
+      <c r="HA268" s="1"/>
+      <c r="HB268" s="1"/>
+      <c r="IQ268" s="1">
+        <v>888016191</v>
+      </c>
+      <c r="IR268" t="s">
+        <v>2209</v>
+      </c>
+      <c r="IS268" s="1">
+        <v>46302.533738425933</v>
+      </c>
+      <c r="IU268" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW268" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX268" t="s">
+        <v>2210</v>
+      </c>
+      <c r="IY268">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A269" s="1">
+        <v>46302.674566250003</v>
+      </c>
+      <c r="B269" s="1">
+        <v>46302.684317071762</v>
+      </c>
+      <c r="C269" s="1">
+        <v>46297</v>
+      </c>
+      <c r="D269" t="s">
+        <v>690</v>
+      </c>
+      <c r="E269" t="s">
+        <v>280</v>
+      </c>
+      <c r="F269" t="s">
+        <v>349</v>
+      </c>
+      <c r="G269" t="s">
+        <v>198</v>
+      </c>
+      <c r="H269" t="s">
+        <v>282</v>
+      </c>
+      <c r="AX269" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AY269" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ269" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA269" t="s">
+        <v>2211</v>
+      </c>
+      <c r="BB269">
+        <v>22</v>
+      </c>
+      <c r="BC269">
+        <v>3</v>
+      </c>
+      <c r="BD269" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE269" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF269" t="s">
+        <v>395</v>
+      </c>
+      <c r="BG269" t="s">
+        <v>2212</v>
+      </c>
+      <c r="BH269" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI269" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ269" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK269">
+        <v>12</v>
+      </c>
+      <c r="BL269" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM269">
+        <v>180</v>
+      </c>
+      <c r="BN269">
+        <v>90</v>
+      </c>
+      <c r="BO269" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP269" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ269" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BS269" t="s">
+        <v>2213</v>
+      </c>
+      <c r="BT269" t="s">
+        <v>2214</v>
+      </c>
+      <c r="BU269" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV269" t="s">
+        <v>2215</v>
+      </c>
+      <c r="BW269" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX269" t="s">
+        <v>2216</v>
+      </c>
+      <c r="EY269" s="1"/>
+      <c r="GQ269" s="1"/>
+      <c r="GR269" s="1"/>
+      <c r="GY269" s="1"/>
+      <c r="GZ269" s="1"/>
+      <c r="HA269" s="1"/>
+      <c r="HB269" s="1"/>
+      <c r="IQ269" s="1">
+        <v>888040389</v>
+      </c>
+      <c r="IR269" t="s">
+        <v>2217</v>
+      </c>
+      <c r="IS269" s="1">
+        <v>46302.551018518519</v>
+      </c>
+      <c r="IU269" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW269" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX269" t="s">
+        <v>2218</v>
+      </c>
+      <c r="IY269">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A270" s="1">
+        <v>46302.687822835651</v>
+      </c>
+      <c r="B270" s="1">
+        <v>46302.699744999998</v>
+      </c>
+      <c r="C270" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D270" t="s">
+        <v>952</v>
+      </c>
+      <c r="E270" t="s">
+        <v>280</v>
+      </c>
+      <c r="F270" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G270" t="s">
+        <v>198</v>
+      </c>
+      <c r="H270" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS270" t="s">
+        <v>2219</v>
+      </c>
+      <c r="BT270" t="s">
+        <v>2220</v>
+      </c>
+      <c r="BU270" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW270" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX270" t="s">
+        <v>2221</v>
+      </c>
+      <c r="BY270" t="s">
+        <v>561</v>
+      </c>
+      <c r="DE270" t="s">
+        <v>1069</v>
+      </c>
+      <c r="DF270" t="s">
+        <v>1070</v>
+      </c>
+      <c r="DG270">
+        <v>0</v>
+      </c>
+      <c r="DH270">
+        <v>1</v>
+      </c>
+      <c r="DI270">
+        <v>0</v>
+      </c>
+      <c r="DJ270">
+        <v>1</v>
+      </c>
+      <c r="DK270">
+        <v>0</v>
+      </c>
+      <c r="DU270" t="s">
+        <v>2222</v>
+      </c>
+      <c r="DV270" t="s">
+        <v>2223</v>
+      </c>
+      <c r="DW270" t="s">
+        <v>961</v>
+      </c>
+      <c r="EC270" t="s">
+        <v>2224</v>
+      </c>
+      <c r="ED270" t="s">
+        <v>2225</v>
+      </c>
+      <c r="EE270" t="s">
+        <v>2226</v>
+      </c>
+      <c r="EY270" s="1"/>
+      <c r="GQ270" s="1"/>
+      <c r="GR270" s="1"/>
+      <c r="GY270" s="1"/>
+      <c r="GZ270" s="1"/>
+      <c r="HA270" s="1"/>
+      <c r="HB270" s="1"/>
+      <c r="IQ270" s="1">
+        <v>888062015</v>
+      </c>
+      <c r="IR270" t="s">
+        <v>2227</v>
+      </c>
+      <c r="IS270" s="1">
+        <v>46302.566446759258</v>
+      </c>
+      <c r="IU270" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW270" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX270" t="s">
+        <v>2228</v>
+      </c>
+      <c r="IY270">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A271" s="1">
+        <v>46302.699748969913</v>
+      </c>
+      <c r="B271" s="1">
+        <v>46302.704906331019</v>
+      </c>
+      <c r="C271" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D271" t="s">
+        <v>952</v>
+      </c>
+      <c r="E271" t="s">
+        <v>280</v>
+      </c>
+      <c r="F271" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G271" t="s">
+        <v>198</v>
+      </c>
+      <c r="H271" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS271" t="s">
+        <v>2229</v>
+      </c>
+      <c r="BT271" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU271" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV271" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW271" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX271" t="s">
+        <v>1236</v>
+      </c>
+      <c r="BY271" t="s">
+        <v>561</v>
+      </c>
+      <c r="DE271" t="s">
+        <v>1140</v>
+      </c>
+      <c r="DF271" t="s">
+        <v>1090</v>
+      </c>
+      <c r="DG271">
+        <v>1</v>
+      </c>
+      <c r="DH271">
+        <v>0</v>
+      </c>
+      <c r="DI271">
+        <v>0</v>
+      </c>
+      <c r="DJ271">
+        <v>0</v>
+      </c>
+      <c r="DK271">
+        <v>0</v>
+      </c>
+      <c r="DM271" t="s">
+        <v>2230</v>
+      </c>
+      <c r="DN271" t="s">
+        <v>2231</v>
+      </c>
+      <c r="DO271" t="s">
+        <v>2232</v>
+      </c>
+      <c r="DP271">
+        <v>0</v>
+      </c>
+      <c r="DQ271">
+        <v>1</v>
+      </c>
+      <c r="DR271">
+        <v>0</v>
+      </c>
+      <c r="DS271" t="s">
+        <v>1144</v>
+      </c>
+      <c r="EY271" s="1"/>
+      <c r="GQ271" s="1"/>
+      <c r="GR271" s="1"/>
+      <c r="GY271" s="1"/>
+      <c r="GZ271" s="1"/>
+      <c r="HA271" s="1"/>
+      <c r="HB271" s="1"/>
+      <c r="IQ271" s="1">
+        <v>888069103</v>
+      </c>
+      <c r="IR271" t="s">
+        <v>2233</v>
+      </c>
+      <c r="IS271" s="1">
+        <v>46302.571608796286</v>
+      </c>
+      <c r="IU271" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW271" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX271" t="s">
+        <v>2234</v>
+      </c>
+      <c r="IY271">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A272" s="1">
+        <v>46301.806419375003</v>
+      </c>
+      <c r="B272" s="1">
+        <v>46302.739205590267</v>
+      </c>
+      <c r="C272" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D272" t="s">
+        <v>691</v>
+      </c>
+      <c r="E272" t="s">
+        <v>210</v>
+      </c>
+      <c r="F272" t="s">
+        <v>401</v>
+      </c>
+      <c r="G272" t="s">
+        <v>198</v>
+      </c>
+      <c r="H272" t="s">
+        <v>212</v>
+      </c>
+      <c r="J272" t="s">
+        <v>425</v>
+      </c>
+      <c r="K272" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L272" t="s">
+        <v>324</v>
+      </c>
+      <c r="M272" t="s">
+        <v>612</v>
+      </c>
+      <c r="N272" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O272" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R272">
+        <v>54</v>
+      </c>
+      <c r="S272">
+        <v>26</v>
+      </c>
+      <c r="T272" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U272" t="s">
+        <v>2235</v>
+      </c>
+      <c r="V272">
+        <v>0</v>
+      </c>
+      <c r="W272">
+        <v>0</v>
+      </c>
+      <c r="X272">
+        <v>1</v>
+      </c>
+      <c r="Y272">
+        <v>0</v>
+      </c>
+      <c r="Z272">
+        <v>0</v>
+      </c>
+      <c r="AA272">
+        <v>0</v>
+      </c>
+      <c r="AB272" t="s">
+        <v>2236</v>
+      </c>
+      <c r="AC272">
+        <v>0</v>
+      </c>
+      <c r="AD272">
+        <v>1</v>
+      </c>
+      <c r="AE272">
+        <v>0</v>
+      </c>
+      <c r="AF272">
+        <v>0</v>
+      </c>
+      <c r="AG272">
+        <v>0</v>
+      </c>
+      <c r="AH272">
+        <v>912</v>
+      </c>
+      <c r="AI272">
+        <v>141</v>
+      </c>
+      <c r="AJ272">
+        <v>267</v>
+      </c>
+      <c r="AK272">
+        <v>4</v>
+      </c>
+      <c r="AL272">
+        <v>3</v>
+      </c>
+      <c r="AM272">
+        <v>0</v>
+      </c>
+      <c r="AN272">
+        <v>0</v>
+      </c>
+      <c r="AO272" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP272">
+        <v>6</v>
+      </c>
+      <c r="AQ272" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR272" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS272" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT272" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU272" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV272" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW272" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS272" t="s">
+        <v>2237</v>
+      </c>
+      <c r="BT272" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU272" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW272" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX272" t="s">
+        <v>1202</v>
+      </c>
+      <c r="EY272" s="1"/>
+      <c r="GQ272" s="1"/>
+      <c r="GR272" s="1"/>
+      <c r="GY272" s="1"/>
+      <c r="GZ272" s="1"/>
+      <c r="HA272" s="1"/>
+      <c r="HB272" s="1"/>
+      <c r="IQ272" s="1">
+        <v>888204620</v>
+      </c>
+      <c r="IR272" t="s">
+        <v>2238</v>
+      </c>
+      <c r="IS272" s="1">
+        <v>46302.670277777783</v>
+      </c>
+      <c r="IU272" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW272" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX272" t="s">
+        <v>2239</v>
+      </c>
+      <c r="IY272">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A273" s="1">
+        <v>46302.739207951388</v>
+      </c>
+      <c r="B273" s="1">
+        <v>46302.752659375001</v>
+      </c>
+      <c r="C273" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D273" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E273" t="s">
+        <v>210</v>
+      </c>
+      <c r="F273" t="s">
+        <v>401</v>
+      </c>
+      <c r="G273" t="s">
+        <v>198</v>
+      </c>
+      <c r="H273" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS273" t="s">
+        <v>954</v>
+      </c>
+      <c r="BT273" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU273" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW273" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX273" t="s">
+        <v>1202</v>
+      </c>
+      <c r="BY273" t="s">
+        <v>359</v>
+      </c>
+      <c r="EK273" t="s">
+        <v>2240</v>
+      </c>
+      <c r="EL273" t="s">
+        <v>2241</v>
+      </c>
+      <c r="EM273" t="s">
+        <v>2242</v>
+      </c>
+      <c r="EN273" t="s">
+        <v>2243</v>
+      </c>
+      <c r="EY273" s="1"/>
+      <c r="GQ273" s="1"/>
+      <c r="GR273" s="1"/>
+      <c r="GY273" s="1"/>
+      <c r="GZ273" s="1"/>
+      <c r="HA273" s="1"/>
+      <c r="HB273" s="1"/>
+      <c r="IQ273" s="1">
+        <v>888204633</v>
+      </c>
+      <c r="IR273" t="s">
+        <v>2244</v>
+      </c>
+      <c r="IS273" s="1">
+        <v>46302.670289351852</v>
+      </c>
+      <c r="IU273" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW273" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX273" t="s">
+        <v>2245</v>
+      </c>
+      <c r="IY273">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A274" s="1">
+        <v>46302.75280141204</v>
+      </c>
+      <c r="B274" s="1">
+        <v>46302.795163182869</v>
+      </c>
+      <c r="C274" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D274" t="s">
+        <v>691</v>
+      </c>
+      <c r="E274" t="s">
+        <v>210</v>
+      </c>
+      <c r="F274" t="s">
+        <v>2246</v>
+      </c>
+      <c r="G274" t="s">
+        <v>198</v>
+      </c>
+      <c r="H274" t="s">
+        <v>212</v>
+      </c>
+      <c r="J274" t="s">
+        <v>2247</v>
+      </c>
+      <c r="K274" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L274" t="s">
+        <v>324</v>
+      </c>
+      <c r="M274" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N274" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O274" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R274">
+        <v>25</v>
+      </c>
+      <c r="S274">
+        <v>18</v>
+      </c>
+      <c r="T274" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U274" t="s">
+        <v>2235</v>
+      </c>
+      <c r="V274">
+        <v>0</v>
+      </c>
+      <c r="W274">
+        <v>0</v>
+      </c>
+      <c r="X274">
+        <v>1</v>
+      </c>
+      <c r="Y274">
+        <v>0</v>
+      </c>
+      <c r="Z274">
+        <v>0</v>
+      </c>
+      <c r="AA274">
+        <v>0</v>
+      </c>
+      <c r="AB274" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC274">
+        <v>1</v>
+      </c>
+      <c r="AD274">
+        <v>1</v>
+      </c>
+      <c r="AE274">
+        <v>0</v>
+      </c>
+      <c r="AF274">
+        <v>0</v>
+      </c>
+      <c r="AG274">
+        <v>0</v>
+      </c>
+      <c r="AH274">
+        <v>853</v>
+      </c>
+      <c r="AI274">
+        <v>31</v>
+      </c>
+      <c r="AJ274">
+        <v>46</v>
+      </c>
+      <c r="AK274">
+        <v>1</v>
+      </c>
+      <c r="AL274">
+        <v>3</v>
+      </c>
+      <c r="AM274">
+        <v>0</v>
+      </c>
+      <c r="AN274">
+        <v>0</v>
+      </c>
+      <c r="AO274" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AP274">
+        <v>7</v>
+      </c>
+      <c r="AQ274" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR274" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS274" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT274" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU274" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV274" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW274" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS274" t="s">
+        <v>2249</v>
+      </c>
+      <c r="BT274" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU274" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW274" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX274" t="s">
+        <v>1202</v>
+      </c>
+      <c r="EY274" s="1"/>
+      <c r="GQ274" s="1"/>
+      <c r="GR274" s="1"/>
+      <c r="GY274" s="1"/>
+      <c r="GZ274" s="1"/>
+      <c r="HA274" s="1"/>
+      <c r="HB274" s="1"/>
+      <c r="IQ274" s="1">
+        <v>888204640</v>
+      </c>
+      <c r="IR274" t="s">
+        <v>2250</v>
+      </c>
+      <c r="IS274" s="1">
+        <v>46302.670289351852</v>
+      </c>
+      <c r="IU274" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW274" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX274" t="s">
+        <v>2251</v>
+      </c>
+      <c r="IY274">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54EF4CB0-AFCE-914B-8063-4FF879F015EE}"/>
+  <xr:revisionPtr revIDLastSave="379" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01365FBA-AE17-C646-AB54-CF842F981CEB}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1500" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="1060" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Public Health Emergencies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId3"/>
+    <pivotCache cacheId="7" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6678" uniqueCount="2252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7311" uniqueCount="2385">
   <si>
     <t>start</t>
   </si>
@@ -6793,6 +6793,405 @@
   </si>
   <si>
     <t>uuid:d3324116-878e-4189-a21b-e650dffea3e1</t>
+  </si>
+  <si>
+    <t>Ebola is not curable because even if they say you are cured the side effects after are very bad i have.heard stories</t>
+  </si>
+  <si>
+    <t>Diverse backgrounds of the students  their levels of exposure is different  and they have different individual challenges</t>
+  </si>
+  <si>
+    <t>To remind everyone to verify all the information they get</t>
+  </si>
+  <si>
+    <t>The school had no clubs active so even if different activities came about there was a gap between the administration,pupils didn't have a proper channel to raise questions and the pupils</t>
+  </si>
+  <si>
+    <t>The Headteacher believes the created club is going to positively impact the children. He says most of them are from the slums and that in many ways affects their esteem but having a club where they are active and in charge is going to boost their confidence</t>
+  </si>
+  <si>
+    <t>The club is now to be in charge of Health issues  ,even on assembly it's the Fundoo members who will address health related issues every Friday And on every Tuesday, sports day for them instead of uniform they will wear the Club tshirts</t>
+  </si>
+  <si>
+    <t>We are grooming future leaders, these opportunities help identify those with potential</t>
+  </si>
+  <si>
+    <t>e35ee5d1-0c62-4cad-8be9-11ffed1a0b46</t>
+  </si>
+  <si>
+    <t>uuid:e35ee5d1-0c62-4cad-8be9-11ffed1a0b46</t>
+  </si>
+  <si>
+    <t>Bodaboda stage kinawataka roundabout</t>
+  </si>
+  <si>
+    <t>They committed to having a hand wash facility</t>
+  </si>
+  <si>
+    <t>Ebola outbreak was never real</t>
+  </si>
+  <si>
+    <t>5f2c3c34-60f3-4c5e-8c88-23a2d927ec1d</t>
+  </si>
+  <si>
+    <t>uuid:5f2c3c34-60f3-4c5e-8c88-23a2d927ec1d</t>
+  </si>
+  <si>
+    <t>Kiswa market</t>
+  </si>
+  <si>
+    <t>Ro</t>
+  </si>
+  <si>
+    <t>Why are we preparing them for outbreaks is government planning to fake another one</t>
+  </si>
+  <si>
+    <t>a94be7af-2e87-4187-94e6-7f7b275f9400</t>
+  </si>
+  <si>
+    <t>uuid:a94be7af-2e87-4187-94e6-7f7b275f9400</t>
+  </si>
+  <si>
+    <t>Anthony A</t>
+  </si>
+  <si>
+    <t>Whenever the government announces about the Ebola suspects, social media tends to confuse the studets that the schools are closed and there won't be any lessons and schools will be closed for a given period of time.</t>
+  </si>
+  <si>
+    <t>The social media platforms that are not regulated in any way. This leads to sharing of false information in the community</t>
+  </si>
+  <si>
+    <t>Encourage the learners to first confirm information got from social media to be sure that they are not spreading misinformation</t>
+  </si>
+  <si>
+    <t>St Stevens High School</t>
+  </si>
+  <si>
+    <t>053d79f7-9514-43b2-b615-afd24bb60a74</t>
+  </si>
+  <si>
+    <t>uuid:053d79f7-9514-43b2-b615-afd24bb60a74</t>
+  </si>
+  <si>
+    <t>Visit 3</t>
+  </si>
+  <si>
+    <t>6cd50c57-80bb-4590-9862-e4af848acb0f</t>
+  </si>
+  <si>
+    <t>uuid:6cd50c57-80bb-4590-9862-e4af848acb0f</t>
+  </si>
+  <si>
+    <t>Wednesday Friday</t>
+  </si>
+  <si>
+    <t>Ebola is in the villages because they eat wild animals</t>
+  </si>
+  <si>
+    <t>11737be8-68ad-4aae-8e1b-80e08eccc7eb</t>
+  </si>
+  <si>
+    <t>uuid:11737be8-68ad-4aae-8e1b-80e08eccc7eb</t>
+  </si>
+  <si>
+    <t>Mukono Municipal PDM Saaco Leaders</t>
+  </si>
+  <si>
+    <t>Reporting people with the thirst three warning signs of ebola.  Cascading the information and the gospel of proper hand washing with soap and water. Utilizing their Sacco groups to share information about the PHEs</t>
+  </si>
+  <si>
+    <t>didnt really share</t>
+  </si>
+  <si>
+    <t>wasn't able to identify</t>
+  </si>
+  <si>
+    <t>Having more of these sessions to senstize the leaders</t>
+  </si>
+  <si>
+    <t>0add8e92-9ad4-4c09-ab55-dad7224add99</t>
+  </si>
+  <si>
+    <t>uuid:0add8e92-9ad4-4c09-ab55-dad7224add99</t>
+  </si>
+  <si>
+    <t>Mistrust of information from leaders</t>
+  </si>
+  <si>
+    <t>Rubbish all over, no handwashing equipment</t>
+  </si>
+  <si>
+    <t>Knowledge wheel session</t>
+  </si>
+  <si>
+    <t>From the market leader, PHE preparedness where I participated in the wheel session, I did t know the importance of preparedness and also symptoms of Ebola, but now I know and I have ensure that the different market sections have hand washing facilities.</t>
+  </si>
+  <si>
+    <t>It is important because when an outbreak comes it will find us prepared.when the people in the market know they have to wash their hands</t>
+  </si>
+  <si>
+    <t>4cdc64aa-3447-4ef7-b6ed-ed61f6272510</t>
+  </si>
+  <si>
+    <t>uuid:4cdc64aa-3447-4ef7-b6ed-ed61f6272510</t>
+  </si>
+  <si>
+    <t>Landing Site / Informal Settlement</t>
+  </si>
+  <si>
+    <t>Chairman Luzira portbell</t>
+  </si>
+  <si>
+    <t>To have hand washing at the landing site, at the fish monger points</t>
+  </si>
+  <si>
+    <t>Ebola is not real, it is ment to keep us in fear</t>
+  </si>
+  <si>
+    <t>032bedae-f5fe-4e59-8296-f0a53544279e</t>
+  </si>
+  <si>
+    <t>uuid:032bedae-f5fe-4e59-8296-f0a53544279e</t>
+  </si>
+  <si>
+    <t>Tuesday Friday</t>
+  </si>
+  <si>
+    <t>Ebola is one way government makes money</t>
+  </si>
+  <si>
+    <t>ffbe529f-f0cb-4e5c-b62d-00ea6a7b59f8</t>
+  </si>
+  <si>
+    <t>uuid:ffbe529f-f0cb-4e5c-b62d-00ea6a7b59f8</t>
+  </si>
+  <si>
+    <t>Ebola is only in the villages</t>
+  </si>
+  <si>
+    <t>066174e3-9ede-4e09-bc40-ddb5a9ee5882</t>
+  </si>
+  <si>
+    <t>uuid:066174e3-9ede-4e09-bc40-ddb5a9ee5882</t>
+  </si>
+  <si>
+    <t>Progressive SS kitintale</t>
+  </si>
+  <si>
+    <t>Monday Friday</t>
+  </si>
+  <si>
+    <t>f3207910-121b-490b-a411-d5fb4f479724</t>
+  </si>
+  <si>
+    <t>uuid:f3207910-121b-490b-a411-d5fb4f479724</t>
+  </si>
+  <si>
+    <t>That handwashing facilities waste a lot of water and should not be used frequently. That soap placed at handwashing stations will be stolen, so there is no need to provide it. How can the health club keep monitoring handwashing in school?</t>
+  </si>
+  <si>
+    <t>Broken and faulty handwashing taps that were spoilt by the community, leaving no functional handwashing facilities for pupils.Lack of soap at handwashing points due to theft and no budget for replacement.Limited involvement of pupils in hygiene promotion before activation of the U-Report Health Club.</t>
+  </si>
+  <si>
+    <t>Replacing the faulty ordinary taps with durable press taps that cannot easily be broken by the community, and securing them with community agreement on protection and maintenance. The U-Report Health Club will monitor proper use and report any faults to teachers for quick action.</t>
+  </si>
+  <si>
+    <t>Health risks.During the transect walk, it was observed that the school had no functional handwashing facilities - the existing ones were broken. The HM explained that the outside community used to invade the school and spoil the tapsThe school had very few toilet stances compared to the large number of pupils, making the stance-to-pupil ratio highly disproportionate and far above the recommended standard of 1 stance to 25 girls and 1 stance to 50 boys..Handwashing with soap was a challenge because the school did not have soap available for washing. The Head Teacher expressed concern that the school budget would increase because children would keep stealing the bar soap provided, and the school could not use liquid soap because they were not using proper handwashing facilities but rather ordinary taps.There was also a fear of cost overruns due to increased water usage from frequent handwashing.</t>
+  </si>
+  <si>
+    <t>All the activities contributed to the shift, but most importantly the Snakes &amp; Ladders game was key. The game clearly illustrated the good hygiene behaviors that pupils must follow, represented by the ladders, and the bad behaviors that must be ignored and avoided, represented by the snakes, making it easy for the children to understand and adopt positive practicesThe transect walk with the Head Teacher made him realize that handwashing facilities are very important. Following the walk, he committed to working on the faulty taps that had been spoilt by the community..</t>
+  </si>
+  <si>
+    <t>The school is doing things differently now. Following the transect walk with the Head Teacher, he realized how important handwashing facilities are. He did not just commit but also worked on repairing the broken and faulty taps that were spoilt by the community to ensure handwashing facilities are functional again.The U-Report Health Club is now more active in the school. Members are leading by example in practicing the good hygiene behaviors learned from the Snakes &amp; Ladders game, following the ladders and ignoring the snakes, and are responsible for sensitizing fellow pupils, monitoring handwashing, and reporting hygiene-related issues to teachers for action.</t>
+  </si>
+  <si>
+    <t>From the storyteller's perspective, this change is the most meaningful because having functional handwashing facilities restored dignity and health for the pupils. When the taps were broken, children could not practice what they were taught, but now with the Head Teacher repairing them and the U-Report Health Club actively promoting good behaviors from the Snakes &amp; Ladders game, hygiene has become a daily practice, not just a lesson. It means fewer illnesses, more confidence for the children, and pride for the school in maintaining a clean and healthy environment.</t>
+  </si>
+  <si>
+    <t>5a141bdd-8fa0-43d0-af39-551a4f9c66f2</t>
+  </si>
+  <si>
+    <t>uuid:5a141bdd-8fa0-43d0-af39-551a4f9c66f2</t>
+  </si>
+  <si>
+    <t>Place of Worship (Church / Mosque)</t>
+  </si>
+  <si>
+    <t>Religious / Cultural Leader</t>
+  </si>
+  <si>
+    <t>Reverand</t>
+  </si>
+  <si>
+    <t>Committed to always encourage the people to follow the S4Ps</t>
+  </si>
+  <si>
+    <t>14925f0a-756a-44f6-b6c7-0d9b44a1b7f5</t>
+  </si>
+  <si>
+    <t>uuid:14925f0a-756a-44f6-b6c7-0d9b44a1b7f5</t>
+  </si>
+  <si>
+    <t>Market chairman</t>
+  </si>
+  <si>
+    <t>To ensure there is water and soap for washing hands</t>
+  </si>
+  <si>
+    <t>They are political matters</t>
+  </si>
+  <si>
+    <t>0605eafb-4226-4f3a-b6c2-03c1b44c21d0</t>
+  </si>
+  <si>
+    <t>uuid:0605eafb-4226-4f3a-b6c2-03c1b44c21d0</t>
+  </si>
+  <si>
+    <t>Fear of unrecognized Ebola case that died in Kenya through Uganda</t>
+  </si>
+  <si>
+    <t>Gaps in the screening processes at boarder points</t>
+  </si>
+  <si>
+    <t>Screening at boarder points and at the airport should be tightened</t>
+  </si>
+  <si>
+    <t>Before the intervation, the school had hygiene and sanitation challenges were it had places like near the kitchen where there was stagnant water in a drainage channel. There was also absence of a health club. This is at Mamtaz Secondary school.</t>
+  </si>
+  <si>
+    <t>With introduction of the PHE project, gaps were brought to attention of the patron which they were agreed upon to be improved through the health club patron. The learners also are able to pass on accurate information to the rest this is observed through the use of the spin and learn wheel.</t>
+  </si>
+  <si>
+    <t>The school formed a Health Club that meets on a weekly basis, through the club the drainage of the water channels at the school was improved even hygiene at the kitchen.</t>
+  </si>
+  <si>
+    <t>Before it was business as usual and we didn't see the health risks associated with poor hygiene but again also the magnitude of the health club through which change is observed for better health</t>
+  </si>
+  <si>
+    <t>716c72bf-c6ab-4f26-8ff9-431201551c8c</t>
+  </si>
+  <si>
+    <t>uuid:716c72bf-c6ab-4f26-8ff9-431201551c8c</t>
+  </si>
+  <si>
+    <t>Ebola is not curable because there is no medicine for it,old people do not get Ebola</t>
+  </si>
+  <si>
+    <t>Financial constraints most of these children are coming from families that are financially struggling and it has a toll on them</t>
+  </si>
+  <si>
+    <t>More sensitization on need to verify the rumors</t>
+  </si>
+  <si>
+    <t>36e63ee4-2167-4e35-82a6-34a3929f0ac6</t>
+  </si>
+  <si>
+    <t>uuid:36e63ee4-2167-4e35-82a6-34a3929f0ac6</t>
+  </si>
+  <si>
+    <t>Kabalagala parish</t>
+  </si>
+  <si>
+    <t>St Janan Luwum secondary  school</t>
+  </si>
+  <si>
+    <t>One functional washing place at the Gate only</t>
+  </si>
+  <si>
+    <t>Provide more hand washing  facilities</t>
+  </si>
+  <si>
+    <t>9725ab16-63dc-4e2d-b9c7-f0d4c7882048</t>
+  </si>
+  <si>
+    <t>uuid:9725ab16-63dc-4e2d-b9c7-f0d4c7882048</t>
+  </si>
+  <si>
+    <t>Tropical  secondary  school</t>
+  </si>
+  <si>
+    <t>Lack handwashing set up on site</t>
+  </si>
+  <si>
+    <t>Provision  of handwashing  facilities  around the key points</t>
+  </si>
+  <si>
+    <t>5a8e0020-bbe9-4eaf-8dcb-30def18dec32</t>
+  </si>
+  <si>
+    <t>uuid:5a8e0020-bbe9-4eaf-8dcb-30def18dec32</t>
+  </si>
+  <si>
+    <t>Katwe COU Primary  school</t>
+  </si>
+  <si>
+    <t>Health teacher</t>
+  </si>
+  <si>
+    <t>Does ebola heal?,we don't  eat monkeys,why is it we get sick of ebola</t>
+  </si>
+  <si>
+    <t>d6fd5add-02d6-41bb-aa91-d441bae57254</t>
+  </si>
+  <si>
+    <t>uuid:d6fd5add-02d6-41bb-aa91-d441bae57254</t>
+  </si>
+  <si>
+    <t>Nabakyala,Defence,LC1 chairperson</t>
+  </si>
+  <si>
+    <t>Made a commitment  to continue  encourage  people by leveragingthe council meetings,and other meeting  ti talk about  Ebol</t>
+  </si>
+  <si>
+    <t>1-what are the signs and symptoms of mpox and Ebola diseases?  Why is it that Mpox and Ebola have abit similar symptoms and signs? 3-is mpox virus disease? 4-how can we protect our self from mpox and Ebola diseases  ? 5-can condom prevent you from getting mpox?</t>
+  </si>
+  <si>
+    <t>Neighbors</t>
+  </si>
+  <si>
+    <t>8c9cfcee-fec6-4efb-ab99-0b3e38b7f1ea</t>
+  </si>
+  <si>
+    <t>uuid:8c9cfcee-fec6-4efb-ab99-0b3e38b7f1ea</t>
+  </si>
+  <si>
+    <t>The  mechanics  and the bodaboda  riders, didn't  understand    the reference  point incase of an emergency</t>
+  </si>
+  <si>
+    <t>The  Nabakyala  of the place assuring them that they can  come to her incase of emergency  and incase they didn't  know what to do</t>
+  </si>
+  <si>
+    <t>The mechanics  and border riders tend to delay to seek care, or self Medicare until the  sickness has put them  down.</t>
+  </si>
+  <si>
+    <t>During the spin and wheel, we got to know that one of them had  a  girl friend  with the mpox signs and yet they didn't  know what to do. But after the assurance from  the VHT and and the Nabakyala  of the area, the person requested  if they could  to tge Nabakyala  after the session on how to protect himself  but how to seek help for girl friend</t>
+  </si>
+  <si>
+    <t>d26ffc83-f00a-4be8-ac59-95660662fe83</t>
+  </si>
+  <si>
+    <t>uuid:d26ffc83-f00a-4be8-ac59-95660662fe83</t>
+  </si>
+  <si>
+    <t>Tool 11: U-Report Recruitment</t>
+  </si>
+  <si>
+    <t>Community Congregate Setting (Market / Boda Stage / Taxi Park)</t>
+  </si>
+  <si>
+    <t>1d36ac9c-ab4f-45d2-9b34-90af9a37576b</t>
+  </si>
+  <si>
+    <t>uuid:1d36ac9c-ab4f-45d2-9b34-90af9a37576b</t>
+  </si>
+  <si>
+    <t>School (Upper Class Learners / Patrons)</t>
+  </si>
+  <si>
+    <t>4fdf8012-234e-4bf0-a026-baadbf933a37</t>
+  </si>
+  <si>
+    <t>uuid:4fdf8012-234e-4bf0-a026-baadbf933a37</t>
   </si>
 </sst>
 </file>
@@ -20847,7 +21246,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -21197,8 +21596,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY274" totalsRowShown="0">
-  <autoFilter ref="A1:IY274" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY298" totalsRowShown="0">
+  <autoFilter ref="A1:IY298" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -21751,7 +22150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY274"/>
+  <dimension ref="A1:IY298"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -53655,6 +54054,3129 @@
         <v>273</v>
       </c>
     </row>
+    <row r="275" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A275" s="1">
+        <v>46302.860038148137</v>
+      </c>
+      <c r="B275" s="1">
+        <v>46302.872560648153</v>
+      </c>
+      <c r="C275" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D275" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E275" t="s">
+        <v>280</v>
+      </c>
+      <c r="F275" t="s">
+        <v>281</v>
+      </c>
+      <c r="G275" t="s">
+        <v>198</v>
+      </c>
+      <c r="H275" t="s">
+        <v>282</v>
+      </c>
+      <c r="BS275" t="s">
+        <v>2252</v>
+      </c>
+      <c r="BT275" t="s">
+        <v>2253</v>
+      </c>
+      <c r="BU275" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW275" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX275" t="s">
+        <v>2254</v>
+      </c>
+      <c r="BY275" t="s">
+        <v>359</v>
+      </c>
+      <c r="EK275" t="s">
+        <v>2255</v>
+      </c>
+      <c r="EL275" t="s">
+        <v>2256</v>
+      </c>
+      <c r="EM275" t="s">
+        <v>2257</v>
+      </c>
+      <c r="EN275" t="s">
+        <v>2258</v>
+      </c>
+      <c r="EY275" s="1"/>
+      <c r="GQ275" s="1"/>
+      <c r="GR275" s="1"/>
+      <c r="GY275" s="1"/>
+      <c r="GZ275" s="1"/>
+      <c r="HA275" s="1"/>
+      <c r="HB275" s="1"/>
+      <c r="IQ275" s="1">
+        <v>888289681</v>
+      </c>
+      <c r="IR275" t="s">
+        <v>2259</v>
+      </c>
+      <c r="IS275" s="1">
+        <v>46302.739270833343</v>
+      </c>
+      <c r="IU275" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW275" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX275" t="s">
+        <v>2260</v>
+      </c>
+      <c r="IY275">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A276" s="1">
+        <v>46302.430333680553</v>
+      </c>
+      <c r="B276" s="1">
+        <v>46302.438017326393</v>
+      </c>
+      <c r="C276" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D276" t="s">
+        <v>690</v>
+      </c>
+      <c r="E276" t="s">
+        <v>196</v>
+      </c>
+      <c r="F276" t="s">
+        <v>777</v>
+      </c>
+      <c r="G276" t="s">
+        <v>198</v>
+      </c>
+      <c r="H276" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX276" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY276" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ276" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA276" t="s">
+        <v>2261</v>
+      </c>
+      <c r="BB276">
+        <v>20</v>
+      </c>
+      <c r="BC276">
+        <v>5</v>
+      </c>
+      <c r="BD276" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE276" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF276" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG276" t="s">
+        <v>2262</v>
+      </c>
+      <c r="BH276" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI276" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ276" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK276">
+        <v>8</v>
+      </c>
+      <c r="BL276" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM276">
+        <v>20</v>
+      </c>
+      <c r="BN276">
+        <v>30</v>
+      </c>
+      <c r="BO276" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP276" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ276" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS276" t="s">
+        <v>2263</v>
+      </c>
+      <c r="BT276" t="s">
+        <v>1845</v>
+      </c>
+      <c r="BU276" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW276" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX276" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY276" s="1"/>
+      <c r="GQ276" s="1"/>
+      <c r="GR276" s="1"/>
+      <c r="GY276" s="1"/>
+      <c r="GZ276" s="1"/>
+      <c r="HA276" s="1"/>
+      <c r="HB276" s="1"/>
+      <c r="IQ276" s="1">
+        <v>888604914</v>
+      </c>
+      <c r="IR276" t="s">
+        <v>2264</v>
+      </c>
+      <c r="IS276" s="1">
+        <v>46303.295856481483</v>
+      </c>
+      <c r="IU276" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW276" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX276" t="s">
+        <v>2265</v>
+      </c>
+      <c r="IY276">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A277" s="1">
+        <v>46302.441966284721</v>
+      </c>
+      <c r="B277" s="1">
+        <v>46303.43359886574</v>
+      </c>
+      <c r="C277" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D277" t="s">
+        <v>690</v>
+      </c>
+      <c r="E277" t="s">
+        <v>196</v>
+      </c>
+      <c r="F277" t="s">
+        <v>196</v>
+      </c>
+      <c r="G277" t="s">
+        <v>198</v>
+      </c>
+      <c r="H277" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX277" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY277" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ277" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA277" t="s">
+        <v>2266</v>
+      </c>
+      <c r="BB277">
+        <v>5</v>
+      </c>
+      <c r="BC277">
+        <v>10</v>
+      </c>
+      <c r="BD277" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE277" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF277" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG277" t="s">
+        <v>2267</v>
+      </c>
+      <c r="BH277" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI277" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ277" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK277">
+        <v>5</v>
+      </c>
+      <c r="BL277" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM277">
+        <v>48</v>
+      </c>
+      <c r="BN277">
+        <v>66</v>
+      </c>
+      <c r="BO277" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP277" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ277" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS277" t="s">
+        <v>2268</v>
+      </c>
+      <c r="BT277" t="s">
+        <v>1637</v>
+      </c>
+      <c r="BU277" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV277" t="s">
+        <v>936</v>
+      </c>
+      <c r="BW277" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX277" t="s">
+        <v>1135</v>
+      </c>
+      <c r="EY277" s="1"/>
+      <c r="GQ277" s="1"/>
+      <c r="GR277" s="1"/>
+      <c r="GY277" s="1"/>
+      <c r="GZ277" s="1"/>
+      <c r="HA277" s="1"/>
+      <c r="HB277" s="1"/>
+      <c r="IQ277" s="1">
+        <v>888620434</v>
+      </c>
+      <c r="IR277" t="s">
+        <v>2269</v>
+      </c>
+      <c r="IS277" s="1">
+        <v>46303.308622685188</v>
+      </c>
+      <c r="IU277" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW277" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX277" t="s">
+        <v>2270</v>
+      </c>
+      <c r="IY277">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A278" s="1">
+        <v>46300.70079787037</v>
+      </c>
+      <c r="B278" s="1">
+        <v>46303.434641145832</v>
+      </c>
+      <c r="C278" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D278" t="s">
+        <v>776</v>
+      </c>
+      <c r="E278" t="s">
+        <v>309</v>
+      </c>
+      <c r="F278" t="s">
+        <v>2271</v>
+      </c>
+      <c r="G278" t="s">
+        <v>198</v>
+      </c>
+      <c r="H278" t="s">
+        <v>311</v>
+      </c>
+      <c r="BS278" t="s">
+        <v>2272</v>
+      </c>
+      <c r="BT278" t="s">
+        <v>2273</v>
+      </c>
+      <c r="BU278" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW278" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX278" t="s">
+        <v>2274</v>
+      </c>
+      <c r="EY278" s="1"/>
+      <c r="GJ278" s="1">
+        <v>46302</v>
+      </c>
+      <c r="GK278" t="s">
+        <v>2275</v>
+      </c>
+      <c r="GL278" t="s">
+        <v>376</v>
+      </c>
+      <c r="GN278">
+        <v>333</v>
+      </c>
+      <c r="GO278">
+        <v>347</v>
+      </c>
+      <c r="GP278">
+        <v>20</v>
+      </c>
+      <c r="GQ278" s="1">
+        <v>22</v>
+      </c>
+      <c r="GR278" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="GT278" t="s">
+        <v>476</v>
+      </c>
+      <c r="GU278" t="s">
+        <v>449</v>
+      </c>
+      <c r="GV278" t="s">
+        <v>615</v>
+      </c>
+      <c r="GX278" t="s">
+        <v>380</v>
+      </c>
+      <c r="GY278" s="1">
+        <v>6</v>
+      </c>
+      <c r="GZ278" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="HA278" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="HB278" s="1">
+        <v>16</v>
+      </c>
+      <c r="HC278">
+        <v>16</v>
+      </c>
+      <c r="HD278" t="s">
+        <v>383</v>
+      </c>
+      <c r="HE278" t="s">
+        <v>384</v>
+      </c>
+      <c r="HF278" t="s">
+        <v>431</v>
+      </c>
+      <c r="HG278">
+        <v>1</v>
+      </c>
+      <c r="HH278">
+        <v>0</v>
+      </c>
+      <c r="HI278">
+        <v>0</v>
+      </c>
+      <c r="HJ278">
+        <v>0</v>
+      </c>
+      <c r="HK278" t="s">
+        <v>395</v>
+      </c>
+      <c r="HM278">
+        <v>10</v>
+      </c>
+      <c r="HN278">
+        <v>6</v>
+      </c>
+      <c r="HO278">
+        <v>4</v>
+      </c>
+      <c r="HP278">
+        <v>6</v>
+      </c>
+      <c r="HQ278">
+        <v>3</v>
+      </c>
+      <c r="HR278">
+        <v>0</v>
+      </c>
+      <c r="IQ278" s="1">
+        <v>888621758</v>
+      </c>
+      <c r="IR278" t="s">
+        <v>2276</v>
+      </c>
+      <c r="IS278" s="1">
+        <v>46303.309675925928</v>
+      </c>
+      <c r="IU278" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW278" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX278" t="s">
+        <v>2277</v>
+      </c>
+      <c r="IY278">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A279" s="1">
+        <v>46303.433600277778</v>
+      </c>
+      <c r="B279" s="1">
+        <v>46303.441392152781</v>
+      </c>
+      <c r="C279" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D279" t="s">
+        <v>691</v>
+      </c>
+      <c r="E279" t="s">
+        <v>196</v>
+      </c>
+      <c r="F279" t="s">
+        <v>777</v>
+      </c>
+      <c r="G279" t="s">
+        <v>198</v>
+      </c>
+      <c r="H279" t="s">
+        <v>199</v>
+      </c>
+      <c r="J279" t="s">
+        <v>781</v>
+      </c>
+      <c r="K279" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L279" t="s">
+        <v>395</v>
+      </c>
+      <c r="M279" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N279" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O279" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R279">
+        <v>15</v>
+      </c>
+      <c r="S279">
+        <v>13</v>
+      </c>
+      <c r="T279" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U279" t="s">
+        <v>2115</v>
+      </c>
+      <c r="V279">
+        <v>0</v>
+      </c>
+      <c r="W279">
+        <v>1</v>
+      </c>
+      <c r="X279">
+        <v>0</v>
+      </c>
+      <c r="Y279">
+        <v>1</v>
+      </c>
+      <c r="Z279">
+        <v>0</v>
+      </c>
+      <c r="AA279">
+        <v>0</v>
+      </c>
+      <c r="AB279" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC279">
+        <v>1</v>
+      </c>
+      <c r="AD279">
+        <v>1</v>
+      </c>
+      <c r="AE279">
+        <v>0</v>
+      </c>
+      <c r="AF279">
+        <v>0</v>
+      </c>
+      <c r="AG279">
+        <v>0</v>
+      </c>
+      <c r="AH279">
+        <v>870</v>
+      </c>
+      <c r="AI279">
+        <v>420</v>
+      </c>
+      <c r="AJ279">
+        <v>450</v>
+      </c>
+      <c r="AK279">
+        <v>8</v>
+      </c>
+      <c r="AL279">
+        <v>2</v>
+      </c>
+      <c r="AM279">
+        <v>0</v>
+      </c>
+      <c r="AN279">
+        <v>0</v>
+      </c>
+      <c r="AO279" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP279">
+        <v>5</v>
+      </c>
+      <c r="AQ279" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR279" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS279" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT279" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU279" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV279" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW279" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS279" t="s">
+        <v>1122</v>
+      </c>
+      <c r="BT279" t="s">
+        <v>1712</v>
+      </c>
+      <c r="BU279" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW279" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX279" t="s">
+        <v>1135</v>
+      </c>
+      <c r="EY279" s="1"/>
+      <c r="GQ279" s="1"/>
+      <c r="GR279" s="1"/>
+      <c r="GY279" s="1"/>
+      <c r="GZ279" s="1"/>
+      <c r="HA279" s="1"/>
+      <c r="HB279" s="1"/>
+      <c r="IQ279" s="1">
+        <v>888630389</v>
+      </c>
+      <c r="IR279" t="s">
+        <v>2279</v>
+      </c>
+      <c r="IS279" s="1">
+        <v>46303.316412037027</v>
+      </c>
+      <c r="IU279" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW279" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX279" t="s">
+        <v>2280</v>
+      </c>
+      <c r="IY279">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A280" s="1">
+        <v>46303.446988136573</v>
+      </c>
+      <c r="B280" s="1">
+        <v>46303.453122824067</v>
+      </c>
+      <c r="C280" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D280" t="s">
+        <v>691</v>
+      </c>
+      <c r="E280" t="s">
+        <v>196</v>
+      </c>
+      <c r="F280" t="s">
+        <v>196</v>
+      </c>
+      <c r="G280" t="s">
+        <v>198</v>
+      </c>
+      <c r="H280" t="s">
+        <v>199</v>
+      </c>
+      <c r="J280" t="s">
+        <v>200</v>
+      </c>
+      <c r="K280" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L280" t="s">
+        <v>395</v>
+      </c>
+      <c r="M280" t="s">
+        <v>612</v>
+      </c>
+      <c r="N280" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O280" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R280">
+        <v>21</v>
+      </c>
+      <c r="S280">
+        <v>16</v>
+      </c>
+      <c r="T280" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U280" t="s">
+        <v>2281</v>
+      </c>
+      <c r="V280">
+        <v>0</v>
+      </c>
+      <c r="W280">
+        <v>0</v>
+      </c>
+      <c r="X280">
+        <v>1</v>
+      </c>
+      <c r="Y280">
+        <v>0</v>
+      </c>
+      <c r="Z280">
+        <v>1</v>
+      </c>
+      <c r="AA280">
+        <v>0</v>
+      </c>
+      <c r="AB280" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC280">
+        <v>1</v>
+      </c>
+      <c r="AD280">
+        <v>1</v>
+      </c>
+      <c r="AE280">
+        <v>0</v>
+      </c>
+      <c r="AF280">
+        <v>0</v>
+      </c>
+      <c r="AG280">
+        <v>0</v>
+      </c>
+      <c r="AH280">
+        <v>1680</v>
+      </c>
+      <c r="AI280">
+        <v>804</v>
+      </c>
+      <c r="AJ280">
+        <v>876</v>
+      </c>
+      <c r="AK280">
+        <v>2</v>
+      </c>
+      <c r="AL280">
+        <v>2</v>
+      </c>
+      <c r="AM280">
+        <v>0</v>
+      </c>
+      <c r="AN280">
+        <v>0</v>
+      </c>
+      <c r="AO280" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP280">
+        <v>5</v>
+      </c>
+      <c r="AQ280" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR280" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS280" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT280" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU280" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV280" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW280" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS280" t="s">
+        <v>2282</v>
+      </c>
+      <c r="BT280" t="s">
+        <v>1712</v>
+      </c>
+      <c r="BU280" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW280" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX280" t="s">
+        <v>1135</v>
+      </c>
+      <c r="EY280" s="1"/>
+      <c r="GQ280" s="1"/>
+      <c r="GR280" s="1"/>
+      <c r="GY280" s="1"/>
+      <c r="GZ280" s="1"/>
+      <c r="HA280" s="1"/>
+      <c r="HB280" s="1"/>
+      <c r="IQ280" s="1">
+        <v>888644189</v>
+      </c>
+      <c r="IR280" t="s">
+        <v>2283</v>
+      </c>
+      <c r="IS280" s="1">
+        <v>46303.328148148154</v>
+      </c>
+      <c r="IU280" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW280" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX280" t="s">
+        <v>2284</v>
+      </c>
+      <c r="IY280">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A281" s="1">
+        <v>46303.434641805557</v>
+      </c>
+      <c r="B281" s="1">
+        <v>46303.453408831017</v>
+      </c>
+      <c r="C281" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D281" t="s">
+        <v>690</v>
+      </c>
+      <c r="E281" t="s">
+        <v>309</v>
+      </c>
+      <c r="F281" t="s">
+        <v>2271</v>
+      </c>
+      <c r="G281" t="s">
+        <v>198</v>
+      </c>
+      <c r="H281" t="s">
+        <v>311</v>
+      </c>
+      <c r="AX281" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY281" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ281" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA281" t="s">
+        <v>2285</v>
+      </c>
+      <c r="BB281">
+        <v>100</v>
+      </c>
+      <c r="BC281">
+        <v>50</v>
+      </c>
+      <c r="BD281" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE281" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF281" t="s">
+        <v>395</v>
+      </c>
+      <c r="BG281" t="s">
+        <v>2286</v>
+      </c>
+      <c r="BH281" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI281" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ281" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK281">
+        <v>3</v>
+      </c>
+      <c r="BL281" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM281">
+        <v>0</v>
+      </c>
+      <c r="BN281">
+        <v>0</v>
+      </c>
+      <c r="BO281" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP281" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ281" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BS281" t="s">
+        <v>2287</v>
+      </c>
+      <c r="BT281" t="s">
+        <v>2288</v>
+      </c>
+      <c r="BU281" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW281" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX281" t="s">
+        <v>2289</v>
+      </c>
+      <c r="EY281" s="1"/>
+      <c r="GQ281" s="1"/>
+      <c r="GR281" s="1"/>
+      <c r="GY281" s="1"/>
+      <c r="GZ281" s="1"/>
+      <c r="HA281" s="1"/>
+      <c r="HB281" s="1"/>
+      <c r="IQ281" s="1">
+        <v>888644563</v>
+      </c>
+      <c r="IR281" t="s">
+        <v>2290</v>
+      </c>
+      <c r="IS281" s="1">
+        <v>46303.328425925924</v>
+      </c>
+      <c r="IU281" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW281" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX281" t="s">
+        <v>2291</v>
+      </c>
+      <c r="IY281">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A282" s="1">
+        <v>46303.507944050929</v>
+      </c>
+      <c r="B282" s="1">
+        <v>46303.518720451393</v>
+      </c>
+      <c r="C282" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D282" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E282" t="s">
+        <v>196</v>
+      </c>
+      <c r="F282" t="s">
+        <v>289</v>
+      </c>
+      <c r="G282" t="s">
+        <v>198</v>
+      </c>
+      <c r="H282" t="s">
+        <v>199</v>
+      </c>
+      <c r="BS282" t="s">
+        <v>549</v>
+      </c>
+      <c r="BT282" t="s">
+        <v>2292</v>
+      </c>
+      <c r="BU282" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW282" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX282" t="s">
+        <v>1135</v>
+      </c>
+      <c r="BY282" t="s">
+        <v>456</v>
+      </c>
+      <c r="EK282" t="s">
+        <v>2293</v>
+      </c>
+      <c r="EL282" t="s">
+        <v>2294</v>
+      </c>
+      <c r="EM282" t="s">
+        <v>2295</v>
+      </c>
+      <c r="EN282" t="s">
+        <v>2296</v>
+      </c>
+      <c r="EY282" s="1"/>
+      <c r="GQ282" s="1"/>
+      <c r="GR282" s="1"/>
+      <c r="GY282" s="1"/>
+      <c r="GZ282" s="1"/>
+      <c r="HA282" s="1"/>
+      <c r="HB282" s="1"/>
+      <c r="IQ282" s="1">
+        <v>888733067</v>
+      </c>
+      <c r="IR282" t="s">
+        <v>2297</v>
+      </c>
+      <c r="IS282" s="1">
+        <v>46303.393750000003</v>
+      </c>
+      <c r="IU282" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW282" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX282" t="s">
+        <v>2298</v>
+      </c>
+      <c r="IY282">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A283" s="1">
+        <v>46303.518722094908</v>
+      </c>
+      <c r="B283" s="1">
+        <v>46303.525950717587</v>
+      </c>
+      <c r="C283" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D283" t="s">
+        <v>690</v>
+      </c>
+      <c r="E283" t="s">
+        <v>196</v>
+      </c>
+      <c r="F283" t="s">
+        <v>289</v>
+      </c>
+      <c r="G283" t="s">
+        <v>198</v>
+      </c>
+      <c r="H283" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX283" t="s">
+        <v>2299</v>
+      </c>
+      <c r="AY283" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ283" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA283" t="s">
+        <v>2300</v>
+      </c>
+      <c r="BB283">
+        <v>25</v>
+      </c>
+      <c r="BC283">
+        <v>30</v>
+      </c>
+      <c r="BD283" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE283" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF283" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG283" t="s">
+        <v>2301</v>
+      </c>
+      <c r="BH283" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI283" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ283" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK283">
+        <v>5</v>
+      </c>
+      <c r="BL283" t="s">
+        <v>2012</v>
+      </c>
+      <c r="BM283">
+        <v>624</v>
+      </c>
+      <c r="BN283">
+        <v>570</v>
+      </c>
+      <c r="BO283" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP283" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ283" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BS283" t="s">
+        <v>2302</v>
+      </c>
+      <c r="BT283" t="s">
+        <v>1712</v>
+      </c>
+      <c r="BU283" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW283" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX283" t="s">
+        <v>1135</v>
+      </c>
+      <c r="EY283" s="1"/>
+      <c r="GQ283" s="1"/>
+      <c r="GR283" s="1"/>
+      <c r="GY283" s="1"/>
+      <c r="GZ283" s="1"/>
+      <c r="HA283" s="1"/>
+      <c r="HB283" s="1"/>
+      <c r="IQ283" s="1">
+        <v>888741738</v>
+      </c>
+      <c r="IR283" t="s">
+        <v>2303</v>
+      </c>
+      <c r="IS283" s="1">
+        <v>46303.400972222233</v>
+      </c>
+      <c r="IU283" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW283" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX283" t="s">
+        <v>2304</v>
+      </c>
+      <c r="IY283">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A284" s="1">
+        <v>46303.533923391202</v>
+      </c>
+      <c r="B284" s="1">
+        <v>46303.541657071757</v>
+      </c>
+      <c r="C284" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D284" t="s">
+        <v>691</v>
+      </c>
+      <c r="E284" t="s">
+        <v>196</v>
+      </c>
+      <c r="F284" t="s">
+        <v>228</v>
+      </c>
+      <c r="G284" t="s">
+        <v>198</v>
+      </c>
+      <c r="H284" t="s">
+        <v>199</v>
+      </c>
+      <c r="J284" t="s">
+        <v>1352</v>
+      </c>
+      <c r="K284" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L284" t="s">
+        <v>395</v>
+      </c>
+      <c r="M284" t="s">
+        <v>612</v>
+      </c>
+      <c r="N284" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O284" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R284">
+        <v>14</v>
+      </c>
+      <c r="S284">
+        <v>11</v>
+      </c>
+      <c r="T284" t="s">
+        <v>1815</v>
+      </c>
+      <c r="U284" t="s">
+        <v>2305</v>
+      </c>
+      <c r="V284">
+        <v>0</v>
+      </c>
+      <c r="W284">
+        <v>1</v>
+      </c>
+      <c r="X284">
+        <v>0</v>
+      </c>
+      <c r="Y284">
+        <v>0</v>
+      </c>
+      <c r="Z284">
+        <v>1</v>
+      </c>
+      <c r="AA284">
+        <v>0</v>
+      </c>
+      <c r="AB284" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC284">
+        <v>1</v>
+      </c>
+      <c r="AD284">
+        <v>1</v>
+      </c>
+      <c r="AE284">
+        <v>0</v>
+      </c>
+      <c r="AF284">
+        <v>0</v>
+      </c>
+      <c r="AG284">
+        <v>0</v>
+      </c>
+      <c r="AH284">
+        <v>800</v>
+      </c>
+      <c r="AI284">
+        <v>378</v>
+      </c>
+      <c r="AJ284">
+        <v>422</v>
+      </c>
+      <c r="AK284">
+        <v>2</v>
+      </c>
+      <c r="AL284">
+        <v>2</v>
+      </c>
+      <c r="AM284">
+        <v>0</v>
+      </c>
+      <c r="AN284">
+        <v>0</v>
+      </c>
+      <c r="AO284" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP284">
+        <v>5</v>
+      </c>
+      <c r="AQ284" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR284" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS284" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT284" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU284" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV284" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW284" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS284" t="s">
+        <v>2306</v>
+      </c>
+      <c r="BT284" t="s">
+        <v>1637</v>
+      </c>
+      <c r="BU284" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW284" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX284" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY284" s="1"/>
+      <c r="GQ284" s="1"/>
+      <c r="GR284" s="1"/>
+      <c r="GY284" s="1"/>
+      <c r="GZ284" s="1"/>
+      <c r="HA284" s="1"/>
+      <c r="HB284" s="1"/>
+      <c r="IQ284" s="1">
+        <v>888760909</v>
+      </c>
+      <c r="IR284" t="s">
+        <v>2307</v>
+      </c>
+      <c r="IS284" s="1">
+        <v>46303.416678240741</v>
+      </c>
+      <c r="IU284" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW284" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX284" t="s">
+        <v>2308</v>
+      </c>
+      <c r="IY284">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A285" s="1">
+        <v>46303.602467268523</v>
+      </c>
+      <c r="B285" s="1">
+        <v>46303.609750347219</v>
+      </c>
+      <c r="C285" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D285" t="s">
+        <v>691</v>
+      </c>
+      <c r="E285" t="s">
+        <v>196</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+      <c r="G285" t="s">
+        <v>198</v>
+      </c>
+      <c r="H285" t="s">
+        <v>199</v>
+      </c>
+      <c r="J285" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K285" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L285" t="s">
+        <v>395</v>
+      </c>
+      <c r="M285" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N285" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O285" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R285">
+        <v>22</v>
+      </c>
+      <c r="S285">
+        <v>17</v>
+      </c>
+      <c r="T285" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U285" t="s">
+        <v>2115</v>
+      </c>
+      <c r="V285">
+        <v>0</v>
+      </c>
+      <c r="W285">
+        <v>1</v>
+      </c>
+      <c r="X285">
+        <v>0</v>
+      </c>
+      <c r="Y285">
+        <v>1</v>
+      </c>
+      <c r="Z285">
+        <v>0</v>
+      </c>
+      <c r="AA285">
+        <v>0</v>
+      </c>
+      <c r="AB285" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC285">
+        <v>1</v>
+      </c>
+      <c r="AD285">
+        <v>1</v>
+      </c>
+      <c r="AE285">
+        <v>0</v>
+      </c>
+      <c r="AF285">
+        <v>0</v>
+      </c>
+      <c r="AG285">
+        <v>0</v>
+      </c>
+      <c r="AH285">
+        <v>3335</v>
+      </c>
+      <c r="AI285">
+        <v>1206</v>
+      </c>
+      <c r="AJ285">
+        <v>903</v>
+      </c>
+      <c r="AK285">
+        <v>8</v>
+      </c>
+      <c r="AL285">
+        <v>2</v>
+      </c>
+      <c r="AM285">
+        <v>0</v>
+      </c>
+      <c r="AN285">
+        <v>0</v>
+      </c>
+      <c r="AO285" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP285">
+        <v>6</v>
+      </c>
+      <c r="AQ285" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR285" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS285" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT285" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU285" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV285" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW285" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS285" t="s">
+        <v>2309</v>
+      </c>
+      <c r="BT285" t="s">
+        <v>1637</v>
+      </c>
+      <c r="BU285" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW285" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX285" t="s">
+        <v>1135</v>
+      </c>
+      <c r="EY285" s="1"/>
+      <c r="GQ285" s="1"/>
+      <c r="GR285" s="1"/>
+      <c r="GY285" s="1"/>
+      <c r="GZ285" s="1"/>
+      <c r="HA285" s="1"/>
+      <c r="HB285" s="1"/>
+      <c r="IQ285" s="1">
+        <v>888839932</v>
+      </c>
+      <c r="IR285" t="s">
+        <v>2310</v>
+      </c>
+      <c r="IS285" s="1">
+        <v>46303.484780092593</v>
+      </c>
+      <c r="IU285" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW285" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX285" t="s">
+        <v>2311</v>
+      </c>
+      <c r="IY285">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A286" s="1">
+        <v>46303.665873425933</v>
+      </c>
+      <c r="B286" s="1">
+        <v>46303.67173869213</v>
+      </c>
+      <c r="C286" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D286" t="s">
+        <v>691</v>
+      </c>
+      <c r="E286" t="s">
+        <v>196</v>
+      </c>
+      <c r="F286" t="s">
+        <v>618</v>
+      </c>
+      <c r="G286" t="s">
+        <v>198</v>
+      </c>
+      <c r="H286" t="s">
+        <v>199</v>
+      </c>
+      <c r="J286" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K286" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L286" t="s">
+        <v>395</v>
+      </c>
+      <c r="M286" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N286" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O286" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R286">
+        <v>17</v>
+      </c>
+      <c r="S286">
+        <v>11</v>
+      </c>
+      <c r="T286" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U286" t="s">
+        <v>2313</v>
+      </c>
+      <c r="V286">
+        <v>1</v>
+      </c>
+      <c r="W286">
+        <v>0</v>
+      </c>
+      <c r="X286">
+        <v>0</v>
+      </c>
+      <c r="Y286">
+        <v>0</v>
+      </c>
+      <c r="Z286">
+        <v>1</v>
+      </c>
+      <c r="AA286">
+        <v>0</v>
+      </c>
+      <c r="AB286" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC286">
+        <v>1</v>
+      </c>
+      <c r="AD286">
+        <v>1</v>
+      </c>
+      <c r="AE286">
+        <v>0</v>
+      </c>
+      <c r="AF286">
+        <v>0</v>
+      </c>
+      <c r="AG286">
+        <v>0</v>
+      </c>
+      <c r="AH286">
+        <v>830</v>
+      </c>
+      <c r="AI286">
+        <v>210</v>
+      </c>
+      <c r="AJ286">
+        <v>327</v>
+      </c>
+      <c r="AK286">
+        <v>2</v>
+      </c>
+      <c r="AL286">
+        <v>2</v>
+      </c>
+      <c r="AM286">
+        <v>0</v>
+      </c>
+      <c r="AN286">
+        <v>0</v>
+      </c>
+      <c r="AO286" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP286">
+        <v>5</v>
+      </c>
+      <c r="AQ286" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR286" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS286" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT286" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU286" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV286" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW286" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS286" t="s">
+        <v>1122</v>
+      </c>
+      <c r="BT286" t="s">
+        <v>1637</v>
+      </c>
+      <c r="BU286" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW286" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX286" t="s">
+        <v>1135</v>
+      </c>
+      <c r="EY286" s="1"/>
+      <c r="GQ286" s="1"/>
+      <c r="GR286" s="1"/>
+      <c r="GY286" s="1"/>
+      <c r="GZ286" s="1"/>
+      <c r="HA286" s="1"/>
+      <c r="HB286" s="1"/>
+      <c r="IQ286" s="1">
+        <v>888930793</v>
+      </c>
+      <c r="IR286" t="s">
+        <v>2314</v>
+      </c>
+      <c r="IS286" s="1">
+        <v>46303.546759259261</v>
+      </c>
+      <c r="IU286" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW286" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX286" t="s">
+        <v>2315</v>
+      </c>
+      <c r="IY286">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A287" s="1">
+        <v>46303.453409363428</v>
+      </c>
+      <c r="B287" s="1">
+        <v>46303.741336400461</v>
+      </c>
+      <c r="C287" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D287" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E287" t="s">
+        <v>309</v>
+      </c>
+      <c r="F287" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G287" t="s">
+        <v>198</v>
+      </c>
+      <c r="H287" t="s">
+        <v>311</v>
+      </c>
+      <c r="BS287" t="s">
+        <v>2316</v>
+      </c>
+      <c r="BT287" t="s">
+        <v>2317</v>
+      </c>
+      <c r="BU287" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW287" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX287" t="s">
+        <v>2318</v>
+      </c>
+      <c r="BY287" t="s">
+        <v>359</v>
+      </c>
+      <c r="EK287" t="s">
+        <v>2319</v>
+      </c>
+      <c r="EL287" t="s">
+        <v>2320</v>
+      </c>
+      <c r="EM287" t="s">
+        <v>2321</v>
+      </c>
+      <c r="EN287" t="s">
+        <v>2322</v>
+      </c>
+      <c r="EY287" s="1"/>
+      <c r="GQ287" s="1"/>
+      <c r="GR287" s="1"/>
+      <c r="GY287" s="1"/>
+      <c r="GZ287" s="1"/>
+      <c r="HA287" s="1"/>
+      <c r="HB287" s="1"/>
+      <c r="IQ287" s="1">
+        <v>889028053</v>
+      </c>
+      <c r="IR287" t="s">
+        <v>2323</v>
+      </c>
+      <c r="IS287" s="1">
+        <v>46303.616412037038</v>
+      </c>
+      <c r="IU287" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW287" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX287" t="s">
+        <v>2324</v>
+      </c>
+      <c r="IY287">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A288" s="1">
+        <v>46303.922115277783</v>
+      </c>
+      <c r="B288" s="1">
+        <v>46303.937444386567</v>
+      </c>
+      <c r="C288" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D288" t="s">
+        <v>690</v>
+      </c>
+      <c r="E288" t="s">
+        <v>210</v>
+      </c>
+      <c r="F288" t="s">
+        <v>970</v>
+      </c>
+      <c r="G288" t="s">
+        <v>198</v>
+      </c>
+      <c r="H288" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX288" t="s">
+        <v>2325</v>
+      </c>
+      <c r="AY288" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ288" t="s">
+        <v>2326</v>
+      </c>
+      <c r="BA288" t="s">
+        <v>2327</v>
+      </c>
+      <c r="BB288">
+        <v>5</v>
+      </c>
+      <c r="BC288">
+        <v>2</v>
+      </c>
+      <c r="BD288" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE288" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF288" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG288" t="s">
+        <v>2328</v>
+      </c>
+      <c r="BH288" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI288" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ288" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK288">
+        <v>1</v>
+      </c>
+      <c r="BL288" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM288">
+        <v>50</v>
+      </c>
+      <c r="BN288">
+        <v>36</v>
+      </c>
+      <c r="BO288" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP288" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ288" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS288" t="s">
+        <v>1231</v>
+      </c>
+      <c r="BT288" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU288" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW288" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX288" t="s">
+        <v>1202</v>
+      </c>
+      <c r="EY288" s="1"/>
+      <c r="GQ288" s="1"/>
+      <c r="GR288" s="1"/>
+      <c r="GY288" s="1"/>
+      <c r="GZ288" s="1"/>
+      <c r="HA288" s="1"/>
+      <c r="HB288" s="1"/>
+      <c r="IQ288" s="1">
+        <v>889229654</v>
+      </c>
+      <c r="IR288" t="s">
+        <v>2329</v>
+      </c>
+      <c r="IS288" s="1">
+        <v>46303.8124537037</v>
+      </c>
+      <c r="IU288" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW288" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX288" t="s">
+        <v>2330</v>
+      </c>
+      <c r="IY288">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A289" s="1">
+        <v>46303.937445104173</v>
+      </c>
+      <c r="B289" s="1">
+        <v>46303.950223715277</v>
+      </c>
+      <c r="C289" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D289" t="s">
+        <v>690</v>
+      </c>
+      <c r="E289" t="s">
+        <v>210</v>
+      </c>
+      <c r="F289" t="s">
+        <v>2246</v>
+      </c>
+      <c r="G289" t="s">
+        <v>198</v>
+      </c>
+      <c r="H289" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX289" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY289" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ289" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA289" t="s">
+        <v>2331</v>
+      </c>
+      <c r="BB289">
+        <v>36</v>
+      </c>
+      <c r="BC289">
+        <v>42</v>
+      </c>
+      <c r="BD289" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE289" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF289" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG289" t="s">
+        <v>2332</v>
+      </c>
+      <c r="BH289" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI289" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ289" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK289">
+        <v>2</v>
+      </c>
+      <c r="BL289" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM289">
+        <v>24</v>
+      </c>
+      <c r="BN289">
+        <v>38</v>
+      </c>
+      <c r="BO289" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP289" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ289" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS289" t="s">
+        <v>2333</v>
+      </c>
+      <c r="BT289" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU289" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW289" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX289" t="s">
+        <v>1202</v>
+      </c>
+      <c r="EY289" s="1"/>
+      <c r="GQ289" s="1"/>
+      <c r="GR289" s="1"/>
+      <c r="GY289" s="1"/>
+      <c r="GZ289" s="1"/>
+      <c r="HA289" s="1"/>
+      <c r="HB289" s="1"/>
+      <c r="IQ289" s="1">
+        <v>889241748</v>
+      </c>
+      <c r="IR289" t="s">
+        <v>2334</v>
+      </c>
+      <c r="IS289" s="1">
+        <v>46303.825231481482</v>
+      </c>
+      <c r="IU289" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW289" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX289" t="s">
+        <v>2335</v>
+      </c>
+      <c r="IY289">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A290" s="1">
+        <v>46302.837925925924</v>
+      </c>
+      <c r="B290" s="1">
+        <v>46304.004320902779</v>
+      </c>
+      <c r="C290" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D290" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E290" t="s">
+        <v>254</v>
+      </c>
+      <c r="F290" t="s">
+        <v>267</v>
+      </c>
+      <c r="G290" t="s">
+        <v>198</v>
+      </c>
+      <c r="H290" t="s">
+        <v>256</v>
+      </c>
+      <c r="BS290" t="s">
+        <v>2336</v>
+      </c>
+      <c r="BT290" t="s">
+        <v>2337</v>
+      </c>
+      <c r="BU290" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW290" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX290" t="s">
+        <v>2338</v>
+      </c>
+      <c r="BY290" t="s">
+        <v>359</v>
+      </c>
+      <c r="EK290" t="s">
+        <v>2339</v>
+      </c>
+      <c r="EL290" t="s">
+        <v>2340</v>
+      </c>
+      <c r="EM290" t="s">
+        <v>2341</v>
+      </c>
+      <c r="EN290" t="s">
+        <v>2342</v>
+      </c>
+      <c r="EY290" s="1"/>
+      <c r="GQ290" s="1"/>
+      <c r="GR290" s="1"/>
+      <c r="GY290" s="1"/>
+      <c r="GZ290" s="1"/>
+      <c r="HA290" s="1"/>
+      <c r="HB290" s="1"/>
+      <c r="IQ290" s="1">
+        <v>889277719</v>
+      </c>
+      <c r="IR290" t="s">
+        <v>2343</v>
+      </c>
+      <c r="IS290" s="1">
+        <v>46303.879328703697</v>
+      </c>
+      <c r="IU290" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW290" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX290" t="s">
+        <v>2344</v>
+      </c>
+      <c r="IY290">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A291" s="1">
+        <v>46304.309806493053</v>
+      </c>
+      <c r="B291" s="1">
+        <v>46304.31571466435</v>
+      </c>
+      <c r="C291" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D291" t="s">
+        <v>691</v>
+      </c>
+      <c r="E291" t="s">
+        <v>280</v>
+      </c>
+      <c r="F291" t="s">
+        <v>656</v>
+      </c>
+      <c r="G291" t="s">
+        <v>198</v>
+      </c>
+      <c r="H291" t="s">
+        <v>282</v>
+      </c>
+      <c r="J291" t="s">
+        <v>661</v>
+      </c>
+      <c r="K291" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L291" t="s">
+        <v>395</v>
+      </c>
+      <c r="M291" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N291" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O291" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P291" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AH291">
+        <v>1466</v>
+      </c>
+      <c r="AI291">
+        <v>443</v>
+      </c>
+      <c r="AJ291">
+        <v>581</v>
+      </c>
+      <c r="AK291">
+        <v>11</v>
+      </c>
+      <c r="AL291">
+        <v>2</v>
+      </c>
+      <c r="AM291">
+        <v>40</v>
+      </c>
+      <c r="AN291">
+        <v>10</v>
+      </c>
+      <c r="AO291" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP291">
+        <v>20</v>
+      </c>
+      <c r="AQ291" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR291" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS291" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT291" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU291" t="s">
+        <v>202</v>
+      </c>
+      <c r="AV291" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW291" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS291" t="s">
+        <v>2345</v>
+      </c>
+      <c r="BT291" t="s">
+        <v>2346</v>
+      </c>
+      <c r="BU291" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW291" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX291" t="s">
+        <v>2347</v>
+      </c>
+      <c r="EY291" s="1"/>
+      <c r="GQ291" s="1"/>
+      <c r="GR291" s="1"/>
+      <c r="GY291" s="1"/>
+      <c r="GZ291" s="1"/>
+      <c r="HA291" s="1"/>
+      <c r="HB291" s="1"/>
+      <c r="IQ291" s="1">
+        <v>889379357</v>
+      </c>
+      <c r="IR291" t="s">
+        <v>2348</v>
+      </c>
+      <c r="IS291" s="1">
+        <v>46304.182743055557</v>
+      </c>
+      <c r="IU291" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW291" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX291" t="s">
+        <v>2349</v>
+      </c>
+      <c r="IY291">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A292" s="1">
+        <v>46302.507222314824</v>
+      </c>
+      <c r="B292" s="1">
+        <v>46304.399318333337</v>
+      </c>
+      <c r="C292" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D292" t="s">
+        <v>691</v>
+      </c>
+      <c r="E292" t="s">
+        <v>237</v>
+      </c>
+      <c r="F292" t="s">
+        <v>2350</v>
+      </c>
+      <c r="G292" t="s">
+        <v>198</v>
+      </c>
+      <c r="H292" t="s">
+        <v>240</v>
+      </c>
+      <c r="J292" t="s">
+        <v>2351</v>
+      </c>
+      <c r="K292" t="s">
+        <v>201</v>
+      </c>
+      <c r="L292" t="s">
+        <v>324</v>
+      </c>
+      <c r="M292" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N292" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O292" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH292">
+        <v>980</v>
+      </c>
+      <c r="AI292">
+        <v>485</v>
+      </c>
+      <c r="AJ292">
+        <v>495</v>
+      </c>
+      <c r="AK292">
+        <v>10</v>
+      </c>
+      <c r="AL292">
+        <v>2</v>
+      </c>
+      <c r="AM292">
+        <v>0</v>
+      </c>
+      <c r="AN292">
+        <v>0</v>
+      </c>
+      <c r="AO292" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP292">
+        <v>1</v>
+      </c>
+      <c r="AQ292" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR292" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS292" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT292" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU292" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV292" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW292" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS292" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT292" t="s">
+        <v>2352</v>
+      </c>
+      <c r="BU292" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV292" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW292" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX292" t="s">
+        <v>2353</v>
+      </c>
+      <c r="EY292" s="1"/>
+      <c r="GQ292" s="1"/>
+      <c r="GR292" s="1"/>
+      <c r="GY292" s="1"/>
+      <c r="GZ292" s="1"/>
+      <c r="HA292" s="1"/>
+      <c r="HB292" s="1"/>
+      <c r="IQ292" s="1">
+        <v>889457936</v>
+      </c>
+      <c r="IR292" t="s">
+        <v>2354</v>
+      </c>
+      <c r="IS292" s="1">
+        <v>46304.274351851847</v>
+      </c>
+      <c r="IU292" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW292" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX292" t="s">
+        <v>2355</v>
+      </c>
+      <c r="IY292">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A293" s="1">
+        <v>46304.399320115743</v>
+      </c>
+      <c r="B293" s="1">
+        <v>46304.406027233803</v>
+      </c>
+      <c r="C293" s="1">
+        <v>46304</v>
+      </c>
+      <c r="D293" t="s">
+        <v>691</v>
+      </c>
+      <c r="E293" t="s">
+        <v>237</v>
+      </c>
+      <c r="F293" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G293" t="s">
+        <v>198</v>
+      </c>
+      <c r="H293" t="s">
+        <v>240</v>
+      </c>
+      <c r="J293" t="s">
+        <v>2356</v>
+      </c>
+      <c r="K293" t="s">
+        <v>201</v>
+      </c>
+      <c r="L293" t="s">
+        <v>324</v>
+      </c>
+      <c r="M293" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N293" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O293" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH293">
+        <v>938</v>
+      </c>
+      <c r="AI293">
+        <v>315</v>
+      </c>
+      <c r="AJ293">
+        <v>423</v>
+      </c>
+      <c r="AK293">
+        <v>9</v>
+      </c>
+      <c r="AL293">
+        <v>2</v>
+      </c>
+      <c r="AM293">
+        <v>60</v>
+      </c>
+      <c r="AN293">
+        <v>0</v>
+      </c>
+      <c r="AO293" t="s">
+        <v>2034</v>
+      </c>
+      <c r="AP293">
+        <v>4</v>
+      </c>
+      <c r="AQ293" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR293" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS293" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT293" t="s">
+        <v>216</v>
+      </c>
+      <c r="AU293" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV293" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW293" t="s">
+        <v>230</v>
+      </c>
+      <c r="BS293" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT293" t="s">
+        <v>2357</v>
+      </c>
+      <c r="BU293" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV293" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW293" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX293" t="s">
+        <v>2358</v>
+      </c>
+      <c r="EY293" s="1"/>
+      <c r="GQ293" s="1"/>
+      <c r="GR293" s="1"/>
+      <c r="GY293" s="1"/>
+      <c r="GZ293" s="1"/>
+      <c r="HA293" s="1"/>
+      <c r="HB293" s="1"/>
+      <c r="IQ293" s="1">
+        <v>889465699</v>
+      </c>
+      <c r="IR293" t="s">
+        <v>2359</v>
+      </c>
+      <c r="IS293" s="1">
+        <v>46304.281053240738</v>
+      </c>
+      <c r="IU293" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW293" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX293" t="s">
+        <v>2360</v>
+      </c>
+      <c r="IY293">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A294" s="1">
+        <v>46304.406028958343</v>
+      </c>
+      <c r="B294" s="1">
+        <v>46304.41601828704</v>
+      </c>
+      <c r="C294" s="1">
+        <v>46304</v>
+      </c>
+      <c r="D294" t="s">
+        <v>691</v>
+      </c>
+      <c r="E294" t="s">
+        <v>237</v>
+      </c>
+      <c r="F294" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G294" t="s">
+        <v>198</v>
+      </c>
+      <c r="H294" t="s">
+        <v>240</v>
+      </c>
+      <c r="J294" t="s">
+        <v>2361</v>
+      </c>
+      <c r="K294" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L294" t="s">
+        <v>324</v>
+      </c>
+      <c r="M294" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N294" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O294" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P294" t="s">
+        <v>1702</v>
+      </c>
+      <c r="Q294" t="s">
+        <v>2362</v>
+      </c>
+      <c r="AH294">
+        <v>380</v>
+      </c>
+      <c r="AI294">
+        <v>160</v>
+      </c>
+      <c r="AJ294">
+        <v>120</v>
+      </c>
+      <c r="AK294">
+        <v>8</v>
+      </c>
+      <c r="AL294">
+        <v>1</v>
+      </c>
+      <c r="AM294">
+        <v>0</v>
+      </c>
+      <c r="AN294">
+        <v>0</v>
+      </c>
+      <c r="AO294" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP294">
+        <v>3</v>
+      </c>
+      <c r="AQ294" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR294" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS294" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT294" t="s">
+        <v>216</v>
+      </c>
+      <c r="AU294" t="s">
+        <v>202</v>
+      </c>
+      <c r="AV294" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW294" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS294" t="s">
+        <v>2363</v>
+      </c>
+      <c r="BT294" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU294" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV294" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW294" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX294" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY294" s="1"/>
+      <c r="GQ294" s="1"/>
+      <c r="GR294" s="1"/>
+      <c r="GY294" s="1"/>
+      <c r="GZ294" s="1"/>
+      <c r="HA294" s="1"/>
+      <c r="HB294" s="1"/>
+      <c r="IQ294" s="1">
+        <v>889476703</v>
+      </c>
+      <c r="IR294" t="s">
+        <v>2364</v>
+      </c>
+      <c r="IS294" s="1">
+        <v>46304.291076388887</v>
+      </c>
+      <c r="IU294" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW294" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX294" t="s">
+        <v>2365</v>
+      </c>
+      <c r="IY294">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A295" s="1">
+        <v>46304.416021053243</v>
+      </c>
+      <c r="B295" s="1">
+        <v>46304.429590729167</v>
+      </c>
+      <c r="C295" s="1">
+        <v>46304</v>
+      </c>
+      <c r="D295" t="s">
+        <v>690</v>
+      </c>
+      <c r="E295" t="s">
+        <v>237</v>
+      </c>
+      <c r="F295" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G295" t="s">
+        <v>198</v>
+      </c>
+      <c r="H295" t="s">
+        <v>240</v>
+      </c>
+      <c r="AX295" t="s">
+        <v>2299</v>
+      </c>
+      <c r="AY295" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ295" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA295" t="s">
+        <v>2366</v>
+      </c>
+      <c r="BB295">
+        <v>4</v>
+      </c>
+      <c r="BC295">
+        <v>6</v>
+      </c>
+      <c r="BD295" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE295" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF295" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG295" t="s">
+        <v>2367</v>
+      </c>
+      <c r="BH295" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI295" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ295" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK295">
+        <v>4</v>
+      </c>
+      <c r="BL295" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM295">
+        <v>50</v>
+      </c>
+      <c r="BN295">
+        <v>26</v>
+      </c>
+      <c r="BO295" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP295" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ295" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS295" t="s">
+        <v>2368</v>
+      </c>
+      <c r="BT295" t="s">
+        <v>727</v>
+      </c>
+      <c r="BU295" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV295" t="s">
+        <v>2369</v>
+      </c>
+      <c r="BW295" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX295" t="s">
+        <v>2099</v>
+      </c>
+      <c r="EY295" s="1"/>
+      <c r="GQ295" s="1"/>
+      <c r="GR295" s="1"/>
+      <c r="GY295" s="1"/>
+      <c r="GZ295" s="1"/>
+      <c r="HA295" s="1"/>
+      <c r="HB295" s="1"/>
+      <c r="IQ295" s="1">
+        <v>889491698</v>
+      </c>
+      <c r="IR295" t="s">
+        <v>2370</v>
+      </c>
+      <c r="IS295" s="1">
+        <v>46304.304606481477</v>
+      </c>
+      <c r="IU295" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW295" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX295" t="s">
+        <v>2371</v>
+      </c>
+      <c r="IY295">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A296" s="1">
+        <v>46304.429592418979</v>
+      </c>
+      <c r="B296" s="1">
+        <v>46304.440478900462</v>
+      </c>
+      <c r="C296" s="1">
+        <v>46304</v>
+      </c>
+      <c r="D296" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E296" t="s">
+        <v>237</v>
+      </c>
+      <c r="F296" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G296" t="s">
+        <v>198</v>
+      </c>
+      <c r="H296" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS296" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT296" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU296" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV296" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW296" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX296" t="s">
+        <v>612</v>
+      </c>
+      <c r="BY296" t="s">
+        <v>930</v>
+      </c>
+      <c r="EK296" t="s">
+        <v>2372</v>
+      </c>
+      <c r="EL296" t="s">
+        <v>2373</v>
+      </c>
+      <c r="EM296" t="s">
+        <v>2374</v>
+      </c>
+      <c r="EN296" t="s">
+        <v>2375</v>
+      </c>
+      <c r="EY296" s="1"/>
+      <c r="GQ296" s="1"/>
+      <c r="GR296" s="1"/>
+      <c r="GY296" s="1"/>
+      <c r="GZ296" s="1"/>
+      <c r="HA296" s="1"/>
+      <c r="HB296" s="1"/>
+      <c r="IQ296" s="1">
+        <v>889503171</v>
+      </c>
+      <c r="IR296" t="s">
+        <v>2376</v>
+      </c>
+      <c r="IS296" s="1">
+        <v>46304.315509259257</v>
+      </c>
+      <c r="IU296" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW296" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX296" t="s">
+        <v>2377</v>
+      </c>
+      <c r="IY296">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A297" s="1">
+        <v>46304.440482337966</v>
+      </c>
+      <c r="B297" s="1">
+        <v>46304.443005046298</v>
+      </c>
+      <c r="C297" s="1">
+        <v>46304</v>
+      </c>
+      <c r="D297" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E297" t="s">
+        <v>237</v>
+      </c>
+      <c r="F297" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G297" t="s">
+        <v>198</v>
+      </c>
+      <c r="H297" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS297" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT297" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU297" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV297" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW297" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX297" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY297" s="1"/>
+      <c r="GQ297" s="1"/>
+      <c r="GR297" s="1"/>
+      <c r="GY297" s="1"/>
+      <c r="GZ297" s="1"/>
+      <c r="HA297" s="1"/>
+      <c r="HB297" s="1"/>
+      <c r="HS297" t="s">
+        <v>2379</v>
+      </c>
+      <c r="HT297">
+        <v>2</v>
+      </c>
+      <c r="HU297">
+        <v>2</v>
+      </c>
+      <c r="IQ297" s="1">
+        <v>889505901</v>
+      </c>
+      <c r="IR297" t="s">
+        <v>2380</v>
+      </c>
+      <c r="IS297" s="1">
+        <v>46304.318020833343</v>
+      </c>
+      <c r="IU297" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW297" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX297" t="s">
+        <v>2381</v>
+      </c>
+      <c r="IY297">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A298" s="1">
+        <v>46304.443006539354</v>
+      </c>
+      <c r="B298" s="1">
+        <v>46304.444836122682</v>
+      </c>
+      <c r="C298" s="1">
+        <v>46304</v>
+      </c>
+      <c r="D298" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E298" t="s">
+        <v>237</v>
+      </c>
+      <c r="F298" t="s">
+        <v>248</v>
+      </c>
+      <c r="G298" t="s">
+        <v>198</v>
+      </c>
+      <c r="H298" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS298" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT298" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU298" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV298" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW298" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX298" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY298" s="1"/>
+      <c r="GQ298" s="1"/>
+      <c r="GR298" s="1"/>
+      <c r="GY298" s="1"/>
+      <c r="GZ298" s="1"/>
+      <c r="HA298" s="1"/>
+      <c r="HB298" s="1"/>
+      <c r="HS298" t="s">
+        <v>2382</v>
+      </c>
+      <c r="HT298">
+        <v>1</v>
+      </c>
+      <c r="HU298">
+        <v>0</v>
+      </c>
+      <c r="IQ298" s="1">
+        <v>889508079</v>
+      </c>
+      <c r="IR298" t="s">
+        <v>2383</v>
+      </c>
+      <c r="IS298" s="1">
+        <v>46304.319849537038</v>
+      </c>
+      <c r="IU298" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW298" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX298" t="s">
+        <v>2384</v>
+      </c>
+      <c r="IY298">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="379" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01365FBA-AE17-C646-AB54-CF842F981CEB}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711CA4C0-1BC9-D445-AE9D-3D0F8CA23579}"/>
   <bookViews>
     <workbookView xWindow="2520" yWindow="1060" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7311" uniqueCount="2385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="2514">
   <si>
     <t>start</t>
   </si>
@@ -7192,6 +7192,393 @@
   </si>
   <si>
     <t>uuid:4fdf8012-234e-4bf0-a026-baadbf933a37</t>
+  </si>
+  <si>
+    <t>fa333177-aac4-4a97-8beb-0308a808b169</t>
+  </si>
+  <si>
+    <t>uuid:fa333177-aac4-4a97-8beb-0308a808b169</t>
+  </si>
+  <si>
+    <t>Monday Wednesday Friday</t>
+  </si>
+  <si>
+    <t>Encourage proper waste disposal</t>
+  </si>
+  <si>
+    <t>4b621bcc-19b9-43c8-9704-6db5006c995e</t>
+  </si>
+  <si>
+    <t>uuid:4b621bcc-19b9-43c8-9704-6db5006c995e</t>
+  </si>
+  <si>
+    <t>Ensure that the drainage system is working properly by the next visit</t>
+  </si>
+  <si>
+    <t>83a2964f-dc3e-4949-9623-46892ade8661</t>
+  </si>
+  <si>
+    <t>uuid:83a2964f-dc3e-4949-9623-46892ade8661</t>
+  </si>
+  <si>
+    <t>Does Ebola have a cure?</t>
+  </si>
+  <si>
+    <t>Water flow is very bad</t>
+  </si>
+  <si>
+    <t>No rumor but the question was answered</t>
+  </si>
+  <si>
+    <t>Talk to NWSC to ensure that the water flows</t>
+  </si>
+  <si>
+    <t>aa44372b-afaf-4ee8-af30-97e731cb8a9e</t>
+  </si>
+  <si>
+    <t>uuid:aa44372b-afaf-4ee8-af30-97e731cb8a9e</t>
+  </si>
+  <si>
+    <t>Why does Ebola come out of the blue?</t>
+  </si>
+  <si>
+    <t>Commercial sex worker</t>
+  </si>
+  <si>
+    <t>Before the public health emergency sensitization activities, I had limited information about public health emergencies such as Ebola. Like many people in my line of work, I was more concerned about earning a living and meeting my daily needs than thinking about diseases that could threaten my health and the health of others. There was fear and uncertainty surrounding Ebola, and some people believed that the disease was either exaggerated or did not exist. This made it difficult to know which information to trust and what precautions to take. Because my work involves interacting with different people, I could potentially be exposed to health risks. However, I did not fully understand how to recognize warning signs, protect myself, or respond appropriately if I suspected that someone had a dangerous infectious disease. I also did not know clearly where to report a suspected case or where to obtain reliable information during a public health emergency.</t>
+  </si>
+  <si>
+    <t>The turning point came when I participated in a public health emergency sensitization activity conducted under the Solutions for People (S4P) project, with support from UNICEF and the Ministry of Health. Through the interactive health education session, including the Knowledge Wheel activity, I had an opportunity to learn about Ebola and other public health emergencies in a way that was easier to understand. The session helped me understand that public health emergencies are real and that everyone has a role to play in preventing the spread of disease. I learned the importance of seeking information from health workers, recognizing possible warning signs, avoiding contact with suspected infectious cases, and promptly reporting concerns to the appropriate health authorities. What stood out to me was that the information was relevant to ordinary people, including those whose work and daily interactions bring them into contact with many different individuals. I realized that protecting myself was also a way of protecting the people around me.</t>
+  </si>
+  <si>
+    <t>After the sensitization, I became more conscious of my health and the importance of taking public health information seriously. I understood better that rumours should not guide my decisions and that I should seek clarification from reliable health sources whenever I hear information about a possible outbreak. I also became more aware of the importance of practising good hygiene, washing my hands regularly, and avoiding unnecessary contact with anyone suspected of having a serious infectious disease. I learned that if I noticed warning signs or became concerned about a possible case, I should seek guidance from health workers and report the concern promptly rather than conceal it or spread unverified information. I am now better informed about the importance of sharing accurate health information with people around me. I can encourage others to take public health warnings seriously and to seek professional guidance instead of relying on rumours or dismissing the existence of dangerous diseases.</t>
+  </si>
+  <si>
+    <t>For me, this change is significant because my health is directly connected to my ability to earn a living and support myself. Becoming ill could affect my income, my independence, and my ability to meet my daily needs. Understanding how to respond to a public health emergency gives me greater confidence to protect myself and make informed decisions. The sensitization also reminded me that people in my line of work should not be left out of public health education. We are part of the community, and we need accurate information just like everyone else. Being informed helps us protect ourselves and those with whom we interact. My greatest lesson is that public health emergencies require everyone’s participation. I may not be a health worker, but I can still contribute by practising good hygiene, sharing accurate information, avoiding rumours, and reporting concerns to the appropriate authorities. For me, knowledge is important because it helps replace fear and uncertainty with informed action.</t>
+  </si>
+  <si>
+    <t>b46095b4-3c20-45c0-a7e3-ba0216795f63</t>
+  </si>
+  <si>
+    <t>uuid:b46095b4-3c20-45c0-a7e3-ba0216795f63</t>
+  </si>
+  <si>
+    <t>Nateete Muslim Secondary School</t>
+  </si>
+  <si>
+    <t>Senior woman</t>
+  </si>
+  <si>
+    <t>Ensure to work on the drainqge system before the next visit</t>
+  </si>
+  <si>
+    <t>32704e31-8919-4718-aa63-7c01d8c4dee7</t>
+  </si>
+  <si>
+    <t>uuid:32704e31-8919-4718-aa63-7c01d8c4dee7</t>
+  </si>
+  <si>
+    <t>65b4bfb5-a9aa-4f10-991c-4b437e060e56</t>
+  </si>
+  <si>
+    <t>uuid:65b4bfb5-a9aa-4f10-991c-4b437e060e56</t>
+  </si>
+  <si>
+    <t>24180823-a9f0-445f-87e2-cc4fe5f07adb</t>
+  </si>
+  <si>
+    <t>uuid:24180823-a9f0-445f-87e2-cc4fe5f07adb</t>
+  </si>
+  <si>
+    <t>e8d8e6e7-d578-4b81-beb2-02596a0d06c5</t>
+  </si>
+  <si>
+    <t>uuid:e8d8e6e7-d578-4b81-beb2-02596a0d06c5</t>
+  </si>
+  <si>
+    <t>Collect money within themselves to purchase hand washing facilities</t>
+  </si>
+  <si>
+    <t>Why are these diseases always abrupt</t>
+  </si>
+  <si>
+    <t>Poor waste management</t>
+  </si>
+  <si>
+    <t>Sensitization on proper waste management</t>
+  </si>
+  <si>
+    <t>73158254-dc5b-406b-ad97-f157db160bf1</t>
+  </si>
+  <si>
+    <t>uuid:73158254-dc5b-406b-ad97-f157db160bf1</t>
+  </si>
+  <si>
+    <t>Provide ahan washing facility at the gate</t>
+  </si>
+  <si>
+    <t>99fdf528-f899-4f1b-8344-60eff323764c</t>
+  </si>
+  <si>
+    <t>uuid:99fdf528-f899-4f1b-8344-60eff323764c</t>
+  </si>
+  <si>
+    <t>Mengo market</t>
+  </si>
+  <si>
+    <t>Ensure proper waste management, try and get hand washing facilities</t>
+  </si>
+  <si>
+    <t>127ea79b-63ea-4099-b059-8550d5bc2c20</t>
+  </si>
+  <si>
+    <t>uuid:127ea79b-63ea-4099-b059-8550d5bc2c20</t>
+  </si>
+  <si>
+    <t>Mengo boda stage</t>
+  </si>
+  <si>
+    <t>Get a hand washing facility, be champions of change</t>
+  </si>
+  <si>
+    <t>487fea67-04ea-49a9-9c18-c1069d8645af</t>
+  </si>
+  <si>
+    <t>uuid:487fea67-04ea-49a9-9c18-c1069d8645af</t>
+  </si>
+  <si>
+    <t>Market vendors chairman</t>
+  </si>
+  <si>
+    <t>Enforce hand washing</t>
+  </si>
+  <si>
+    <t>Is Ebola back</t>
+  </si>
+  <si>
+    <t>Enforce proper waste management</t>
+  </si>
+  <si>
+    <t>13a59dea-3002-41ea-acc6-c7d2dee79aeb</t>
+  </si>
+  <si>
+    <t>uuid:13a59dea-3002-41ea-acc6-c7d2dee79aeb</t>
+  </si>
+  <si>
+    <t>Chairman</t>
+  </si>
+  <si>
+    <t>Become champions of change in their area</t>
+  </si>
+  <si>
+    <t>35549800-ca70-4d91-ba37-5fae8975d420</t>
+  </si>
+  <si>
+    <t>uuid:35549800-ca70-4d91-ba37-5fae8975d420</t>
+  </si>
+  <si>
+    <t>Ensure people in the market learn the various signs and symptoms of public health emergencies</t>
+  </si>
+  <si>
+    <t>Why do these diseases come when the year is ending</t>
+  </si>
+  <si>
+    <t>The question was answered</t>
+  </si>
+  <si>
+    <t>Encourage proper waste management</t>
+  </si>
+  <si>
+    <t>1fd898f8-f682-459e-a15d-2b83a3063968</t>
+  </si>
+  <si>
+    <t>uuid:1fd898f8-f682-459e-a15d-2b83a3063968</t>
+  </si>
+  <si>
+    <t>Talk to people about various signs and symptoms of public health emergencies</t>
+  </si>
+  <si>
+    <t>These diseases do not exist</t>
+  </si>
+  <si>
+    <t>b05da31f-0d9c-470f-8bc4-790f2e2c7385</t>
+  </si>
+  <si>
+    <t>uuid:b05da31f-0d9c-470f-8bc4-790f2e2c7385</t>
+  </si>
+  <si>
+    <t>Commercial sex workers</t>
+  </si>
+  <si>
+    <t>Talk to their customers about public health emergencies</t>
+  </si>
+  <si>
+    <t>Continuous sensitization on public health emergencies</t>
+  </si>
+  <si>
+    <t>dd54d4f4-02f2-483d-9e14-50f224558e97</t>
+  </si>
+  <si>
+    <t>uuid:dd54d4f4-02f2-483d-9e14-50f224558e97</t>
+  </si>
+  <si>
+    <t>Before the public health emergency sensitization, I did not know much about Ebola and other diseases that can spread quickly in the community. Some pupils had heard about Ebola but did not understand how it spreads, how to protect themselves, or what to do if someone showed signs of a serious illness. There was also fear and confusion, and some people believed that Ebola did not exist. At school, we knew that washing our hands was important, but we did not always understand how good hygiene could help protect us from diseases. I also did not know what I should do if a fellow pupil or someone in my community became seriously ill.</t>
+  </si>
+  <si>
+    <t>My turning point came when the Solutions for People (S4P) team, with support from UNICEF and the Ministry of Health, visited our school and conducted a public health emergency sensitization session. During the interactive Knowledge Wheel activity, we answered questions, learned about Ebola, and discussed how to protect ourselves during a disease outbreak. The activity made learning interesting because we could participate, ask questions, and discover whether our answers were correct. I learned that Ebola is real and that public health emergencies should be taken seriously. I also learned the importance of washing my hands, avoiding contact with body fluids from a sick person, and informing a trusted adult or health worker if someone shows signs of a serious illness.</t>
+  </si>
+  <si>
+    <t>After the sensitization, I became more careful about my hygiene and more aware of how to protect myself and my classmates. I understood the importance of washing my hands with soap and water, especially after using the toilet and before eating. I also learned not to spread rumours or laugh at people who are afraid of diseases. Instead, I should ask teachers, parents, or health workers for correct information. If a pupil or someone in the community becomes seriously ill, I now understand that I should inform a responsible adult rather than try to handle the situation myself. I can also share what I learned with my family and friends so that they too understand the importance of good hygiene and taking public health emergencies seriously.</t>
+  </si>
+  <si>
+    <t>This change is important to me because I want to stay healthy, continue attending school, and play with my friends without putting myself or others at unnecessary risk. I now understand that protecting myself from diseases also helps protect my classmates, teachers, family, and the wider community. The most meaningful thing I learned is that I do not have to be a doctor or a health worker to help prevent the spread of disease. As a pupil, I can practise good hygiene, share correct information, avoid spreading rumours, and tell a trusted adult when I am concerned about someone's health. The sensitization helped me understand that public health emergencies are real and that everyone, including children, has a role to play in keeping the community safe.</t>
+  </si>
+  <si>
+    <t>0b5e8f2b-8de8-4ea4-9e40-12ab47a7c530</t>
+  </si>
+  <si>
+    <t>uuid:0b5e8f2b-8de8-4ea4-9e40-12ab47a7c530</t>
+  </si>
+  <si>
+    <t>Nansana COU PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>Is ebola back in the country like it is in Kenya.</t>
+  </si>
+  <si>
+    <t>More sensitization still needed within the parents</t>
+  </si>
+  <si>
+    <t>5debe6c8-1c58-4f38-a3c3-d90d09a474d5</t>
+  </si>
+  <si>
+    <t>uuid:5debe6c8-1c58-4f38-a3c3-d90d09a474d5</t>
+  </si>
+  <si>
+    <t>Is ebola back in Uganda, could it be the government is covering up due to AFCON</t>
+  </si>
+  <si>
+    <t>Encouraging landlord to put up more hand washing facilities.</t>
+  </si>
+  <si>
+    <t>Holyfarm market is one of the markets that brings together many market vendors to sell their farm products, unfortunately the market had only one hand washing facility and without water nor soap. Some of the people in the market couldn't remember the signs and symptoms of PHE dieases.</t>
+  </si>
+  <si>
+    <t>During the wheel sessions, most of the people in the market started remembering the signs and symptoms, where to report, how to avoid getting the virus and so on. After engagements with the market leadership,, they agreed to add on the number of hand washing facilities in the market.</t>
+  </si>
+  <si>
+    <t>The market leadership agreed to enforce handwashing before anyone enters the market.</t>
+  </si>
+  <si>
+    <t>The change is significant because the market leadership agreed to provide soap and water.</t>
+  </si>
+  <si>
+    <t>b14793c8-9387-4dc0-b581-fb4011c79e55</t>
+  </si>
+  <si>
+    <t>uuid:b14793c8-9387-4dc0-b581-fb4011c79e55</t>
+  </si>
+  <si>
+    <t>Drug Shop / Private Clinic</t>
+  </si>
+  <si>
+    <t>Health Volunteer (VHT/Drug shop operator)</t>
+  </si>
+  <si>
+    <t>Drug shop operater</t>
+  </si>
+  <si>
+    <t>Committed to refer those suspected to have signs of Ebola to the health facility</t>
+  </si>
+  <si>
+    <t>Ebola was a political move</t>
+  </si>
+  <si>
+    <t>Refer all suspected to have ebola to the health facility</t>
+  </si>
+  <si>
+    <t>f8588c08-c720-45e1-bb2e-dd3c6c1f62de</t>
+  </si>
+  <si>
+    <t>uuid:f8588c08-c720-45e1-bb2e-dd3c6c1f62de</t>
+  </si>
+  <si>
+    <t>Area defense</t>
+  </si>
+  <si>
+    <t>Committed to encourage the LC1 council.</t>
+  </si>
+  <si>
+    <t>Ebola can not be got by people who are healthy.</t>
+  </si>
+  <si>
+    <t>Engagement with other local leaders</t>
+  </si>
+  <si>
+    <t>6917f376-b485-4a35-9568-b3af153e20a6</t>
+  </si>
+  <si>
+    <t>uuid:6917f376-b485-4a35-9568-b3af153e20a6</t>
+  </si>
+  <si>
+    <t>de4e526b-3511-4dda-948e-0e1c335acf7b</t>
+  </si>
+  <si>
+    <t>uuid:de4e526b-3511-4dda-948e-0e1c335acf7b</t>
+  </si>
+  <si>
+    <t>They are just false accusations</t>
+  </si>
+  <si>
+    <t>da8d5ff6-a2f5-4d79-9fc1-e60c111e2260</t>
+  </si>
+  <si>
+    <t>uuid:da8d5ff6-a2f5-4d79-9fc1-e60c111e2260</t>
+  </si>
+  <si>
+    <t>Do we have another Ebola outbreak? The country was declared Ebola free</t>
+  </si>
+  <si>
+    <t>Misinformation in the community from unverified sources and myths</t>
+  </si>
+  <si>
+    <t>Use of digital media and influencer online to spread health information</t>
+  </si>
+  <si>
+    <t>The place is maintained well, there is no vector breeding sites</t>
+  </si>
+  <si>
+    <t>The school has moderate space which leads to moderate congestion during peak hours</t>
+  </si>
+  <si>
+    <t>3 boys 4 girls</t>
+  </si>
+  <si>
+    <t>The nurse has ever received the orientation on epidemics</t>
+  </si>
+  <si>
+    <t>c3325b02-8f70-4847-b04e-1304b2d1ca46</t>
+  </si>
+  <si>
+    <t>uuid:c3325b02-8f70-4847-b04e-1304b2d1ca46</t>
+  </si>
+  <si>
+    <t>Gaddafi Secondary School(integrated Academy)</t>
+  </si>
+  <si>
+    <t>How long does it take for a person to die when gets</t>
+  </si>
+  <si>
+    <t>Attitude of some individuals</t>
+  </si>
+  <si>
+    <t>More sensitization should be carried out on using media and at community level like community meetings</t>
+  </si>
+  <si>
+    <t>add0c950-442f-486f-840d-8318f602e16c</t>
+  </si>
+  <si>
+    <t>uuid:add0c950-442f-486f-840d-8318f602e16c</t>
   </si>
 </sst>
 </file>
@@ -21246,7 +21633,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -21596,8 +21983,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY298" totalsRowShown="0">
-  <autoFilter ref="A1:IY298" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY325" totalsRowShown="0">
+  <autoFilter ref="A1:IY325" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -22150,7 +22537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY298"/>
+  <dimension ref="A1:IY325"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -57177,6 +57564,3750 @@
         <v>297</v>
       </c>
     </row>
+    <row r="299" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A299" s="1">
+        <v>46304.549563611108</v>
+      </c>
+      <c r="B299" s="1">
+        <v>46304.552869340281</v>
+      </c>
+      <c r="C299" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D299" t="s">
+        <v>691</v>
+      </c>
+      <c r="E299" t="s">
+        <v>295</v>
+      </c>
+      <c r="F299" t="s">
+        <v>305</v>
+      </c>
+      <c r="G299" t="s">
+        <v>198</v>
+      </c>
+      <c r="H299" t="s">
+        <v>297</v>
+      </c>
+      <c r="J299" t="s">
+        <v>448</v>
+      </c>
+      <c r="K299" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L299" t="s">
+        <v>395</v>
+      </c>
+      <c r="M299" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N299" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O299" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P299" t="s">
+        <v>2050</v>
+      </c>
+      <c r="AH299">
+        <v>714</v>
+      </c>
+      <c r="AI299">
+        <v>12</v>
+      </c>
+      <c r="AJ299">
+        <v>20</v>
+      </c>
+      <c r="AK299">
+        <v>3</v>
+      </c>
+      <c r="AL299">
+        <v>2</v>
+      </c>
+      <c r="AM299">
+        <v>0</v>
+      </c>
+      <c r="AN299">
+        <v>0</v>
+      </c>
+      <c r="AO299" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP299">
+        <v>7</v>
+      </c>
+      <c r="AQ299" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR299" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS299" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT299" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU299" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV299" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW299" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS299" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT299" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU299" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV299" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW299" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX299" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY299" s="1"/>
+      <c r="GQ299" s="1"/>
+      <c r="GR299" s="1"/>
+      <c r="GY299" s="1"/>
+      <c r="GZ299" s="1"/>
+      <c r="HA299" s="1"/>
+      <c r="HB299" s="1"/>
+      <c r="IQ299" s="1">
+        <v>889623302</v>
+      </c>
+      <c r="IR299" t="s">
+        <v>2385</v>
+      </c>
+      <c r="IS299" s="1">
+        <v>46304.427893518521</v>
+      </c>
+      <c r="IU299" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW299" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX299" t="s">
+        <v>2386</v>
+      </c>
+      <c r="IY299">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A300" s="1">
+        <v>46304.552871203698</v>
+      </c>
+      <c r="B300" s="1">
+        <v>46304.555432581023</v>
+      </c>
+      <c r="C300" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D300" t="s">
+        <v>691</v>
+      </c>
+      <c r="E300" t="s">
+        <v>295</v>
+      </c>
+      <c r="F300" t="s">
+        <v>296</v>
+      </c>
+      <c r="G300" t="s">
+        <v>198</v>
+      </c>
+      <c r="H300" t="s">
+        <v>297</v>
+      </c>
+      <c r="J300" t="s">
+        <v>666</v>
+      </c>
+      <c r="K300" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L300" t="s">
+        <v>395</v>
+      </c>
+      <c r="M300" t="s">
+        <v>612</v>
+      </c>
+      <c r="N300" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O300" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R300">
+        <v>15</v>
+      </c>
+      <c r="S300">
+        <v>15</v>
+      </c>
+      <c r="T300" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U300" t="s">
+        <v>2387</v>
+      </c>
+      <c r="V300">
+        <v>1</v>
+      </c>
+      <c r="W300">
+        <v>0</v>
+      </c>
+      <c r="X300">
+        <v>1</v>
+      </c>
+      <c r="Y300">
+        <v>0</v>
+      </c>
+      <c r="Z300">
+        <v>1</v>
+      </c>
+      <c r="AA300">
+        <v>0</v>
+      </c>
+      <c r="AB300" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC300">
+        <v>1</v>
+      </c>
+      <c r="AD300">
+        <v>1</v>
+      </c>
+      <c r="AE300">
+        <v>0</v>
+      </c>
+      <c r="AF300">
+        <v>0</v>
+      </c>
+      <c r="AG300">
+        <v>0</v>
+      </c>
+      <c r="AH300">
+        <v>1260</v>
+      </c>
+      <c r="AI300">
+        <v>611</v>
+      </c>
+      <c r="AJ300">
+        <v>619</v>
+      </c>
+      <c r="AK300">
+        <v>8</v>
+      </c>
+      <c r="AL300">
+        <v>2</v>
+      </c>
+      <c r="AM300">
+        <v>0</v>
+      </c>
+      <c r="AN300">
+        <v>0</v>
+      </c>
+      <c r="AO300" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP300">
+        <v>5</v>
+      </c>
+      <c r="AQ300" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR300" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS300" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT300" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU300" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV300" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW300" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS300" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT300" t="s">
+        <v>576</v>
+      </c>
+      <c r="BU300" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV300" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW300" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX300" t="s">
+        <v>2388</v>
+      </c>
+      <c r="EY300" s="1"/>
+      <c r="GQ300" s="1"/>
+      <c r="GR300" s="1"/>
+      <c r="GY300" s="1"/>
+      <c r="GZ300" s="1"/>
+      <c r="HA300" s="1"/>
+      <c r="HB300" s="1"/>
+      <c r="IQ300" s="1">
+        <v>889625912</v>
+      </c>
+      <c r="IR300" t="s">
+        <v>2389</v>
+      </c>
+      <c r="IS300" s="1">
+        <v>46304.430439814823</v>
+      </c>
+      <c r="IU300" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW300" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX300" t="s">
+        <v>2390</v>
+      </c>
+      <c r="IY300">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A301" s="1">
+        <v>46304.55543482639</v>
+      </c>
+      <c r="B301" s="1">
+        <v>46304.558060381947</v>
+      </c>
+      <c r="C301" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D301" t="s">
+        <v>691</v>
+      </c>
+      <c r="E301" t="s">
+        <v>295</v>
+      </c>
+      <c r="F301" t="s">
+        <v>296</v>
+      </c>
+      <c r="G301" t="s">
+        <v>198</v>
+      </c>
+      <c r="H301" t="s">
+        <v>297</v>
+      </c>
+      <c r="J301" t="s">
+        <v>298</v>
+      </c>
+      <c r="K301" t="s">
+        <v>201</v>
+      </c>
+      <c r="L301" t="s">
+        <v>324</v>
+      </c>
+      <c r="M301" t="s">
+        <v>612</v>
+      </c>
+      <c r="N301" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O301" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P301" t="s">
+        <v>2050</v>
+      </c>
+      <c r="AH301">
+        <v>736</v>
+      </c>
+      <c r="AI301">
+        <v>396</v>
+      </c>
+      <c r="AJ301">
+        <v>388</v>
+      </c>
+      <c r="AK301">
+        <v>8</v>
+      </c>
+      <c r="AL301">
+        <v>2</v>
+      </c>
+      <c r="AM301">
+        <v>0</v>
+      </c>
+      <c r="AN301">
+        <v>8</v>
+      </c>
+      <c r="AO301" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP301">
+        <v>3</v>
+      </c>
+      <c r="AQ301" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR301" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS301" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT301" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU301" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV301" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW301" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS301" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT301" t="s">
+        <v>613</v>
+      </c>
+      <c r="BU301" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV301" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW301" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX301" t="s">
+        <v>2391</v>
+      </c>
+      <c r="EY301" s="1"/>
+      <c r="GQ301" s="1"/>
+      <c r="GR301" s="1"/>
+      <c r="GY301" s="1"/>
+      <c r="GZ301" s="1"/>
+      <c r="HA301" s="1"/>
+      <c r="HB301" s="1"/>
+      <c r="IQ301" s="1">
+        <v>889628800</v>
+      </c>
+      <c r="IR301" t="s">
+        <v>2392</v>
+      </c>
+      <c r="IS301" s="1">
+        <v>46304.433067129627</v>
+      </c>
+      <c r="IU301" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW301" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX301" t="s">
+        <v>2393</v>
+      </c>
+      <c r="IY301">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A302" s="1">
+        <v>46304.558062291668</v>
+      </c>
+      <c r="B302" s="1">
+        <v>46304.560550821763</v>
+      </c>
+      <c r="C302" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D302" t="s">
+        <v>691</v>
+      </c>
+      <c r="E302" t="s">
+        <v>295</v>
+      </c>
+      <c r="F302" t="s">
+        <v>296</v>
+      </c>
+      <c r="G302" t="s">
+        <v>198</v>
+      </c>
+      <c r="H302" t="s">
+        <v>297</v>
+      </c>
+      <c r="J302" t="s">
+        <v>298</v>
+      </c>
+      <c r="K302" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L302" t="s">
+        <v>395</v>
+      </c>
+      <c r="M302" t="s">
+        <v>612</v>
+      </c>
+      <c r="N302" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O302" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R302">
+        <v>15</v>
+      </c>
+      <c r="S302">
+        <v>15</v>
+      </c>
+      <c r="T302" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U302" t="s">
+        <v>2387</v>
+      </c>
+      <c r="V302">
+        <v>1</v>
+      </c>
+      <c r="W302">
+        <v>0</v>
+      </c>
+      <c r="X302">
+        <v>1</v>
+      </c>
+      <c r="Y302">
+        <v>0</v>
+      </c>
+      <c r="Z302">
+        <v>1</v>
+      </c>
+      <c r="AA302">
+        <v>0</v>
+      </c>
+      <c r="AB302" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC302">
+        <v>1</v>
+      </c>
+      <c r="AD302">
+        <v>1</v>
+      </c>
+      <c r="AE302">
+        <v>0</v>
+      </c>
+      <c r="AF302">
+        <v>0</v>
+      </c>
+      <c r="AG302">
+        <v>0</v>
+      </c>
+      <c r="AH302">
+        <v>736</v>
+      </c>
+      <c r="AI302">
+        <v>396</v>
+      </c>
+      <c r="AJ302">
+        <v>388</v>
+      </c>
+      <c r="AK302">
+        <v>3</v>
+      </c>
+      <c r="AL302">
+        <v>2</v>
+      </c>
+      <c r="AM302">
+        <v>0</v>
+      </c>
+      <c r="AN302">
+        <v>0</v>
+      </c>
+      <c r="AO302" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP302">
+        <v>5</v>
+      </c>
+      <c r="AQ302" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR302" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS302" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT302" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU302" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV302" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW302" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS302" t="s">
+        <v>2394</v>
+      </c>
+      <c r="BT302" t="s">
+        <v>2395</v>
+      </c>
+      <c r="BU302" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV302" t="s">
+        <v>2396</v>
+      </c>
+      <c r="BW302" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX302" t="s">
+        <v>2397</v>
+      </c>
+      <c r="EY302" s="1"/>
+      <c r="GQ302" s="1"/>
+      <c r="GR302" s="1"/>
+      <c r="GY302" s="1"/>
+      <c r="GZ302" s="1"/>
+      <c r="HA302" s="1"/>
+      <c r="HB302" s="1"/>
+      <c r="IQ302" s="1">
+        <v>889631612</v>
+      </c>
+      <c r="IR302" t="s">
+        <v>2398</v>
+      </c>
+      <c r="IS302" s="1">
+        <v>46304.435555555552</v>
+      </c>
+      <c r="IU302" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW302" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX302" t="s">
+        <v>2399</v>
+      </c>
+      <c r="IY302">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A303" s="1">
+        <v>46304.560552812502</v>
+      </c>
+      <c r="B303" s="1">
+        <v>46304.566008148147</v>
+      </c>
+      <c r="C303" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D303" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E303" t="s">
+        <v>295</v>
+      </c>
+      <c r="F303" t="s">
+        <v>296</v>
+      </c>
+      <c r="G303" t="s">
+        <v>198</v>
+      </c>
+      <c r="H303" t="s">
+        <v>297</v>
+      </c>
+      <c r="BS303" t="s">
+        <v>2400</v>
+      </c>
+      <c r="BT303" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU303" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV303" t="s">
+        <v>224</v>
+      </c>
+      <c r="BW303" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX303" t="s">
+        <v>612</v>
+      </c>
+      <c r="BY303" t="s">
+        <v>809</v>
+      </c>
+      <c r="BZ303" t="s">
+        <v>2401</v>
+      </c>
+      <c r="EK303" t="s">
+        <v>2402</v>
+      </c>
+      <c r="EL303" t="s">
+        <v>2403</v>
+      </c>
+      <c r="EM303" t="s">
+        <v>2404</v>
+      </c>
+      <c r="EN303" t="s">
+        <v>2405</v>
+      </c>
+      <c r="EY303" s="1"/>
+      <c r="GQ303" s="1"/>
+      <c r="GR303" s="1"/>
+      <c r="GY303" s="1"/>
+      <c r="GZ303" s="1"/>
+      <c r="HA303" s="1"/>
+      <c r="HB303" s="1"/>
+      <c r="IQ303" s="1">
+        <v>889638145</v>
+      </c>
+      <c r="IR303" t="s">
+        <v>2406</v>
+      </c>
+      <c r="IS303" s="1">
+        <v>46304.441018518519</v>
+      </c>
+      <c r="IU303" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW303" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX303" t="s">
+        <v>2407</v>
+      </c>
+      <c r="IY303">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A304" s="1">
+        <v>46304.56600979167</v>
+      </c>
+      <c r="B304" s="1">
+        <v>46304.56854670139</v>
+      </c>
+      <c r="C304" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D304" t="s">
+        <v>691</v>
+      </c>
+      <c r="E304" t="s">
+        <v>295</v>
+      </c>
+      <c r="F304" t="s">
+        <v>338</v>
+      </c>
+      <c r="G304" t="s">
+        <v>249</v>
+      </c>
+      <c r="J304" t="s">
+        <v>2408</v>
+      </c>
+      <c r="K304" t="s">
+        <v>201</v>
+      </c>
+      <c r="L304" t="s">
+        <v>324</v>
+      </c>
+      <c r="M304" t="s">
+        <v>612</v>
+      </c>
+      <c r="N304" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O304" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P304" t="s">
+        <v>2409</v>
+      </c>
+      <c r="AH304">
+        <v>1455</v>
+      </c>
+      <c r="AI304">
+        <v>723</v>
+      </c>
+      <c r="AJ304">
+        <v>732</v>
+      </c>
+      <c r="AK304">
+        <v>8</v>
+      </c>
+      <c r="AL304">
+        <v>2</v>
+      </c>
+      <c r="AM304">
+        <v>0</v>
+      </c>
+      <c r="AN304">
+        <v>0</v>
+      </c>
+      <c r="AO304" t="s">
+        <v>1675</v>
+      </c>
+      <c r="AP304">
+        <v>2</v>
+      </c>
+      <c r="AQ304" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR304" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS304" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT304" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU304" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV304" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW304" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS304" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT304" t="s">
+        <v>613</v>
+      </c>
+      <c r="BU304" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV304" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW304" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX304" t="s">
+        <v>2410</v>
+      </c>
+      <c r="EY304" s="1"/>
+      <c r="GQ304" s="1"/>
+      <c r="GR304" s="1"/>
+      <c r="GY304" s="1"/>
+      <c r="GZ304" s="1"/>
+      <c r="HA304" s="1"/>
+      <c r="HB304" s="1"/>
+      <c r="IQ304" s="1">
+        <v>889641313</v>
+      </c>
+      <c r="IR304" t="s">
+        <v>2411</v>
+      </c>
+      <c r="IS304" s="1">
+        <v>46304.443553240737</v>
+      </c>
+      <c r="IU304" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW304" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX304" t="s">
+        <v>2412</v>
+      </c>
+      <c r="IY304">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A305" s="1">
+        <v>46304.568548668984</v>
+      </c>
+      <c r="B305" s="1">
+        <v>46304.572297719897</v>
+      </c>
+      <c r="C305" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D305" t="s">
+        <v>691</v>
+      </c>
+      <c r="E305" t="s">
+        <v>295</v>
+      </c>
+      <c r="F305" t="s">
+        <v>338</v>
+      </c>
+      <c r="G305" t="s">
+        <v>198</v>
+      </c>
+      <c r="H305" t="s">
+        <v>297</v>
+      </c>
+      <c r="J305" t="s">
+        <v>2408</v>
+      </c>
+      <c r="K305" t="s">
+        <v>201</v>
+      </c>
+      <c r="L305" t="s">
+        <v>395</v>
+      </c>
+      <c r="M305" t="s">
+        <v>612</v>
+      </c>
+      <c r="N305" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O305" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R305">
+        <v>15</v>
+      </c>
+      <c r="S305">
+        <v>15</v>
+      </c>
+      <c r="T305" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U305" t="s">
+        <v>2281</v>
+      </c>
+      <c r="V305">
+        <v>0</v>
+      </c>
+      <c r="W305">
+        <v>0</v>
+      </c>
+      <c r="X305">
+        <v>1</v>
+      </c>
+      <c r="Y305">
+        <v>0</v>
+      </c>
+      <c r="Z305">
+        <v>1</v>
+      </c>
+      <c r="AA305">
+        <v>0</v>
+      </c>
+      <c r="AB305" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC305">
+        <v>1</v>
+      </c>
+      <c r="AD305">
+        <v>1</v>
+      </c>
+      <c r="AE305">
+        <v>0</v>
+      </c>
+      <c r="AF305">
+        <v>0</v>
+      </c>
+      <c r="AG305">
+        <v>0</v>
+      </c>
+      <c r="AH305">
+        <v>1455</v>
+      </c>
+      <c r="AI305">
+        <v>723</v>
+      </c>
+      <c r="AJ305">
+        <v>732</v>
+      </c>
+      <c r="AK305">
+        <v>85</v>
+      </c>
+      <c r="AL305">
+        <v>2</v>
+      </c>
+      <c r="AM305">
+        <v>0</v>
+      </c>
+      <c r="AN305">
+        <v>0</v>
+      </c>
+      <c r="AO305" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP305">
+        <v>8</v>
+      </c>
+      <c r="AQ305" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR305" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS305" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT305" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU305" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV305" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW305" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS305" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT305" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU305" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV305" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW305" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX305" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY305" s="1"/>
+      <c r="GQ305" s="1"/>
+      <c r="GR305" s="1"/>
+      <c r="GY305" s="1"/>
+      <c r="GZ305" s="1"/>
+      <c r="HA305" s="1"/>
+      <c r="HB305" s="1"/>
+      <c r="IQ305" s="1">
+        <v>889646290</v>
+      </c>
+      <c r="IR305" t="s">
+        <v>2413</v>
+      </c>
+      <c r="IS305" s="1">
+        <v>46304.447442129633</v>
+      </c>
+      <c r="IU305" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW305" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX305" t="s">
+        <v>2414</v>
+      </c>
+      <c r="IY305">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A306" s="1">
+        <v>46304.572299814812</v>
+      </c>
+      <c r="B306" s="1">
+        <v>46304.577531678238</v>
+      </c>
+      <c r="C306" s="1">
+        <v>46290</v>
+      </c>
+      <c r="D306" t="s">
+        <v>691</v>
+      </c>
+      <c r="E306" t="s">
+        <v>295</v>
+      </c>
+      <c r="F306" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G306" t="s">
+        <v>198</v>
+      </c>
+      <c r="H306" t="s">
+        <v>297</v>
+      </c>
+      <c r="J306" t="s">
+        <v>1607</v>
+      </c>
+      <c r="K306" t="s">
+        <v>201</v>
+      </c>
+      <c r="L306" t="s">
+        <v>324</v>
+      </c>
+      <c r="M306" t="s">
+        <v>612</v>
+      </c>
+      <c r="N306" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O306" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R306">
+        <v>15</v>
+      </c>
+      <c r="S306">
+        <v>15</v>
+      </c>
+      <c r="T306" t="s">
+        <v>1815</v>
+      </c>
+      <c r="U306" t="s">
+        <v>2305</v>
+      </c>
+      <c r="V306">
+        <v>0</v>
+      </c>
+      <c r="W306">
+        <v>1</v>
+      </c>
+      <c r="X306">
+        <v>0</v>
+      </c>
+      <c r="Y306">
+        <v>0</v>
+      </c>
+      <c r="Z306">
+        <v>1</v>
+      </c>
+      <c r="AA306">
+        <v>0</v>
+      </c>
+      <c r="AB306" t="s">
+        <v>2236</v>
+      </c>
+      <c r="AC306">
+        <v>0</v>
+      </c>
+      <c r="AD306">
+        <v>1</v>
+      </c>
+      <c r="AE306">
+        <v>0</v>
+      </c>
+      <c r="AF306">
+        <v>0</v>
+      </c>
+      <c r="AG306">
+        <v>0</v>
+      </c>
+      <c r="AH306">
+        <v>762</v>
+      </c>
+      <c r="AI306">
+        <v>368</v>
+      </c>
+      <c r="AJ306">
+        <v>394</v>
+      </c>
+      <c r="AK306">
+        <v>5</v>
+      </c>
+      <c r="AL306">
+        <v>2</v>
+      </c>
+      <c r="AM306">
+        <v>0</v>
+      </c>
+      <c r="AN306">
+        <v>0</v>
+      </c>
+      <c r="AO306" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP306">
+        <v>4</v>
+      </c>
+      <c r="AQ306" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR306" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS306" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT306" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU306" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV306" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW306" t="s">
+        <v>205</v>
+      </c>
+      <c r="BS306" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT306" t="s">
+        <v>576</v>
+      </c>
+      <c r="BU306" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV306" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW306" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX306" t="s">
+        <v>2388</v>
+      </c>
+      <c r="EY306" s="1"/>
+      <c r="GQ306" s="1"/>
+      <c r="GR306" s="1"/>
+      <c r="GY306" s="1"/>
+      <c r="GZ306" s="1"/>
+      <c r="HA306" s="1"/>
+      <c r="HB306" s="1"/>
+      <c r="IQ306" s="1">
+        <v>889653515</v>
+      </c>
+      <c r="IR306" t="s">
+        <v>2415</v>
+      </c>
+      <c r="IS306" s="1">
+        <v>46304.452546296299</v>
+      </c>
+      <c r="IU306" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW306" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX306" t="s">
+        <v>2416</v>
+      </c>
+      <c r="IY306">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A307" s="1">
+        <v>46304.577533622687</v>
+      </c>
+      <c r="B307" s="1">
+        <v>46304.579429675927</v>
+      </c>
+      <c r="C307" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D307" t="s">
+        <v>691</v>
+      </c>
+      <c r="E307" t="s">
+        <v>295</v>
+      </c>
+      <c r="F307" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G307" t="s">
+        <v>198</v>
+      </c>
+      <c r="H307" t="s">
+        <v>297</v>
+      </c>
+      <c r="J307" t="s">
+        <v>1607</v>
+      </c>
+      <c r="K307" t="s">
+        <v>201</v>
+      </c>
+      <c r="L307" t="s">
+        <v>395</v>
+      </c>
+      <c r="M307" t="s">
+        <v>612</v>
+      </c>
+      <c r="N307" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O307" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R307">
+        <v>15</v>
+      </c>
+      <c r="S307">
+        <v>15</v>
+      </c>
+      <c r="T307" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U307" t="s">
+        <v>2387</v>
+      </c>
+      <c r="V307">
+        <v>1</v>
+      </c>
+      <c r="W307">
+        <v>0</v>
+      </c>
+      <c r="X307">
+        <v>1</v>
+      </c>
+      <c r="Y307">
+        <v>0</v>
+      </c>
+      <c r="Z307">
+        <v>1</v>
+      </c>
+      <c r="AA307">
+        <v>0</v>
+      </c>
+      <c r="AB307" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC307">
+        <v>1</v>
+      </c>
+      <c r="AD307">
+        <v>1</v>
+      </c>
+      <c r="AE307">
+        <v>0</v>
+      </c>
+      <c r="AF307">
+        <v>0</v>
+      </c>
+      <c r="AG307">
+        <v>0</v>
+      </c>
+      <c r="AH307">
+        <v>762</v>
+      </c>
+      <c r="AI307">
+        <v>368</v>
+      </c>
+      <c r="AJ307">
+        <v>394</v>
+      </c>
+      <c r="AK307">
+        <v>5</v>
+      </c>
+      <c r="AL307">
+        <v>2</v>
+      </c>
+      <c r="AM307">
+        <v>0</v>
+      </c>
+      <c r="AN307">
+        <v>0</v>
+      </c>
+      <c r="AO307" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP307">
+        <v>7</v>
+      </c>
+      <c r="AQ307" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR307" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS307" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT307" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU307" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV307" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW307" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS307" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT307" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU307" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV307" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW307" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX307" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY307" s="1"/>
+      <c r="GQ307" s="1"/>
+      <c r="GR307" s="1"/>
+      <c r="GY307" s="1"/>
+      <c r="GZ307" s="1"/>
+      <c r="HA307" s="1"/>
+      <c r="HB307" s="1"/>
+      <c r="IQ307" s="1">
+        <v>889656381</v>
+      </c>
+      <c r="IR307" t="s">
+        <v>2417</v>
+      </c>
+      <c r="IS307" s="1">
+        <v>46304.454432870371</v>
+      </c>
+      <c r="IU307" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW307" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX307" t="s">
+        <v>2418</v>
+      </c>
+      <c r="IY307">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A308" s="1">
+        <v>46304.57943135417</v>
+      </c>
+      <c r="B308" s="1">
+        <v>46304.592506712957</v>
+      </c>
+      <c r="C308" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D308" t="s">
+        <v>690</v>
+      </c>
+      <c r="E308" t="s">
+        <v>210</v>
+      </c>
+      <c r="F308" t="s">
+        <v>296</v>
+      </c>
+      <c r="G308" t="s">
+        <v>198</v>
+      </c>
+      <c r="H308" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX308" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY308" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ308" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA308" t="s">
+        <v>635</v>
+      </c>
+      <c r="BB308">
+        <v>200</v>
+      </c>
+      <c r="BC308">
+        <v>300</v>
+      </c>
+      <c r="BD308" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE308" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF308" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG308" t="s">
+        <v>2419</v>
+      </c>
+      <c r="BH308" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI308" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ308" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK308">
+        <v>5</v>
+      </c>
+      <c r="BL308" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM308">
+        <v>50</v>
+      </c>
+      <c r="BN308">
+        <v>50</v>
+      </c>
+      <c r="BO308" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP308" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ308" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS308" t="s">
+        <v>2420</v>
+      </c>
+      <c r="BT308" t="s">
+        <v>2421</v>
+      </c>
+      <c r="BU308" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV308" t="s">
+        <v>1010</v>
+      </c>
+      <c r="BW308" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX308" t="s">
+        <v>2422</v>
+      </c>
+      <c r="EY308" s="1"/>
+      <c r="GQ308" s="1"/>
+      <c r="GR308" s="1"/>
+      <c r="GY308" s="1"/>
+      <c r="GZ308" s="1"/>
+      <c r="HA308" s="1"/>
+      <c r="HB308" s="1"/>
+      <c r="IQ308" s="1">
+        <v>889673768</v>
+      </c>
+      <c r="IR308" t="s">
+        <v>2423</v>
+      </c>
+      <c r="IS308" s="1">
+        <v>46304.467534722222</v>
+      </c>
+      <c r="IU308" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW308" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX308" t="s">
+        <v>2424</v>
+      </c>
+      <c r="IY308">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A309" s="1">
+        <v>46304.592508761583</v>
+      </c>
+      <c r="B309" s="1">
+        <v>46304.594359201386</v>
+      </c>
+      <c r="C309" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D309" t="s">
+        <v>690</v>
+      </c>
+      <c r="E309" t="s">
+        <v>295</v>
+      </c>
+      <c r="F309" t="s">
+        <v>296</v>
+      </c>
+      <c r="G309" t="s">
+        <v>198</v>
+      </c>
+      <c r="H309" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX309" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY309" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ309" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA309" t="s">
+        <v>1596</v>
+      </c>
+      <c r="BB309">
+        <v>30</v>
+      </c>
+      <c r="BC309">
+        <v>5</v>
+      </c>
+      <c r="BD309" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE309" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF309" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG309" t="s">
+        <v>2425</v>
+      </c>
+      <c r="BH309" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI309" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ309" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK309">
+        <v>8</v>
+      </c>
+      <c r="BL309" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM309">
+        <v>18</v>
+      </c>
+      <c r="BN309">
+        <v>10</v>
+      </c>
+      <c r="BO309" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP309" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ309" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS309" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT309" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU309" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV309" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW309" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX309" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY309" s="1"/>
+      <c r="GQ309" s="1"/>
+      <c r="GR309" s="1"/>
+      <c r="GY309" s="1"/>
+      <c r="GZ309" s="1"/>
+      <c r="HA309" s="1"/>
+      <c r="HB309" s="1"/>
+      <c r="IQ309" s="1">
+        <v>889675823</v>
+      </c>
+      <c r="IR309" t="s">
+        <v>2426</v>
+      </c>
+      <c r="IS309" s="1">
+        <v>46304.469375000001</v>
+      </c>
+      <c r="IU309" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW309" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX309" t="s">
+        <v>2427</v>
+      </c>
+      <c r="IY309">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A310" s="1">
+        <v>46304.594360937503</v>
+      </c>
+      <c r="B310" s="1">
+        <v>46304.596570532412</v>
+      </c>
+      <c r="C310" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D310" t="s">
+        <v>690</v>
+      </c>
+      <c r="E310" t="s">
+        <v>295</v>
+      </c>
+      <c r="F310" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G310" t="s">
+        <v>198</v>
+      </c>
+      <c r="H310" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX310" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY310" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ310" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA310" t="s">
+        <v>2428</v>
+      </c>
+      <c r="BB310">
+        <v>1</v>
+      </c>
+      <c r="BC310">
+        <v>1</v>
+      </c>
+      <c r="BD310" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE310" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF310" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG310" t="s">
+        <v>2429</v>
+      </c>
+      <c r="BH310" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI310" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ310" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK310">
+        <v>5</v>
+      </c>
+      <c r="BL310" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM310">
+        <v>28</v>
+      </c>
+      <c r="BN310">
+        <v>5</v>
+      </c>
+      <c r="BO310" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP310" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ310" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS310" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT310" t="s">
+        <v>2421</v>
+      </c>
+      <c r="BU310" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV310" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW310" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX310" t="s">
+        <v>2422</v>
+      </c>
+      <c r="EY310" s="1"/>
+      <c r="GQ310" s="1"/>
+      <c r="GR310" s="1"/>
+      <c r="GY310" s="1"/>
+      <c r="GZ310" s="1"/>
+      <c r="HA310" s="1"/>
+      <c r="HB310" s="1"/>
+      <c r="IQ310" s="1">
+        <v>889678335</v>
+      </c>
+      <c r="IR310" t="s">
+        <v>2430</v>
+      </c>
+      <c r="IS310" s="1">
+        <v>46304.471574074072</v>
+      </c>
+      <c r="IU310" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW310" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX310" t="s">
+        <v>2431</v>
+      </c>
+      <c r="IY310">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A311" s="1">
+        <v>46304.596572002323</v>
+      </c>
+      <c r="B311" s="1">
+        <v>46304.597966215268</v>
+      </c>
+      <c r="C311" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D311" t="s">
+        <v>690</v>
+      </c>
+      <c r="E311" t="s">
+        <v>295</v>
+      </c>
+      <c r="F311" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G311" t="s">
+        <v>249</v>
+      </c>
+      <c r="AX311" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY311" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ311" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA311" t="s">
+        <v>2432</v>
+      </c>
+      <c r="BB311">
+        <v>3</v>
+      </c>
+      <c r="BC311">
+        <v>0</v>
+      </c>
+      <c r="BD311" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE311" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF311" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG311" t="s">
+        <v>2433</v>
+      </c>
+      <c r="BH311" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI311" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ311" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK311">
+        <v>5</v>
+      </c>
+      <c r="BL311" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM311">
+        <v>10</v>
+      </c>
+      <c r="BN311">
+        <v>25</v>
+      </c>
+      <c r="BO311" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP311" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ311" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BS311" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT311" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU311" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV311" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW311" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX311" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY311" s="1"/>
+      <c r="GQ311" s="1"/>
+      <c r="GR311" s="1"/>
+      <c r="GY311" s="1"/>
+      <c r="GZ311" s="1"/>
+      <c r="HA311" s="1"/>
+      <c r="HB311" s="1"/>
+      <c r="IQ311" s="1">
+        <v>889680018</v>
+      </c>
+      <c r="IR311" t="s">
+        <v>2434</v>
+      </c>
+      <c r="IS311" s="1">
+        <v>46304.472974537042</v>
+      </c>
+      <c r="IU311" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW311" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX311" t="s">
+        <v>2435</v>
+      </c>
+      <c r="IY311">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A312" s="1">
+        <v>46304.597967986112</v>
+      </c>
+      <c r="B312" s="1">
+        <v>46304.623653333343</v>
+      </c>
+      <c r="C312" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D312" t="s">
+        <v>690</v>
+      </c>
+      <c r="E312" t="s">
+        <v>295</v>
+      </c>
+      <c r="F312" t="s">
+        <v>338</v>
+      </c>
+      <c r="G312" t="s">
+        <v>198</v>
+      </c>
+      <c r="H312" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX312" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY312" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ312" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA312" t="s">
+        <v>2436</v>
+      </c>
+      <c r="BB312">
+        <v>2</v>
+      </c>
+      <c r="BC312">
+        <v>1</v>
+      </c>
+      <c r="BD312" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE312" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF312" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG312" t="s">
+        <v>2437</v>
+      </c>
+      <c r="BH312" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI312" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ312" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK312">
+        <v>5</v>
+      </c>
+      <c r="BL312" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM312">
+        <v>35</v>
+      </c>
+      <c r="BN312">
+        <v>15</v>
+      </c>
+      <c r="BO312" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP312" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ312" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS312" t="s">
+        <v>2438</v>
+      </c>
+      <c r="BT312" t="s">
+        <v>576</v>
+      </c>
+      <c r="BU312" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV312" t="s">
+        <v>1010</v>
+      </c>
+      <c r="BW312" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX312" t="s">
+        <v>2439</v>
+      </c>
+      <c r="EY312" s="1"/>
+      <c r="GQ312" s="1"/>
+      <c r="GR312" s="1"/>
+      <c r="GY312" s="1"/>
+      <c r="GZ312" s="1"/>
+      <c r="HA312" s="1"/>
+      <c r="HB312" s="1"/>
+      <c r="IQ312" s="1">
+        <v>889710892</v>
+      </c>
+      <c r="IR312" t="s">
+        <v>2440</v>
+      </c>
+      <c r="IS312" s="1">
+        <v>46304.498680555553</v>
+      </c>
+      <c r="IU312" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW312" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX312" t="s">
+        <v>2441</v>
+      </c>
+      <c r="IY312">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A313" s="1">
+        <v>46304.623656099538</v>
+      </c>
+      <c r="B313" s="1">
+        <v>46304.625299756954</v>
+      </c>
+      <c r="C313" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D313" t="s">
+        <v>690</v>
+      </c>
+      <c r="E313" t="s">
+        <v>295</v>
+      </c>
+      <c r="F313" t="s">
+        <v>338</v>
+      </c>
+      <c r="G313" t="s">
+        <v>198</v>
+      </c>
+      <c r="H313" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX313" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY313" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ313" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA313" t="s">
+        <v>2442</v>
+      </c>
+      <c r="BB313">
+        <v>1</v>
+      </c>
+      <c r="BC313">
+        <v>0</v>
+      </c>
+      <c r="BD313" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE313" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF313" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG313" t="s">
+        <v>2443</v>
+      </c>
+      <c r="BH313" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI313" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ313" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK313">
+        <v>5</v>
+      </c>
+      <c r="BL313" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM313">
+        <v>10</v>
+      </c>
+      <c r="BN313">
+        <v>15</v>
+      </c>
+      <c r="BO313" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP313" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ313" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS313" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT313" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU313" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV313" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW313" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX313" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY313" s="1"/>
+      <c r="GQ313" s="1"/>
+      <c r="GR313" s="1"/>
+      <c r="GY313" s="1"/>
+      <c r="GZ313" s="1"/>
+      <c r="HA313" s="1"/>
+      <c r="HB313" s="1"/>
+      <c r="IQ313" s="1">
+        <v>889712939</v>
+      </c>
+      <c r="IR313" t="s">
+        <v>2444</v>
+      </c>
+      <c r="IS313" s="1">
+        <v>46304.500324074077</v>
+      </c>
+      <c r="IU313" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW313" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX313" t="s">
+        <v>2445</v>
+      </c>
+      <c r="IY313">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A314" s="1">
+        <v>46304.625301782413</v>
+      </c>
+      <c r="B314" s="1">
+        <v>46304.627621064807</v>
+      </c>
+      <c r="C314" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D314" t="s">
+        <v>690</v>
+      </c>
+      <c r="E314" t="s">
+        <v>295</v>
+      </c>
+      <c r="F314" t="s">
+        <v>305</v>
+      </c>
+      <c r="G314" t="s">
+        <v>198</v>
+      </c>
+      <c r="H314" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX314" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY314" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ314" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA314" t="s">
+        <v>2442</v>
+      </c>
+      <c r="BB314">
+        <v>2</v>
+      </c>
+      <c r="BC314">
+        <v>1</v>
+      </c>
+      <c r="BD314" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE314" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF314" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG314" t="s">
+        <v>2446</v>
+      </c>
+      <c r="BH314" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI314" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ314" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK314">
+        <v>7</v>
+      </c>
+      <c r="BL314" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM314">
+        <v>10</v>
+      </c>
+      <c r="BN314">
+        <v>5</v>
+      </c>
+      <c r="BO314" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP314" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ314" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS314" t="s">
+        <v>2447</v>
+      </c>
+      <c r="BT314" t="s">
+        <v>2421</v>
+      </c>
+      <c r="BU314" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV314" t="s">
+        <v>2448</v>
+      </c>
+      <c r="BW314" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX314" t="s">
+        <v>2449</v>
+      </c>
+      <c r="EY314" s="1"/>
+      <c r="GQ314" s="1"/>
+      <c r="GR314" s="1"/>
+      <c r="GY314" s="1"/>
+      <c r="GZ314" s="1"/>
+      <c r="HA314" s="1"/>
+      <c r="HB314" s="1"/>
+      <c r="IQ314" s="1">
+        <v>889715539</v>
+      </c>
+      <c r="IR314" t="s">
+        <v>2450</v>
+      </c>
+      <c r="IS314" s="1">
+        <v>46304.502627314818</v>
+      </c>
+      <c r="IU314" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW314" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX314" t="s">
+        <v>2451</v>
+      </c>
+      <c r="IY314">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A315" s="1">
+        <v>46304.627622789347</v>
+      </c>
+      <c r="B315" s="1">
+        <v>46304.629609826392</v>
+      </c>
+      <c r="C315" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D315" t="s">
+        <v>690</v>
+      </c>
+      <c r="E315" t="s">
+        <v>295</v>
+      </c>
+      <c r="F315" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G315" t="s">
+        <v>198</v>
+      </c>
+      <c r="H315" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX315" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY315" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ315" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA315" t="s">
+        <v>2442</v>
+      </c>
+      <c r="BB315">
+        <v>9</v>
+      </c>
+      <c r="BC315">
+        <v>1</v>
+      </c>
+      <c r="BD315" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE315" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF315" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG315" t="s">
+        <v>2452</v>
+      </c>
+      <c r="BH315" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI315" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ315" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK315">
+        <v>5</v>
+      </c>
+      <c r="BL315" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM315">
+        <v>10</v>
+      </c>
+      <c r="BN315">
+        <v>20</v>
+      </c>
+      <c r="BO315" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP315" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ315" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS315" t="s">
+        <v>2453</v>
+      </c>
+      <c r="BT315" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU315" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV315" t="s">
+        <v>1596</v>
+      </c>
+      <c r="BW315" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX315" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY315" s="1"/>
+      <c r="GQ315" s="1"/>
+      <c r="GR315" s="1"/>
+      <c r="GY315" s="1"/>
+      <c r="GZ315" s="1"/>
+      <c r="HA315" s="1"/>
+      <c r="HB315" s="1"/>
+      <c r="IQ315" s="1">
+        <v>889717941</v>
+      </c>
+      <c r="IR315" t="s">
+        <v>2454</v>
+      </c>
+      <c r="IS315" s="1">
+        <v>46304.504618055558</v>
+      </c>
+      <c r="IU315" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW315" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX315" t="s">
+        <v>2455</v>
+      </c>
+      <c r="IY315">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A316" s="1">
+        <v>46304.629611412027</v>
+      </c>
+      <c r="B316" s="1">
+        <v>46304.632132604173</v>
+      </c>
+      <c r="C316" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D316" t="s">
+        <v>690</v>
+      </c>
+      <c r="E316" t="s">
+        <v>295</v>
+      </c>
+      <c r="F316" t="s">
+        <v>296</v>
+      </c>
+      <c r="G316" t="s">
+        <v>198</v>
+      </c>
+      <c r="H316" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX316" t="s">
+        <v>2299</v>
+      </c>
+      <c r="AY316" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ316" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA316" t="s">
+        <v>2456</v>
+      </c>
+      <c r="BB316">
+        <v>0</v>
+      </c>
+      <c r="BC316">
+        <v>2</v>
+      </c>
+      <c r="BD316" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE316" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF316" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG316" t="s">
+        <v>2457</v>
+      </c>
+      <c r="BH316" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI316" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ316" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK316">
+        <v>5</v>
+      </c>
+      <c r="BL316" t="s">
+        <v>2012</v>
+      </c>
+      <c r="BM316">
+        <v>0</v>
+      </c>
+      <c r="BN316">
+        <v>0</v>
+      </c>
+      <c r="BO316" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP316" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ316" t="s">
+        <v>1630</v>
+      </c>
+      <c r="BS316" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT316" t="s">
+        <v>1604</v>
+      </c>
+      <c r="BU316" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV316" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW316" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX316" t="s">
+        <v>2458</v>
+      </c>
+      <c r="EY316" s="1"/>
+      <c r="GQ316" s="1"/>
+      <c r="GR316" s="1"/>
+      <c r="GY316" s="1"/>
+      <c r="GZ316" s="1"/>
+      <c r="HA316" s="1"/>
+      <c r="HB316" s="1"/>
+      <c r="IQ316" s="1">
+        <v>889721044</v>
+      </c>
+      <c r="IR316" t="s">
+        <v>2459</v>
+      </c>
+      <c r="IS316" s="1">
+        <v>46304.507141203707</v>
+      </c>
+      <c r="IU316" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW316" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX316" t="s">
+        <v>2460</v>
+      </c>
+      <c r="IY316">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A317" s="1">
+        <v>46304.63213510417</v>
+      </c>
+      <c r="B317" s="1">
+        <v>46304.635030173609</v>
+      </c>
+      <c r="C317" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D317" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E317" t="s">
+        <v>295</v>
+      </c>
+      <c r="F317" t="s">
+        <v>305</v>
+      </c>
+      <c r="G317" t="s">
+        <v>198</v>
+      </c>
+      <c r="H317" t="s">
+        <v>297</v>
+      </c>
+      <c r="BS317" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT317" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU317" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV317" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW317" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX317" t="s">
+        <v>612</v>
+      </c>
+      <c r="BY317" t="s">
+        <v>359</v>
+      </c>
+      <c r="EK317" t="s">
+        <v>2461</v>
+      </c>
+      <c r="EL317" t="s">
+        <v>2462</v>
+      </c>
+      <c r="EM317" t="s">
+        <v>2463</v>
+      </c>
+      <c r="EN317" t="s">
+        <v>2464</v>
+      </c>
+      <c r="EY317" s="1"/>
+      <c r="GQ317" s="1"/>
+      <c r="GR317" s="1"/>
+      <c r="GY317" s="1"/>
+      <c r="GZ317" s="1"/>
+      <c r="HA317" s="1"/>
+      <c r="HB317" s="1"/>
+      <c r="IQ317" s="1">
+        <v>889724514</v>
+      </c>
+      <c r="IR317" t="s">
+        <v>2465</v>
+      </c>
+      <c r="IS317" s="1">
+        <v>46304.510046296287</v>
+      </c>
+      <c r="IU317" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW317" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX317" t="s">
+        <v>2466</v>
+      </c>
+      <c r="IY317">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A318" s="1">
+        <v>46302.81901608796</v>
+      </c>
+      <c r="B318" s="1">
+        <v>46304.718805671298</v>
+      </c>
+      <c r="C318" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D318" t="s">
+        <v>691</v>
+      </c>
+      <c r="E318" t="s">
+        <v>210</v>
+      </c>
+      <c r="F318" t="s">
+        <v>275</v>
+      </c>
+      <c r="G318" t="s">
+        <v>198</v>
+      </c>
+      <c r="H318" t="s">
+        <v>212</v>
+      </c>
+      <c r="J318" t="s">
+        <v>2467</v>
+      </c>
+      <c r="K318" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L318" t="s">
+        <v>324</v>
+      </c>
+      <c r="M318" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N318" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O318" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R318">
+        <v>34</v>
+      </c>
+      <c r="S318">
+        <v>28</v>
+      </c>
+      <c r="T318" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U318" t="s">
+        <v>1816</v>
+      </c>
+      <c r="V318">
+        <v>0</v>
+      </c>
+      <c r="W318">
+        <v>0</v>
+      </c>
+      <c r="X318">
+        <v>0</v>
+      </c>
+      <c r="Y318">
+        <v>1</v>
+      </c>
+      <c r="Z318">
+        <v>0</v>
+      </c>
+      <c r="AA318">
+        <v>0</v>
+      </c>
+      <c r="AB318" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC318">
+        <v>1</v>
+      </c>
+      <c r="AD318">
+        <v>1</v>
+      </c>
+      <c r="AE318">
+        <v>0</v>
+      </c>
+      <c r="AF318">
+        <v>0</v>
+      </c>
+      <c r="AG318">
+        <v>0</v>
+      </c>
+      <c r="AH318">
+        <v>593</v>
+      </c>
+      <c r="AI318">
+        <v>200</v>
+      </c>
+      <c r="AJ318">
+        <v>195</v>
+      </c>
+      <c r="AK318">
+        <v>2</v>
+      </c>
+      <c r="AL318">
+        <v>2</v>
+      </c>
+      <c r="AM318">
+        <v>0</v>
+      </c>
+      <c r="AN318">
+        <v>0</v>
+      </c>
+      <c r="AO318" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP318">
+        <v>8</v>
+      </c>
+      <c r="AQ318" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR318" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS318" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT318" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU318" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV318" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW318" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS318" t="s">
+        <v>2468</v>
+      </c>
+      <c r="BT318" t="s">
+        <v>324</v>
+      </c>
+      <c r="BU318" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW318" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX318" t="s">
+        <v>2469</v>
+      </c>
+      <c r="EY318" s="1"/>
+      <c r="GQ318" s="1"/>
+      <c r="GR318" s="1"/>
+      <c r="GY318" s="1"/>
+      <c r="GZ318" s="1"/>
+      <c r="HA318" s="1"/>
+      <c r="HB318" s="1"/>
+      <c r="IQ318" s="1">
+        <v>889849337</v>
+      </c>
+      <c r="IR318" t="s">
+        <v>2470</v>
+      </c>
+      <c r="IS318" s="1">
+        <v>46304.609189814822</v>
+      </c>
+      <c r="IU318" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW318" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX318" t="s">
+        <v>2471</v>
+      </c>
+      <c r="IY318">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A319" s="1">
+        <v>46304.719278657409</v>
+      </c>
+      <c r="B319" s="1">
+        <v>46304.726659224543</v>
+      </c>
+      <c r="C319" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D319" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E319" t="s">
+        <v>210</v>
+      </c>
+      <c r="F319" t="s">
+        <v>275</v>
+      </c>
+      <c r="G319" t="s">
+        <v>198</v>
+      </c>
+      <c r="H319" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS319" t="s">
+        <v>2472</v>
+      </c>
+      <c r="BT319" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU319" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW319" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX319" t="s">
+        <v>2473</v>
+      </c>
+      <c r="BY319" t="s">
+        <v>456</v>
+      </c>
+      <c r="EK319" t="s">
+        <v>2474</v>
+      </c>
+      <c r="EL319" t="s">
+        <v>2475</v>
+      </c>
+      <c r="EM319" t="s">
+        <v>2476</v>
+      </c>
+      <c r="EN319" t="s">
+        <v>2477</v>
+      </c>
+      <c r="EY319" s="1"/>
+      <c r="GQ319" s="1"/>
+      <c r="GR319" s="1"/>
+      <c r="GY319" s="1"/>
+      <c r="GZ319" s="1"/>
+      <c r="HA319" s="1"/>
+      <c r="HB319" s="1"/>
+      <c r="IQ319" s="1">
+        <v>889849348</v>
+      </c>
+      <c r="IR319" t="s">
+        <v>2478</v>
+      </c>
+      <c r="IS319" s="1">
+        <v>46304.609201388892</v>
+      </c>
+      <c r="IU319" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW319" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX319" t="s">
+        <v>2479</v>
+      </c>
+      <c r="IY319">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A320" s="1">
+        <v>46304.726662002307</v>
+      </c>
+      <c r="B320" s="1">
+        <v>46304.827422465278</v>
+      </c>
+      <c r="C320" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D320" t="s">
+        <v>690</v>
+      </c>
+      <c r="E320" t="s">
+        <v>210</v>
+      </c>
+      <c r="F320" t="s">
+        <v>401</v>
+      </c>
+      <c r="G320" t="s">
+        <v>198</v>
+      </c>
+      <c r="H320" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX320" t="s">
+        <v>2480</v>
+      </c>
+      <c r="AY320" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ320" t="s">
+        <v>2481</v>
+      </c>
+      <c r="BA320" t="s">
+        <v>2482</v>
+      </c>
+      <c r="BB320">
+        <v>0</v>
+      </c>
+      <c r="BC320">
+        <v>3</v>
+      </c>
+      <c r="BD320" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE320" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF320" t="s">
+        <v>395</v>
+      </c>
+      <c r="BG320" t="s">
+        <v>2483</v>
+      </c>
+      <c r="BH320" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI320" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ320" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK320">
+        <v>2</v>
+      </c>
+      <c r="BL320" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM320">
+        <v>40</v>
+      </c>
+      <c r="BN320">
+        <v>38</v>
+      </c>
+      <c r="BO320" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP320" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ320" t="s">
+        <v>1630</v>
+      </c>
+      <c r="BS320" t="s">
+        <v>2484</v>
+      </c>
+      <c r="BT320" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU320" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV320" t="s">
+        <v>1835</v>
+      </c>
+      <c r="BW320" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX320" t="s">
+        <v>2485</v>
+      </c>
+      <c r="EY320" s="1"/>
+      <c r="GQ320" s="1"/>
+      <c r="GR320" s="1"/>
+      <c r="GY320" s="1"/>
+      <c r="GZ320" s="1"/>
+      <c r="HA320" s="1"/>
+      <c r="HB320" s="1"/>
+      <c r="IQ320" s="1">
+        <v>889967083</v>
+      </c>
+      <c r="IR320" t="s">
+        <v>2486</v>
+      </c>
+      <c r="IS320" s="1">
+        <v>46304.714479166672</v>
+      </c>
+      <c r="IU320" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW320" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX320" t="s">
+        <v>2487</v>
+      </c>
+      <c r="IY320">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A321" s="1">
+        <v>46304.827425219897</v>
+      </c>
+      <c r="B321" s="1">
+        <v>46304.839314560188</v>
+      </c>
+      <c r="C321" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D321" t="s">
+        <v>690</v>
+      </c>
+      <c r="E321" t="s">
+        <v>210</v>
+      </c>
+      <c r="F321" t="s">
+        <v>2097</v>
+      </c>
+      <c r="G321" t="s">
+        <v>198</v>
+      </c>
+      <c r="H321" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX321" t="s">
+        <v>2025</v>
+      </c>
+      <c r="AY321" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ321" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA321" t="s">
+        <v>2488</v>
+      </c>
+      <c r="BB321">
+        <v>17</v>
+      </c>
+      <c r="BC321">
+        <v>8</v>
+      </c>
+      <c r="BD321" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE321" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF321" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG321" t="s">
+        <v>2489</v>
+      </c>
+      <c r="BH321" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI321" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ321" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK321">
+        <v>3</v>
+      </c>
+      <c r="BL321" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM321">
+        <v>90</v>
+      </c>
+      <c r="BN321">
+        <v>65</v>
+      </c>
+      <c r="BO321" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP321" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ321" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS321" t="s">
+        <v>2490</v>
+      </c>
+      <c r="BT321" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU321" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW321" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX321" t="s">
+        <v>2491</v>
+      </c>
+      <c r="EY321" s="1"/>
+      <c r="GQ321" s="1"/>
+      <c r="GR321" s="1"/>
+      <c r="GY321" s="1"/>
+      <c r="GZ321" s="1"/>
+      <c r="HA321" s="1"/>
+      <c r="HB321" s="1"/>
+      <c r="IQ321" s="1">
+        <v>889967087</v>
+      </c>
+      <c r="IR321" t="s">
+        <v>2492</v>
+      </c>
+      <c r="IS321" s="1">
+        <v>46304.714490740742</v>
+      </c>
+      <c r="IU321" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW321" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX321" t="s">
+        <v>2493</v>
+      </c>
+      <c r="IY321">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A322" s="1">
+        <v>46304.845099108803</v>
+      </c>
+      <c r="B322" s="1">
+        <v>46304.866174583331</v>
+      </c>
+      <c r="C322" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D322" t="s">
+        <v>691</v>
+      </c>
+      <c r="E322" t="s">
+        <v>210</v>
+      </c>
+      <c r="F322" t="s">
+        <v>401</v>
+      </c>
+      <c r="G322" t="s">
+        <v>198</v>
+      </c>
+      <c r="H322" t="s">
+        <v>212</v>
+      </c>
+      <c r="J322" t="s">
+        <v>653</v>
+      </c>
+      <c r="K322" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L322" t="s">
+        <v>324</v>
+      </c>
+      <c r="M322" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N322" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O322" t="s">
+        <v>1814</v>
+      </c>
+      <c r="R322">
+        <v>62</v>
+      </c>
+      <c r="S322">
+        <v>47</v>
+      </c>
+      <c r="T322" t="s">
+        <v>2114</v>
+      </c>
+      <c r="U322" t="s">
+        <v>2235</v>
+      </c>
+      <c r="V322">
+        <v>0</v>
+      </c>
+      <c r="W322">
+        <v>0</v>
+      </c>
+      <c r="X322">
+        <v>1</v>
+      </c>
+      <c r="Y322">
+        <v>0</v>
+      </c>
+      <c r="Z322">
+        <v>0</v>
+      </c>
+      <c r="AA322">
+        <v>0</v>
+      </c>
+      <c r="AB322" t="s">
+        <v>2248</v>
+      </c>
+      <c r="AC322">
+        <v>1</v>
+      </c>
+      <c r="AD322">
+        <v>1</v>
+      </c>
+      <c r="AE322">
+        <v>0</v>
+      </c>
+      <c r="AF322">
+        <v>0</v>
+      </c>
+      <c r="AG322">
+        <v>0</v>
+      </c>
+      <c r="AH322">
+        <v>945</v>
+      </c>
+      <c r="AI322">
+        <v>87</v>
+      </c>
+      <c r="AJ322">
+        <v>100</v>
+      </c>
+      <c r="AK322">
+        <v>4</v>
+      </c>
+      <c r="AL322">
+        <v>3</v>
+      </c>
+      <c r="AM322">
+        <v>0</v>
+      </c>
+      <c r="AN322">
+        <v>0</v>
+      </c>
+      <c r="AO322" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP322">
+        <v>5</v>
+      </c>
+      <c r="AQ322" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR322" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS322" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT322" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU322" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV322" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW322" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS322" t="s">
+        <v>954</v>
+      </c>
+      <c r="BT322" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU322" t="s">
+        <v>1677</v>
+      </c>
+      <c r="BW322" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX322" t="s">
+        <v>956</v>
+      </c>
+      <c r="EY322" s="1"/>
+      <c r="GQ322" s="1"/>
+      <c r="GR322" s="1"/>
+      <c r="GY322" s="1"/>
+      <c r="GZ322" s="1"/>
+      <c r="HA322" s="1"/>
+      <c r="HB322" s="1"/>
+      <c r="IQ322" s="1">
+        <v>889990479</v>
+      </c>
+      <c r="IR322" t="s">
+        <v>2494</v>
+      </c>
+      <c r="IS322" s="1">
+        <v>46304.741354166668</v>
+      </c>
+      <c r="IU322" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW322" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX322" t="s">
+        <v>2495</v>
+      </c>
+      <c r="IY322">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A323" s="1">
+        <v>46304.904140416656</v>
+      </c>
+      <c r="B323" s="1">
+        <v>46304.910171759257</v>
+      </c>
+      <c r="C323" s="1">
+        <v>46301</v>
+      </c>
+      <c r="D323" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E323" t="s">
+        <v>210</v>
+      </c>
+      <c r="F323" t="s">
+        <v>2246</v>
+      </c>
+      <c r="G323" t="s">
+        <v>198</v>
+      </c>
+      <c r="H323" t="s">
+        <v>212</v>
+      </c>
+      <c r="BS323" t="s">
+        <v>2496</v>
+      </c>
+      <c r="BT323" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU323" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW323" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX323" t="s">
+        <v>1202</v>
+      </c>
+      <c r="EY323" s="1"/>
+      <c r="GQ323" s="1"/>
+      <c r="GR323" s="1"/>
+      <c r="GY323" s="1"/>
+      <c r="GZ323" s="1"/>
+      <c r="HA323" s="1"/>
+      <c r="HB323" s="1"/>
+      <c r="HS323" t="s">
+        <v>2382</v>
+      </c>
+      <c r="HT323">
+        <v>26</v>
+      </c>
+      <c r="HU323">
+        <v>14</v>
+      </c>
+      <c r="IQ323" s="1">
+        <v>890023397</v>
+      </c>
+      <c r="IR323" t="s">
+        <v>2497</v>
+      </c>
+      <c r="IS323" s="1">
+        <v>46304.785185185188</v>
+      </c>
+      <c r="IU323" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW323" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX323" t="s">
+        <v>2498</v>
+      </c>
+      <c r="IY323">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A324" s="1">
+        <v>46302.598696724534</v>
+      </c>
+      <c r="B324" s="1">
+        <v>46306.922155856482</v>
+      </c>
+      <c r="C324" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D324" t="s">
+        <v>354</v>
+      </c>
+      <c r="E324" t="s">
+        <v>254</v>
+      </c>
+      <c r="F324" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G324" t="s">
+        <v>198</v>
+      </c>
+      <c r="H324" t="s">
+        <v>256</v>
+      </c>
+      <c r="BS324" t="s">
+        <v>2499</v>
+      </c>
+      <c r="BT324" t="s">
+        <v>2500</v>
+      </c>
+      <c r="BU324" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW324" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX324" t="s">
+        <v>2501</v>
+      </c>
+      <c r="BY324" t="s">
+        <v>359</v>
+      </c>
+      <c r="CB324" t="s">
+        <v>360</v>
+      </c>
+      <c r="CC324">
+        <v>2</v>
+      </c>
+      <c r="CD324">
+        <v>560</v>
+      </c>
+      <c r="CE324" t="s">
+        <v>405</v>
+      </c>
+      <c r="CF324" t="s">
+        <v>2502</v>
+      </c>
+      <c r="CG324" t="s">
+        <v>392</v>
+      </c>
+      <c r="CH324" t="s">
+        <v>2503</v>
+      </c>
+      <c r="CI324" t="s">
+        <v>458</v>
+      </c>
+      <c r="CK324" t="s">
+        <v>721</v>
+      </c>
+      <c r="CL324" t="s">
+        <v>2504</v>
+      </c>
+      <c r="CM324" t="s">
+        <v>397</v>
+      </c>
+      <c r="CN324" t="s">
+        <v>2505</v>
+      </c>
+      <c r="EY324" s="1"/>
+      <c r="GQ324" s="1"/>
+      <c r="GR324" s="1"/>
+      <c r="GY324" s="1"/>
+      <c r="GZ324" s="1"/>
+      <c r="HA324" s="1"/>
+      <c r="HB324" s="1"/>
+      <c r="IQ324" s="1">
+        <v>891252880</v>
+      </c>
+      <c r="IR324" t="s">
+        <v>2506</v>
+      </c>
+      <c r="IS324" s="1">
+        <v>46306.797164351847</v>
+      </c>
+      <c r="IU324" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW324" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX324" t="s">
+        <v>2507</v>
+      </c>
+      <c r="IY324">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A325" s="1">
+        <v>46304.759218159721</v>
+      </c>
+      <c r="B325" s="1">
+        <v>46306.922665069447</v>
+      </c>
+      <c r="C325" s="1">
+        <v>46295</v>
+      </c>
+      <c r="D325" t="s">
+        <v>691</v>
+      </c>
+      <c r="E325" t="s">
+        <v>254</v>
+      </c>
+      <c r="F325" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G325" t="s">
+        <v>198</v>
+      </c>
+      <c r="H325" t="s">
+        <v>256</v>
+      </c>
+      <c r="J325" t="s">
+        <v>2508</v>
+      </c>
+      <c r="K325" t="s">
+        <v>201</v>
+      </c>
+      <c r="L325" t="s">
+        <v>324</v>
+      </c>
+      <c r="M325" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N325" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O325" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH325">
+        <v>560</v>
+      </c>
+      <c r="AI325">
+        <v>250</v>
+      </c>
+      <c r="AJ325">
+        <v>310</v>
+      </c>
+      <c r="AK325">
+        <v>10</v>
+      </c>
+      <c r="AL325">
+        <v>2</v>
+      </c>
+      <c r="AM325">
+        <v>0</v>
+      </c>
+      <c r="AN325">
+        <v>0</v>
+      </c>
+      <c r="AO325" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP325">
+        <v>4</v>
+      </c>
+      <c r="AQ325" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR325" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS325" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT325" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU325" t="s">
+        <v>202</v>
+      </c>
+      <c r="AV325" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW325" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS325" t="s">
+        <v>2509</v>
+      </c>
+      <c r="BT325" t="s">
+        <v>2510</v>
+      </c>
+      <c r="BU325" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW325" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX325" t="s">
+        <v>2511</v>
+      </c>
+      <c r="EY325" s="1"/>
+      <c r="GQ325" s="1"/>
+      <c r="GR325" s="1"/>
+      <c r="GY325" s="1"/>
+      <c r="GZ325" s="1"/>
+      <c r="HA325" s="1"/>
+      <c r="HB325" s="1"/>
+      <c r="IQ325" s="1">
+        <v>891253171</v>
+      </c>
+      <c r="IR325" t="s">
+        <v>2512</v>
+      </c>
+      <c r="IS325" s="1">
+        <v>46306.797673611109</v>
+      </c>
+      <c r="IU325" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW325" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX325" t="s">
+        <v>2513</v>
+      </c>
+      <c r="IY325">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711CA4C0-1BC9-D445-AE9D-3D0F8CA23579}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B94CA3D-CB40-8540-86D5-257F15E31F0A}"/>
   <bookViews>
     <workbookView xWindow="2520" yWindow="1060" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="6" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="2514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8195" uniqueCount="2539">
   <si>
     <t>start</t>
   </si>
@@ -7579,6 +7579,81 @@
   </si>
   <si>
     <t>uuid:add0c950-442f-486f-840d-8318f602e16c</t>
+  </si>
+  <si>
+    <t>Taxi drivers Nakawa</t>
+  </si>
+  <si>
+    <t>To report any one who shows un usual symptoms,to put had washing equipment in place</t>
+  </si>
+  <si>
+    <t>Doubted Ebola</t>
+  </si>
+  <si>
+    <t>Mistrust, miscommunication</t>
+  </si>
+  <si>
+    <t>f52ab584-3443-4789-848b-046088767a47</t>
+  </si>
+  <si>
+    <t>uuid:f52ab584-3443-4789-848b-046088767a47</t>
+  </si>
+  <si>
+    <t>Ocheng 7-8</t>
+  </si>
+  <si>
+    <t>Market committee</t>
+  </si>
+  <si>
+    <t>They committed to encourage market vendors to be with a hand sanitizer</t>
+  </si>
+  <si>
+    <t>Now that one person died of ebola in Kenya, does it mean it's also in Uganda.</t>
+  </si>
+  <si>
+    <t>Promoting hand washing in this market</t>
+  </si>
+  <si>
+    <t>1f3c93ba-4a6f-4b2d-b4b8-3c61351e88ad</t>
+  </si>
+  <si>
+    <t>uuid:1f3c93ba-4a6f-4b2d-b4b8-3c61351e88ad</t>
+  </si>
+  <si>
+    <t>Gaddafi Secondary School (Integrated Academy</t>
+  </si>
+  <si>
+    <t>Is it true the kenya Ebola death passed through Uganda? Is there a shortest emergency number</t>
+  </si>
+  <si>
+    <t>Porus boarders were Congolese pass to Uganda</t>
+  </si>
+  <si>
+    <t>More activities should be done through the health clubs so as learners are more empowered</t>
+  </si>
+  <si>
+    <t>e2da1304-cfba-4783-b9c4-3dd3decd8c41</t>
+  </si>
+  <si>
+    <t>uuid:e2da1304-cfba-4783-b9c4-3dd3decd8c41</t>
+  </si>
+  <si>
+    <t>Kisaasi</t>
+  </si>
+  <si>
+    <t>How long does Ebola treatment take?</t>
+  </si>
+  <si>
+    <t>Presence of various Misinformation on social media</t>
+  </si>
+  <si>
+    <t>More sensitization to.address wrong information on social media should be carried out</t>
+  </si>
+  <si>
+    <t>1a028d94-aece-43f2-8a9e-ea5b688efda9</t>
+  </si>
+  <si>
+    <t>uuid:1a028d94-aece-43f2-8a9e-ea5b688efda9</t>
   </si>
 </sst>
 </file>
@@ -21633,7 +21708,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -21983,8 +22058,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY325" totalsRowShown="0">
-  <autoFilter ref="A1:IY325" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY329" totalsRowShown="0">
+  <autoFilter ref="A1:IY329" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -22537,7 +22612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY325"/>
+  <dimension ref="A1:IY329"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -61308,6 +61383,543 @@
         <v>324</v>
       </c>
     </row>
+    <row r="326" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A326" s="1">
+        <v>46307.727778900473</v>
+      </c>
+      <c r="B326" s="1">
+        <v>46307.734355196757</v>
+      </c>
+      <c r="C326" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D326" t="s">
+        <v>690</v>
+      </c>
+      <c r="E326" t="s">
+        <v>196</v>
+      </c>
+      <c r="F326" t="s">
+        <v>196</v>
+      </c>
+      <c r="G326" t="s">
+        <v>198</v>
+      </c>
+      <c r="H326" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX326" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AY326" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ326" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA326" t="s">
+        <v>2514</v>
+      </c>
+      <c r="BB326">
+        <v>10</v>
+      </c>
+      <c r="BC326">
+        <v>2</v>
+      </c>
+      <c r="BD326" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE326" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF326" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG326" t="s">
+        <v>2515</v>
+      </c>
+      <c r="BH326" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI326" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ326" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK326">
+        <v>5</v>
+      </c>
+      <c r="BL326" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM326">
+        <v>110</v>
+      </c>
+      <c r="BN326">
+        <v>70</v>
+      </c>
+      <c r="BO326" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP326" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ326" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS326" t="s">
+        <v>2516</v>
+      </c>
+      <c r="BT326" t="s">
+        <v>2517</v>
+      </c>
+      <c r="BU326" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW326" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX326" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY326" s="1"/>
+      <c r="GQ326" s="1"/>
+      <c r="GR326" s="1"/>
+      <c r="GY326" s="1"/>
+      <c r="GZ326" s="1"/>
+      <c r="HA326" s="1"/>
+      <c r="HB326" s="1"/>
+      <c r="IQ326" s="1">
+        <v>891862138</v>
+      </c>
+      <c r="IR326" t="s">
+        <v>2518</v>
+      </c>
+      <c r="IS326" s="1">
+        <v>46307.609386574077</v>
+      </c>
+      <c r="IU326" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW326" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX326" t="s">
+        <v>2519</v>
+      </c>
+      <c r="IY326">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A327" s="1">
+        <v>46305.476612465267</v>
+      </c>
+      <c r="B327" s="1">
+        <v>46307.790556585649</v>
+      </c>
+      <c r="C327" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D327" t="s">
+        <v>690</v>
+      </c>
+      <c r="E327" t="s">
+        <v>210</v>
+      </c>
+      <c r="F327" t="s">
+        <v>2520</v>
+      </c>
+      <c r="G327" t="s">
+        <v>198</v>
+      </c>
+      <c r="H327" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX327" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY327" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ327" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA327" t="s">
+        <v>2521</v>
+      </c>
+      <c r="BB327">
+        <v>4</v>
+      </c>
+      <c r="BC327">
+        <v>3</v>
+      </c>
+      <c r="BD327" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE327" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF327" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG327" t="s">
+        <v>2522</v>
+      </c>
+      <c r="BH327" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI327" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ327" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK327">
+        <v>8</v>
+      </c>
+      <c r="BL327" t="s">
+        <v>1629</v>
+      </c>
+      <c r="BM327">
+        <v>455</v>
+      </c>
+      <c r="BN327">
+        <v>300</v>
+      </c>
+      <c r="BO327" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP327" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ327" t="s">
+        <v>1630</v>
+      </c>
+      <c r="BS327" t="s">
+        <v>2523</v>
+      </c>
+      <c r="BT327" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU327" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV327" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BW327" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX327" t="s">
+        <v>2524</v>
+      </c>
+      <c r="EY327" s="1"/>
+      <c r="GQ327" s="1"/>
+      <c r="GR327" s="1"/>
+      <c r="GY327" s="1"/>
+      <c r="GZ327" s="1"/>
+      <c r="HA327" s="1"/>
+      <c r="HB327" s="1"/>
+      <c r="IQ327" s="1">
+        <v>891927448</v>
+      </c>
+      <c r="IR327" t="s">
+        <v>2525</v>
+      </c>
+      <c r="IS327" s="1">
+        <v>46307.665613425917</v>
+      </c>
+      <c r="IU327" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW327" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX327" t="s">
+        <v>2526</v>
+      </c>
+      <c r="IY327">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A328" s="1">
+        <v>46307.915130335648</v>
+      </c>
+      <c r="B328" s="1">
+        <v>46307.929743437497</v>
+      </c>
+      <c r="C328" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D328" t="s">
+        <v>691</v>
+      </c>
+      <c r="E328" t="s">
+        <v>254</v>
+      </c>
+      <c r="F328" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G328" t="s">
+        <v>198</v>
+      </c>
+      <c r="H328" t="s">
+        <v>256</v>
+      </c>
+      <c r="J328" t="s">
+        <v>2527</v>
+      </c>
+      <c r="K328" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L328" t="s">
+        <v>324</v>
+      </c>
+      <c r="M328" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N328" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O328" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P328" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AH328">
+        <v>560</v>
+      </c>
+      <c r="AI328">
+        <v>153</v>
+      </c>
+      <c r="AJ328">
+        <v>225</v>
+      </c>
+      <c r="AK328">
+        <v>2</v>
+      </c>
+      <c r="AL328">
+        <v>2</v>
+      </c>
+      <c r="AM328">
+        <v>0</v>
+      </c>
+      <c r="AN328">
+        <v>0</v>
+      </c>
+      <c r="AO328" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP328">
+        <v>5</v>
+      </c>
+      <c r="AQ328" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR328" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS328" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT328" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU328" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV328" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW328" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS328" t="s">
+        <v>2528</v>
+      </c>
+      <c r="BT328" t="s">
+        <v>2529</v>
+      </c>
+      <c r="BU328" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW328" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX328" t="s">
+        <v>2530</v>
+      </c>
+      <c r="EY328" s="1"/>
+      <c r="GQ328" s="1"/>
+      <c r="GR328" s="1"/>
+      <c r="GY328" s="1"/>
+      <c r="GZ328" s="1"/>
+      <c r="HA328" s="1"/>
+      <c r="HB328" s="1"/>
+      <c r="IQ328" s="1">
+        <v>892042141</v>
+      </c>
+      <c r="IR328" t="s">
+        <v>2531</v>
+      </c>
+      <c r="IS328" s="1">
+        <v>46307.804756944453</v>
+      </c>
+      <c r="IU328" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW328" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX328" t="s">
+        <v>2532</v>
+      </c>
+      <c r="IY328">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A329" s="1">
+        <v>46307.929744861111</v>
+      </c>
+      <c r="B329" s="1">
+        <v>46307.934005185183</v>
+      </c>
+      <c r="C329" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D329" t="s">
+        <v>691</v>
+      </c>
+      <c r="E329" t="s">
+        <v>254</v>
+      </c>
+      <c r="F329" t="s">
+        <v>2533</v>
+      </c>
+      <c r="G329" t="s">
+        <v>198</v>
+      </c>
+      <c r="H329" t="s">
+        <v>256</v>
+      </c>
+      <c r="J329" t="s">
+        <v>257</v>
+      </c>
+      <c r="K329" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L329" t="s">
+        <v>324</v>
+      </c>
+      <c r="M329" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N329" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O329" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P329" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AH329">
+        <v>645</v>
+      </c>
+      <c r="AI329">
+        <v>0</v>
+      </c>
+      <c r="AJ329">
+        <v>399</v>
+      </c>
+      <c r="AK329">
+        <v>12</v>
+      </c>
+      <c r="AL329">
+        <v>2</v>
+      </c>
+      <c r="AM329">
+        <v>0</v>
+      </c>
+      <c r="AN329">
+        <v>0</v>
+      </c>
+      <c r="AO329" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP329">
+        <v>4</v>
+      </c>
+      <c r="AQ329" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR329" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS329" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT329" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU329" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV329" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW329" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS329" t="s">
+        <v>2534</v>
+      </c>
+      <c r="BT329" t="s">
+        <v>2535</v>
+      </c>
+      <c r="BU329" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW329" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX329" t="s">
+        <v>2536</v>
+      </c>
+      <c r="EY329" s="1"/>
+      <c r="GQ329" s="1"/>
+      <c r="GR329" s="1"/>
+      <c r="GY329" s="1"/>
+      <c r="GZ329" s="1"/>
+      <c r="HA329" s="1"/>
+      <c r="HB329" s="1"/>
+      <c r="IQ329" s="1">
+        <v>892045172</v>
+      </c>
+      <c r="IR329" t="s">
+        <v>2537</v>
+      </c>
+      <c r="IS329" s="1">
+        <v>46307.809016203697</v>
+      </c>
+      <c r="IU329" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW329" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX329" t="s">
+        <v>2538</v>
+      </c>
+      <c r="IY329">
+        <v>328</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B94CA3D-CB40-8540-86D5-257F15E31F0A}"/>
+  <xr:revisionPtr revIDLastSave="382" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CAB88F3-BE93-A146-9504-0F8979165B3E}"/>
   <bookViews>
     <workbookView xWindow="2520" yWindow="1060" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8195" uniqueCount="2539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8633" uniqueCount="2628">
   <si>
     <t>start</t>
   </si>
@@ -7654,6 +7654,273 @@
   </si>
   <si>
     <t>uuid:1a028d94-aece-43f2-8a9e-ea5b688efda9</t>
+  </si>
+  <si>
+    <t>Ebola is not real outbreak in Uganda</t>
+  </si>
+  <si>
+    <t>26508120-4d7a-49c5-a2c1-c63172aac6a2</t>
+  </si>
+  <si>
+    <t>uuid:26508120-4d7a-49c5-a2c1-c63172aac6a2</t>
+  </si>
+  <si>
+    <t>Market vendor leaders,</t>
+  </si>
+  <si>
+    <t>To report any an usual signs and symptoms, to set up hand washing everything</t>
+  </si>
+  <si>
+    <t>Why do outbreaks start in Kamapala, is it because that is where there is money?</t>
+  </si>
+  <si>
+    <t>Slum setting, mistrust.</t>
+  </si>
+  <si>
+    <t>3a730195-9844-4492-890a-f1cce88f33cb</t>
+  </si>
+  <si>
+    <t>uuid:3a730195-9844-4492-890a-f1cce88f33cb</t>
+  </si>
+  <si>
+    <t>b1683b37-b6a1-4fc9-ace4-5d459b386496</t>
+  </si>
+  <si>
+    <t>uuid:b1683b37-b6a1-4fc9-ace4-5d459b386496</t>
+  </si>
+  <si>
+    <t>Sex worker leaders, youth leader,and bar manager gayitono bar and lodge</t>
+  </si>
+  <si>
+    <t>Have hand washing equipment</t>
+  </si>
+  <si>
+    <t>Ebola was never in Uganda</t>
+  </si>
+  <si>
+    <t>Illiterate community with sex workers and all have mistrust</t>
+  </si>
+  <si>
+    <t>More sensitization about PHE preparedness is needed</t>
+  </si>
+  <si>
+    <t>1569877e-65c9-419a-af1d-4219ab247489</t>
+  </si>
+  <si>
+    <t>uuid:1569877e-65c9-419a-af1d-4219ab247489</t>
+  </si>
+  <si>
+    <t>Market leaders and vendors</t>
+  </si>
+  <si>
+    <t>Encouraging people to follow SOPs</t>
+  </si>
+  <si>
+    <t>It is said that man was long ago from the monkey family, does it mean that ebola was also their.</t>
+  </si>
+  <si>
+    <t>Handwashing at the market</t>
+  </si>
+  <si>
+    <t>c0789cad-fdd6-494f-99a6-1687daad6a7e</t>
+  </si>
+  <si>
+    <t>uuid:c0789cad-fdd6-494f-99a6-1687daad6a7e</t>
+  </si>
+  <si>
+    <t>They committed to share the information with their clients.</t>
+  </si>
+  <si>
+    <t>Handwashing with a sanitizer</t>
+  </si>
+  <si>
+    <t>e4fe8159-4fae-40b7-afd9-de87adb6ed17</t>
+  </si>
+  <si>
+    <t>uuid:e4fe8159-4fae-40b7-afd9-de87adb6ed17</t>
+  </si>
+  <si>
+    <t>St. Steven High School</t>
+  </si>
+  <si>
+    <t>During times of the outbreak, students are normally mislead by the rumors that come through on social media that they are no studies or all school have been closes</t>
+  </si>
+  <si>
+    <t>Failure to mitigate the false information  that is passed on social media</t>
+  </si>
+  <si>
+    <t>The students should firstly verify information withs platforms of the Ministry of health begre spreading or sharing it</t>
+  </si>
+  <si>
+    <t>ce13b8aa-e479-44f5-91c3-c8b8af6e5bc0</t>
+  </si>
+  <si>
+    <t>uuid:ce13b8aa-e479-44f5-91c3-c8b8af6e5bc0</t>
+  </si>
+  <si>
+    <t>Gwaffu</t>
+  </si>
+  <si>
+    <t>Boda Riders</t>
+  </si>
+  <si>
+    <t>Sharing some if the information  that is in like with the public health emergencies  with the clients.</t>
+  </si>
+  <si>
+    <t>Ebola is contracted through eating meat from the bushes. Ebola doesn't cure. The government always organises ways how it can get t money from whites and this is one of them.</t>
+  </si>
+  <si>
+    <t>Lack of hand washing facilities at the entrance.  The boda are mobile so this makes their adherence to SOPs complex</t>
+  </si>
+  <si>
+    <t>Endeavor to have a sanitizer and also wash their hands where it is unavoidable like when going to eat food or when from work</t>
+  </si>
+  <si>
+    <t>99360cf7-55d9-4479-b1cc-e311eed8afd9</t>
+  </si>
+  <si>
+    <t>uuid:99360cf7-55d9-4479-b1cc-e311eed8afd9</t>
+  </si>
+  <si>
+    <t>Nabuta</t>
+  </si>
+  <si>
+    <t>Bar attendants and the manager</t>
+  </si>
+  <si>
+    <t>To always encourage the commercial sex workers to be vigilant and keen on the new people that are coming to meet then</t>
+  </si>
+  <si>
+    <t>As long as you have a condom, you can protect yourself  from ebola. You are safe from contracting it</t>
+  </si>
+  <si>
+    <t>The fact that these CSW are engaged by so many people from different places, it is hard to deny one a customer services which increases the risk of contracting.</t>
+  </si>
+  <si>
+    <t>Availing hand washing facilities and using the bar manager to cascade the important information about PHe to the members</t>
+  </si>
+  <si>
+    <t>30cb147d-0912-4950-8246-51e7f163fdc2</t>
+  </si>
+  <si>
+    <t>uuid:30cb147d-0912-4950-8246-51e7f163fdc2</t>
+  </si>
+  <si>
+    <t>Market leader kitintale</t>
+  </si>
+  <si>
+    <t>To have more hand washing facilities, to isolate and report any any one with an usual signs and symptoms</t>
+  </si>
+  <si>
+    <t>Ebola is not real and other outbreaks are exaggerated apart from covid19</t>
+  </si>
+  <si>
+    <t>Mistrust, poverty</t>
+  </si>
+  <si>
+    <t>ac2c2c1e-158a-4619-937d-bea5e2c36562</t>
+  </si>
+  <si>
+    <t>uuid:ac2c2c1e-158a-4619-937d-bea5e2c36562</t>
+  </si>
+  <si>
+    <t>Bodaboda stage leader</t>
+  </si>
+  <si>
+    <t>To report any suspected case.</t>
+  </si>
+  <si>
+    <t>Why don't we see the victims of outbreaks like Ebola but we just hear about them</t>
+  </si>
+  <si>
+    <t>Mistrust and misinformation</t>
+  </si>
+  <si>
+    <t>ded4b66c-f42e-4bf4-8648-42341a6087c3</t>
+  </si>
+  <si>
+    <t>uuid:ded4b66c-f42e-4bf4-8648-42341a6087c3</t>
+  </si>
+  <si>
+    <t>Manager of Prestige warehouse</t>
+  </si>
+  <si>
+    <t>Empowering workers with health information</t>
+  </si>
+  <si>
+    <t>How can we differentiate Mpox from Ebola?</t>
+  </si>
+  <si>
+    <t>Misinformation on social media</t>
+  </si>
+  <si>
+    <t>More sensitization drives should be carried out</t>
+  </si>
+  <si>
+    <t>45bd1f37-c6ec-4fa3-94f8-031bda900f28</t>
+  </si>
+  <si>
+    <t>uuid:45bd1f37-c6ec-4fa3-94f8-031bda900f28</t>
+  </si>
+  <si>
+    <t>Sharing of approved or confirmed information</t>
+  </si>
+  <si>
+    <t>Is the MOH contact toll free?</t>
+  </si>
+  <si>
+    <t>Limited knowledge about emergencies</t>
+  </si>
+  <si>
+    <t>More sensitization should be carried out at community level</t>
+  </si>
+  <si>
+    <t>ad8f55b6-9f08-4bb7-a96d-8c3184d5a750</t>
+  </si>
+  <si>
+    <t>uuid:ad8f55b6-9f08-4bb7-a96d-8c3184d5a750</t>
+  </si>
+  <si>
+    <t>Factory manager</t>
+  </si>
+  <si>
+    <t>Re activate the hand washing facility at the gate</t>
+  </si>
+  <si>
+    <t>What causes Ebola? What if I report a suspect and yet is not confirmed to be positive for Ebola won't I be hated?</t>
+  </si>
+  <si>
+    <t>Misinformation about the outbreaks</t>
+  </si>
+  <si>
+    <t>More sensitization activities should be carried out in the communiy</t>
+  </si>
+  <si>
+    <t>06c26319-a937-4cfd-afed-f7bf5690e2d8</t>
+  </si>
+  <si>
+    <t>uuid:06c26319-a937-4cfd-afed-f7bf5690e2d8</t>
+  </si>
+  <si>
+    <t>Bwaise II</t>
+  </si>
+  <si>
+    <t>Truck drivers</t>
+  </si>
+  <si>
+    <t>Making use of the MOH toll free number to.report suspects</t>
+  </si>
+  <si>
+    <t>Is there a vaccine for Ebola</t>
+  </si>
+  <si>
+    <t>VHTS should be empowered so they conduct sensitization</t>
+  </si>
+  <si>
+    <t>2b42a5e1-9b80-4b46-ae76-5caed6c14ba7</t>
+  </si>
+  <si>
+    <t>uuid:2b42a5e1-9b80-4b46-ae76-5caed6c14ba7</t>
   </si>
 </sst>
 </file>
@@ -21708,7 +21975,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -22058,8 +22325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY329" totalsRowShown="0">
-  <autoFilter ref="A1:IY329" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY344" totalsRowShown="0">
+  <autoFilter ref="A1:IY344" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -22612,7 +22879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY329"/>
+  <dimension ref="A1:IY344"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -61920,6 +62187,1977 @@
         <v>328</v>
       </c>
     </row>
+    <row r="330" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A330" s="1">
+        <v>46307.734356793982</v>
+      </c>
+      <c r="B330" s="1">
+        <v>46308.497021828713</v>
+      </c>
+      <c r="C330" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D330" t="s">
+        <v>691</v>
+      </c>
+      <c r="E330" t="s">
+        <v>196</v>
+      </c>
+      <c r="F330" t="s">
+        <v>777</v>
+      </c>
+      <c r="G330" t="s">
+        <v>198</v>
+      </c>
+      <c r="H330" t="s">
+        <v>199</v>
+      </c>
+      <c r="J330" t="s">
+        <v>781</v>
+      </c>
+      <c r="K330" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L330" t="s">
+        <v>2113</v>
+      </c>
+      <c r="M330" t="s">
+        <v>1701</v>
+      </c>
+      <c r="N330" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O330" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P330" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AH330">
+        <v>870</v>
+      </c>
+      <c r="AI330">
+        <v>280</v>
+      </c>
+      <c r="AJ330">
+        <v>310</v>
+      </c>
+      <c r="AK330">
+        <v>2</v>
+      </c>
+      <c r="AL330">
+        <v>2</v>
+      </c>
+      <c r="AM330">
+        <v>0</v>
+      </c>
+      <c r="AN330">
+        <v>0</v>
+      </c>
+      <c r="AO330" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP330">
+        <v>3</v>
+      </c>
+      <c r="AQ330" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR330" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS330" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT330" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU330" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV330" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW330" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS330" t="s">
+        <v>2539</v>
+      </c>
+      <c r="BT330" t="s">
+        <v>1712</v>
+      </c>
+      <c r="BU330" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW330" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX330" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY330" s="1"/>
+      <c r="GQ330" s="1"/>
+      <c r="GR330" s="1"/>
+      <c r="GY330" s="1"/>
+      <c r="GZ330" s="1"/>
+      <c r="HA330" s="1"/>
+      <c r="HB330" s="1"/>
+      <c r="IQ330" s="1">
+        <v>892365937</v>
+      </c>
+      <c r="IR330" t="s">
+        <v>2540</v>
+      </c>
+      <c r="IS330" s="1">
+        <v>46308.372048611112</v>
+      </c>
+      <c r="IU330" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW330" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX330" t="s">
+        <v>2541</v>
+      </c>
+      <c r="IY330">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A331" s="1">
+        <v>46308.497023148149</v>
+      </c>
+      <c r="B331" s="1">
+        <v>46308.505716701387</v>
+      </c>
+      <c r="C331" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D331" t="s">
+        <v>690</v>
+      </c>
+      <c r="E331" t="s">
+        <v>196</v>
+      </c>
+      <c r="F331" t="s">
+        <v>199</v>
+      </c>
+      <c r="G331" t="s">
+        <v>198</v>
+      </c>
+      <c r="H331" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX331" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY331" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ331" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA331" t="s">
+        <v>2542</v>
+      </c>
+      <c r="BB331">
+        <v>3</v>
+      </c>
+      <c r="BC331">
+        <v>4</v>
+      </c>
+      <c r="BD331" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE331" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF331" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG331" t="s">
+        <v>2543</v>
+      </c>
+      <c r="BH331" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI331" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ331" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK331">
+        <v>4</v>
+      </c>
+      <c r="BL331" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM331">
+        <v>50</v>
+      </c>
+      <c r="BN331">
+        <v>38</v>
+      </c>
+      <c r="BO331" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP331" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ331" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS331" t="s">
+        <v>2544</v>
+      </c>
+      <c r="BT331" t="s">
+        <v>2545</v>
+      </c>
+      <c r="BU331" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW331" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX331" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY331" s="1"/>
+      <c r="GQ331" s="1"/>
+      <c r="GR331" s="1"/>
+      <c r="GY331" s="1"/>
+      <c r="GZ331" s="1"/>
+      <c r="HA331" s="1"/>
+      <c r="HB331" s="1"/>
+      <c r="IQ331" s="1">
+        <v>892377436</v>
+      </c>
+      <c r="IR331" t="s">
+        <v>2546</v>
+      </c>
+      <c r="IS331" s="1">
+        <v>46308.380752314813</v>
+      </c>
+      <c r="IU331" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW331" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX331" t="s">
+        <v>2547</v>
+      </c>
+      <c r="IY331">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A332" s="1">
+        <v>46308.522087534722</v>
+      </c>
+      <c r="B332" s="1">
+        <v>46308.525839479167</v>
+      </c>
+      <c r="C332" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D332" t="s">
+        <v>691</v>
+      </c>
+      <c r="E332" t="s">
+        <v>196</v>
+      </c>
+      <c r="F332" t="s">
+        <v>196</v>
+      </c>
+      <c r="G332" t="s">
+        <v>198</v>
+      </c>
+      <c r="H332" t="s">
+        <v>199</v>
+      </c>
+      <c r="J332" t="s">
+        <v>200</v>
+      </c>
+      <c r="K332" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L332" t="s">
+        <v>395</v>
+      </c>
+      <c r="M332" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N332" t="s">
+        <v>1672</v>
+      </c>
+      <c r="O332" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P332" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AH332">
+        <v>1680</v>
+      </c>
+      <c r="AI332">
+        <v>450</v>
+      </c>
+      <c r="AJ332">
+        <v>620</v>
+      </c>
+      <c r="AK332">
+        <v>2</v>
+      </c>
+      <c r="AL332">
+        <v>2</v>
+      </c>
+      <c r="AM332">
+        <v>0</v>
+      </c>
+      <c r="AN332">
+        <v>0</v>
+      </c>
+      <c r="AO332" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP332">
+        <v>4</v>
+      </c>
+      <c r="AQ332" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR332" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS332" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT332" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU332" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV332" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW332" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS332" t="s">
+        <v>1122</v>
+      </c>
+      <c r="BT332" t="s">
+        <v>1637</v>
+      </c>
+      <c r="BU332" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW332" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX332" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY332" s="1"/>
+      <c r="GQ332" s="1"/>
+      <c r="GR332" s="1"/>
+      <c r="GY332" s="1"/>
+      <c r="GZ332" s="1"/>
+      <c r="HA332" s="1"/>
+      <c r="HB332" s="1"/>
+      <c r="IQ332" s="1">
+        <v>892406526</v>
+      </c>
+      <c r="IR332" t="s">
+        <v>2548</v>
+      </c>
+      <c r="IS332" s="1">
+        <v>46308.400879629633</v>
+      </c>
+      <c r="IU332" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW332" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX332" t="s">
+        <v>2549</v>
+      </c>
+      <c r="IY332">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A333" s="1">
+        <v>46308.582957048609</v>
+      </c>
+      <c r="B333" s="1">
+        <v>46308.588726030102</v>
+      </c>
+      <c r="C333" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D333" t="s">
+        <v>690</v>
+      </c>
+      <c r="E333" t="s">
+        <v>196</v>
+      </c>
+      <c r="F333" t="s">
+        <v>777</v>
+      </c>
+      <c r="G333" t="s">
+        <v>198</v>
+      </c>
+      <c r="H333" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX333" t="s">
+        <v>2025</v>
+      </c>
+      <c r="AY333" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ333" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA333" t="s">
+        <v>2550</v>
+      </c>
+      <c r="BB333">
+        <v>2</v>
+      </c>
+      <c r="BC333">
+        <v>5</v>
+      </c>
+      <c r="BD333" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE333" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF333" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG333" t="s">
+        <v>2551</v>
+      </c>
+      <c r="BH333" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI333" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ333" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK333">
+        <v>4</v>
+      </c>
+      <c r="BL333" t="s">
+        <v>2012</v>
+      </c>
+      <c r="BM333">
+        <v>45</v>
+      </c>
+      <c r="BN333">
+        <v>6</v>
+      </c>
+      <c r="BO333" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP333" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ333" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BS333" t="s">
+        <v>2552</v>
+      </c>
+      <c r="BT333" t="s">
+        <v>2553</v>
+      </c>
+      <c r="BU333" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW333" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX333" t="s">
+        <v>2554</v>
+      </c>
+      <c r="EY333" s="1"/>
+      <c r="GQ333" s="1"/>
+      <c r="GR333" s="1"/>
+      <c r="GY333" s="1"/>
+      <c r="GZ333" s="1"/>
+      <c r="HA333" s="1"/>
+      <c r="HB333" s="1"/>
+      <c r="IQ333" s="1">
+        <v>892486784</v>
+      </c>
+      <c r="IR333" t="s">
+        <v>2555</v>
+      </c>
+      <c r="IS333" s="1">
+        <v>46308.463761574072</v>
+      </c>
+      <c r="IU333" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW333" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX333" t="s">
+        <v>2556</v>
+      </c>
+      <c r="IY333">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A334" s="1">
+        <v>46308.826819849543</v>
+      </c>
+      <c r="B334" s="1">
+        <v>46308.830797939823</v>
+      </c>
+      <c r="C334" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D334" t="s">
+        <v>690</v>
+      </c>
+      <c r="E334" t="s">
+        <v>210</v>
+      </c>
+      <c r="F334" t="s">
+        <v>970</v>
+      </c>
+      <c r="G334" t="s">
+        <v>198</v>
+      </c>
+      <c r="H334" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX334" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY334" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ334" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA334" t="s">
+        <v>2557</v>
+      </c>
+      <c r="BB334">
+        <v>1</v>
+      </c>
+      <c r="BC334">
+        <v>4</v>
+      </c>
+      <c r="BD334" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE334" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF334" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG334" t="s">
+        <v>2558</v>
+      </c>
+      <c r="BH334" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI334" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ334" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK334">
+        <v>6</v>
+      </c>
+      <c r="BL334" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM334">
+        <v>495</v>
+      </c>
+      <c r="BN334">
+        <v>300</v>
+      </c>
+      <c r="BO334" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP334" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ334" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS334" t="s">
+        <v>2559</v>
+      </c>
+      <c r="BT334" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU334" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV334" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BW334" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX334" t="s">
+        <v>2560</v>
+      </c>
+      <c r="EY334" s="1"/>
+      <c r="GQ334" s="1"/>
+      <c r="GR334" s="1"/>
+      <c r="GY334" s="1"/>
+      <c r="GZ334" s="1"/>
+      <c r="HA334" s="1"/>
+      <c r="HB334" s="1"/>
+      <c r="IQ334" s="1">
+        <v>892783502</v>
+      </c>
+      <c r="IR334" t="s">
+        <v>2561</v>
+      </c>
+      <c r="IS334" s="1">
+        <v>46308.70584490741</v>
+      </c>
+      <c r="IU334" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW334" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX334" t="s">
+        <v>2562</v>
+      </c>
+      <c r="IY334">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A335" s="1">
+        <v>46308.830801377313</v>
+      </c>
+      <c r="B335" s="1">
+        <v>46308.833384583333</v>
+      </c>
+      <c r="C335" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D335" t="s">
+        <v>690</v>
+      </c>
+      <c r="E335" t="s">
+        <v>210</v>
+      </c>
+      <c r="F335" t="s">
+        <v>970</v>
+      </c>
+      <c r="G335" t="s">
+        <v>198</v>
+      </c>
+      <c r="H335" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX335" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY335" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ335" t="s">
+        <v>1717</v>
+      </c>
+      <c r="BA335" t="s">
+        <v>1626</v>
+      </c>
+      <c r="BB335">
+        <v>2</v>
+      </c>
+      <c r="BC335">
+        <v>0</v>
+      </c>
+      <c r="BD335" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE335" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF335" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG335" t="s">
+        <v>2563</v>
+      </c>
+      <c r="BH335" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI335" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ335" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK335">
+        <v>2</v>
+      </c>
+      <c r="BL335" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM335">
+        <v>25</v>
+      </c>
+      <c r="BN335">
+        <v>40</v>
+      </c>
+      <c r="BO335" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP335" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ335" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS335" t="s">
+        <v>954</v>
+      </c>
+      <c r="BT335" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU335" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV335" t="s">
+        <v>954</v>
+      </c>
+      <c r="BW335" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX335" t="s">
+        <v>2564</v>
+      </c>
+      <c r="EY335" s="1"/>
+      <c r="GQ335" s="1"/>
+      <c r="GR335" s="1"/>
+      <c r="GY335" s="1"/>
+      <c r="GZ335" s="1"/>
+      <c r="HA335" s="1"/>
+      <c r="HB335" s="1"/>
+      <c r="IQ335" s="1">
+        <v>892786101</v>
+      </c>
+      <c r="IR335" t="s">
+        <v>2565</v>
+      </c>
+      <c r="IS335" s="1">
+        <v>46308.708414351851</v>
+      </c>
+      <c r="IU335" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW335" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX335" t="s">
+        <v>2566</v>
+      </c>
+      <c r="IY335">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A336" s="1">
+        <v>46302.448508472233</v>
+      </c>
+      <c r="B336" s="1">
+        <v>46309.452078946757</v>
+      </c>
+      <c r="C336" s="1">
+        <v>46302</v>
+      </c>
+      <c r="D336" t="s">
+        <v>691</v>
+      </c>
+      <c r="E336" t="s">
+        <v>309</v>
+      </c>
+      <c r="F336" t="s">
+        <v>2157</v>
+      </c>
+      <c r="G336" t="s">
+        <v>198</v>
+      </c>
+      <c r="H336" t="s">
+        <v>311</v>
+      </c>
+      <c r="J336" t="s">
+        <v>2567</v>
+      </c>
+      <c r="K336" t="s">
+        <v>201</v>
+      </c>
+      <c r="L336" t="s">
+        <v>324</v>
+      </c>
+      <c r="M336" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N336" t="s">
+        <v>1709</v>
+      </c>
+      <c r="O336" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH336">
+        <v>680</v>
+      </c>
+      <c r="AI336">
+        <v>0</v>
+      </c>
+      <c r="AJ336">
+        <v>0</v>
+      </c>
+      <c r="AK336">
+        <v>3</v>
+      </c>
+      <c r="AL336">
+        <v>2</v>
+      </c>
+      <c r="AM336">
+        <v>50</v>
+      </c>
+      <c r="AN336">
+        <v>0</v>
+      </c>
+      <c r="AO336" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AP336">
+        <v>1</v>
+      </c>
+      <c r="AQ336" t="s">
+        <v>2051</v>
+      </c>
+      <c r="AR336" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS336" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT336" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU336" t="s">
+        <v>202</v>
+      </c>
+      <c r="AV336" t="s">
+        <v>204</v>
+      </c>
+      <c r="AW336" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS336" t="s">
+        <v>2568</v>
+      </c>
+      <c r="BT336" t="s">
+        <v>2569</v>
+      </c>
+      <c r="BU336" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW336" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX336" t="s">
+        <v>2570</v>
+      </c>
+      <c r="EY336" s="1"/>
+      <c r="GQ336" s="1"/>
+      <c r="GR336" s="1"/>
+      <c r="GY336" s="1"/>
+      <c r="GZ336" s="1"/>
+      <c r="HA336" s="1"/>
+      <c r="HB336" s="1"/>
+      <c r="IQ336" s="1">
+        <v>893143974</v>
+      </c>
+      <c r="IR336" t="s">
+        <v>2571</v>
+      </c>
+      <c r="IS336" s="1">
+        <v>46309.327106481483</v>
+      </c>
+      <c r="IU336" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW336" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX336" t="s">
+        <v>2572</v>
+      </c>
+      <c r="IY336">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A337" s="1">
+        <v>46309.452083784723</v>
+      </c>
+      <c r="B337" s="1">
+        <v>46309.478267418977</v>
+      </c>
+      <c r="C337" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D337" t="s">
+        <v>690</v>
+      </c>
+      <c r="E337" t="s">
+        <v>309</v>
+      </c>
+      <c r="F337" t="s">
+        <v>2573</v>
+      </c>
+      <c r="G337" t="s">
+        <v>198</v>
+      </c>
+      <c r="H337" t="s">
+        <v>311</v>
+      </c>
+      <c r="AX337" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY337" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ337" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA337" t="s">
+        <v>2574</v>
+      </c>
+      <c r="BB337">
+        <v>6</v>
+      </c>
+      <c r="BC337">
+        <v>1</v>
+      </c>
+      <c r="BD337" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE337" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF337" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG337" t="s">
+        <v>2575</v>
+      </c>
+      <c r="BH337" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI337" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ337" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK337">
+        <v>0</v>
+      </c>
+      <c r="BL337" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM337">
+        <v>1</v>
+      </c>
+      <c r="BN337">
+        <v>3</v>
+      </c>
+      <c r="BO337" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP337" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ337" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS337" t="s">
+        <v>2576</v>
+      </c>
+      <c r="BT337" t="s">
+        <v>2577</v>
+      </c>
+      <c r="BU337" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW337" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX337" t="s">
+        <v>2578</v>
+      </c>
+      <c r="EY337" s="1"/>
+      <c r="GQ337" s="1"/>
+      <c r="GR337" s="1"/>
+      <c r="GY337" s="1"/>
+      <c r="GZ337" s="1"/>
+      <c r="HA337" s="1"/>
+      <c r="HB337" s="1"/>
+      <c r="IQ337" s="1">
+        <v>893177080</v>
+      </c>
+      <c r="IR337" t="s">
+        <v>2579</v>
+      </c>
+      <c r="IS337" s="1">
+        <v>46309.353298611109</v>
+      </c>
+      <c r="IU337" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW337" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX337" t="s">
+        <v>2580</v>
+      </c>
+      <c r="IY337">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A338" s="1">
+        <v>46309.478270914347</v>
+      </c>
+      <c r="B338" s="1">
+        <v>46309.492943310193</v>
+      </c>
+      <c r="C338" s="1">
+        <v>46309</v>
+      </c>
+      <c r="D338" t="s">
+        <v>690</v>
+      </c>
+      <c r="E338" t="s">
+        <v>309</v>
+      </c>
+      <c r="F338" t="s">
+        <v>2581</v>
+      </c>
+      <c r="G338" t="s">
+        <v>198</v>
+      </c>
+      <c r="H338" t="s">
+        <v>311</v>
+      </c>
+      <c r="AX338" t="s">
+        <v>2025</v>
+      </c>
+      <c r="AY338" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ338" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA338" t="s">
+        <v>2582</v>
+      </c>
+      <c r="BB338">
+        <v>5</v>
+      </c>
+      <c r="BC338">
+        <v>10</v>
+      </c>
+      <c r="BD338" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE338" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF338" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG338" t="s">
+        <v>2583</v>
+      </c>
+      <c r="BH338" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI338" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ338" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK338">
+        <v>5</v>
+      </c>
+      <c r="BL338" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM338">
+        <v>2</v>
+      </c>
+      <c r="BN338">
+        <v>33</v>
+      </c>
+      <c r="BO338" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP338" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BQ338" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS338" t="s">
+        <v>2584</v>
+      </c>
+      <c r="BT338" t="s">
+        <v>2585</v>
+      </c>
+      <c r="BU338" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW338" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX338" t="s">
+        <v>2586</v>
+      </c>
+      <c r="EY338" s="1"/>
+      <c r="GQ338" s="1"/>
+      <c r="GR338" s="1"/>
+      <c r="GY338" s="1"/>
+      <c r="GZ338" s="1"/>
+      <c r="HA338" s="1"/>
+      <c r="HB338" s="1"/>
+      <c r="IQ338" s="1">
+        <v>893196369</v>
+      </c>
+      <c r="IR338" t="s">
+        <v>2587</v>
+      </c>
+      <c r="IS338" s="1">
+        <v>46309.367986111109</v>
+      </c>
+      <c r="IU338" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW338" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX338" t="s">
+        <v>2588</v>
+      </c>
+      <c r="IY338">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A339" s="1">
+        <v>46308.588728125003</v>
+      </c>
+      <c r="B339" s="1">
+        <v>46309.696014097222</v>
+      </c>
+      <c r="C339" s="1">
+        <v>46309</v>
+      </c>
+      <c r="D339" t="s">
+        <v>690</v>
+      </c>
+      <c r="E339" t="s">
+        <v>196</v>
+      </c>
+      <c r="F339" t="s">
+        <v>228</v>
+      </c>
+      <c r="G339" t="s">
+        <v>198</v>
+      </c>
+      <c r="H339" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX339" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY339" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ339" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA339" t="s">
+        <v>2589</v>
+      </c>
+      <c r="BB339">
+        <v>4</v>
+      </c>
+      <c r="BC339">
+        <v>6</v>
+      </c>
+      <c r="BD339" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE339" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF339" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG339" t="s">
+        <v>2590</v>
+      </c>
+      <c r="BH339" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI339" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ339" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK339">
+        <v>8</v>
+      </c>
+      <c r="BL339" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM339">
+        <v>158</v>
+      </c>
+      <c r="BN339">
+        <v>126</v>
+      </c>
+      <c r="BO339" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP339" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ339" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS339" t="s">
+        <v>2591</v>
+      </c>
+      <c r="BT339" t="s">
+        <v>2592</v>
+      </c>
+      <c r="BU339" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW339" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX339" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY339" s="1"/>
+      <c r="GQ339" s="1"/>
+      <c r="GR339" s="1"/>
+      <c r="GY339" s="1"/>
+      <c r="GZ339" s="1"/>
+      <c r="HA339" s="1"/>
+      <c r="HB339" s="1"/>
+      <c r="IQ339" s="1">
+        <v>893475254</v>
+      </c>
+      <c r="IR339" t="s">
+        <v>2593</v>
+      </c>
+      <c r="IS339" s="1">
+        <v>46309.57104166667</v>
+      </c>
+      <c r="IU339" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW339" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX339" t="s">
+        <v>2594</v>
+      </c>
+      <c r="IY339">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A340" s="1">
+        <v>46309.700310613429</v>
+      </c>
+      <c r="B340" s="1">
+        <v>46309.704765752307</v>
+      </c>
+      <c r="C340" s="1">
+        <v>46309</v>
+      </c>
+      <c r="D340" t="s">
+        <v>690</v>
+      </c>
+      <c r="E340" t="s">
+        <v>196</v>
+      </c>
+      <c r="F340" t="s">
+        <v>289</v>
+      </c>
+      <c r="G340" t="s">
+        <v>198</v>
+      </c>
+      <c r="H340" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX340" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY340" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ340" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA340" t="s">
+        <v>2595</v>
+      </c>
+      <c r="BB340">
+        <v>3</v>
+      </c>
+      <c r="BC340">
+        <v>0</v>
+      </c>
+      <c r="BD340" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE340" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF340" t="s">
+        <v>1627</v>
+      </c>
+      <c r="BG340" t="s">
+        <v>2596</v>
+      </c>
+      <c r="BH340" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI340" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ340" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK340">
+        <v>3</v>
+      </c>
+      <c r="BL340" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM340">
+        <v>30</v>
+      </c>
+      <c r="BN340">
+        <v>45</v>
+      </c>
+      <c r="BO340" t="s">
+        <v>327</v>
+      </c>
+      <c r="BP340" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ340" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS340" t="s">
+        <v>2597</v>
+      </c>
+      <c r="BT340" t="s">
+        <v>2598</v>
+      </c>
+      <c r="BU340" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW340" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX340" t="s">
+        <v>1119</v>
+      </c>
+      <c r="EY340" s="1"/>
+      <c r="GQ340" s="1"/>
+      <c r="GR340" s="1"/>
+      <c r="GY340" s="1"/>
+      <c r="GZ340" s="1"/>
+      <c r="HA340" s="1"/>
+      <c r="HB340" s="1"/>
+      <c r="IQ340" s="1">
+        <v>893490198</v>
+      </c>
+      <c r="IR340" t="s">
+        <v>2599</v>
+      </c>
+      <c r="IS340" s="1">
+        <v>46309.579780092587</v>
+      </c>
+      <c r="IU340" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW340" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX340" t="s">
+        <v>2600</v>
+      </c>
+      <c r="IY340">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A341" s="1">
+        <v>46309.797192349542</v>
+      </c>
+      <c r="B341" s="1">
+        <v>46309.802370324083</v>
+      </c>
+      <c r="C341" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D341" t="s">
+        <v>690</v>
+      </c>
+      <c r="E341" t="s">
+        <v>254</v>
+      </c>
+      <c r="F341" t="s">
+        <v>765</v>
+      </c>
+      <c r="G341" t="s">
+        <v>198</v>
+      </c>
+      <c r="H341" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX341" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY341" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ341" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA341" t="s">
+        <v>2601</v>
+      </c>
+      <c r="BB341">
+        <v>4</v>
+      </c>
+      <c r="BC341">
+        <v>2</v>
+      </c>
+      <c r="BD341" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE341" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF341" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG341" t="s">
+        <v>2602</v>
+      </c>
+      <c r="BH341" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI341" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ341" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK341">
+        <v>4</v>
+      </c>
+      <c r="BL341" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM341">
+        <v>48</v>
+      </c>
+      <c r="BN341">
+        <v>32</v>
+      </c>
+      <c r="BO341" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP341" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ341" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS341" t="s">
+        <v>2603</v>
+      </c>
+      <c r="BT341" t="s">
+        <v>2604</v>
+      </c>
+      <c r="BU341" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW341" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX341" t="s">
+        <v>2605</v>
+      </c>
+      <c r="EY341" s="1"/>
+      <c r="GQ341" s="1"/>
+      <c r="GR341" s="1"/>
+      <c r="GY341" s="1"/>
+      <c r="GZ341" s="1"/>
+      <c r="HA341" s="1"/>
+      <c r="HB341" s="1"/>
+      <c r="IQ341" s="1">
+        <v>893649948</v>
+      </c>
+      <c r="IR341" t="s">
+        <v>2606</v>
+      </c>
+      <c r="IS341" s="1">
+        <v>46309.677384259259</v>
+      </c>
+      <c r="IU341" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW341" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX341" t="s">
+        <v>2607</v>
+      </c>
+      <c r="IY341">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="342" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A342" s="1">
+        <v>46309.802371759259</v>
+      </c>
+      <c r="B342" s="1">
+        <v>46309.805187800928</v>
+      </c>
+      <c r="C342" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D342" t="s">
+        <v>690</v>
+      </c>
+      <c r="E342" t="s">
+        <v>254</v>
+      </c>
+      <c r="F342" t="s">
+        <v>765</v>
+      </c>
+      <c r="G342" t="s">
+        <v>198</v>
+      </c>
+      <c r="H342" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX342" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY342" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ342" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA342" t="s">
+        <v>1596</v>
+      </c>
+      <c r="BB342">
+        <v>8</v>
+      </c>
+      <c r="BC342">
+        <v>2</v>
+      </c>
+      <c r="BD342" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE342" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF342" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG342" t="s">
+        <v>2608</v>
+      </c>
+      <c r="BH342" t="s">
+        <v>327</v>
+      </c>
+      <c r="BI342" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ342" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK342">
+        <v>5</v>
+      </c>
+      <c r="BL342" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM342">
+        <v>86</v>
+      </c>
+      <c r="BN342">
+        <v>134</v>
+      </c>
+      <c r="BO342" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP342" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ342" t="s">
+        <v>1982</v>
+      </c>
+      <c r="BS342" t="s">
+        <v>2609</v>
+      </c>
+      <c r="BT342" t="s">
+        <v>2610</v>
+      </c>
+      <c r="BU342" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV342" t="s">
+        <v>292</v>
+      </c>
+      <c r="BW342" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX342" t="s">
+        <v>2611</v>
+      </c>
+      <c r="EY342" s="1"/>
+      <c r="GQ342" s="1"/>
+      <c r="GR342" s="1"/>
+      <c r="GY342" s="1"/>
+      <c r="GZ342" s="1"/>
+      <c r="HA342" s="1"/>
+      <c r="HB342" s="1"/>
+      <c r="IQ342" s="1">
+        <v>893654614</v>
+      </c>
+      <c r="IR342" t="s">
+        <v>2612</v>
+      </c>
+      <c r="IS342" s="1">
+        <v>46309.680289351847</v>
+      </c>
+      <c r="IU342" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW342" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX342" t="s">
+        <v>2613</v>
+      </c>
+      <c r="IY342">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="343" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A343" s="1">
+        <v>46309.805189317129</v>
+      </c>
+      <c r="B343" s="1">
+        <v>46309.811969710638</v>
+      </c>
+      <c r="C343" s="1">
+        <v>46309</v>
+      </c>
+      <c r="D343" t="s">
+        <v>690</v>
+      </c>
+      <c r="E343" t="s">
+        <v>254</v>
+      </c>
+      <c r="F343" t="s">
+        <v>267</v>
+      </c>
+      <c r="G343" t="s">
+        <v>198</v>
+      </c>
+      <c r="H343" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX343" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY343" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ343" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BA343" t="s">
+        <v>2614</v>
+      </c>
+      <c r="BB343">
+        <v>78</v>
+      </c>
+      <c r="BC343">
+        <v>123</v>
+      </c>
+      <c r="BD343" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE343" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF343" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG343" t="s">
+        <v>2615</v>
+      </c>
+      <c r="BH343" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI343" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ343" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK343">
+        <v>6</v>
+      </c>
+      <c r="BL343" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM343">
+        <v>78</v>
+      </c>
+      <c r="BN343">
+        <v>123</v>
+      </c>
+      <c r="BO343" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP343" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ343" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS343" t="s">
+        <v>2616</v>
+      </c>
+      <c r="BT343" t="s">
+        <v>2617</v>
+      </c>
+      <c r="BU343" t="s">
+        <v>1638</v>
+      </c>
+      <c r="BW343" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX343" t="s">
+        <v>2618</v>
+      </c>
+      <c r="EY343" s="1"/>
+      <c r="GQ343" s="1"/>
+      <c r="GR343" s="1"/>
+      <c r="GY343" s="1"/>
+      <c r="GZ343" s="1"/>
+      <c r="HA343" s="1"/>
+      <c r="HB343" s="1"/>
+      <c r="IQ343" s="1">
+        <v>893664930</v>
+      </c>
+      <c r="IR343" t="s">
+        <v>2619</v>
+      </c>
+      <c r="IS343" s="1">
+        <v>46309.686990740738</v>
+      </c>
+      <c r="IU343" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW343" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX343" t="s">
+        <v>2620</v>
+      </c>
+      <c r="IY343">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="344" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A344" s="1">
+        <v>46309.811972060183</v>
+      </c>
+      <c r="B344" s="1">
+        <v>46309.822535856481</v>
+      </c>
+      <c r="C344" s="1">
+        <v>46309</v>
+      </c>
+      <c r="D344" t="s">
+        <v>690</v>
+      </c>
+      <c r="E344" t="s">
+        <v>254</v>
+      </c>
+      <c r="F344" t="s">
+        <v>2621</v>
+      </c>
+      <c r="G344" t="s">
+        <v>198</v>
+      </c>
+      <c r="H344" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX344" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AY344" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ344" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA344" t="s">
+        <v>2622</v>
+      </c>
+      <c r="BB344">
+        <v>37</v>
+      </c>
+      <c r="BC344">
+        <v>6</v>
+      </c>
+      <c r="BD344" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE344" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF344" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG344" t="s">
+        <v>2623</v>
+      </c>
+      <c r="BH344" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI344" t="s">
+        <v>327</v>
+      </c>
+      <c r="BJ344" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK344">
+        <v>4</v>
+      </c>
+      <c r="BL344" t="s">
+        <v>1720</v>
+      </c>
+      <c r="BM344">
+        <v>422</v>
+      </c>
+      <c r="BN344">
+        <v>366</v>
+      </c>
+      <c r="BO344" t="s">
+        <v>1721</v>
+      </c>
+      <c r="BP344" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ344" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS344" t="s">
+        <v>2624</v>
+      </c>
+      <c r="BT344" t="s">
+        <v>1282</v>
+      </c>
+      <c r="BU344" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV344" t="s">
+        <v>292</v>
+      </c>
+      <c r="BW344" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX344" t="s">
+        <v>2625</v>
+      </c>
+      <c r="EY344" s="1"/>
+      <c r="GQ344" s="1"/>
+      <c r="GR344" s="1"/>
+      <c r="GY344" s="1"/>
+      <c r="GZ344" s="1"/>
+      <c r="HA344" s="1"/>
+      <c r="HB344" s="1"/>
+      <c r="IQ344" s="1">
+        <v>893677260</v>
+      </c>
+      <c r="IR344" t="s">
+        <v>2626</v>
+      </c>
+      <c r="IS344" s="1">
+        <v>46309.697604166657</v>
+      </c>
+      <c r="IU344" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW344" t="s">
+        <v>1803</v>
+      </c>
+      <c r="IX344" t="s">
+        <v>2627</v>
+      </c>
+      <c r="IY344">
+        <v>343</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="523" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{296F2BD9-0679-C548-8CD6-D12FAF436C2F}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD4636AF-6C5B-D849-9EB7-1A7A1925CD02}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="2580" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2240" yWindow="2320" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Public Health Emergencies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -21890,7 +21890,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -22241,7 +22241,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY344" totalsRowShown="0">
-  <autoFilter ref="A1:IY344" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+  <autoFilter ref="A1:IY344" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Tool 7: Community Gatekeeper Dialogue"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -23758,7 +23764,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>46249.414428877317</v>
       </c>
@@ -23844,7 +23850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46249.547709293976</v>
       </c>
@@ -23960,7 +23966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46250.286187777783</v>
       </c>
@@ -24073,7 +24079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>46250.46087855324</v>
       </c>
@@ -24159,7 +24165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>46250.466584988433</v>
       </c>
@@ -24245,7 +24251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>46250.497120729167</v>
       </c>
@@ -24346,7 +24352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46250.533912256942</v>
       </c>
@@ -24432,7 +24438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>46250.537403483802</v>
       </c>
@@ -24536,7 +24542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46250.540434641203</v>
       </c>
@@ -24637,7 +24643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46250.414366365738</v>
       </c>
@@ -24744,7 +24750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46250.624036134257</v>
       </c>
@@ -24845,7 +24851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46250.632341759258</v>
       </c>
@@ -24925,7 +24931,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>46250.641756342593</v>
       </c>
@@ -25008,7 +25014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>46250.294262037038</v>
       </c>
@@ -25121,7 +25127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>46252.447340914347</v>
       </c>
@@ -25228,7 +25234,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>46254.584788715278</v>
       </c>
@@ -25341,7 +25347,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>46254.605106875002</v>
       </c>
@@ -25454,7 +25460,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>46254.600437835637</v>
       </c>
@@ -25567,7 +25573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>46254.607456979167</v>
       </c>
@@ -25680,7 +25686,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>46254.607334918983</v>
       </c>
@@ -25796,7 +25802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>46251.696995150473</v>
       </c>
@@ -26001,7 +26007,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>46250.644191562496</v>
       </c>
@@ -26111,7 +26117,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>46254.679082291666</v>
       </c>
@@ -26224,7 +26230,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>46258.698712662037</v>
       </c>
@@ -26337,7 +26343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>46258.704543402782</v>
       </c>
@@ -26450,7 +26456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>46286.486514849537</v>
       </c>
@@ -26554,7 +26560,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>46287.464698229167</v>
       </c>
@@ -26709,7 +26715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>46287.502297326391</v>
       </c>
@@ -26813,7 +26819,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>46254.648548703713</v>
       </c>
@@ -26917,7 +26923,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>46287.510715671298</v>
       </c>
@@ -27057,7 +27063,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>46287.534076979173</v>
       </c>
@@ -27215,7 +27221,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>46287.519374965283</v>
       </c>
@@ -27373,7 +27379,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>46288.399354398149</v>
       </c>
@@ -27474,7 +27480,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>46287.692998923609</v>
       </c>
@@ -27575,7 +27581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>46288.44941760417</v>
       </c>
@@ -27676,7 +27682,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>46288.434134374998</v>
       </c>
@@ -27834,7 +27840,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>46288.494234097219</v>
       </c>
@@ -27992,7 +27998,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>46288.347859687499</v>
       </c>
@@ -28096,7 +28102,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>46288.565498645832</v>
       </c>
@@ -28254,7 +28260,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>46288.55452568287</v>
       </c>
@@ -28409,7 +28415,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>46288.580843194453</v>
       </c>
@@ -28510,7 +28516,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>46288.629755868053</v>
       </c>
@@ -28614,7 +28620,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>46287.534877442129</v>
       </c>
@@ -28715,7 +28721,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>46288.642067997687</v>
       </c>
@@ -28819,7 +28825,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46288.66133771991</v>
       </c>
@@ -28920,7 +28926,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46288.465177546299</v>
       </c>
@@ -29024,7 +29030,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>46288.522137094908</v>
       </c>
@@ -29179,7 +29185,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46288.678131909721</v>
       </c>
@@ -29280,7 +29286,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>46289.400980995371</v>
       </c>
@@ -29384,7 +29390,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>46289.412856574083</v>
       </c>
@@ -29542,7 +29548,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>46289.416582500002</v>
       </c>
@@ -29697,7 +29703,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>46289.457423287036</v>
       </c>
@@ -29798,7 +29804,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>46289.480812314818</v>
       </c>
@@ -29899,7 +29905,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>46289.500007476847</v>
       </c>
@@ -30000,7 +30006,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>46289.513280347222</v>
       </c>
@@ -30155,7 +30161,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>46289.544489988417</v>
       </c>
@@ -30313,7 +30319,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>46289.516512256952</v>
       </c>
@@ -30560,7 +30566,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>46289.587290000003</v>
       </c>
@@ -30670,7 +30676,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>46289.554760902778</v>
       </c>
@@ -30771,7 +30777,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>46289.634438969908</v>
       </c>
@@ -30929,7 +30935,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>46289.67084796296</v>
       </c>
@@ -31119,7 +31125,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>46289.762437013887</v>
       </c>
@@ -31223,7 +31229,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>46289.776139745372</v>
       </c>
@@ -31327,7 +31333,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>46289.376371157407</v>
       </c>
@@ -31428,7 +31434,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>46289.780517430547</v>
       </c>
@@ -31532,7 +31538,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>46289.364937314807</v>
       </c>
@@ -31633,7 +31639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>46289.417317129628</v>
       </c>
@@ -31788,7 +31794,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>46289.470136354168</v>
       </c>
@@ -31889,7 +31895,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>46290.410415590282</v>
       </c>
@@ -32047,7 +32053,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>46254.660598761577</v>
       </c>
@@ -32154,7 +32160,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>46290.505176122693</v>
       </c>
@@ -32430,7 +32436,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>46290.580511817127</v>
       </c>
@@ -32531,7 +32537,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>46290.598360659722</v>
       </c>
@@ -32635,7 +32641,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>46290.579465543982</v>
       </c>
@@ -32739,7 +32745,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>46290.758861805552</v>
       </c>
@@ -32849,7 +32855,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>46290.782907303241</v>
       </c>
@@ -32953,7 +32959,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>46290.808730833327</v>
       </c>
@@ -33111,7 +33117,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>46290.814761828697</v>
       </c>
@@ -33269,7 +33275,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>46290.824045995367</v>
       </c>
@@ -33370,7 +33376,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>46290.843395416668</v>
       </c>
@@ -33480,7 +33486,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>46290.847394305558</v>
       </c>
@@ -33584,7 +33590,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>46290.854527256954</v>
       </c>
@@ -33742,7 +33748,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>46293.365824699067</v>
       </c>
@@ -33840,7 +33846,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>46293.48316689815</v>
       </c>
@@ -33947,7 +33953,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>46293.491838668982</v>
       </c>
@@ -34042,7 +34048,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>46293.50166144676</v>
       </c>
@@ -34140,7 +34146,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>46293.511540266198</v>
       </c>
@@ -34235,7 +34241,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>46293.515931678237</v>
       </c>
@@ -34330,7 +34336,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>46292.875610428237</v>
       </c>
@@ -34434,7 +34440,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>46293.525056585648</v>
       </c>
@@ -34532,7 +34538,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>46293.462860451393</v>
       </c>
@@ -34645,7 +34651,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>46293.542157442127</v>
       </c>
@@ -34761,7 +34767,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>46289.549434942128</v>
       </c>
@@ -34871,7 +34877,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>46288.648351516204</v>
       </c>
@@ -35026,7 +35032,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>46293.729340034719</v>
       </c>
@@ -35136,7 +35142,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>46293.732859988428</v>
       </c>
@@ -35237,7 +35243,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>46293.73679451389</v>
       </c>
@@ -35338,7 +35344,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>46293.731438472219</v>
       </c>
@@ -35442,7 +35448,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>46293.815275972222</v>
       </c>
@@ -35546,7 +35552,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>46293.823807754627</v>
       </c>
@@ -35650,7 +35656,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>46293.803378958342</v>
       </c>
@@ -35793,7 +35799,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>46293.813637777777</v>
       </c>
@@ -35897,7 +35903,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>46293.816578796293</v>
       </c>
@@ -36013,7 +36019,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>46293.625744837962</v>
       </c>
@@ -36120,7 +36126,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>46294.488265138891</v>
       </c>
@@ -36236,7 +36242,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>46294.552163206019</v>
       </c>
@@ -36337,7 +36343,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>46294.55584572917</v>
       </c>
@@ -36432,7 +36438,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>46293.535828969907</v>
       </c>
@@ -36527,7 +36533,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>46293.556273576389</v>
       </c>
@@ -36622,7 +36628,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>46293.571447662027</v>
       </c>
@@ -36726,7 +36732,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>46293.583647256943</v>
       </c>
@@ -36821,7 +36827,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>46293.585437430564</v>
       </c>
@@ -36937,7 +36943,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>46293.596938391202</v>
       </c>
@@ -37047,7 +37053,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>46294.49139398148</v>
       </c>
@@ -37142,7 +37148,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>46294.586004293982</v>
       </c>
@@ -37246,7 +37252,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>46294.634888472217</v>
       </c>
@@ -37350,7 +37356,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>46294.638466377313</v>
       </c>
@@ -37445,7 +37451,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>46294.640932835653</v>
       </c>
@@ -37549,7 +37555,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>46294.642854039354</v>
       </c>
@@ -37653,7 +37659,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>46294.64522431713</v>
       </c>
@@ -37757,7 +37763,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>46294.684677696758</v>
       </c>
@@ -37855,7 +37861,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>46294.7240499537</v>
       </c>
@@ -37959,7 +37965,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>46294.740338090283</v>
       </c>
@@ -38060,7 +38066,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>46294.739667569447</v>
       </c>
@@ -38164,7 +38170,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>46294.755193831021</v>
       </c>
@@ -38265,7 +38271,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>46294.75193539352</v>
       </c>
@@ -38369,7 +38375,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>46294.761264895831</v>
       </c>
@@ -38473,7 +38479,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>46294.754593750004</v>
       </c>
@@ -38577,7 +38583,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>46294.757487442133</v>
       </c>
@@ -38681,7 +38687,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>46294.760891759259</v>
       </c>
@@ -38785,7 +38791,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>46294.776597719909</v>
       </c>
@@ -38889,7 +38895,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>46294.795517766201</v>
       </c>
@@ -38993,7 +38999,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>46294.799215694453</v>
       </c>
@@ -39097,7 +39103,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>46294.802037627313</v>
       </c>
@@ -39201,7 +39207,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>46294.620284849538</v>
       </c>
@@ -39317,7 +39323,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>46294.750292604163</v>
       </c>
@@ -39421,7 +39427,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>46294.75457420139</v>
       </c>
@@ -39525,7 +39531,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>46294.76850484954</v>
       </c>
@@ -39629,7 +39635,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>46294.770551990739</v>
       </c>
@@ -39733,7 +39739,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>46294.77235269676</v>
       </c>
@@ -39837,7 +39843,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>46294.774383877317</v>
       </c>
@@ -39941,7 +39947,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>46295.431909814812</v>
       </c>
@@ -40039,7 +40045,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>46294.713914699067</v>
       </c>
@@ -40143,7 +40149,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>46295.534696747687</v>
       </c>
@@ -40247,7 +40253,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>46295.537180023151</v>
       </c>
@@ -40351,7 +40357,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>46295.538939444443</v>
       </c>
@@ -40455,7 +40461,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>46295.541104618052</v>
       </c>
@@ -40559,7 +40565,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>46294.620388888892</v>
       </c>
@@ -40669,7 +40675,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>46295.648789212973</v>
       </c>
@@ -40951,7 +40957,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>46295.701731238427</v>
       </c>
@@ -41058,7 +41064,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>46295.704093333326</v>
       </c>
@@ -41174,7 +41180,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>46295.709935613428</v>
       </c>
@@ -41290,7 +41296,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>46295.71365740741</v>
       </c>
@@ -41385,7 +41391,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>46295.716885624999</v>
       </c>
@@ -41501,7 +41507,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>46295.665477905102</v>
       </c>
@@ -41611,7 +41617,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>46295.813936377323</v>
       </c>
@@ -41715,7 +41721,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>46295.822483449083</v>
       </c>
@@ -41819,7 +41825,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>46295.82530034722</v>
       </c>
@@ -41923,7 +41929,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>46295.82738480324</v>
       </c>
@@ -42027,7 +42033,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>46295.831523148147</v>
       </c>
@@ -42131,7 +42137,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>46295.870190428242</v>
       </c>
@@ -42226,7 +42232,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>46295.421994247678</v>
       </c>
@@ -42321,7 +42327,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>46295.425309699072</v>
       </c>
@@ -42425,7 +42431,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>46295.428430567132</v>
       </c>
@@ -42520,7 +42526,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>46295.43050869213</v>
       </c>
@@ -42615,7 +42621,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>46295.491448726847</v>
       </c>
@@ -42719,7 +42725,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>46295.497799629629</v>
       </c>
@@ -42823,7 +42829,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>46295.50835103009</v>
       </c>
@@ -42918,7 +42924,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>46295.519981921287</v>
       </c>
@@ -43022,7 +43028,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>46295.621399178242</v>
       </c>
@@ -43117,7 +43123,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>46293.856906226851</v>
       </c>
@@ -43313,7 +43319,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>46295.89000162037</v>
       </c>
@@ -43423,7 +43429,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>46295.876588113417</v>
       </c>
@@ -43533,7 +43539,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>46295.947029872688</v>
       </c>
@@ -43643,7 +43649,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>46296.290502754629</v>
       </c>
@@ -43750,7 +43756,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>46296.293855810189</v>
       </c>
@@ -43908,7 +43914,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>46296.29973741898</v>
       </c>
@@ -44015,7 +44021,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>46296.304758252307</v>
       </c>
@@ -44248,7 +44254,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>46296.414372060193</v>
       </c>
@@ -44352,7 +44358,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>46296.443119699077</v>
       </c>
@@ -44453,7 +44459,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>46296.446367986107</v>
       </c>
@@ -44548,7 +44554,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>46296.452167673611</v>
       </c>
@@ -44643,7 +44649,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>46296.462310613417</v>
       </c>
@@ -44747,7 +44753,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>46296.474542962962</v>
       </c>
@@ -44878,7 +44884,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>46296.517473321757</v>
       </c>
@@ -44982,7 +44988,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>46296.528989340281</v>
       </c>
@@ -45086,7 +45092,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>46296.454655682872</v>
       </c>
@@ -45220,7 +45226,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>46295.956040567129</v>
       </c>
@@ -45471,7 +45477,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>46296.562106122678</v>
       </c>
@@ -45572,7 +45578,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>46296.710014999997</v>
       </c>
@@ -45670,7 +45676,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>46296.716005798611</v>
       </c>
@@ -45777,7 +45783,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>46296.721711759259</v>
       </c>
@@ -45875,7 +45881,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>46296.714952511567</v>
       </c>
@@ -46030,7 +46036,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>46296.724340370369</v>
       </c>
@@ -46140,7 +46146,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>46296.728354641207</v>
       </c>
@@ -46271,7 +46277,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>46296.730641527778</v>
       </c>
@@ -46378,7 +46384,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>46296.657187523153</v>
       </c>
@@ -46513,7 +46519,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>46296.826218819442</v>
       </c>
@@ -46636,7 +46642,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>46296.903357361109</v>
       </c>
@@ -46771,7 +46777,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>46296.906311192128</v>
       </c>
@@ -46885,7 +46891,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>46296.908534444447</v>
       </c>
@@ -47044,7 +47050,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>46297.307513391213</v>
       </c>
@@ -47493,7 +47499,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>46297.595784861107</v>
       </c>
@@ -47598,7 +47604,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>46297.603049039353</v>
       </c>
@@ -47712,7 +47718,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>46297.523460810182</v>
       </c>
@@ -47844,7 +47850,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>46297.616067442133</v>
       </c>
@@ -47949,7 +47955,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>46297.611051006941</v>
       </c>
@@ -48072,7 +48078,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>46297.623010995369</v>
       </c>
@@ -48177,7 +48183,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>46297.629230914346</v>
       </c>
@@ -48291,7 +48297,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>46297.625507025463</v>
       </c>
@@ -48402,7 +48408,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>46297.636685254627</v>
       </c>
@@ -48507,7 +48513,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>46297.642068576388</v>
       </c>
@@ -48609,7 +48615,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>46297.642087673608</v>
       </c>
@@ -48714,7 +48720,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>46297.645297141207</v>
       </c>
@@ -48825,7 +48831,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>46297.647905798607</v>
       </c>
@@ -48936,7 +48942,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>46297.658319340277</v>
       </c>
@@ -49038,7 +49044,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>46297.664371840277</v>
       </c>
@@ -49149,7 +49155,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>46297.697087002307</v>
       </c>
@@ -49251,7 +49257,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>46297.717215694443</v>
       </c>
@@ -49353,7 +49359,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>46297.720690405091</v>
       </c>
@@ -49464,7 +49470,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>46297.726336203697</v>
       </c>
@@ -49575,7 +49581,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>46297.727836921287</v>
       </c>
@@ -49713,7 +49719,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>46297.733303923611</v>
       </c>
@@ -50510,7 +50516,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>46297.645588900457</v>
       </c>
@@ -50763,7 +50769,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>46298.436995810189</v>
       </c>
@@ -50898,7 +50904,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>46294.744592546303</v>
       </c>
@@ -51009,7 +51015,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>46298.477973055553</v>
       </c>
@@ -51280,7 +51286,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>46298.534485775461</v>
       </c>
@@ -51391,7 +51397,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>46298.551648703702</v>
       </c>
@@ -51550,7 +51556,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>46298.56466358796</v>
       </c>
@@ -51691,7 +51697,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>46298.60764490741</v>
       </c>
@@ -51802,7 +51808,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>46298.613122175928</v>
       </c>
@@ -51913,7 +51919,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>46300.650030763893</v>
       </c>
@@ -52127,7 +52133,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>46301.522519942133</v>
       </c>
@@ -52440,7 +52446,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>46301.538739317133</v>
       </c>
@@ -52657,7 +52663,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>46302.423721701387</v>
       </c>
@@ -52795,7 +52801,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>46302.43387108796</v>
       </c>
@@ -52936,7 +52942,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>46302.446020150463</v>
       </c>
@@ -53044,7 +53050,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>46302.438089305557</v>
       </c>
@@ -53445,7 +53451,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>46302.480987708332</v>
       </c>
@@ -53553,7 +53559,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>46302.507625208331</v>
       </c>
@@ -53664,7 +53670,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>46302.632995671287</v>
       </c>
@@ -54038,7 +54044,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>46302.687822835651</v>
       </c>
@@ -54149,7 +54155,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>46302.699748969913</v>
       </c>
@@ -54266,7 +54272,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>46301.806419375003</v>
       </c>
@@ -54449,7 +54455,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>46302.739207951388</v>
       </c>
@@ -54533,7 +54539,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>46302.75280141204</v>
       </c>
@@ -54716,7 +54722,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>46302.860038148137</v>
       </c>
@@ -55063,7 +55069,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>46300.70079787037</v>
       </c>
@@ -55219,7 +55225,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>46303.433600277778</v>
       </c>
@@ -55402,7 +55408,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>46303.446988136573</v>
       </c>
@@ -55715,7 +55721,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>46303.507944050929</v>
       </c>
@@ -55929,7 +55935,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>46303.533923391202</v>
       </c>
@@ -56112,7 +56118,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>46303.602467268523</v>
       </c>
@@ -56295,7 +56301,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>46303.665873425933</v>
       </c>
@@ -56478,7 +56484,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>46303.453409363428</v>
       </c>
@@ -56822,7 +56828,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>46302.837925925924</v>
       </c>
@@ -56906,7 +56912,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>46304.309806493053</v>
       </c>
@@ -57044,7 +57050,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>46302.507222314824</v>
       </c>
@@ -57182,7 +57188,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>46304.399320115743</v>
       </c>
@@ -57320,7 +57326,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>46304.406028958343</v>
       </c>
@@ -57597,7 +57603,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>46304.429592418979</v>
       </c>
@@ -57684,7 +57690,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>46304.440482337966</v>
       </c>
@@ -57765,7 +57771,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>46304.443006539354</v>
       </c>
@@ -57846,7 +57852,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>46304.549563611108</v>
       </c>
@@ -57987,7 +57993,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>46304.552871203698</v>
       </c>
@@ -58173,7 +58179,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>46304.55543482639</v>
       </c>
@@ -58314,7 +58320,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>46304.558062291668</v>
       </c>
@@ -58500,7 +58506,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>46304.560552812502</v>
       </c>
@@ -58590,7 +58596,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>46304.56600979167</v>
       </c>
@@ -58728,7 +58734,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>46304.568548668984</v>
       </c>
@@ -58914,7 +58920,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>46304.572299814812</v>
       </c>
@@ -59100,7 +59106,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>46304.577533622687</v>
       </c>
@@ -60480,7 +60486,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>46304.63213510417</v>
       </c>
@@ -60567,7 +60573,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>46302.81901608796</v>
       </c>
@@ -60750,7 +60756,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>46304.719278657409</v>
       </c>
@@ -61097,7 +61103,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>46304.845099108803</v>
       </c>
@@ -61280,7 +61286,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>46304.904140416656</v>
       </c>
@@ -61358,7 +61364,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>46302.598696724534</v>
       </c>
@@ -61466,7 +61472,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>46304.759218159721</v>
       </c>
@@ -61864,7 +61870,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>46307.915130335648</v>
       </c>
@@ -62002,7 +62008,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>46307.929744861111</v>
       </c>
@@ -62140,7 +62146,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>46307.734356793982</v>
       </c>
@@ -62408,7 +62414,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>46308.522087534722</v>
       </c>
@@ -62942,7 +62948,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:259" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>46302.448508472233</v>
       </c>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="524" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD4636AF-6C5B-D849-9EB7-1A7A1925CD02}"/>
+  <xr:revisionPtr revIDLastSave="525" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEA16BF7-F0D4-9345-960F-8CC17888F775}"/>
   <bookViews>
     <workbookView xWindow="2240" yWindow="2320" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22241,13 +22241,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY344" totalsRowShown="0">
-  <autoFilter ref="A1:IY344" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Tool 7: Community Gatekeeper Dialogue"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:IY344" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -23764,7 +23758,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>46249.414428877317</v>
       </c>
@@ -23850,7 +23844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>46249.547709293976</v>
       </c>
@@ -23966,7 +23960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>46250.286187777783</v>
       </c>
@@ -24079,7 +24073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>46250.46087855324</v>
       </c>
@@ -24165,7 +24159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>46250.466584988433</v>
       </c>
@@ -24251,7 +24245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>46250.497120729167</v>
       </c>
@@ -24352,7 +24346,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>46250.533912256942</v>
       </c>
@@ -24438,7 +24432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>46250.537403483802</v>
       </c>
@@ -24542,7 +24536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>46250.540434641203</v>
       </c>
@@ -24643,7 +24637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>46250.414366365738</v>
       </c>
@@ -24750,7 +24744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>46250.624036134257</v>
       </c>
@@ -24851,7 +24845,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>46250.632341759258</v>
       </c>
@@ -24931,7 +24925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>46250.641756342593</v>
       </c>
@@ -25014,7 +25008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>46250.294262037038</v>
       </c>
@@ -25127,7 +25121,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>46252.447340914347</v>
       </c>
@@ -25234,7 +25228,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>46254.584788715278</v>
       </c>
@@ -25347,7 +25341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>46254.605106875002</v>
       </c>
@@ -25460,7 +25454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>46254.600437835637</v>
       </c>
@@ -25573,7 +25567,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>46254.607456979167</v>
       </c>
@@ -25686,7 +25680,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>46254.607334918983</v>
       </c>
@@ -25802,7 +25796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>46251.696995150473</v>
       </c>
@@ -26007,7 +26001,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>46250.644191562496</v>
       </c>
@@ -26117,7 +26111,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>46254.679082291666</v>
       </c>
@@ -26230,7 +26224,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>46258.698712662037</v>
       </c>
@@ -26343,7 +26337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>46258.704543402782</v>
       </c>
@@ -26456,7 +26450,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>46286.486514849537</v>
       </c>
@@ -26560,7 +26554,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>46287.464698229167</v>
       </c>
@@ -26715,7 +26709,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>46287.502297326391</v>
       </c>
@@ -26819,7 +26813,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>46254.648548703713</v>
       </c>
@@ -26923,7 +26917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>46287.510715671298</v>
       </c>
@@ -27063,7 +27057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>46287.534076979173</v>
       </c>
@@ -27221,7 +27215,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>46287.519374965283</v>
       </c>
@@ -27379,7 +27373,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>46288.399354398149</v>
       </c>
@@ -27480,7 +27474,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>46287.692998923609</v>
       </c>
@@ -27581,7 +27575,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>46288.44941760417</v>
       </c>
@@ -27682,7 +27676,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>46288.434134374998</v>
       </c>
@@ -27840,7 +27834,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>46288.494234097219</v>
       </c>
@@ -27998,7 +27992,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>46288.347859687499</v>
       </c>
@@ -28102,7 +28096,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>46288.565498645832</v>
       </c>
@@ -28260,7 +28254,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>46288.55452568287</v>
       </c>
@@ -28415,7 +28409,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>46288.580843194453</v>
       </c>
@@ -28516,7 +28510,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>46288.629755868053</v>
       </c>
@@ -28620,7 +28614,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>46287.534877442129</v>
       </c>
@@ -28721,7 +28715,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>46288.642067997687</v>
       </c>
@@ -28825,7 +28819,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46288.66133771991</v>
       </c>
@@ -28926,7 +28920,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46288.465177546299</v>
       </c>
@@ -29030,7 +29024,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>46288.522137094908</v>
       </c>
@@ -29185,7 +29179,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>46288.678131909721</v>
       </c>
@@ -29286,7 +29280,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>46289.400980995371</v>
       </c>
@@ -29390,7 +29384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>46289.412856574083</v>
       </c>
@@ -29548,7 +29542,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>46289.416582500002</v>
       </c>
@@ -29703,7 +29697,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>46289.457423287036</v>
       </c>
@@ -29804,7 +29798,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>46289.480812314818</v>
       </c>
@@ -29905,7 +29899,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>46289.500007476847</v>
       </c>
@@ -30006,7 +30000,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>46289.513280347222</v>
       </c>
@@ -30161,7 +30155,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>46289.544489988417</v>
       </c>
@@ -30319,7 +30313,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>46289.516512256952</v>
       </c>
@@ -30566,7 +30560,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>46289.587290000003</v>
       </c>
@@ -30676,7 +30670,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>46289.554760902778</v>
       </c>
@@ -30777,7 +30771,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>46289.634438969908</v>
       </c>
@@ -30935,7 +30929,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>46289.67084796296</v>
       </c>
@@ -31125,7 +31119,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>46289.762437013887</v>
       </c>
@@ -31229,7 +31223,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>46289.776139745372</v>
       </c>
@@ -31333,7 +31327,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>46289.376371157407</v>
       </c>
@@ -31434,7 +31428,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>46289.780517430547</v>
       </c>
@@ -31538,7 +31532,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>46289.364937314807</v>
       </c>
@@ -31639,7 +31633,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>46289.417317129628</v>
       </c>
@@ -31794,7 +31788,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>46289.470136354168</v>
       </c>
@@ -31895,7 +31889,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>46290.410415590282</v>
       </c>
@@ -32053,7 +32047,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>46254.660598761577</v>
       </c>
@@ -32160,7 +32154,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>46290.505176122693</v>
       </c>
@@ -32436,7 +32430,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>46290.580511817127</v>
       </c>
@@ -32537,7 +32531,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>46290.598360659722</v>
       </c>
@@ -32641,7 +32635,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>46290.579465543982</v>
       </c>
@@ -32745,7 +32739,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>46290.758861805552</v>
       </c>
@@ -32855,7 +32849,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>46290.782907303241</v>
       </c>
@@ -32959,7 +32953,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>46290.808730833327</v>
       </c>
@@ -33117,7 +33111,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>46290.814761828697</v>
       </c>
@@ -33275,7 +33269,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>46290.824045995367</v>
       </c>
@@ -33376,7 +33370,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>46290.843395416668</v>
       </c>
@@ -33486,7 +33480,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>46290.847394305558</v>
       </c>
@@ -33590,7 +33584,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>46290.854527256954</v>
       </c>
@@ -33748,7 +33742,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>46293.365824699067</v>
       </c>
@@ -33846,7 +33840,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>46293.48316689815</v>
       </c>
@@ -33953,7 +33947,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>46293.491838668982</v>
       </c>
@@ -34048,7 +34042,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>46293.50166144676</v>
       </c>
@@ -34146,7 +34140,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>46293.511540266198</v>
       </c>
@@ -34241,7 +34235,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>46293.515931678237</v>
       </c>
@@ -34336,7 +34330,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>46292.875610428237</v>
       </c>
@@ -34440,7 +34434,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>46293.525056585648</v>
       </c>
@@ -34538,7 +34532,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>46293.462860451393</v>
       </c>
@@ -34651,7 +34645,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>46293.542157442127</v>
       </c>
@@ -34767,7 +34761,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>46289.549434942128</v>
       </c>
@@ -34877,7 +34871,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>46288.648351516204</v>
       </c>
@@ -35032,7 +35026,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>46293.729340034719</v>
       </c>
@@ -35142,7 +35136,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>46293.732859988428</v>
       </c>
@@ -35243,7 +35237,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>46293.73679451389</v>
       </c>
@@ -35344,7 +35338,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>46293.731438472219</v>
       </c>
@@ -35448,7 +35442,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>46293.815275972222</v>
       </c>
@@ -35552,7 +35546,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>46293.823807754627</v>
       </c>
@@ -35656,7 +35650,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>46293.803378958342</v>
       </c>
@@ -35799,7 +35793,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>46293.813637777777</v>
       </c>
@@ -35903,7 +35897,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>46293.816578796293</v>
       </c>
@@ -36019,7 +36013,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>46293.625744837962</v>
       </c>
@@ -36126,7 +36120,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>46294.488265138891</v>
       </c>
@@ -36242,7 +36236,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>46294.552163206019</v>
       </c>
@@ -36343,7 +36337,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>46294.55584572917</v>
       </c>
@@ -36438,7 +36432,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>46293.535828969907</v>
       </c>
@@ -36533,7 +36527,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>46293.556273576389</v>
       </c>
@@ -36628,7 +36622,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>46293.571447662027</v>
       </c>
@@ -36732,7 +36726,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>46293.583647256943</v>
       </c>
@@ -36827,7 +36821,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>46293.585437430564</v>
       </c>
@@ -36943,7 +36937,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>46293.596938391202</v>
       </c>
@@ -37053,7 +37047,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>46294.49139398148</v>
       </c>
@@ -37148,7 +37142,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>46294.586004293982</v>
       </c>
@@ -37252,7 +37246,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>46294.634888472217</v>
       </c>
@@ -37356,7 +37350,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>46294.638466377313</v>
       </c>
@@ -37451,7 +37445,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>46294.640932835653</v>
       </c>
@@ -37555,7 +37549,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>46294.642854039354</v>
       </c>
@@ -37659,7 +37653,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>46294.64522431713</v>
       </c>
@@ -37763,7 +37757,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>46294.684677696758</v>
       </c>
@@ -37861,7 +37855,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>46294.7240499537</v>
       </c>
@@ -37965,7 +37959,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>46294.740338090283</v>
       </c>
@@ -38066,7 +38060,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>46294.739667569447</v>
       </c>
@@ -38170,7 +38164,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>46294.755193831021</v>
       </c>
@@ -38271,7 +38265,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>46294.75193539352</v>
       </c>
@@ -38375,7 +38369,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>46294.761264895831</v>
       </c>
@@ -38479,7 +38473,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>46294.754593750004</v>
       </c>
@@ -38583,7 +38577,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>46294.757487442133</v>
       </c>
@@ -38687,7 +38681,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>46294.760891759259</v>
       </c>
@@ -38791,7 +38785,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>46294.776597719909</v>
       </c>
@@ -38895,7 +38889,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>46294.795517766201</v>
       </c>
@@ -38999,7 +38993,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>46294.799215694453</v>
       </c>
@@ -39103,7 +39097,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>46294.802037627313</v>
       </c>
@@ -39207,7 +39201,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>46294.620284849538</v>
       </c>
@@ -39323,7 +39317,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>46294.750292604163</v>
       </c>
@@ -39427,7 +39421,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>46294.75457420139</v>
       </c>
@@ -39531,7 +39525,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>46294.76850484954</v>
       </c>
@@ -39635,7 +39629,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>46294.770551990739</v>
       </c>
@@ -39739,7 +39733,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>46294.77235269676</v>
       </c>
@@ -39843,7 +39837,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>46294.774383877317</v>
       </c>
@@ -39947,7 +39941,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>46295.431909814812</v>
       </c>
@@ -40045,7 +40039,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>46294.713914699067</v>
       </c>
@@ -40149,7 +40143,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>46295.534696747687</v>
       </c>
@@ -40253,7 +40247,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>46295.537180023151</v>
       </c>
@@ -40357,7 +40351,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>46295.538939444443</v>
       </c>
@@ -40461,7 +40455,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>46295.541104618052</v>
       </c>
@@ -40565,7 +40559,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>46294.620388888892</v>
       </c>
@@ -40675,7 +40669,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>46295.648789212973</v>
       </c>
@@ -40957,7 +40951,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>46295.701731238427</v>
       </c>
@@ -41064,7 +41058,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>46295.704093333326</v>
       </c>
@@ -41180,7 +41174,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>46295.709935613428</v>
       </c>
@@ -41296,7 +41290,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>46295.71365740741</v>
       </c>
@@ -41391,7 +41385,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>46295.716885624999</v>
       </c>
@@ -41507,7 +41501,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>46295.665477905102</v>
       </c>
@@ -41617,7 +41611,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>46295.813936377323</v>
       </c>
@@ -41721,7 +41715,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>46295.822483449083</v>
       </c>
@@ -41825,7 +41819,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>46295.82530034722</v>
       </c>
@@ -41929,7 +41923,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>46295.82738480324</v>
       </c>
@@ -42033,7 +42027,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>46295.831523148147</v>
       </c>
@@ -42137,7 +42131,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>46295.870190428242</v>
       </c>
@@ -42232,7 +42226,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>46295.421994247678</v>
       </c>
@@ -42327,7 +42321,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>46295.425309699072</v>
       </c>
@@ -42431,7 +42425,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>46295.428430567132</v>
       </c>
@@ -42526,7 +42520,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>46295.43050869213</v>
       </c>
@@ -42621,7 +42615,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>46295.491448726847</v>
       </c>
@@ -42725,7 +42719,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>46295.497799629629</v>
       </c>
@@ -42829,7 +42823,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>46295.50835103009</v>
       </c>
@@ -42924,7 +42918,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>46295.519981921287</v>
       </c>
@@ -43028,7 +43022,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>46295.621399178242</v>
       </c>
@@ -43123,7 +43117,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>46293.856906226851</v>
       </c>
@@ -43319,7 +43313,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>46295.89000162037</v>
       </c>
@@ -43429,7 +43423,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>46295.876588113417</v>
       </c>
@@ -43539,7 +43533,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>46295.947029872688</v>
       </c>
@@ -43649,7 +43643,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>46296.290502754629</v>
       </c>
@@ -43756,7 +43750,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>46296.293855810189</v>
       </c>
@@ -43914,7 +43908,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>46296.29973741898</v>
       </c>
@@ -44021,7 +44015,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>46296.304758252307</v>
       </c>
@@ -44254,7 +44248,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>46296.414372060193</v>
       </c>
@@ -44358,7 +44352,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>46296.443119699077</v>
       </c>
@@ -44459,7 +44453,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>46296.446367986107</v>
       </c>
@@ -44554,7 +44548,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>46296.452167673611</v>
       </c>
@@ -44649,7 +44643,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>46296.462310613417</v>
       </c>
@@ -44753,7 +44747,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>46296.474542962962</v>
       </c>
@@ -44884,7 +44878,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>46296.517473321757</v>
       </c>
@@ -44988,7 +44982,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>46296.528989340281</v>
       </c>
@@ -45092,7 +45086,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>46296.454655682872</v>
       </c>
@@ -45226,7 +45220,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>46295.956040567129</v>
       </c>
@@ -45477,7 +45471,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>46296.562106122678</v>
       </c>
@@ -45578,7 +45572,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>46296.710014999997</v>
       </c>
@@ -45676,7 +45670,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>46296.716005798611</v>
       </c>
@@ -45783,7 +45777,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="203" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>46296.721711759259</v>
       </c>
@@ -45881,7 +45875,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>46296.714952511567</v>
       </c>
@@ -46036,7 +46030,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="205" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>46296.724340370369</v>
       </c>
@@ -46146,7 +46140,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>46296.728354641207</v>
       </c>
@@ -46277,7 +46271,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="207" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>46296.730641527778</v>
       </c>
@@ -46384,7 +46378,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="208" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>46296.657187523153</v>
       </c>
@@ -46519,7 +46513,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="209" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>46296.826218819442</v>
       </c>
@@ -46642,7 +46636,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="210" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>46296.903357361109</v>
       </c>
@@ -46777,7 +46771,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="211" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>46296.906311192128</v>
       </c>
@@ -46891,7 +46885,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="212" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>46296.908534444447</v>
       </c>
@@ -47050,7 +47044,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="213" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>46297.307513391213</v>
       </c>
@@ -47499,7 +47493,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="216" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>46297.595784861107</v>
       </c>
@@ -47604,7 +47598,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="217" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>46297.603049039353</v>
       </c>
@@ -47718,7 +47712,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="218" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>46297.523460810182</v>
       </c>
@@ -47850,7 +47844,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>46297.616067442133</v>
       </c>
@@ -47955,7 +47949,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="220" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>46297.611051006941</v>
       </c>
@@ -48078,7 +48072,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="221" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>46297.623010995369</v>
       </c>
@@ -48183,7 +48177,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>46297.629230914346</v>
       </c>
@@ -48297,7 +48291,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="223" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>46297.625507025463</v>
       </c>
@@ -48408,7 +48402,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="224" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>46297.636685254627</v>
       </c>
@@ -48513,7 +48507,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="225" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>46297.642068576388</v>
       </c>
@@ -48615,7 +48609,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="226" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>46297.642087673608</v>
       </c>
@@ -48720,7 +48714,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>46297.645297141207</v>
       </c>
@@ -48831,7 +48825,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="228" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>46297.647905798607</v>
       </c>
@@ -48942,7 +48936,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="229" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>46297.658319340277</v>
       </c>
@@ -49044,7 +49038,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="230" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>46297.664371840277</v>
       </c>
@@ -49155,7 +49149,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="231" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>46297.697087002307</v>
       </c>
@@ -49257,7 +49251,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>46297.717215694443</v>
       </c>
@@ -49359,7 +49353,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>46297.720690405091</v>
       </c>
@@ -49470,7 +49464,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>46297.726336203697</v>
       </c>
@@ -49581,7 +49575,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>46297.727836921287</v>
       </c>
@@ -49719,7 +49713,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>46297.733303923611</v>
       </c>
@@ -50516,7 +50510,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="242" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>46297.645588900457</v>
       </c>
@@ -50769,7 +50763,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="244" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>46298.436995810189</v>
       </c>
@@ -50904,7 +50898,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="245" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>46294.744592546303</v>
       </c>
@@ -51015,7 +51009,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="246" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>46298.477973055553</v>
       </c>
@@ -51286,7 +51280,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="248" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>46298.534485775461</v>
       </c>
@@ -51397,7 +51391,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="249" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>46298.551648703702</v>
       </c>
@@ -51556,7 +51550,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="250" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>46298.56466358796</v>
       </c>
@@ -51697,7 +51691,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="251" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>46298.60764490741</v>
       </c>
@@ -51808,7 +51802,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="252" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>46298.613122175928</v>
       </c>
@@ -51919,7 +51913,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="253" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>46300.650030763893</v>
       </c>
@@ -52133,7 +52127,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="255" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>46301.522519942133</v>
       </c>
@@ -52446,7 +52440,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>46301.538739317133</v>
       </c>
@@ -52663,7 +52657,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="259" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>46302.423721701387</v>
       </c>
@@ -52801,7 +52795,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>46302.43387108796</v>
       </c>
@@ -52942,7 +52936,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="261" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>46302.446020150463</v>
       </c>
@@ -53050,7 +53044,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="262" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>46302.438089305557</v>
       </c>
@@ -53451,7 +53445,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="265" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>46302.480987708332</v>
       </c>
@@ -53559,7 +53553,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="266" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>46302.507625208331</v>
       </c>
@@ -53670,7 +53664,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="267" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>46302.632995671287</v>
       </c>
@@ -54044,7 +54038,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="270" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>46302.687822835651</v>
       </c>
@@ -54155,7 +54149,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="271" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>46302.699748969913</v>
       </c>
@@ -54272,7 +54266,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="272" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>46301.806419375003</v>
       </c>
@@ -54455,7 +54449,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="273" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>46302.739207951388</v>
       </c>
@@ -54539,7 +54533,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="274" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>46302.75280141204</v>
       </c>
@@ -54722,7 +54716,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="275" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>46302.860038148137</v>
       </c>
@@ -55069,7 +55063,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="278" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>46300.70079787037</v>
       </c>
@@ -55225,7 +55219,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>46303.433600277778</v>
       </c>
@@ -55408,7 +55402,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>46303.446988136573</v>
       </c>
@@ -55721,7 +55715,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>46303.507944050929</v>
       </c>
@@ -55935,7 +55929,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="284" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>46303.533923391202</v>
       </c>
@@ -56118,7 +56112,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="285" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>46303.602467268523</v>
       </c>
@@ -56301,7 +56295,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="286" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>46303.665873425933</v>
       </c>
@@ -56484,7 +56478,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>46303.453409363428</v>
       </c>
@@ -56828,7 +56822,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="290" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>46302.837925925924</v>
       </c>
@@ -56912,7 +56906,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>46304.309806493053</v>
       </c>
@@ -57050,7 +57044,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="292" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>46302.507222314824</v>
       </c>
@@ -57188,7 +57182,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="293" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>46304.399320115743</v>
       </c>
@@ -57326,7 +57320,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>46304.406028958343</v>
       </c>
@@ -57603,7 +57597,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>46304.429592418979</v>
       </c>
@@ -57690,7 +57684,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="297" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>46304.440482337966</v>
       </c>
@@ -57771,7 +57765,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="298" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>46304.443006539354</v>
       </c>
@@ -57852,7 +57846,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="299" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>46304.549563611108</v>
       </c>
@@ -57993,7 +57987,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="300" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>46304.552871203698</v>
       </c>
@@ -58179,7 +58173,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="301" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>46304.55543482639</v>
       </c>
@@ -58320,7 +58314,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>46304.558062291668</v>
       </c>
@@ -58506,7 +58500,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="303" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>46304.560552812502</v>
       </c>
@@ -58596,7 +58590,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="304" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>46304.56600979167</v>
       </c>
@@ -58734,7 +58728,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="305" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>46304.568548668984</v>
       </c>
@@ -58920,7 +58914,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="306" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>46304.572299814812</v>
       </c>
@@ -59106,7 +59100,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="307" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>46304.577533622687</v>
       </c>
@@ -60486,7 +60480,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="317" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>46304.63213510417</v>
       </c>
@@ -60573,7 +60567,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="318" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>46302.81901608796</v>
       </c>
@@ -60756,7 +60750,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="319" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>46304.719278657409</v>
       </c>
@@ -61103,7 +61097,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="322" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>46304.845099108803</v>
       </c>
@@ -61286,7 +61280,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="323" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>46304.904140416656</v>
       </c>
@@ -61364,7 +61358,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="324" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>46302.598696724534</v>
       </c>
@@ -61472,7 +61466,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="325" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>46304.759218159721</v>
       </c>
@@ -61870,7 +61864,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="328" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>46307.915130335648</v>
       </c>
@@ -62008,7 +62002,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>46307.929744861111</v>
       </c>
@@ -62146,7 +62140,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="330" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>46307.734356793982</v>
       </c>
@@ -62414,7 +62408,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="332" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>46308.522087534722</v>
       </c>
@@ -62948,7 +62942,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="336" spans="1:259" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:259" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>46302.448508472233</v>
       </c>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="525" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEA16BF7-F0D4-9345-960F-8CC17888F775}"/>
+  <xr:revisionPtr revIDLastSave="526" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{192FB353-71AD-4A46-BB73-E1235AB10802}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="2320" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="660" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Public Health Emergencies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8583" uniqueCount="2596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8611" uniqueCount="2604">
   <si>
     <t>start</t>
   </si>
@@ -7836,6 +7836,30 @@
   </si>
   <si>
     <t>Parish leaders</t>
+  </si>
+  <si>
+    <t>Boda boda stage leader.</t>
+  </si>
+  <si>
+    <t>Sharing of the emergency number with other people met</t>
+  </si>
+  <si>
+    <t>Ebola is like cholera</t>
+  </si>
+  <si>
+    <t>Misinformation in the community</t>
+  </si>
+  <si>
+    <t>More sensitization in the community should be carried out</t>
+  </si>
+  <si>
+    <t>360f1409-1a71-47af-950c-1c7e9b08ae52</t>
+  </si>
+  <si>
+    <t>voFsDnKQp2BcHbB8NCEFfC</t>
+  </si>
+  <si>
+    <t>uuid:360f1409-1a71-47af-950c-1c7e9b08ae52</t>
   </si>
 </sst>
 </file>
@@ -21890,7 +21914,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -22240,8 +22264,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY344" totalsRowShown="0">
-  <autoFilter ref="A1:IY344" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY345" totalsRowShown="0">
+  <autoFilter ref="A1:IY345" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -22794,7 +22818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY344"/>
+  <dimension ref="A1:IY345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -64123,6 +64147,132 @@
         <v>343</v>
       </c>
     </row>
+    <row r="345" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A345" s="1">
+        <v>46310.820348877307</v>
+      </c>
+      <c r="B345" s="1">
+        <v>46310.824536354157</v>
+      </c>
+      <c r="C345" s="1">
+        <v>46310</v>
+      </c>
+      <c r="D345" t="s">
+        <v>690</v>
+      </c>
+      <c r="E345" t="s">
+        <v>254</v>
+      </c>
+      <c r="F345" t="s">
+        <v>271</v>
+      </c>
+      <c r="G345" t="s">
+        <v>443</v>
+      </c>
+      <c r="H345" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX345" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY345" t="s">
+        <v>2596</v>
+      </c>
+      <c r="AZ345" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BB345">
+        <v>2</v>
+      </c>
+      <c r="BC345">
+        <v>3</v>
+      </c>
+      <c r="BD345" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE345" t="s">
+        <v>324</v>
+      </c>
+      <c r="BF345" t="s">
+        <v>324</v>
+      </c>
+      <c r="BG345" t="s">
+        <v>2597</v>
+      </c>
+      <c r="BH345" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI345" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ345" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK345">
+        <v>3</v>
+      </c>
+      <c r="BL345" t="s">
+        <v>1628</v>
+      </c>
+      <c r="BM345">
+        <v>56</v>
+      </c>
+      <c r="BN345">
+        <v>78</v>
+      </c>
+      <c r="BO345" t="s">
+        <v>1719</v>
+      </c>
+      <c r="BP345" t="s">
+        <v>1719</v>
+      </c>
+      <c r="BQ345" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS345" t="s">
+        <v>2598</v>
+      </c>
+      <c r="BT345" t="s">
+        <v>2599</v>
+      </c>
+      <c r="BU345" t="s">
+        <v>1637</v>
+      </c>
+      <c r="BW345" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX345" t="s">
+        <v>2600</v>
+      </c>
+      <c r="EY345" s="1"/>
+      <c r="GQ345" s="1"/>
+      <c r="GR345" s="1"/>
+      <c r="GY345" s="1"/>
+      <c r="GZ345" s="1"/>
+      <c r="HA345" s="1"/>
+      <c r="HB345" s="1"/>
+      <c r="IQ345" s="1">
+        <v>894630015</v>
+      </c>
+      <c r="IR345" t="s">
+        <v>2601</v>
+      </c>
+      <c r="IS345" s="1">
+        <v>46310.699548611112</v>
+      </c>
+      <c r="IU345" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW345" t="s">
+        <v>2602</v>
+      </c>
+      <c r="IX345" t="s">
+        <v>2603</v>
+      </c>
+      <c r="IY345">
+        <v>344</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Public_Health_Emergencies.xlsx
+++ b/Public_Health_Emergencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solutions4people878-my.sharepoint.com/personal/k_mulondo_s4pgroup_org/Documents/S4P Group Work/PHE/PHE Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="526" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{192FB353-71AD-4A46-BB73-E1235AB10802}"/>
+  <xr:revisionPtr revIDLastSave="527" documentId="11_978F1AEF8400AA337625AB90F45CC233702D776C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84727B25-3A33-EC43-B4FE-2B6D7B7B2364}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="660" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="1520" windowWidth="26000" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Public Health Emergencies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8611" uniqueCount="2604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9059" uniqueCount="2672">
   <si>
     <t>start</t>
   </si>
@@ -7860,6 +7860,210 @@
   </si>
   <si>
     <t>uuid:360f1409-1a71-47af-950c-1c7e9b08ae52</t>
+  </si>
+  <si>
+    <t>Bwaise Parents Primary School</t>
+  </si>
+  <si>
+    <t>Is Uganda having any Ebola case? Is there an Ebola vaccine</t>
+  </si>
+  <si>
+    <t>Low risk perception by some individuals</t>
+  </si>
+  <si>
+    <t>Supervision should be carried out during outbreaks so as SOPs are followed</t>
+  </si>
+  <si>
+    <t>4053f0cc-454c-4a10-8eaf-d8f9eea44594</t>
+  </si>
+  <si>
+    <t>uuid:4053f0cc-454c-4a10-8eaf-d8f9eea44594</t>
+  </si>
+  <si>
+    <t>Bwaise Parents</t>
+  </si>
+  <si>
+    <t>Is Uganda having any new Ebola case?</t>
+  </si>
+  <si>
+    <t>Low risk perception by community members</t>
+  </si>
+  <si>
+    <t>Social media and individual in the community</t>
+  </si>
+  <si>
+    <t>More school engagements should be carried out so as learners are endowed with health facts and information</t>
+  </si>
+  <si>
+    <t>c9accb64-6558-4b01-9523-f2ee67f7d23c</t>
+  </si>
+  <si>
+    <t>uuid:c9accb64-6558-4b01-9523-f2ee67f7d23c</t>
+  </si>
+  <si>
+    <t>If I have stomach pain, and I vomit blood, does it mean I have ebola</t>
+  </si>
+  <si>
+    <t>Encouraging more students to join the health club.</t>
+  </si>
+  <si>
+    <t>821d3fab-0c52-4e06-acdf-43fe8ab4a5aa</t>
+  </si>
+  <si>
+    <t>uuid:821d3fab-0c52-4e06-acdf-43fe8ab4a5aa</t>
+  </si>
+  <si>
+    <t>Bukasa primary  school</t>
+  </si>
+  <si>
+    <t>Ebola  is not there,</t>
+  </si>
+  <si>
+    <t>38f4075c-c2a2-4966-81fd-8b3b831fc223</t>
+  </si>
+  <si>
+    <t>uuid:38f4075c-c2a2-4966-81fd-8b3b831fc223</t>
+  </si>
+  <si>
+    <t>Bukasa Primary  school</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>662cc87b-35d2-47b1-8cd9-d0098a395daf</t>
+  </si>
+  <si>
+    <t>uuid:662cc87b-35d2-47b1-8cd9-d0098a395daf</t>
+  </si>
+  <si>
+    <t>Nansana SDA Primary school</t>
+  </si>
+  <si>
+    <t>Most of the students currently know the PHE</t>
+  </si>
+  <si>
+    <t>aede8df4-1971-4229-a670-62d46fd467e4</t>
+  </si>
+  <si>
+    <t>uuid:aede8df4-1971-4229-a670-62d46fd467e4</t>
+  </si>
+  <si>
+    <t>Nsambya  central</t>
+  </si>
+  <si>
+    <t>St Paul primary  school ,Nsambya</t>
+  </si>
+  <si>
+    <t>7bf83f53-dcaf-4b19-976b-b9d2df875671</t>
+  </si>
+  <si>
+    <t>uuid:7bf83f53-dcaf-4b19-976b-b9d2df875671</t>
+  </si>
+  <si>
+    <t>To engage other riders</t>
+  </si>
+  <si>
+    <t>Is ebola back</t>
+  </si>
+  <si>
+    <t>3643e096-2fbb-4ac5-8405-9c635ee2c35a</t>
+  </si>
+  <si>
+    <t>uuid:3643e096-2fbb-4ac5-8405-9c635ee2c35a</t>
+  </si>
+  <si>
+    <t>St Paul primary  school Nsambya</t>
+  </si>
+  <si>
+    <t>d2da9266-a2e9-4878-aa38-fc6387829f28</t>
+  </si>
+  <si>
+    <t>uuid:d2da9266-a2e9-4878-aa38-fc6387829f28</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Encouraging learners to teach their parents</t>
+  </si>
+  <si>
+    <t>569ea56c-42b3-4ea4-bc9b-7a86ef09b592</t>
+  </si>
+  <si>
+    <t>uuid:569ea56c-42b3-4ea4-bc9b-7a86ef09b592</t>
+  </si>
+  <si>
+    <t>Katwe martyrs  primary  school</t>
+  </si>
+  <si>
+    <t>Does ebola exist,  Does Ebola cause death</t>
+  </si>
+  <si>
+    <t>Children  mishandled soap</t>
+  </si>
+  <si>
+    <t>77c767c8-377a-45f5-bfbe-b493bdfed1a4</t>
+  </si>
+  <si>
+    <t>uuid:77c767c8-377a-45f5-bfbe-b493bdfed1a4</t>
+  </si>
+  <si>
+    <t>Taxi park chairman</t>
+  </si>
+  <si>
+    <t>Continue  encouraging the  drivers to protect themselvew</t>
+  </si>
+  <si>
+    <t>Someone asked if the teaching is about sensitization  or  there something government  wants to pass, are the street muchomos owners</t>
+  </si>
+  <si>
+    <t>fc6928d2-83c7-4c7e-8f3e-3eee1ceccd3c</t>
+  </si>
+  <si>
+    <t>uuid:fc6928d2-83c7-4c7e-8f3e-3eee1ceccd3c</t>
+  </si>
+  <si>
+    <t>Stage chair man</t>
+  </si>
+  <si>
+    <t>To educate other  bodaboda  riders  on how they should protect themselves</t>
+  </si>
+  <si>
+    <t>Does using a mask and sanitizer help in preventing  Ebola</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>4bf18939-b2e1-477e-a4a8-0b3f60f3a0a2</t>
+  </si>
+  <si>
+    <t>uuid:4bf18939-b2e1-477e-a4a8-0b3f60f3a0a2</t>
+  </si>
+  <si>
+    <t>f93b87d3-cb55-48eb-8f8f-765b1d8a4a0d</t>
+  </si>
+  <si>
+    <t>uuid:f93b87d3-cb55-48eb-8f8f-765b1d8a4a0d</t>
+  </si>
+  <si>
+    <t>abe6e058-8cfb-4602-b6bd-1f5cd02e92b2</t>
+  </si>
+  <si>
+    <t>uuid:abe6e058-8cfb-4602-b6bd-1f5cd02e92b2</t>
+  </si>
+  <si>
+    <t>Nsamya</t>
+  </si>
+  <si>
+    <t>18a78b49-45e6-4ad5-bf5a-ab664a907383</t>
+  </si>
+  <si>
+    <t>uuid:18a78b49-45e6-4ad5-bf5a-ab664a907383</t>
   </si>
 </sst>
 </file>
@@ -21914,7 +22118,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F8C30C6-06BF-E647-B784-8C39B547537C}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="214">
     <pivotField numFmtId="164" showAll="0"/>
@@ -22264,8 +22468,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY345" totalsRowShown="0">
-  <autoFilter ref="A1:IY345" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}" name="Table1" displayName="Table1" ref="A1:IY361" totalsRowShown="0">
+  <autoFilter ref="A1:IY361" xr:uid="{DAB945CB-98A2-7348-B103-235BF1C5C0A7}"/>
   <tableColumns count="259">
     <tableColumn id="1" xr3:uid="{C94166E9-6484-E345-8DA1-B366A10EA145}" name="start" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{34B20598-52A2-0E4A-A1CD-E66C42F7D130}" name="end" dataDxfId="10"/>
@@ -22818,7 +23022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY345"/>
+  <dimension ref="A1:IY361"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -64273,6 +64477,2358 @@
         <v>344</v>
       </c>
     </row>
+    <row r="346" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A346" s="1">
+        <v>46304.978979340267</v>
+      </c>
+      <c r="B346" s="1">
+        <v>46311.373076192132</v>
+      </c>
+      <c r="C346" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D346" t="s">
+        <v>691</v>
+      </c>
+      <c r="E346" t="s">
+        <v>254</v>
+      </c>
+      <c r="F346" t="s">
+        <v>271</v>
+      </c>
+      <c r="G346" t="s">
+        <v>443</v>
+      </c>
+      <c r="H346" t="s">
+        <v>256</v>
+      </c>
+      <c r="J346" t="s">
+        <v>2604</v>
+      </c>
+      <c r="K346" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L346" t="s">
+        <v>324</v>
+      </c>
+      <c r="M346" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N346" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O346" t="s">
+        <v>1812</v>
+      </c>
+      <c r="R346">
+        <v>5</v>
+      </c>
+      <c r="S346">
+        <v>5</v>
+      </c>
+      <c r="T346" t="s">
+        <v>1813</v>
+      </c>
+      <c r="U346" t="s">
+        <v>1814</v>
+      </c>
+      <c r="V346">
+        <v>0</v>
+      </c>
+      <c r="W346">
+        <v>0</v>
+      </c>
+      <c r="X346">
+        <v>0</v>
+      </c>
+      <c r="Y346">
+        <v>1</v>
+      </c>
+      <c r="Z346">
+        <v>0</v>
+      </c>
+      <c r="AA346">
+        <v>0</v>
+      </c>
+      <c r="AB346" t="s">
+        <v>1815</v>
+      </c>
+      <c r="AC346">
+        <v>1</v>
+      </c>
+      <c r="AD346">
+        <v>0</v>
+      </c>
+      <c r="AE346">
+        <v>0</v>
+      </c>
+      <c r="AF346">
+        <v>0</v>
+      </c>
+      <c r="AG346">
+        <v>0</v>
+      </c>
+      <c r="AH346">
+        <v>430</v>
+      </c>
+      <c r="AI346">
+        <v>145</v>
+      </c>
+      <c r="AJ346">
+        <v>105</v>
+      </c>
+      <c r="AK346">
+        <v>8</v>
+      </c>
+      <c r="AL346">
+        <v>2</v>
+      </c>
+      <c r="AM346">
+        <v>0</v>
+      </c>
+      <c r="AN346">
+        <v>0</v>
+      </c>
+      <c r="AO346" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP346">
+        <v>3</v>
+      </c>
+      <c r="AQ346" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AR346" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS346" t="s">
+        <v>203</v>
+      </c>
+      <c r="AT346" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU346" t="s">
+        <v>203</v>
+      </c>
+      <c r="AV346" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW346" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS346" t="s">
+        <v>2605</v>
+      </c>
+      <c r="BT346" t="s">
+        <v>2606</v>
+      </c>
+      <c r="BU346" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV346" t="s">
+        <v>1475</v>
+      </c>
+      <c r="BW346" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX346" t="s">
+        <v>2607</v>
+      </c>
+      <c r="EY346" s="1"/>
+      <c r="GQ346" s="1"/>
+      <c r="GR346" s="1"/>
+      <c r="GY346" s="1"/>
+      <c r="GZ346" s="1"/>
+      <c r="HA346" s="1"/>
+      <c r="HB346" s="1"/>
+      <c r="IQ346" s="1">
+        <v>894899629</v>
+      </c>
+      <c r="IR346" t="s">
+        <v>2608</v>
+      </c>
+      <c r="IS346" s="1">
+        <v>46311.248090277782</v>
+      </c>
+      <c r="IU346" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW346" t="s">
+        <v>2602</v>
+      </c>
+      <c r="IX346" t="s">
+        <v>2609</v>
+      </c>
+      <c r="IY346">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="347" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A347" s="1">
+        <v>46310.811120671293</v>
+      </c>
+      <c r="B347" s="1">
+        <v>46311.375286099537</v>
+      </c>
+      <c r="C347" s="1">
+        <v>46310</v>
+      </c>
+      <c r="D347" t="s">
+        <v>691</v>
+      </c>
+      <c r="E347" t="s">
+        <v>254</v>
+      </c>
+      <c r="F347" t="s">
+        <v>271</v>
+      </c>
+      <c r="G347" t="s">
+        <v>443</v>
+      </c>
+      <c r="H347" t="s">
+        <v>256</v>
+      </c>
+      <c r="J347" t="s">
+        <v>2610</v>
+      </c>
+      <c r="K347" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L347" t="s">
+        <v>395</v>
+      </c>
+      <c r="M347" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N347" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O347" t="s">
+        <v>1812</v>
+      </c>
+      <c r="R347">
+        <v>26</v>
+      </c>
+      <c r="S347">
+        <v>22</v>
+      </c>
+      <c r="T347" t="s">
+        <v>2103</v>
+      </c>
+      <c r="U347" t="s">
+        <v>1814</v>
+      </c>
+      <c r="V347">
+        <v>0</v>
+      </c>
+      <c r="W347">
+        <v>0</v>
+      </c>
+      <c r="X347">
+        <v>0</v>
+      </c>
+      <c r="Y347">
+        <v>1</v>
+      </c>
+      <c r="Z347">
+        <v>0</v>
+      </c>
+      <c r="AA347">
+        <v>0</v>
+      </c>
+      <c r="AB347" t="s">
+        <v>2222</v>
+      </c>
+      <c r="AC347">
+        <v>0</v>
+      </c>
+      <c r="AD347">
+        <v>1</v>
+      </c>
+      <c r="AE347">
+        <v>0</v>
+      </c>
+      <c r="AF347">
+        <v>0</v>
+      </c>
+      <c r="AG347">
+        <v>0</v>
+      </c>
+      <c r="AH347">
+        <v>430</v>
+      </c>
+      <c r="AI347">
+        <v>132</v>
+      </c>
+      <c r="AJ347">
+        <v>86</v>
+      </c>
+      <c r="AK347">
+        <v>1</v>
+      </c>
+      <c r="AL347">
+        <v>2</v>
+      </c>
+      <c r="AM347">
+        <v>0</v>
+      </c>
+      <c r="AN347">
+        <v>0</v>
+      </c>
+      <c r="AO347" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP347">
+        <v>3</v>
+      </c>
+      <c r="AQ347" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AR347" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS347" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT347" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU347" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV347" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW347" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS347" t="s">
+        <v>2611</v>
+      </c>
+      <c r="BT347" t="s">
+        <v>2612</v>
+      </c>
+      <c r="BU347" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV347" t="s">
+        <v>2613</v>
+      </c>
+      <c r="BW347" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX347" t="s">
+        <v>2614</v>
+      </c>
+      <c r="EY347" s="1"/>
+      <c r="GQ347" s="1"/>
+      <c r="GR347" s="1"/>
+      <c r="GY347" s="1"/>
+      <c r="GZ347" s="1"/>
+      <c r="HA347" s="1"/>
+      <c r="HB347" s="1"/>
+      <c r="IQ347" s="1">
+        <v>894900890</v>
+      </c>
+      <c r="IR347" t="s">
+        <v>2615</v>
+      </c>
+      <c r="IS347" s="1">
+        <v>46311.250300925924</v>
+      </c>
+      <c r="IU347" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW347" t="s">
+        <v>2602</v>
+      </c>
+      <c r="IX347" t="s">
+        <v>2616</v>
+      </c>
+      <c r="IY347">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="348" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A348" s="1">
+        <v>46310.240743842587</v>
+      </c>
+      <c r="B348" s="1">
+        <v>46310.248605358793</v>
+      </c>
+      <c r="C348" s="1">
+        <v>46309</v>
+      </c>
+      <c r="D348" t="s">
+        <v>691</v>
+      </c>
+      <c r="E348" t="s">
+        <v>210</v>
+      </c>
+      <c r="F348" t="s">
+        <v>970</v>
+      </c>
+      <c r="G348" t="s">
+        <v>198</v>
+      </c>
+      <c r="H348" t="s">
+        <v>212</v>
+      </c>
+      <c r="J348" t="s">
+        <v>425</v>
+      </c>
+      <c r="K348" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L348" t="s">
+        <v>395</v>
+      </c>
+      <c r="M348" t="s">
+        <v>612</v>
+      </c>
+      <c r="N348" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O348" t="s">
+        <v>1812</v>
+      </c>
+      <c r="R348">
+        <v>100</v>
+      </c>
+      <c r="S348">
+        <v>46</v>
+      </c>
+      <c r="T348" t="s">
+        <v>2103</v>
+      </c>
+      <c r="U348" t="s">
+        <v>2221</v>
+      </c>
+      <c r="V348">
+        <v>0</v>
+      </c>
+      <c r="W348">
+        <v>0</v>
+      </c>
+      <c r="X348">
+        <v>1</v>
+      </c>
+      <c r="Y348">
+        <v>0</v>
+      </c>
+      <c r="Z348">
+        <v>0</v>
+      </c>
+      <c r="AA348">
+        <v>0</v>
+      </c>
+      <c r="AB348" t="s">
+        <v>2222</v>
+      </c>
+      <c r="AC348">
+        <v>0</v>
+      </c>
+      <c r="AD348">
+        <v>1</v>
+      </c>
+      <c r="AE348">
+        <v>0</v>
+      </c>
+      <c r="AF348">
+        <v>0</v>
+      </c>
+      <c r="AG348">
+        <v>0</v>
+      </c>
+      <c r="AH348">
+        <v>900</v>
+      </c>
+      <c r="AI348">
+        <v>46</v>
+      </c>
+      <c r="AJ348">
+        <v>100</v>
+      </c>
+      <c r="AK348">
+        <v>1</v>
+      </c>
+      <c r="AL348">
+        <v>2</v>
+      </c>
+      <c r="AM348">
+        <v>0</v>
+      </c>
+      <c r="AN348">
+        <v>0</v>
+      </c>
+      <c r="AO348" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP348">
+        <v>6</v>
+      </c>
+      <c r="AQ348" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR348" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS348" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT348" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU348" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV348" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW348" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS348" t="s">
+        <v>2617</v>
+      </c>
+      <c r="BT348" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU348" t="s">
+        <v>1676</v>
+      </c>
+      <c r="BW348" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX348" t="s">
+        <v>2618</v>
+      </c>
+      <c r="EY348" s="1"/>
+      <c r="GQ348" s="1"/>
+      <c r="GR348" s="1"/>
+      <c r="GY348" s="1"/>
+      <c r="GZ348" s="1"/>
+      <c r="HA348" s="1"/>
+      <c r="HB348" s="1"/>
+      <c r="IQ348" s="1">
+        <v>894906877</v>
+      </c>
+      <c r="IR348" t="s">
+        <v>2619</v>
+      </c>
+      <c r="IS348" s="1">
+        <v>46311.260763888888</v>
+      </c>
+      <c r="IU348" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW348" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX348" t="s">
+        <v>2620</v>
+      </c>
+      <c r="IY348">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="349" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A349" s="1">
+        <v>46311.379574872677</v>
+      </c>
+      <c r="B349" s="1">
+        <v>46311.386292337957</v>
+      </c>
+      <c r="C349" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D349" t="s">
+        <v>691</v>
+      </c>
+      <c r="E349" t="s">
+        <v>237</v>
+      </c>
+      <c r="F349" t="s">
+        <v>473</v>
+      </c>
+      <c r="G349" t="s">
+        <v>198</v>
+      </c>
+      <c r="H349" t="s">
+        <v>240</v>
+      </c>
+      <c r="J349" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K349" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L349" t="s">
+        <v>395</v>
+      </c>
+      <c r="M349" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N349" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O349" t="s">
+        <v>1672</v>
+      </c>
+      <c r="P349" t="s">
+        <v>2388</v>
+      </c>
+      <c r="AH349">
+        <v>546</v>
+      </c>
+      <c r="AI349">
+        <v>221</v>
+      </c>
+      <c r="AJ349">
+        <v>325</v>
+      </c>
+      <c r="AK349">
+        <v>10</v>
+      </c>
+      <c r="AL349">
+        <v>1</v>
+      </c>
+      <c r="AM349">
+        <v>30</v>
+      </c>
+      <c r="AN349">
+        <v>0</v>
+      </c>
+      <c r="AO349" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP349">
+        <v>2</v>
+      </c>
+      <c r="AQ349" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR349" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS349" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT349" t="s">
+        <v>202</v>
+      </c>
+      <c r="AU349" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV349" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW349" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS349" t="s">
+        <v>2622</v>
+      </c>
+      <c r="BT349" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU349" t="s">
+        <v>1605</v>
+      </c>
+      <c r="BW349" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX349" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY349" s="1"/>
+      <c r="GQ349" s="1"/>
+      <c r="GR349" s="1"/>
+      <c r="GY349" s="1"/>
+      <c r="GZ349" s="1"/>
+      <c r="HA349" s="1"/>
+      <c r="HB349" s="1"/>
+      <c r="IQ349" s="1">
+        <v>894907187</v>
+      </c>
+      <c r="IR349" t="s">
+        <v>2623</v>
+      </c>
+      <c r="IS349" s="1">
+        <v>46311.261319444442</v>
+      </c>
+      <c r="IU349" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW349" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX349" t="s">
+        <v>2624</v>
+      </c>
+      <c r="IY349">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="350" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A350" s="1">
+        <v>46311.386293958327</v>
+      </c>
+      <c r="B350" s="1">
+        <v>46311.389851180553</v>
+      </c>
+      <c r="C350" s="1">
+        <v>46309</v>
+      </c>
+      <c r="D350" t="s">
+        <v>691</v>
+      </c>
+      <c r="E350" t="s">
+        <v>237</v>
+      </c>
+      <c r="F350" t="s">
+        <v>473</v>
+      </c>
+      <c r="G350" t="s">
+        <v>198</v>
+      </c>
+      <c r="H350" t="s">
+        <v>240</v>
+      </c>
+      <c r="J350" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K350" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L350" t="s">
+        <v>2102</v>
+      </c>
+      <c r="M350" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N350" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O350" t="s">
+        <v>1812</v>
+      </c>
+      <c r="R350">
+        <v>25</v>
+      </c>
+      <c r="S350">
+        <v>15</v>
+      </c>
+      <c r="T350" t="s">
+        <v>2103</v>
+      </c>
+      <c r="U350" t="s">
+        <v>2626</v>
+      </c>
+      <c r="V350">
+        <v>0</v>
+      </c>
+      <c r="W350">
+        <v>1</v>
+      </c>
+      <c r="X350">
+        <v>0</v>
+      </c>
+      <c r="Y350">
+        <v>0</v>
+      </c>
+      <c r="Z350">
+        <v>0</v>
+      </c>
+      <c r="AA350">
+        <v>0</v>
+      </c>
+      <c r="AB350" t="s">
+        <v>1815</v>
+      </c>
+      <c r="AC350">
+        <v>1</v>
+      </c>
+      <c r="AD350">
+        <v>0</v>
+      </c>
+      <c r="AE350">
+        <v>0</v>
+      </c>
+      <c r="AF350">
+        <v>0</v>
+      </c>
+      <c r="AG350">
+        <v>0</v>
+      </c>
+      <c r="AH350">
+        <v>546</v>
+      </c>
+      <c r="AI350">
+        <v>221</v>
+      </c>
+      <c r="AJ350">
+        <v>325</v>
+      </c>
+      <c r="AK350">
+        <v>1</v>
+      </c>
+      <c r="AL350">
+        <v>1</v>
+      </c>
+      <c r="AM350">
+        <v>0</v>
+      </c>
+      <c r="AN350">
+        <v>0</v>
+      </c>
+      <c r="AO350" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP350">
+        <v>1</v>
+      </c>
+      <c r="AQ350" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AR350" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS350" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT350" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU350" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV350" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW350" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS350" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT350" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU350" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV350" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW350" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX350" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY350" s="1"/>
+      <c r="GQ350" s="1"/>
+      <c r="GR350" s="1"/>
+      <c r="GY350" s="1"/>
+      <c r="GZ350" s="1"/>
+      <c r="HA350" s="1"/>
+      <c r="HB350" s="1"/>
+      <c r="IQ350" s="1">
+        <v>894909325</v>
+      </c>
+      <c r="IR350" t="s">
+        <v>2627</v>
+      </c>
+      <c r="IS350" s="1">
+        <v>46311.264872685177</v>
+      </c>
+      <c r="IU350" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW350" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX350" t="s">
+        <v>2628</v>
+      </c>
+      <c r="IY350">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="351" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A351" s="1">
+        <v>46310.248607951391</v>
+      </c>
+      <c r="B351" s="1">
+        <v>46311.38991135417</v>
+      </c>
+      <c r="C351" s="1">
+        <v>46310</v>
+      </c>
+      <c r="D351" t="s">
+        <v>691</v>
+      </c>
+      <c r="E351" t="s">
+        <v>210</v>
+      </c>
+      <c r="F351" t="s">
+        <v>275</v>
+      </c>
+      <c r="G351" t="s">
+        <v>198</v>
+      </c>
+      <c r="H351" t="s">
+        <v>212</v>
+      </c>
+      <c r="J351" t="s">
+        <v>2629</v>
+      </c>
+      <c r="K351" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L351" t="s">
+        <v>395</v>
+      </c>
+      <c r="M351" t="s">
+        <v>612</v>
+      </c>
+      <c r="N351" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O351" t="s">
+        <v>1812</v>
+      </c>
+      <c r="R351">
+        <v>42</v>
+      </c>
+      <c r="S351">
+        <v>56</v>
+      </c>
+      <c r="T351" t="s">
+        <v>2103</v>
+      </c>
+      <c r="U351" t="s">
+        <v>1814</v>
+      </c>
+      <c r="V351">
+        <v>0</v>
+      </c>
+      <c r="W351">
+        <v>0</v>
+      </c>
+      <c r="X351">
+        <v>0</v>
+      </c>
+      <c r="Y351">
+        <v>1</v>
+      </c>
+      <c r="Z351">
+        <v>0</v>
+      </c>
+      <c r="AA351">
+        <v>0</v>
+      </c>
+      <c r="AB351" t="s">
+        <v>2234</v>
+      </c>
+      <c r="AC351">
+        <v>1</v>
+      </c>
+      <c r="AD351">
+        <v>1</v>
+      </c>
+      <c r="AE351">
+        <v>0</v>
+      </c>
+      <c r="AF351">
+        <v>0</v>
+      </c>
+      <c r="AG351">
+        <v>0</v>
+      </c>
+      <c r="AH351">
+        <v>520</v>
+      </c>
+      <c r="AI351">
+        <v>42</v>
+      </c>
+      <c r="AJ351">
+        <v>56</v>
+      </c>
+      <c r="AK351">
+        <v>1</v>
+      </c>
+      <c r="AL351">
+        <v>2</v>
+      </c>
+      <c r="AM351">
+        <v>0</v>
+      </c>
+      <c r="AN351">
+        <v>0</v>
+      </c>
+      <c r="AO351" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP351">
+        <v>8</v>
+      </c>
+      <c r="AQ351" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AR351" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS351" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT351" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU351" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV351" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW351" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS351" t="s">
+        <v>954</v>
+      </c>
+      <c r="BT351" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU351" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV351" t="s">
+        <v>954</v>
+      </c>
+      <c r="BW351" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX351" t="s">
+        <v>2630</v>
+      </c>
+      <c r="EY351" s="1"/>
+      <c r="GQ351" s="1"/>
+      <c r="GR351" s="1"/>
+      <c r="GY351" s="1"/>
+      <c r="GZ351" s="1"/>
+      <c r="HA351" s="1"/>
+      <c r="HB351" s="1"/>
+      <c r="IQ351" s="1">
+        <v>894911694</v>
+      </c>
+      <c r="IR351" t="s">
+        <v>2631</v>
+      </c>
+      <c r="IS351" s="1">
+        <v>46311.268067129633</v>
+      </c>
+      <c r="IU351" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW351" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX351" t="s">
+        <v>2632</v>
+      </c>
+      <c r="IY351">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="352" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A352" s="1">
+        <v>46311.389853900473</v>
+      </c>
+      <c r="B352" s="1">
+        <v>46311.395807083332</v>
+      </c>
+      <c r="C352" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D352" t="s">
+        <v>691</v>
+      </c>
+      <c r="E352" t="s">
+        <v>237</v>
+      </c>
+      <c r="F352" t="s">
+        <v>2633</v>
+      </c>
+      <c r="G352" t="s">
+        <v>198</v>
+      </c>
+      <c r="H352" t="s">
+        <v>240</v>
+      </c>
+      <c r="J352" t="s">
+        <v>2634</v>
+      </c>
+      <c r="K352" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L352" t="s">
+        <v>395</v>
+      </c>
+      <c r="M352" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N352" t="s">
+        <v>1708</v>
+      </c>
+      <c r="O352" t="s">
+        <v>1672</v>
+      </c>
+      <c r="P352" t="s">
+        <v>2388</v>
+      </c>
+      <c r="AH352">
+        <v>900</v>
+      </c>
+      <c r="AI352">
+        <v>427</v>
+      </c>
+      <c r="AJ352">
+        <v>473</v>
+      </c>
+      <c r="AK352">
+        <v>10</v>
+      </c>
+      <c r="AL352">
+        <v>2</v>
+      </c>
+      <c r="AM352">
+        <v>30</v>
+      </c>
+      <c r="AN352">
+        <v>0</v>
+      </c>
+      <c r="AO352" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP352">
+        <v>2</v>
+      </c>
+      <c r="AQ352" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AR352" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS352" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT352" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU352" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV352" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW352" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS352" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT352" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU352" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV352" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW352" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX352" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY352" s="1"/>
+      <c r="GQ352" s="1"/>
+      <c r="GR352" s="1"/>
+      <c r="GY352" s="1"/>
+      <c r="GZ352" s="1"/>
+      <c r="HA352" s="1"/>
+      <c r="HB352" s="1"/>
+      <c r="IQ352" s="1">
+        <v>894913475</v>
+      </c>
+      <c r="IR352" t="s">
+        <v>2635</v>
+      </c>
+      <c r="IS352" s="1">
+        <v>46311.270821759259</v>
+      </c>
+      <c r="IU352" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW352" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX352" t="s">
+        <v>2636</v>
+      </c>
+      <c r="IY352">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="353" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A353" s="1">
+        <v>46311.393052314823</v>
+      </c>
+      <c r="B353" s="1">
+        <v>46311.396756655093</v>
+      </c>
+      <c r="C353" s="1">
+        <v>46310</v>
+      </c>
+      <c r="D353" t="s">
+        <v>690</v>
+      </c>
+      <c r="E353" t="s">
+        <v>210</v>
+      </c>
+      <c r="F353" t="s">
+        <v>642</v>
+      </c>
+      <c r="G353" t="s">
+        <v>443</v>
+      </c>
+      <c r="H353" t="s">
+        <v>212</v>
+      </c>
+      <c r="AX353" t="s">
+        <v>1827</v>
+      </c>
+      <c r="AY353" t="s">
+        <v>2596</v>
+      </c>
+      <c r="AZ353" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BB353">
+        <v>8</v>
+      </c>
+      <c r="BC353">
+        <v>0</v>
+      </c>
+      <c r="BD353" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE353" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF353" t="s">
+        <v>1626</v>
+      </c>
+      <c r="BG353" t="s">
+        <v>2637</v>
+      </c>
+      <c r="BH353" t="s">
+        <v>671</v>
+      </c>
+      <c r="BI353" t="s">
+        <v>671</v>
+      </c>
+      <c r="BJ353" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK353">
+        <v>5</v>
+      </c>
+      <c r="BL353" t="s">
+        <v>1628</v>
+      </c>
+      <c r="BM353">
+        <v>42</v>
+      </c>
+      <c r="BN353">
+        <v>30</v>
+      </c>
+      <c r="BO353" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP353" t="s">
+        <v>671</v>
+      </c>
+      <c r="BQ353" t="s">
+        <v>1977</v>
+      </c>
+      <c r="BS353" t="s">
+        <v>2638</v>
+      </c>
+      <c r="BT353" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU353" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV353" t="s">
+        <v>1831</v>
+      </c>
+      <c r="BW353" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX353" t="s">
+        <v>1829</v>
+      </c>
+      <c r="EY353" s="1"/>
+      <c r="GQ353" s="1"/>
+      <c r="GR353" s="1"/>
+      <c r="GY353" s="1"/>
+      <c r="GZ353" s="1"/>
+      <c r="HA353" s="1"/>
+      <c r="HB353" s="1"/>
+      <c r="IQ353" s="1">
+        <v>894913980</v>
+      </c>
+      <c r="IR353" t="s">
+        <v>2639</v>
+      </c>
+      <c r="IS353" s="1">
+        <v>46311.271793981483</v>
+      </c>
+      <c r="IU353" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW353" t="s">
+        <v>2602</v>
+      </c>
+      <c r="IX353" t="s">
+        <v>2640</v>
+      </c>
+      <c r="IY353">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="354" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A354" s="1">
+        <v>46311.395808865738</v>
+      </c>
+      <c r="B354" s="1">
+        <v>46311.399011701389</v>
+      </c>
+      <c r="C354" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D354" t="s">
+        <v>691</v>
+      </c>
+      <c r="E354" t="s">
+        <v>237</v>
+      </c>
+      <c r="F354" t="s">
+        <v>2633</v>
+      </c>
+      <c r="G354" t="s">
+        <v>198</v>
+      </c>
+      <c r="H354" t="s">
+        <v>240</v>
+      </c>
+      <c r="J354" t="s">
+        <v>2641</v>
+      </c>
+      <c r="K354" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L354" t="s">
+        <v>2102</v>
+      </c>
+      <c r="M354" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N354" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O354" t="s">
+        <v>1812</v>
+      </c>
+      <c r="R354">
+        <v>18</v>
+      </c>
+      <c r="S354">
+        <v>12</v>
+      </c>
+      <c r="T354" t="s">
+        <v>2103</v>
+      </c>
+      <c r="U354" t="s">
+        <v>2626</v>
+      </c>
+      <c r="V354">
+        <v>0</v>
+      </c>
+      <c r="W354">
+        <v>1</v>
+      </c>
+      <c r="X354">
+        <v>0</v>
+      </c>
+      <c r="Y354">
+        <v>0</v>
+      </c>
+      <c r="Z354">
+        <v>0</v>
+      </c>
+      <c r="AA354">
+        <v>0</v>
+      </c>
+      <c r="AB354" t="s">
+        <v>2234</v>
+      </c>
+      <c r="AC354">
+        <v>1</v>
+      </c>
+      <c r="AD354">
+        <v>1</v>
+      </c>
+      <c r="AE354">
+        <v>0</v>
+      </c>
+      <c r="AF354">
+        <v>0</v>
+      </c>
+      <c r="AG354">
+        <v>0</v>
+      </c>
+      <c r="AH354">
+        <v>900</v>
+      </c>
+      <c r="AI354">
+        <v>427</v>
+      </c>
+      <c r="AJ354">
+        <v>473</v>
+      </c>
+      <c r="AK354">
+        <v>2</v>
+      </c>
+      <c r="AL354">
+        <v>2</v>
+      </c>
+      <c r="AM354">
+        <v>30</v>
+      </c>
+      <c r="AN354">
+        <v>0</v>
+      </c>
+      <c r="AO354" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP354">
+        <v>1</v>
+      </c>
+      <c r="AQ354" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AR354" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS354" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT354" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU354" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV354" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW354" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS354" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT354" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU354" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV354" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW354" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX354" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY354" s="1"/>
+      <c r="GQ354" s="1"/>
+      <c r="GR354" s="1"/>
+      <c r="GY354" s="1"/>
+      <c r="GZ354" s="1"/>
+      <c r="HA354" s="1"/>
+      <c r="HB354" s="1"/>
+      <c r="IQ354" s="1">
+        <v>894915256</v>
+      </c>
+      <c r="IR354" t="s">
+        <v>2642</v>
+      </c>
+      <c r="IS354" s="1">
+        <v>46311.274039351847</v>
+      </c>
+      <c r="IU354" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW354" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX354" t="s">
+        <v>2643</v>
+      </c>
+      <c r="IY354">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A355" s="1">
+        <v>46311.397552326387</v>
+      </c>
+      <c r="B355" s="1">
+        <v>46311.40010402778</v>
+      </c>
+      <c r="C355" s="1">
+        <v>46311</v>
+      </c>
+      <c r="D355" t="s">
+        <v>691</v>
+      </c>
+      <c r="E355" t="s">
+        <v>210</v>
+      </c>
+      <c r="F355" t="s">
+        <v>275</v>
+      </c>
+      <c r="G355" t="s">
+        <v>443</v>
+      </c>
+      <c r="H355" t="s">
+        <v>212</v>
+      </c>
+      <c r="J355" t="s">
+        <v>2441</v>
+      </c>
+      <c r="K355" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L355" t="s">
+        <v>395</v>
+      </c>
+      <c r="M355" t="s">
+        <v>1670</v>
+      </c>
+      <c r="N355" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O355" t="s">
+        <v>1812</v>
+      </c>
+      <c r="R355">
+        <v>45</v>
+      </c>
+      <c r="S355">
+        <v>36</v>
+      </c>
+      <c r="T355" t="s">
+        <v>2103</v>
+      </c>
+      <c r="U355" t="s">
+        <v>2644</v>
+      </c>
+      <c r="V355">
+        <v>0</v>
+      </c>
+      <c r="W355">
+        <v>0</v>
+      </c>
+      <c r="X355">
+        <v>0</v>
+      </c>
+      <c r="Y355">
+        <v>0</v>
+      </c>
+      <c r="Z355">
+        <v>1</v>
+      </c>
+      <c r="AA355">
+        <v>0</v>
+      </c>
+      <c r="AB355" t="s">
+        <v>2222</v>
+      </c>
+      <c r="AC355">
+        <v>0</v>
+      </c>
+      <c r="AD355">
+        <v>1</v>
+      </c>
+      <c r="AE355">
+        <v>0</v>
+      </c>
+      <c r="AF355">
+        <v>0</v>
+      </c>
+      <c r="AG355">
+        <v>0</v>
+      </c>
+      <c r="AH355">
+        <v>580</v>
+      </c>
+      <c r="AI355">
+        <v>45</v>
+      </c>
+      <c r="AJ355">
+        <v>36</v>
+      </c>
+      <c r="AK355">
+        <v>2</v>
+      </c>
+      <c r="AL355">
+        <v>3</v>
+      </c>
+      <c r="AM355">
+        <v>0</v>
+      </c>
+      <c r="AN355">
+        <v>0</v>
+      </c>
+      <c r="AO355" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AP355">
+        <v>6</v>
+      </c>
+      <c r="AQ355" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AR355" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS355" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT355" t="s">
+        <v>217</v>
+      </c>
+      <c r="AU355" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV355" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW355" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS355" t="s">
+        <v>954</v>
+      </c>
+      <c r="BT355" t="s">
+        <v>954</v>
+      </c>
+      <c r="BU355" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV355" t="s">
+        <v>954</v>
+      </c>
+      <c r="BW355" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX355" t="s">
+        <v>2645</v>
+      </c>
+      <c r="EY355" s="1"/>
+      <c r="GQ355" s="1"/>
+      <c r="GR355" s="1"/>
+      <c r="GY355" s="1"/>
+      <c r="GZ355" s="1"/>
+      <c r="HA355" s="1"/>
+      <c r="HB355" s="1"/>
+      <c r="IQ355" s="1">
+        <v>894916063</v>
+      </c>
+      <c r="IR355" t="s">
+        <v>2646</v>
+      </c>
+      <c r="IS355" s="1">
+        <v>46311.27511574074</v>
+      </c>
+      <c r="IU355" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW355" t="s">
+        <v>2602</v>
+      </c>
+      <c r="IX355" t="s">
+        <v>2647</v>
+      </c>
+      <c r="IY355">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="356" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A356" s="1">
+        <v>46311.399014907409</v>
+      </c>
+      <c r="B356" s="1">
+        <v>46311.403349386572</v>
+      </c>
+      <c r="C356" s="1">
+        <v>46311</v>
+      </c>
+      <c r="D356" t="s">
+        <v>691</v>
+      </c>
+      <c r="E356" t="s">
+        <v>237</v>
+      </c>
+      <c r="F356" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G356" t="s">
+        <v>198</v>
+      </c>
+      <c r="H356" t="s">
+        <v>240</v>
+      </c>
+      <c r="J356" t="s">
+        <v>2648</v>
+      </c>
+      <c r="K356" t="s">
+        <v>2262</v>
+      </c>
+      <c r="L356" t="s">
+        <v>395</v>
+      </c>
+      <c r="M356" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N356" t="s">
+        <v>1671</v>
+      </c>
+      <c r="O356" t="s">
+        <v>1672</v>
+      </c>
+      <c r="P356" t="s">
+        <v>2388</v>
+      </c>
+      <c r="AH356">
+        <v>290</v>
+      </c>
+      <c r="AI356">
+        <v>110</v>
+      </c>
+      <c r="AJ356">
+        <v>180</v>
+      </c>
+      <c r="AK356">
+        <v>8</v>
+      </c>
+      <c r="AL356">
+        <v>1</v>
+      </c>
+      <c r="AM356">
+        <v>0</v>
+      </c>
+      <c r="AN356">
+        <v>0</v>
+      </c>
+      <c r="AO356" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AP356">
+        <v>1</v>
+      </c>
+      <c r="AQ356" t="s">
+        <v>2041</v>
+      </c>
+      <c r="AR356" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS356" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT356" t="s">
+        <v>203</v>
+      </c>
+      <c r="AU356" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV356" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW356" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS356" t="s">
+        <v>2649</v>
+      </c>
+      <c r="BT356" t="s">
+        <v>2650</v>
+      </c>
+      <c r="BU356" t="s">
+        <v>1676</v>
+      </c>
+      <c r="BW356" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX356" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY356" s="1"/>
+      <c r="GQ356" s="1"/>
+      <c r="GR356" s="1"/>
+      <c r="GY356" s="1"/>
+      <c r="GZ356" s="1"/>
+      <c r="HA356" s="1"/>
+      <c r="HB356" s="1"/>
+      <c r="IQ356" s="1">
+        <v>894918448</v>
+      </c>
+      <c r="IR356" t="s">
+        <v>2651</v>
+      </c>
+      <c r="IS356" s="1">
+        <v>46311.278379629628</v>
+      </c>
+      <c r="IU356" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW356" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX356" t="s">
+        <v>2652</v>
+      </c>
+      <c r="IY356">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="357" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A357" s="1">
+        <v>46311.40335212963</v>
+      </c>
+      <c r="B357" s="1">
+        <v>46311.411739710653</v>
+      </c>
+      <c r="C357" s="1">
+        <v>46307</v>
+      </c>
+      <c r="D357" t="s">
+        <v>690</v>
+      </c>
+      <c r="E357" t="s">
+        <v>237</v>
+      </c>
+      <c r="F357" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G357" t="s">
+        <v>198</v>
+      </c>
+      <c r="H357" t="s">
+        <v>240</v>
+      </c>
+      <c r="AX357" t="s">
+        <v>1975</v>
+      </c>
+      <c r="AY357" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ357" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA357" t="s">
+        <v>2653</v>
+      </c>
+      <c r="BB357">
+        <v>4</v>
+      </c>
+      <c r="BC357">
+        <v>0</v>
+      </c>
+      <c r="BD357" t="s">
+        <v>324</v>
+      </c>
+      <c r="BE357" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF357" t="s">
+        <v>1626</v>
+      </c>
+      <c r="BG357" t="s">
+        <v>2654</v>
+      </c>
+      <c r="BH357" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI357" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ357" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK357">
+        <v>6</v>
+      </c>
+      <c r="BL357" t="s">
+        <v>1718</v>
+      </c>
+      <c r="BM357">
+        <v>30</v>
+      </c>
+      <c r="BN357">
+        <v>25</v>
+      </c>
+      <c r="BO357" t="s">
+        <v>671</v>
+      </c>
+      <c r="BP357" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ357" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS357" t="s">
+        <v>2655</v>
+      </c>
+      <c r="BT357" t="s">
+        <v>727</v>
+      </c>
+      <c r="BU357" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV357" t="s">
+        <v>2348</v>
+      </c>
+      <c r="BW357" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX357" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY357" s="1"/>
+      <c r="GQ357" s="1"/>
+      <c r="GR357" s="1"/>
+      <c r="GY357" s="1"/>
+      <c r="GZ357" s="1"/>
+      <c r="HA357" s="1"/>
+      <c r="HB357" s="1"/>
+      <c r="IQ357" s="1">
+        <v>894923810</v>
+      </c>
+      <c r="IR357" t="s">
+        <v>2656</v>
+      </c>
+      <c r="IS357" s="1">
+        <v>46311.286770833343</v>
+      </c>
+      <c r="IU357" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW357" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX357" t="s">
+        <v>2657</v>
+      </c>
+      <c r="IY357">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="358" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A358" s="1">
+        <v>46311.411742384262</v>
+      </c>
+      <c r="B358" s="1">
+        <v>46311.415313252313</v>
+      </c>
+      <c r="C358" s="1">
+        <v>46308</v>
+      </c>
+      <c r="D358" t="s">
+        <v>690</v>
+      </c>
+      <c r="E358" t="s">
+        <v>237</v>
+      </c>
+      <c r="F358" t="s">
+        <v>473</v>
+      </c>
+      <c r="G358" t="s">
+        <v>198</v>
+      </c>
+      <c r="H358" t="s">
+        <v>240</v>
+      </c>
+      <c r="AX358" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AY358" t="s">
+        <v>809</v>
+      </c>
+      <c r="AZ358" t="s">
+        <v>1625</v>
+      </c>
+      <c r="BA358" t="s">
+        <v>2658</v>
+      </c>
+      <c r="BB358">
+        <v>3</v>
+      </c>
+      <c r="BC358">
+        <v>0</v>
+      </c>
+      <c r="BD358" t="s">
+        <v>395</v>
+      </c>
+      <c r="BE358" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF358" t="s">
+        <v>1626</v>
+      </c>
+      <c r="BG358" t="s">
+        <v>2659</v>
+      </c>
+      <c r="BH358" t="s">
+        <v>326</v>
+      </c>
+      <c r="BI358" t="s">
+        <v>326</v>
+      </c>
+      <c r="BJ358" t="s">
+        <v>324</v>
+      </c>
+      <c r="BK358">
+        <v>3</v>
+      </c>
+      <c r="BL358" t="s">
+        <v>1718</v>
+      </c>
+      <c r="BM358">
+        <v>15</v>
+      </c>
+      <c r="BN358">
+        <v>40</v>
+      </c>
+      <c r="BO358" t="s">
+        <v>1719</v>
+      </c>
+      <c r="BP358" t="s">
+        <v>327</v>
+      </c>
+      <c r="BQ358" t="s">
+        <v>389</v>
+      </c>
+      <c r="BS358" t="s">
+        <v>2660</v>
+      </c>
+      <c r="BT358" t="s">
+        <v>2661</v>
+      </c>
+      <c r="BU358" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV358" t="s">
+        <v>2662</v>
+      </c>
+      <c r="BW358" t="s">
+        <v>446</v>
+      </c>
+      <c r="BX358" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY358" s="1"/>
+      <c r="GQ358" s="1"/>
+      <c r="GR358" s="1"/>
+      <c r="GY358" s="1"/>
+      <c r="GZ358" s="1"/>
+      <c r="HA358" s="1"/>
+      <c r="HB358" s="1"/>
+      <c r="IQ358" s="1">
+        <v>894926154</v>
+      </c>
+      <c r="IR358" t="s">
+        <v>2663</v>
+      </c>
+      <c r="IS358" s="1">
+        <v>46311.290335648147</v>
+      </c>
+      <c r="IU358" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW358" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX358" t="s">
+        <v>2664</v>
+      </c>
+      <c r="IY358">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="359" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A359" s="1">
+        <v>46311.415315185193</v>
+      </c>
+      <c r="B359" s="1">
+        <v>46311.416434421299</v>
+      </c>
+      <c r="C359" s="1">
+        <v>46311</v>
+      </c>
+      <c r="D359" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E359" t="s">
+        <v>237</v>
+      </c>
+      <c r="F359" t="s">
+        <v>248</v>
+      </c>
+      <c r="G359" t="s">
+        <v>198</v>
+      </c>
+      <c r="H359" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS359" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT359" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU359" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV359" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW359" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX359" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY359" s="1"/>
+      <c r="GQ359" s="1"/>
+      <c r="GR359" s="1"/>
+      <c r="GY359" s="1"/>
+      <c r="GZ359" s="1"/>
+      <c r="HA359" s="1"/>
+      <c r="HB359" s="1"/>
+      <c r="HS359" t="s">
+        <v>2358</v>
+      </c>
+      <c r="HT359">
+        <v>1</v>
+      </c>
+      <c r="HU359">
+        <v>1</v>
+      </c>
+      <c r="IQ359" s="1">
+        <v>894927101</v>
+      </c>
+      <c r="IR359" t="s">
+        <v>2665</v>
+      </c>
+      <c r="IS359" s="1">
+        <v>46311.291446759264</v>
+      </c>
+      <c r="IU359" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW359" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX359" t="s">
+        <v>2666</v>
+      </c>
+      <c r="IY359">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="360" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A360" s="1">
+        <v>46311.416435312502</v>
+      </c>
+      <c r="B360" s="1">
+        <v>46311.417111493058</v>
+      </c>
+      <c r="C360" s="1">
+        <v>46311</v>
+      </c>
+      <c r="D360" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E360" t="s">
+        <v>237</v>
+      </c>
+      <c r="F360" t="s">
+        <v>237</v>
+      </c>
+      <c r="G360" t="s">
+        <v>198</v>
+      </c>
+      <c r="H360" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS360" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT360" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU360" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV360" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW360" t="s">
+        <v>389</v>
+      </c>
+      <c r="BX360" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY360" s="1"/>
+      <c r="GQ360" s="1"/>
+      <c r="GR360" s="1"/>
+      <c r="GY360" s="1"/>
+      <c r="GZ360" s="1"/>
+      <c r="HA360" s="1"/>
+      <c r="HB360" s="1"/>
+      <c r="HS360" t="s">
+        <v>2358</v>
+      </c>
+      <c r="HT360">
+        <v>0</v>
+      </c>
+      <c r="HU360">
+        <v>1</v>
+      </c>
+      <c r="IQ360" s="1">
+        <v>894927568</v>
+      </c>
+      <c r="IR360" t="s">
+        <v>2667</v>
+      </c>
+      <c r="IS360" s="1">
+        <v>46311.292129629634</v>
+      </c>
+      <c r="IU360" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW360" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX360" t="s">
+        <v>2668</v>
+      </c>
+      <c r="IY360">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="361" spans="1:259" x14ac:dyDescent="0.2">
+      <c r="A361" s="1">
+        <v>46311.417112523151</v>
+      </c>
+      <c r="B361" s="1">
+        <v>46311.418879282413</v>
+      </c>
+      <c r="C361" s="1">
+        <v>46311</v>
+      </c>
+      <c r="D361" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E361" t="s">
+        <v>237</v>
+      </c>
+      <c r="F361" t="s">
+        <v>2669</v>
+      </c>
+      <c r="G361" t="s">
+        <v>198</v>
+      </c>
+      <c r="H361" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS361" t="s">
+        <v>612</v>
+      </c>
+      <c r="BT361" t="s">
+        <v>612</v>
+      </c>
+      <c r="BU361" t="s">
+        <v>809</v>
+      </c>
+      <c r="BV361" t="s">
+        <v>612</v>
+      </c>
+      <c r="BW361" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX361" t="s">
+        <v>612</v>
+      </c>
+      <c r="EY361" s="1"/>
+      <c r="GQ361" s="1"/>
+      <c r="GR361" s="1"/>
+      <c r="GY361" s="1"/>
+      <c r="GZ361" s="1"/>
+      <c r="HA361" s="1"/>
+      <c r="HB361" s="1"/>
+      <c r="HS361" t="s">
+        <v>2358</v>
+      </c>
+      <c r="HT361">
+        <v>5</v>
+      </c>
+      <c r="HU361">
+        <v>5</v>
+      </c>
+      <c r="IQ361" s="1">
+        <v>894928897</v>
+      </c>
+      <c r="IR361" t="s">
+        <v>2670</v>
+      </c>
+      <c r="IS361" s="1">
+        <v>46311.293888888889</v>
+      </c>
+      <c r="IU361" t="s">
+        <v>207</v>
+      </c>
+      <c r="IW361" t="s">
+        <v>1801</v>
+      </c>
+      <c r="IX361" t="s">
+        <v>2671</v>
+      </c>
+      <c r="IY361">
+        <v>360</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
